--- a/Migration-Status-Report.xlsx
+++ b/Migration-Status-Report.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Remaining Work" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Full Detail'!$A$1:$D$317</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Remaining Work'!$A$1:$D$31</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Full Detail'!$A$1:$D$318</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Remaining Work'!$A$1:$D$32</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="608">
   <si>
     <t xml:space="preserve">Tony Greenberg site — Next.js migration status</t>
   </si>
@@ -904,6 +904,759 @@
     <t xml:space="preserve">Discourse comments (shown straight away like live, honeypot and a 5-per-10-minutes limit, Tony emailed for each), reactions, Rate this thinking, Micro-commitment: supabase/migrations/0002_blog_engagement.sql, server actions src/app/blog/[slug]/engagement-actions.ts; essays stay prebuilt (the blocks load after the page). Needs the 0002 script run in Supabase (Phase 2) and Resend for the emails; until then the forms say "isn't available just now".</t>
   </si>
   <si>
+    <t xml:space="preserve">/brewsoul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">welcome/landing gate (built, not yet pushed — pending local review), along with the shared foundation the rest of Phase 6 depends on. Ported BrewSoulLayout.tsx → app/brewsoul/layout.tsx + components/brewsoul/brewsoul-nav.tsx (BrewSoulNav/BrewSoulFooter), CategoryBadge.tsx → components/brewsoul/category-badge.tsx, brewsoul-config.ts → lib/content/brewsoul-config.ts, and BrewSoulDirectory.tsx's CATEGORIES/PAGE_CATEGORY_MAP data (not the page itself yet) → lib/content/brewsoul-directory.ts. Real architecture decision: BrewSoul is a self-contained sub-site with its own nav/footer/coffee-brown palette, same as legacy — but this app has one flat root layout with no route groups, so the main site's SiteHeader/SiteFooter needed to be suppressed for this one subtree without restructuring every existing route. Added components/site-chrome.tsx (SiteChrome, a small client wrapper checking pathname.startsWith("/brewsoul")) around both in app/layout.tsx — verified via literal &lt;header&gt;/&lt;footer&gt;/&lt;nav&gt; tag counts in real SSR HTML (not text search, which false-positives on Next dev mode's RSC debug payload) that /brewsoul gets zero main-site chrome and its own real nav+footer, while / still gets exactly one of each. Dropped TonyAvatarTrigger (FauxTony chatbot widget — Phase 10, no backend yet, same "don't fake it" call made elsewhere) from the nav. Ported BrewSoulWelcome.tsx → components/brewsoul/brewsoul-welcome-quiz.tsx (8-screen onboarding quiz, real identity-scoring logic, palate questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/first-sip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">onboarding intro (built, not yet pushed — pending local review). Ported "The First Sip Is a Vote" in full — the complete manifesto essay (5 sections, 3 pullquotes, the couplets block, the disclosure-demands grid), the 5-tool journey map, 6 related-essay links (real slugs, cross-checked against this session's already-verified corpus), the closing + sources, and the email capture. Built as a Server Component (all static except the email form) + components/brewsoul/next-steps.tsx (shared "what's next" CTA, itself a Server Component — legacy's hover effects were plain CSS-able, no JS state needed) + components/brewsoul/first-sip-email-capture.tsx (client island, mailto: fallback since no subscribe backend exists, same pattern as newsletter-popup.tsx). Dropped the canvas CoffeeDust decoration and the confirmed-dead hero photo (/api/img/brewsoul-orig_84eb4bc9.jpg, 404, same Manus proxy) — with no image left, the scroll-linked parallax that moved it went too. The 5 tool-card links (prescription/health/pairings/economics/compare) point at later Phase 6 routes not built yet — same forward-reference pattern as /find-my. Verified live: 200 OK, full essay text present, CategoryBadge correctly shows "Start Here" (from PAGE_CATEGORY_MAP), zero main-site chrome leaking in, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the real BrewSoul dashboard (distinct from /brewsoul's identity-quiz welcome gate and /brewsoul/first-sip's manifesto): hero + stats, Follow the Dollar teaser, Top QPR coffees (computed live via computeQPR), the 2025 crisis callout, New Drops, a Wall of Shame preview (SHAME_ENTRIES), the research-hub card grid, and a cyclable health-fact ticker (components/brewsoul/health-ticker.tsx, its own small client island so the rest of the page stays a Server Component). Canvas WarmParticles/ParallaxBg decorations and the dead hero photo (/api/img/brewsoul-orig_84eb4bc9.jpg, same confirmed-404 Manus proxy used elsewhere in Phase 6) dropped for CSS gradients. Stats use the real live BREWSOUL_COFFEES.length (107) in place of legacy's stale "103". Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/browse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coffee listing (components/brewsoul/browse-explorer.tsx), real filter/search over the full BREWSOUL_COFFEES catalog. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/coffee/[id]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coffee detail page (breadcrumb, QPR + tier header, quick stats, tasting notes, flavor-profile bars, the 4 intelligence scores, transparency/ethics data, buy links, competition wins, similar-coffees cross-links, journey CTAs), server-rendered with generateStaticParams over all 107 real coffees (this repo's bounded-dynamic-route convention, same as /blog/[slug]) instead of legacy's client-side useParams lookup. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/quiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matching quiz (built, not yet pushed — pending local review), along with the real data/engine foundation most of the rest of Phase 6 depends on. Ported lib/intelligence-engine/{types,scoring}.ts verbatim (generic scoring engine — QPR/availability/scarcity/wow/tier/freshness — reusable beyond BrewSoul) and the full coffee catalog (legacy's 3 files: brewsoul-coffees.ts + -expanded.ts + -expanded2.ts, merged at import time) → one lib/content/brewsoul-coffees.ts, extracted via tsx (not hand-typed — 107 real entries, ~6.5K lines). Caught a real stale count: legacy's own file header claimed "105" and its UI copy said "103", but the actual merged arrays contain 107 — this migration shows the live BREWSOUL_COFFEES.length everywhere instead of a repeated hardcoded number. Ported JourneyBar.tsx (components/brewsoul/journey-bar.tsx) — the fixed bottom "what's next" bar shown on every BrewSoul content page except the identity quiz — and retrofitted it onto /brewsoul/first-sip too (built before JourneyBar existed). Built components/brewsoul/brewsoul-quiz.tsx: real 7-question taste quiz scored against each coffee's real flavorProfile via the real scoring engine, ranking the full catalog by match. Legacy's useMarkVisited was renamed to markVisited (it's a plain localStorage write, not a hook — its old use-prefixed name tripped React's rules-of-hooks lint when called from inside a useEffect). Dropped the canvas WarmParticles decoration and the dead hero photo (same confirmed-404 Manus proxy,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/wall-of-shame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">content page. Real 13 entries (brand/category/evidence/severity/response) from SHAME_ENTRIES, unchanged. Category filter buttons extracted into components/brewsoul/shame-explorer.tsx (the only interactive piece) so the page itself stays a Server Component. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/follow-the-dollar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supply-chain essay. Real DOLLAR_BREAKDOWNS segment bars (farmer/exporter/importer/roaster/retailer %, real commentary), unchanged. The farmer-segment bar's data-driven color (green/gold/red by threshold) is a small known set of variants — precomposed as 3 literal Tailwind classes rather than an inline style background, per this repo's dynamic-class rule; only the genuinely per-item width stays as style. Fully static, Server Component. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/farms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sourcing content ("Farm Passports"). Real FARMS entries (country/region/producer/altitude/story/varieties/certifications), unchanged. Fully static. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/mold-free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mycotoxin content. Real verified/claims/untested split computed live over the full BREWSOUL_COFFEES catalog by moldTestStatus. Fully static. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/experiences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">experiential content ("Experience Map"). Real EXPERIENCES entries (farm tours, cafés, cupping labs, roastery visits), unchanged. Country filter buttons extracted into components/brewsoul/experiences-explorer.tsx, same split-out-the-interactive-bit pattern as wall-of-shame. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">health deep-dive, ported from BrewSoulHealthFull.tsx (the file legacy's own router actually uses for this route — BrewSoulContent.tsx's same-named BrewSoulHealth export is real but genuinely dead/unrouted code in legacy, shadowed by this one). Real 8 longevity findings with real citations/participant counts, 7 real risks with severity ratings, CYP1A2 caffeine-metabolism genetics, a 6-step chronobiology timing schedule, 8 real bioactive compounds, 3 real mycotoxin threats, and a 3-step "simplification protocol," all ported unchanged and verbatim. Dead Manus hero image dropped for a CSS gradient. Legacy's own redundant BrewSoulLayout wrapper dropped — app/brewsoul/layout.tsx already wraps every route. The two real interactive pieces (show-all-risks toggle, per-compound click-to-expand) split into components/brewsoul/health-{risks,compounds}.tsx client islands so the rest stays a Server Component. Legacy's bespoke earthy "science" palette (soil/clay/sage/moss — distinct from the rest of BrewSoul's amber/gold commercial palette) kept as a deliberate one-off sub-identity for this one page, same reasoning as /attention-theft's own "crusade" palette elsewhere in this migration. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/varieties</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference: varieties. Real VARIETIES encyclopedia entries (species/origin/genetics/cup profile/yield/disease resistance), unchanged. Search extracted into components/brewsoul/varieties-explorer.tsx. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/processing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference: processing. Real PROCESSING_METHODS entries (description/flavor impact/complexity/controversy), unchanged. Fully static. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/roasters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference: roaster directory. Real ROASTERS entries (philosophy/quality/transparency/farmer-equity scores), unchanged. Search + tier filter extracted into components/brewsoul/roasters-explorer.tsx. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/glossary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference: glossary. Real GLOSSARY terms, unchanged. Search + alphabetical grouping extracted into components/brewsoul/glossary-explorer.tsx. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/pairings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference: pairings. Real PAIRINGS (food/drink pairings by origin) and 3 real curated FLIGHTS (each linking to real coffees in the catalog), unchanged. Fully static. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference: economics. Real live-computed stats (coffee/origin/roaster/variety counts, average price, average farmer share via DOLLAR_BREAKDOWNS), a real price-distribution histogram, and a real top-origins ranking — all computed directly from BREWSOUL_COFFEES at render time, unchanged. Fully static. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/compare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tool: compare coffees. Real side-by-side comparison of up to 4 coffees across origin/producer/variety/process/price/cupping and the 4 intelligence scores (QPR/availability/wow/overall), unchanged. Interactivity in components/brewsoul/compare-explorer.tsx. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/blend-builder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tool: blend builder. Real combine-up-to-5-coffees ratio calculator with weighted-average QPR/Wow/Overall scores via range sliders, unchanged (never persisted anywhere in legacy either — a pure in-session calculator). Interactivity in components/brewsoul/blend-builder-explorer.tsx. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/drops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tool: product drops ("Latest Drops"). Real top-12-by-overall-score coffees. No client-side state at all (legacy's own useMemo had no changing dependencies — a pure derived list), so this ships as a plain Server Component. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/collection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tool: personal collection tracker ("My Collection"). Real save/toggle-to-collection behavior, unchanged. Real bug found and fixed: legacy read localStorage directly inside a useState initializer — unsafe during SSR, same hydration-mismatch class already fixed in journey-bar.tsx/journey-tracker.tsx — rebuilt around a module-level external store fed through useSyncExternalStore in components/brewsoul/collection-explorer.tsx. Also found and fixed: the already-ported brewsoul-directory.ts listed this page's path as /brewsoul/my-coffees — a real dead link in legacy's own directory (legacy's actual router only ever served this at /brewsoul/collection, /brewsoul/my-coffees never existed) — corrected to the real path. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/submit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tool: submit a coffee ("Submit or Appeal"). Real submit-a-coffee / appeal-a-score form, unchanged in structure. Real bug found and fixed: legacy's own comment admitted "In production this would POST to a tRPC endpoint" but in the meantime wrote the submission to localStorage and showed "Received. We'll review your submission" regardless — actively misleading, since nobody would ever see a localStorage-only write. Replaced with a real mailto: fallback pre-filled with the form fields, same honest-degradation pattern as first-sip-email-capture.tsx — no fake success state. Verified live: 200 OK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/prescription</t>
+  </si>
+  <si>
+    <t xml:space="preserve">personalized "prescription", ported from BrewSoulPrescriptionFull.tsx (the file legacy's router actually uses — BrewSoulTools.tsx's same-named export is dead/unrouted, same shadowed-file trap as /brewsoul/health). Real 5-step questionnaire (genetics/timing/health/flavor/budget) generating a real, deterministic prescription (generatePrescription — real roast/cup-count/brand/pricing/warning logic), all ported unchanged and verbatim. Legacy's trpc.coffeePrescription.generate AI-enhancement mutation doesn't exist in this migration — dropped along with its "AI ANALYSIS LOADING..." block, which would otherwise spin forever and never resolve; the real prescription itself never depended on that call, it's already fully computed client-side. Same bespoke earthy "science" palette as /brewsoul/health kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/chains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Top 100 Coffee Chains" ranking (not supply-chain visualization — that's /brewsoul/economics//brewsoul/follow-the-dollar; this is chain rankings). Real 100-chain dataset extracted from legacy's computed CHAIN_RANKINGS export (5 real weighted dimensions → aggregate → S-F tier) via a one-off tsx script (same approach as brewsoul-coffees.ts) into lib/content/brewsoul-chains.ts, with a new ChainEntry type added to intelligence-engine/types.ts. Real tier/type filters, search, and per-chain expand, unchanged, extracted into components/brewsoul/chains-explorer.tsx. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/biodynamic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biodynamic content. The complete real census of Demeter-certified biodynamic coffee: 3 real source farms, 6 real roasters/brands with real product tables and pricing, real nutritional-science compounds, a real cost calculator, and a real impact/tokenization section, all ported unchanged and verbatim. Dead Manus hero image dropped for a CSS gradient. The 3 genuinely interactive pieces (click-to-expand farms/roasters, cups-per-day cost slider) split into components/brewsoul/{biodynamic-farms,biodynamic-roasters,cost-calculator}.tsx client islands so the rest stays a Server Component. Same bespoke earthy "science" palette as /brewsoul/health and /brewsoul/prescription kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/decaf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decaf content ("Paint Stripper or Pure Water?"). Real 3-process breakdown (methylene chloride/Swiss Water/supercritical CO₂), 13 real clean-decaf brands ("Hall of Fame"), 10 real methylene-chloride brands ("Wall of Shame," with real Clean Label Project lawsuit citations), a real carbon footprint comparison, real decaf health science, and a real price-comparison table, all ported unchanged and verbatim. Legacy's manual document.title/&lt;meta keywords&gt; mutation in a useEffect (a real anti-pattern — Next's generateMetadata already owns the head) dropped for the real metadata export. Real bug found and fixed: the 13-brand FAME dataset was initially exported from the "use client" decaf-fame.tsx component file and imported into the Server Component page for its price-comparison table — non-component exports from a client module aren't available across the RSC boundary, which threw FAME is not iterable at runtime (only caught by live verification, not typecheck/lint). Moved the data to a plain lib/content/brewsoul-decaf.ts module instead. The 2 genuinely interactive pieces (click-to-expand Hall of Fame, reveal-toggle Wall of Shame) split into components/brewsoul/decaf-{fame,shame}.tsx client islands. Same bespoke earthy "science" palette as the other /brewsoul deep-dive pages kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/esoteric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rare-coffee content ("Esoteric Coffee Index"). Real 9-coffee index across 2 tiers (Panama Geisha, Yemen Mokha, Liberica, Eugenioides, Wush Wush, Sidra, Pink Bourbon, Bourbon Aji, Sudan Rume) with real tasting notes, rarity scores, and real named buy sources, plus a real acquisition-priority list and explorer scorecard, all ported unchanged and verbatim. Real content gap found, not fixed: legacy's own "Top 10 Acquisition Priority" list and scorecard table both reference "Laurina" as a 10th entry, but no coffee card for it exists anywhere in the source dataset — ported as-is rather than inventing card content that was never written. Zero client-side state anywhere in this page (only CSS-able hover) — ships entirely as a Server Component. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/cities + /brewsoul/cities/[slug]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">city directory + detail ("City Intelligence Module"). Real 25-city leaderboard (name/state/grade/score/tagline/verdict/live stats), a real 7-dimension scoring methodology, and real national + universal/nuanced chain report cards, all ported unchanged and verbatim into lib/content/brewsoul-cities.ts. Real data-completeness note, not a bug: legacy's own comment admits only Portland has full shop-by-shop data (25 real best + 5 real worst shops with real blurbs/scores/order-this/skip-this) — the other 24 cities have real city-level stats but empty shop/chain/bridge-drink/non-coffee arrays; legacy's own UI already handles this honestly (a real "Full data coming soon" state on both the card and detail page, not fake data) — preserved exactly, verified for both Portland (full tabs) and Seattle (coming-soon state). Grade filter, methodology modal, and chain-toggle interactivity in components/brewsoul/cities-explorer.tsx; per-city tab switching and per-shop expand in components/brewsoul/city-detail-tabs.tsx. Detail route uses generateStaticParams over all 25 real slugs. Scroll-linked parallax and floating-particle backgrounds dropped, same decoration call made throughout this migration. Real image-hosting gap flagged, not silently worked around: the 25 city hero photos are real, live Unsplash URLs (not a dead Manus proxy) but aren't yet uploaded to Sanity per this repo's own image convention — added images.unsplash.com to next.config.ts's remotePatterns as an interim measure rather th</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real master page index ("Everything Inside BrewSoul," not a roaster directory — that's /brewsoul/roasters). Real 6 categories with real page descriptions/icons, unchanged; the underlying data already lived in lib/content/brewsoul-directory.ts (built earlier this phase to power CategoryBadge) — this route is where it finally becomes a real browsable page. Category filter extracted into components/brewsoul/directory-explorer.tsx. Fixed the stale "Browse All 103 Coffees" label (real count is 107) by dropping the hardcoded number from the shared data module — benefits every other consumer of that module too. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/brewsoul/guest + /brewsoul/guest/shanita-nicholas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">guest series index + profile ("Tony G Guest Series"). Real single guest entry (Shanita Nicholas — real headline/teaser/tags) on the index, and the real 10-question interview on the detail page (Fair Trade economics, roasting mythology, the C Market, regenerative vs. sustainable, origin-roasting economics vs. Fair Trade, blockchain traceability, pre-harvest financing — real substantive answers with real citations), all ported unchanged and verbatim into components/brewsoul/shanita-interview.tsx. Legacy's guest photo (/api/img/brewsoul-orig_84eb4bc9.jpg) was the same dead Manus proxy confirmed 404 throughout this migration — dropped for a plain initial avatar on both pages rather than a broken headshot. Per-question expand/collapse, "Expand/Collapse All," and the real Twitter/LinkedIn/copy-link share row are genuinely interactive, split into client islands. Verified live: 200 OK on both, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shared: port BrewSoulLayout, CategoryBadge, JourneyBar, NextSteps as Next.js layout/components</t>
+  </si>
+  <si>
+    <t xml:space="preserve">app/brewsoul/layout.tsx + components/brewsoul/{brewsoul-nav,category-badge,journey-bar,next-steps}.tsx, all built and reused by every /brewsoul/* route above.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kava shared foundation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">app/kava/layout.tsx + components/kava/kava-nav.tsx (KavaNav/KavaFooter, 10 real nav items) + components/kava/kava-ui.tsx (KavaHero/KavaSection/KavaSectionTitle/KavaCard/KavaBadge/KavaDivider/KavaDisclaimer, converted from legacy inline style={} to Tailwind + new --kava-* tokens in globals.css). Added /kava to site-chrome.tsx's SUPPRESSED_PREFIXES (self-contained sub-site, same pattern as BrewSoul and /attention-theft). Real dead link fixed: legacy nav pointed at /pri, which legacy's own App.tsx never routed (only /psychedelic-readiness-index exists) — corrected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/kava (home)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 module cards, "Threshold Doctrine," "Sacred Masculine Triad" (Mezcal/Kava/Peyote), 4 market stats, all ported unchanged. Verified live: 200 OK, exactly 1 header/1 footer (chrome suppression confirmed), typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/kava/origins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real migration timeline (6 Pacific nations, ~3000 BCE–1000 CE), real 6-island selector (Vanuatu/Fiji/Tonga/Samoa/Hawaii/Pohnpei, each with real facts/ceremony/cultivar/safety content), and the real Noble vs. Tudei safety comparison, all ported unchanged and verbatim. Island-selector interactivity in components/kava/origins-explorer.tsx. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/kava/interactions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real 24-substance drug interaction database (real severity ratings across an 11-value scale, real pharmacological mechanisms, real PRI protocol guidance) and real 5-enzyme CYP450 inhibition profile, ported unchanged and verbatim. Search + severity-filter interactivity in components/kava/interactions-explorer.tsx, using a precomposed SEVERITY_CONFIG class lookup (not string-built classes — same Tailwind static-scanner rule enforced elsewhere this migration). Legacy's unused Download icon import (dead code, no export feature attached to it) not ported. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/kava/science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real 6 major kavalactones (real receptor mechanisms, real PRI relevance) and real 11-item combined pharmacological profile, ported unchanged into lib/content/kava-science.ts. RSC-boundary bug caught proactively before shipping: initially drafted KAVALACTONES as an export of the "use client" chemotype-decoder.tsx, which would have thrown the same TypeError: X is not iterable already hit once this migration on /brewsoul/decaf when the Server Component page tried to import it — moved to the plain data module before ever running it. Chemotype decoder tool (enter e.g. 4-2-6-5-3-1, see dominant kavalactones) kept as the real interactive client island. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/kava/assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real 5-domain, 20-question PRI readiness assessment (somatic/psychological/relational/cultural/integration), real per-domain point weights, and real 4-band recommendation scoring (CLEARED/CONDITIONAL/DEFER/NOT READY), all ported unchanged into components/kava/assessment-quiz.tsx. Fully stateful (domain navigation, per-question answers, results view), so kept as a single client island per this migration's established pattern for multi-step assessments. Domain and recommendation accent colors (5 + 4 distinct hexes, none matching the --kava-* brand palette) precomposed into literal DOMAIN_STYLES/RECOMMENDATION_STYLES lookup objects rather than style={}, avoiding the dynamic-class bug already caught twice this migration (chains-explorer.tsx, biodynamic/page.tsx). Real backend gap, handled honestly: legacy's AssessmentResultActions took sessionId/serialized-answers props feeding a trpc.assessments.submit mutation this migration never built — used the already-simplified, print-only AssessmentResultActions (components/assessments/result-actions.tsx, built during Phase 9) instead of reproducing a submit call with no backend. Verified live: 200 OK, real domain/question content confirmed in rendered HTML, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/kava/hawaii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real ICE/meth crisis statistics (Quest Diagnostics 410% figure, Hawaii DOH conviction rates, law enforcement seizure data), real dual crisis/revival timeline (1985–present), the real (explicitly-labeled hypothesis, not proven) pharmacological alignment table, and real recovery resource listings, all ported unchanged and verbatim. Fully static, no client island needed. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/kava/myths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real 7-myth evidence review (2002/2014 European kava ban and reversal, WHO findings, CYP2D6 metabolism differences by population, chemotype/preparation distinctions) and the real closing takeaway, ported unchanged. Expand/collapse interactivity in components/kava/myths-explorer.tsx, verdict colors (3-value enum) precomposed into a literal VERDICT_CLASS lookup. Extended shared KavaCard (kava-ui.tsx) with an optional onClick prop to support this — first Kava page needing a clickable card. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/kava/caffeine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real CYP1A2 inhibition mechanism (56%, the same pathway grapefruit juice uses on medications), real caffeine cutoff protocol, and the real kava-vs-coffee comparison table, ported unchanged. Fully static, no client island needed. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/kava/products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real 5-category product index (ceremonial powder, fresh frozen, RTD beverages, supplements, kava bars) with real named vendors/cultivars/chemotypes/pricing/PRI ratings and real outbound buy links (all live vendor domains, not Manus proxies — no image assets on this page to check), ported unchanged into components/kava/products-explorer.tsx. Category-tab interactivity kept as the client island. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/kava/certification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real 12-module, 80-hour facilitator curriculum, real 3-tier certification structure (Practitioner/Threshold Facilitator/Master Facilitator), and real prerequisites list, ported unchanged. Fully static, no client island needed; legacy's wouter cross-links replaced with next/link. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRI shared data: lib/content/pri-data.ts (copied verbatim from legacy pri/data.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real 39-medicine pharmacopoeia, 50+ questions across 6 domains, MAO-B interaction matrix, medication interaction guide, crisis/integration resources, pathway questions), lib/content/pri-safety-data.ts (verbatim safety data merge source), lib/content/pri-medicine-images.ts (verbatim real CloudFront hero-image map, all spot-checked 200 OK — RampRate's own CDN, already whitelisted, not Manus), lib/content/pri-shared.ts (the real scoring engine — computeScores/READINESS_LEVELS/getMedicineWithSafety — extracted to a plain module per the RSC-boundary lesson from /brewsoul/decaf and /kava/science). Added --pri-* CSS custom properties to globals.css (this subsystem's own purple/parchment/near-black palette, same pattern as --kava-/--crusade-) since Phase 7's PRI section spans 9 more routes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/psychedelic-readiness-index (core tool)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the real hero, 39-medicine grid with compare/save/bookmark tooling, MAO-B interaction matrix, medication interaction guide, crisis resources, the real 5-state assessment flow (philosophy intro → readiness quiz → pathway &amp; access questions → legal disclaimer gate → results), medicine detail modal (overview/safety/correction tabs), testimonials, and ImpactSoul cross-promotion, all ported unchanged and verbatim into components/pri/psychedelic-readiness-index.tsx plus supporting client islands (disclaimer-gate.tsx, medicine-modal.tsx, safety-section.tsx, correction-form.tsx, share-bar.tsx, cinematic-band.tsx). Kept as one client island — a single state machine drives which section renders, same call made for other large multi-step assessments this migration. Real hero/section photography (8 CloudFront images) kept via next/image; legacy's purely decorative glitch-scanline overlay divs and CSS shimmer/glow @keyframes dropped (no framer-motion — CONTRIBUTING.md rule 5 — and "decoration not worth the cost," same call made throughout this migration).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRI: /peyote-mescaline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MescalineDeepDive, real receptor pharmacology table, the real "Latuda Mirror" same-target-opposite-action comparison, real clinical outcomes (Agin-Liebes et al. 2021, n=452), the real 16-row pharma-to-plant alternatives table, real supplement protocol (pre/day-of/post-integration), real mescaline-specific PRI dimension scores, the real medicine-selector comparison table, and real sources, all ported unchanged and verbatim into lib/content/pri-mescaline-module.ts (copied verbatim) + app/peyote-mescaline/page.tsx. Fully static except the pharma-table expand toggle, extracted into components/pri/pharma-table.tsx; shared PriSection/PriEyebrow wrapper (components/pri/pri-section.tsx) introduced here for reuse by the remaining PRI deep-dive modules. All 8 real section photos (CloudFront) spot-checked live before use; legacy's purely decorative glitch-scanline overlays dropped. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRI: /iboga-ibogaine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IbogaDeepDive, "The Plant vs The Isolate": real alkaloid-profile comparison, real receptor pharmacology, real head-to-head iboga-vs-ibogaine table, real clinical outcomes (Mash/Noller/Schenberg/Brown &amp; Alper/Cherian/Williams — including the 2024 Stanford Nature Medicine SOF-veteran data and the 2026 19,071-patient safety analysis), real pharma-to-plant alternatives, real supplement protocol, real dimension thresholds, real medicine selector, Tony's real first-hand account of sitting ibogaine at The Mission Within, real hard-stop contraindications, a real 9-facility directory (with the 2 facilities legacy explicitly removed and why), real Nagoya Protocol / extractive-capitalism argument, real 2026 US legal-status rundown, the embedded Iboga Compass v2 documentation section (components/pri/iboga-compass-section.tsx, its own client island for the question-group toggles), and real sources — all ported unchanged and verbatim into lib/content/pri-iboga-module.ts + lib/content/pri-iboga-compass-data.ts (both copied verbatim) + app/iboga-ibogaine/page.tsx. Fully static except the pharma-table expand toggle (components/pri/iboga-pharma-table.tsx) and the compass section's toggles; reused the shared PriSection/PriEyebrow wrapper from the mescaline module. All 5 real hero/section photos (CloudFront) spot-checked live before use. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRI: /iboga-compass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IbogaCompassAssessment, the real interactive 28-question / 7-section compass (outcome/medical/approach/logistics/geography/personal/aftercare), the real drag-or-arrow priority-rank step (top dimension ×2.0, bottom ×0.5), the real facility-scoring engine, and the real results view (matched facilities with real "why this matched" reasoning and real elimination reasons), all ported unchanged and verbatim. lib/content/pri-iboga-compass-engine.ts (real scoring logic — weight deltas, hard filters, substance bonuses, priority-rank application, facility scoring) and lib/content/pri-iboga-facility-data.ts (real facility directory + substance-bonus data) both copied verbatim from legacy rather than hand-transcribed, given this is the actual matching algorithm — correctness matters more here than anywhere else in this migration. Uses this site's own brand-gold/foreground/muted-foreground design tokens rather than the pri-* palette — legacy's own hex here (#8B6914) is an exact match for brand-gold, confirming this one page always used the main site identity, not a PRI-specific one. Real backend gap handled honestly: legacy's lead-capture gate posted a rich structured payload (question-by-question answers, top facility matches, primary goal, budget range) to trpc.assessments.submit (no backend built for this migration) — replaced with a mailto: to Tony carrying the same structured summary, same pattern used throughout this migration; the meaningless "Submitting..." pending state and its e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRI: /pri-calibration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forced-rank calibration study, the real Bradley-Terry pairwise-comparison model (all 15 unique pairs of the 6 PRI dimensions), the real drag-or-arrow full ranking step, real methodology copy (acquiescence-bias explanation, the 4 headline validation stats), and the real Monte Carlo validation metrics (lib/content/pri-efficacy-data.json, copied verbatim from legacy — also feeds /pri-efficacy below), all ported unchanged into components/pri/calibration-assessment.tsx. Real backend gap, handled honestly: legacy's "Contribute to Research?" opt-in phase posted to trpc.priCalibration.submit (no backend built for this migration), and the results view's "Community Data" section read a live trpc.priCalibration.stats aggregate query showing other users' scores — neither has an honest backend-free equivalent (a cross-user aggregate can't be faked locally, and a research opt-in toggle with nothing behind it would be dishonest UI, the same call already made dropping the main PRI results page's inert research-pool checkbox). Both dropped; the flow goes straight from ranking to results. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRI: /pri-efficacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">psychometric validation dashboard, the real Monte Carlo simulation results (10,000 synthetic respondents), real classification-accuracy comparison, real dimension-priority distribution (the real first-dimension-inflation finding), real test-retest reliability and entropy metrics, and the real methodology writeup, all ported unchanged into app/pri-efficacy/page.tsx, reading the same lib/content/pri-efficacy-data.json also used by /pri-calibration. Real backend gap, handled honestly: legacy's "Live Calibrations" tab read a live trpc.priCalibration.stats query — since /pri-calibration's own submit call was already dropped (no backend, see that page's port note), this tab would permanently render "0 total calibrations, no data yet," a dead feature masquerading as a live one. Dropped entirely rather than ship a perpetually-empty tab; only the real, fully-populated Simulation view ships — which also means this page has no state left at all, so it's a plain Server Component now instead of a client one. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRI: /pri-research Built 2026-10-06 behind the login: admins are the emails in ADMIN_EMAILS; everyone else gets live's "Access Denied"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totals, anonymized opt-in table, admin-only CSV export (/pri-research/export). /pri-calibration regained legacy's "Contribute to Research?" step and now saves every calibration anonymously to pri_calibrations (opt-ins flagged). Was: — Deferred, not skipped (access-model question resolved by inspection). Read the real legacy source: this is a genuine admin-only dashboard (useAuth() gated to role === "admin") showing trpc.priCalibration.researchData — the same calibration-submission backend already confirmed absent and intentionally not built for /pri-calibration and /pri-efficacy (see their port notes). No admin-auth system exists anywhere in this Next.js migration yet either. So this isn't just an access-control decision — even fully wired up, the page would have zero real data to show, forever. Not worth building an admin dashboard against a backend this migration has twice already decided not to build. Added to "Explicitly deferred" below alongside the other admin dashboards; revisit only if/when both a real admin-auth system and a real calibration-submission backend exist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRI: /facilitator-index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"The Facilitator Index: Know Who You Go With," the real 15-question quick-intake archetype quiz (real Bradley-Terry-style axis derivation, fully client-computed via deriveArchetype()), the real 108-item, 12-band (plus Band 0) practitioner self-assessment instrument, and the real methodology prose (rationale, code/tier system, data-handling policy, Reciprocity Gate, Corroboration token system), all ported unchanged and verbatim into lib/content/facilitator-index-data.ts (single authoritative content source) + components/facilitator/* + app/facilitator-index/page.tsx. Real content-drift bug found and fixed: legacy shipped two divergent copies of the same "108 items" — the on-page JSX and a separate printFacilitatorQuestions() print/PDF export using an older, different set of item numbers and band groupings (missing the on-page "Twenty-Five Traditions and Protocols" band entirely) — the print export was never updated when the on-page instrument was revised. Used the on-page version (the one actually shown to visitors) as the single source of truth and rebuilt the print export to generate from that same data, so the two can never diverge again. Real fake-data found and dropped: legacy's PeerStats component's own comment admits its numbers ("163 practitioners mapped so far," etc.) are "seeded, realistic-feeling" — fabricated, not real — dropped entirely, same principle as BrewSoul's stale "reads" counts; UsageCounter's hardcoded 160-practitioner fallback (shown forever since no ba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port shared safety/medicine data modules (safety-data.ts, medicine-images.ts) as typed .ts content in the new codebase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">done as part of the main PRI page above (lib/content/pri-safety-data.ts, lib/content/pri-medicine-images.ts, both copied verbatim).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/attention-theft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">consolidated mega-page. Real content ported in full across all 9 sections (hero, The Sacred, The Heresy economics data + full breakdown table + sources, the 10 Weapons, Legal Arsenal w/ filter + letter template, AI Blocker Finder quiz, Report a Spammer, closing vow + related reading) — AttentionTheft.tsx used as the single source, the 5 pre-consolidation sub-pages not resurrected (they never existed in this codebase anyway). Section "glamour" photography is real, live imagery on RampRate's own CloudFront (already whitelisted in next.config.ts as a non-Manus, permanent host — confirmed all 7 URLs 200 before using them), rendered via next/image. Real backend gap found and handled honestly: legacy's Wall of Shame (a live trpc.spam.wallOfShame ranked list) and the Report form's trpc.spam.submit both depended on a spam-tracking backend that this migration explicitly defers (see "Explicitly deferred" list below: "/youve-been-reported, /spamtoast, admin spam tooling") — rather than fake a public database with no real data behind it, the report form now composes a mailto: to Tony (same honest non-fake-success pattern as newsletter-popup.tsx), and the ranked Wall of Shame list isn't reproduced. Two simplifications matching precedent set elsewhere in this migration: legacy's "Fraunces" serif (loaded for this one page only) was dropped for font-heading (Playfair Display, already loaded — same call made on /akbar), and the glitch/VHS/ember-particle/shattered-glass decoration layer was dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy anchor redirects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/attention-theft/economics, /blocker-finder, /legal, /weapons, /report → /attention-theft#&lt;anchor&gt; via next.config.ts redirects(). Verified live: all return real 308s to the correct anchor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port ManifestoLayout scroll-tracking wrapper behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">components/manifesto/manifesto-nav.tsx tracks which section is in view on scroll and highlights the matching nav pill (desktop + mobile), real behavior kept per this line item rather than simplified away.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HumanOS section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/humanos, /humanos/philosophy, /humanos/ecosystem, /humanos/resources, /humanos/connect, /humanos/path-to-here, ported from _legacy-manus-app/client/src/pages/HumanOS.tsx + humanos/*.tsx. The top-level HumanOS.tsx (an iframe embed of an external manus.space site) turned out to be dead code, never wired into legacy's router — the real, routed implementation is HumanosHome/HumanosPhilosophy/HumanosEcosystem/HumanosResources/HumanosConnect/HumanosPathToHere behind HumanosLayout, which is what got ported, with its own nested layout.tsx (route now added to site-chrome.tsx's SUPPRESSED_PREFIXES so the main SiteHeader/SiteFooter don't double up around HumanOS's own nav/footer). Real content in full: the Maximizer-vs-Satisficer framework and "Boiling the Human"/"Maximizer Trap"/"Conscious Satisficer" philosophy sections, the full ecosystem roster (1 mentor, 8 advisors, 3 partners, 29 clients), all 4 transformation playbooks + 3 daily-practice protocols + 8-book reading list, all 4 connect channels, and the 6-entry "Path to Here" timeline (2010 H+ Summit through 2025). Real bugs fixed: every "Take the Diagnostic" CTA site-wide pointed at /assessment, an 8-question Maximizer/Satisficer quiz that was never actually built anywhere (legacy's real /assessment and /assessments routes are two different, unrelated quiz sets) — redirected to /humanos/philosophy, which delivers the actual promised content; Connect's "Read the Living Declaration" pointed at /manifesto, a dead redirect stub in le</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/find-your-me (+ /find-my-me, /discover)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Find My — To Find Your We," the ecosystem hub assessment and by far the largest page in Phase 9. Real 5 NLP-driven questions, 6 dimensions (relationships/purpose/body/truth/tribe/consciousness), and 6 real archetypes (each with a real description, real blog article links, real satellite-site links, real "go deeper" forward-references, and a real share text) ported unchanged and verbatim into a new lib/content/find-your-me.ts data module (kept separate from the component given the file's exceptional size, same pattern as brewsoul-directory.ts). All 17 unique blog article slugs referenced across the 6 archetypes were individually verified live (200 OK) against this migration's real Sanity blog before porting — zero dead article links. Real accuracy fix: legacy's "Full Ecosystem Directory" (26 items across 5 categories, with a real LIVE/COMING pill UI already built for exactly this purpose) marked everything "live," including several routes that don't exist anywhere in this migration yet (/find-my, /the-mirror, /assessments/dharma-finder, /assessments/consciousness-scale, /assessments/grant-study, /flow-circuit) — corrected each item's status to this app's actual current build state rather than shipping false LIVE labels on what would be 404s. Real completeness fix: added Find Your Peptide and Find Your Sexuality to the directory (Body &amp; Temple and Love &amp; Belonging) — both are real, fully-built assessments elsewhere in this migration that didn't exist yet when legacy was writte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/find-your-therapy (+ /find-my-therapy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real 25 questions across 6 dimensions (Cognitive/Somatic/Relational/Depth-Unconscious/Altered States/Integrative), 6 real therapeutic modalities (each with a real description, "how it works," best-for/not-ideal-for lists, real named pioneers, and real book/directory resources), and the real archetype-matching logic (highest-scoring dimension wins) ported unchanged and verbatim. Three real stale-count bugs found and fixed: legacy's own file-header comment claimed "10 questions," its AssessmentIntro stats prop claimed 20 — neither matches the real 25-item array (the scoring code's own maxPossible = 30 // rough max per dimension with 25 questions comment confirms 25 is correct) — replaced both with live QUESTIONS.length. Real dead-link bug fixed: legacy's "Journey Continues" grid linked "Find Your Spirit"/"Find Your Religion" to external findmyassess-9eekxcob.manus.space stub URLs (dead Manus domain) despite this migration already having real, fully-built internal pages at /find-your-spirit and /find-your-religion — repointed to the real internal routes, and corrected Religion's stale "15 Questions" badge to the real 20. Real accent-color inconsistency fixed: legacy passed accentColor="#7B1FA2" only to the landing screen, then hardcoded brand-gold everywhere on the results screen instead — threaded one ACCENT constant through intro/radar/result-actions consistently, matching every other assessment in this migration. The "Also Worth Exploring" related-modality cards were dropped </t>
+  </si>
+  <si>
+    <t xml:space="preserve">/find-your-sake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real 20 questions across 5 dimensions (Palate/Ritual/Terroir/Philosophy/Season) and the real 5 sake profiles (each with real Japanese name, tasting notes, food pairings, serving temperature, named producers with region/note, and further-reading resources) ported unchanged and verbatim. Legacy's own AssessmentIntro stats prop claimed "15 questions, 6 dimensions" — didn't match the real 20/5 implementation — replaced with live QUESTIONS.length/DIMENSIONS.length counts, same fix pattern already applied on /find-your-attachment-style and /find-your-sexuality. Two real bugs found and fixed: (1) legacy's "Journey Continues" list read "Find Myzcal" — a literal typo for "Find Your Mezcal" — corrected. (2) legacy's JSX rendered &lt;WhatsNext /&gt; (a full page section) nested inside the small "Retake the Tasting" &lt;button&gt; element — moved to a proper top-level section, same class of nested-interactive-content bug already fixed on /find-your-religion. The dark GlassPanel treatment (near-black translucent cards with light cream text, sitting on the page's own light parchment ThemedBackground) was kept as a real, intentional design choice rather than "fixed" to this migration's usual light-card convention — unlike the light-text-directly-on-light-background contrast bugs found on Style/Sexuality/Peptide/Religion, the text here sits inside its own correctly-contrasted dark card. SacredGeometryBg's canvas-based floating rice-grain particles dropped (same decoration-not-worth-the-JS-cost call made</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/find-your-spirit (+ /find-my-spirit), along with a shared PDF-export component the rest of Phase 9 can reuse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real 35 questions, 10 dimensions, and the 6 real spiritual traditions (each with real description/practices/key texts/figures/modern expressions/growth edge) ported unchanged and verbatim — legacy's own file-header comment claimed "12 archetypes," but only 6 TRADITIONS actually exist in the code; ported the real 6, not the stale doc comment. The real weighted tradition-matching logic (top 3 dimensions per tradition, weighted 3/2/1) is unchanged. Ported components/assessments/result-actions.tsx from legacy's AssessmentResultActions — kept only the real, backend-free "Download PDF" action (browser print); the "Send to Tony"/"Keep Private" buttons posted to an unbuilt trpc.assessments.submit and weren't reproduced, same honest-degradation pattern used throughout this migration. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/find-your-religion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real 20 questions across 8 dimensions, 8 real spiritual/philosophical archetypes (each with real description/practices/key texts/figures/resonant traditions/growth-edge tensions), and the real scoring/matching logic ported unchanged and verbatim. Real bug found and fixed: legacy's own JSX rendered &lt;AssessmentResultActions&gt; nested inside the "Retake Assessment" &lt;button&gt; element — a button inside a button, invalid HTML — fixed by rendering it as a sibling instead, same fix pattern already applied on /find-your-spirit. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/find-your-diet (+ /find-my-diet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real 15 questions, 6 real archetypes (with descriptions), and the real nearest-neighbor archetype-matching logic ported unchanged. Legacy's dead JourneyTracker import wired in for real (see journey-tracker.tsx). /find-my-diet → /find-your-diet redirect added. Verified live: 200 OK, full quiz flow, redirect confirmed 308, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/find-your-movement (+ /find-my-movement), along with the shared assessment foundation the rest of Phase 9 depends on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ported components/assessments/{themed-background,assessment-intro,email-gate,whats-next}.tsx from legacy's ThemedBackground/AssessmentIntro/EmailGate/WhatsNext — real content/behavior unchanged, with 2 real fixes along the way: (1) EmailGate now posts to the real /api/subscribe Route Handler (built earlier this migration) using the exact find-your-&lt;slug&gt; source keys already defined in lib/content/kit-source-tags.ts's KIT_TAG_MAP — legacy's own assessment-gate:&lt;slug&gt; prefix didn't match any tag in that map, so this is a genuine improvement, not just a port. (2) ThemedBackground's per-theme decorative particle field + SVG sacred-geometry overlay + 2 extra radial-glow layers dropped (same "not worth the cost" call made repeatedly elsewhere) — the real per-theme base gradient (16 themes) is kept, precomposed as one literal Tailwind class per theme rather than assembled from fragments. find-your-movement-quiz.tsx ports all 15 real questions and the real 6-dimension (Strength/Flexibility/Endurance/Mindfulness/Community/Adventure) scoring unchanged; the legacy JourneyTracker/useJourneyProgress import in the source file was dead code (imported, never rendered) and not ported. /find-my-movement → /find-your-movement redirect added (next.config.ts), same duplicate-route pattern as /find-my-tribe. Verified live: 200 OK, full quiz flow renders, redirect confirmed 308, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/find-your-sleep (+ /find-my-sleep)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real 15 questions, 6 real archetypes, and the real cascading archetype-match logic ported unchanged, including legacy's own real behavioral quirk of rendering JourneyTracker on every phase (not just results). One real duplicate-destination "Journey Continues" link pair dropped (see file's own port note), the one real distinct link (Find Your Diet) kept. /find-my-sleep → /find-your-sleep redirect added. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/find-your-coffee (+ /find-my-coffee)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real 15 questions, 6 dimensions (Roast Preference/Origin Curiosity/Brewing Ritual/Social Context/Caffeine Sensitivity/Flavor Complexity), 6 real archetypes (each with a real description and 5 real named coffee recommendations — roaster, origin, roast level, tasting notes, real "why" rationale), and the real archetype-matching logic (sum of each archetype's 2 primary dimensions, highest wins) ported unchanged and verbatim. This legacy page predates the shared ThemedBackground/AssessmentIntro component system the rest of Phase 9 is built on — it hand-rolled its own hero-image page shell — so it needed more normalization than most: its hero image (/api/img/coffee-orig_a935f111.jpg) was a dead Manus asset, dropped for the standard ThemedBackground light theme (added a new "coffee" warm-cream entry) instead of reproducing a broken background; the canvas bean-particle field, floating steam-wisp divs, and SVG sacred-geometry overlay all dropped (same decoration-not-worth-the-JS-cost call made repeatedly elsewhere). Real bug found and fixed: legacy read window.innerWidth directly during render (twice — to pick grid columns and flex direction), unsafe during SSR and a real hydration-mismatch source — replaced with responsive Tailwind classes. EmailGate's prop was legacy's assessmentName; ported using this repo's real assessmentSlug="coffee" to match find-your-coffee in KIT_TAG_MAP. Legacy imported useJourneyProgress for markComplete but never rendered a visible JourneyTracker, and nev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/find-your-kitchen. Real 15 questions (all rendered on one page at once</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a genuinely different, legacy-intentional UX from the other paginated quizzes, kept as-is) and the real dual-tracking scoring (answer score keys split into archetype tallies vs. 6 separate radar-chart dimensions) ported unchanged, including the 3 real "Journey Continues" links (one to already-built /find-your-diet, one forward-reference to /find-your-style). Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/find-your-style. Real 15 questions, 6 real archetypes, and the real (if crude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">legacy's own comment admits "Simple mapping for demonstration") threshold-based archetype match ported unchanged. Two real inconsistencies found and normalized: legacy's own inline styles used near-illegible light text on ThemedBackground's actual light pastel "style" theme (inconsistent with every other assessment in this migration); and legacy rendered &lt;JourneyTracker /&gt; defaulting to variant="dark" on a light results screen instead of the variant="light" every other assessment passes. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/find-your-attachment-style (+ /find-my-attachment-style, /find-my-we)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real 18 questions (legacy's own AssessmentIntro stats prop under-reported this as "15" — used the live QUESTIONS.length instead of repeating the stale number, same live-count discipline used elsewhere in this migration), the 4 real archetypes, and the real scoring/selection logic all ported unchanged, including the real closing note on attachment theory. Both alt-path redirects added. Verified live: 200 OK, both redirects confirmed 308, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/find-your-love-language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real 15 questions (incl. the negative-score "disconnect" question), 5 real archetypes with descriptions/tips, and Dr. Gary Chapman's real attribution note all ported unchanged. Verified live: 200 OK, full quiz flow, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/find-your-peptide (+ /find-my-peptide)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"The Peptide Clarity Index™." A real, evidence-cited 10-question assessment across 7 clinical axes, mapping to 16 real peptide archetype profiles — every question (with its real PubMed/journal citation), every profile's real primary/secondary peptides with mechanisms and evidence, suggested lab work, red flags, and stacking notes ported unchanged and verbatim (clinical-adjacent content, not paraphrased). The real Peptide Readiness Score, contraindication-flag screening, share buttons (Twitter/LinkedIn/email/copy — real, backend-free), and the real medical disclaimer are all preserved. Real hero image (CloudFront, confirmed live) kept via next/image. Reused the simplified AssessmentResultActions (PDF-only) built for /find-your-spirit. Same light-text-on-light-background contrast bug already caught elsewhere was fixed here too. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/find-your-sexuality (+ /find-my-sexuality)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A research-informed assessment across 6 real dimensions, grounded in real cited research (Klein Sexual Orientation Grid 1978, Kinsey Scale 1948, Lisa Diamond 2008, Sari van Anders 2015) — real 16 questions (with per-question research context notes), real 12 archetypes (each with a real description + research note), and the real scoring/selection logic all ported unchanged and verbatim, including the real closing disclaimer. Legacy's own AssessmentIntro stats prop claimed "20 questions, 7 dimensions" — didn't match the real 16/6 implementation, used the live counts instead. Legacy's results screen also used light grey text on the real light pastel theme background (same low-contrast bug already caught on /find-your-style) — normalized to dark ink. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/find-my</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Find What's Yours," the real destination of the homepage's "Diagnose" door (confirmed by grepping lib/content/home-doors.ts's /find-my href) and of whats-next.tsx's "Take Another Assessment" link, both already pointing here as forward-references before this page existed. Legacy's 26-item ALL_LINKS directory (Featured + 6 categories) ported unchanged and verbatim into lib/content/find-my-directory.ts. Real accuracy fix, same pattern as /find-your-me's own port note: cross-checked all 26 destinations against the real route list — /find-your-ev, /life-assessment, and /soulscore (at the time) didn't exist yet, rendered as real "Coming Soon" cards instead of links that would 404 (dharma-finder/consciousness-scale/grant-study have since shipped and now flip to live — see below). Real reuse, not re-derivation: every item whose destination already exists in find-your-me.ts's audited DIRECTORY pulls that entry's real hook text and status at build time via a lookup helper, instead of hand-copying a second, driftable copy of the same facts. Two real live destinations added that legacy linked but find-your-me.ts's directory didn't track: /brewsoul (confirmed 200) and the external findmystem-s3lknc4h.manus.space sibling tool (confirmed live), both using the same "real external sibling product" trust already established for the other manus.space tools. Legacy's dead Manus hero image dropped for ThemedBackground (theme="ecosystem"), same call as /find-your-me. AssessmentProgressBar (never </t>
+  </si>
+  <si>
+    <t xml:space="preserve">/assessments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Three Maps. One Journey," confirmed genuinely distinct from /find-my rather than a duplicate: /find-my is the wide 26-item ecosystem directory, /assessments is its own page for exactly 3 long research-grounded instruments (Dharma Finder / Consciousness Scale / Grant Study) that also happen to appear as one category inside /find-my's directory — legacy kept these as two separate pages, so the port does too. Real title/subtitle/description/time/icon/accent content for all 3 instruments ported unchanged and verbatim into lib/content/assessments-hub.ts, including the full "Why These Three" closing essay (Schmachtenberger/Hawkins/Harvard Grant Study triangulation). All 3 instrument cards now link live (dharma-finder/consciousness-scale/grant-study shipped alongside this page). Legacy's footer claim "Results saved for your return" was dropped — replaced with an honest line since nothing persists results yet. Added a real cross-link to /find-my. JourneyTracker reused unchanged; no EmailGate/AssessmentResultActions — pure preview/hub page with no quiz or results step of its own. Verified live: 200 OK, exactly 1 header/footer, real content in all 3 cards, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/dharma-finder (+ /assessments/dharma-finder redirect). Structurally different from every other Phase 9 quiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">legacy's real 25 questions are open-text reflection prompts, not multiple choice, distilled from Daniel Schmachtenberger's Dharma Inquiry and grouped into 4 real sections (Capacities/Values/Propensities/The Shadow Inquiry), each with a real framing quote, plus 3 real interstitial quotes shown between sections with the original 4-second auto-advance. All 25 questions, all quotes, and legacy's own keyword-matching generateDharmaProfile (deriving up to 3 archetypal roles and up to 4 core values from free-text answers, plus a completion-depth percentage) are ported unchanged and verbatim into a new dharma-finder-quiz.tsx. Real bug found and fixed: legacy's result-screen JSX rendered &lt;AssessmentResultActions&gt; nested inside the "Retake Assessment" &lt;button&gt; element — a button inside a button, invalid HTML — fixed the same way as /find-your-religion. Real dead-link bug fixed: "Journey Continues" linked to /assessments/consciousness-scale (repointed to the real /consciousness-scale) and /assessments/grant-study (dropped at the time, now live too). EmailGate (new here; legacy had none) is a real ecosystem-consistency addition. find-your-me.ts's ecosystem-directory status flipped from "coming" to "live" now that this page ships. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/consciousness-scale (+ /assessments/consciousness-scale redirect)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real 25 questions, each scored against David R. Hawkins' real 17-level Map of Consciousness (Shame 20 through Enlightenment 700+, final score = average of all 25 answers) — every question/option, every level's name/emotion/threshold, and getInsight's exact 6 tiers of interpretive copy ported unchanged and verbatim into a new consciousness-scale-quiz.tsx, along with the real live running-average indicator, visual scale gauge, full 17-level map, 6-month reminder, and X/LinkedIn/copy share. Since this assessment produces one composite score on a single axis rather than independent dimensions, a bespoke single-axis gauge replaces AssessmentRadarChart; per-level colors (17 known-at-build-time values) are precomposed literal Tailwind classes rather than assembled from hex fragments. Real Manus-dependency bug found and fixed: legacy's cinematic Q1 hero used a /api/img/consciousness-scale-hero-v2_085e0746.jpg Manus-proxied image — forbidden even temporarily per this migration's Zero-Manus rule — dropped for the plain question-card layout every other assessment uses; a real Sanity-hosted replacement is a tracked follow-up (see BLOG-IMAGE-BRIEFS.md-style tracking). find-your-me.ts's ecosystem-directory status flipped from "coming" to "live" now that this page ships. Verified live: 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/grant-study (+ /assessments/grant-study redirect)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Find Your Score," the real 25-question (5 per factor), 5-factor Harvard Grant Study life-satisfaction assessment (724 men, 1938–present, 85+ years — the longest-running study of human happiness). Every question, the 5 real factors (Warm Relationships/Adaptive Coping/Generativity/Career Satisfaction/Physical Vitality), every per-factor/per-tier insight (real named findings — Vaillant's "mature defenses," Erikson's generativity, Waldinger's quote), and the closing "Tony's Note" (Vaillant's "Happiness is love. Full stop." + Waldinger's "good relationships keep us happier and healthier") all ported unchanged and verbatim. Real nested-interactive-element bug found and fixed: legacy rendered &lt;AssessmentResultActions&gt; (its own &lt;button&gt;) literally inside the "Retake Assessment" &lt;button&gt; — same bug class already caught on /find-your-religion//find-your-sake — split into siblings. Real dead-link fix: "Journey Continues" pointed "Find Your Spirit" at a dead external Manus stub despite the real internal /find-your-spirit existing — repointed. Real ecosystem-consistency normalization: unlike every sibling "Find Your X" quiz, legacy skipped EmailGate entirely and went straight to results — added for consistency, plus new find-your-grant-study/find-your-dharma-finder/find-your-consciousness-scale alias keys in kit-source-tags.ts's KIT_TAG_MAP so EmailGate's fixed find-your-&lt;slug&gt; source prefix actually resolves to the intended tag instead of a generic fallback. resultSlug="grant-study" pas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/soulscore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SoulScore™, ImpactSoul's 12-dimension impact measurement engine (1231-line legacy file, the largest remaining port). Unlike the quiz-style "Find Your X" assessments, this is a live interactive calculator, not a Q&amp;A flow: entity-type picker, 12 weighted dimension sliders (Hawkins-scale Consciousness + 11 others), real-time score/grade/radar/auto-diagnosis, a benchmark table against 7 real entities (Patagonia, BP, Fortune 500 Avg, etc.), a 6-tier/30-factor supply chain drill-down, 20 "why every impact system failed" entries, a real Consciousness-Adjusted NPV calculator, and the gig-economy 5-layer stack comparison — all real content/formulas ported verbatim. Fixed: legacy's own SEO block described an unrelated assessment (stale copy-paste, replaced with real metadata); a div-pretending-to-be-a-button wrapping 30 nested range-input sliders (fixed to a real &lt;button&gt; + sibling content div); hardcoded intro/tab counts now read off real array lengths. No EmailGate (legacy never had one here — it's an open calculator, not a report unlock), matching /find-your-peptide's precedent. AssessmentResultActions wired with resultSlug="soulscore". journey-tracker.tsx's JOURNEY_MAP and /impact-dashboard's "Launch SoulScore Engine"/"Launch C-NPV Calculator" links (previously a disabled "Coming Soon" note) now point at the real page. This closes the real dead-end referenced from site-nav-data.ts (/soulscore appears twice in nav) and from /impact-dashboard — the last item in the STATUS.md dead-end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/self-portrait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">composite of completed assessments. Decision made: local-only (a real cookie, not Supabase — Phase 2 isn't provisioned yet). AssessmentResultActions (components/assessments/result-actions.tsx) takes an optional resultSlug and logs completions to a tg_assessment_results cookie via lib/assessments/result-log.ts, the same real-cookie-read-via-next/headers pattern already established by returning-visitor-hero.tsx/track-last-blog-visit.tsx — the page itself is a Server Component reading that cookie with zero client hydration step. Real, deliberate scope cut, not a silent one: legacy's SelfPortrait.tsx combined each assessment's own per-dimension scores (16 separate localStorage keys) into one composite radar chart across 15 unified dimensions, gated behind "5+ completed." This migration's result log only ever records that an assessment was completed, not its actual scored answers — building the real composite radar would mean threading a second, much larger data channel through every quiz. Shipped the honest subset instead: a real completed-assessments list (title, real completion date, retake link) plus a real "X of N completed" count and a "Still to Explore" section for the rest, via a new lib/content/self-portrait-catalog.ts. Wired resultSlug into the 7 remaining older "Find Your X" quizzes that already call AssessmentResultActions but hadn't been threaded yet (spirit/therapy/religion/sake/coffee/peptide/me) — /self-portrait now tracks 13 real assessments total. /find-my's "Sel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/the-mirror (+ /life-assessment)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uses mirrorData.json, real 6-dimension/18-question life assessment ("The Mirror") ported into a typed lib/content/mirror-data.ts. Legacy served the identical component at both paths; /the-mirror is canonical (it's the only URL every existing internal link already pointed to — nav, journey tracker, Find Your Me), /life-assessment permanently redirects there. Real dimension-averaged scoring, radar chart via the shared AssessmentRadarChart, and weakest-dimension article/satellite-site recommendations ported unchanged. A live Sanity check found only 27 of 85 legacy article slugs still resolve; recommendations now resolve server-side and defensively skip missing ones, matching legacy's own behavior. Fixed: a hydration-unsafe typeof window branch computing the share URL, three stale manus.space satellite URLs superseded by their current live counterparts already used elsewhere in this migration, and dead /assessments/*/external-stub links in the "Journey Continues" grid. Added find-your-mirror to kit-source-tags.ts's KIT_TAG_MAP and reconciled journey-tracker.tsx's stale 10-minute estimate to legacy's real "~4 minutes" claim. find-your-me.ts's ecosystem-directory status flipped to "live." Verified live: 200 OK on both paths, redirect confirmed, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confirmed via full legacy read this is not a "Find Your X" quiz (it predates that convention): it's Tony's own 3-way reader-path diagnostic — Builder / Crusader / Investor — 5 real questions, one point per matching answer, highest tally wins. Real questions and real archetype copy ported unchanged, reused from lib/content/archetypes.ts (already ported for /essays's archetype filter) rather than duplicated — added the page's ASSESSMENT_QUESTIONS to that same module since both come from the identical legacy source file. Preserved the real, distinct UX (no landing screen, no ThemedBackground/JourneyTracker — this page sits outside that ecosystem). Real bugs fixed: JS onMouseEnter/onMouseLeave inline-style hover hack replaced with Tailwind hover: classes; literal "..." pending-state text replaced with a real Loader2 spinner per house rule; dead trpc.subscribe.add replaced with a real POST /api/subscribe call. Real link audit: kept /impact-dashboard, /find-your-me, /living-declaration, and the real /blog/boiling-the-human-summit-harvard-kurzweil article as live links; /soulscore and /humanos are established forward-references used repeatedly elsewhere in this migration and both now ship too. The Human OS CTA reuses the border-red-800/30 text-red-800 treatment /living-declaration already established for the identical button instead of a new one-off raw-hex pair. AssessmentResultActions resultSlug="assessment" added (didn't exist when legacy was written). Added assessment-builder/as</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix dead-end pages flagged in STATUS.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sake, therapy, and love-language all got real next-step navigation (WhatsNext + real "Journey Continues" links) during their ports — the last remaining one, soulscore, is now built (see above), closing this out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port shared radar-chart / PDF-export / email-gate components used across assessments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">components/assessments/{radar-chart,result-actions,email-gate}.tsx, built during Phase 9 and reused unchanged by all 15 "Find Your X" quizzes plus /find-your-me.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src/lib/admin/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">guardrails (fixes the removed version's proxy.ts pattern, which missed the real src/proxy.ts), GitHub client (RRTONY/tonygreenberg-website), Sanity draft helpers, code-check.ts (ESLint + CONTRIBUTING.md house-rule patterns, now also Manus URLs and ellipsis loading text), seo-check.ts, tools.ts, mcp-server.ts, mcp-handler.ts, mcp-tool-context.ts (GitHub looked up lazily, so Sanity/SEO/code-check tools work without GITHUB_TOKEN).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-person access via MCP_ADMIN_USERS (read/edit/write roles, tools filtered per role, calls logged, commits stamped [by &lt;name&gt;])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mcp-auth.ts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rules gate: get_project_rules serves CONTRIBUTING.md + AGENTS.md + docs/ai/ guides with a rulesVersion; all 6 write tools require it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">project-rules.ts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src/app/api/mcp/route.ts (header auth) + src/app/api/mcp/[token]/route.ts (token in URL).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docs/ai/ knowledge base (README, TASK_GUIDE, PROJECT_STRUCTURE, project_mcp_server), linked from CONTRIBUTING.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@modelcontextprotocol/sdk ^1.30.0 re-added (approved 2026-09-29); GITHUB_TOKEN/MCP_ADMIN_USERS/MCP_SITE_ORIGIN documented in .env.local.example.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified locally</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auth (401/405), role filtering, rules-gate markers, token-in-URL route, code check, Sanity query, SEO check.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign-in for the MCP server (OAuth 2.1, ported from ramprate-ui, 2026-09-30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/oauth/authorize sign-in page + /.well-known metadata + register/authorize/token endpoints, stateless (signed tokens, no database), no new dependency. Verified end to end on a local production build. See docs/ai/project_mcp_server.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set GITHUB_TOKEN, MCP_ADMIN_USERS, MCP_LOGIN_PASSWORD, MCP_OAUTH_SECRET, MCP_SITE_ORIGIN, MCP_PUBLIC_ORIGIN in Netlify (done) (checked 2026-…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-07: all already set in Netlify). Left: connect Claude.ai to /api/mcp for real, and verify the GitHub flow end to end (branch → PR → deploy preview → publish_changes) against a real PR.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit a team-wide .mcp.json (URL only) once the production URL is settled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google read-only tools added (2026-10-02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check_analytics (GA4), search_console_sites / _performance / _inspect_url / _sitemaps (list only, no submit or delete), lighthouse_check_page (PageSpeed Insights). New files google-auth.ts, ga4-client.ts, gsc-client.ts, lighthouse-check.ts; no new dependency. Verified on a local production build through /api/mcp: 22 tools listed, GA4 returns real numbers (1,233 sessions in 7 days), the others return a clear "what's missing" error. Env vars added to .env.local.example.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">publish_changes fixed (2026-10-02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">it published every draft in Sanity (31 waiting for review today), so any one-line fix would have pushed them all live. Now it publishes only the drafts named in draft_ids; unknown ids are refused before anything happens (verified).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seo_check_page decoded &amp;#39; but not React's &amp;#x27;, so descriptions showed Tony Greenberg&amp;#x27;s and the length was off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed and verified (2026-10-02).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search Console access for the service account added by the team (2026-10-02); all four search_console_* tools verified with real tonygreenbe…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rg.com data (99 clicks / 1,663 impressions in 28 days, homepage indexed, sitemap 284 URLs, 0 errors, 82 warnings).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOOGLE_GA_CLIENT_EMAIL, GOOGLE_GA_PRIVATE_KEY, GA4_PROPERTY_ID_TONYGREENBERG set in Netlify (2026-10-02, via the Netlify API, values checked…</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> equal to .env.local; this plan can't limit a variable's scopes, so they're available to builds and functions). Used from the next deploy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-request change system ported from ramprate-ui (2026-10-02, owner said yes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">, covering the 10 review points the team raised for RampRate's setup: (1) discard_change; (2) one request = one change with its own branch, PR and drafts, so publishing never takes another request live; (3) a review with pages affected, a server-written "what's included" line and preview links; (4) publish needs the review's reviewToken, and the rules make the AI ask "You are about to publish these changes to the live tonygreenberg.com website. Are you sure you want to continue?"; (5) list_change_history, also visible read-only in Studio under "Website change history" (new adminChange type); (6) undo_change; (7) before/after (automatic for Sanity, given by the AI for code); (8) preview_on_devices phone + laptop screenshots (needs GOOGLE_API_KEY); (9) the AI's plain summary plus the server's facts line; (10) Draft → Ready for review → Published / Discarded. Files: change-sets.ts, change-describe.ts, device-preview.ts, mcp-tool-context.ts, mcp-server.ts, github-client.ts (RampRate's full version), src/sanity/schemas/adminChange.ts, sanity.config.ts. Tested end to end with a real throwaway change, then discarded (see docs/ai/project_mcp_server.md).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merge the CI fix into main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(done with PR #3; checked 2026-10-06: main's pr-lint.yml runs Node 22 and next typegen before the type check). The test change's GitHub check failed because main still has the old pr-lint.yml (Node 20 crash). Every MCP change will fail its site check, and so can't be published, until this branch's work (or at least .github/workflows/pr-lint.yml) is on main. Then test a real publish and undo_change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blocked on you (Google)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">create a GOOGLE_API_KEY in Google Cloud (project of the vcos-ga4-reader service account, where the PageSpeed Insights API is already on), restricted to the PageSpeed Insights API, then add it to .env.local and Netlify. Creating it from here was blocked by the session's safety check (it would use the service account's credentials to change the Cloud project). Note lighthouse_check_page may time out on Netlify (10 s function limit on the free plan).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-page generateMetadata (title, description, OG, Twitter Card, canonical) for every ported route, sourced from Sanity seo object where con…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tent is CMS-backed, static otherwise. Audited all 140 page.tsx files: only /studio has none (correct — it's robots.txt-disallowed, not public content). Real gap found and fixed: /blog/category/[slug] had no alternates.canonical at all, and no page-aware title for its own real pagination (?page=N) — every paginated page was serving an identical title with no canonical, a real duplicate-content signal. Fixed: generateMetadata now reads searchParams too, self-canonicals each page (?page=N pages canonical to themselves, not consolidated to page 1 — genuinely different posts per page, matching Google's current pagination guidance) and appends "— Page N" to the title past page 1. Verified live: page 1 canonicals to the bare URL, ?page=2 canonicals to ?page=2 with a distinct title.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sitemap.ts generated from real Sanity content + static route list, auto-updates on publish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extended from the Phase 5-era version (homepage + blog posts only, 122 URLs) to every real route: the full static route list (130 routes, generated from find src/app -name page.tsx, excluding /studio (robots.txt-disallowed), /(auth)/login (noindex via its own metadata), and /life-assessment (a pure redirect, not distinct content)) plus all 5 real dynamic sources — blog categories (allCategorySlugsQuery), BrewSoul cities (25), BrewSoul coffees (107), and charity-scorecard entries (103) — each pulled from the exact same data source its own page's generateStaticParams already uses, not re-derived. Auto-updates on publish for anything Sanity-backed (blog posts/categories) since it's a live client.fetch on every build; the static route list itself needs a one-line addition whenever a new page ships (same as any other route-registration step). Verified live: 496 real &lt;loc&gt; entries, spot-checked a coffee/city/charity/category URL each, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">llms.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fetched verbatim from the still-live site and saved to web/public/llms.txt (real content: Tony's bio, expertise, full article index by category, every product/tool section) — do this before Manus goes away, it won't be recoverable after</t>
+  </si>
+  <si>
+    <t xml:space="preserve">robots.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same approach: fetched the real live file (not my earlier guessed robots.ts, which has been removed) and saved verbatim to web/public/robots.txt, plus added Disallow: /studio for the new Sanity Studio route. Confirmed live: real AI-crawler allowlist (GPTBot, Claude-Web, PerplexityBot, etc.), scraper blocklist, and the site's non-standard LLMs: directive all intact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JSON-LD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WebSite + Person schema ported verbatim from the live homepage's actual &lt;script type="application/ld+json"&gt; tags (not reconstructed from memory) — rendered site-wide from src/lib/structured-data.ts in the root layout. The Person image was hardcoded to a /api/img/... legacy proxy path on the live site — rescued that headshot (downloaded it while still live, uploaded to Sanity as the author-tony-greenberg document's avatar) so the new site's JSON-LD has zero Manus dependency instead of just copying the fragile path forward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Article JSON-LD on /blog/[slug], built from real per-post Sanity data (headline, image, datePublished/dateModified, author, canonical URL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verified live on a real post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/path/:archetype (src/app/path/[archetype]/page.tsx)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per-archetype landing page for /assessment's Builder/Crusader/Investor result, reusing lib/content/archetypes.ts. Real content ported in full (top-5 essential-reading list per archetype via allPostsForArchiveQuery, real PathSubscribeForm posting to /api/subscribe, AUTHORITY_ITEMS strip). Real bug fixed vs. legacy: replaced a hand-rolled inline-styled "Path not found" div with a real notFound() (this route's generateStaticParams only ever produces the 3 real keys). Verified live: all 3 archetype routes 200 OK, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/my-journey (src/app/my-journey/page.tsx + components/assessments/my-journey-dashboard.tsx)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"My Journey Dashboard," real grid/timeline views across all 28 JOURNEY_MAP experiences, category/status filters, phase progress ring, recommended-next card, using the same real useJourneyProgress/JOURNEY_MAP completion tracking every "Find Your X" quiz already writes to (not the narrower tg_assessment_results cookie built for /self-portrait). Legacy's per-quiz scored-result caching (RESULT_KEYS, feeding a mini radar chart) was not ported — no quiz in this migration writes that data either, same honest-degradation call already made for /self-portrait's own composite radar. Fixed a real legacy dead link (/ecosystem-map, a still-unbuilt page) to /self-portrait. Verified live: 200 OK, real content confirmed, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/the-open-door (src/app/the-open-door/page.tsx)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real press/credibility content: all 10 "Magic Genie" client-pitch prompts (real named targets — Marco Argenti/Goldman Sachs, Adam Smith/Disney, etc.), 18 real client testimonials, all 8 explicitly-labeled satirical "parody" quotes (kept with disclaimers, not presented as real). Real overlap found and reconciled: this page's publications/speaking/podcasts arrays substantially duplicate the already-shipped /published's fuller bibliography — kept only what /published doesn't cover (Forbes + Business Insider bylines, the Clinton Global Initiative keynote, 4 of 5 podcast appearances) and cross-linked to /published for the rest, same reconciliation pattern as /assessments vs /find-my. Real bugs fixed: 3 genie/keynote links pointed externally at tonygreenberg.com/&lt;slug&gt; for posts that are real internal posts in this migration — relinked to /blog/psychedelics-could-become-extractive-capitalism, /blog/boiling-the-human-summit-harvard-kurzweil, /blog/return-on-investment-going-green-going-green-2 (all verified 200); a bare self-link to tonygreenberg.com remapped to /. Ships as a pure Server Component (legacy's FadeIn/Section/editorial-component dependencies don't exist here and weren't needed). Verified live: 200 OK, real content in raw SSR HTML, typecheck/lint clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homepage "Recent Updates" band (2026-09-29)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">on the live site (a newer Blog.tsx than _legacy-manus-app/, so rebuilt from the live page's markup), replacing the older "Latest Thinking" pair. Found while doing it: two live essays are missing from Sanity, the-tollbooth-and-the-alternative (Aug 18, 2026, the live site's newest) and what-quest-could-fix. Both were published on live after the legacy snapshot and need importing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-sync the legacy reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_legacy-manus-app/ is older than what's live (Recent Updates proves it), so visual diffs should be against the live site, not only that folder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visual diff pass: every ported page vs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">legacy page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padding / spacing on the story pages matched to live (2026-10-01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measured margins, text column and spacing on 31 pages, live vs a production build, at 375px and 1280px. The "door" story pages were the clear mismatch: live's text column is ~546px (ours was 720px), 20px side margins on phones / 40px on desktop, body text 19px/1.8 on phones and 18px/1.85 on desktop (ours 16px/1.5). Fixed on /the-body, /engine-room, /under-nda, /the-nightstand, /the-web, /the-territory, /about, /intel (Intel uses live's 16.8px/1.9; About's hero line 480px max, 18.4px/1.8). Re-measured: all 8 match live to within 2px (About's column 28px narrower), no sideways scroll at 375px.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header-to-title spacing re-checked (2026-10-02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 2026-10-01 note compared different things: live's header wasn't measured (it showed 0), so "96px vs 168px" was really 161px vs 168px from the top of the page. Measured again from the top of the page, live vs a production build, at 375px and 1280px: most pages were already within 10px. Fixed the real gaps: /the-open-door (now live's dark centered hero band, 56px title, 546px text column; title was 72px too high), /start-here (live's 48px/96px top padding; 25px too high on desktop), /invest and /engage (label spacing and live's 32px/51px title; /invest's desktop title was 36px), /impact-dashboard on phones (card edge to edge under the header like live; title was 89px too low). Re-measured: all within 8px of live, no sideways scroll at 375px, no JS errors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HumanOS headings in capitals like live (2026-10-02, owner said yes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the 4 headings live capitalises on /humanos (title, "Are you a Maximizer...", "Take the Diagnostic", "The Diagnostic") get uppercase; the words are unchanged. The subpages already matched.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More layout gaps matched to live (2026-10-02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/series (live's centered 546px column, and a bug fixed: every card kept an empty 240px picture column, squeezing the text; live's per-series picture is one generic placeholder on the Manus proxy, so not copied), /humanos (middle section 900px like live), homepage desktop widths (hero text 804px, Four Doors 1000px, Editor's Picks 1168px, GemSpark edge, section title sizes; live's /blog now shows the homepage), /find-my (photo undimmed and plain background, like live; our site header kept). Re-measured: headings within 3px (/series) to 20px (homepage) of live, no sideways scroll, no JS errors. Note: live's "New here?" tour bar sits over its header and doesn't move the page, so it doesn't affect these numbers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full sweep vs live (2026-10-02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142 pages (every non-blog page, 3 of each templated set) at 375px and 1280px, title position, text column, title size. Fixed the shared causes: BrewSoul (live wraps most pages in its frame twice, so a second 52px offset plus the category badge; the landing, cities, directory and quiz pages have neither: src/components/brewsoul/brewsoul-main.tsx; intro paragraphs uncapped like live; 38px titles), Kava (live's extra 52px offset), /the-body, /the-nightstand, /the-web (405px top photo like live), the 6 peptide pages (live's 768/896px intro column), /journeys, /pick-up-the-phone, /published, /ecosystem (546px story column and live's text size). Re-measured: 110 of 120 within 40px / 60px of live.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweep leftovers fixed (2026-10-06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ported legacy's exact title sizes, margins and column widths. Measured live vs a production build at 375px and 1280px (H1 distance from the top, H1 size, intro and table widths). Now within 8px and the same title size on /published, /brewsoul/first-sip, /brewsoul/home, /brewsoul/chains (intro 912px like live), /brewsoul/browse, /brewsoul/directory (3-column 952px grid like live), /brewsoul and /brewsoul/quiz (intro 520px), /amplifier (546px column), /diamond-cut, /speaking, /living-declaration, /spirits, /protecting-your-business (tables 730px), and the 5 HumanOS subpages (titles smaller like live, 752px column). No sideways scroll at 375px. Left on purpose: /self-portrait (font matches; our page has a different title and no back link, so it sits 23-57px higher), BrewSoul pages 3-6px off (the shared journey bar row), and the different-layout pages /dharma-finder, /grant-study, /search, /quiz_25q, /soulscore. Also: /brewsoul/quiz rebuilt as a step registry (src/components/brewsoul/brewsoul-quiz/: parent + hook/ + components/step-* + data/), same questions, scoring and look; Back/Skip/Retake use lucide icons. New CONTRIBUTING rule 19 (multi-step flows, FydoPartner pattern). brewsoul-welcome-quiz.tsx (/brewsoul) still has the old shape and text arrows.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Match live's redesigned pages (2026-10-06, owner said go)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/self-portrait (live: dark page, progress ring, "N more brushstrokes" lock until 5 assessments), /grant-study and /dharma-finder (live opens straight on question 1, no intro screen), /quiz_25q (live adds a hero picture above the title; rescue it into Sanity first), /search (live: one search box across essays, BrewSoul, peptides, HumanOS, assessments, kava and pages with filter chips). Measure live vs a production build at 375px and 1280px when done. Done 2026-10-06: /grant-study and /dharma-finder open straight on question 1 like live (title block / part header above the first question, live's 546px column, plain page, credit under every question), both rebuilt as step registries (rule 19); measured within 3px of live at the top (dharma's question block within 7px). /quiz_25q's hero rescued into Sanity and placed like live (within 2px). Found and fixed on the way: on the deployed copy /grant-study's answer buttons could not be clicked (the themed page background was fixed z-0, painted over the quiz); ThemedBackground is now -z-10 pointer-events-none (backgrounds unchanged on all 21 pages that use it), and the shared email gate no longer scrolls sideways on phones. Both quizzes clicked through to results in Chrome and Safari. /self-portrait restyled to live (dark page, "The Composite You", progress ring, "N More Brushstrokes Needed" lock until 5 done, live's copy) on our real cookie data; within 3px of live at both widths; tested with 0, 2 and 6 completed. Counts are ours (13 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Still different from live (needs a yes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blog posts (done) (done 2026-10-07, see Phase 5); /find-my on live hides the site header. /walk-through is a 404 on live now.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design change on live, needs a decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">live's story pages now use Cormorant Garamond for titles (ours: Playfair Display), a lighter title weight (400 vs our 700), and a red eyebrow label (#8E1E25, wider letter spacing) instead of our gold. A site-wide font swap is a design call, so not done.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link check across all ported pages (no 404s, no broken internal cross-references)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First full pass done 2026-09-29 (510 pages crawled from the sitemap plus every internal link, on a production build). Fixed in code: /brewsoul/coffee/…-tarrazú 404 (the route got the id still percent-encoded), 30+ links that went through the /assessments/* redirects, /find-your-me's dead Homeaglow link, the two root-level Iboga essay links, and the dead FauxTony nav item. Fixed as Sanity drafts (scripts/fix-blog-body-links.ts, 14 posts): broken post links, leaked !… placeholder text, Energy Is Money's split author bio, and scraped WordPress furniture ("Share this / Related / You Might Also Like / Copyright", "Show More / Top News", [mc4wp_form]). Left for a decision: /framework's "Ask FauxTony" button, when-healing-becomes-extraction's two links to a Dr. Lee case file that doesn't exist, and the-clock-keeper-chronicles-part-1's link to the deferred /clock-keeper-part-2. Re-run after the drafts are published. 2026-10-01 re-run (local production build, all 498 sitemap URLs load; 440 unique internal links): 5 broken. Fixed as a Sanity draft: molecule-as-mirror-10-what-the-pioneers-know's "Final installment" link pointed at a non-existent part-10 slug (now part 11; live also shows that line twice, kept). Already fixed in a waiting draft: forever-chemicals-... → /blog/psychedelic-readiness-index. Still the 3 known decisions: /fauxtony (from /framework), /clock-keeper-part-2, /blog/the-case-file-dr-samuel-lee.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lighthouse pass (performance/accessibility/SEO) on top 20 pages by traffic 2026-09-30, 20 key pages (no traffic data yet), local production …</t>
+  </si>
+  <si>
+    <t xml:space="preserve">build, mobile: averages performance 87, accessibility 99→100, best practices 100, SEO 92→100, CLS 0 everywhere. Fixed: public/robots.txt had an LLMs: line (not a real directive) that made Google treat the whole file as invalid, now a comment; h3/h4 headings skipping a level on /assessments, /kava, /peptide-watch (same look, right tag); the Kava and /attention-theft back-arrow links had no accessible name on phones; two small phone-width contrast misses. Left: performance is local-machine only (±10-15 points, see CONTRIBUTING.md); the slowest were / 76 (LCP 5.2 s), /psychedelic-readiness-index 82, /iboga-ibogaine 83. Re-run against the Netlify deploy before launch. 2026-10-06 re-run against the Netlify deploy (14 key pages, mobile): accessibility 100 and CLS 0 on every page, SEO clean (only the expected netlify.app noindex), performance 77-97 held back by 3-4 s LCP. Fixed: all 21 hero images moved off the deprecated priority prop to fetchPriority="high" + loading="eager" (Next 16); /iboga-ibogaine hero and the first card on /blog and category pages no longer lazy-loaded; sizes on the Four Doors cards (~150 KiB per page), /humanos diagram (~100 KiB) and /about headshot; urlFor no longer imports the Sanity client, so ~115 KB of Sanity client code stopped loading on / and /blog; React hydration error #418 on / and /blog (post dates) gone, checked in two time zones; /blog is static again; empty icon &lt;th&gt;s on /iboga-ibogaine labelled; category page reads use sanityFetch(). Left: se</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEO audit fixes (2026-10-06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEO audit items needing a yes (2026-10-06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
+  </si>
+  <si>
     <t xml:space="preserve">"Keep going" strip above the footer on every page (2026-10-07)</t>
   </si>
   <si>
@@ -940,757 +1693,10 @@
     <t xml:space="preserve">dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
   </si>
   <si>
-    <t xml:space="preserve">/brewsoul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">welcome/landing gate (built, not yet pushed — pending local review), along with the shared foundation the rest of Phase 6 depends on. Ported BrewSoulLayout.tsx → app/brewsoul/layout.tsx + components/brewsoul/brewsoul-nav.tsx (BrewSoulNav/BrewSoulFooter), CategoryBadge.tsx → components/brewsoul/category-badge.tsx, brewsoul-config.ts → lib/content/brewsoul-config.ts, and BrewSoulDirectory.tsx's CATEGORIES/PAGE_CATEGORY_MAP data (not the page itself yet) → lib/content/brewsoul-directory.ts. Real architecture decision: BrewSoul is a self-contained sub-site with its own nav/footer/coffee-brown palette, same as legacy — but this app has one flat root layout with no route groups, so the main site's SiteHeader/SiteFooter needed to be suppressed for this one subtree without restructuring every existing route. Added components/site-chrome.tsx (SiteChrome, a small client wrapper checking pathname.startsWith("/brewsoul")) around both in app/layout.tsx — verified via literal &lt;header&gt;/&lt;footer&gt;/&lt;nav&gt; tag counts in real SSR HTML (not text search, which false-positives on Next dev mode's RSC debug payload) that /brewsoul gets zero main-site chrome and its own real nav+footer, while / still gets exactly one of each. Dropped TonyAvatarTrigger (FauxTony chatbot widget — Phase 10, no backend yet, same "don't fake it" call made elsewhere) from the nav. Ported BrewSoulWelcome.tsx → components/brewsoul/brewsoul-welcome-quiz.tsx (8-screen onboarding quiz, real identity-scoring logic, palate questions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/first-sip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">onboarding intro (built, not yet pushed — pending local review). Ported "The First Sip Is a Vote" in full — the complete manifesto essay (5 sections, 3 pullquotes, the couplets block, the disclosure-demands grid), the 5-tool journey map, 6 related-essay links (real slugs, cross-checked against this session's already-verified corpus), the closing + sources, and the email capture. Built as a Server Component (all static except the email form) + components/brewsoul/next-steps.tsx (shared "what's next" CTA, itself a Server Component — legacy's hover effects were plain CSS-able, no JS state needed) + components/brewsoul/first-sip-email-capture.tsx (client island, mailto: fallback since no subscribe backend exists, same pattern as newsletter-popup.tsx). Dropped the canvas CoffeeDust decoration and the confirmed-dead hero photo (/api/img/brewsoul-orig_84eb4bc9.jpg, 404, same Manus proxy) — with no image left, the scroll-linked parallax that moved it went too. The 5 tool-card links (prescription/health/pairings/economics/compare) point at later Phase 6 routes not built yet — same forward-reference pattern as /find-my. Verified live: 200 OK, full essay text present, CategoryBadge correctly shows "Start Here" (from PAGE_CATEGORY_MAP), zero main-site chrome leaking in, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">the real BrewSoul dashboard (distinct from /brewsoul's identity-quiz welcome gate and /brewsoul/first-sip's manifesto): hero + stats, Follow the Dollar teaser, Top QPR coffees (computed live via computeQPR), the 2025 crisis callout, New Drops, a Wall of Shame preview (SHAME_ENTRIES), the research-hub card grid, and a cyclable health-fact ticker (components/brewsoul/health-ticker.tsx, its own small client island so the rest of the page stays a Server Component). Canvas WarmParticles/ParallaxBg decorations and the dead hero photo (/api/img/brewsoul-orig_84eb4bc9.jpg, same confirmed-404 Manus proxy used elsewhere in Phase 6) dropped for CSS gradients. Stats use the real live BREWSOUL_COFFEES.length (107) in place of legacy's stale "103". Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/browse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coffee listing (components/brewsoul/browse-explorer.tsx), real filter/search over the full BREWSOUL_COFFEES catalog. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/coffee/[id]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coffee detail page (breadcrumb, QPR + tier header, quick stats, tasting notes, flavor-profile bars, the 4 intelligence scores, transparency/ethics data, buy links, competition wins, similar-coffees cross-links, journey CTAs), server-rendered with generateStaticParams over all 107 real coffees (this repo's bounded-dynamic-route convention, same as /blog/[slug]) instead of legacy's client-side useParams lookup. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/quiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">matching quiz (built, not yet pushed — pending local review), along with the real data/engine foundation most of the rest of Phase 6 depends on. Ported lib/intelligence-engine/{types,scoring}.ts verbatim (generic scoring engine — QPR/availability/scarcity/wow/tier/freshness — reusable beyond BrewSoul) and the full coffee catalog (legacy's 3 files: brewsoul-coffees.ts + -expanded.ts + -expanded2.ts, merged at import time) → one lib/content/brewsoul-coffees.ts, extracted via tsx (not hand-typed — 107 real entries, ~6.5K lines). Caught a real stale count: legacy's own file header claimed "105" and its UI copy said "103", but the actual merged arrays contain 107 — this migration shows the live BREWSOUL_COFFEES.length everywhere instead of a repeated hardcoded number. Ported JourneyBar.tsx (components/brewsoul/journey-bar.tsx) — the fixed bottom "what's next" bar shown on every BrewSoul content page except the identity quiz — and retrofitted it onto /brewsoul/first-sip too (built before JourneyBar existed). Built components/brewsoul/brewsoul-quiz.tsx: real 7-question taste quiz scored against each coffee's real flavorProfile via the real scoring engine, ranking the full catalog by match. Legacy's useMarkVisited was renamed to markVisited (it's a plain localStorage write, not a hook — its old use-prefixed name tripped React's rules-of-hooks lint when called from inside a useEffect). Dropped the canvas WarmParticles decoration and the dead hero photo (same confirmed-404 Manus proxy,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/wall-of-shame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">content page. Real 13 entries (brand/category/evidence/severity/response) from SHAME_ENTRIES, unchanged. Category filter buttons extracted into components/brewsoul/shame-explorer.tsx (the only interactive piece) so the page itself stays a Server Component. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/follow-the-dollar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">supply-chain essay. Real DOLLAR_BREAKDOWNS segment bars (farmer/exporter/importer/roaster/retailer %, real commentary), unchanged. The farmer-segment bar's data-driven color (green/gold/red by threshold) is a small known set of variants — precomposed as 3 literal Tailwind classes rather than an inline style background, per this repo's dynamic-class rule; only the genuinely per-item width stays as style. Fully static, Server Component. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/farms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sourcing content ("Farm Passports"). Real FARMS entries (country/region/producer/altitude/story/varieties/certifications), unchanged. Fully static. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/mold-free</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mycotoxin content. Real verified/claims/untested split computed live over the full BREWSOUL_COFFEES catalog by moldTestStatus. Fully static. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/experiences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">experiential content ("Experience Map"). Real EXPERIENCES entries (farm tours, cafés, cupping labs, roastery visits), unchanged. Country filter buttons extracted into components/brewsoul/experiences-explorer.tsx, same split-out-the-interactive-bit pattern as wall-of-shame. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">health deep-dive, ported from BrewSoulHealthFull.tsx (the file legacy's own router actually uses for this route — BrewSoulContent.tsx's same-named BrewSoulHealth export is real but genuinely dead/unrouted code in legacy, shadowed by this one). Real 8 longevity findings with real citations/participant counts, 7 real risks with severity ratings, CYP1A2 caffeine-metabolism genetics, a 6-step chronobiology timing schedule, 8 real bioactive compounds, 3 real mycotoxin threats, and a 3-step "simplification protocol," all ported unchanged and verbatim. Dead Manus hero image dropped for a CSS gradient. Legacy's own redundant BrewSoulLayout wrapper dropped — app/brewsoul/layout.tsx already wraps every route. The two real interactive pieces (show-all-risks toggle, per-compound click-to-expand) split into components/brewsoul/health-{risks,compounds}.tsx client islands so the rest stays a Server Component. Legacy's bespoke earthy "science" palette (soil/clay/sage/moss — distinct from the rest of BrewSoul's amber/gold commercial palette) kept as a deliberate one-off sub-identity for this one page, same reasoning as /attention-theft's own "crusade" palette elsewhere in this migration. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/varieties</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reference: varieties. Real VARIETIES encyclopedia entries (species/origin/genetics/cup profile/yield/disease resistance), unchanged. Search extracted into components/brewsoul/varieties-explorer.tsx. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/processing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reference: processing. Real PROCESSING_METHODS entries (description/flavor impact/complexity/controversy), unchanged. Fully static. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/roasters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reference: roaster directory. Real ROASTERS entries (philosophy/quality/transparency/farmer-equity scores), unchanged. Search + tier filter extracted into components/brewsoul/roasters-explorer.tsx. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/glossary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reference: glossary. Real GLOSSARY terms, unchanged. Search + alphabetical grouping extracted into components/brewsoul/glossary-explorer.tsx. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/pairings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reference: pairings. Real PAIRINGS (food/drink pairings by origin) and 3 real curated FLIGHTS (each linking to real coffees in the catalog), unchanged. Fully static. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reference: economics. Real live-computed stats (coffee/origin/roaster/variety counts, average price, average farmer share via DOLLAR_BREAKDOWNS), a real price-distribution histogram, and a real top-origins ranking — all computed directly from BREWSOUL_COFFEES at render time, unchanged. Fully static. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/compare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tool: compare coffees. Real side-by-side comparison of up to 4 coffees across origin/producer/variety/process/price/cupping and the 4 intelligence scores (QPR/availability/wow/overall), unchanged. Interactivity in components/brewsoul/compare-explorer.tsx. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/blend-builder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tool: blend builder. Real combine-up-to-5-coffees ratio calculator with weighted-average QPR/Wow/Overall scores via range sliders, unchanged (never persisted anywhere in legacy either — a pure in-session calculator). Interactivity in components/brewsoul/blend-builder-explorer.tsx. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/drops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tool: product drops ("Latest Drops"). Real top-12-by-overall-score coffees. No client-side state at all (legacy's own useMemo had no changing dependencies — a pure derived list), so this ships as a plain Server Component. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/collection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tool: personal collection tracker ("My Collection"). Real save/toggle-to-collection behavior, unchanged. Real bug found and fixed: legacy read localStorage directly inside a useState initializer — unsafe during SSR, same hydration-mismatch class already fixed in journey-bar.tsx/journey-tracker.tsx — rebuilt around a module-level external store fed through useSyncExternalStore in components/brewsoul/collection-explorer.tsx. Also found and fixed: the already-ported brewsoul-directory.ts listed this page's path as /brewsoul/my-coffees — a real dead link in legacy's own directory (legacy's actual router only ever served this at /brewsoul/collection, /brewsoul/my-coffees never existed) — corrected to the real path. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/submit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tool: submit a coffee ("Submit or Appeal"). Real submit-a-coffee / appeal-a-score form, unchanged in structure. Real bug found and fixed: legacy's own comment admitted "In production this would POST to a tRPC endpoint" but in the meantime wrote the submission to localStorage and showed "Received. We'll review your submission" regardless — actively misleading, since nobody would ever see a localStorage-only write. Replaced with a real mailto: fallback pre-filled with the form fields, same honest-degradation pattern as first-sip-email-capture.tsx — no fake success state. Verified live: 200 OK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/prescription</t>
-  </si>
-  <si>
-    <t xml:space="preserve">personalized "prescription", ported from BrewSoulPrescriptionFull.tsx (the file legacy's router actually uses — BrewSoulTools.tsx's same-named export is dead/unrouted, same shadowed-file trap as /brewsoul/health). Real 5-step questionnaire (genetics/timing/health/flavor/budget) generating a real, deterministic prescription (generatePrescription — real roast/cup-count/brand/pricing/warning logic), all ported unchanged and verbatim. Legacy's trpc.coffeePrescription.generate AI-enhancement mutation doesn't exist in this migration — dropped along with its "AI ANALYSIS LOADING..." block, which would otherwise spin forever and never resolve; the real prescription itself never depended on that call, it's already fully computed client-side. Same bespoke earthy "science" palette as /brewsoul/health kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/chains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Top 100 Coffee Chains" ranking (not supply-chain visualization — that's /brewsoul/economics//brewsoul/follow-the-dollar; this is chain rankings). Real 100-chain dataset extracted from legacy's computed CHAIN_RANKINGS export (5 real weighted dimensions → aggregate → S-F tier) via a one-off tsx script (same approach as brewsoul-coffees.ts) into lib/content/brewsoul-chains.ts, with a new ChainEntry type added to intelligence-engine/types.ts. Real tier/type filters, search, and per-chain expand, unchanged, extracted into components/brewsoul/chains-explorer.tsx. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/biodynamic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">biodynamic content. The complete real census of Demeter-certified biodynamic coffee: 3 real source farms, 6 real roasters/brands with real product tables and pricing, real nutritional-science compounds, a real cost calculator, and a real impact/tokenization section, all ported unchanged and verbatim. Dead Manus hero image dropped for a CSS gradient. The 3 genuinely interactive pieces (click-to-expand farms/roasters, cups-per-day cost slider) split into components/brewsoul/{biodynamic-farms,biodynamic-roasters,cost-calculator}.tsx client islands so the rest stays a Server Component. Same bespoke earthy "science" palette as /brewsoul/health and /brewsoul/prescription kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/decaf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decaf content ("Paint Stripper or Pure Water?"). Real 3-process breakdown (methylene chloride/Swiss Water/supercritical CO₂), 13 real clean-decaf brands ("Hall of Fame"), 10 real methylene-chloride brands ("Wall of Shame," with real Clean Label Project lawsuit citations), a real carbon footprint comparison, real decaf health science, and a real price-comparison table, all ported unchanged and verbatim. Legacy's manual document.title/&lt;meta keywords&gt; mutation in a useEffect (a real anti-pattern — Next's generateMetadata already owns the head) dropped for the real metadata export. Real bug found and fixed: the 13-brand FAME dataset was initially exported from the "use client" decaf-fame.tsx component file and imported into the Server Component page for its price-comparison table — non-component exports from a client module aren't available across the RSC boundary, which threw FAME is not iterable at runtime (only caught by live verification, not typecheck/lint). Moved the data to a plain lib/content/brewsoul-decaf.ts module instead. The 2 genuinely interactive pieces (click-to-expand Hall of Fame, reveal-toggle Wall of Shame) split into components/brewsoul/decaf-{fame,shame}.tsx client islands. Same bespoke earthy "science" palette as the other /brewsoul deep-dive pages kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/esoteric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rare-coffee content ("Esoteric Coffee Index"). Real 9-coffee index across 2 tiers (Panama Geisha, Yemen Mokha, Liberica, Eugenioides, Wush Wush, Sidra, Pink Bourbon, Bourbon Aji, Sudan Rume) with real tasting notes, rarity scores, and real named buy sources, plus a real acquisition-priority list and explorer scorecard, all ported unchanged and verbatim. Real content gap found, not fixed: legacy's own "Top 10 Acquisition Priority" list and scorecard table both reference "Laurina" as a 10th entry, but no coffee card for it exists anywhere in the source dataset — ported as-is rather than inventing card content that was never written. Zero client-side state anywhere in this page (only CSS-able hover) — ships entirely as a Server Component. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/cities + /brewsoul/cities/[slug]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">city directory + detail ("City Intelligence Module"). Real 25-city leaderboard (name/state/grade/score/tagline/verdict/live stats), a real 7-dimension scoring methodology, and real national + universal/nuanced chain report cards, all ported unchanged and verbatim into lib/content/brewsoul-cities.ts. Real data-completeness note, not a bug: legacy's own comment admits only Portland has full shop-by-shop data (25 real best + 5 real worst shops with real blurbs/scores/order-this/skip-this) — the other 24 cities have real city-level stats but empty shop/chain/bridge-drink/non-coffee arrays; legacy's own UI already handles this honestly (a real "Full data coming soon" state on both the card and detail page, not fake data) — preserved exactly, verified for both Portland (full tabs) and Seattle (coming-soon state). Grade filter, methodology modal, and chain-toggle interactivity in components/brewsoul/cities-explorer.tsx; per-city tab switching and per-shop expand in components/brewsoul/city-detail-tabs.tsx. Detail route uses generateStaticParams over all 25 real slugs. Scroll-linked parallax and floating-particle backgrounds dropped, same decoration call made throughout this migration. Real image-hosting gap flagged, not silently worked around: the 25 city hero photos are real, live Unsplash URLs (not a dead Manus proxy) but aren't yet uploaded to Sanity per this repo's own image convention — added images.unsplash.com to next.config.ts's remotePatterns as an interim measure rather th</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real master page index ("Everything Inside BrewSoul," not a roaster directory — that's /brewsoul/roasters). Real 6 categories with real page descriptions/icons, unchanged; the underlying data already lived in lib/content/brewsoul-directory.ts (built earlier this phase to power CategoryBadge) — this route is where it finally becomes a real browsable page. Category filter extracted into components/brewsoul/directory-explorer.tsx. Fixed the stale "Browse All 103 Coffees" label (real count is 107) by dropping the hardcoded number from the shared data module — benefits every other consumer of that module too. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/brewsoul/guest + /brewsoul/guest/shanita-nicholas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">guest series index + profile ("Tony G Guest Series"). Real single guest entry (Shanita Nicholas — real headline/teaser/tags) on the index, and the real 10-question interview on the detail page (Fair Trade economics, roasting mythology, the C Market, regenerative vs. sustainable, origin-roasting economics vs. Fair Trade, blockchain traceability, pre-harvest financing — real substantive answers with real citations), all ported unchanged and verbatim into components/brewsoul/shanita-interview.tsx. Legacy's guest photo (/api/img/brewsoul-orig_84eb4bc9.jpg) was the same dead Manus proxy confirmed 404 throughout this migration — dropped for a plain initial avatar on both pages rather than a broken headshot. Per-question expand/collapse, "Expand/Collapse All," and the real Twitter/LinkedIn/copy-link share row are genuinely interactive, split into client islands. Verified live: 200 OK on both, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shared: port BrewSoulLayout, CategoryBadge, JourneyBar, NextSteps as Next.js layout/components</t>
-  </si>
-  <si>
-    <t xml:space="preserve">app/brewsoul/layout.tsx + components/brewsoul/{brewsoul-nav,category-badge,journey-bar,next-steps}.tsx, all built and reused by every /brewsoul/* route above.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kava shared foundation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">app/kava/layout.tsx + components/kava/kava-nav.tsx (KavaNav/KavaFooter, 10 real nav items) + components/kava/kava-ui.tsx (KavaHero/KavaSection/KavaSectionTitle/KavaCard/KavaBadge/KavaDivider/KavaDisclaimer, converted from legacy inline style={} to Tailwind + new --kava-* tokens in globals.css). Added /kava to site-chrome.tsx's SUPPRESSED_PREFIXES (self-contained sub-site, same pattern as BrewSoul and /attention-theft). Real dead link fixed: legacy nav pointed at /pri, which legacy's own App.tsx never routed (only /psychedelic-readiness-index exists) — corrected.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/kava (home)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 module cards, "Threshold Doctrine," "Sacred Masculine Triad" (Mezcal/Kava/Peyote), 4 market stats, all ported unchanged. Verified live: 200 OK, exactly 1 header/1 footer (chrome suppression confirmed), typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/kava/origins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real migration timeline (6 Pacific nations, ~3000 BCE–1000 CE), real 6-island selector (Vanuatu/Fiji/Tonga/Samoa/Hawaii/Pohnpei, each with real facts/ceremony/cultivar/safety content), and the real Noble vs. Tudei safety comparison, all ported unchanged and verbatim. Island-selector interactivity in components/kava/origins-explorer.tsx. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/kava/interactions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real 24-substance drug interaction database (real severity ratings across an 11-value scale, real pharmacological mechanisms, real PRI protocol guidance) and real 5-enzyme CYP450 inhibition profile, ported unchanged and verbatim. Search + severity-filter interactivity in components/kava/interactions-explorer.tsx, using a precomposed SEVERITY_CONFIG class lookup (not string-built classes — same Tailwind static-scanner rule enforced elsewhere this migration). Legacy's unused Download icon import (dead code, no export feature attached to it) not ported. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/kava/science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real 6 major kavalactones (real receptor mechanisms, real PRI relevance) and real 11-item combined pharmacological profile, ported unchanged into lib/content/kava-science.ts. RSC-boundary bug caught proactively before shipping: initially drafted KAVALACTONES as an export of the "use client" chemotype-decoder.tsx, which would have thrown the same TypeError: X is not iterable already hit once this migration on /brewsoul/decaf when the Server Component page tried to import it — moved to the plain data module before ever running it. Chemotype decoder tool (enter e.g. 4-2-6-5-3-1, see dominant kavalactones) kept as the real interactive client island. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/kava/assessment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real 5-domain, 20-question PRI readiness assessment (somatic/psychological/relational/cultural/integration), real per-domain point weights, and real 4-band recommendation scoring (CLEARED/CONDITIONAL/DEFER/NOT READY), all ported unchanged into components/kava/assessment-quiz.tsx. Fully stateful (domain navigation, per-question answers, results view), so kept as a single client island per this migration's established pattern for multi-step assessments. Domain and recommendation accent colors (5 + 4 distinct hexes, none matching the --kava-* brand palette) precomposed into literal DOMAIN_STYLES/RECOMMENDATION_STYLES lookup objects rather than style={}, avoiding the dynamic-class bug already caught twice this migration (chains-explorer.tsx, biodynamic/page.tsx). Real backend gap, handled honestly: legacy's AssessmentResultActions took sessionId/serialized-answers props feeding a trpc.assessments.submit mutation this migration never built — used the already-simplified, print-only AssessmentResultActions (components/assessments/result-actions.tsx, built during Phase 9) instead of reproducing a submit call with no backend. Verified live: 200 OK, real domain/question content confirmed in rendered HTML, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/kava/hawaii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real ICE/meth crisis statistics (Quest Diagnostics 410% figure, Hawaii DOH conviction rates, law enforcement seizure data), real dual crisis/revival timeline (1985–present), the real (explicitly-labeled hypothesis, not proven) pharmacological alignment table, and real recovery resource listings, all ported unchanged and verbatim. Fully static, no client island needed. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/kava/myths</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real 7-myth evidence review (2002/2014 European kava ban and reversal, WHO findings, CYP2D6 metabolism differences by population, chemotype/preparation distinctions) and the real closing takeaway, ported unchanged. Expand/collapse interactivity in components/kava/myths-explorer.tsx, verdict colors (3-value enum) precomposed into a literal VERDICT_CLASS lookup. Extended shared KavaCard (kava-ui.tsx) with an optional onClick prop to support this — first Kava page needing a clickable card. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/kava/caffeine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real CYP1A2 inhibition mechanism (56%, the same pathway grapefruit juice uses on medications), real caffeine cutoff protocol, and the real kava-vs-coffee comparison table, ported unchanged. Fully static, no client island needed. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/kava/products</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real 5-category product index (ceremonial powder, fresh frozen, RTD beverages, supplements, kava bars) with real named vendors/cultivars/chemotypes/pricing/PRI ratings and real outbound buy links (all live vendor domains, not Manus proxies — no image assets on this page to check), ported unchanged into components/kava/products-explorer.tsx. Category-tab interactivity kept as the client island. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/kava/certification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real 12-module, 80-hour facilitator curriculum, real 3-tier certification structure (Practitioner/Threshold Facilitator/Master Facilitator), and real prerequisites list, ported unchanged. Fully static, no client island needed; legacy's wouter cross-links replaced with next/link. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRI shared data: lib/content/pri-data.ts (copied verbatim from legacy pri/data.ts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real 39-medicine pharmacopoeia, 50+ questions across 6 domains, MAO-B interaction matrix, medication interaction guide, crisis/integration resources, pathway questions), lib/content/pri-safety-data.ts (verbatim safety data merge source), lib/content/pri-medicine-images.ts (verbatim real CloudFront hero-image map, all spot-checked 200 OK — RampRate's own CDN, already whitelisted, not Manus), lib/content/pri-shared.ts (the real scoring engine — computeScores/READINESS_LEVELS/getMedicineWithSafety — extracted to a plain module per the RSC-boundary lesson from /brewsoul/decaf and /kava/science). Added --pri-* CSS custom properties to globals.css (this subsystem's own purple/parchment/near-black palette, same pattern as --kava-/--crusade-) since Phase 7's PRI section spans 9 more routes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/psychedelic-readiness-index (core tool)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">the real hero, 39-medicine grid with compare/save/bookmark tooling, MAO-B interaction matrix, medication interaction guide, crisis resources, the real 5-state assessment flow (philosophy intro → readiness quiz → pathway &amp; access questions → legal disclaimer gate → results), medicine detail modal (overview/safety/correction tabs), testimonials, and ImpactSoul cross-promotion, all ported unchanged and verbatim into components/pri/psychedelic-readiness-index.tsx plus supporting client islands (disclaimer-gate.tsx, medicine-modal.tsx, safety-section.tsx, correction-form.tsx, share-bar.tsx, cinematic-band.tsx). Kept as one client island — a single state machine drives which section renders, same call made for other large multi-step assessments this migration. Real hero/section photography (8 CloudFront images) kept via next/image; legacy's purely decorative glitch-scanline overlay divs and CSS shimmer/glow @keyframes dropped (no framer-motion — CONTRIBUTING.md rule 5 — and "decoration not worth the cost," same call made throughout this migration).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRI: /peyote-mescaline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MescalineDeepDive, real receptor pharmacology table, the real "Latuda Mirror" same-target-opposite-action comparison, real clinical outcomes (Agin-Liebes et al. 2021, n=452), the real 16-row pharma-to-plant alternatives table, real supplement protocol (pre/day-of/post-integration), real mescaline-specific PRI dimension scores, the real medicine-selector comparison table, and real sources, all ported unchanged and verbatim into lib/content/pri-mescaline-module.ts (copied verbatim) + app/peyote-mescaline/page.tsx. Fully static except the pharma-table expand toggle, extracted into components/pri/pharma-table.tsx; shared PriSection/PriEyebrow wrapper (components/pri/pri-section.tsx) introduced here for reuse by the remaining PRI deep-dive modules. All 8 real section photos (CloudFront) spot-checked live before use; legacy's purely decorative glitch-scanline overlays dropped. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRI: /iboga-ibogaine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IbogaDeepDive, "The Plant vs The Isolate": real alkaloid-profile comparison, real receptor pharmacology, real head-to-head iboga-vs-ibogaine table, real clinical outcomes (Mash/Noller/Schenberg/Brown &amp; Alper/Cherian/Williams — including the 2024 Stanford Nature Medicine SOF-veteran data and the 2026 19,071-patient safety analysis), real pharma-to-plant alternatives, real supplement protocol, real dimension thresholds, real medicine selector, Tony's real first-hand account of sitting ibogaine at The Mission Within, real hard-stop contraindications, a real 9-facility directory (with the 2 facilities legacy explicitly removed and why), real Nagoya Protocol / extractive-capitalism argument, real 2026 US legal-status rundown, the embedded Iboga Compass v2 documentation section (components/pri/iboga-compass-section.tsx, its own client island for the question-group toggles), and real sources — all ported unchanged and verbatim into lib/content/pri-iboga-module.ts + lib/content/pri-iboga-compass-data.ts (both copied verbatim) + app/iboga-ibogaine/page.tsx. Fully static except the pharma-table expand toggle (components/pri/iboga-pharma-table.tsx) and the compass section's toggles; reused the shared PriSection/PriEyebrow wrapper from the mescaline module. All 5 real hero/section photos (CloudFront) spot-checked live before use. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRI: /iboga-compass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IbogaCompassAssessment, the real interactive 28-question / 7-section compass (outcome/medical/approach/logistics/geography/personal/aftercare), the real drag-or-arrow priority-rank step (top dimension ×2.0, bottom ×0.5), the real facility-scoring engine, and the real results view (matched facilities with real "why this matched" reasoning and real elimination reasons), all ported unchanged and verbatim. lib/content/pri-iboga-compass-engine.ts (real scoring logic — weight deltas, hard filters, substance bonuses, priority-rank application, facility scoring) and lib/content/pri-iboga-facility-data.ts (real facility directory + substance-bonus data) both copied verbatim from legacy rather than hand-transcribed, given this is the actual matching algorithm — correctness matters more here than anywhere else in this migration. Uses this site's own brand-gold/foreground/muted-foreground design tokens rather than the pri-* palette — legacy's own hex here (#8B6914) is an exact match for brand-gold, confirming this one page always used the main site identity, not a PRI-specific one. Real backend gap handled honestly: legacy's lead-capture gate posted a rich structured payload (question-by-question answers, top facility matches, primary goal, budget range) to trpc.assessments.submit (no backend built for this migration) — replaced with a mailto: to Tony carrying the same structured summary, same pattern used throughout this migration; the meaningless "Submitting..." pending state and its e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRI: /pri-calibration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forced-rank calibration study, the real Bradley-Terry pairwise-comparison model (all 15 unique pairs of the 6 PRI dimensions), the real drag-or-arrow full ranking step, real methodology copy (acquiescence-bias explanation, the 4 headline validation stats), and the real Monte Carlo validation metrics (lib/content/pri-efficacy-data.json, copied verbatim from legacy — also feeds /pri-efficacy below), all ported unchanged into components/pri/calibration-assessment.tsx. Real backend gap, handled honestly: legacy's "Contribute to Research?" opt-in phase posted to trpc.priCalibration.submit (no backend built for this migration), and the results view's "Community Data" section read a live trpc.priCalibration.stats aggregate query showing other users' scores — neither has an honest backend-free equivalent (a cross-user aggregate can't be faked locally, and a research opt-in toggle with nothing behind it would be dishonest UI, the same call already made dropping the main PRI results page's inert research-pool checkbox). Both dropped; the flow goes straight from ranking to results. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRI: /pri-efficacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">psychometric validation dashboard, the real Monte Carlo simulation results (10,000 synthetic respondents), real classification-accuracy comparison, real dimension-priority distribution (the real first-dimension-inflation finding), real test-retest reliability and entropy metrics, and the real methodology writeup, all ported unchanged into app/pri-efficacy/page.tsx, reading the same lib/content/pri-efficacy-data.json also used by /pri-calibration. Real backend gap, handled honestly: legacy's "Live Calibrations" tab read a live trpc.priCalibration.stats query — since /pri-calibration's own submit call was already dropped (no backend, see that page's port note), this tab would permanently render "0 total calibrations, no data yet," a dead feature masquerading as a live one. Dropped entirely rather than ship a perpetually-empty tab; only the real, fully-populated Simulation view ships — which also means this page has no state left at all, so it's a plain Server Component now instead of a client one. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRI: /pri-research Built 2026-10-06 behind the login: admins are the emails in ADMIN_EMAILS; everyone else gets live's "Access Denied"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Totals, anonymized opt-in table, admin-only CSV export (/pri-research/export). /pri-calibration regained legacy's "Contribute to Research?" step and now saves every calibration anonymously to pri_calibrations (opt-ins flagged). Was: — Deferred, not skipped (access-model question resolved by inspection). Read the real legacy source: this is a genuine admin-only dashboard (useAuth() gated to role === "admin") showing trpc.priCalibration.researchData — the same calibration-submission backend already confirmed absent and intentionally not built for /pri-calibration and /pri-efficacy (see their port notes). No admin-auth system exists anywhere in this Next.js migration yet either. So this isn't just an access-control decision — even fully wired up, the page would have zero real data to show, forever. Not worth building an admin dashboard against a backend this migration has twice already decided not to build. Added to "Explicitly deferred" below alongside the other admin dashboards; revisit only if/when both a real admin-auth system and a real calibration-submission backend exist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRI: /facilitator-index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"The Facilitator Index: Know Who You Go With," the real 15-question quick-intake archetype quiz (real Bradley-Terry-style axis derivation, fully client-computed via deriveArchetype()), the real 108-item, 12-band (plus Band 0) practitioner self-assessment instrument, and the real methodology prose (rationale, code/tier system, data-handling policy, Reciprocity Gate, Corroboration token system), all ported unchanged and verbatim into lib/content/facilitator-index-data.ts (single authoritative content source) + components/facilitator/* + app/facilitator-index/page.tsx. Real content-drift bug found and fixed: legacy shipped two divergent copies of the same "108 items" — the on-page JSX and a separate printFacilitatorQuestions() print/PDF export using an older, different set of item numbers and band groupings (missing the on-page "Twenty-Five Traditions and Protocols" band entirely) — the print export was never updated when the on-page instrument was revised. Used the on-page version (the one actually shown to visitors) as the single source of truth and rebuilt the print export to generate from that same data, so the two can never diverge again. Real fake-data found and dropped: legacy's PeerStats component's own comment admits its numbers ("163 practitioners mapped so far," etc.) are "seeded, realistic-feeling" — fabricated, not real — dropped entirely, same principle as BrewSoul's stale "reads" counts; UsageCounter's hardcoded 160-practitioner fallback (shown forever since no ba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Port shared safety/medicine data modules (safety-data.ts, medicine-images.ts) as typed .ts content in the new codebase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">done as part of the main PRI page above (lib/content/pri-safety-data.ts, lib/content/pri-medicine-images.ts, both copied verbatim).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/attention-theft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">consolidated mega-page. Real content ported in full across all 9 sections (hero, The Sacred, The Heresy economics data + full breakdown table + sources, the 10 Weapons, Legal Arsenal w/ filter + letter template, AI Blocker Finder quiz, Report a Spammer, closing vow + related reading) — AttentionTheft.tsx used as the single source, the 5 pre-consolidation sub-pages not resurrected (they never existed in this codebase anyway). Section "glamour" photography is real, live imagery on RampRate's own CloudFront (already whitelisted in next.config.ts as a non-Manus, permanent host — confirmed all 7 URLs 200 before using them), rendered via next/image. Real backend gap found and handled honestly: legacy's Wall of Shame (a live trpc.spam.wallOfShame ranked list) and the Report form's trpc.spam.submit both depended on a spam-tracking backend that this migration explicitly defers (see "Explicitly deferred" list below: "/youve-been-reported, /spamtoast, admin spam tooling") — rather than fake a public database with no real data behind it, the report form now composes a mailto: to Tony (same honest non-fake-success pattern as newsletter-popup.tsx), and the ranked Wall of Shame list isn't reproduced. Two simplifications matching precedent set elsewhere in this migration: legacy's "Fraunces" serif (loaded for this one page only) was dropped for font-heading (Playfair Display, already loaded — same call made on /akbar), and the glitch/VHS/ember-particle/shattered-glass decoration layer was dr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy anchor redirects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/attention-theft/economics, /blocker-finder, /legal, /weapons, /report → /attention-theft#&lt;anchor&gt; via next.config.ts redirects(). Verified live: all return real 308s to the correct anchor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Port ManifestoLayout scroll-tracking wrapper behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">components/manifesto/manifesto-nav.tsx tracks which section is in view on scroll and highlights the matching nav pill (desktop + mobile), real behavior kept per this line item rather than simplified away.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HumanOS section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/humanos, /humanos/philosophy, /humanos/ecosystem, /humanos/resources, /humanos/connect, /humanos/path-to-here, ported from _legacy-manus-app/client/src/pages/HumanOS.tsx + humanos/*.tsx. The top-level HumanOS.tsx (an iframe embed of an external manus.space site) turned out to be dead code, never wired into legacy's router — the real, routed implementation is HumanosHome/HumanosPhilosophy/HumanosEcosystem/HumanosResources/HumanosConnect/HumanosPathToHere behind HumanosLayout, which is what got ported, with its own nested layout.tsx (route now added to site-chrome.tsx's SUPPRESSED_PREFIXES so the main SiteHeader/SiteFooter don't double up around HumanOS's own nav/footer). Real content in full: the Maximizer-vs-Satisficer framework and "Boiling the Human"/"Maximizer Trap"/"Conscious Satisficer" philosophy sections, the full ecosystem roster (1 mentor, 8 advisors, 3 partners, 29 clients), all 4 transformation playbooks + 3 daily-practice protocols + 8-book reading list, all 4 connect channels, and the 6-entry "Path to Here" timeline (2010 H+ Summit through 2025). Real bugs fixed: every "Take the Diagnostic" CTA site-wide pointed at /assessment, an 8-question Maximizer/Satisficer quiz that was never actually built anywhere (legacy's real /assessment and /assessments routes are two different, unrelated quiz sets) — redirected to /humanos/philosophy, which delivers the actual promised content; Connect's "Read the Living Declaration" pointed at /manifesto, a dead redirect stub in le</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/find-your-me (+ /find-my-me, /discover)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Find My — To Find Your We," the ecosystem hub assessment and by far the largest page in Phase 9. Real 5 NLP-driven questions, 6 dimensions (relationships/purpose/body/truth/tribe/consciousness), and 6 real archetypes (each with a real description, real blog article links, real satellite-site links, real "go deeper" forward-references, and a real share text) ported unchanged and verbatim into a new lib/content/find-your-me.ts data module (kept separate from the component given the file's exceptional size, same pattern as brewsoul-directory.ts). All 17 unique blog article slugs referenced across the 6 archetypes were individually verified live (200 OK) against this migration's real Sanity blog before porting — zero dead article links. Real accuracy fix: legacy's "Full Ecosystem Directory" (26 items across 5 categories, with a real LIVE/COMING pill UI already built for exactly this purpose) marked everything "live," including several routes that don't exist anywhere in this migration yet (/find-my, /the-mirror, /assessments/dharma-finder, /assessments/consciousness-scale, /assessments/grant-study, /flow-circuit) — corrected each item's status to this app's actual current build state rather than shipping false LIVE labels on what would be 404s. Real completeness fix: added Find Your Peptide and Find Your Sexuality to the directory (Body &amp; Temple and Love &amp; Belonging) — both are real, fully-built assessments elsewhere in this migration that didn't exist yet when legacy was writte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/find-your-therapy (+ /find-my-therapy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real 25 questions across 6 dimensions (Cognitive/Somatic/Relational/Depth-Unconscious/Altered States/Integrative), 6 real therapeutic modalities (each with a real description, "how it works," best-for/not-ideal-for lists, real named pioneers, and real book/directory resources), and the real archetype-matching logic (highest-scoring dimension wins) ported unchanged and verbatim. Three real stale-count bugs found and fixed: legacy's own file-header comment claimed "10 questions," its AssessmentIntro stats prop claimed 20 — neither matches the real 25-item array (the scoring code's own maxPossible = 30 // rough max per dimension with 25 questions comment confirms 25 is correct) — replaced both with live QUESTIONS.length. Real dead-link bug fixed: legacy's "Journey Continues" grid linked "Find Your Spirit"/"Find Your Religion" to external findmyassess-9eekxcob.manus.space stub URLs (dead Manus domain) despite this migration already having real, fully-built internal pages at /find-your-spirit and /find-your-religion — repointed to the real internal routes, and corrected Religion's stale "15 Questions" badge to the real 20. Real accent-color inconsistency fixed: legacy passed accentColor="#7B1FA2" only to the landing screen, then hardcoded brand-gold everywhere on the results screen instead — threaded one ACCENT constant through intro/radar/result-actions consistently, matching every other assessment in this migration. The "Also Worth Exploring" related-modality cards were dropped </t>
-  </si>
-  <si>
-    <t xml:space="preserve">/find-your-sake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real 20 questions across 5 dimensions (Palate/Ritual/Terroir/Philosophy/Season) and the real 5 sake profiles (each with real Japanese name, tasting notes, food pairings, serving temperature, named producers with region/note, and further-reading resources) ported unchanged and verbatim. Legacy's own AssessmentIntro stats prop claimed "15 questions, 6 dimensions" — didn't match the real 20/5 implementation — replaced with live QUESTIONS.length/DIMENSIONS.length counts, same fix pattern already applied on /find-your-attachment-style and /find-your-sexuality. Two real bugs found and fixed: (1) legacy's "Journey Continues" list read "Find Myzcal" — a literal typo for "Find Your Mezcal" — corrected. (2) legacy's JSX rendered &lt;WhatsNext /&gt; (a full page section) nested inside the small "Retake the Tasting" &lt;button&gt; element — moved to a proper top-level section, same class of nested-interactive-content bug already fixed on /find-your-religion. The dark GlassPanel treatment (near-black translucent cards with light cream text, sitting on the page's own light parchment ThemedBackground) was kept as a real, intentional design choice rather than "fixed" to this migration's usual light-card convention — unlike the light-text-directly-on-light-background contrast bugs found on Style/Sexuality/Peptide/Religion, the text here sits inside its own correctly-contrasted dark card. SacredGeometryBg's canvas-based floating rice-grain particles dropped (same decoration-not-worth-the-JS-cost call made</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/find-your-spirit (+ /find-my-spirit), along with a shared PDF-export component the rest of Phase 9 can reuse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real 35 questions, 10 dimensions, and the 6 real spiritual traditions (each with real description/practices/key texts/figures/modern expressions/growth edge) ported unchanged and verbatim — legacy's own file-header comment claimed "12 archetypes," but only 6 TRADITIONS actually exist in the code; ported the real 6, not the stale doc comment. The real weighted tradition-matching logic (top 3 dimensions per tradition, weighted 3/2/1) is unchanged. Ported components/assessments/result-actions.tsx from legacy's AssessmentResultActions — kept only the real, backend-free "Download PDF" action (browser print); the "Send to Tony"/"Keep Private" buttons posted to an unbuilt trpc.assessments.submit and weren't reproduced, same honest-degradation pattern used throughout this migration. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/find-your-religion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real 20 questions across 8 dimensions, 8 real spiritual/philosophical archetypes (each with real description/practices/key texts/figures/resonant traditions/growth-edge tensions), and the real scoring/matching logic ported unchanged and verbatim. Real bug found and fixed: legacy's own JSX rendered &lt;AssessmentResultActions&gt; nested inside the "Retake Assessment" &lt;button&gt; element — a button inside a button, invalid HTML — fixed by rendering it as a sibling instead, same fix pattern already applied on /find-your-spirit. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/find-your-diet (+ /find-my-diet)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real 15 questions, 6 real archetypes (with descriptions), and the real nearest-neighbor archetype-matching logic ported unchanged. Legacy's dead JourneyTracker import wired in for real (see journey-tracker.tsx). /find-my-diet → /find-your-diet redirect added. Verified live: 200 OK, full quiz flow, redirect confirmed 308, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/find-your-movement (+ /find-my-movement), along with the shared assessment foundation the rest of Phase 9 depends on</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ported components/assessments/{themed-background,assessment-intro,email-gate,whats-next}.tsx from legacy's ThemedBackground/AssessmentIntro/EmailGate/WhatsNext — real content/behavior unchanged, with 2 real fixes along the way: (1) EmailGate now posts to the real /api/subscribe Route Handler (built earlier this migration) using the exact find-your-&lt;slug&gt; source keys already defined in lib/content/kit-source-tags.ts's KIT_TAG_MAP — legacy's own assessment-gate:&lt;slug&gt; prefix didn't match any tag in that map, so this is a genuine improvement, not just a port. (2) ThemedBackground's per-theme decorative particle field + SVG sacred-geometry overlay + 2 extra radial-glow layers dropped (same "not worth the cost" call made repeatedly elsewhere) — the real per-theme base gradient (16 themes) is kept, precomposed as one literal Tailwind class per theme rather than assembled from fragments. find-your-movement-quiz.tsx ports all 15 real questions and the real 6-dimension (Strength/Flexibility/Endurance/Mindfulness/Community/Adventure) scoring unchanged; the legacy JourneyTracker/useJourneyProgress import in the source file was dead code (imported, never rendered) and not ported. /find-my-movement → /find-your-movement redirect added (next.config.ts), same duplicate-route pattern as /find-my-tribe. Verified live: 200 OK, full quiz flow renders, redirect confirmed 308, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/find-your-sleep (+ /find-my-sleep)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real 15 questions, 6 real archetypes, and the real cascading archetype-match logic ported unchanged, including legacy's own real behavioral quirk of rendering JourneyTracker on every phase (not just results). One real duplicate-destination "Journey Continues" link pair dropped (see file's own port note), the one real distinct link (Find Your Diet) kept. /find-my-sleep → /find-your-sleep redirect added. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/find-your-coffee (+ /find-my-coffee)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real 15 questions, 6 dimensions (Roast Preference/Origin Curiosity/Brewing Ritual/Social Context/Caffeine Sensitivity/Flavor Complexity), 6 real archetypes (each with a real description and 5 real named coffee recommendations — roaster, origin, roast level, tasting notes, real "why" rationale), and the real archetype-matching logic (sum of each archetype's 2 primary dimensions, highest wins) ported unchanged and verbatim. This legacy page predates the shared ThemedBackground/AssessmentIntro component system the rest of Phase 9 is built on — it hand-rolled its own hero-image page shell — so it needed more normalization than most: its hero image (/api/img/coffee-orig_a935f111.jpg) was a dead Manus asset, dropped for the standard ThemedBackground light theme (added a new "coffee" warm-cream entry) instead of reproducing a broken background; the canvas bean-particle field, floating steam-wisp divs, and SVG sacred-geometry overlay all dropped (same decoration-not-worth-the-JS-cost call made repeatedly elsewhere). Real bug found and fixed: legacy read window.innerWidth directly during render (twice — to pick grid columns and flex direction), unsafe during SSR and a real hydration-mismatch source — replaced with responsive Tailwind classes. EmailGate's prop was legacy's assessmentName; ported using this repo's real assessmentSlug="coffee" to match find-your-coffee in KIT_TAG_MAP. Legacy imported useJourneyProgress for markComplete but never rendered a visible JourneyTracker, and nev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/find-your-kitchen. Real 15 questions (all rendered on one page at once</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a genuinely different, legacy-intentional UX from the other paginated quizzes, kept as-is) and the real dual-tracking scoring (answer score keys split into archetype tallies vs. 6 separate radar-chart dimensions) ported unchanged, including the 3 real "Journey Continues" links (one to already-built /find-your-diet, one forward-reference to /find-your-style). Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/find-your-style. Real 15 questions, 6 real archetypes, and the real (if crude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">legacy's own comment admits "Simple mapping for demonstration") threshold-based archetype match ported unchanged. Two real inconsistencies found and normalized: legacy's own inline styles used near-illegible light text on ThemedBackground's actual light pastel "style" theme (inconsistent with every other assessment in this migration); and legacy rendered &lt;JourneyTracker /&gt; defaulting to variant="dark" on a light results screen instead of the variant="light" every other assessment passes. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/find-your-attachment-style (+ /find-my-attachment-style, /find-my-we)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real 18 questions (legacy's own AssessmentIntro stats prop under-reported this as "15" — used the live QUESTIONS.length instead of repeating the stale number, same live-count discipline used elsewhere in this migration), the 4 real archetypes, and the real scoring/selection logic all ported unchanged, including the real closing note on attachment theory. Both alt-path redirects added. Verified live: 200 OK, both redirects confirmed 308, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/find-your-love-language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real 15 questions (incl. the negative-score "disconnect" question), 5 real archetypes with descriptions/tips, and Dr. Gary Chapman's real attribution note all ported unchanged. Verified live: 200 OK, full quiz flow, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/find-your-peptide (+ /find-my-peptide)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"The Peptide Clarity Index™." A real, evidence-cited 10-question assessment across 7 clinical axes, mapping to 16 real peptide archetype profiles — every question (with its real PubMed/journal citation), every profile's real primary/secondary peptides with mechanisms and evidence, suggested lab work, red flags, and stacking notes ported unchanged and verbatim (clinical-adjacent content, not paraphrased). The real Peptide Readiness Score, contraindication-flag screening, share buttons (Twitter/LinkedIn/email/copy — real, backend-free), and the real medical disclaimer are all preserved. Real hero image (CloudFront, confirmed live) kept via next/image. Reused the simplified AssessmentResultActions (PDF-only) built for /find-your-spirit. Same light-text-on-light-background contrast bug already caught elsewhere was fixed here too. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/find-your-sexuality (+ /find-my-sexuality)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A research-informed assessment across 6 real dimensions, grounded in real cited research (Klein Sexual Orientation Grid 1978, Kinsey Scale 1948, Lisa Diamond 2008, Sari van Anders 2015) — real 16 questions (with per-question research context notes), real 12 archetypes (each with a real description + research note), and the real scoring/selection logic all ported unchanged and verbatim, including the real closing disclaimer. Legacy's own AssessmentIntro stats prop claimed "20 questions, 7 dimensions" — didn't match the real 16/6 implementation, used the live counts instead. Legacy's results screen also used light grey text on the real light pastel theme background (same low-contrast bug already caught on /find-your-style) — normalized to dark ink. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/find-my</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Find What's Yours," the real destination of the homepage's "Diagnose" door (confirmed by grepping lib/content/home-doors.ts's /find-my href) and of whats-next.tsx's "Take Another Assessment" link, both already pointing here as forward-references before this page existed. Legacy's 26-item ALL_LINKS directory (Featured + 6 categories) ported unchanged and verbatim into lib/content/find-my-directory.ts. Real accuracy fix, same pattern as /find-your-me's own port note: cross-checked all 26 destinations against the real route list — /find-your-ev, /life-assessment, and /soulscore (at the time) didn't exist yet, rendered as real "Coming Soon" cards instead of links that would 404 (dharma-finder/consciousness-scale/grant-study have since shipped and now flip to live — see below). Real reuse, not re-derivation: every item whose destination already exists in find-your-me.ts's audited DIRECTORY pulls that entry's real hook text and status at build time via a lookup helper, instead of hand-copying a second, driftable copy of the same facts. Two real live destinations added that legacy linked but find-your-me.ts's directory didn't track: /brewsoul (confirmed 200) and the external findmystem-s3lknc4h.manus.space sibling tool (confirmed live), both using the same "real external sibling product" trust already established for the other manus.space tools. Legacy's dead Manus hero image dropped for ThemedBackground (theme="ecosystem"), same call as /find-your-me. AssessmentProgressBar (never </t>
-  </si>
-  <si>
-    <t xml:space="preserve">/assessments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Three Maps. One Journey," confirmed genuinely distinct from /find-my rather than a duplicate: /find-my is the wide 26-item ecosystem directory, /assessments is its own page for exactly 3 long research-grounded instruments (Dharma Finder / Consciousness Scale / Grant Study) that also happen to appear as one category inside /find-my's directory — legacy kept these as two separate pages, so the port does too. Real title/subtitle/description/time/icon/accent content for all 3 instruments ported unchanged and verbatim into lib/content/assessments-hub.ts, including the full "Why These Three" closing essay (Schmachtenberger/Hawkins/Harvard Grant Study triangulation). All 3 instrument cards now link live (dharma-finder/consciousness-scale/grant-study shipped alongside this page). Legacy's footer claim "Results saved for your return" was dropped — replaced with an honest line since nothing persists results yet. Added a real cross-link to /find-my. JourneyTracker reused unchanged; no EmailGate/AssessmentResultActions — pure preview/hub page with no quiz or results step of its own. Verified live: 200 OK, exactly 1 header/footer, real content in all 3 cards, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/dharma-finder (+ /assessments/dharma-finder redirect). Structurally different from every other Phase 9 quiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">legacy's real 25 questions are open-text reflection prompts, not multiple choice, distilled from Daniel Schmachtenberger's Dharma Inquiry and grouped into 4 real sections (Capacities/Values/Propensities/The Shadow Inquiry), each with a real framing quote, plus 3 real interstitial quotes shown between sections with the original 4-second auto-advance. All 25 questions, all quotes, and legacy's own keyword-matching generateDharmaProfile (deriving up to 3 archetypal roles and up to 4 core values from free-text answers, plus a completion-depth percentage) are ported unchanged and verbatim into a new dharma-finder-quiz.tsx. Real bug found and fixed: legacy's result-screen JSX rendered &lt;AssessmentResultActions&gt; nested inside the "Retake Assessment" &lt;button&gt; element — a button inside a button, invalid HTML — fixed the same way as /find-your-religion. Real dead-link bug fixed: "Journey Continues" linked to /assessments/consciousness-scale (repointed to the real /consciousness-scale) and /assessments/grant-study (dropped at the time, now live too). EmailGate (new here; legacy had none) is a real ecosystem-consistency addition. find-your-me.ts's ecosystem-directory status flipped from "coming" to "live" now that this page ships. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/consciousness-scale (+ /assessments/consciousness-scale redirect)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real 25 questions, each scored against David R. Hawkins' real 17-level Map of Consciousness (Shame 20 through Enlightenment 700+, final score = average of all 25 answers) — every question/option, every level's name/emotion/threshold, and getInsight's exact 6 tiers of interpretive copy ported unchanged and verbatim into a new consciousness-scale-quiz.tsx, along with the real live running-average indicator, visual scale gauge, full 17-level map, 6-month reminder, and X/LinkedIn/copy share. Since this assessment produces one composite score on a single axis rather than independent dimensions, a bespoke single-axis gauge replaces AssessmentRadarChart; per-level colors (17 known-at-build-time values) are precomposed literal Tailwind classes rather than assembled from hex fragments. Real Manus-dependency bug found and fixed: legacy's cinematic Q1 hero used a /api/img/consciousness-scale-hero-v2_085e0746.jpg Manus-proxied image — forbidden even temporarily per this migration's Zero-Manus rule — dropped for the plain question-card layout every other assessment uses; a real Sanity-hosted replacement is a tracked follow-up (see BLOG-IMAGE-BRIEFS.md-style tracking). find-your-me.ts's ecosystem-directory status flipped from "coming" to "live" now that this page ships. Verified live: 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/grant-study (+ /assessments/grant-study redirect)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Find Your Score," the real 25-question (5 per factor), 5-factor Harvard Grant Study life-satisfaction assessment (724 men, 1938–present, 85+ years — the longest-running study of human happiness). Every question, the 5 real factors (Warm Relationships/Adaptive Coping/Generativity/Career Satisfaction/Physical Vitality), every per-factor/per-tier insight (real named findings — Vaillant's "mature defenses," Erikson's generativity, Waldinger's quote), and the closing "Tony's Note" (Vaillant's "Happiness is love. Full stop." + Waldinger's "good relationships keep us happier and healthier") all ported unchanged and verbatim. Real nested-interactive-element bug found and fixed: legacy rendered &lt;AssessmentResultActions&gt; (its own &lt;button&gt;) literally inside the "Retake Assessment" &lt;button&gt; — same bug class already caught on /find-your-religion//find-your-sake — split into siblings. Real dead-link fix: "Journey Continues" pointed "Find Your Spirit" at a dead external Manus stub despite the real internal /find-your-spirit existing — repointed. Real ecosystem-consistency normalization: unlike every sibling "Find Your X" quiz, legacy skipped EmailGate entirely and went straight to results — added for consistency, plus new find-your-grant-study/find-your-dharma-finder/find-your-consciousness-scale alias keys in kit-source-tags.ts's KIT_TAG_MAP so EmailGate's fixed find-your-&lt;slug&gt; source prefix actually resolves to the intended tag instead of a generic fallback. resultSlug="grant-study" pas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/soulscore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SoulScore™, ImpactSoul's 12-dimension impact measurement engine (1231-line legacy file, the largest remaining port). Unlike the quiz-style "Find Your X" assessments, this is a live interactive calculator, not a Q&amp;A flow: entity-type picker, 12 weighted dimension sliders (Hawkins-scale Consciousness + 11 others), real-time score/grade/radar/auto-diagnosis, a benchmark table against 7 real entities (Patagonia, BP, Fortune 500 Avg, etc.), a 6-tier/30-factor supply chain drill-down, 20 "why every impact system failed" entries, a real Consciousness-Adjusted NPV calculator, and the gig-economy 5-layer stack comparison — all real content/formulas ported verbatim. Fixed: legacy's own SEO block described an unrelated assessment (stale copy-paste, replaced with real metadata); a div-pretending-to-be-a-button wrapping 30 nested range-input sliders (fixed to a real &lt;button&gt; + sibling content div); hardcoded intro/tab counts now read off real array lengths. No EmailGate (legacy never had one here — it's an open calculator, not a report unlock), matching /find-your-peptide's precedent. AssessmentResultActions wired with resultSlug="soulscore". journey-tracker.tsx's JOURNEY_MAP and /impact-dashboard's "Launch SoulScore Engine"/"Launch C-NPV Calculator" links (previously a disabled "Coming Soon" note) now point at the real page. This closes the real dead-end referenced from site-nav-data.ts (/soulscore appears twice in nav) and from /impact-dashboard — the last item in the STATUS.md dead-end</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/self-portrait</t>
-  </si>
-  <si>
-    <t xml:space="preserve">composite of completed assessments. Decision made: local-only (a real cookie, not Supabase — Phase 2 isn't provisioned yet). AssessmentResultActions (components/assessments/result-actions.tsx) takes an optional resultSlug and logs completions to a tg_assessment_results cookie via lib/assessments/result-log.ts, the same real-cookie-read-via-next/headers pattern already established by returning-visitor-hero.tsx/track-last-blog-visit.tsx — the page itself is a Server Component reading that cookie with zero client hydration step. Real, deliberate scope cut, not a silent one: legacy's SelfPortrait.tsx combined each assessment's own per-dimension scores (16 separate localStorage keys) into one composite radar chart across 15 unified dimensions, gated behind "5+ completed." This migration's result log only ever records that an assessment was completed, not its actual scored answers — building the real composite radar would mean threading a second, much larger data channel through every quiz. Shipped the honest subset instead: a real completed-assessments list (title, real completion date, retake link) plus a real "X of N completed" count and a "Still to Explore" section for the rest, via a new lib/content/self-portrait-catalog.ts. Wired resultSlug into the 7 remaining older "Find Your X" quizzes that already call AssessmentResultActions but hadn't been threaded yet (spirit/therapy/religion/sake/coffee/peptide/me) — /self-portrait now tracks 13 real assessments total. /find-my's "Sel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/the-mirror (+ /life-assessment)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uses mirrorData.json, real 6-dimension/18-question life assessment ("The Mirror") ported into a typed lib/content/mirror-data.ts. Legacy served the identical component at both paths; /the-mirror is canonical (it's the only URL every existing internal link already pointed to — nav, journey tracker, Find Your Me), /life-assessment permanently redirects there. Real dimension-averaged scoring, radar chart via the shared AssessmentRadarChart, and weakest-dimension article/satellite-site recommendations ported unchanged. A live Sanity check found only 27 of 85 legacy article slugs still resolve; recommendations now resolve server-side and defensively skip missing ones, matching legacy's own behavior. Fixed: a hydration-unsafe typeof window branch computing the share URL, three stale manus.space satellite URLs superseded by their current live counterparts already used elsewhere in this migration, and dead /assessments/*/external-stub links in the "Journey Continues" grid. Added find-your-mirror to kit-source-tags.ts's KIT_TAG_MAP and reconciled journey-tracker.tsx's stale 10-minute estimate to legacy's real "~4 minutes" claim. find-your-me.ts's ecosystem-directory status flipped to "live." Verified live: 200 OK on both paths, redirect confirmed, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/assessment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">confirmed via full legacy read this is not a "Find Your X" quiz (it predates that convention): it's Tony's own 3-way reader-path diagnostic — Builder / Crusader / Investor — 5 real questions, one point per matching answer, highest tally wins. Real questions and real archetype copy ported unchanged, reused from lib/content/archetypes.ts (already ported for /essays's archetype filter) rather than duplicated — added the page's ASSESSMENT_QUESTIONS to that same module since both come from the identical legacy source file. Preserved the real, distinct UX (no landing screen, no ThemedBackground/JourneyTracker — this page sits outside that ecosystem). Real bugs fixed: JS onMouseEnter/onMouseLeave inline-style hover hack replaced with Tailwind hover: classes; literal "..." pending-state text replaced with a real Loader2 spinner per house rule; dead trpc.subscribe.add replaced with a real POST /api/subscribe call. Real link audit: kept /impact-dashboard, /find-your-me, /living-declaration, and the real /blog/boiling-the-human-summit-harvard-kurzweil article as live links; /soulscore and /humanos are established forward-references used repeatedly elsewhere in this migration and both now ship too. The Human OS CTA reuses the border-red-800/30 text-red-800 treatment /living-declaration already established for the identical button instead of a new one-off raw-hex pair. AssessmentResultActions resultSlug="assessment" added (didn't exist when legacy was written). Added assessment-builder/as</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fix dead-end pages flagged in STATUS.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sake, therapy, and love-language all got real next-step navigation (WhatsNext + real "Journey Continues" links) during their ports — the last remaining one, soulscore, is now built (see above), closing this out.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Port shared radar-chart / PDF-export / email-gate components used across assessments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">components/assessments/{radar-chart,result-actions,email-gate}.tsx, built during Phase 9 and reused unchanged by all 15 "Find Your X" quizzes plus /find-your-me.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">src/lib/admin/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">guardrails (fixes the removed version's proxy.ts pattern, which missed the real src/proxy.ts), GitHub client (RRTONY/tonygreenberg-website), Sanity draft helpers, code-check.ts (ESLint + CONTRIBUTING.md house-rule patterns, now also Manus URLs and ellipsis loading text), seo-check.ts, tools.ts, mcp-server.ts, mcp-handler.ts, mcp-tool-context.ts (GitHub looked up lazily, so Sanity/SEO/code-check tools work without GITHUB_TOKEN).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per-person access via MCP_ADMIN_USERS (read/edit/write roles, tools filtered per role, calls logged, commits stamped [by &lt;name&gt;])</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mcp-auth.ts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rules gate: get_project_rules serves CONTRIBUTING.md + AGENTS.md + docs/ai/ guides with a rulesVersion; all 6 write tools require it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">project-rules.ts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">src/app/api/mcp/route.ts (header auth) + src/app/api/mcp/[token]/route.ts (token in URL).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">docs/ai/ knowledge base (README, TASK_GUIDE, PROJECT_STRUCTURE, project_mcp_server), linked from CONTRIBUTING.md.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@modelcontextprotocol/sdk ^1.30.0 re-added (approved 2026-09-29); GITHUB_TOKEN/MCP_ADMIN_USERS/MCP_SITE_ORIGIN documented in .env.local.example.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verified locally</t>
-  </si>
-  <si>
-    <t xml:space="preserve">auth (401/405), role filtering, rules-gate markers, token-in-URL route, code check, Sanity query, SEO check.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sign-in for the MCP server (OAuth 2.1, ported from ramprate-ui, 2026-09-30)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/oauth/authorize sign-in page + /.well-known metadata + register/authorize/token endpoints, stateless (signed tokens, no database), no new dependency. Verified end to end on a local production build. See docs/ai/project_mcp_server.md.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set GITHUB_TOKEN, MCP_ADMIN_USERS, MCP_LOGIN_PASSWORD, MCP_OAUTH_SECRET, MCP_SITE_ORIGIN, MCP_PUBLIC_ORIGIN in Netlify (done) (checked 2026-…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-07: all already set in Netlify). Left: connect Claude.ai to /api/mcp for real, and verify the GitHub flow end to end (branch → PR → deploy preview → publish_changes) against a real PR.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit a team-wide .mcp.json (URL only) once the production URL is settled.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google read-only tools added (2026-10-02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">check_analytics (GA4), search_console_sites / _performance / _inspect_url / _sitemaps (list only, no submit or delete), lighthouse_check_page (PageSpeed Insights). New files google-auth.ts, ga4-client.ts, gsc-client.ts, lighthouse-check.ts; no new dependency. Verified on a local production build through /api/mcp: 22 tools listed, GA4 returns real numbers (1,233 sessions in 7 days), the others return a clear "what's missing" error. Env vars added to .env.local.example.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">publish_changes fixed (2026-10-02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">it published every draft in Sanity (31 waiting for review today), so any one-line fix would have pushed them all live. Now it publishes only the drafts named in draft_ids; unknown ids are refused before anything happens (verified).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seo_check_page decoded &amp;#39; but not React's &amp;#x27;, so descriptions showed Tony Greenberg&amp;#x27;s and the length was off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed and verified (2026-10-02).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search Console access for the service account added by the team (2026-10-02); all four search_console_* tools verified with real tonygreenbe…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rg.com data (99 clicks / 1,663 impressions in 28 days, homepage indexed, sitemap 284 URLs, 0 errors, 82 warnings).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOOGLE_GA_CLIENT_EMAIL, GOOGLE_GA_PRIVATE_KEY, GA4_PROPERTY_ID_TONYGREENBERG set in Netlify (2026-10-02, via the Netlify API, values checked…</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> equal to .env.local; this plan can't limit a variable's scopes, so they're available to builds and functions). Used from the next deploy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per-request change system ported from ramprate-ui (2026-10-02, owner said yes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">, covering the 10 review points the team raised for RampRate's setup: (1) discard_change; (2) one request = one change with its own branch, PR and drafts, so publishing never takes another request live; (3) a review with pages affected, a server-written "what's included" line and preview links; (4) publish needs the review's reviewToken, and the rules make the AI ask "You are about to publish these changes to the live tonygreenberg.com website. Are you sure you want to continue?"; (5) list_change_history, also visible read-only in Studio under "Website change history" (new adminChange type); (6) undo_change; (7) before/after (automatic for Sanity, given by the AI for code); (8) preview_on_devices phone + laptop screenshots (needs GOOGLE_API_KEY); (9) the AI's plain summary plus the server's facts line; (10) Draft → Ready for review → Published / Discarded. Files: change-sets.ts, change-describe.ts, device-preview.ts, mcp-tool-context.ts, mcp-server.ts, github-client.ts (RampRate's full version), src/sanity/schemas/adminChange.ts, sanity.config.ts. Tested end to end with a real throwaway change, then discarded (see docs/ai/project_mcp_server.md).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merge the CI fix into main</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(done with PR #3; checked 2026-10-06: main's pr-lint.yml runs Node 22 and next typegen before the type check). The test change's GitHub check failed because main still has the old pr-lint.yml (Node 20 crash). Every MCP change will fail its site check, and so can't be published, until this branch's work (or at least .github/workflows/pr-lint.yml) is on main. Then test a real publish and undo_change.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blocked on you (Google)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">create a GOOGLE_API_KEY in Google Cloud (project of the vcos-ga4-reader service account, where the PageSpeed Insights API is already on), restricted to the PageSpeed Insights API, then add it to .env.local and Netlify. Creating it from here was blocked by the session's safety check (it would use the service account's credentials to change the Cloud project). Note lighthouse_check_page may time out on Netlify (10 s function limit on the free plan).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per-page generateMetadata (title, description, OG, Twitter Card, canonical) for every ported route, sourced from Sanity seo object where con…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tent is CMS-backed, static otherwise. Audited all 140 page.tsx files: only /studio has none (correct — it's robots.txt-disallowed, not public content). Real gap found and fixed: /blog/category/[slug] had no alternates.canonical at all, and no page-aware title for its own real pagination (?page=N) — every paginated page was serving an identical title with no canonical, a real duplicate-content signal. Fixed: generateMetadata now reads searchParams too, self-canonicals each page (?page=N pages canonical to themselves, not consolidated to page 1 — genuinely different posts per page, matching Google's current pagination guidance) and appends "— Page N" to the title past page 1. Verified live: page 1 canonicals to the bare URL, ?page=2 canonicals to ?page=2 with a distinct title.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sitemap.ts generated from real Sanity content + static route list, auto-updates on publish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extended from the Phase 5-era version (homepage + blog posts only, 122 URLs) to every real route: the full static route list (130 routes, generated from find src/app -name page.tsx, excluding /studio (robots.txt-disallowed), /(auth)/login (noindex via its own metadata), and /life-assessment (a pure redirect, not distinct content)) plus all 5 real dynamic sources — blog categories (allCategorySlugsQuery), BrewSoul cities (25), BrewSoul coffees (107), and charity-scorecard entries (103) — each pulled from the exact same data source its own page's generateStaticParams already uses, not re-derived. Auto-updates on publish for anything Sanity-backed (blog posts/categories) since it's a live client.fetch on every build; the static route list itself needs a one-line addition whenever a new page ships (same as any other route-registration step). Verified live: 496 real &lt;loc&gt; entries, spot-checked a coffee/city/charity/category URL each, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">llms.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fetched verbatim from the still-live site and saved to web/public/llms.txt (real content: Tony's bio, expertise, full article index by category, every product/tool section) — do this before Manus goes away, it won't be recoverable after</t>
-  </si>
-  <si>
-    <t xml:space="preserve">robots.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">same approach: fetched the real live file (not my earlier guessed robots.ts, which has been removed) and saved verbatim to web/public/robots.txt, plus added Disallow: /studio for the new Sanity Studio route. Confirmed live: real AI-crawler allowlist (GPTBot, Claude-Web, PerplexityBot, etc.), scraper blocklist, and the site's non-standard LLMs: directive all intact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JSON-LD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WebSite + Person schema ported verbatim from the live homepage's actual &lt;script type="application/ld+json"&gt; tags (not reconstructed from memory) — rendered site-wide from src/lib/structured-data.ts in the root layout. The Person image was hardcoded to a /api/img/... legacy proxy path on the live site — rescued that headshot (downloaded it while still live, uploaded to Sanity as the author-tony-greenberg document's avatar) so the new site's JSON-LD has zero Manus dependency instead of just copying the fragile path forward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Article JSON-LD on /blog/[slug], built from real per-post Sanity data (headline, image, datePublished/dateModified, author, canonical URL)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">verified live on a real post</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/path/:archetype (src/app/path/[archetype]/page.tsx)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per-archetype landing page for /assessment's Builder/Crusader/Investor result, reusing lib/content/archetypes.ts. Real content ported in full (top-5 essential-reading list per archetype via allPostsForArchiveQuery, real PathSubscribeForm posting to /api/subscribe, AUTHORITY_ITEMS strip). Real bug fixed vs. legacy: replaced a hand-rolled inline-styled "Path not found" div with a real notFound() (this route's generateStaticParams only ever produces the 3 real keys). Verified live: all 3 archetype routes 200 OK, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/my-journey (src/app/my-journey/page.tsx + components/assessments/my-journey-dashboard.tsx)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"My Journey Dashboard," real grid/timeline views across all 28 JOURNEY_MAP experiences, category/status filters, phase progress ring, recommended-next card, using the same real useJourneyProgress/JOURNEY_MAP completion tracking every "Find Your X" quiz already writes to (not the narrower tg_assessment_results cookie built for /self-portrait). Legacy's per-quiz scored-result caching (RESULT_KEYS, feeding a mini radar chart) was not ported — no quiz in this migration writes that data either, same honest-degradation call already made for /self-portrait's own composite radar. Fixed a real legacy dead link (/ecosystem-map, a still-unbuilt page) to /self-portrait. Verified live: 200 OK, real content confirmed, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/the-open-door (src/app/the-open-door/page.tsx)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real press/credibility content: all 10 "Magic Genie" client-pitch prompts (real named targets — Marco Argenti/Goldman Sachs, Adam Smith/Disney, etc.), 18 real client testimonials, all 8 explicitly-labeled satirical "parody" quotes (kept with disclaimers, not presented as real). Real overlap found and reconciled: this page's publications/speaking/podcasts arrays substantially duplicate the already-shipped /published's fuller bibliography — kept only what /published doesn't cover (Forbes + Business Insider bylines, the Clinton Global Initiative keynote, 4 of 5 podcast appearances) and cross-linked to /published for the rest, same reconciliation pattern as /assessments vs /find-my. Real bugs fixed: 3 genie/keynote links pointed externally at tonygreenberg.com/&lt;slug&gt; for posts that are real internal posts in this migration — relinked to /blog/psychedelics-could-become-extractive-capitalism, /blog/boiling-the-human-summit-harvard-kurzweil, /blog/return-on-investment-going-green-going-green-2 (all verified 200); a bare self-link to tonygreenberg.com remapped to /. Ships as a pure Server Component (legacy's FadeIn/Section/editorial-component dependencies don't exist here and weren't needed). Verified live: 200 OK, real content in raw SSR HTML, typecheck/lint clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homepage "Recent Updates" band (2026-09-29)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">on the live site (a newer Blog.tsx than _legacy-manus-app/, so rebuilt from the live page's markup), replacing the older "Latest Thinking" pair. Found while doing it: two live essays are missing from Sanity, the-tollbooth-and-the-alternative (Aug 18, 2026, the live site's newest) and what-quest-could-fix. Both were published on live after the legacy snapshot and need importing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re-sync the legacy reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_legacy-manus-app/ is older than what's live (Recent Updates proves it), so visual diffs should be against the live site, not only that folder.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visual diff pass: every ported page vs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">legacy page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Padding / spacing on the story pages matched to live (2026-10-01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Measured margins, text column and spacing on 31 pages, live vs a production build, at 375px and 1280px. The "door" story pages were the clear mismatch: live's text column is ~546px (ours was 720px), 20px side margins on phones / 40px on desktop, body text 19px/1.8 on phones and 18px/1.85 on desktop (ours 16px/1.5). Fixed on /the-body, /engine-room, /under-nda, /the-nightstand, /the-web, /the-territory, /about, /intel (Intel uses live's 16.8px/1.9; About's hero line 480px max, 18.4px/1.8). Re-measured: all 8 match live to within 2px (About's column 28px narrower), no sideways scroll at 375px.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Header-to-title spacing re-checked (2026-10-02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The 2026-10-01 note compared different things: live's header wasn't measured (it showed 0), so "96px vs 168px" was really 161px vs 168px from the top of the page. Measured again from the top of the page, live vs a production build, at 375px and 1280px: most pages were already within 10px. Fixed the real gaps: /the-open-door (now live's dark centered hero band, 56px title, 546px text column; title was 72px too high), /start-here (live's 48px/96px top padding; 25px too high on desktop), /invest and /engage (label spacing and live's 32px/51px title; /invest's desktop title was 36px), /impact-dashboard on phones (card edge to edge under the header like live; title was 89px too low). Re-measured: all within 8px of live, no sideways scroll at 375px, no JS errors.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HumanOS headings in capitals like live (2026-10-02, owner said yes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">the 4 headings live capitalises on /humanos (title, "Are you a Maximizer...", "Take the Diagnostic", "The Diagnostic") get uppercase; the words are unchanged. The subpages already matched.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">More layout gaps matched to live (2026-10-02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/series (live's centered 546px column, and a bug fixed: every card kept an empty 240px picture column, squeezing the text; live's per-series picture is one generic placeholder on the Manus proxy, so not copied), /humanos (middle section 900px like live), homepage desktop widths (hero text 804px, Four Doors 1000px, Editor's Picks 1168px, GemSpark edge, section title sizes; live's /blog now shows the homepage), /find-my (photo undimmed and plain background, like live; our site header kept). Re-measured: headings within 3px (/series) to 20px (homepage) of live, no sideways scroll, no JS errors. Note: live's "New here?" tour bar sits over its header and doesn't move the page, so it doesn't affect these numbers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full sweep vs live (2026-10-02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142 pages (every non-blog page, 3 of each templated set) at 375px and 1280px, title position, text column, title size. Fixed the shared causes: BrewSoul (live wraps most pages in its frame twice, so a second 52px offset plus the category badge; the landing, cities, directory and quiz pages have neither: src/components/brewsoul/brewsoul-main.tsx; intro paragraphs uncapped like live; 38px titles), Kava (live's extra 52px offset), /the-body, /the-nightstand, /the-web (405px top photo like live), the 6 peptide pages (live's 768/896px intro column), /journeys, /pick-up-the-phone, /published, /ecosystem (546px story column and live's text size). Re-measured: 110 of 120 within 40px / 60px of live.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweep leftovers fixed (2026-10-06)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ported legacy's exact title sizes, margins and column widths. Measured live vs a production build at 375px and 1280px (H1 distance from the top, H1 size, intro and table widths). Now within 8px and the same title size on /published, /brewsoul/first-sip, /brewsoul/home, /brewsoul/chains (intro 912px like live), /brewsoul/browse, /brewsoul/directory (3-column 952px grid like live), /brewsoul and /brewsoul/quiz (intro 520px), /amplifier (546px column), /diamond-cut, /speaking, /living-declaration, /spirits, /protecting-your-business (tables 730px), and the 5 HumanOS subpages (titles smaller like live, 752px column). No sideways scroll at 375px. Left on purpose: /self-portrait (font matches; our page has a different title and no back link, so it sits 23-57px higher), BrewSoul pages 3-6px off (the shared journey bar row), and the different-layout pages /dharma-finder, /grant-study, /search, /quiz_25q, /soulscore. Also: /brewsoul/quiz rebuilt as a step registry (src/components/brewsoul/brewsoul-quiz/: parent + hook/ + components/step-* + data/), same questions, scoring and look; Back/Skip/Retake use lucide icons. New CONTRIBUTING rule 19 (multi-step flows, FydoPartner pattern). brewsoul-welcome-quiz.tsx (/brewsoul) still has the old shape and text arrows.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Match live's redesigned pages (2026-10-06, owner said go)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/self-portrait (live: dark page, progress ring, "N more brushstrokes" lock until 5 assessments), /grant-study and /dharma-finder (live opens straight on question 1, no intro screen), /quiz_25q (live adds a hero picture above the title; rescue it into Sanity first), /search (live: one search box across essays, BrewSoul, peptides, HumanOS, assessments, kava and pages with filter chips). Measure live vs a production build at 375px and 1280px when done. Done 2026-10-06: /grant-study and /dharma-finder open straight on question 1 like live (title block / part header above the first question, live's 546px column, plain page, credit under every question), both rebuilt as step registries (rule 19); measured within 3px of live at the top (dharma's question block within 7px). /quiz_25q's hero rescued into Sanity and placed like live (within 2px). Found and fixed on the way: on the deployed copy /grant-study's answer buttons could not be clicked (the themed page background was fixed z-0, painted over the quiz); ThemedBackground is now -z-10 pointer-events-none (backgrounds unchanged on all 21 pages that use it), and the shared email gate no longer scrolls sideways on phones. Both quizzes clicked through to results in Chrome and Safari. /self-portrait restyled to live (dark page, "The Composite You", progress ring, "N More Brushstrokes Needed" lock until 5 done, live's copy) on our real cookie data; within 3px of live at both widths; tested with 0, 2 and 6 completed. Counts are ours (13 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Still different from live (needs a yes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blog posts (done) (done 2026-10-07, see Phase 5); /find-my on live hides the site header. /walk-through is a 404 on live now.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design change on live, needs a decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">live's story pages now use Cormorant Garamond for titles (ours: Playfair Display), a lighter title weight (400 vs our 700), and a red eyebrow label (#8E1E25, wider letter spacing) instead of our gold. A site-wide font swap is a design call, so not done.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link check across all ported pages (no 404s, no broken internal cross-references)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First full pass done 2026-09-29 (510 pages crawled from the sitemap plus every internal link, on a production build). Fixed in code: /brewsoul/coffee/…-tarrazú 404 (the route got the id still percent-encoded), 30+ links that went through the /assessments/* redirects, /find-your-me's dead Homeaglow link, the two root-level Iboga essay links, and the dead FauxTony nav item. Fixed as Sanity drafts (scripts/fix-blog-body-links.ts, 14 posts): broken post links, leaked !… placeholder text, Energy Is Money's split author bio, and scraped WordPress furniture ("Share this / Related / You Might Also Like / Copyright", "Show More / Top News", [mc4wp_form]). Left for a decision: /framework's "Ask FauxTony" button, when-healing-becomes-extraction's two links to a Dr. Lee case file that doesn't exist, and the-clock-keeper-chronicles-part-1's link to the deferred /clock-keeper-part-2. Re-run after the drafts are published. 2026-10-01 re-run (local production build, all 498 sitemap URLs load; 440 unique internal links): 5 broken. Fixed as a Sanity draft: molecule-as-mirror-10-what-the-pioneers-know's "Final installment" link pointed at a non-existent part-10 slug (now part 11; live also shows that line twice, kept). Already fixed in a waiting draft: forever-chemicals-... → /blog/psychedelic-readiness-index. Still the 3 known decisions: /fauxtony (from /framework), /clock-keeper-part-2, /blog/the-case-file-dr-samuel-lee.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lighthouse pass (performance/accessibility/SEO) on top 20 pages by traffic 2026-09-30, 20 key pages (no traffic data yet), local production …</t>
-  </si>
-  <si>
-    <t xml:space="preserve">build, mobile: averages performance 87, accessibility 99→100, best practices 100, SEO 92→100, CLS 0 everywhere. Fixed: public/robots.txt had an LLMs: line (not a real directive) that made Google treat the whole file as invalid, now a comment; h3/h4 headings skipping a level on /assessments, /kava, /peptide-watch (same look, right tag); the Kava and /attention-theft back-arrow links had no accessible name on phones; two small phone-width contrast misses. Left: performance is local-machine only (±10-15 points, see CONTRIBUTING.md); the slowest were / 76 (LCP 5.2 s), /psychedelic-readiness-index 82, /iboga-ibogaine 83. Re-run against the Netlify deploy before launch. 2026-10-06 re-run against the Netlify deploy (14 key pages, mobile): accessibility 100 and CLS 0 on every page, SEO clean (only the expected netlify.app noindex), performance 77-97 held back by 3-4 s LCP. Fixed: all 21 hero images moved off the deprecated priority prop to fetchPriority="high" + loading="eager" (Next 16); /iboga-ibogaine hero and the first card on /blog and category pages no longer lazy-loaded; sizes on the Four Doors cards (~150 KiB per page), /humanos diagram (~100 KiB) and /about headshot; urlFor no longer imports the Sanity client, so ~115 KB of Sanity client code stopped loading on / and /blog; React hydration error #418 on / and /blog (post dates) gone, checked in two time zones; /blog is static again; empty icon &lt;th&gt;s on /iboga-ibogaine labelled; category page reads use sanityFetch(). Left: se</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEO audit fixes (2026-10-06)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEO audit items needing a yes (2026-10-06)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
+    <t xml:space="preserve">Live's redesign, second group (started 2026-10-07, cut off by the usage limit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/living-declaration is done (dark bands, Cormorant title; all of live's text checked present). Still to match live: /the-web, /spirits, /iboga-ibogaine (title weight 800), /find-your-journey (64px title, red label), /impact-dashboard (64px title), red labels on /published and /speaking, label colours on /recent-creations and /soulscore, /pri-calibration (title weight 900), /quiz_25q; /pri-efficacy's "Simulation / Live Calibrations" switch (counts from the pri_calibrations table); live's BrewSoul photo (already in Sanity: 1c8cf85c…-1200x670.webp) on the BrewSoul hero, first-sip, guest and browse pages; the page re-check of /clients, /humanos/connect, /peptide-hall-of-shame (its hero is rescued, not wired) and the blend-builder / biodynamic pages.</t>
   </si>
   <si>
     <t xml:space="preserve">Manus media rescue (2026-09-29)</t>
@@ -2494,15 +2500,15 @@
         <v>8</v>
       </c>
       <c r="B5" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A5,'Full Detail'!$C$2:$C$317,"Done")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A5,'Full Detail'!$C$2:$C$318,"Done")</f>
         <v>12</v>
       </c>
       <c r="C5" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A5,'Full Detail'!$C$2:$C$317,"Remaining")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A5,'Full Detail'!$C$2:$C$318,"Remaining")</f>
         <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A5,'Full Detail'!$C$2:$C$317,"Deferred")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A5,'Full Detail'!$C$2:$C$318,"Deferred")</f>
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
@@ -2519,15 +2525,15 @@
         <v>9</v>
       </c>
       <c r="B6" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A6,'Full Detail'!$C$2:$C$317,"Done")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A6,'Full Detail'!$C$2:$C$318,"Done")</f>
         <v>16</v>
       </c>
       <c r="C6" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A6,'Full Detail'!$C$2:$C$317,"Remaining")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A6,'Full Detail'!$C$2:$C$318,"Remaining")</f>
         <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A6,'Full Detail'!$C$2:$C$317,"Deferred")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A6,'Full Detail'!$C$2:$C$318,"Deferred")</f>
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
@@ -2544,15 +2550,15 @@
         <v>10</v>
       </c>
       <c r="B7" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A7,'Full Detail'!$C$2:$C$317,"Done")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A7,'Full Detail'!$C$2:$C$318,"Done")</f>
         <v>8</v>
       </c>
       <c r="C7" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A7,'Full Detail'!$C$2:$C$317,"Remaining")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A7,'Full Detail'!$C$2:$C$318,"Remaining")</f>
         <v>2</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A7,'Full Detail'!$C$2:$C$317,"Deferred")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A7,'Full Detail'!$C$2:$C$318,"Deferred")</f>
         <v>0</v>
       </c>
       <c r="E7" s="5" t="n">
@@ -2569,15 +2575,15 @@
         <v>11</v>
       </c>
       <c r="B8" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A8,'Full Detail'!$C$2:$C$317,"Done")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A8,'Full Detail'!$C$2:$C$318,"Done")</f>
         <v>14</v>
       </c>
       <c r="C8" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A8,'Full Detail'!$C$2:$C$317,"Remaining")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A8,'Full Detail'!$C$2:$C$318,"Remaining")</f>
         <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A8,'Full Detail'!$C$2:$C$317,"Deferred")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A8,'Full Detail'!$C$2:$C$318,"Deferred")</f>
         <v>0</v>
       </c>
       <c r="E8" s="5" t="n">
@@ -2594,15 +2600,15 @@
         <v>12</v>
       </c>
       <c r="B9" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A9,'Full Detail'!$C$2:$C$317,"Done")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A9,'Full Detail'!$C$2:$C$318,"Done")</f>
         <v>63</v>
       </c>
       <c r="C9" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A9,'Full Detail'!$C$2:$C$317,"Remaining")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A9,'Full Detail'!$C$2:$C$318,"Remaining")</f>
         <v>0</v>
       </c>
       <c r="D9" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A9,'Full Detail'!$C$2:$C$317,"Deferred")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A9,'Full Detail'!$C$2:$C$318,"Deferred")</f>
         <v>1</v>
       </c>
       <c r="E9" s="5" t="n">
@@ -2619,20 +2625,20 @@
         <v>13</v>
       </c>
       <c r="B10" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A10,'Full Detail'!$C$2:$C$317,"Done")</f>
-        <v>32</v>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A10,'Full Detail'!$C$2:$C$318,"Done")</f>
+        <v>26</v>
       </c>
       <c r="C10" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A10,'Full Detail'!$C$2:$C$317,"Remaining")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A10,'Full Detail'!$C$2:$C$318,"Remaining")</f>
         <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A10,'Full Detail'!$C$2:$C$317,"Deferred")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A10,'Full Detail'!$C$2:$C$318,"Deferred")</f>
         <v>0</v>
       </c>
       <c r="E10" s="5" t="n">
         <f aca="false">SUM(B10:D10)</f>
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F10" s="6" t="n">
         <f aca="false">IF(E10=0,0,B10/E10)</f>
@@ -2644,15 +2650,15 @@
         <v>14</v>
       </c>
       <c r="B11" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A11,'Full Detail'!$C$2:$C$317,"Done")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A11,'Full Detail'!$C$2:$C$318,"Done")</f>
         <v>32</v>
       </c>
       <c r="C11" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A11,'Full Detail'!$C$2:$C$317,"Remaining")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A11,'Full Detail'!$C$2:$C$318,"Remaining")</f>
         <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A11,'Full Detail'!$C$2:$C$317,"Deferred")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A11,'Full Detail'!$C$2:$C$318,"Deferred")</f>
         <v>0</v>
       </c>
       <c r="E11" s="5" t="n">
@@ -2669,15 +2675,15 @@
         <v>15</v>
       </c>
       <c r="B12" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A12,'Full Detail'!$C$2:$C$317,"Done")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A12,'Full Detail'!$C$2:$C$318,"Done")</f>
         <v>21</v>
       </c>
       <c r="C12" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A12,'Full Detail'!$C$2:$C$317,"Remaining")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A12,'Full Detail'!$C$2:$C$318,"Remaining")</f>
         <v>0</v>
       </c>
       <c r="D12" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A12,'Full Detail'!$C$2:$C$317,"Deferred")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A12,'Full Detail'!$C$2:$C$318,"Deferred")</f>
         <v>0</v>
       </c>
       <c r="E12" s="5" t="n">
@@ -2694,15 +2700,15 @@
         <v>16</v>
       </c>
       <c r="B13" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A13,'Full Detail'!$C$2:$C$317,"Done")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A13,'Full Detail'!$C$2:$C$318,"Done")</f>
         <v>3</v>
       </c>
       <c r="C13" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A13,'Full Detail'!$C$2:$C$317,"Remaining")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A13,'Full Detail'!$C$2:$C$318,"Remaining")</f>
         <v>0</v>
       </c>
       <c r="D13" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A13,'Full Detail'!$C$2:$C$317,"Deferred")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A13,'Full Detail'!$C$2:$C$318,"Deferred")</f>
         <v>0</v>
       </c>
       <c r="E13" s="5" t="n">
@@ -2719,15 +2725,15 @@
         <v>17</v>
       </c>
       <c r="B14" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A14,'Full Detail'!$C$2:$C$317,"Done")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A14,'Full Detail'!$C$2:$C$318,"Done")</f>
         <v>27</v>
       </c>
       <c r="C14" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A14,'Full Detail'!$C$2:$C$317,"Remaining")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A14,'Full Detail'!$C$2:$C$318,"Remaining")</f>
         <v>0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A14,'Full Detail'!$C$2:$C$317,"Deferred")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A14,'Full Detail'!$C$2:$C$318,"Deferred")</f>
         <v>0</v>
       </c>
       <c r="E14" s="5" t="n">
@@ -2744,15 +2750,15 @@
         <v>18</v>
       </c>
       <c r="B15" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A15,'Full Detail'!$C$2:$C$317,"Done")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A15,'Full Detail'!$C$2:$C$318,"Done")</f>
         <v>0</v>
       </c>
       <c r="C15" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A15,'Full Detail'!$C$2:$C$317,"Remaining")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A15,'Full Detail'!$C$2:$C$318,"Remaining")</f>
         <v>0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A15,'Full Detail'!$C$2:$C$317,"Deferred")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A15,'Full Detail'!$C$2:$C$318,"Deferred")</f>
         <v>0</v>
       </c>
       <c r="E15" s="5" t="n">
@@ -2769,15 +2775,15 @@
         <v>19</v>
       </c>
       <c r="B16" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A16,'Full Detail'!$C$2:$C$317,"Done")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A16,'Full Detail'!$C$2:$C$318,"Done")</f>
         <v>15</v>
       </c>
       <c r="C16" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A16,'Full Detail'!$C$2:$C$317,"Remaining")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A16,'Full Detail'!$C$2:$C$318,"Remaining")</f>
         <v>3</v>
       </c>
       <c r="D16" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A16,'Full Detail'!$C$2:$C$317,"Deferred")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A16,'Full Detail'!$C$2:$C$318,"Deferred")</f>
         <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
@@ -2794,24 +2800,24 @@
         <v>20</v>
       </c>
       <c r="B17" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A17,'Full Detail'!$C$2:$C$317,"Done")</f>
-        <v>19</v>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A17,'Full Detail'!$C$2:$C$318,"Done")</f>
+        <v>25</v>
       </c>
       <c r="C17" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A17,'Full Detail'!$C$2:$C$317,"Remaining")</f>
-        <v>7</v>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A17,'Full Detail'!$C$2:$C$318,"Remaining")</f>
+        <v>8</v>
       </c>
       <c r="D17" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A17,'Full Detail'!$C$2:$C$317,"Deferred")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A17,'Full Detail'!$C$2:$C$318,"Deferred")</f>
         <v>1</v>
       </c>
       <c r="E17" s="5" t="n">
         <f aca="false">SUM(B17:D17)</f>
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F17" s="6" t="n">
         <f aca="false">IF(E17=0,0,B17/E17)</f>
-        <v>0.703703703703704</v>
+        <v>0.735294117647059</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2819,15 +2825,15 @@
         <v>21</v>
       </c>
       <c r="B18" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A18,'Full Detail'!$C$2:$C$317,"Done")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A18,'Full Detail'!$C$2:$C$318,"Done")</f>
         <v>16</v>
       </c>
       <c r="C18" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A18,'Full Detail'!$C$2:$C$317,"Remaining")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A18,'Full Detail'!$C$2:$C$318,"Remaining")</f>
         <v>3</v>
       </c>
       <c r="D18" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A18,'Full Detail'!$C$2:$C$317,"Deferred")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A18,'Full Detail'!$C$2:$C$318,"Deferred")</f>
         <v>0</v>
       </c>
       <c r="E18" s="5" t="n">
@@ -2844,15 +2850,15 @@
         <v>22</v>
       </c>
       <c r="B19" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A19,'Full Detail'!$C$2:$C$317,"Done")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A19,'Full Detail'!$C$2:$C$318,"Done")</f>
         <v>0</v>
       </c>
       <c r="C19" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A19,'Full Detail'!$C$2:$C$317,"Remaining")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A19,'Full Detail'!$C$2:$C$318,"Remaining")</f>
         <v>7</v>
       </c>
       <c r="D19" s="5" t="n">
-        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$317,$A19,'Full Detail'!$C$2:$C$317,"Deferred")</f>
+        <f aca="false">COUNTIFS('Full Detail'!$E$2:$E$318,$A19,'Full Detail'!$C$2:$C$318,"Deferred")</f>
         <v>0</v>
       </c>
       <c r="E19" s="5" t="n">
@@ -2874,7 +2880,7 @@
       </c>
       <c r="C20" s="8" t="n">
         <f aca="false">SUM(C5:C19)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D20" s="8" t="n">
         <f aca="false">SUM(D5:D19)</f>
@@ -2882,11 +2888,11 @@
       </c>
       <c r="E20" s="8" t="n">
         <f aca="false">SUM(E5:E19)</f>
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F20" s="9" t="n">
         <f aca="false">IF(E20=0,0,B20/E20)</f>
-        <v>0.920529801324503</v>
+        <v>0.917491749174918</v>
       </c>
     </row>
   </sheetData>
@@ -2905,7 +2911,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E317"/>
+  <dimension ref="A1:E318"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -5078,105 +5084,105 @@
         <v>13</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="4"/>
-      <c r="B150" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="C150" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="E150" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B150" s="10"/>
+      <c r="C150" s="10"/>
+      <c r="D150" s="10"/>
+    </row>
+    <row r="151" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="4"/>
       <c r="B151" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C151" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E151" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="4"/>
       <c r="B152" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C152" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E152" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="4"/>
       <c r="B153" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C153" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E153" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="4"/>
       <c r="B154" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C154" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E154" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="4"/>
       <c r="B155" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C155" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="E155" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="4"/>
+      <c r="B156" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C155" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="4" t="s">
+      <c r="C156" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="E155" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="10" t="s">
+      <c r="E156" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B156" s="10"/>
-      <c r="C156" s="10"/>
-      <c r="D156" s="10"/>
-    </row>
-    <row r="157" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="157" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="4"/>
       <c r="B157" s="4" t="s">
         <v>304</v>
@@ -5191,7 +5197,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="4"/>
       <c r="B158" s="4" t="s">
         <v>306</v>
@@ -5206,7 +5212,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="4"/>
       <c r="B159" s="4" t="s">
         <v>308</v>
@@ -5236,7 +5242,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="4"/>
       <c r="B161" s="4" t="s">
         <v>312</v>
@@ -5251,7 +5257,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="4"/>
       <c r="B162" s="4" t="s">
         <v>314</v>
@@ -5266,7 +5272,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="4"/>
       <c r="B163" s="4" t="s">
         <v>316</v>
@@ -5281,7 +5287,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="4"/>
       <c r="B164" s="4" t="s">
         <v>318</v>
@@ -5326,7 +5332,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="4"/>
       <c r="B167" s="4" t="s">
         <v>324</v>
@@ -5341,7 +5347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="4"/>
       <c r="B168" s="4" t="s">
         <v>326</v>
@@ -5356,7 +5362,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="4"/>
       <c r="B169" s="4" t="s">
         <v>328</v>
@@ -5371,7 +5377,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="4"/>
       <c r="B170" s="4" t="s">
         <v>330</v>
@@ -5386,7 +5392,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="4"/>
       <c r="B171" s="4" t="s">
         <v>332</v>
@@ -5401,7 +5407,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="4"/>
       <c r="B172" s="4" t="s">
         <v>334</v>
@@ -5416,7 +5422,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="4"/>
       <c r="B173" s="4" t="s">
         <v>336</v>
@@ -5431,7 +5437,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="4"/>
       <c r="B174" s="4" t="s">
         <v>338</v>
@@ -5446,7 +5452,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="4"/>
       <c r="B175" s="4" t="s">
         <v>340</v>
@@ -5461,7 +5467,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="4"/>
       <c r="B176" s="4" t="s">
         <v>342</v>
@@ -5476,7 +5482,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="4"/>
       <c r="B177" s="4" t="s">
         <v>344</v>
@@ -5506,7 +5512,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="4"/>
       <c r="B179" s="4" t="s">
         <v>348</v>
@@ -5521,7 +5527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="4"/>
       <c r="B180" s="4" t="s">
         <v>350</v>
@@ -5536,7 +5542,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="4"/>
       <c r="B181" s="4" t="s">
         <v>352</v>
@@ -5551,7 +5557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="4"/>
       <c r="B182" s="4" t="s">
         <v>354</v>
@@ -5566,105 +5572,105 @@
         <v>14</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="4"/>
-      <c r="B183" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="C183" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="E183" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="184" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A183" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" s="10"/>
+      <c r="C183" s="10"/>
+      <c r="D183" s="10"/>
+    </row>
+    <row r="184" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="4"/>
       <c r="B184" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C184" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E184" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="185" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="4"/>
       <c r="B185" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C185" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E185" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="186" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="4"/>
       <c r="B186" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C186" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E186" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="187" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="4"/>
       <c r="B187" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C187" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E187" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="188" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="4"/>
       <c r="B188" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C188" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="E188" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="4"/>
+      <c r="B189" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="C188" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="4" t="s">
+      <c r="C189" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="E188" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="10" t="s">
+      <c r="E189" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B189" s="10"/>
-      <c r="C189" s="10"/>
-      <c r="D189" s="10"/>
-    </row>
-    <row r="190" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="190" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="4"/>
       <c r="B190" s="4" t="s">
         <v>368</v>
@@ -5679,7 +5685,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="4"/>
       <c r="B191" s="4" t="s">
         <v>370</v>
@@ -5694,7 +5700,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="4"/>
       <c r="B192" s="4" t="s">
         <v>372</v>
@@ -5709,7 +5715,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="4"/>
       <c r="B193" s="4" t="s">
         <v>374</v>
@@ -5724,7 +5730,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="4"/>
       <c r="B194" s="4" t="s">
         <v>376</v>
@@ -5739,7 +5745,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="4"/>
       <c r="B195" s="4" t="s">
         <v>378</v>
@@ -5754,7 +5760,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="4"/>
       <c r="B196" s="4" t="s">
         <v>380</v>
@@ -5769,7 +5775,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="4"/>
       <c r="B197" s="4" t="s">
         <v>382</v>
@@ -5784,7 +5790,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="4"/>
       <c r="B198" s="4" t="s">
         <v>384</v>
@@ -5799,7 +5805,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="4"/>
       <c r="B199" s="4" t="s">
         <v>386</v>
@@ -5814,7 +5820,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="4"/>
       <c r="B200" s="4" t="s">
         <v>388</v>
@@ -5829,7 +5835,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="4"/>
       <c r="B201" s="4" t="s">
         <v>390</v>
@@ -5859,7 +5865,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="4"/>
       <c r="B203" s="4" t="s">
         <v>394</v>
@@ -5874,7 +5880,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="4"/>
       <c r="B204" s="4" t="s">
         <v>396</v>
@@ -5889,158 +5895,158 @@
         <v>15</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="4"/>
-      <c r="B205" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="C205" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="E205" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="206" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A205" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B205" s="10"/>
+      <c r="C205" s="10"/>
+      <c r="D205" s="10"/>
+    </row>
+    <row r="206" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="4"/>
       <c r="B206" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C206" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E206" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="207" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="4"/>
       <c r="B207" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C207" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E207" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="208" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="4"/>
       <c r="B208" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C208" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E208" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="209" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="4"/>
-      <c r="B209" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="C209" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D209" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="E209" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="210" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A209" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B209" s="10"/>
+      <c r="C209" s="10"/>
+      <c r="D209" s="10"/>
+    </row>
+    <row r="210" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="4"/>
       <c r="B210" s="4" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C210" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E210" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A211" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B211" s="10"/>
-      <c r="C211" s="10"/>
-      <c r="D211" s="10"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="4"/>
+      <c r="B211" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="C211" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D211" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="E211" s="12" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="212" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="4"/>
       <c r="B212" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C212" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E212" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="213" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="4"/>
       <c r="B213" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C213" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E213" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="214" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="4"/>
       <c r="B214" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C214" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D214" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="E214" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="4"/>
+      <c r="B215" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="C214" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D214" s="4" t="s">
+      <c r="C215" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="E214" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A215" s="10" t="s">
+      <c r="E215" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B215" s="10"/>
-      <c r="C215" s="10"/>
-      <c r="D215" s="10"/>
-    </row>
-    <row r="216" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="216" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="4"/>
       <c r="B216" s="4" t="s">
         <v>416</v>
@@ -6070,7 +6076,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="4"/>
       <c r="B218" s="4" t="s">
         <v>420</v>
@@ -6100,7 +6106,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="4"/>
       <c r="B220" s="4" t="s">
         <v>424</v>
@@ -6115,7 +6121,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="4"/>
       <c r="B221" s="4" t="s">
         <v>426</v>
@@ -6130,7 +6136,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="4"/>
       <c r="B222" s="4" t="s">
         <v>428</v>
@@ -6145,7 +6151,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="4"/>
       <c r="B223" s="4" t="s">
         <v>430</v>
@@ -6160,7 +6166,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="4"/>
       <c r="B224" s="4" t="s">
         <v>432</v>
@@ -6175,7 +6181,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="4"/>
       <c r="B225" s="4" t="s">
         <v>434</v>
@@ -6190,7 +6196,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="4"/>
       <c r="B226" s="4" t="s">
         <v>436</v>
@@ -6205,7 +6211,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="4"/>
       <c r="B227" s="4" t="s">
         <v>438</v>
@@ -6220,7 +6226,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="4"/>
       <c r="B228" s="4" t="s">
         <v>440</v>
@@ -6235,7 +6241,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="4"/>
       <c r="B229" s="4" t="s">
         <v>442</v>
@@ -6250,7 +6256,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="4"/>
       <c r="B230" s="4" t="s">
         <v>444</v>
@@ -6265,7 +6271,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="4"/>
       <c r="B231" s="4" t="s">
         <v>446</v>
@@ -6280,7 +6286,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="4"/>
       <c r="B232" s="4" t="s">
         <v>448</v>
@@ -6310,7 +6316,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="4"/>
       <c r="B234" s="4" t="s">
         <v>452</v>
@@ -6325,7 +6331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="4"/>
       <c r="B235" s="4" t="s">
         <v>454</v>
@@ -6340,7 +6346,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="4"/>
       <c r="B236" s="4" t="s">
         <v>456</v>
@@ -6355,114 +6361,108 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="4"/>
-      <c r="B237" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="C237" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D237" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="E237" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="238" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A237" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B237" s="10"/>
+      <c r="C237" s="10"/>
+      <c r="D237" s="10"/>
+    </row>
+    <row r="238" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="4"/>
       <c r="B238" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C238" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E238" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="239" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="4"/>
       <c r="B239" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C239" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E239" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="240" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="4"/>
       <c r="B240" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C240" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E240" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="4"/>
       <c r="B241" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C241" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D241" s="4" t="s">
-        <v>467</v>
-      </c>
+      <c r="D241" s="4"/>
       <c r="E241" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="242" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="4"/>
       <c r="B242" s="4" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C242" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D242" s="4" t="s">
-        <v>469</v>
-      </c>
+      <c r="D242" s="4"/>
       <c r="E242" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A243" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B243" s="10"/>
-      <c r="C243" s="10"/>
-      <c r="D243" s="10"/>
-    </row>
-    <row r="244" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="243" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="4"/>
+      <c r="B243" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="C243" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D243" s="4"/>
+      <c r="E243" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="4"/>
       <c r="B244" s="4" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C244" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E244" s="12" t="s">
         <v>19</v>
@@ -6471,28 +6471,28 @@
     <row r="245" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="4"/>
       <c r="B245" s="4" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C245" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E245" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="4"/>
       <c r="B246" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="C246" s="11" t="s">
-        <v>3</v>
+        <v>471</v>
+      </c>
+      <c r="C246" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E246" s="12" t="s">
         <v>19</v>
@@ -6501,67 +6501,71 @@
     <row r="247" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="4"/>
       <c r="B247" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="C247" s="11" t="s">
-        <v>3</v>
+        <v>473</v>
+      </c>
+      <c r="C247" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="D247" s="4"/>
       <c r="E247" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="4"/>
       <c r="B248" s="4" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C248" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D248" s="4"/>
+      <c r="D248" s="4" t="s">
+        <v>475</v>
+      </c>
       <c r="E248" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="4"/>
       <c r="B249" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C249" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D249" s="4"/>
+      <c r="D249" s="4" t="s">
+        <v>477</v>
+      </c>
       <c r="E249" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="4"/>
       <c r="B250" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C250" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D250" s="4" t="s">
         <v>479</v>
-      </c>
-      <c r="C250" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D250" s="4" t="s">
-        <v>480</v>
       </c>
       <c r="E250" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="4"/>
       <c r="B251" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C251" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D251" s="4" t="s">
         <v>481</v>
-      </c>
-      <c r="C251" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D251" s="4" t="s">
-        <v>482</v>
       </c>
       <c r="E251" s="12" t="s">
         <v>19</v>
@@ -6570,32 +6574,34 @@
     <row r="252" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="4"/>
       <c r="B252" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C252" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D252" s="4" t="s">
         <v>483</v>
-      </c>
-      <c r="C252" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D252" s="4" t="s">
-        <v>484</v>
       </c>
       <c r="E252" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="4"/>
       <c r="B253" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C253" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D253" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="C253" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D253" s="4"/>
       <c r="E253" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="4"/>
       <c r="B254" s="4" t="s">
         <v>486</v>
@@ -6610,13 +6616,13 @@
         <v>19</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="4"/>
       <c r="B255" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="C255" s="11" t="s">
-        <v>3</v>
+      <c r="C255" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="D255" s="4" t="s">
         <v>489</v>
@@ -6625,105 +6631,105 @@
         <v>19</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="4"/>
-      <c r="B256" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="C256" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D256" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="E256" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="257" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A256" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B256" s="10"/>
+      <c r="C256" s="10"/>
+      <c r="D256" s="10"/>
+    </row>
+    <row r="257" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="4"/>
       <c r="B257" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C257" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E257" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="258" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="4"/>
       <c r="B258" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C258" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E258" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="259" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="4"/>
       <c r="B259" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C259" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E259" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="4"/>
       <c r="B260" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C260" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E260" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="261" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="4"/>
       <c r="B261" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="C261" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D261" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="E261" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="4"/>
+      <c r="B262" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="C261" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D261" s="4" t="s">
+      <c r="C262" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D262" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="E261" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A262" s="10" t="s">
+      <c r="E262" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B262" s="10"/>
-      <c r="C262" s="10"/>
-      <c r="D262" s="10"/>
-    </row>
-    <row r="263" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="263" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="4"/>
       <c r="B263" s="4" t="s">
         <v>502</v>
@@ -6738,7 +6744,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="4"/>
       <c r="B264" s="4" t="s">
         <v>504</v>
@@ -6753,7 +6759,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="4"/>
       <c r="B265" s="4" t="s">
         <v>506</v>
@@ -6783,13 +6789,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="4"/>
       <c r="B267" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="C267" s="11" t="s">
-        <v>3</v>
+      <c r="C267" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="D267" s="4" t="s">
         <v>511</v>
@@ -6798,13 +6804,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="4"/>
       <c r="B268" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="C268" s="11" t="s">
-        <v>3</v>
+      <c r="C268" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="D268" s="4" t="s">
         <v>513</v>
@@ -6813,7 +6819,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="4"/>
       <c r="B269" s="4" t="s">
         <v>514</v>
@@ -6843,7 +6849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="4"/>
       <c r="B271" s="4" t="s">
         <v>518</v>
@@ -6858,7 +6864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="272" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="4"/>
       <c r="B272" s="4" t="s">
         <v>520</v>
@@ -6873,13 +6879,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="273" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="4"/>
       <c r="B273" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="C273" s="13" t="s">
-        <v>4</v>
+      <c r="C273" s="11" t="s">
+        <v>3</v>
       </c>
       <c r="D273" s="4" t="s">
         <v>523</v>
@@ -6888,13 +6894,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="4"/>
       <c r="B274" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="C274" s="13" t="s">
-        <v>4</v>
+      <c r="C274" s="11" t="s">
+        <v>3</v>
       </c>
       <c r="D274" s="4" t="s">
         <v>525</v>
@@ -6903,7 +6909,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="4"/>
       <c r="B275" s="4" t="s">
         <v>526</v>
@@ -6918,13 +6924,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="4"/>
       <c r="B276" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="C276" s="11" t="s">
-        <v>3</v>
+      <c r="C276" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>529</v>
@@ -6933,13 +6939,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="4"/>
       <c r="B277" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="C277" s="11" t="s">
-        <v>3</v>
+      <c r="C277" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>531</v>
@@ -6948,13 +6954,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="4"/>
       <c r="B278" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="C278" s="11" t="s">
-        <v>3</v>
+      <c r="C278" s="14" t="s">
+        <v>5</v>
       </c>
       <c r="D278" s="4" t="s">
         <v>533</v>
@@ -6963,13 +6969,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="4"/>
       <c r="B279" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="C279" s="11" t="s">
-        <v>3</v>
+      <c r="C279" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="D279" s="4" t="s">
         <v>535</v>
@@ -6978,7 +6984,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="4"/>
       <c r="B280" s="4" t="s">
         <v>536</v>
@@ -6993,13 +6999,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="4"/>
       <c r="B281" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="C281" s="11" t="s">
-        <v>3</v>
+      <c r="C281" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="D281" s="4" t="s">
         <v>539</v>
@@ -7016,83 +7022,81 @@
       <c r="C282" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D282" s="4" t="s">
-        <v>541</v>
-      </c>
+      <c r="D282" s="4"/>
       <c r="E282" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="4"/>
       <c r="B283" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="C283" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D283" s="4" t="s">
         <v>542</v>
-      </c>
-      <c r="C283" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D283" s="4" t="s">
-        <v>543</v>
       </c>
       <c r="E283" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="4"/>
       <c r="B284" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="C284" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D284" s="4" t="s">
         <v>544</v>
-      </c>
-      <c r="C284" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D284" s="4" t="s">
-        <v>545</v>
       </c>
       <c r="E284" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="4"/>
       <c r="B285" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="C285" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D285" s="4" t="s">
         <v>546</v>
-      </c>
-      <c r="C285" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D285" s="4" t="s">
-        <v>547</v>
       </c>
       <c r="E285" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="286" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="4"/>
       <c r="B286" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="C286" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D286" s="4" t="s">
         <v>548</v>
-      </c>
-      <c r="C286" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D286" s="4" t="s">
-        <v>549</v>
       </c>
       <c r="E286" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="4"/>
       <c r="B287" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C287" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D287" s="4" t="s">
         <v>550</v>
-      </c>
-      <c r="C287" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D287" s="4" t="s">
-        <v>551</v>
       </c>
       <c r="E287" s="12" t="s">
         <v>20</v>
@@ -7101,17 +7105,19 @@
     <row r="288" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="4"/>
       <c r="B288" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C288" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D288" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="C288" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D288" s="4"/>
       <c r="E288" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="4"/>
       <c r="B289" s="4" t="s">
         <v>553</v>
@@ -7126,30 +7132,30 @@
         <v>20</v>
       </c>
     </row>
-    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A290" s="10" t="s">
+    <row r="290" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="4"/>
+      <c r="B290" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="C290" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D290" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E290" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A291" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B290" s="10"/>
-      <c r="C290" s="10"/>
-      <c r="D290" s="10"/>
-    </row>
-    <row r="291" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="4"/>
-      <c r="B291" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="C291" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D291" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="E291" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B291" s="10"/>
+      <c r="C291" s="10"/>
+      <c r="D291" s="10"/>
+    </row>
+    <row r="292" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="4"/>
       <c r="B292" s="4" t="s">
         <v>557</v>
@@ -7164,13 +7170,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="293" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="4"/>
       <c r="B293" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="C293" s="13" t="s">
-        <v>4</v>
+      <c r="C293" s="11" t="s">
+        <v>3</v>
       </c>
       <c r="D293" s="4" t="s">
         <v>560</v>
@@ -7184,8 +7190,8 @@
       <c r="B294" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="C294" s="11" t="s">
-        <v>3</v>
+      <c r="C294" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="D294" s="4" t="s">
         <v>562</v>
@@ -7194,7 +7200,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="4"/>
       <c r="B295" s="4" t="s">
         <v>563</v>
@@ -7209,7 +7215,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="4"/>
       <c r="B296" s="4" t="s">
         <v>565</v>
@@ -7239,13 +7245,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="298" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="4"/>
       <c r="B298" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="C298" s="13" t="s">
-        <v>4</v>
+      <c r="C298" s="11" t="s">
+        <v>3</v>
       </c>
       <c r="D298" s="4" t="s">
         <v>570</v>
@@ -7254,13 +7260,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="4"/>
       <c r="B299" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="C299" s="11" t="s">
-        <v>3</v>
+      <c r="C299" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>572</v>
@@ -7269,7 +7275,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="300" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="4"/>
       <c r="B300" s="4" t="s">
         <v>573</v>
@@ -7284,7 +7290,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="301" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="4"/>
       <c r="B301" s="4" t="s">
         <v>575</v>
@@ -7299,7 +7305,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="4"/>
       <c r="B302" s="4" t="s">
         <v>577</v>
@@ -7314,7 +7320,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="4"/>
       <c r="B303" s="4" t="s">
         <v>579</v>
@@ -7329,7 +7335,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="304" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="4"/>
       <c r="B304" s="4" t="s">
         <v>581</v>
@@ -7344,7 +7350,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="4"/>
       <c r="B305" s="4" t="s">
         <v>583</v>
@@ -7379,8 +7385,8 @@
       <c r="B307" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="C307" s="13" t="s">
-        <v>4</v>
+      <c r="C307" s="11" t="s">
+        <v>3</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>588</v>
@@ -7389,13 +7395,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="4"/>
       <c r="B308" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="C308" s="11" t="s">
-        <v>3</v>
+      <c r="C308" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="D308" s="4" t="s">
         <v>590</v>
@@ -7404,7 +7410,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="309" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="4"/>
       <c r="B309" s="4" t="s">
         <v>591</v>
@@ -7419,30 +7425,30 @@
         <v>21</v>
       </c>
     </row>
-    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A310" s="10" t="s">
+    <row r="310" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A310" s="4"/>
+      <c r="B310" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="C310" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D310" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="E310" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A311" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B310" s="10"/>
-      <c r="C310" s="10"/>
-      <c r="D310" s="10"/>
-    </row>
-    <row r="311" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="4"/>
-      <c r="B311" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="C311" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D311" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="E311" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="312" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B311" s="10"/>
+      <c r="C311" s="10"/>
+      <c r="D311" s="10"/>
+    </row>
+    <row r="312" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="4"/>
       <c r="B312" s="4" t="s">
         <v>595</v>
@@ -7457,7 +7463,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="4"/>
       <c r="B313" s="4" t="s">
         <v>597</v>
@@ -7472,7 +7478,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="314" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="4"/>
       <c r="B314" s="4" t="s">
         <v>599</v>
@@ -7487,7 +7493,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="4"/>
       <c r="B315" s="4" t="s">
         <v>601</v>
@@ -7510,7 +7516,9 @@
       <c r="C316" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D316" s="4"/>
+      <c r="D316" s="4" t="s">
+        <v>604</v>
+      </c>
       <c r="E316" s="12" t="s">
         <v>22</v>
       </c>
@@ -7518,7 +7526,7 @@
     <row r="317" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="4"/>
       <c r="B317" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C317" s="13" t="s">
         <v>4</v>
@@ -7528,8 +7536,21 @@
         <v>22</v>
       </c>
     </row>
+    <row r="318" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A318" s="4"/>
+      <c r="B318" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="C318" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D318" s="4"/>
+      <c r="E318" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D317"/>
+  <autoFilter ref="A1:D318"/>
   <mergeCells count="14">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A15:D15"/>
@@ -7537,14 +7558,14 @@
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A123:D123"/>
-    <mergeCell ref="A156:D156"/>
-    <mergeCell ref="A189:D189"/>
-    <mergeCell ref="A211:D211"/>
-    <mergeCell ref="A215:D215"/>
-    <mergeCell ref="A243:D243"/>
-    <mergeCell ref="A262:D262"/>
-    <mergeCell ref="A290:D290"/>
-    <mergeCell ref="A310:D310"/>
+    <mergeCell ref="A150:D150"/>
+    <mergeCell ref="A183:D183"/>
+    <mergeCell ref="A205:D205"/>
+    <mergeCell ref="A209:D209"/>
+    <mergeCell ref="A237:D237"/>
+    <mergeCell ref="A256:D256"/>
+    <mergeCell ref="A291:D291"/>
+    <mergeCell ref="A311:D311"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7562,7 +7583,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -7583,7 +7604,7 @@
         <v>25</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>27</v>
@@ -7661,13 +7682,13 @@
     <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>19</v>
@@ -7676,7 +7697,7 @@
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>4</v>
@@ -7689,13 +7710,13 @@
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>19</v>
@@ -7712,13 +7733,13 @@
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>20</v>
@@ -7727,13 +7748,13 @@
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>20</v>
@@ -7742,13 +7763,13 @@
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>20</v>
@@ -7757,13 +7778,13 @@
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>20</v>
@@ -7772,13 +7793,13 @@
     <row r="16" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>20</v>
@@ -7787,13 +7808,13 @@
     <row r="17" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>20</v>
@@ -7802,13 +7823,13 @@
     <row r="18" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>20</v>
@@ -7817,7 +7838,7 @@
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>4</v>
@@ -7827,83 +7848,83 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
+    <row r="20" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-    </row>
-    <row r="25" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+    </row>
+    <row r="26" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
         <v>595</v>
@@ -7918,7 +7939,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
         <v>597</v>
@@ -7933,7 +7954,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>599</v>
@@ -7948,7 +7969,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
         <v>601</v>
@@ -7971,7 +7992,9 @@
       <c r="C30" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="4" t="s">
+        <v>604</v>
+      </c>
       <c r="E30" s="12" t="s">
         <v>22</v>
       </c>
@@ -7979,7 +8002,7 @@
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>4</v>
@@ -7989,15 +8012,28 @@
         <v>22</v>
       </c>
     </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D31"/>
+  <autoFilter ref="A1:D32"/>
   <mergeCells count="6">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A25:D25"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Migration-Status-Report.xlsx
+++ b/Migration-Status-Report.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Remaining Work" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$322</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Remaining Work'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$324</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Remaining Work'!$A$1:$D$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -596,7 +596,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from NEXTJS-MIGRATION-TODO.md on 2026-10-08 by scripts/build-migration-status-report.py — a living document; re-run the script after updating the todo file. Counts are formulas over the Full Detail tab.</t>
+          <t>Generated from NEXTJS-MIGRATION-TODO.md on 2026-10-09 by scripts/build-migration-status-report.py — a living document; re-run the script after updating the todo file. Counts are formulas over the Full Detail tab.</t>
         </is>
       </c>
     </row>
@@ -639,15 +639,15 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A5,'Full Detail'!$C$2:$C$322,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A5,'Full Detail'!$C$2:$C$324,"Done")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A5,'Full Detail'!$C$2:$C$322,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A5,'Full Detail'!$C$2:$C$324,"Remaining")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A5,'Full Detail'!$C$2:$C$322,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A5,'Full Detail'!$C$2:$C$324,"Deferred")</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -666,15 +666,15 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A6,'Full Detail'!$C$2:$C$322,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A6,'Full Detail'!$C$2:$C$324,"Done")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A6,'Full Detail'!$C$2:$C$322,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A6,'Full Detail'!$C$2:$C$324,"Remaining")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A6,'Full Detail'!$C$2:$C$322,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A6,'Full Detail'!$C$2:$C$324,"Deferred")</f>
         <v/>
       </c>
       <c r="E6" s="5">
@@ -693,15 +693,15 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A7,'Full Detail'!$C$2:$C$322,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A7,'Full Detail'!$C$2:$C$324,"Done")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A7,'Full Detail'!$C$2:$C$322,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A7,'Full Detail'!$C$2:$C$324,"Remaining")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A7,'Full Detail'!$C$2:$C$322,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A7,'Full Detail'!$C$2:$C$324,"Deferred")</f>
         <v/>
       </c>
       <c r="E7" s="5">
@@ -720,15 +720,15 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A8,'Full Detail'!$C$2:$C$322,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A8,'Full Detail'!$C$2:$C$324,"Done")</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A8,'Full Detail'!$C$2:$C$322,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A8,'Full Detail'!$C$2:$C$324,"Remaining")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A8,'Full Detail'!$C$2:$C$322,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A8,'Full Detail'!$C$2:$C$324,"Deferred")</f>
         <v/>
       </c>
       <c r="E8" s="5">
@@ -747,15 +747,15 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A9,'Full Detail'!$C$2:$C$322,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A9,'Full Detail'!$C$2:$C$324,"Done")</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A9,'Full Detail'!$C$2:$C$322,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A9,'Full Detail'!$C$2:$C$324,"Remaining")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A9,'Full Detail'!$C$2:$C$322,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A9,'Full Detail'!$C$2:$C$324,"Deferred")</f>
         <v/>
       </c>
       <c r="E9" s="5">
@@ -774,15 +774,15 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A10,'Full Detail'!$C$2:$C$322,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A10,'Full Detail'!$C$2:$C$324,"Done")</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A10,'Full Detail'!$C$2:$C$322,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A10,'Full Detail'!$C$2:$C$324,"Remaining")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A10,'Full Detail'!$C$2:$C$322,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A10,'Full Detail'!$C$2:$C$324,"Deferred")</f>
         <v/>
       </c>
       <c r="E10" s="5">
@@ -801,15 +801,15 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A11,'Full Detail'!$C$2:$C$322,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A11,'Full Detail'!$C$2:$C$324,"Done")</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A11,'Full Detail'!$C$2:$C$322,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A11,'Full Detail'!$C$2:$C$324,"Remaining")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A11,'Full Detail'!$C$2:$C$322,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A11,'Full Detail'!$C$2:$C$324,"Deferred")</f>
         <v/>
       </c>
       <c r="E11" s="5">
@@ -828,15 +828,15 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A12,'Full Detail'!$C$2:$C$322,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A12,'Full Detail'!$C$2:$C$324,"Done")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A12,'Full Detail'!$C$2:$C$322,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A12,'Full Detail'!$C$2:$C$324,"Remaining")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A12,'Full Detail'!$C$2:$C$322,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A12,'Full Detail'!$C$2:$C$324,"Deferred")</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -855,15 +855,15 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A13,'Full Detail'!$C$2:$C$322,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A13,'Full Detail'!$C$2:$C$324,"Done")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A13,'Full Detail'!$C$2:$C$322,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A13,'Full Detail'!$C$2:$C$324,"Remaining")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A13,'Full Detail'!$C$2:$C$322,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A13,'Full Detail'!$C$2:$C$324,"Deferred")</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -882,15 +882,15 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A14,'Full Detail'!$C$2:$C$322,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A14,'Full Detail'!$C$2:$C$324,"Done")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A14,'Full Detail'!$C$2:$C$322,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A14,'Full Detail'!$C$2:$C$324,"Remaining")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A14,'Full Detail'!$C$2:$C$322,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A14,'Full Detail'!$C$2:$C$324,"Deferred")</f>
         <v/>
       </c>
       <c r="E14" s="5">
@@ -909,15 +909,15 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A15,'Full Detail'!$C$2:$C$322,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A15,'Full Detail'!$C$2:$C$324,"Done")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A15,'Full Detail'!$C$2:$C$322,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A15,'Full Detail'!$C$2:$C$324,"Remaining")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A15,'Full Detail'!$C$2:$C$322,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A15,'Full Detail'!$C$2:$C$324,"Deferred")</f>
         <v/>
       </c>
       <c r="E15" s="5">
@@ -936,15 +936,15 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A16,'Full Detail'!$C$2:$C$322,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A16,'Full Detail'!$C$2:$C$324,"Done")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A16,'Full Detail'!$C$2:$C$322,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A16,'Full Detail'!$C$2:$C$324,"Remaining")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A16,'Full Detail'!$C$2:$C$322,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A16,'Full Detail'!$C$2:$C$324,"Deferred")</f>
         <v/>
       </c>
       <c r="E16" s="5">
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A17,'Full Detail'!$C$2:$C$322,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A17,'Full Detail'!$C$2:$C$324,"Done")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A17,'Full Detail'!$C$2:$C$322,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A17,'Full Detail'!$C$2:$C$324,"Remaining")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A17,'Full Detail'!$C$2:$C$322,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A17,'Full Detail'!$C$2:$C$324,"Deferred")</f>
         <v/>
       </c>
       <c r="E17" s="5">
@@ -990,15 +990,15 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A18,'Full Detail'!$C$2:$C$322,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A18,'Full Detail'!$C$2:$C$324,"Done")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A18,'Full Detail'!$C$2:$C$322,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A18,'Full Detail'!$C$2:$C$324,"Remaining")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A18,'Full Detail'!$C$2:$C$322,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A18,'Full Detail'!$C$2:$C$324,"Deferred")</f>
         <v/>
       </c>
       <c r="E18" s="5">
@@ -1017,15 +1017,15 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A19,'Full Detail'!$C$2:$C$322,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A19,'Full Detail'!$C$2:$C$324,"Done")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A19,'Full Detail'!$C$2:$C$322,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A19,'Full Detail'!$C$2:$C$324,"Remaining")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$322,$A19,'Full Detail'!$C$2:$C$322,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A19,'Full Detail'!$C$2:$C$324,"Deferred")</f>
         <v/>
       </c>
       <c r="E19" s="5">
@@ -1075,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E322"/>
+  <dimension ref="A1:E324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6732,66 +6732,66 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="10" t="inlineStr">
-        <is>
-          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
-        </is>
-      </c>
-      <c r="B256" s="11" t="n"/>
-      <c r="C256" s="11" t="n"/>
-      <c r="D256" s="12" t="n"/>
+      <c r="A256" s="4" t="n"/>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>Synced with ramprate-ui's MCP server (2026-10-09, owner asked; card included by their choice)</t>
+        </is>
+      </c>
+      <c r="C256" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D256" s="4" t="inlineStr">
+        <is>
+          <t>the review card for ChatGPT/Claude (one status and next step, Build / Type check / Lint / GitHub / phone-and-laptop checks, "what goes live" and what doesn't, Preview / Discard / Publish / Retry, history with Restore); start_change restates the request (understood_as) and unclear ones wait for the person's OK (confirm_change); before (live) / after (preview) screenshots on phone and laptop; attached images and files (ChatGPT file, or request_upload_link, a private 30-minute upload page at /api/mcp/upload, size and real-type checked); every change result lists the other waiting changes and the AI ends its reply with them (new Status Report line); the server lints changed files itself; ESLint now traced into the deployed function (serverExternalPackages; ramprate's tracing globs crash Turbopack under pnpm, left out). Everything named for tonygreenberg.com only (Netlify tonygreenberg-website, live tonygreenberg.com, card ui://tonygreenberg-admin/...). Verified on a local production build: type check, lint, build; 30 tools listed; card served and its script valid; rules include migrationStatus; list_pending_changes returns other pending changes; check_code_quality runs ESLint; upload page refuses bad links (401). See docs/ai/project_mcp_server.md.</t>
+        </is>
+      </c>
+      <c r="E256" s="14" t="inlineStr">
+        <is>
+          <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="4" t="n"/>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Per-page generateMetadata (title, description, OG, Twitter Card, canonical) for every ported route, sourced from Sanity seo object where con…</t>
-        </is>
-      </c>
-      <c r="C257" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Test the new review end to end on a deploy preview</t>
+        </is>
+      </c>
+      <c r="C257" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>tent is CMS-backed, static otherwise. Audited all 140 page.tsx files: only /studio has none (correct — it's robots.txt-disallowed, not public content). Real gap found and fixed: /blog/category/[slug] had no alternates.canonical at all, and no page-aware title for its own real pagination (?page=N) — every paginated page was serving an identical title with no canonical, a real duplicate-content signal. Fixed: generateMetadata now reads searchParams too, self-canonicals each page (?page=N pages canonical to themselves, not consolidated to page 1 — genuinely different posts per page, matching Google's current pagination guidance) and appends "— Page N" to the title past page 1. Verified live: page 1 canonicals to the bare URL, ?page=2 canonicals to ?page=2 with a distinct title.</t>
+          <t>(needs a yes, it opens a real pull request): one throwaway change from Claude.ai or ChatGPT: start (unclear request, so the confirm step shows), confirm, edit, review card, screenshots, upload link, then discard.</t>
         </is>
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
+          <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="10" t="inlineStr">
+        <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
         </is>
       </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="4" t="n"/>
-      <c r="B258" s="4" t="inlineStr">
-        <is>
-          <t>sitemap.ts generated from real Sanity content + static route list, auto-updates on publish</t>
-        </is>
-      </c>
-      <c r="C258" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D258" s="4" t="inlineStr">
-        <is>
-          <t>Extended from the Phase 5-era version (homepage + blog posts only, 122 URLs) to every real route: the full static route list (130 routes, generated from find src/app -name page.tsx, excluding /studio (robots.txt-disallowed), /(auth)/login (noindex via its own metadata), and /life-assessment (a pure redirect, not distinct content)) plus all 5 real dynamic sources — blog categories (allCategorySlugsQuery), BrewSoul cities (25), BrewSoul coffees (107), and charity-scorecard entries (103) — each pulled from the exact same data source its own page's generateStaticParams already uses, not re-derived. Auto-updates on publish for anything Sanity-backed (blog posts/categories) since it's a live client.fetch on every build; the static route list itself needs a one-line addition whenever a new page ships (same as any other route-registration step). Verified live: 496 real &lt;loc&gt; entries, spot-checked a coffee/city/charity/category URL each, typecheck/lint clean.</t>
-        </is>
-      </c>
-      <c r="E258" s="14" t="inlineStr">
-        <is>
-          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
-        </is>
-      </c>
+      <c r="B258" s="11" t="n"/>
+      <c r="C258" s="11" t="n"/>
+      <c r="D258" s="12" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="n"/>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>llms.txt</t>
+          <t>Per-page generateMetadata (title, description, OG, Twitter Card, canonical) for every ported route, sourced from Sanity seo object where con…</t>
         </is>
       </c>
       <c r="C259" s="13" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>fetched verbatim from the still-live site and saved to web/public/llms.txt (real content: Tony's bio, expertise, full article index by category, every product/tool section) — do this before Manus goes away, it won't be recoverable after</t>
+          <t>tent is CMS-backed, static otherwise. Audited all 140 page.tsx files: only /studio has none (correct — it's robots.txt-disallowed, not public content). Real gap found and fixed: /blog/category/[slug] had no alternates.canonical at all, and no page-aware title for its own real pagination (?page=N) — every paginated page was serving an identical title with no canonical, a real duplicate-content signal. Fixed: generateMetadata now reads searchParams too, self-canonicals each page (?page=N pages canonical to themselves, not consolidated to page 1 — genuinely different posts per page, matching Google's current pagination guidance) and appends "— Page N" to the title past page 1. Verified live: page 1 canonicals to the bare URL, ?page=2 canonicals to ?page=2 with a distinct title.</t>
         </is>
       </c>
       <c r="E259" s="14" t="inlineStr">
@@ -6814,7 +6814,7 @@
       <c r="A260" s="4" t="n"/>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>robots.txt</t>
+          <t>sitemap.ts generated from real Sanity content + static route list, auto-updates on publish</t>
         </is>
       </c>
       <c r="C260" s="13" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>same approach: fetched the real live file (not my earlier guessed robots.ts, which has been removed) and saved verbatim to web/public/robots.txt, plus added Disallow: /studio for the new Sanity Studio route. Confirmed live: real AI-crawler allowlist (GPTBot, Claude-Web, PerplexityBot, etc.), scraper blocklist, and the site's non-standard LLMs: directive all intact</t>
+          <t>Extended from the Phase 5-era version (homepage + blog posts only, 122 URLs) to every real route: the full static route list (130 routes, generated from find src/app -name page.tsx, excluding /studio (robots.txt-disallowed), /(auth)/login (noindex via its own metadata), and /life-assessment (a pure redirect, not distinct content)) plus all 5 real dynamic sources — blog categories (allCategorySlugsQuery), BrewSoul cities (25), BrewSoul coffees (107), and charity-scorecard entries (103) — each pulled from the exact same data source its own page's generateStaticParams already uses, not re-derived. Auto-updates on publish for anything Sanity-backed (blog posts/categories) since it's a live client.fetch on every build; the static route list itself needs a one-line addition whenever a new page ships (same as any other route-registration step). Verified live: 496 real &lt;loc&gt; entries, spot-checked a coffee/city/charity/category URL each, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E260" s="14" t="inlineStr">
@@ -6837,7 +6837,7 @@
       <c r="A261" s="4" t="n"/>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>JSON-LD</t>
+          <t>llms.txt</t>
         </is>
       </c>
       <c r="C261" s="13" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>WebSite + Person schema ported verbatim from the live homepage's actual &lt;script type="application/ld+json"&gt; tags (not reconstructed from memory) — rendered site-wide from src/lib/structured-data.ts in the root layout. The Person image was hardcoded to a /api/img/... legacy proxy path on the live site — rescued that headshot (downloaded it while still live, uploaded to Sanity as the author-tony-greenberg document's avatar) so the new site's JSON-LD has zero Manus dependency instead of just copying the fragile path forward</t>
+          <t>fetched verbatim from the still-live site and saved to web/public/llms.txt (real content: Tony's bio, expertise, full article index by category, every product/tool section) — do this before Manus goes away, it won't be recoverable after</t>
         </is>
       </c>
       <c r="E261" s="14" t="inlineStr">
@@ -6860,7 +6860,7 @@
       <c r="A262" s="4" t="n"/>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>Article JSON-LD on /blog/[slug], built from real per-post Sanity data (headline, image, datePublished/dateModified, author, canonical URL)</t>
+          <t>robots.txt</t>
         </is>
       </c>
       <c r="C262" s="13" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>verified live on a real post</t>
+          <t>same approach: fetched the real live file (not my earlier guessed robots.ts, which has been removed) and saved verbatim to web/public/robots.txt, plus added Disallow: /studio for the new Sanity Studio route. Confirmed live: real AI-crawler allowlist (GPTBot, Claude-Web, PerplexityBot, etc.), scraper blocklist, and the site's non-standard LLMs: directive all intact</t>
         </is>
       </c>
       <c r="E262" s="14" t="inlineStr">
@@ -6883,7 +6883,7 @@
       <c r="A263" s="4" t="n"/>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>/path/:archetype (src/app/path/[archetype]/page.tsx)</t>
+          <t>JSON-LD</t>
         </is>
       </c>
       <c r="C263" s="13" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>per-archetype landing page for /assessment's Builder/Crusader/Investor result, reusing lib/content/archetypes.ts. Real content ported in full (top-5 essential-reading list per archetype via allPostsForArchiveQuery, real PathSubscribeForm posting to /api/subscribe, AUTHORITY_ITEMS strip). Real bug fixed vs. legacy: replaced a hand-rolled inline-styled "Path not found" div with a real notFound() (this route's generateStaticParams only ever produces the 3 real keys). Verified live: all 3 archetype routes 200 OK, typecheck/lint clean.</t>
+          <t>WebSite + Person schema ported verbatim from the live homepage's actual &lt;script type="application/ld+json"&gt; tags (not reconstructed from memory) — rendered site-wide from src/lib/structured-data.ts in the root layout. The Person image was hardcoded to a /api/img/... legacy proxy path on the live site — rescued that headshot (downloaded it while still live, uploaded to Sanity as the author-tony-greenberg document's avatar) so the new site's JSON-LD has zero Manus dependency instead of just copying the fragile path forward</t>
         </is>
       </c>
       <c r="E263" s="14" t="inlineStr">
@@ -6906,7 +6906,7 @@
       <c r="A264" s="4" t="n"/>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>/my-journey (src/app/my-journey/page.tsx + components/assessments/my-journey-dashboard.tsx)</t>
+          <t>Article JSON-LD on /blog/[slug], built from real per-post Sanity data (headline, image, datePublished/dateModified, author, canonical URL)</t>
         </is>
       </c>
       <c r="C264" s="13" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>"My Journey Dashboard," real grid/timeline views across all 28 JOURNEY_MAP experiences, category/status filters, phase progress ring, recommended-next card, using the same real useJourneyProgress/JOURNEY_MAP completion tracking every "Find Your X" quiz already writes to (not the narrower tg_assessment_results cookie built for /self-portrait). Legacy's per-quiz scored-result caching (RESULT_KEYS, feeding a mini radar chart) was not ported — no quiz in this migration writes that data either, same honest-degradation call already made for /self-portrait's own composite radar. Fixed a real legacy dead link (/ecosystem-map, a still-unbuilt page) to /self-portrait. Verified live: 200 OK, real content confirmed, typecheck/lint clean.</t>
+          <t>verified live on a real post</t>
         </is>
       </c>
       <c r="E264" s="14" t="inlineStr">
@@ -6929,7 +6929,7 @@
       <c r="A265" s="4" t="n"/>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>/the-open-door (src/app/the-open-door/page.tsx)</t>
+          <t>/path/:archetype (src/app/path/[archetype]/page.tsx)</t>
         </is>
       </c>
       <c r="C265" s="13" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>real press/credibility content: all 10 "Magic Genie" client-pitch prompts (real named targets — Marco Argenti/Goldman Sachs, Adam Smith/Disney, etc.), 18 real client testimonials, all 8 explicitly-labeled satirical "parody" quotes (kept with disclaimers, not presented as real). Real overlap found and reconciled: this page's publications/speaking/podcasts arrays substantially duplicate the already-shipped /published's fuller bibliography — kept only what /published doesn't cover (Forbes + Business Insider bylines, the Clinton Global Initiative keynote, 4 of 5 podcast appearances) and cross-linked to /published for the rest, same reconciliation pattern as /assessments vs /find-my. Real bugs fixed: 3 genie/keynote links pointed externally at tonygreenberg.com/&lt;slug&gt; for posts that are real internal posts in this migration — relinked to /blog/psychedelics-could-become-extractive-capitalism, /blog/boiling-the-human-summit-harvard-kurzweil, /blog/return-on-investment-going-green-going-green-2 (all verified 200); a bare self-link to tonygreenberg.com remapped to /. Ships as a pure Server Component (legacy's FadeIn/Section/editorial-component dependencies don't exist here and weren't needed). Verified live: 200 OK, real content in raw SSR HTML, typecheck/lint clean.</t>
+          <t>per-archetype landing page for /assessment's Builder/Crusader/Investor result, reusing lib/content/archetypes.ts. Real content ported in full (top-5 essential-reading list per archetype via allPostsForArchiveQuery, real PathSubscribeForm posting to /api/subscribe, AUTHORITY_ITEMS strip). Real bug fixed vs. legacy: replaced a hand-rolled inline-styled "Path not found" div with a real notFound() (this route's generateStaticParams only ever produces the 3 real keys). Verified live: all 3 archetype routes 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E265" s="14" t="inlineStr">
@@ -6952,7 +6952,7 @@
       <c r="A266" s="4" t="n"/>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>Homepage "Recent Updates" band (2026-09-29)</t>
+          <t>/my-journey (src/app/my-journey/page.tsx + components/assessments/my-journey-dashboard.tsx)</t>
         </is>
       </c>
       <c r="C266" s="13" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>on the live site (a newer Blog.tsx than _legacy-manus-app/, so rebuilt from the live page's markup), replacing the older "Latest Thinking" pair. Found while doing it: two live essays are missing from Sanity, the-tollbooth-and-the-alternative (Aug 18, 2026, the live site's newest) and what-quest-could-fix. Both were published on live after the legacy snapshot and need importing.</t>
+          <t>"My Journey Dashboard," real grid/timeline views across all 28 JOURNEY_MAP experiences, category/status filters, phase progress ring, recommended-next card, using the same real useJourneyProgress/JOURNEY_MAP completion tracking every "Find Your X" quiz already writes to (not the narrower tg_assessment_results cookie built for /self-portrait). Legacy's per-quiz scored-result caching (RESULT_KEYS, feeding a mini radar chart) was not ported — no quiz in this migration writes that data either, same honest-degradation call already made for /self-portrait's own composite radar. Fixed a real legacy dead link (/ecosystem-map, a still-unbuilt page) to /self-portrait. Verified live: 200 OK, real content confirmed, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E266" s="14" t="inlineStr">
@@ -6975,7 +6975,7 @@
       <c r="A267" s="4" t="n"/>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Re-sync the legacy reference</t>
+          <t>/the-open-door (src/app/the-open-door/page.tsx)</t>
         </is>
       </c>
       <c r="C267" s="13" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>_legacy-manus-app/ is older than what's live (Recent Updates proves it), so visual diffs should be against the live site, not only that folder. Closed 2026-10-08: done the way this item suggests: every comparison since 2026-10-01 is against the live site itself (163 pages + 121 posts on 2026-10-01, 188 pages on 2026-10-07, 18 redesigned pages on 2026-10-08), with _legacy-manus-app/ used only as the code reference.</t>
+          <t>real press/credibility content: all 10 "Magic Genie" client-pitch prompts (real named targets — Marco Argenti/Goldman Sachs, Adam Smith/Disney, etc.), 18 real client testimonials, all 8 explicitly-labeled satirical "parody" quotes (kept with disclaimers, not presented as real). Real overlap found and reconciled: this page's publications/speaking/podcasts arrays substantially duplicate the already-shipped /published's fuller bibliography — kept only what /published doesn't cover (Forbes + Business Insider bylines, the Clinton Global Initiative keynote, 4 of 5 podcast appearances) and cross-linked to /published for the rest, same reconciliation pattern as /assessments vs /find-my. Real bugs fixed: 3 genie/keynote links pointed externally at tonygreenberg.com/&lt;slug&gt; for posts that are real internal posts in this migration — relinked to /blog/psychedelics-could-become-extractive-capitalism, /blog/boiling-the-human-summit-harvard-kurzweil, /blog/return-on-investment-going-green-going-green-2 (all verified 200); a bare self-link to tonygreenberg.com remapped to /. Ships as a pure Server Component (legacy's FadeIn/Section/editorial-component dependencies don't exist here and weren't needed). Verified live: 200 OK, real content in raw SSR HTML, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E267" s="14" t="inlineStr">
@@ -6998,7 +6998,7 @@
       <c r="A268" s="4" t="n"/>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>Visual diff pass: every ported page vs</t>
+          <t>Homepage "Recent Updates" band (2026-09-29)</t>
         </is>
       </c>
       <c r="C268" s="13" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>legacy page Closed 2026-10-08: covered by the live-site sweeps above (screenshots and measured title/label/spacing per page, see the 2026-10-01, 10-02, 10-07 and 10-08 entries in this phase). Remaining differences are listed as decisions (Cormorant titles, /find-my header) or deliberate (CONTRIBUTING rule 20).</t>
+          <t>on the live site (a newer Blog.tsx than _legacy-manus-app/, so rebuilt from the live page's markup), replacing the older "Latest Thinking" pair. Found while doing it: two live essays are missing from Sanity, the-tollbooth-and-the-alternative (Aug 18, 2026, the live site's newest) and what-quest-could-fix. Both were published on live after the legacy snapshot and need importing.</t>
         </is>
       </c>
       <c r="E268" s="14" t="inlineStr">
@@ -7021,7 +7021,7 @@
       <c r="A269" s="4" t="n"/>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Padding / spacing on the story pages matched to live (2026-10-01)</t>
+          <t>Re-sync the legacy reference</t>
         </is>
       </c>
       <c r="C269" s="13" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>Measured margins, text column and spacing on 31 pages, live vs a production build, at 375px and 1280px. The "door" story pages were the clear mismatch: live's text column is ~546px (ours was 720px), 20px side margins on phones / 40px on desktop, body text 19px/1.8 on phones and 18px/1.85 on desktop (ours 16px/1.5). Fixed on /the-body, /engine-room, /under-nda, /the-nightstand, /the-web, /the-territory, /about, /intel (Intel uses live's 16.8px/1.9; About's hero line 480px max, 18.4px/1.8). Re-measured: all 8 match live to within 2px (About's column 28px narrower), no sideways scroll at 375px.</t>
+          <t>_legacy-manus-app/ is older than what's live (Recent Updates proves it), so visual diffs should be against the live site, not only that folder. Closed 2026-10-08: done the way this item suggests: every comparison since 2026-10-01 is against the live site itself (163 pages + 121 posts on 2026-10-01, 188 pages on 2026-10-07, 18 redesigned pages on 2026-10-08), with _legacy-manus-app/ used only as the code reference.</t>
         </is>
       </c>
       <c r="E269" s="14" t="inlineStr">
@@ -7044,7 +7044,7 @@
       <c r="A270" s="4" t="n"/>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>Header-to-title spacing re-checked (2026-10-02)</t>
+          <t>Visual diff pass: every ported page vs</t>
         </is>
       </c>
       <c r="C270" s="13" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>The 2026-10-01 note compared different things: live's header wasn't measured (it showed 0), so "96px vs 168px" was really 161px vs 168px from the top of the page. Measured again from the top of the page, live vs a production build, at 375px and 1280px: most pages were already within 10px. Fixed the real gaps: /the-open-door (now live's dark centered hero band, 56px title, 546px text column; title was 72px too high), /start-here (live's 48px/96px top padding; 25px too high on desktop), /invest and /engage (label spacing and live's 32px/51px title; /invest's desktop title was 36px), /impact-dashboard on phones (card edge to edge under the header like live; title was 89px too low). Re-measured: all within 8px of live, no sideways scroll at 375px, no JS errors.</t>
+          <t>legacy page Closed 2026-10-08: covered by the live-site sweeps above (screenshots and measured title/label/spacing per page, see the 2026-10-01, 10-02, 10-07 and 10-08 entries in this phase). Remaining differences are listed as decisions (Cormorant titles, /find-my header) or deliberate (CONTRIBUTING rule 20).</t>
         </is>
       </c>
       <c r="E270" s="14" t="inlineStr">
@@ -7067,7 +7067,7 @@
       <c r="A271" s="4" t="n"/>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>HumanOS headings in capitals like live (2026-10-02, owner said yes)</t>
+          <t>Padding / spacing on the story pages matched to live (2026-10-01)</t>
         </is>
       </c>
       <c r="C271" s="13" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>the 4 headings live capitalises on /humanos (title, "Are you a Maximizer...", "Take the Diagnostic", "The Diagnostic") get uppercase; the words are unchanged. The subpages already matched.</t>
+          <t>Measured margins, text column and spacing on 31 pages, live vs a production build, at 375px and 1280px. The "door" story pages were the clear mismatch: live's text column is ~546px (ours was 720px), 20px side margins on phones / 40px on desktop, body text 19px/1.8 on phones and 18px/1.85 on desktop (ours 16px/1.5). Fixed on /the-body, /engine-room, /under-nda, /the-nightstand, /the-web, /the-territory, /about, /intel (Intel uses live's 16.8px/1.9; About's hero line 480px max, 18.4px/1.8). Re-measured: all 8 match live to within 2px (About's column 28px narrower), no sideways scroll at 375px.</t>
         </is>
       </c>
       <c r="E271" s="14" t="inlineStr">
@@ -7090,7 +7090,7 @@
       <c r="A272" s="4" t="n"/>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>More layout gaps matched to live (2026-10-02)</t>
+          <t>Header-to-title spacing re-checked (2026-10-02)</t>
         </is>
       </c>
       <c r="C272" s="13" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>/series (live's centered 546px column, and a bug fixed: every card kept an empty 240px picture column, squeezing the text; live's per-series picture is one generic placeholder on the Manus proxy, so not copied), /humanos (middle section 900px like live), homepage desktop widths (hero text 804px, Four Doors 1000px, Editor's Picks 1168px, GemSpark edge, section title sizes; live's /blog now shows the homepage), /find-my (photo undimmed and plain background, like live; our site header kept). Re-measured: headings within 3px (/series) to 20px (homepage) of live, no sideways scroll, no JS errors. Note: live's "New here?" tour bar sits over its header and doesn't move the page, so it doesn't affect these numbers.</t>
+          <t>The 2026-10-01 note compared different things: live's header wasn't measured (it showed 0), so "96px vs 168px" was really 161px vs 168px from the top of the page. Measured again from the top of the page, live vs a production build, at 375px and 1280px: most pages were already within 10px. Fixed the real gaps: /the-open-door (now live's dark centered hero band, 56px title, 546px text column; title was 72px too high), /start-here (live's 48px/96px top padding; 25px too high on desktop), /invest and /engage (label spacing and live's 32px/51px title; /invest's desktop title was 36px), /impact-dashboard on phones (card edge to edge under the header like live; title was 89px too low). Re-measured: all within 8px of live, no sideways scroll at 375px, no JS errors.</t>
         </is>
       </c>
       <c r="E272" s="14" t="inlineStr">
@@ -7113,7 +7113,7 @@
       <c r="A273" s="4" t="n"/>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Full sweep vs live (2026-10-02)</t>
+          <t>HumanOS headings in capitals like live (2026-10-02, owner said yes)</t>
         </is>
       </c>
       <c r="C273" s="13" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>142 pages (every non-blog page, 3 of each templated set) at 375px and 1280px, title position, text column, title size. Fixed the shared causes: BrewSoul (live wraps most pages in its frame twice, so a second 52px offset plus the category badge; the landing, cities, directory and quiz pages have neither: src/components/brewsoul/brewsoul-main.tsx; intro paragraphs uncapped like live; 38px titles), Kava (live's extra 52px offset), /the-body, /the-nightstand, /the-web (405px top photo like live), the 6 peptide pages (live's 768/896px intro column), /journeys, /pick-up-the-phone, /published, /ecosystem (546px story column and live's text size). Re-measured: 110 of 120 within 40px / 60px of live.</t>
+          <t>the 4 headings live capitalises on /humanos (title, "Are you a Maximizer...", "Take the Diagnostic", "The Diagnostic") get uppercase; the words are unchanged. The subpages already matched.</t>
         </is>
       </c>
       <c r="E273" s="14" t="inlineStr">
@@ -7136,7 +7136,7 @@
       <c r="A274" s="4" t="n"/>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>Sweep leftovers fixed (2026-10-06)</t>
+          <t>More layout gaps matched to live (2026-10-02)</t>
         </is>
       </c>
       <c r="C274" s="13" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>Ported legacy's exact title sizes, margins and column widths. Measured live vs a production build at 375px and 1280px (H1 distance from the top, H1 size, intro and table widths). Now within 8px and the same title size on /published, /brewsoul/first-sip, /brewsoul/home, /brewsoul/chains (intro 912px like live), /brewsoul/browse, /brewsoul/directory (3-column 952px grid like live), /brewsoul and /brewsoul/quiz (intro 520px), /amplifier (546px column), /diamond-cut, /speaking, /living-declaration, /spirits, /protecting-your-business (tables 730px), and the 5 HumanOS subpages (titles smaller like live, 752px column). No sideways scroll at 375px. Left on purpose: /self-portrait (font matches; our page has a different title and no back link, so it sits 23-57px higher), BrewSoul pages 3-6px off (the shared journey bar row), and the different-layout pages /dharma-finder, /grant-study, /search, /quiz_25q, /soulscore. Also: /brewsoul/quiz rebuilt as a step registry (src/components/brewsoul/brewsoul-quiz/: parent + hook/ + components/step-* + data/), same questions, scoring and look; Back/Skip/Retake use lucide icons. New CONTRIBUTING rule 19 (multi-step flows, FydoPartner pattern). brewsoul-welcome-quiz.tsx (/brewsoul) still has the old shape and text arrows.</t>
+          <t>/series (live's centered 546px column, and a bug fixed: every card kept an empty 240px picture column, squeezing the text; live's per-series picture is one generic placeholder on the Manus proxy, so not copied), /humanos (middle section 900px like live), homepage desktop widths (hero text 804px, Four Doors 1000px, Editor's Picks 1168px, GemSpark edge, section title sizes; live's /blog now shows the homepage), /find-my (photo undimmed and plain background, like live; our site header kept). Re-measured: headings within 3px (/series) to 20px (homepage) of live, no sideways scroll, no JS errors. Note: live's "New here?" tour bar sits over its header and doesn't move the page, so it doesn't affect these numbers.</t>
         </is>
       </c>
       <c r="E274" s="14" t="inlineStr">
@@ -7159,7 +7159,7 @@
       <c r="A275" s="4" t="n"/>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Match live's redesigned pages (2026-10-06, owner said go)</t>
+          <t>Full sweep vs live (2026-10-02)</t>
         </is>
       </c>
       <c r="C275" s="13" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">/self-portrait (live: dark page, progress ring, "N more brushstrokes" lock until 5 assessments), /grant-study and /dharma-finder (live opens straight on question 1, no intro screen), /quiz_25q (live adds a hero picture above the title; rescue it into Sanity first), /search (live: one search box across essays, BrewSoul, peptides, HumanOS, assessments, kava and pages with filter chips). Measure live vs a production build at 375px and 1280px when done. Done 2026-10-06: /grant-study and /dharma-finder open straight on question 1 like live (title block / part header above the first question, live's 546px column, plain page, credit under every question), both rebuilt as step registries (rule 19); measured within 3px of live at the top (dharma's question block within 7px). /quiz_25q's hero rescued into Sanity and placed like live (within 2px). Found and fixed on the way: on the deployed copy /grant-study's answer buttons could not be clicked (the themed page background was fixed z-0, painted over the quiz); ThemedBackground is now -z-10 pointer-events-none (backgrounds unchanged on all 21 pages that use it), and the shared email gate no longer scrolls sideways on phones. Both quizzes clicked through to results in Chrome and Safari. /self-portrait restyled to live (dark page, "The Composite You", progress ring, "N More Brushstrokes Needed" lock until 5 done, live's copy) on our real cookie data; within 3px of live at both widths; tested with 0, 2 and 6 completed. Counts are ours (13 </t>
+          <t>142 pages (every non-blog page, 3 of each templated set) at 375px and 1280px, title position, text column, title size. Fixed the shared causes: BrewSoul (live wraps most pages in its frame twice, so a second 52px offset plus the category badge; the landing, cities, directory and quiz pages have neither: src/components/brewsoul/brewsoul-main.tsx; intro paragraphs uncapped like live; 38px titles), Kava (live's extra 52px offset), /the-body, /the-nightstand, /the-web (405px top photo like live), the 6 peptide pages (live's 768/896px intro column), /journeys, /pick-up-the-phone, /published, /ecosystem (546px story column and live's text size). Re-measured: 110 of 120 within 40px / 60px of live.</t>
         </is>
       </c>
       <c r="E275" s="14" t="inlineStr">
@@ -7182,17 +7182,17 @@
       <c r="A276" s="4" t="n"/>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>Still different from live (needs a yes)</t>
-        </is>
-      </c>
-      <c r="C276" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Sweep leftovers fixed (2026-10-06)</t>
+        </is>
+      </c>
+      <c r="C276" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>blog posts (done) (done 2026-10-07, see Phase 5); /find-my on live hides the site header. /walk-through is a 404 on live now.</t>
+          <t>Ported legacy's exact title sizes, margins and column widths. Measured live vs a production build at 375px and 1280px (H1 distance from the top, H1 size, intro and table widths). Now within 8px and the same title size on /published, /brewsoul/first-sip, /brewsoul/home, /brewsoul/chains (intro 912px like live), /brewsoul/browse, /brewsoul/directory (3-column 952px grid like live), /brewsoul and /brewsoul/quiz (intro 520px), /amplifier (546px column), /diamond-cut, /speaking, /living-declaration, /spirits, /protecting-your-business (tables 730px), and the 5 HumanOS subpages (titles smaller like live, 752px column). No sideways scroll at 375px. Left on purpose: /self-portrait (font matches; our page has a different title and no back link, so it sits 23-57px higher), BrewSoul pages 3-6px off (the shared journey bar row), and the different-layout pages /dharma-finder, /grant-study, /search, /quiz_25q, /soulscore. Also: /brewsoul/quiz rebuilt as a step registry (src/components/brewsoul/brewsoul-quiz/: parent + hook/ + components/step-* + data/), same questions, scoring and look; Back/Skip/Retake use lucide icons. New CONTRIBUTING rule 19 (multi-step flows, FydoPartner pattern). brewsoul-welcome-quiz.tsx (/brewsoul) still has the old shape and text arrows.</t>
         </is>
       </c>
       <c r="E276" s="14" t="inlineStr">
@@ -7205,17 +7205,17 @@
       <c r="A277" s="4" t="n"/>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Design change on live, needs a decision</t>
-        </is>
-      </c>
-      <c r="C277" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Match live's redesigned pages (2026-10-06, owner said go)</t>
+        </is>
+      </c>
+      <c r="C277" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>live's story pages now use Cormorant Garamond for titles (ours: Playfair Display), a lighter title weight (400 vs our 700), and a red eyebrow label (#8E1E25, wider letter spacing) instead of our gold. A site-wide font swap is a design call, so not done.</t>
+          <t xml:space="preserve">/self-portrait (live: dark page, progress ring, "N more brushstrokes" lock until 5 assessments), /grant-study and /dharma-finder (live opens straight on question 1, no intro screen), /quiz_25q (live adds a hero picture above the title; rescue it into Sanity first), /search (live: one search box across essays, BrewSoul, peptides, HumanOS, assessments, kava and pages with filter chips). Measure live vs a production build at 375px and 1280px when done. Done 2026-10-06: /grant-study and /dharma-finder open straight on question 1 like live (title block / part header above the first question, live's 546px column, plain page, credit under every question), both rebuilt as step registries (rule 19); measured within 3px of live at the top (dharma's question block within 7px). /quiz_25q's hero rescued into Sanity and placed like live (within 2px). Found and fixed on the way: on the deployed copy /grant-study's answer buttons could not be clicked (the themed page background was fixed z-0, painted over the quiz); ThemedBackground is now -z-10 pointer-events-none (backgrounds unchanged on all 21 pages that use it), and the shared email gate no longer scrolls sideways on phones. Both quizzes clicked through to results in Chrome and Safari. /self-portrait restyled to live (dark page, "The Composite You", progress ring, "N More Brushstrokes Needed" lock until 5 done, live's copy) on our real cookie data; within 3px of live at both widths; tested with 0, 2 and 6 completed. Counts are ours (13 </t>
         </is>
       </c>
       <c r="E277" s="14" t="inlineStr">
@@ -7228,17 +7228,17 @@
       <c r="A278" s="4" t="n"/>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>Link check across all ported pages (no 404s, no broken internal cross-references)</t>
-        </is>
-      </c>
-      <c r="C278" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Still different from live (needs a yes)</t>
+        </is>
+      </c>
+      <c r="C278" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>First full pass done 2026-09-29 (510 pages crawled from the sitemap plus every internal link, on a production build). Fixed in code: /brewsoul/coffee/…-tarrazú 404 (the route got the id still percent-encoded), 30+ links that went through the /assessments/* redirects, /find-your-me's dead Homeaglow link, the two root-level Iboga essay links, and the dead FauxTony nav item. Fixed as Sanity drafts (scripts/fix-blog-body-links.ts, 14 posts): broken post links, leaked !… placeholder text, Energy Is Money's split author bio, and scraped WordPress furniture ("Share this / Related / You Might Also Like / Copyright", "Show More / Top News", [mc4wp_form]). Left for a decision: /framework's "Ask FauxTony" button, when-healing-becomes-extraction's two links to a Dr. Lee case file that doesn't exist, and the-clock-keeper-chronicles-part-1's link to the deferred /clock-keeper-part-2. Re-run after the drafts are published. 2026-10-01 re-run (local production build, all 498 sitemap URLs load; 440 unique internal links): 5 broken. Fixed as a Sanity draft: molecule-as-mirror-10-what-the-pioneers-know's "Final installment" link pointed at a non-existent part-10 slug (now part 11; live also shows that line twice, kept). Already fixed in a waiting draft: forever-chemicals-... → /blog/psychedelic-readiness-index. Still the 3 known decisions: /fauxtony (from /framework), /clock-keeper-part-2, /blog/the-case-file-dr-samuel-lee. 2026-10-08 re-run (production build, all 497 sitemap pages, 453 unique i</t>
+          <t>blog posts (done) (done 2026-10-07, see Phase 5); /find-my on live hides the site header. /walk-through is a 404 on live now.</t>
         </is>
       </c>
       <c r="E278" s="14" t="inlineStr">
@@ -7251,17 +7251,17 @@
       <c r="A279" s="4" t="n"/>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Sitemap: no noindex pages (2026-10-08)</t>
-        </is>
-      </c>
-      <c r="C279" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design change on live, needs a decision</t>
+        </is>
+      </c>
+      <c r="C279" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>the password-locked /blog/you-are-the-moat was in the sitemap while telling Google not to index it (a Search Console sitemap warning). Gated posts and posts that redirect are now left out (src/app/sitemap.ts); all 497 sitemap addresses return 200 with a matching canonical and no noindex. The 82 warnings Search Console shows are for the old live sitemap, so re-check them after cutover.</t>
+          <t>live's story pages now use Cormorant Garamond for titles (ours: Playfair Display), a lighter title weight (400 vs our 700), and a red eyebrow label (#8E1E25, wider letter spacing) instead of our gold. A site-wide font swap is a design call, so not done.</t>
         </is>
       </c>
       <c r="E279" s="14" t="inlineStr">
@@ -7274,17 +7274,17 @@
       <c r="A280" s="4" t="n"/>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>Lighthouse pass (performance/accessibility/SEO) on top 20 pages by traffic 2026-09-30, 20 key pages (no traffic data yet), local production …</t>
-        </is>
-      </c>
-      <c r="C280" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Link check across all ported pages (no 404s, no broken internal cross-references)</t>
+        </is>
+      </c>
+      <c r="C280" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>build, mobile: averages performance 87, accessibility 99→100, best practices 100, SEO 92→100, CLS 0 everywhere. Fixed: public/robots.txt had an LLMs: line (not a real directive) that made Google treat the whole file as invalid, now a comment; h3/h4 headings skipping a level on /assessments, /kava, /peptide-watch (same look, right tag); the Kava and /attention-theft back-arrow links had no accessible name on phones; two small phone-width contrast misses. Left: performance is local-machine only (±10-15 points, see CONTRIBUTING.md); the slowest were / 76 (LCP 5.2 s), /psychedelic-readiness-index 82, /iboga-ibogaine 83. Re-run against the Netlify deploy before launch. 2026-10-06 re-run against the Netlify deploy (14 key pages, mobile): accessibility 100 and CLS 0 on every page, SEO clean (only the expected netlify.app noindex), performance 77-97 held back by 3-4 s LCP. Fixed: all 21 hero images moved off the deprecated priority prop to fetchPriority="high" + loading="eager" (Next 16); /iboga-ibogaine hero and the first card on /blog and category pages no longer lazy-loaded; sizes on the Four Doors cards (~150 KiB per page), /humanos diagram (~100 KiB) and /about headshot; urlFor no longer imports the Sanity client, so ~115 KB of Sanity client code stopped loading on / and /blog; React hydration error #418 on / and /blog (post dates) gone, checked in two time zones; /blog is static again; empty icon &lt;th&gt;s on /iboga-ibogaine labelled; category page reads use sanityFetch(). Left: se</t>
+          <t>First full pass done 2026-09-29 (510 pages crawled from the sitemap plus every internal link, on a production build). Fixed in code: /brewsoul/coffee/…-tarrazú 404 (the route got the id still percent-encoded), 30+ links that went through the /assessments/* redirects, /find-your-me's dead Homeaglow link, the two root-level Iboga essay links, and the dead FauxTony nav item. Fixed as Sanity drafts (scripts/fix-blog-body-links.ts, 14 posts): broken post links, leaked !… placeholder text, Energy Is Money's split author bio, and scraped WordPress furniture ("Share this / Related / You Might Also Like / Copyright", "Show More / Top News", [mc4wp_form]). Left for a decision: /framework's "Ask FauxTony" button, when-healing-becomes-extraction's two links to a Dr. Lee case file that doesn't exist, and the-clock-keeper-chronicles-part-1's link to the deferred /clock-keeper-part-2. Re-run after the drafts are published. 2026-10-01 re-run (local production build, all 498 sitemap URLs load; 440 unique internal links): 5 broken. Fixed as a Sanity draft: molecule-as-mirror-10-what-the-pioneers-know's "Final installment" link pointed at a non-existent part-10 slug (now part 11; live also shows that line twice, kept). Already fixed in a waiting draft: forever-chemicals-... → /blog/psychedelic-readiness-index. Still the 3 known decisions: /fauxtony (from /framework), /clock-keeper-part-2, /blog/the-case-file-dr-samuel-lee. 2026-10-08 re-run (production build, all 497 sitemap pages, 453 unique i</t>
         </is>
       </c>
       <c r="E280" s="14" t="inlineStr">
@@ -7297,7 +7297,7 @@
       <c r="A281" s="4" t="n"/>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>SEO audit fixes (2026-10-06)</t>
+          <t>Sitemap: no noindex pages (2026-10-08)</t>
         </is>
       </c>
       <c r="C281" s="13" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
+          <t>the password-locked /blog/you-are-the-moat was in the sitemap while telling Google not to index it (a Search Console sitemap warning). Gated posts and posts that redirect are now left out (src/app/sitemap.ts); all 497 sitemap addresses return 200 with a matching canonical and no noindex. The 82 warnings Search Console shows are for the old live sitemap, so re-check them after cutover.</t>
         </is>
       </c>
       <c r="E281" s="14" t="inlineStr">
@@ -7320,7 +7320,7 @@
       <c r="A282" s="4" t="n"/>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>SEO audit items needing a yes (2026-10-06)</t>
+          <t>Lighthouse pass (performance/accessibility/SEO) on top 20 pages by traffic 2026-09-30, 20 key pages (no traffic data yet), local production …</t>
         </is>
       </c>
       <c r="C282" s="15" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+          <t>build, mobile: averages performance 87, accessibility 99→100, best practices 100, SEO 92→100, CLS 0 everywhere. Fixed: public/robots.txt had an LLMs: line (not a real directive) that made Google treat the whole file as invalid, now a comment; h3/h4 headings skipping a level on /assessments, /kava, /peptide-watch (same look, right tag); the Kava and /attention-theft back-arrow links had no accessible name on phones; two small phone-width contrast misses. Left: performance is local-machine only (±10-15 points, see CONTRIBUTING.md); the slowest were / 76 (LCP 5.2 s), /psychedelic-readiness-index 82, /iboga-ibogaine 83. Re-run against the Netlify deploy before launch. 2026-10-06 re-run against the Netlify deploy (14 key pages, mobile): accessibility 100 and CLS 0 on every page, SEO clean (only the expected netlify.app noindex), performance 77-97 held back by 3-4 s LCP. Fixed: all 21 hero images moved off the deprecated priority prop to fetchPriority="high" + loading="eager" (Next 16); /iboga-ibogaine hero and the first card on /blog and category pages no longer lazy-loaded; sizes on the Four Doors cards (~150 KiB per page), /humanos diagram (~100 KiB) and /about headshot; urlFor no longer imports the Sanity client, so ~115 KB of Sanity client code stopped loading on / and /blog; React hydration error #418 on / and /blog (post dates) gone, checked in two time zones; /blog is static again; empty icon &lt;th&gt;s on /iboga-ibogaine labelled; category page reads use sanityFetch(). Left: se</t>
         </is>
       </c>
       <c r="E282" s="14" t="inlineStr">
@@ -7343,15 +7343,19 @@
       <c r="A283" s="4" t="n"/>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
-        </is>
-      </c>
-      <c r="C283" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D283" s="4" t="inlineStr"/>
+          <t>SEO audit fixes (2026-10-06)</t>
+        </is>
+      </c>
+      <c r="C283" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D283" s="4" t="inlineStr">
+        <is>
+          <t>Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
+        </is>
+      </c>
       <c r="E283" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -7362,17 +7366,17 @@
       <c r="A284" s="4" t="n"/>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
-        </is>
-      </c>
-      <c r="C284" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>SEO audit items needing a yes (2026-10-06)</t>
+        </is>
+      </c>
+      <c r="C284" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
+          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
         </is>
       </c>
       <c r="E284" s="14" t="inlineStr">
@@ -7385,19 +7389,15 @@
       <c r="A285" s="4" t="n"/>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>"Keep going" strip above the footer on every page (2026-10-07)</t>
-        </is>
-      </c>
-      <c r="C285" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D285" s="4" t="inlineStr">
-        <is>
-          <t>legacy's WhereNext (deferred in Phase 3, never picked up) with its per-page suggestions, Home · Site Index · All Assessments; links pointed at current routes.</t>
-        </is>
-      </c>
+          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+        </is>
+      </c>
+      <c r="C285" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D285" s="4" t="inlineStr"/>
       <c r="E285" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -7408,7 +7408,7 @@
       <c r="A286" s="4" t="n"/>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>Live-only and redesigned pages from the 2026-10-07 page sweep (188 pages compared with live)</t>
+          <t>Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
         </is>
       </c>
       <c r="C286" s="13" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>/the-index rebuilt from live's code (20 concepts, related-word search across essays and site pages, full-text search on the server, "three related places to go next"; the old redirect to /search removed and its links, including the "Site Index" link in "Keep going", point at it again); /the-mirror (and /life-assessment) opens on live's intro (dark hero, "What We Measure" with the six areas, "The Ecosystem"), rebuilt as a step registry (rule 19); /essays header, order and column like live; /about "What They Say" styled like live (live picks 3 of the same 19 quotes at random; ours shows a fixed 3 so they're in the server HTML); /impact-futurism list titles and subtitles; /supplier-intake is a real page again with live's Stage 1 form; /seven-doors and /projects redirect home like live; /impact, /health, /library, /built-on-manus, /heroes are 404 on live too. Left as is on purpose: /blog stays our archive page (on live it repeats the homepage), the email gates on /framework and /peptide-supply-chain, the attention-theft Wall of Shame.</t>
+          <t>2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
         </is>
       </c>
       <c r="E286" s="14" t="inlineStr">
@@ -7431,7 +7431,7 @@
       <c r="A287" s="4" t="n"/>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>/alex-azzi locked like live (2026-10-07, owner said match it)</t>
+          <t>"Keep going" strip above the footer on every page (2026-10-07)</t>
         </is>
       </c>
       <c r="C287" s="13" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>same server-checked password as the locked essay (GATED_POST_PASSWORD, now also set in Netlify), live's "Restricted Access" screen, the report not in the page until unlocked, out of search and the sitemap.</t>
+          <t>legacy's WhereNext (deferred in Phase 3, never picked up) with its per-page suggestions, Home · Site Index · All Assessments; links pointed at current routes.</t>
         </is>
       </c>
       <c r="E287" s="14" t="inlineStr">
@@ -7454,7 +7454,7 @@
       <c r="A288" s="4" t="n"/>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>Live's title fonts and sizes (2026-10-07, "fix the style")</t>
+          <t>Live-only and redesigned pages from the 2026-10-07 page sweep (188 pages compared with live)</t>
         </is>
       </c>
       <c r="C288" s="13" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>measured every page's title font, weight, size and label colour on live vs ours (136 pages). Now like live: Kava headings in Fraunces, HumanOS in Space Grotesk, the peptide tools / charity scorecard / thesis threads in the system serif, America Unbundled in the Iowan Old Style stack at live's size, /akbar in Fraunces 900, friend-gate and post-intervention in Georgia, and live's title sizes on peptide-matrix, peptide-supply-chain, rip-peptide-sciences and the HumanOS pages. Fonts load only on the pages that use them (src/lib/fonts/page-fonts.ts). Label colours stay the darker AA-contrast versions where live's lighter ones fail on a light background.</t>
+          <t>/the-index rebuilt from live's code (20 concepts, related-word search across essays and site pages, full-text search on the server, "three related places to go next"; the old redirect to /search removed and its links, including the "Site Index" link in "Keep going", point at it again); /the-mirror (and /life-assessment) opens on live's intro (dark hero, "What We Measure" with the six areas, "The Ecosystem"), rebuilt as a step registry (rule 19); /essays header, order and column like live; /about "What They Say" styled like live (live picks 3 of the same 19 quotes at random; ours shows a fixed 3 so they're in the server HTML); /impact-futurism list titles and subtitles; /supplier-intake is a real page again with live's Stage 1 form; /seven-doors and /projects redirect home like live; /impact, /health, /library, /built-on-manus, /heroes are 404 on live too. Left as is on purpose: /blog stays our archive page (on live it repeats the homepage), the email gates on /framework and /peptide-supply-chain, the attention-theft Wall of Shame.</t>
         </is>
       </c>
       <c r="E288" s="14" t="inlineStr">
@@ -7477,7 +7477,7 @@
       <c r="A289" s="4" t="n"/>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Peptide page images rescued into Sanity and wired (2026-10-07)</t>
+          <t>/alex-azzi locked like live (2026-10-07, owner said match it)</t>
         </is>
       </c>
       <c r="C289" s="13" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>/peptide-watch hero plus its 11 section banners, /peptide-matrix and /peptide-supply-chain heroes, the /peptide-hall-of-shame hero (scripts/rescue-2026-10-07-peptide-images.ts, logged in docs/ai/manus-media-rescue.md).</t>
+          <t>same server-checked password as the locked essay (GATED_POST_PASSWORD, now also set in Netlify), live's "Restricted Access" screen, the report not in the page until unlocked, out of search and the sitemap.</t>
         </is>
       </c>
       <c r="E289" s="14" t="inlineStr">
@@ -7500,7 +7500,7 @@
       <c r="A290" s="4" t="n"/>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>Live's editorial redesign, first group (2026-10-07)</t>
+          <t>Live's title fonts and sizes (2026-10-07, "fix the style")</t>
         </is>
       </c>
       <c r="C290" s="13" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
+          <t>measured every page's title font, weight, size and label colour on live vs ours (136 pages). Now like live: Kava headings in Fraunces, HumanOS in Space Grotesk, the peptide tools / charity scorecard / thesis threads in the system serif, America Unbundled in the Iowan Old Style stack at live's size, /akbar in Fraunces 900, friend-gate and post-intervention in Georgia, and live's title sizes on peptide-matrix, peptide-supply-chain, rip-peptide-sciences and the HumanOS pages. Fonts load only on the pages that use them (src/lib/fonts/page-fonts.ts). Label colours stay the darker AA-contrast versions where live's lighter ones fail on a light background.</t>
         </is>
       </c>
       <c r="E290" s="14" t="inlineStr">
@@ -7523,7 +7523,7 @@
       <c r="A291" s="4" t="n"/>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Live's redesign, second group (done 2026-10-08)</t>
+          <t>Peptide page images rescued into Sanity and wired (2026-10-07)</t>
         </is>
       </c>
       <c r="C291" s="13" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>re-measured all 18 pages on live vs a fresh production build (title font/size/weight/colour, labels, hero images). Already matching from 2026-10-07: /the-web, /spirits, /iboga-ibogaine (weight 800), /living-declaration, BrewSoul photo on /brewsoul, /brewsoul/browse, /brewsoul/first-sip (live has none there either), /quiz_25q, /recent-creations. Fixed today: /find-your-journey (64px title, red label), /impact-dashboard (64px title in essay ink, label spacing), red labels on /published and /speaking (plus its "rooms" chips), /soulscore "by ImpactSoul" label, /pri-calibration title (weight 900, solid cream, was a purple gradient), /clients (live's narrow 546px column for the whole page, 56px title, roomier stats band, cards 2 per row; two static inline styles moved to classes), /brewsoul/guest (live's BrewSoul photo on the guest card instead of "SN" initials, labels in capitals), /humanos/connect (cards line up with the title), /peptide-hall-of-shame (stats and label readable light gold; were dark gold on dark). Typed arrows on the touched links are icons now (rule 18). Deliberately not copied from live (new CONTRIBUTING rule 20, owner 2026-10-08): red labels on dark bands use #E07A80 (live's #8E1E25 on black is about 2:1, unreadable); /recent-creations keeps our darker label colours (live's fail contrast on white); /humanos/connect keeps "Start Reading" (that card links to the philosophy page, the quiz live's "Start the Assessment" implies doesn't exist). Checked: type check, l</t>
+          <t>/peptide-watch hero plus its 11 section banners, /peptide-matrix and /peptide-supply-chain heroes, the /peptide-hall-of-shame hero (scripts/rescue-2026-10-07-peptide-images.ts, logged in docs/ai/manus-media-rescue.md).</t>
         </is>
       </c>
       <c r="E291" s="14" t="inlineStr">
@@ -7546,7 +7546,7 @@
       <c r="A292" s="4" t="n"/>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>BrewSoul top of page (2026-10-08, owner: "button in the center at the top doesn't look good")</t>
+          <t>Live's editorial redesign, first group (2026-10-07)</t>
         </is>
       </c>
       <c r="C292" s="13" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>the category badge ("Deep Research" etc.) sat centred in an empty strip, squeezed against the hero, because we copied live's doubled 52px top gap. Now one gap everywhere and the badge floats in the top-left corner, lined up with the BrewSoul logo (brewsoul-main.tsx, category-badge.tsx); checked on all 26 badge pages at 3 widths that it covers nothing. BrewSoul menu: on tablets (768-1023px) the links were cut off and "More" was hidden with no menu button at all; now the menu button shows below 1024px, 5 links + "More" from 1024px, all 8 from 1280px, "More" always visible.</t>
+          <t>dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
         </is>
       </c>
       <c r="E292" s="14" t="inlineStr">
@@ -7569,7 +7569,7 @@
       <c r="A293" s="4" t="n"/>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>/pri-efficacy's "Simulation / Live Calibrations" switch like live (2026-10-08)</t>
+          <t>Live's redesign, second group (done 2026-10-08)</t>
         </is>
       </c>
       <c r="C293" s="13" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>shadcn Tabs, both panels in the server HTML (forceMount). The Live tab reads real aggregate numbers from pri_calibrations (getPriLiveStats() in src/lib/pri-research.ts: totals, opt-ins, average score per dimension; no rows leave the server), page stays static and refreshes every 10 minutes. Until the Supabase scripts are run (Phase 2) it says the numbers "aren't available just now" instead of a fake zero. Checked: build (○, 10m), server HTML has both tabs, tab switch at 390/1280px, no JS errors. Re-check with real numbers once the table exists.</t>
+          <t>re-measured all 18 pages on live vs a fresh production build (title font/size/weight/colour, labels, hero images). Already matching from 2026-10-07: /the-web, /spirits, /iboga-ibogaine (weight 800), /living-declaration, BrewSoul photo on /brewsoul, /brewsoul/browse, /brewsoul/first-sip (live has none there either), /quiz_25q, /recent-creations. Fixed today: /find-your-journey (64px title, red label), /impact-dashboard (64px title in essay ink, label spacing), red labels on /published and /speaking (plus its "rooms" chips), /soulscore "by ImpactSoul" label, /pri-calibration title (weight 900, solid cream, was a purple gradient), /clients (live's narrow 546px column for the whole page, 56px title, roomier stats band, cards 2 per row; two static inline styles moved to classes), /brewsoul/guest (live's BrewSoul photo on the guest card instead of "SN" initials, labels in capitals), /humanos/connect (cards line up with the title), /peptide-hall-of-shame (stats and label readable light gold; were dark gold on dark). Typed arrows on the touched links are icons now (rule 18). Deliberately not copied from live (new CONTRIBUTING rule 20, owner 2026-10-08): red labels on dark bands use #E07A80 (live's #8E1E25 on black is about 2:1, unreadable); /recent-creations keeps our darker label colours (live's fail contrast on white); /humanos/connect keeps "Start Reading" (that card links to the philosophy page, the quiz live's "Start the Assessment" implies doesn't exist). Checked: type check, l</t>
         </is>
       </c>
       <c r="E293" s="14" t="inlineStr">
@@ -7592,7 +7592,7 @@
       <c r="A294" s="4" t="n"/>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/browse hero readable (2026-10-08, owner said go ahead)</t>
+          <t>BrewSoul top of page (2026-10-08, owner: "button in the center at the top doesn't look good")</t>
         </is>
       </c>
       <c r="C294" s="13" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>a soft cream glow behind the title block so "The Catalog", the subtitle and the stat labels read clearly over the coffee photo (live is hard to read there too; rule 20). Photo still shows around the edges. Checked at 390/1280px.</t>
+          <t>the category badge ("Deep Research" etc.) sat centred in an empty strip, squeezed against the hero, because we copied live's doubled 52px top gap. Now one gap everywhere and the badge floats in the top-left corner, lined up with the BrewSoul logo (brewsoul-main.tsx, category-badge.tsx); checked on all 26 badge pages at 3 widths that it covers nothing. BrewSoul menu: on tablets (768-1023px) the links were cut off and "More" was hidden with no menu button at all; now the menu button shows below 1024px, 5 links + "More" from 1024px, all 8 from 1280px, "More" always visible.</t>
         </is>
       </c>
       <c r="E294" s="14" t="inlineStr">
@@ -7612,20 +7612,33 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="10" t="inlineStr">
-        <is>
-          <t>Phase 13 — Images Needed in Sanity</t>
-        </is>
-      </c>
-      <c r="B295" s="11" t="n"/>
-      <c r="C295" s="11" t="n"/>
-      <c r="D295" s="12" t="n"/>
+      <c r="A295" s="4" t="n"/>
+      <c r="B295" s="4" t="inlineStr">
+        <is>
+          <t>/pri-efficacy's "Simulation / Live Calibrations" switch like live (2026-10-08)</t>
+        </is>
+      </c>
+      <c r="C295" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D295" s="4" t="inlineStr">
+        <is>
+          <t>shadcn Tabs, both panels in the server HTML (forceMount). The Live tab reads real aggregate numbers from pri_calibrations (getPriLiveStats() in src/lib/pri-research.ts: totals, opt-ins, average score per dimension; no rows leave the server), page stays static and refreshes every 10 minutes. Until the Supabase scripts are run (Phase 2) it says the numbers "aren't available just now" instead of a fake zero. Checked: build (○, 10m), server HTML has both tabs, tab switch at 390/1280px, no JS errors. Re-check with real numbers once the table exists.</t>
+        </is>
+      </c>
+      <c r="E295" s="14" t="inlineStr">
+        <is>
+          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="4" t="n"/>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>Manus media rescue (2026-09-29)</t>
+          <t>/brewsoul/browse hero readable (2026-10-08, owner said go ahead)</t>
         </is>
       </c>
       <c r="C296" s="13" t="inlineStr">
@@ -7635,53 +7648,40 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>all 94 Manus-hosted image/video references in the legacy source (/api/img/, /manus-storage/) were checked live. 91 were still downloadable, including the /akbar photos the entry below calls "permanently lost", and all 91 are now Sanity assets (scripts/rescue-manus-media.ts; Sanity dedupes by SHA-1). 3 were gone (HTTP 502). The manifest docs/ai/manus-media-rescue.md maps each one to the legacy files that used it and its Sanity URL. They are not wired into pages yet: go page by page, with real alt text. /facilitator-index's two diagrams are done (scripts/rescue-facilitator-images.ts).</t>
+          <t>a soft cream glow behind the title block so "The Catalog", the subtitle and the stat labels read clearly over the coffee photo (live is hard to read there too; rule 20). Photo still shows around the edges. Checked at 390/1280px.</t>
         </is>
       </c>
       <c r="E296" s="14" t="inlineStr">
         <is>
+          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="10" t="inlineStr">
+        <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="4" t="n"/>
-      <c r="B297" s="4" t="inlineStr">
-        <is>
-          <t>Favicon</t>
-        </is>
-      </c>
-      <c r="C297" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D297" s="4" t="inlineStr">
-        <is>
-          <t>real "G" brand mark generated from the header's actual wordmark treatment (src/app/icon.tsx), see Phase 3</t>
-        </is>
-      </c>
-      <c r="E297" s="14" t="inlineStr">
-        <is>
-          <t>Phase 13 — Images Needed in Sanity</t>
-        </is>
-      </c>
+      <c r="B297" s="11" t="n"/>
+      <c r="C297" s="11" t="n"/>
+      <c r="D297" s="12" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="4" t="n"/>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
-        </is>
-      </c>
-      <c r="C298" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Manus media rescue (2026-09-29)</t>
+        </is>
+      </c>
+      <c r="C298" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
+          <t>all 94 Manus-hosted image/video references in the legacy source (/api/img/, /manus-storage/) were checked live. 91 were still downloadable, including the /akbar photos the entry below calls "permanently lost", and all 91 are now Sanity assets (scripts/rescue-manus-media.ts; Sanity dedupes by SHA-1). 3 were gone (HTTP 502). The manifest docs/ai/manus-media-rescue.md maps each one to the legacy files that used it and its Sanity URL. They are not wired into pages yet: go page by page, with real alt text. /facilitator-index's two diagrams are done (scripts/rescue-facilitator-images.ts).</t>
         </is>
       </c>
       <c r="E298" s="14" t="inlineStr">
@@ -7694,7 +7694,7 @@
       <c r="A299" s="4" t="n"/>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Author photo(s) for blog author schema (Tony Greenberg headshot at minimum)</t>
+          <t>Favicon</t>
         </is>
       </c>
       <c r="C299" s="13" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: the rescued headshot is already the author avatar in Sanity; now also in every post's Article JSON-LD (author image + url /about). The JSON-LD publisher logo pointed at /favicon.ico, a 404 here; now /icon.</t>
+          <t>real "G" brand mark generated from the header's actual wordmark treatment (src/app/icon.tsx), see Phase 3</t>
         </is>
       </c>
       <c r="E299" s="14" t="inlineStr">
@@ -7717,17 +7717,17 @@
       <c r="A300" s="4" t="n"/>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>Blog hero images</t>
-        </is>
-      </c>
-      <c r="C300" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
+        </is>
+      </c>
+      <c r="C300" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>audited, then migrated. Final state:</t>
+          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
         </is>
       </c>
       <c r="E300" s="14" t="inlineStr">
@@ -7740,7 +7740,7 @@
       <c r="A301" s="4" t="n"/>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>22 posts have a real hero image, now live in Sanity (17 already on RampRate's own CloudFront + 4 rescued from the legacy /api/img/ proxy + 1…</t>
+          <t>Author photo(s) for blog author schema (Tony Greenberg headshot at minimum)</t>
         </is>
       </c>
       <c r="C301" s="13" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> rescued from /manus-storage/, all pulled over by migrate-blog-posts.ts before Manus is decommissioned)</t>
+          <t>2026-10-02: the rescued headshot is already the author avatar in Sanity; now also in every post's Article JSON-LD (author image + url /about). The JSON-LD publisher logo pointed at /favicon.ico, a 404 here; now /icon.</t>
         </is>
       </c>
       <c r="E301" s="14" t="inlineStr">
@@ -7763,7 +7763,7 @@
       <c r="A302" s="4" t="n"/>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>7 more posts got a real, unique hero image rescued from the live legacy site's newly-added art this pass (scripts/rescue-2026-09-blog-images…</t>
+          <t>Blog hero images</t>
         </is>
       </c>
       <c r="C302" s="13" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>.ts — see the correction note above): california-toll-roads-legalized-scam, the-1000-hour-hold, conscious-capital-partnership-ecosystem, the-peptide-truth-65m-fraud-industry-vs-life-changing-medicine, clear-communication, building-services-market-transhuman-era, heart-protocol-addendum.</t>
+          <t>audited, then migrated. Final state:</t>
         </is>
       </c>
       <c r="E302" s="14" t="inlineStr">
@@ -7786,17 +7786,17 @@
       <c r="A303" s="4" t="n"/>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>92 posts still need a real, unique hero image</t>
-        </is>
-      </c>
-      <c r="C303" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>22 posts have a real hero image, now live in Sanity (17 already on RampRate's own CloudFront + 4 rescued from the legacy /api/img/ proxy + 1…</t>
+        </is>
+      </c>
+      <c r="C303" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
+          <t xml:space="preserve"> rescued from /manus-storage/, all pulled over by migrate-blog-posts.ts before Manus is decommissioned)</t>
         </is>
       </c>
       <c r="E303" s="14" t="inlineStr">
@@ -7809,7 +7809,7 @@
       <c r="A304" s="4" t="n"/>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>Blog: per-post OG image if different from hero (many posts can reuse hero as OG)</t>
+          <t>7 more posts got a real, unique hero image rescued from the live legacy site's newly-added art this pass (scripts/rescue-2026-09-blog-images…</t>
         </is>
       </c>
       <c r="C304" s="13" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>Confirmed 2026-10-02: generateMetadata uses seo.ogImage, else the hero, else the default OG image.</t>
+          <t>.ts — see the correction note above): california-toll-roads-legalized-scam, the-1000-hour-hold, conscious-capital-partnership-ecosystem, the-peptide-truth-65m-fraud-industry-vs-life-changing-medicine, clear-communication, building-services-market-transhuman-era, heart-protocol-addendum.</t>
         </is>
       </c>
       <c r="E304" s="14" t="inlineStr">
@@ -7832,17 +7832,17 @@
       <c r="A305" s="4" t="n"/>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Marketing pages</t>
-        </is>
-      </c>
-      <c r="C305" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>92 posts still need a real, unique hero image</t>
+        </is>
+      </c>
+      <c r="C305" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>hero/section images for /the-letter, /the-territory, /engine-room, /the-body, /the-nightstand, /recent-creations (portfolio thumbnails), /published (publication logos), /clients (client logos — confirm licensing before re-hosting). Checked against live 2026-10-02: same image count on every one; /the-territory, /engine-room, /recent-creations, /published, /clients have no images on live either.</t>
+          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
         </is>
       </c>
       <c r="E305" s="14" t="inlineStr">
@@ -7855,7 +7855,7 @@
       <c r="A306" s="4" t="n"/>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>/akbar essay images</t>
+          <t>Blog: per-post OG image if different from hero (many posts can reuse hero as OG)</t>
         </is>
       </c>
       <c r="C306" s="13" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>not lost after all: 20 of the 21 were rescued into Sanity by scripts/rescue-manus-media.ts (2026-09-28) and are wired back in legacy's layout (hero mosaic, JC portrait, 2x2 grid, 3 full-bleeds, 3-up strip, footer gallery) as of 2026-09-29. Only slider-3 was gone (HTTP 502); the hero mosaic is 4 tiles instead of 5.</t>
+          <t>Confirmed 2026-10-02: generateMetadata uses seo.ogImage, else the hero, else the default OG image.</t>
         </is>
       </c>
       <c r="E306" s="14" t="inlineStr">
@@ -7878,7 +7878,7 @@
       <c r="A307" s="4" t="n"/>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Rescued page images wired back in (2026-09-29)</t>
+          <t>Marketing pages</t>
         </is>
       </c>
       <c r="C307" s="13" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>/living-declaration hero, hand image and Clarisse Abelarde artwork; /impact-dashboard earth hero; /find-my banner; /find-your-coffee dark photo landing (legacy copy restored, replacing an intro that wasn't in legacy). Also wired (second pass): /consciousness-scale (legacy's hero-first flow restored, the invented intro screen removed), /find-your-me hero, /humanos hero, the HumanOS nav logo, and all 12 HumanOS people headshots (/humanos/ecosystem, /humanos/philosophy). Blog-body images (2026-09-29): all 19 the migration dropped are restored by scripts/restore-blog-body-images.ts as Sanity drafts on 4 posts (Clarisse Abelarde 7, You Are the Moat 4, FRQNCY 6, Energy Is Money 2), waiting to be published in Studio; the other blog-listed assets were heroes already set. Still unwired from docs/ai/manus-media-rescue.md: and /alex-azzi's subject photo (a photo of a real person on an accusation page: needs Tony's yes first).</t>
+          <t>hero/section images for /the-letter, /the-territory, /engine-room, /the-body, /the-nightstand, /recent-creations (portfolio thumbnails), /published (publication logos), /clients (client logos — confirm licensing before re-hosting). Checked against live 2026-10-02: same image count on every one; /the-territory, /engine-room, /recent-creations, /published, /clients have no images on live either.</t>
         </is>
       </c>
       <c r="E307" s="14" t="inlineStr">
@@ -7901,7 +7901,7 @@
       <c r="A308" s="4" t="n"/>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>BrewSoul: coffee/product images (brewsoul-coffees-expanded.ts likely has image refs</t>
+          <t>/akbar essay images</t>
         </is>
       </c>
       <c r="C308" s="13" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>audit), city guide header images, roaster directory photos. Audited 2026-09-09 (status spreadsheet), confirmed 2026-10-02: city guides already have photos; coffees, chains and roasters have no image field in legacy or here (text-only by design); farms got real photos.</t>
+          <t>not lost after all: 20 of the 21 were rescued into Sanity by scripts/rescue-manus-media.ts (2026-09-28) and are wired back in legacy's layout (hero mosaic, JC portrait, 2x2 grid, 3 full-bleeds, 3-up strip, footer gallery) as of 2026-09-29. Only slider-3 was gone (HTTP 502); the hero mosaic is 4 tiles instead of 5.</t>
         </is>
       </c>
       <c r="E308" s="14" t="inlineStr">
@@ -7924,7 +7924,7 @@
       <c r="A309" s="4" t="n"/>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>65 page images moved off the Manus storage copy into Sanity (2026-10-02)</t>
+          <t>Rescued page images wired back in (2026-09-29)</t>
         </is>
       </c>
       <c r="C309" s="13" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>every image the code loaded from d2xsxph8kpxj0f.cloudfront.net (PRI medicine images, Iboga module, facilitator index, /attention-theft, /alex-azzi, /protecting-your-business, /peyote-mescaline, HumanOS, the peptide quiz). Notes called it "RampRate's own CloudFront", but every file sits in the legacy Manus project's folder and its owner couldn't be confirmed. All 65 uploaded (scripts/rescue-cloudfront-images.ts), code rewritten, host removed from images.remotePatterns, no Sanity document used it. Table in docs/ai/manus-media-rescue.md.</t>
+          <t>/living-declaration hero, hand image and Clarisse Abelarde artwork; /impact-dashboard earth hero; /find-my banner; /find-your-coffee dark photo landing (legacy copy restored, replacing an intro that wasn't in legacy). Also wired (second pass): /consciousness-scale (legacy's hero-first flow restored, the invented intro screen removed), /find-your-me hero, /humanos hero, the HumanOS nav logo, and all 12 HumanOS people headshots (/humanos/ecosystem, /humanos/philosophy). Blog-body images (2026-09-29): all 19 the migration dropped are restored by scripts/restore-blog-body-images.ts as Sanity drafts on 4 posts (Clarisse Abelarde 7, You Are the Moat 4, FRQNCY 6, Energy Is Money 2), waiting to be published in Studio; the other blog-listed assets were heroes already set. Still unwired from docs/ai/manus-media-rescue.md: and /alex-azzi's subject photo (a photo of a real person on an accusation page: needs Tony's yes first).</t>
         </is>
       </c>
       <c r="E309" s="14" t="inlineStr">
@@ -7947,7 +7947,7 @@
       <c r="A310" s="4" t="n"/>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>PRI/Kava: medicine reference images (medicine-images.ts), facility images for /facilitator-index</t>
+          <t>BrewSoul: coffee/product images (brewsoul-coffees-expanded.ts likely has image refs</t>
         </is>
       </c>
       <c r="C310" s="13" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: all in Sanity; image counts match live on PRI, Kava, Iboga, Peyote, facilitator pages.</t>
+          <t>audit), city guide header images, roaster directory photos. Audited 2026-09-09 (status spreadsheet), confirmed 2026-10-02: city guides already have photos; coffees, chains and roasters have no image field in legacy or here (text-only by design); farms got real photos.</t>
         </is>
       </c>
       <c r="E310" s="14" t="inlineStr">
@@ -7970,7 +7970,7 @@
       <c r="A311" s="4" t="n"/>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Manifesto/Attention Theft: any diagram/illustration assets used on the mega-page</t>
+          <t>65 page images moved off the Manus storage copy into Sanity (2026-10-02)</t>
         </is>
       </c>
       <c r="C311" s="13" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: 6 of live's 7 are in (now in Sanity); the 7th belongs to the Wall of Shame section left out on purpose.</t>
+          <t>every image the code loaded from d2xsxph8kpxj0f.cloudfront.net (PRI medicine images, Iboga module, facilitator index, /attention-theft, /alex-azzi, /protecting-your-business, /peyote-mescaline, HumanOS, the peptide quiz). Notes called it "RampRate's own CloudFront", but every file sits in the legacy Manus project's folder and its owner couldn't be confirmed. All 65 uploaded (scripts/rescue-cloudfront-images.ts), code rewritten, host removed from images.remotePatterns, no Sanity document used it. Table in docs/ai/manus-media-rescue.md.</t>
         </is>
       </c>
       <c r="E311" s="14" t="inlineStr">
@@ -7993,17 +7993,17 @@
       <c r="A312" s="4" t="n"/>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
-        </is>
-      </c>
-      <c r="C312" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>PRI/Kava: medicine reference images (medicine-images.ts), facility images for /facilitator-index</t>
+        </is>
+      </c>
+      <c r="C312" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
+          <t>2026-10-02: all in Sanity; image counts match live on PRI, Kava, Iboga, Peyote, facilitator pages.</t>
         </is>
       </c>
       <c r="E312" s="14" t="inlineStr">
@@ -8016,7 +8016,7 @@
       <c r="A313" s="4" t="n"/>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Chatbot: FauxTony avatar/icon</t>
+          <t>Manifesto/Attention Theft: any diagram/illustration assets used on the mega-page</t>
         </is>
       </c>
       <c r="C313" s="13" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>Not needed (2026-10-02): the chatbot phase (Phase 10) was cancelled.</t>
+          <t>2026-10-02: 6 of live's 7 are in (now in Sanity); the 7th belongs to the Wall of Shame section left out on purpose.</t>
         </is>
       </c>
       <c r="E313" s="14" t="inlineStr">
@@ -8039,17 +8039,17 @@
       <c r="A314" s="4" t="n"/>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>Audit client/public/ (including alex-azzi/, brewsoul/ subfolders) for any static assets already sitting there unused that should be pulled i…</t>
-        </is>
-      </c>
-      <c r="C314" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
+        </is>
+      </c>
+      <c r="C314" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>n rather than re-created. Done 2026-10-02: no images there at all (only llms.txt, a BrewSoul catalog, Manus debug files, design-options.html). Found and fixed a cutover risk instead: live serves two Google site-verification files (/google6881a0411c48b301.html, /alex-azzi/googleedff0185753a4a1f.html) that the new site returned 404 for, so Search Console could lose verification at DNS cutover. Both copied to public/ byte for byte. Not copied: site.webmanifest (its icons don't exist here; Next's app/icon.tsx covers the favicon).</t>
+          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
         </is>
       </c>
       <c r="E314" s="14" t="inlineStr">
@@ -8059,66 +8059,66 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="10" t="inlineStr">
-        <is>
-          <t>Phase 14 — QA &amp; Launch</t>
-        </is>
-      </c>
-      <c r="B315" s="11" t="n"/>
-      <c r="C315" s="11" t="n"/>
-      <c r="D315" s="12" t="n"/>
+      <c r="A315" s="4" t="n"/>
+      <c r="B315" s="4" t="inlineStr">
+        <is>
+          <t>Chatbot: FauxTony avatar/icon</t>
+        </is>
+      </c>
+      <c r="C315" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D315" s="4" t="inlineStr">
+        <is>
+          <t>Not needed (2026-10-02): the chatbot phase (Phase 10) was cancelled.</t>
+        </is>
+      </c>
+      <c r="E315" s="14" t="inlineStr">
+        <is>
+          <t>Phase 13 — Images Needed in Sanity</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="4" t="n"/>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>Mobile responsive pass on every ported section</t>
-        </is>
-      </c>
-      <c r="C316" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Audit client/public/ (including alex-azzi/, brewsoul/ subfolders) for any static assets already sitting there unused that should be pulled i…</t>
+        </is>
+      </c>
+      <c r="C316" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid).</t>
+          <t>n rather than re-created. Done 2026-10-02: no images there at all (only llms.txt, a BrewSoul catalog, Manus debug files, design-options.html). Found and fixed a cutover risk instead: live serves two Google site-verification files (/google6881a0411c48b301.html, /alex-azzi/googleedff0185753a4a1f.html) that the new site returned 404 for, so Search Console could lose verification at DNS cutover. Both copied to public/ byte for byte. Not copied: site.webmanifest (its icons don't exist here; Next's app/icon.tsx covers the favicon).</t>
         </is>
       </c>
       <c r="E316" s="14" t="inlineStr">
         <is>
+          <t>Phase 13 — Images Needed in Sanity</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="10" t="inlineStr">
+        <is>
           <t>Phase 14 — QA &amp; Launch</t>
         </is>
       </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="4" t="n"/>
-      <c r="B317" s="4" t="inlineStr">
-        <is>
-          <t>Accessibility pass (WCAG AA contrast, 44px touch targets, keyboard nav)</t>
-        </is>
-      </c>
-      <c r="C317" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D317" s="4" t="inlineStr">
-        <is>
-          <t>same bar as legacy QA_MASTER_PROMPT.md. 2026-09-29 axe-core pass (WCAG 2.1 AA, same 114 pages, production build): all unlabeled dropdowns/inputs and unnamed links fixed; contrast down from 1,453 failing items on 106 pages to 1,038 on 70 (43 pages fully clean). Shared fixes: brand gold #8b6914 → #836311 site-wide (was 4.3:1 on cream, AA needs 4.5), header "⌘K"/social icons, BrewSoul nav and footer, HumanOS footer, Kava footer, assessment intro footnote, post-card image links. 2026-09-30: contrast finished, 0 axe color-contrast failures left on the same 114 pages (production build). Token changes: --kava-saffron #b86a28 → #8e521f, --pri-purple-light #a855f7 → #b87bf9 (on-dark purple only), --crusade-teal #0e7c7c → #0d7373; PriEyebrow goes light purple inside a dark PriSection via group-data-dark/pri; /find-your-me and the journey tracker's dark glass panels 60-70% → 90% (legacy's own 60% glass on beige rendered gray, cream text failed). Everything else: nearest passing shade of the same hue, or gold ↔ gold-light on the wrong background. Left: 18 links inside text marked only by color (need an underline), 44px tap targets, keyboard nav. 2026-09-30: 18 color-only in-text links underlined (axe link-in-text-block: 0 left); keyboard focus visible on every focusable item on 8 sampled pages (two form fields had none, fixed). 2026-10-02 re-run (axe WCAG 2.2 AA, 142 pages × 375/1280px, production build, plus Tab through 40 stops per page): found 1,370 contrast failures (mostly BrewSoul'</t>
-        </is>
-      </c>
-      <c r="E317" s="14" t="inlineStr">
-        <is>
-          <t>Phase 14 — QA &amp; Launch</t>
-        </is>
-      </c>
+      <c r="B317" s="11" t="n"/>
+      <c r="C317" s="11" t="n"/>
+      <c r="D317" s="12" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="4" t="n"/>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>No dead-end pages (every page links to 2+ others)</t>
+          <t>Mobile responsive pass on every ported section</t>
         </is>
       </c>
       <c r="C318" s="15" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="D318" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
+          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid).</t>
         </is>
       </c>
       <c r="E318" s="14" t="inlineStr">
@@ -8141,17 +8141,17 @@
       <c r="A319" s="4" t="n"/>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
-        </is>
-      </c>
-      <c r="C319" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Accessibility pass (WCAG AA contrast, 44px touch targets, keyboard nav)</t>
+        </is>
+      </c>
+      <c r="C319" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
+          <t>same bar as legacy QA_MASTER_PROMPT.md. 2026-09-29 axe-core pass (WCAG 2.1 AA, same 114 pages, production build): all unlabeled dropdowns/inputs and unnamed links fixed; contrast down from 1,453 failing items on 106 pages to 1,038 on 70 (43 pages fully clean). Shared fixes: brand gold #8b6914 → #836311 site-wide (was 4.3:1 on cream, AA needs 4.5), header "⌘K"/social icons, BrewSoul nav and footer, HumanOS footer, Kava footer, assessment intro footnote, post-card image links. 2026-09-30: contrast finished, 0 axe color-contrast failures left on the same 114 pages (production build). Token changes: --kava-saffron #b86a28 → #8e521f, --pri-purple-light #a855f7 → #b87bf9 (on-dark purple only), --crusade-teal #0e7c7c → #0d7373; PriEyebrow goes light purple inside a dark PriSection via group-data-dark/pri; /find-your-me and the journey tracker's dark glass panels 60-70% → 90% (legacy's own 60% glass on beige rendered gray, cream text failed). Everything else: nearest passing shade of the same hue, or gold ↔ gold-light on the wrong background. Left: 18 links inside text marked only by color (need an underline), 44px tap targets, keyboard nav. 2026-09-30: 18 color-only in-text links underlined (axe link-in-text-block: 0 left); keyboard focus visible on every focusable item on 8 sampled pages (two form fields had none, fixed). 2026-10-02 re-run (axe WCAG 2.2 AA, 142 pages × 375/1280px, production build, plus Tab through 40 stops per page): found 1,370 contrast failures (mostly BrewSoul'</t>
         </is>
       </c>
       <c r="E319" s="14" t="inlineStr">
@@ -8164,7 +8164,7 @@
       <c r="A320" s="4" t="n"/>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>Remove noindex only when sign-off is given</t>
+          <t>No dead-end pages (every page links to 2+ others)</t>
         </is>
       </c>
       <c r="C320" s="15" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
         </is>
       </c>
       <c r="E320" s="14" t="inlineStr">
@@ -8187,7 +8187,7 @@
       <c r="A321" s="4" t="n"/>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
+          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
         </is>
       </c>
       <c r="C321" s="15" t="inlineStr">
@@ -8195,7 +8195,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D321" s="4" t="inlineStr"/>
+      <c r="D321" s="4" t="inlineStr">
+        <is>
+          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
+        </is>
+      </c>
       <c r="E321" s="14" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
@@ -8206,33 +8210,75 @@
       <c r="A322" s="4" t="n"/>
       <c r="B322" s="4" t="inlineStr">
         <is>
+          <t>Remove noindex only when sign-off is given</t>
+        </is>
+      </c>
+      <c r="C322" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D322" s="4" t="inlineStr">
+        <is>
+          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+        </is>
+      </c>
+      <c r="E322" s="14" t="inlineStr">
+        <is>
+          <t>Phase 14 — QA &amp; Launch</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="4" t="n"/>
+      <c r="B323" s="4" t="inlineStr">
+        <is>
+          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
+        </is>
+      </c>
+      <c r="C323" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D323" s="4" t="inlineStr"/>
+      <c r="E323" s="14" t="inlineStr">
+        <is>
+          <t>Phase 14 — QA &amp; Launch</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="4" t="n"/>
+      <c r="B324" s="4" t="inlineStr">
+        <is>
           <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
         </is>
       </c>
-      <c r="C322" s="15" t="inlineStr">
+      <c r="C324" s="15" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D322" s="4" t="inlineStr"/>
-      <c r="E322" s="14" t="inlineStr">
+      <c r="D324" s="4" t="inlineStr"/>
+      <c r="E324" s="14" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D322"/>
+  <autoFilter ref="A1:D324"/>
   <mergeCells count="14">
     <mergeCell ref="A150:D150"/>
     <mergeCell ref="A237:D237"/>
     <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A295:D295"/>
-    <mergeCell ref="A315:D315"/>
+    <mergeCell ref="A258:D258"/>
+    <mergeCell ref="A317:D317"/>
     <mergeCell ref="A209:D209"/>
-    <mergeCell ref="A256:D256"/>
     <mergeCell ref="A205:D205"/>
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A297:D297"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A183:D183"/>
@@ -8249,7 +8295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8451,43 +8497,43 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Test the new review end to end on a deploy preview</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>(needs a yes, it opens a real pull request): one throwaway change from Claude.ai or ChatGPT: start (unclear request, so the confirm step shows), confirm, edit, review card, screenshots, upload link, then discard.</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="12" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Still different from live (needs a yes)</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>blog posts (done) (done 2026-10-07, see Phase 5); /find-my on live hides the site header. /walk-through is a 404 on live now.</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
-        </is>
-      </c>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Design change on live, needs a decision</t>
+          <t>Still different from live (needs a yes)</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -8497,7 +8543,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>live's story pages now use Cormorant Garamond for titles (ours: Playfair Display), a lighter title weight (400 vs our 700), and a red eyebrow label (#8E1E25, wider letter spacing) instead of our gold. A site-wide font swap is a design call, so not done.</t>
+          <t>blog posts (done) (done 2026-10-07, see Phase 5); /find-my on live hides the site header. /walk-through is a 404 on live now.</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -8510,7 +8556,7 @@
       <c r="A14" s="4" t="n"/>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Lighthouse pass (performance/accessibility/SEO) on top 20 pages by traffic 2026-09-30, 20 key pages (no traffic data yet), local production …</t>
+          <t>Design change on live, needs a decision</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -8520,7 +8566,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>build, mobile: averages performance 87, accessibility 99→100, best practices 100, SEO 92→100, CLS 0 everywhere. Fixed: public/robots.txt had an LLMs: line (not a real directive) that made Google treat the whole file as invalid, now a comment; h3/h4 headings skipping a level on /assessments, /kava, /peptide-watch (same look, right tag); the Kava and /attention-theft back-arrow links had no accessible name on phones; two small phone-width contrast misses. Left: performance is local-machine only (±10-15 points, see CONTRIBUTING.md); the slowest were / 76 (LCP 5.2 s), /psychedelic-readiness-index 82, /iboga-ibogaine 83. Re-run against the Netlify deploy before launch. 2026-10-06 re-run against the Netlify deploy (14 key pages, mobile): accessibility 100 and CLS 0 on every page, SEO clean (only the expected netlify.app noindex), performance 77-97 held back by 3-4 s LCP. Fixed: all 21 hero images moved off the deprecated priority prop to fetchPriority="high" + loading="eager" (Next 16); /iboga-ibogaine hero and the first card on /blog and category pages no longer lazy-loaded; sizes on the Four Doors cards (~150 KiB per page), /humanos diagram (~100 KiB) and /about headshot; urlFor no longer imports the Sanity client, so ~115 KB of Sanity client code stopped loading on / and /blog; React hydration error #418 on / and /blog (post dates) gone, checked in two time zones; /blog is static again; empty icon &lt;th&gt;s on /iboga-ibogaine labelled; category page reads use sanityFetch(). Left: se</t>
+          <t>live's story pages now use Cormorant Garamond for titles (ours: Playfair Display), a lighter title weight (400 vs our 700), and a red eyebrow label (#8E1E25, wider letter spacing) instead of our gold. A site-wide font swap is a design call, so not done.</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -8533,7 +8579,7 @@
       <c r="A15" s="4" t="n"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SEO audit items needing a yes (2026-10-06)</t>
+          <t>Lighthouse pass (performance/accessibility/SEO) on top 20 pages by traffic 2026-09-30, 20 key pages (no traffic data yet), local production …</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -8543,7 +8589,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+          <t>build, mobile: averages performance 87, accessibility 99→100, best practices 100, SEO 92→100, CLS 0 everywhere. Fixed: public/robots.txt had an LLMs: line (not a real directive) that made Google treat the whole file as invalid, now a comment; h3/h4 headings skipping a level on /assessments, /kava, /peptide-watch (same look, right tag); the Kava and /attention-theft back-arrow links had no accessible name on phones; two small phone-width contrast misses. Left: performance is local-machine only (±10-15 points, see CONTRIBUTING.md); the slowest were / 76 (LCP 5.2 s), /psychedelic-readiness-index 82, /iboga-ibogaine 83. Re-run against the Netlify deploy before launch. 2026-10-06 re-run against the Netlify deploy (14 key pages, mobile): accessibility 100 and CLS 0 on every page, SEO clean (only the expected netlify.app noindex), performance 77-97 held back by 3-4 s LCP. Fixed: all 21 hero images moved off the deprecated priority prop to fetchPriority="high" + loading="eager" (Next 16); /iboga-ibogaine hero and the first card on /blog and category pages no longer lazy-loaded; sizes on the Four Doors cards (~150 KiB per page), /humanos diagram (~100 KiB) and /about headshot; urlFor no longer imports the Sanity client, so ~115 KB of Sanity client code stopped loading on / and /blog; React hydration error #418 on / and /blog (post dates) gone, checked in two time zones; /blog is static again; empty icon &lt;th&gt;s on /iboga-ibogaine labelled; category page reads use sanityFetch(). Left: se</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -8556,59 +8602,59 @@
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="inlineStr">
         <is>
+          <t>SEO audit items needing a yes (2026-10-06)</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
           <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="12" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>Phase 13 — Images Needed in Sanity</t>
-        </is>
-      </c>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>92 posts still need a real, unique hero image</t>
+          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -8618,7 +8664,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
+          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -8631,63 +8677,63 @@
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="4" t="inlineStr">
         <is>
+          <t>92 posts still need a real, unique hero image</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>Phase 13 — Images Needed in Sanity</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
           <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="12" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Mobile responsive pass on every ported section</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid).</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Phase 14 — QA &amp; Launch</t>
-        </is>
-      </c>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>No dead-end pages (every page links to 2+ others)</t>
+          <t>Mobile responsive pass on every ported section</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
@@ -8697,7 +8743,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
+          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid).</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -8710,7 +8756,7 @@
       <c r="A24" s="4" t="n"/>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
+          <t>No dead-end pages (every page links to 2+ others)</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -8720,7 +8766,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
+          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
@@ -8733,7 +8779,7 @@
       <c r="A25" s="4" t="n"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Remove noindex only when sign-off is given</t>
+          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
@@ -8743,7 +8789,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
@@ -8756,7 +8802,7 @@
       <c r="A26" s="4" t="n"/>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
+          <t>Remove noindex only when sign-off is given</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -8764,7 +8810,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+        </is>
+      </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
@@ -8775,7 +8825,7 @@
       <c r="A27" s="4" t="n"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -8790,15 +8840,34 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>Phase 14 — QA &amp; Launch</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D28"/>
   <mergeCells count="6">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Migration-Status-Report.xlsx
+++ b/Migration-Status-Report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Remaining Work" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$324</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$325</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Remaining Work'!$A$1:$D$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -639,15 +639,15 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A5,'Full Detail'!$C$2:$C$324,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A5,'Full Detail'!$C$2:$C$325,"Done")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A5,'Full Detail'!$C$2:$C$324,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A5,'Full Detail'!$C$2:$C$325,"Remaining")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A5,'Full Detail'!$C$2:$C$324,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A5,'Full Detail'!$C$2:$C$325,"Deferred")</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -666,15 +666,15 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A6,'Full Detail'!$C$2:$C$324,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A6,'Full Detail'!$C$2:$C$325,"Done")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A6,'Full Detail'!$C$2:$C$324,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A6,'Full Detail'!$C$2:$C$325,"Remaining")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A6,'Full Detail'!$C$2:$C$324,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A6,'Full Detail'!$C$2:$C$325,"Deferred")</f>
         <v/>
       </c>
       <c r="E6" s="5">
@@ -693,15 +693,15 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A7,'Full Detail'!$C$2:$C$324,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A7,'Full Detail'!$C$2:$C$325,"Done")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A7,'Full Detail'!$C$2:$C$324,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A7,'Full Detail'!$C$2:$C$325,"Remaining")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A7,'Full Detail'!$C$2:$C$324,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A7,'Full Detail'!$C$2:$C$325,"Deferred")</f>
         <v/>
       </c>
       <c r="E7" s="5">
@@ -720,15 +720,15 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A8,'Full Detail'!$C$2:$C$324,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A8,'Full Detail'!$C$2:$C$325,"Done")</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A8,'Full Detail'!$C$2:$C$324,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A8,'Full Detail'!$C$2:$C$325,"Remaining")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A8,'Full Detail'!$C$2:$C$324,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A8,'Full Detail'!$C$2:$C$325,"Deferred")</f>
         <v/>
       </c>
       <c r="E8" s="5">
@@ -747,15 +747,15 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A9,'Full Detail'!$C$2:$C$324,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A9,'Full Detail'!$C$2:$C$325,"Done")</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A9,'Full Detail'!$C$2:$C$324,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A9,'Full Detail'!$C$2:$C$325,"Remaining")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A9,'Full Detail'!$C$2:$C$324,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A9,'Full Detail'!$C$2:$C$325,"Deferred")</f>
         <v/>
       </c>
       <c r="E9" s="5">
@@ -774,15 +774,15 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A10,'Full Detail'!$C$2:$C$324,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A10,'Full Detail'!$C$2:$C$325,"Done")</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A10,'Full Detail'!$C$2:$C$324,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A10,'Full Detail'!$C$2:$C$325,"Remaining")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A10,'Full Detail'!$C$2:$C$324,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A10,'Full Detail'!$C$2:$C$325,"Deferred")</f>
         <v/>
       </c>
       <c r="E10" s="5">
@@ -801,15 +801,15 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A11,'Full Detail'!$C$2:$C$324,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A11,'Full Detail'!$C$2:$C$325,"Done")</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A11,'Full Detail'!$C$2:$C$324,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A11,'Full Detail'!$C$2:$C$325,"Remaining")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A11,'Full Detail'!$C$2:$C$324,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A11,'Full Detail'!$C$2:$C$325,"Deferred")</f>
         <v/>
       </c>
       <c r="E11" s="5">
@@ -828,15 +828,15 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A12,'Full Detail'!$C$2:$C$324,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A12,'Full Detail'!$C$2:$C$325,"Done")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A12,'Full Detail'!$C$2:$C$324,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A12,'Full Detail'!$C$2:$C$325,"Remaining")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A12,'Full Detail'!$C$2:$C$324,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A12,'Full Detail'!$C$2:$C$325,"Deferred")</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -855,15 +855,15 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A13,'Full Detail'!$C$2:$C$324,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A13,'Full Detail'!$C$2:$C$325,"Done")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A13,'Full Detail'!$C$2:$C$324,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A13,'Full Detail'!$C$2:$C$325,"Remaining")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A13,'Full Detail'!$C$2:$C$324,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A13,'Full Detail'!$C$2:$C$325,"Deferred")</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -882,15 +882,15 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A14,'Full Detail'!$C$2:$C$324,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A14,'Full Detail'!$C$2:$C$325,"Done")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A14,'Full Detail'!$C$2:$C$324,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A14,'Full Detail'!$C$2:$C$325,"Remaining")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A14,'Full Detail'!$C$2:$C$324,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A14,'Full Detail'!$C$2:$C$325,"Deferred")</f>
         <v/>
       </c>
       <c r="E14" s="5">
@@ -909,15 +909,15 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A15,'Full Detail'!$C$2:$C$324,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A15,'Full Detail'!$C$2:$C$325,"Done")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A15,'Full Detail'!$C$2:$C$324,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A15,'Full Detail'!$C$2:$C$325,"Remaining")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A15,'Full Detail'!$C$2:$C$324,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A15,'Full Detail'!$C$2:$C$325,"Deferred")</f>
         <v/>
       </c>
       <c r="E15" s="5">
@@ -936,15 +936,15 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A16,'Full Detail'!$C$2:$C$324,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A16,'Full Detail'!$C$2:$C$325,"Done")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A16,'Full Detail'!$C$2:$C$324,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A16,'Full Detail'!$C$2:$C$325,"Remaining")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A16,'Full Detail'!$C$2:$C$324,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A16,'Full Detail'!$C$2:$C$325,"Deferred")</f>
         <v/>
       </c>
       <c r="E16" s="5">
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A17,'Full Detail'!$C$2:$C$324,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A17,'Full Detail'!$C$2:$C$325,"Done")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A17,'Full Detail'!$C$2:$C$324,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A17,'Full Detail'!$C$2:$C$325,"Remaining")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A17,'Full Detail'!$C$2:$C$324,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A17,'Full Detail'!$C$2:$C$325,"Deferred")</f>
         <v/>
       </c>
       <c r="E17" s="5">
@@ -990,15 +990,15 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A18,'Full Detail'!$C$2:$C$324,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A18,'Full Detail'!$C$2:$C$325,"Done")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A18,'Full Detail'!$C$2:$C$324,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A18,'Full Detail'!$C$2:$C$325,"Remaining")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A18,'Full Detail'!$C$2:$C$324,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A18,'Full Detail'!$C$2:$C$325,"Deferred")</f>
         <v/>
       </c>
       <c r="E18" s="5">
@@ -1017,15 +1017,15 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A19,'Full Detail'!$C$2:$C$324,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A19,'Full Detail'!$C$2:$C$325,"Done")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A19,'Full Detail'!$C$2:$C$324,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A19,'Full Detail'!$C$2:$C$325,"Remaining")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$324,$A19,'Full Detail'!$C$2:$C$324,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A19,'Full Detail'!$C$2:$C$325,"Deferred")</f>
         <v/>
       </c>
       <c r="E19" s="5">
@@ -1075,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E324"/>
+  <dimension ref="A1:E325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7343,7 +7343,7 @@
       <c r="A283" s="4" t="n"/>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>SEO audit fixes (2026-10-06)</t>
+          <t>Error pages (2026-10-09, owner asked)</t>
         </is>
       </c>
       <c r="C283" s="13" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
+          <t>404 page now sets its own title ("Page not found") as a server page around live's 3-second redirect (not-found.tsx + components/not-found-redirect.tsx), arrow as an icon; page error screen (error.tsx) uses Next 16's retry (re-fetches), shows a reference code for the server logs, links home and to the site index; new global-error.tsx for failures in the root layout itself (own &lt;html&gt;, plain links). Verified on a production build: missing page, missing essay and missing Kava page return 404 with the right title; a test page that throws returns 500 with the error screen, "Try again" re-fetches; phone and laptop, no sideways scroll (test page removed).</t>
         </is>
       </c>
       <c r="E283" s="14" t="inlineStr">
@@ -7366,17 +7366,17 @@
       <c r="A284" s="4" t="n"/>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>SEO audit items needing a yes (2026-10-06)</t>
-        </is>
-      </c>
-      <c r="C284" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>SEO audit fixes (2026-10-06)</t>
+        </is>
+      </c>
+      <c r="C284" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+          <t>Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
         </is>
       </c>
       <c r="E284" s="14" t="inlineStr">
@@ -7389,7 +7389,7 @@
       <c r="A285" s="4" t="n"/>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+          <t>SEO audit items needing a yes (2026-10-06)</t>
         </is>
       </c>
       <c r="C285" s="15" t="inlineStr">
@@ -7397,7 +7397,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D285" s="4" t="inlineStr"/>
+      <c r="D285" s="4" t="inlineStr">
+        <is>
+          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+        </is>
+      </c>
       <c r="E285" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -7408,19 +7412,15 @@
       <c r="A286" s="4" t="n"/>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
-        </is>
-      </c>
-      <c r="C286" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D286" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
-        </is>
-      </c>
+          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+        </is>
+      </c>
+      <c r="C286" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D286" s="4" t="inlineStr"/>
       <c r="E286" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -7431,7 +7431,7 @@
       <c r="A287" s="4" t="n"/>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>"Keep going" strip above the footer on every page (2026-10-07)</t>
+          <t>Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
         </is>
       </c>
       <c r="C287" s="13" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>legacy's WhereNext (deferred in Phase 3, never picked up) with its per-page suggestions, Home · Site Index · All Assessments; links pointed at current routes.</t>
+          <t>2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
         </is>
       </c>
       <c r="E287" s="14" t="inlineStr">
@@ -7454,7 +7454,7 @@
       <c r="A288" s="4" t="n"/>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>Live-only and redesigned pages from the 2026-10-07 page sweep (188 pages compared with live)</t>
+          <t>"Keep going" strip above the footer on every page (2026-10-07)</t>
         </is>
       </c>
       <c r="C288" s="13" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>/the-index rebuilt from live's code (20 concepts, related-word search across essays and site pages, full-text search on the server, "three related places to go next"; the old redirect to /search removed and its links, including the "Site Index" link in "Keep going", point at it again); /the-mirror (and /life-assessment) opens on live's intro (dark hero, "What We Measure" with the six areas, "The Ecosystem"), rebuilt as a step registry (rule 19); /essays header, order and column like live; /about "What They Say" styled like live (live picks 3 of the same 19 quotes at random; ours shows a fixed 3 so they're in the server HTML); /impact-futurism list titles and subtitles; /supplier-intake is a real page again with live's Stage 1 form; /seven-doors and /projects redirect home like live; /impact, /health, /library, /built-on-manus, /heroes are 404 on live too. Left as is on purpose: /blog stays our archive page (on live it repeats the homepage), the email gates on /framework and /peptide-supply-chain, the attention-theft Wall of Shame.</t>
+          <t>legacy's WhereNext (deferred in Phase 3, never picked up) with its per-page suggestions, Home · Site Index · All Assessments; links pointed at current routes.</t>
         </is>
       </c>
       <c r="E288" s="14" t="inlineStr">
@@ -7477,7 +7477,7 @@
       <c r="A289" s="4" t="n"/>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>/alex-azzi locked like live (2026-10-07, owner said match it)</t>
+          <t>Live-only and redesigned pages from the 2026-10-07 page sweep (188 pages compared with live)</t>
         </is>
       </c>
       <c r="C289" s="13" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>same server-checked password as the locked essay (GATED_POST_PASSWORD, now also set in Netlify), live's "Restricted Access" screen, the report not in the page until unlocked, out of search and the sitemap.</t>
+          <t>/the-index rebuilt from live's code (20 concepts, related-word search across essays and site pages, full-text search on the server, "three related places to go next"; the old redirect to /search removed and its links, including the "Site Index" link in "Keep going", point at it again); /the-mirror (and /life-assessment) opens on live's intro (dark hero, "What We Measure" with the six areas, "The Ecosystem"), rebuilt as a step registry (rule 19); /essays header, order and column like live; /about "What They Say" styled like live (live picks 3 of the same 19 quotes at random; ours shows a fixed 3 so they're in the server HTML); /impact-futurism list titles and subtitles; /supplier-intake is a real page again with live's Stage 1 form; /seven-doors and /projects redirect home like live; /impact, /health, /library, /built-on-manus, /heroes are 404 on live too. Left as is on purpose: /blog stays our archive page (on live it repeats the homepage), the email gates on /framework and /peptide-supply-chain, the attention-theft Wall of Shame.</t>
         </is>
       </c>
       <c r="E289" s="14" t="inlineStr">
@@ -7500,7 +7500,7 @@
       <c r="A290" s="4" t="n"/>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>Live's title fonts and sizes (2026-10-07, "fix the style")</t>
+          <t>/alex-azzi locked like live (2026-10-07, owner said match it)</t>
         </is>
       </c>
       <c r="C290" s="13" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>measured every page's title font, weight, size and label colour on live vs ours (136 pages). Now like live: Kava headings in Fraunces, HumanOS in Space Grotesk, the peptide tools / charity scorecard / thesis threads in the system serif, America Unbundled in the Iowan Old Style stack at live's size, /akbar in Fraunces 900, friend-gate and post-intervention in Georgia, and live's title sizes on peptide-matrix, peptide-supply-chain, rip-peptide-sciences and the HumanOS pages. Fonts load only on the pages that use them (src/lib/fonts/page-fonts.ts). Label colours stay the darker AA-contrast versions where live's lighter ones fail on a light background.</t>
+          <t>same server-checked password as the locked essay (GATED_POST_PASSWORD, now also set in Netlify), live's "Restricted Access" screen, the report not in the page until unlocked, out of search and the sitemap.</t>
         </is>
       </c>
       <c r="E290" s="14" t="inlineStr">
@@ -7523,7 +7523,7 @@
       <c r="A291" s="4" t="n"/>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Peptide page images rescued into Sanity and wired (2026-10-07)</t>
+          <t>Live's title fonts and sizes (2026-10-07, "fix the style")</t>
         </is>
       </c>
       <c r="C291" s="13" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>/peptide-watch hero plus its 11 section banners, /peptide-matrix and /peptide-supply-chain heroes, the /peptide-hall-of-shame hero (scripts/rescue-2026-10-07-peptide-images.ts, logged in docs/ai/manus-media-rescue.md).</t>
+          <t>measured every page's title font, weight, size and label colour on live vs ours (136 pages). Now like live: Kava headings in Fraunces, HumanOS in Space Grotesk, the peptide tools / charity scorecard / thesis threads in the system serif, America Unbundled in the Iowan Old Style stack at live's size, /akbar in Fraunces 900, friend-gate and post-intervention in Georgia, and live's title sizes on peptide-matrix, peptide-supply-chain, rip-peptide-sciences and the HumanOS pages. Fonts load only on the pages that use them (src/lib/fonts/page-fonts.ts). Label colours stay the darker AA-contrast versions where live's lighter ones fail on a light background.</t>
         </is>
       </c>
       <c r="E291" s="14" t="inlineStr">
@@ -7546,7 +7546,7 @@
       <c r="A292" s="4" t="n"/>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>Live's editorial redesign, first group (2026-10-07)</t>
+          <t>Peptide page images rescued into Sanity and wired (2026-10-07)</t>
         </is>
       </c>
       <c r="C292" s="13" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
+          <t>/peptide-watch hero plus its 11 section banners, /peptide-matrix and /peptide-supply-chain heroes, the /peptide-hall-of-shame hero (scripts/rescue-2026-10-07-peptide-images.ts, logged in docs/ai/manus-media-rescue.md).</t>
         </is>
       </c>
       <c r="E292" s="14" t="inlineStr">
@@ -7569,7 +7569,7 @@
       <c r="A293" s="4" t="n"/>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Live's redesign, second group (done 2026-10-08)</t>
+          <t>Live's editorial redesign, first group (2026-10-07)</t>
         </is>
       </c>
       <c r="C293" s="13" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>re-measured all 18 pages on live vs a fresh production build (title font/size/weight/colour, labels, hero images). Already matching from 2026-10-07: /the-web, /spirits, /iboga-ibogaine (weight 800), /living-declaration, BrewSoul photo on /brewsoul, /brewsoul/browse, /brewsoul/first-sip (live has none there either), /quiz_25q, /recent-creations. Fixed today: /find-your-journey (64px title, red label), /impact-dashboard (64px title in essay ink, label spacing), red labels on /published and /speaking (plus its "rooms" chips), /soulscore "by ImpactSoul" label, /pri-calibration title (weight 900, solid cream, was a purple gradient), /clients (live's narrow 546px column for the whole page, 56px title, roomier stats band, cards 2 per row; two static inline styles moved to classes), /brewsoul/guest (live's BrewSoul photo on the guest card instead of "SN" initials, labels in capitals), /humanos/connect (cards line up with the title), /peptide-hall-of-shame (stats and label readable light gold; were dark gold on dark). Typed arrows on the touched links are icons now (rule 18). Deliberately not copied from live (new CONTRIBUTING rule 20, owner 2026-10-08): red labels on dark bands use #E07A80 (live's #8E1E25 on black is about 2:1, unreadable); /recent-creations keeps our darker label colours (live's fail contrast on white); /humanos/connect keeps "Start Reading" (that card links to the philosophy page, the quiz live's "Start the Assessment" implies doesn't exist). Checked: type check, l</t>
+          <t>dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
         </is>
       </c>
       <c r="E293" s="14" t="inlineStr">
@@ -7592,7 +7592,7 @@
       <c r="A294" s="4" t="n"/>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>BrewSoul top of page (2026-10-08, owner: "button in the center at the top doesn't look good")</t>
+          <t>Live's redesign, second group (done 2026-10-08)</t>
         </is>
       </c>
       <c r="C294" s="13" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>the category badge ("Deep Research" etc.) sat centred in an empty strip, squeezed against the hero, because we copied live's doubled 52px top gap. Now one gap everywhere and the badge floats in the top-left corner, lined up with the BrewSoul logo (brewsoul-main.tsx, category-badge.tsx); checked on all 26 badge pages at 3 widths that it covers nothing. BrewSoul menu: on tablets (768-1023px) the links were cut off and "More" was hidden with no menu button at all; now the menu button shows below 1024px, 5 links + "More" from 1024px, all 8 from 1280px, "More" always visible.</t>
+          <t>re-measured all 18 pages on live vs a fresh production build (title font/size/weight/colour, labels, hero images). Already matching from 2026-10-07: /the-web, /spirits, /iboga-ibogaine (weight 800), /living-declaration, BrewSoul photo on /brewsoul, /brewsoul/browse, /brewsoul/first-sip (live has none there either), /quiz_25q, /recent-creations. Fixed today: /find-your-journey (64px title, red label), /impact-dashboard (64px title in essay ink, label spacing), red labels on /published and /speaking (plus its "rooms" chips), /soulscore "by ImpactSoul" label, /pri-calibration title (weight 900, solid cream, was a purple gradient), /clients (live's narrow 546px column for the whole page, 56px title, roomier stats band, cards 2 per row; two static inline styles moved to classes), /brewsoul/guest (live's BrewSoul photo on the guest card instead of "SN" initials, labels in capitals), /humanos/connect (cards line up with the title), /peptide-hall-of-shame (stats and label readable light gold; were dark gold on dark). Typed arrows on the touched links are icons now (rule 18). Deliberately not copied from live (new CONTRIBUTING rule 20, owner 2026-10-08): red labels on dark bands use #E07A80 (live's #8E1E25 on black is about 2:1, unreadable); /recent-creations keeps our darker label colours (live's fail contrast on white); /humanos/connect keeps "Start Reading" (that card links to the philosophy page, the quiz live's "Start the Assessment" implies doesn't exist). Checked: type check, l</t>
         </is>
       </c>
       <c r="E294" s="14" t="inlineStr">
@@ -7615,7 +7615,7 @@
       <c r="A295" s="4" t="n"/>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>/pri-efficacy's "Simulation / Live Calibrations" switch like live (2026-10-08)</t>
+          <t>BrewSoul top of page (2026-10-08, owner: "button in the center at the top doesn't look good")</t>
         </is>
       </c>
       <c r="C295" s="13" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>shadcn Tabs, both panels in the server HTML (forceMount). The Live tab reads real aggregate numbers from pri_calibrations (getPriLiveStats() in src/lib/pri-research.ts: totals, opt-ins, average score per dimension; no rows leave the server), page stays static and refreshes every 10 minutes. Until the Supabase scripts are run (Phase 2) it says the numbers "aren't available just now" instead of a fake zero. Checked: build (○, 10m), server HTML has both tabs, tab switch at 390/1280px, no JS errors. Re-check with real numbers once the table exists.</t>
+          <t>the category badge ("Deep Research" etc.) sat centred in an empty strip, squeezed against the hero, because we copied live's doubled 52px top gap. Now one gap everywhere and the badge floats in the top-left corner, lined up with the BrewSoul logo (brewsoul-main.tsx, category-badge.tsx); checked on all 26 badge pages at 3 widths that it covers nothing. BrewSoul menu: on tablets (768-1023px) the links were cut off and "More" was hidden with no menu button at all; now the menu button shows below 1024px, 5 links + "More" from 1024px, all 8 from 1280px, "More" always visible.</t>
         </is>
       </c>
       <c r="E295" s="14" t="inlineStr">
@@ -7638,63 +7638,63 @@
       <c r="A296" s="4" t="n"/>
       <c r="B296" s="4" t="inlineStr">
         <is>
+          <t>/pri-efficacy's "Simulation / Live Calibrations" switch like live (2026-10-08)</t>
+        </is>
+      </c>
+      <c r="C296" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D296" s="4" t="inlineStr">
+        <is>
+          <t>shadcn Tabs, both panels in the server HTML (forceMount). The Live tab reads real aggregate numbers from pri_calibrations (getPriLiveStats() in src/lib/pri-research.ts: totals, opt-ins, average score per dimension; no rows leave the server), page stays static and refreshes every 10 minutes. Until the Supabase scripts are run (Phase 2) it says the numbers "aren't available just now" instead of a fake zero. Checked: build (○, 10m), server HTML has both tabs, tab switch at 390/1280px, no JS errors. Re-check with real numbers once the table exists.</t>
+        </is>
+      </c>
+      <c r="E296" s="14" t="inlineStr">
+        <is>
+          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="4" t="n"/>
+      <c r="B297" s="4" t="inlineStr">
+        <is>
           <t>/brewsoul/browse hero readable (2026-10-08, owner said go ahead)</t>
         </is>
       </c>
-      <c r="C296" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D296" s="4" t="inlineStr">
+      <c r="C297" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D297" s="4" t="inlineStr">
         <is>
           <t>a soft cream glow behind the title block so "The Catalog", the subtitle and the stat labels read clearly over the coffee photo (live is hard to read there too; rule 20). Photo still shows around the edges. Checked at 390/1280px.</t>
         </is>
       </c>
-      <c r="E296" s="14" t="inlineStr">
+      <c r="E297" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
         </is>
       </c>
     </row>
-    <row r="297">
-      <c r="A297" s="10" t="inlineStr">
+    <row r="298">
+      <c r="A298" s="10" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
-      <c r="B297" s="11" t="n"/>
-      <c r="C297" s="11" t="n"/>
-      <c r="D297" s="12" t="n"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="4" t="n"/>
-      <c r="B298" s="4" t="inlineStr">
-        <is>
-          <t>Manus media rescue (2026-09-29)</t>
-        </is>
-      </c>
-      <c r="C298" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D298" s="4" t="inlineStr">
-        <is>
-          <t>all 94 Manus-hosted image/video references in the legacy source (/api/img/, /manus-storage/) were checked live. 91 were still downloadable, including the /akbar photos the entry below calls "permanently lost", and all 91 are now Sanity assets (scripts/rescue-manus-media.ts; Sanity dedupes by SHA-1). 3 were gone (HTTP 502). The manifest docs/ai/manus-media-rescue.md maps each one to the legacy files that used it and its Sanity URL. They are not wired into pages yet: go page by page, with real alt text. /facilitator-index's two diagrams are done (scripts/rescue-facilitator-images.ts).</t>
-        </is>
-      </c>
-      <c r="E298" s="14" t="inlineStr">
-        <is>
-          <t>Phase 13 — Images Needed in Sanity</t>
-        </is>
-      </c>
+      <c r="B298" s="11" t="n"/>
+      <c r="C298" s="11" t="n"/>
+      <c r="D298" s="12" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="4" t="n"/>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Favicon</t>
+          <t>Manus media rescue (2026-09-29)</t>
         </is>
       </c>
       <c r="C299" s="13" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>real "G" brand mark generated from the header's actual wordmark treatment (src/app/icon.tsx), see Phase 3</t>
+          <t>all 94 Manus-hosted image/video references in the legacy source (/api/img/, /manus-storage/) were checked live. 91 were still downloadable, including the /akbar photos the entry below calls "permanently lost", and all 91 are now Sanity assets (scripts/rescue-manus-media.ts; Sanity dedupes by SHA-1). 3 were gone (HTTP 502). The manifest docs/ai/manus-media-rescue.md maps each one to the legacy files that used it and its Sanity URL. They are not wired into pages yet: go page by page, with real alt text. /facilitator-index's two diagrams are done (scripts/rescue-facilitator-images.ts).</t>
         </is>
       </c>
       <c r="E299" s="14" t="inlineStr">
@@ -7717,17 +7717,17 @@
       <c r="A300" s="4" t="n"/>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
-        </is>
-      </c>
-      <c r="C300" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Favicon</t>
+        </is>
+      </c>
+      <c r="C300" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
+          <t>real "G" brand mark generated from the header's actual wordmark treatment (src/app/icon.tsx), see Phase 3</t>
         </is>
       </c>
       <c r="E300" s="14" t="inlineStr">
@@ -7740,17 +7740,17 @@
       <c r="A301" s="4" t="n"/>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Author photo(s) for blog author schema (Tony Greenberg headshot at minimum)</t>
-        </is>
-      </c>
-      <c r="C301" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
+        </is>
+      </c>
+      <c r="C301" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: the rescued headshot is already the author avatar in Sanity; now also in every post's Article JSON-LD (author image + url /about). The JSON-LD publisher logo pointed at /favicon.ico, a 404 here; now /icon.</t>
+          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
         </is>
       </c>
       <c r="E301" s="14" t="inlineStr">
@@ -7763,7 +7763,7 @@
       <c r="A302" s="4" t="n"/>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>Blog hero images</t>
+          <t>Author photo(s) for blog author schema (Tony Greenberg headshot at minimum)</t>
         </is>
       </c>
       <c r="C302" s="13" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>audited, then migrated. Final state:</t>
+          <t>2026-10-02: the rescued headshot is already the author avatar in Sanity; now also in every post's Article JSON-LD (author image + url /about). The JSON-LD publisher logo pointed at /favicon.ico, a 404 here; now /icon.</t>
         </is>
       </c>
       <c r="E302" s="14" t="inlineStr">
@@ -7786,7 +7786,7 @@
       <c r="A303" s="4" t="n"/>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>22 posts have a real hero image, now live in Sanity (17 already on RampRate's own CloudFront + 4 rescued from the legacy /api/img/ proxy + 1…</t>
+          <t>Blog hero images</t>
         </is>
       </c>
       <c r="C303" s="13" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> rescued from /manus-storage/, all pulled over by migrate-blog-posts.ts before Manus is decommissioned)</t>
+          <t>audited, then migrated. Final state:</t>
         </is>
       </c>
       <c r="E303" s="14" t="inlineStr">
@@ -7809,7 +7809,7 @@
       <c r="A304" s="4" t="n"/>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>7 more posts got a real, unique hero image rescued from the live legacy site's newly-added art this pass (scripts/rescue-2026-09-blog-images…</t>
+          <t>22 posts have a real hero image, now live in Sanity (17 already on RampRate's own CloudFront + 4 rescued from the legacy /api/img/ proxy + 1…</t>
         </is>
       </c>
       <c r="C304" s="13" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>.ts — see the correction note above): california-toll-roads-legalized-scam, the-1000-hour-hold, conscious-capital-partnership-ecosystem, the-peptide-truth-65m-fraud-industry-vs-life-changing-medicine, clear-communication, building-services-market-transhuman-era, heart-protocol-addendum.</t>
+          <t xml:space="preserve"> rescued from /manus-storage/, all pulled over by migrate-blog-posts.ts before Manus is decommissioned)</t>
         </is>
       </c>
       <c r="E304" s="14" t="inlineStr">
@@ -7832,17 +7832,17 @@
       <c r="A305" s="4" t="n"/>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>92 posts still need a real, unique hero image</t>
-        </is>
-      </c>
-      <c r="C305" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>7 more posts got a real, unique hero image rescued from the live legacy site's newly-added art this pass (scripts/rescue-2026-09-blog-images…</t>
+        </is>
+      </c>
+      <c r="C305" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
+          <t>.ts — see the correction note above): california-toll-roads-legalized-scam, the-1000-hour-hold, conscious-capital-partnership-ecosystem, the-peptide-truth-65m-fraud-industry-vs-life-changing-medicine, clear-communication, building-services-market-transhuman-era, heart-protocol-addendum.</t>
         </is>
       </c>
       <c r="E305" s="14" t="inlineStr">
@@ -7855,17 +7855,17 @@
       <c r="A306" s="4" t="n"/>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>Blog: per-post OG image if different from hero (many posts can reuse hero as OG)</t>
-        </is>
-      </c>
-      <c r="C306" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>92 posts still need a real, unique hero image</t>
+        </is>
+      </c>
+      <c r="C306" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>Confirmed 2026-10-02: generateMetadata uses seo.ogImage, else the hero, else the default OG image.</t>
+          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
         </is>
       </c>
       <c r="E306" s="14" t="inlineStr">
@@ -7878,7 +7878,7 @@
       <c r="A307" s="4" t="n"/>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Marketing pages</t>
+          <t>Blog: per-post OG image if different from hero (many posts can reuse hero as OG)</t>
         </is>
       </c>
       <c r="C307" s="13" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>hero/section images for /the-letter, /the-territory, /engine-room, /the-body, /the-nightstand, /recent-creations (portfolio thumbnails), /published (publication logos), /clients (client logos — confirm licensing before re-hosting). Checked against live 2026-10-02: same image count on every one; /the-territory, /engine-room, /recent-creations, /published, /clients have no images on live either.</t>
+          <t>Confirmed 2026-10-02: generateMetadata uses seo.ogImage, else the hero, else the default OG image.</t>
         </is>
       </c>
       <c r="E307" s="14" t="inlineStr">
@@ -7901,7 +7901,7 @@
       <c r="A308" s="4" t="n"/>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>/akbar essay images</t>
+          <t>Marketing pages</t>
         </is>
       </c>
       <c r="C308" s="13" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>not lost after all: 20 of the 21 were rescued into Sanity by scripts/rescue-manus-media.ts (2026-09-28) and are wired back in legacy's layout (hero mosaic, JC portrait, 2x2 grid, 3 full-bleeds, 3-up strip, footer gallery) as of 2026-09-29. Only slider-3 was gone (HTTP 502); the hero mosaic is 4 tiles instead of 5.</t>
+          <t>hero/section images for /the-letter, /the-territory, /engine-room, /the-body, /the-nightstand, /recent-creations (portfolio thumbnails), /published (publication logos), /clients (client logos — confirm licensing before re-hosting). Checked against live 2026-10-02: same image count on every one; /the-territory, /engine-room, /recent-creations, /published, /clients have no images on live either.</t>
         </is>
       </c>
       <c r="E308" s="14" t="inlineStr">
@@ -7924,7 +7924,7 @@
       <c r="A309" s="4" t="n"/>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>Rescued page images wired back in (2026-09-29)</t>
+          <t>/akbar essay images</t>
         </is>
       </c>
       <c r="C309" s="13" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>/living-declaration hero, hand image and Clarisse Abelarde artwork; /impact-dashboard earth hero; /find-my banner; /find-your-coffee dark photo landing (legacy copy restored, replacing an intro that wasn't in legacy). Also wired (second pass): /consciousness-scale (legacy's hero-first flow restored, the invented intro screen removed), /find-your-me hero, /humanos hero, the HumanOS nav logo, and all 12 HumanOS people headshots (/humanos/ecosystem, /humanos/philosophy). Blog-body images (2026-09-29): all 19 the migration dropped are restored by scripts/restore-blog-body-images.ts as Sanity drafts on 4 posts (Clarisse Abelarde 7, You Are the Moat 4, FRQNCY 6, Energy Is Money 2), waiting to be published in Studio; the other blog-listed assets were heroes already set. Still unwired from docs/ai/manus-media-rescue.md: and /alex-azzi's subject photo (a photo of a real person on an accusation page: needs Tony's yes first).</t>
+          <t>not lost after all: 20 of the 21 were rescued into Sanity by scripts/rescue-manus-media.ts (2026-09-28) and are wired back in legacy's layout (hero mosaic, JC portrait, 2x2 grid, 3 full-bleeds, 3-up strip, footer gallery) as of 2026-09-29. Only slider-3 was gone (HTTP 502); the hero mosaic is 4 tiles instead of 5.</t>
         </is>
       </c>
       <c r="E309" s="14" t="inlineStr">
@@ -7947,7 +7947,7 @@
       <c r="A310" s="4" t="n"/>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>BrewSoul: coffee/product images (brewsoul-coffees-expanded.ts likely has image refs</t>
+          <t>Rescued page images wired back in (2026-09-29)</t>
         </is>
       </c>
       <c r="C310" s="13" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>audit), city guide header images, roaster directory photos. Audited 2026-09-09 (status spreadsheet), confirmed 2026-10-02: city guides already have photos; coffees, chains and roasters have no image field in legacy or here (text-only by design); farms got real photos.</t>
+          <t>/living-declaration hero, hand image and Clarisse Abelarde artwork; /impact-dashboard earth hero; /find-my banner; /find-your-coffee dark photo landing (legacy copy restored, replacing an intro that wasn't in legacy). Also wired (second pass): /consciousness-scale (legacy's hero-first flow restored, the invented intro screen removed), /find-your-me hero, /humanos hero, the HumanOS nav logo, and all 12 HumanOS people headshots (/humanos/ecosystem, /humanos/philosophy). Blog-body images (2026-09-29): all 19 the migration dropped are restored by scripts/restore-blog-body-images.ts as Sanity drafts on 4 posts (Clarisse Abelarde 7, You Are the Moat 4, FRQNCY 6, Energy Is Money 2), waiting to be published in Studio; the other blog-listed assets were heroes already set. Still unwired from docs/ai/manus-media-rescue.md: and /alex-azzi's subject photo (a photo of a real person on an accusation page: needs Tony's yes first).</t>
         </is>
       </c>
       <c r="E310" s="14" t="inlineStr">
@@ -7970,7 +7970,7 @@
       <c r="A311" s="4" t="n"/>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>65 page images moved off the Manus storage copy into Sanity (2026-10-02)</t>
+          <t>BrewSoul: coffee/product images (brewsoul-coffees-expanded.ts likely has image refs</t>
         </is>
       </c>
       <c r="C311" s="13" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>every image the code loaded from d2xsxph8kpxj0f.cloudfront.net (PRI medicine images, Iboga module, facilitator index, /attention-theft, /alex-azzi, /protecting-your-business, /peyote-mescaline, HumanOS, the peptide quiz). Notes called it "RampRate's own CloudFront", but every file sits in the legacy Manus project's folder and its owner couldn't be confirmed. All 65 uploaded (scripts/rescue-cloudfront-images.ts), code rewritten, host removed from images.remotePatterns, no Sanity document used it. Table in docs/ai/manus-media-rescue.md.</t>
+          <t>audit), city guide header images, roaster directory photos. Audited 2026-09-09 (status spreadsheet), confirmed 2026-10-02: city guides already have photos; coffees, chains and roasters have no image field in legacy or here (text-only by design); farms got real photos.</t>
         </is>
       </c>
       <c r="E311" s="14" t="inlineStr">
@@ -7993,7 +7993,7 @@
       <c r="A312" s="4" t="n"/>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>PRI/Kava: medicine reference images (medicine-images.ts), facility images for /facilitator-index</t>
+          <t>65 page images moved off the Manus storage copy into Sanity (2026-10-02)</t>
         </is>
       </c>
       <c r="C312" s="13" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: all in Sanity; image counts match live on PRI, Kava, Iboga, Peyote, facilitator pages.</t>
+          <t>every image the code loaded from d2xsxph8kpxj0f.cloudfront.net (PRI medicine images, Iboga module, facilitator index, /attention-theft, /alex-azzi, /protecting-your-business, /peyote-mescaline, HumanOS, the peptide quiz). Notes called it "RampRate's own CloudFront", but every file sits in the legacy Manus project's folder and its owner couldn't be confirmed. All 65 uploaded (scripts/rescue-cloudfront-images.ts), code rewritten, host removed from images.remotePatterns, no Sanity document used it. Table in docs/ai/manus-media-rescue.md.</t>
         </is>
       </c>
       <c r="E312" s="14" t="inlineStr">
@@ -8016,7 +8016,7 @@
       <c r="A313" s="4" t="n"/>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Manifesto/Attention Theft: any diagram/illustration assets used on the mega-page</t>
+          <t>PRI/Kava: medicine reference images (medicine-images.ts), facility images for /facilitator-index</t>
         </is>
       </c>
       <c r="C313" s="13" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: 6 of live's 7 are in (now in Sanity); the 7th belongs to the Wall of Shame section left out on purpose.</t>
+          <t>2026-10-02: all in Sanity; image counts match live on PRI, Kava, Iboga, Peyote, facilitator pages.</t>
         </is>
       </c>
       <c r="E313" s="14" t="inlineStr">
@@ -8039,17 +8039,17 @@
       <c r="A314" s="4" t="n"/>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
-        </is>
-      </c>
-      <c r="C314" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Manifesto/Attention Theft: any diagram/illustration assets used on the mega-page</t>
+        </is>
+      </c>
+      <c r="C314" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
+          <t>2026-10-02: 6 of live's 7 are in (now in Sanity); the 7th belongs to the Wall of Shame section left out on purpose.</t>
         </is>
       </c>
       <c r="E314" s="14" t="inlineStr">
@@ -8062,17 +8062,17 @@
       <c r="A315" s="4" t="n"/>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>Chatbot: FauxTony avatar/icon</t>
-        </is>
-      </c>
-      <c r="C315" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
+        </is>
+      </c>
+      <c r="C315" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>Not needed (2026-10-02): the chatbot phase (Phase 10) was cancelled.</t>
+          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
         </is>
       </c>
       <c r="E315" s="14" t="inlineStr">
@@ -8085,73 +8085,73 @@
       <c r="A316" s="4" t="n"/>
       <c r="B316" s="4" t="inlineStr">
         <is>
+          <t>Chatbot: FauxTony avatar/icon</t>
+        </is>
+      </c>
+      <c r="C316" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D316" s="4" t="inlineStr">
+        <is>
+          <t>Not needed (2026-10-02): the chatbot phase (Phase 10) was cancelled.</t>
+        </is>
+      </c>
+      <c r="E316" s="14" t="inlineStr">
+        <is>
+          <t>Phase 13 — Images Needed in Sanity</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="4" t="n"/>
+      <c r="B317" s="4" t="inlineStr">
+        <is>
           <t>Audit client/public/ (including alex-azzi/, brewsoul/ subfolders) for any static assets already sitting there unused that should be pulled i…</t>
         </is>
       </c>
-      <c r="C316" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D316" s="4" t="inlineStr">
+      <c r="C317" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D317" s="4" t="inlineStr">
         <is>
           <t>n rather than re-created. Done 2026-10-02: no images there at all (only llms.txt, a BrewSoul catalog, Manus debug files, design-options.html). Found and fixed a cutover risk instead: live serves two Google site-verification files (/google6881a0411c48b301.html, /alex-azzi/googleedff0185753a4a1f.html) that the new site returned 404 for, so Search Console could lose verification at DNS cutover. Both copied to public/ byte for byte. Not copied: site.webmanifest (its icons don't exist here; Next's app/icon.tsx covers the favicon).</t>
         </is>
       </c>
-      <c r="E316" s="14" t="inlineStr">
+      <c r="E317" s="14" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" s="10" t="inlineStr">
+    <row r="318">
+      <c r="A318" s="10" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
         </is>
       </c>
-      <c r="B317" s="11" t="n"/>
-      <c r="C317" s="11" t="n"/>
-      <c r="D317" s="12" t="n"/>
-    </row>
-    <row r="318">
-      <c r="A318" s="4" t="n"/>
-      <c r="B318" s="4" t="inlineStr">
-        <is>
-          <t>Mobile responsive pass on every ported section</t>
-        </is>
-      </c>
-      <c r="C318" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D318" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid).</t>
-        </is>
-      </c>
-      <c r="E318" s="14" t="inlineStr">
-        <is>
-          <t>Phase 14 — QA &amp; Launch</t>
-        </is>
-      </c>
+      <c r="B318" s="11" t="n"/>
+      <c r="C318" s="11" t="n"/>
+      <c r="D318" s="12" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="4" t="n"/>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Accessibility pass (WCAG AA contrast, 44px touch targets, keyboard nav)</t>
-        </is>
-      </c>
-      <c r="C319" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Mobile responsive pass on every ported section</t>
+        </is>
+      </c>
+      <c r="C319" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy QA_MASTER_PROMPT.md. 2026-09-29 axe-core pass (WCAG 2.1 AA, same 114 pages, production build): all unlabeled dropdowns/inputs and unnamed links fixed; contrast down from 1,453 failing items on 106 pages to 1,038 on 70 (43 pages fully clean). Shared fixes: brand gold #8b6914 → #836311 site-wide (was 4.3:1 on cream, AA needs 4.5), header "⌘K"/social icons, BrewSoul nav and footer, HumanOS footer, Kava footer, assessment intro footnote, post-card image links. 2026-09-30: contrast finished, 0 axe color-contrast failures left on the same 114 pages (production build). Token changes: --kava-saffron #b86a28 → #8e521f, --pri-purple-light #a855f7 → #b87bf9 (on-dark purple only), --crusade-teal #0e7c7c → #0d7373; PriEyebrow goes light purple inside a dark PriSection via group-data-dark/pri; /find-your-me and the journey tracker's dark glass panels 60-70% → 90% (legacy's own 60% glass on beige rendered gray, cream text failed). Everything else: nearest passing shade of the same hue, or gold ↔ gold-light on the wrong background. Left: 18 links inside text marked only by color (need an underline), 44px tap targets, keyboard nav. 2026-09-30: 18 color-only in-text links underlined (axe link-in-text-block: 0 left); keyboard focus visible on every focusable item on 8 sampled pages (two form fields had none, fixed). 2026-10-02 re-run (axe WCAG 2.2 AA, 142 pages × 375/1280px, production build, plus Tab through 40 stops per page): found 1,370 contrast failures (mostly BrewSoul'</t>
+          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid).</t>
         </is>
       </c>
       <c r="E319" s="14" t="inlineStr">
@@ -8164,17 +8164,17 @@
       <c r="A320" s="4" t="n"/>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>No dead-end pages (every page links to 2+ others)</t>
-        </is>
-      </c>
-      <c r="C320" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Accessibility pass (WCAG AA contrast, 44px touch targets, keyboard nav)</t>
+        </is>
+      </c>
+      <c r="C320" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
+          <t>same bar as legacy QA_MASTER_PROMPT.md. 2026-09-29 axe-core pass (WCAG 2.1 AA, same 114 pages, production build): all unlabeled dropdowns/inputs and unnamed links fixed; contrast down from 1,453 failing items on 106 pages to 1,038 on 70 (43 pages fully clean). Shared fixes: brand gold #8b6914 → #836311 site-wide (was 4.3:1 on cream, AA needs 4.5), header "⌘K"/social icons, BrewSoul nav and footer, HumanOS footer, Kava footer, assessment intro footnote, post-card image links. 2026-09-30: contrast finished, 0 axe color-contrast failures left on the same 114 pages (production build). Token changes: --kava-saffron #b86a28 → #8e521f, --pri-purple-light #a855f7 → #b87bf9 (on-dark purple only), --crusade-teal #0e7c7c → #0d7373; PriEyebrow goes light purple inside a dark PriSection via group-data-dark/pri; /find-your-me and the journey tracker's dark glass panels 60-70% → 90% (legacy's own 60% glass on beige rendered gray, cream text failed). Everything else: nearest passing shade of the same hue, or gold ↔ gold-light on the wrong background. Left: 18 links inside text marked only by color (need an underline), 44px tap targets, keyboard nav. 2026-09-30: 18 color-only in-text links underlined (axe link-in-text-block: 0 left); keyboard focus visible on every focusable item on 8 sampled pages (two form fields had none, fixed). 2026-10-02 re-run (axe WCAG 2.2 AA, 142 pages × 375/1280px, production build, plus Tab through 40 stops per page): found 1,370 contrast failures (mostly BrewSoul'</t>
         </is>
       </c>
       <c r="E320" s="14" t="inlineStr">
@@ -8187,7 +8187,7 @@
       <c r="A321" s="4" t="n"/>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
+          <t>No dead-end pages (every page links to 2+ others)</t>
         </is>
       </c>
       <c r="C321" s="15" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
+          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
         </is>
       </c>
       <c r="E321" s="14" t="inlineStr">
@@ -8210,7 +8210,7 @@
       <c r="A322" s="4" t="n"/>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>Remove noindex only when sign-off is given</t>
+          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
         </is>
       </c>
       <c r="C322" s="15" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
         </is>
       </c>
       <c r="E322" s="14" t="inlineStr">
@@ -8233,7 +8233,7 @@
       <c r="A323" s="4" t="n"/>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
+          <t>Remove noindex only when sign-off is given</t>
         </is>
       </c>
       <c r="C323" s="15" t="inlineStr">
@@ -8241,7 +8241,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D323" s="4" t="inlineStr"/>
+      <c r="D323" s="4" t="inlineStr">
+        <is>
+          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+        </is>
+      </c>
       <c r="E323" s="14" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
@@ -8252,7 +8256,7 @@
       <c r="A324" s="4" t="n"/>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
         </is>
       </c>
       <c r="C324" s="15" t="inlineStr">
@@ -8267,23 +8271,42 @@
         </is>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" s="4" t="n"/>
+      <c r="B325" s="4" t="inlineStr">
+        <is>
+          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+        </is>
+      </c>
+      <c r="C325" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D325" s="4" t="inlineStr"/>
+      <c r="E325" s="14" t="inlineStr">
+        <is>
+          <t>Phase 14 — QA &amp; Launch</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D324"/>
+  <autoFilter ref="A1:D325"/>
   <mergeCells count="14">
     <mergeCell ref="A150:D150"/>
     <mergeCell ref="A237:D237"/>
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A258:D258"/>
-    <mergeCell ref="A317:D317"/>
     <mergeCell ref="A209:D209"/>
     <mergeCell ref="A205:D205"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A297:D297"/>
+    <mergeCell ref="A318:D318"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A183:D183"/>
     <mergeCell ref="A32:D32"/>
     <mergeCell ref="A123:D123"/>
+    <mergeCell ref="A298:D298"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Migration-Status-Report.xlsx
+++ b/Migration-Status-Report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Remaining Work" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$325</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$326</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Remaining Work'!$A$1:$D$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -639,15 +639,15 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A5,'Full Detail'!$C$2:$C$325,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A5,'Full Detail'!$C$2:$C$326,"Done")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A5,'Full Detail'!$C$2:$C$325,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A5,'Full Detail'!$C$2:$C$326,"Remaining")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A5,'Full Detail'!$C$2:$C$325,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A5,'Full Detail'!$C$2:$C$326,"Deferred")</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -666,15 +666,15 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A6,'Full Detail'!$C$2:$C$325,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A6,'Full Detail'!$C$2:$C$326,"Done")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A6,'Full Detail'!$C$2:$C$325,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A6,'Full Detail'!$C$2:$C$326,"Remaining")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A6,'Full Detail'!$C$2:$C$325,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A6,'Full Detail'!$C$2:$C$326,"Deferred")</f>
         <v/>
       </c>
       <c r="E6" s="5">
@@ -693,15 +693,15 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A7,'Full Detail'!$C$2:$C$325,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A7,'Full Detail'!$C$2:$C$326,"Done")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A7,'Full Detail'!$C$2:$C$325,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A7,'Full Detail'!$C$2:$C$326,"Remaining")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A7,'Full Detail'!$C$2:$C$325,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A7,'Full Detail'!$C$2:$C$326,"Deferred")</f>
         <v/>
       </c>
       <c r="E7" s="5">
@@ -720,15 +720,15 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A8,'Full Detail'!$C$2:$C$325,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A8,'Full Detail'!$C$2:$C$326,"Done")</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A8,'Full Detail'!$C$2:$C$325,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A8,'Full Detail'!$C$2:$C$326,"Remaining")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A8,'Full Detail'!$C$2:$C$325,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A8,'Full Detail'!$C$2:$C$326,"Deferred")</f>
         <v/>
       </c>
       <c r="E8" s="5">
@@ -747,15 +747,15 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A9,'Full Detail'!$C$2:$C$325,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A9,'Full Detail'!$C$2:$C$326,"Done")</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A9,'Full Detail'!$C$2:$C$325,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A9,'Full Detail'!$C$2:$C$326,"Remaining")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A9,'Full Detail'!$C$2:$C$325,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A9,'Full Detail'!$C$2:$C$326,"Deferred")</f>
         <v/>
       </c>
       <c r="E9" s="5">
@@ -774,15 +774,15 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A10,'Full Detail'!$C$2:$C$325,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A10,'Full Detail'!$C$2:$C$326,"Done")</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A10,'Full Detail'!$C$2:$C$325,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A10,'Full Detail'!$C$2:$C$326,"Remaining")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A10,'Full Detail'!$C$2:$C$325,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A10,'Full Detail'!$C$2:$C$326,"Deferred")</f>
         <v/>
       </c>
       <c r="E10" s="5">
@@ -801,15 +801,15 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A11,'Full Detail'!$C$2:$C$325,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A11,'Full Detail'!$C$2:$C$326,"Done")</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A11,'Full Detail'!$C$2:$C$325,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A11,'Full Detail'!$C$2:$C$326,"Remaining")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A11,'Full Detail'!$C$2:$C$325,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A11,'Full Detail'!$C$2:$C$326,"Deferred")</f>
         <v/>
       </c>
       <c r="E11" s="5">
@@ -828,15 +828,15 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A12,'Full Detail'!$C$2:$C$325,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A12,'Full Detail'!$C$2:$C$326,"Done")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A12,'Full Detail'!$C$2:$C$325,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A12,'Full Detail'!$C$2:$C$326,"Remaining")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A12,'Full Detail'!$C$2:$C$325,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A12,'Full Detail'!$C$2:$C$326,"Deferred")</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -855,15 +855,15 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A13,'Full Detail'!$C$2:$C$325,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A13,'Full Detail'!$C$2:$C$326,"Done")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A13,'Full Detail'!$C$2:$C$325,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A13,'Full Detail'!$C$2:$C$326,"Remaining")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A13,'Full Detail'!$C$2:$C$325,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A13,'Full Detail'!$C$2:$C$326,"Deferred")</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -882,15 +882,15 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A14,'Full Detail'!$C$2:$C$325,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A14,'Full Detail'!$C$2:$C$326,"Done")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A14,'Full Detail'!$C$2:$C$325,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A14,'Full Detail'!$C$2:$C$326,"Remaining")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A14,'Full Detail'!$C$2:$C$325,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A14,'Full Detail'!$C$2:$C$326,"Deferred")</f>
         <v/>
       </c>
       <c r="E14" s="5">
@@ -909,15 +909,15 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A15,'Full Detail'!$C$2:$C$325,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A15,'Full Detail'!$C$2:$C$326,"Done")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A15,'Full Detail'!$C$2:$C$325,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A15,'Full Detail'!$C$2:$C$326,"Remaining")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A15,'Full Detail'!$C$2:$C$325,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A15,'Full Detail'!$C$2:$C$326,"Deferred")</f>
         <v/>
       </c>
       <c r="E15" s="5">
@@ -936,15 +936,15 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A16,'Full Detail'!$C$2:$C$325,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A16,'Full Detail'!$C$2:$C$326,"Done")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A16,'Full Detail'!$C$2:$C$325,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A16,'Full Detail'!$C$2:$C$326,"Remaining")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A16,'Full Detail'!$C$2:$C$325,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A16,'Full Detail'!$C$2:$C$326,"Deferred")</f>
         <v/>
       </c>
       <c r="E16" s="5">
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A17,'Full Detail'!$C$2:$C$325,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A17,'Full Detail'!$C$2:$C$326,"Done")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A17,'Full Detail'!$C$2:$C$325,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A17,'Full Detail'!$C$2:$C$326,"Remaining")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A17,'Full Detail'!$C$2:$C$325,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A17,'Full Detail'!$C$2:$C$326,"Deferred")</f>
         <v/>
       </c>
       <c r="E17" s="5">
@@ -990,15 +990,15 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A18,'Full Detail'!$C$2:$C$325,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A18,'Full Detail'!$C$2:$C$326,"Done")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A18,'Full Detail'!$C$2:$C$325,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A18,'Full Detail'!$C$2:$C$326,"Remaining")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A18,'Full Detail'!$C$2:$C$325,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A18,'Full Detail'!$C$2:$C$326,"Deferred")</f>
         <v/>
       </c>
       <c r="E18" s="5">
@@ -1017,15 +1017,15 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A19,'Full Detail'!$C$2:$C$325,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A19,'Full Detail'!$C$2:$C$326,"Done")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A19,'Full Detail'!$C$2:$C$325,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A19,'Full Detail'!$C$2:$C$326,"Remaining")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$325,$A19,'Full Detail'!$C$2:$C$325,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A19,'Full Detail'!$C$2:$C$326,"Deferred")</f>
         <v/>
       </c>
       <c r="E19" s="5">
@@ -1075,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E325"/>
+  <dimension ref="A1:E326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6929,7 +6929,7 @@
       <c r="A265" s="4" t="n"/>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>/path/:archetype (src/app/path/[archetype]/page.tsx)</t>
+          <t>Build the full Manus/legacy-URL → Next.js-URL 301 redirect map (next.config.ts redirects() or Sanity redirect documents)</t>
         </is>
       </c>
       <c r="C265" s="13" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>per-archetype landing page for /assessment's Builder/Crusader/Investor result, reusing lib/content/archetypes.ts. Real content ported in full (top-5 essential-reading list per archetype via allPostsForArchiveQuery, real PathSubscribeForm posting to /api/subscribe, AUTHORITY_ITEMS strip). Real bug fixed vs. legacy: replaced a hand-rolled inline-styled "Path not found" div with a real notFound() (this route's generateStaticParams only ever produces the 3 real keys). Verified live: all 3 archetype routes 200 OK, typecheck/lint clean.</t>
+          <t>hard QA gate, nothing proceeds to DNS cutover until this is complete and tested. First real pass done: extracted all 197 real path= routes from legacy's App.tsx router (not guessed — the actual route table), diffed against this app's real current routes (find src/app -maxdepth 1 -name page.tsx) + next.config.ts's existing redirect sources, normalizing :param/[param] syntax to compare like-for-like. Started at 41 real gaps, closed 10 with new redirects: /attention-theft/{blocker-finder,legal,report,weapons} (legacy registered both a bare AND a /attention-theft/-nested path for each, only the bare ones had redirects before), /find-my-car → /find-my, /the-index → /search (matching the fix already applied to other pages' dead links to it), /supplier-intake-long (bare) + /vendor-intake + /vendor-intake-long (+/:token) → the same real ramprate.com/biochain/supplier-intake destination the token'd path already redirected to, and /spamtoast + /youve-been-reported → / (the live half of legacy's "report a spammer" confrontation flow — a fake IP-fingerprinting/countdown-timer page; the other half, ReportSpammer.tsx, was already a documented drop in Phase 4, this is the same call for its sequel). 21 of the remaining 31 gaps need no redirect — they're /admin/*//analytics//edit/frqncy (internal tools never meant for public discovery) or already-documented intentional defers from Phase 4/7/10 (/clock-keeper-part-2, /ecosystem-map, /friend-gate, /friend-survey/:token, /medicine-sequencing, /m</t>
         </is>
       </c>
       <c r="E265" s="14" t="inlineStr">
@@ -6952,7 +6952,7 @@
       <c r="A266" s="4" t="n"/>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>/my-journey (src/app/my-journey/page.tsx + components/assessments/my-journey-dashboard.tsx)</t>
+          <t>/path/:archetype (src/app/path/[archetype]/page.tsx)</t>
         </is>
       </c>
       <c r="C266" s="13" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>"My Journey Dashboard," real grid/timeline views across all 28 JOURNEY_MAP experiences, category/status filters, phase progress ring, recommended-next card, using the same real useJourneyProgress/JOURNEY_MAP completion tracking every "Find Your X" quiz already writes to (not the narrower tg_assessment_results cookie built for /self-portrait). Legacy's per-quiz scored-result caching (RESULT_KEYS, feeding a mini radar chart) was not ported — no quiz in this migration writes that data either, same honest-degradation call already made for /self-portrait's own composite radar. Fixed a real legacy dead link (/ecosystem-map, a still-unbuilt page) to /self-portrait. Verified live: 200 OK, real content confirmed, typecheck/lint clean.</t>
+          <t>per-archetype landing page for /assessment's Builder/Crusader/Investor result, reusing lib/content/archetypes.ts. Real content ported in full (top-5 essential-reading list per archetype via allPostsForArchiveQuery, real PathSubscribeForm posting to /api/subscribe, AUTHORITY_ITEMS strip). Real bug fixed vs. legacy: replaced a hand-rolled inline-styled "Path not found" div with a real notFound() (this route's generateStaticParams only ever produces the 3 real keys). Verified live: all 3 archetype routes 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E266" s="14" t="inlineStr">
@@ -6975,7 +6975,7 @@
       <c r="A267" s="4" t="n"/>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>/the-open-door (src/app/the-open-door/page.tsx)</t>
+          <t>/my-journey (src/app/my-journey/page.tsx + components/assessments/my-journey-dashboard.tsx)</t>
         </is>
       </c>
       <c r="C267" s="13" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>real press/credibility content: all 10 "Magic Genie" client-pitch prompts (real named targets — Marco Argenti/Goldman Sachs, Adam Smith/Disney, etc.), 18 real client testimonials, all 8 explicitly-labeled satirical "parody" quotes (kept with disclaimers, not presented as real). Real overlap found and reconciled: this page's publications/speaking/podcasts arrays substantially duplicate the already-shipped /published's fuller bibliography — kept only what /published doesn't cover (Forbes + Business Insider bylines, the Clinton Global Initiative keynote, 4 of 5 podcast appearances) and cross-linked to /published for the rest, same reconciliation pattern as /assessments vs /find-my. Real bugs fixed: 3 genie/keynote links pointed externally at tonygreenberg.com/&lt;slug&gt; for posts that are real internal posts in this migration — relinked to /blog/psychedelics-could-become-extractive-capitalism, /blog/boiling-the-human-summit-harvard-kurzweil, /blog/return-on-investment-going-green-going-green-2 (all verified 200); a bare self-link to tonygreenberg.com remapped to /. Ships as a pure Server Component (legacy's FadeIn/Section/editorial-component dependencies don't exist here and weren't needed). Verified live: 200 OK, real content in raw SSR HTML, typecheck/lint clean.</t>
+          <t>"My Journey Dashboard," real grid/timeline views across all 28 JOURNEY_MAP experiences, category/status filters, phase progress ring, recommended-next card, using the same real useJourneyProgress/JOURNEY_MAP completion tracking every "Find Your X" quiz already writes to (not the narrower tg_assessment_results cookie built for /self-portrait). Legacy's per-quiz scored-result caching (RESULT_KEYS, feeding a mini radar chart) was not ported — no quiz in this migration writes that data either, same honest-degradation call already made for /self-portrait's own composite radar. Fixed a real legacy dead link (/ecosystem-map, a still-unbuilt page) to /self-portrait. Verified live: 200 OK, real content confirmed, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E267" s="14" t="inlineStr">
@@ -6998,7 +6998,7 @@
       <c r="A268" s="4" t="n"/>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>Homepage "Recent Updates" band (2026-09-29)</t>
+          <t>/the-open-door (src/app/the-open-door/page.tsx)</t>
         </is>
       </c>
       <c r="C268" s="13" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>on the live site (a newer Blog.tsx than _legacy-manus-app/, so rebuilt from the live page's markup), replacing the older "Latest Thinking" pair. Found while doing it: two live essays are missing from Sanity, the-tollbooth-and-the-alternative (Aug 18, 2026, the live site's newest) and what-quest-could-fix. Both were published on live after the legacy snapshot and need importing.</t>
+          <t>real press/credibility content: all 10 "Magic Genie" client-pitch prompts (real named targets — Marco Argenti/Goldman Sachs, Adam Smith/Disney, etc.), 18 real client testimonials, all 8 explicitly-labeled satirical "parody" quotes (kept with disclaimers, not presented as real). Real overlap found and reconciled: this page's publications/speaking/podcasts arrays substantially duplicate the already-shipped /published's fuller bibliography — kept only what /published doesn't cover (Forbes + Business Insider bylines, the Clinton Global Initiative keynote, 4 of 5 podcast appearances) and cross-linked to /published for the rest, same reconciliation pattern as /assessments vs /find-my. Real bugs fixed: 3 genie/keynote links pointed externally at tonygreenberg.com/&lt;slug&gt; for posts that are real internal posts in this migration — relinked to /blog/psychedelics-could-become-extractive-capitalism, /blog/boiling-the-human-summit-harvard-kurzweil, /blog/return-on-investment-going-green-going-green-2 (all verified 200); a bare self-link to tonygreenberg.com remapped to /. Ships as a pure Server Component (legacy's FadeIn/Section/editorial-component dependencies don't exist here and weren't needed). Verified live: 200 OK, real content in raw SSR HTML, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E268" s="14" t="inlineStr">
@@ -7021,7 +7021,7 @@
       <c r="A269" s="4" t="n"/>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Re-sync the legacy reference</t>
+          <t>Homepage "Recent Updates" band (2026-09-29)</t>
         </is>
       </c>
       <c r="C269" s="13" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>_legacy-manus-app/ is older than what's live (Recent Updates proves it), so visual diffs should be against the live site, not only that folder. Closed 2026-10-08: done the way this item suggests: every comparison since 2026-10-01 is against the live site itself (163 pages + 121 posts on 2026-10-01, 188 pages on 2026-10-07, 18 redesigned pages on 2026-10-08), with _legacy-manus-app/ used only as the code reference.</t>
+          <t>on the live site (a newer Blog.tsx than _legacy-manus-app/, so rebuilt from the live page's markup), replacing the older "Latest Thinking" pair. Found while doing it: two live essays are missing from Sanity, the-tollbooth-and-the-alternative (Aug 18, 2026, the live site's newest) and what-quest-could-fix. Both were published on live after the legacy snapshot and need importing.</t>
         </is>
       </c>
       <c r="E269" s="14" t="inlineStr">
@@ -7044,7 +7044,7 @@
       <c r="A270" s="4" t="n"/>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>Visual diff pass: every ported page vs</t>
+          <t>Re-sync the legacy reference</t>
         </is>
       </c>
       <c r="C270" s="13" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>legacy page Closed 2026-10-08: covered by the live-site sweeps above (screenshots and measured title/label/spacing per page, see the 2026-10-01, 10-02, 10-07 and 10-08 entries in this phase). Remaining differences are listed as decisions (Cormorant titles, /find-my header) or deliberate (CONTRIBUTING rule 20).</t>
+          <t>_legacy-manus-app/ is older than what's live (Recent Updates proves it), so visual diffs should be against the live site, not only that folder. Closed 2026-10-08: done the way this item suggests: every comparison since 2026-10-01 is against the live site itself (163 pages + 121 posts on 2026-10-01, 188 pages on 2026-10-07, 18 redesigned pages on 2026-10-08), with _legacy-manus-app/ used only as the code reference.</t>
         </is>
       </c>
       <c r="E270" s="14" t="inlineStr">
@@ -7067,7 +7067,7 @@
       <c r="A271" s="4" t="n"/>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Padding / spacing on the story pages matched to live (2026-10-01)</t>
+          <t>Visual diff pass: every ported page vs</t>
         </is>
       </c>
       <c r="C271" s="13" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>Measured margins, text column and spacing on 31 pages, live vs a production build, at 375px and 1280px. The "door" story pages were the clear mismatch: live's text column is ~546px (ours was 720px), 20px side margins on phones / 40px on desktop, body text 19px/1.8 on phones and 18px/1.85 on desktop (ours 16px/1.5). Fixed on /the-body, /engine-room, /under-nda, /the-nightstand, /the-web, /the-territory, /about, /intel (Intel uses live's 16.8px/1.9; About's hero line 480px max, 18.4px/1.8). Re-measured: all 8 match live to within 2px (About's column 28px narrower), no sideways scroll at 375px.</t>
+          <t>legacy page Closed 2026-10-08: covered by the live-site sweeps above (screenshots and measured title/label/spacing per page, see the 2026-10-01, 10-02, 10-07 and 10-08 entries in this phase). Remaining differences are listed as decisions (Cormorant titles, /find-my header) or deliberate (CONTRIBUTING rule 20).</t>
         </is>
       </c>
       <c r="E271" s="14" t="inlineStr">
@@ -7090,7 +7090,7 @@
       <c r="A272" s="4" t="n"/>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>Header-to-title spacing re-checked (2026-10-02)</t>
+          <t>Padding / spacing on the story pages matched to live (2026-10-01)</t>
         </is>
       </c>
       <c r="C272" s="13" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>The 2026-10-01 note compared different things: live's header wasn't measured (it showed 0), so "96px vs 168px" was really 161px vs 168px from the top of the page. Measured again from the top of the page, live vs a production build, at 375px and 1280px: most pages were already within 10px. Fixed the real gaps: /the-open-door (now live's dark centered hero band, 56px title, 546px text column; title was 72px too high), /start-here (live's 48px/96px top padding; 25px too high on desktop), /invest and /engage (label spacing and live's 32px/51px title; /invest's desktop title was 36px), /impact-dashboard on phones (card edge to edge under the header like live; title was 89px too low). Re-measured: all within 8px of live, no sideways scroll at 375px, no JS errors.</t>
+          <t>Measured margins, text column and spacing on 31 pages, live vs a production build, at 375px and 1280px. The "door" story pages were the clear mismatch: live's text column is ~546px (ours was 720px), 20px side margins on phones / 40px on desktop, body text 19px/1.8 on phones and 18px/1.85 on desktop (ours 16px/1.5). Fixed on /the-body, /engine-room, /under-nda, /the-nightstand, /the-web, /the-territory, /about, /intel (Intel uses live's 16.8px/1.9; About's hero line 480px max, 18.4px/1.8). Re-measured: all 8 match live to within 2px (About's column 28px narrower), no sideways scroll at 375px.</t>
         </is>
       </c>
       <c r="E272" s="14" t="inlineStr">
@@ -7113,7 +7113,7 @@
       <c r="A273" s="4" t="n"/>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>HumanOS headings in capitals like live (2026-10-02, owner said yes)</t>
+          <t>Header-to-title spacing re-checked (2026-10-02)</t>
         </is>
       </c>
       <c r="C273" s="13" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>the 4 headings live capitalises on /humanos (title, "Are you a Maximizer...", "Take the Diagnostic", "The Diagnostic") get uppercase; the words are unchanged. The subpages already matched.</t>
+          <t>The 2026-10-01 note compared different things: live's header wasn't measured (it showed 0), so "96px vs 168px" was really 161px vs 168px from the top of the page. Measured again from the top of the page, live vs a production build, at 375px and 1280px: most pages were already within 10px. Fixed the real gaps: /the-open-door (now live's dark centered hero band, 56px title, 546px text column; title was 72px too high), /start-here (live's 48px/96px top padding; 25px too high on desktop), /invest and /engage (label spacing and live's 32px/51px title; /invest's desktop title was 36px), /impact-dashboard on phones (card edge to edge under the header like live; title was 89px too low). Re-measured: all within 8px of live, no sideways scroll at 375px, no JS errors.</t>
         </is>
       </c>
       <c r="E273" s="14" t="inlineStr">
@@ -7136,7 +7136,7 @@
       <c r="A274" s="4" t="n"/>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>More layout gaps matched to live (2026-10-02)</t>
+          <t>HumanOS headings in capitals like live (2026-10-02, owner said yes)</t>
         </is>
       </c>
       <c r="C274" s="13" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>/series (live's centered 546px column, and a bug fixed: every card kept an empty 240px picture column, squeezing the text; live's per-series picture is one generic placeholder on the Manus proxy, so not copied), /humanos (middle section 900px like live), homepage desktop widths (hero text 804px, Four Doors 1000px, Editor's Picks 1168px, GemSpark edge, section title sizes; live's /blog now shows the homepage), /find-my (photo undimmed and plain background, like live; our site header kept). Re-measured: headings within 3px (/series) to 20px (homepage) of live, no sideways scroll, no JS errors. Note: live's "New here?" tour bar sits over its header and doesn't move the page, so it doesn't affect these numbers.</t>
+          <t>the 4 headings live capitalises on /humanos (title, "Are you a Maximizer...", "Take the Diagnostic", "The Diagnostic") get uppercase; the words are unchanged. The subpages already matched.</t>
         </is>
       </c>
       <c r="E274" s="14" t="inlineStr">
@@ -7159,7 +7159,7 @@
       <c r="A275" s="4" t="n"/>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Full sweep vs live (2026-10-02)</t>
+          <t>More layout gaps matched to live (2026-10-02)</t>
         </is>
       </c>
       <c r="C275" s="13" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>142 pages (every non-blog page, 3 of each templated set) at 375px and 1280px, title position, text column, title size. Fixed the shared causes: BrewSoul (live wraps most pages in its frame twice, so a second 52px offset plus the category badge; the landing, cities, directory and quiz pages have neither: src/components/brewsoul/brewsoul-main.tsx; intro paragraphs uncapped like live; 38px titles), Kava (live's extra 52px offset), /the-body, /the-nightstand, /the-web (405px top photo like live), the 6 peptide pages (live's 768/896px intro column), /journeys, /pick-up-the-phone, /published, /ecosystem (546px story column and live's text size). Re-measured: 110 of 120 within 40px / 60px of live.</t>
+          <t>/series (live's centered 546px column, and a bug fixed: every card kept an empty 240px picture column, squeezing the text; live's per-series picture is one generic placeholder on the Manus proxy, so not copied), /humanos (middle section 900px like live), homepage desktop widths (hero text 804px, Four Doors 1000px, Editor's Picks 1168px, GemSpark edge, section title sizes; live's /blog now shows the homepage), /find-my (photo undimmed and plain background, like live; our site header kept). Re-measured: headings within 3px (/series) to 20px (homepage) of live, no sideways scroll, no JS errors. Note: live's "New here?" tour bar sits over its header and doesn't move the page, so it doesn't affect these numbers.</t>
         </is>
       </c>
       <c r="E275" s="14" t="inlineStr">
@@ -7182,7 +7182,7 @@
       <c r="A276" s="4" t="n"/>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>Sweep leftovers fixed (2026-10-06)</t>
+          <t>Full sweep vs live (2026-10-02)</t>
         </is>
       </c>
       <c r="C276" s="13" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>Ported legacy's exact title sizes, margins and column widths. Measured live vs a production build at 375px and 1280px (H1 distance from the top, H1 size, intro and table widths). Now within 8px and the same title size on /published, /brewsoul/first-sip, /brewsoul/home, /brewsoul/chains (intro 912px like live), /brewsoul/browse, /brewsoul/directory (3-column 952px grid like live), /brewsoul and /brewsoul/quiz (intro 520px), /amplifier (546px column), /diamond-cut, /speaking, /living-declaration, /spirits, /protecting-your-business (tables 730px), and the 5 HumanOS subpages (titles smaller like live, 752px column). No sideways scroll at 375px. Left on purpose: /self-portrait (font matches; our page has a different title and no back link, so it sits 23-57px higher), BrewSoul pages 3-6px off (the shared journey bar row), and the different-layout pages /dharma-finder, /grant-study, /search, /quiz_25q, /soulscore. Also: /brewsoul/quiz rebuilt as a step registry (src/components/brewsoul/brewsoul-quiz/: parent + hook/ + components/step-* + data/), same questions, scoring and look; Back/Skip/Retake use lucide icons. New CONTRIBUTING rule 19 (multi-step flows, FydoPartner pattern). brewsoul-welcome-quiz.tsx (/brewsoul) still has the old shape and text arrows.</t>
+          <t>142 pages (every non-blog page, 3 of each templated set) at 375px and 1280px, title position, text column, title size. Fixed the shared causes: BrewSoul (live wraps most pages in its frame twice, so a second 52px offset plus the category badge; the landing, cities, directory and quiz pages have neither: src/components/brewsoul/brewsoul-main.tsx; intro paragraphs uncapped like live; 38px titles), Kava (live's extra 52px offset), /the-body, /the-nightstand, /the-web (405px top photo like live), the 6 peptide pages (live's 768/896px intro column), /journeys, /pick-up-the-phone, /published, /ecosystem (546px story column and live's text size). Re-measured: 110 of 120 within 40px / 60px of live.</t>
         </is>
       </c>
       <c r="E276" s="14" t="inlineStr">
@@ -7205,7 +7205,7 @@
       <c r="A277" s="4" t="n"/>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Match live's redesigned pages (2026-10-06, owner said go)</t>
+          <t>Sweep leftovers fixed (2026-10-06)</t>
         </is>
       </c>
       <c r="C277" s="13" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">/self-portrait (live: dark page, progress ring, "N more brushstrokes" lock until 5 assessments), /grant-study and /dharma-finder (live opens straight on question 1, no intro screen), /quiz_25q (live adds a hero picture above the title; rescue it into Sanity first), /search (live: one search box across essays, BrewSoul, peptides, HumanOS, assessments, kava and pages with filter chips). Measure live vs a production build at 375px and 1280px when done. Done 2026-10-06: /grant-study and /dharma-finder open straight on question 1 like live (title block / part header above the first question, live's 546px column, plain page, credit under every question), both rebuilt as step registries (rule 19); measured within 3px of live at the top (dharma's question block within 7px). /quiz_25q's hero rescued into Sanity and placed like live (within 2px). Found and fixed on the way: on the deployed copy /grant-study's answer buttons could not be clicked (the themed page background was fixed z-0, painted over the quiz); ThemedBackground is now -z-10 pointer-events-none (backgrounds unchanged on all 21 pages that use it), and the shared email gate no longer scrolls sideways on phones. Both quizzes clicked through to results in Chrome and Safari. /self-portrait restyled to live (dark page, "The Composite You", progress ring, "N More Brushstrokes Needed" lock until 5 done, live's copy) on our real cookie data; within 3px of live at both widths; tested with 0, 2 and 6 completed. Counts are ours (13 </t>
+          <t>Ported legacy's exact title sizes, margins and column widths. Measured live vs a production build at 375px and 1280px (H1 distance from the top, H1 size, intro and table widths). Now within 8px and the same title size on /published, /brewsoul/first-sip, /brewsoul/home, /brewsoul/chains (intro 912px like live), /brewsoul/browse, /brewsoul/directory (3-column 952px grid like live), /brewsoul and /brewsoul/quiz (intro 520px), /amplifier (546px column), /diamond-cut, /speaking, /living-declaration, /spirits, /protecting-your-business (tables 730px), and the 5 HumanOS subpages (titles smaller like live, 752px column). No sideways scroll at 375px. Left on purpose: /self-portrait (font matches; our page has a different title and no back link, so it sits 23-57px higher), BrewSoul pages 3-6px off (the shared journey bar row), and the different-layout pages /dharma-finder, /grant-study, /search, /quiz_25q, /soulscore. Also: /brewsoul/quiz rebuilt as a step registry (src/components/brewsoul/brewsoul-quiz/: parent + hook/ + components/step-* + data/), same questions, scoring and look; Back/Skip/Retake use lucide icons. New CONTRIBUTING rule 19 (multi-step flows, FydoPartner pattern). brewsoul-welcome-quiz.tsx (/brewsoul) still has the old shape and text arrows.</t>
         </is>
       </c>
       <c r="E277" s="14" t="inlineStr">
@@ -7228,17 +7228,17 @@
       <c r="A278" s="4" t="n"/>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>Still different from live (needs a yes)</t>
-        </is>
-      </c>
-      <c r="C278" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Match live's redesigned pages (2026-10-06, owner said go)</t>
+        </is>
+      </c>
+      <c r="C278" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>blog posts (done) (done 2026-10-07, see Phase 5); /find-my on live hides the site header. /walk-through is a 404 on live now.</t>
+          <t xml:space="preserve">/self-portrait (live: dark page, progress ring, "N more brushstrokes" lock until 5 assessments), /grant-study and /dharma-finder (live opens straight on question 1, no intro screen), /quiz_25q (live adds a hero picture above the title; rescue it into Sanity first), /search (live: one search box across essays, BrewSoul, peptides, HumanOS, assessments, kava and pages with filter chips). Measure live vs a production build at 375px and 1280px when done. Done 2026-10-06: /grant-study and /dharma-finder open straight on question 1 like live (title block / part header above the first question, live's 546px column, plain page, credit under every question), both rebuilt as step registries (rule 19); measured within 3px of live at the top (dharma's question block within 7px). /quiz_25q's hero rescued into Sanity and placed like live (within 2px). Found and fixed on the way: on the deployed copy /grant-study's answer buttons could not be clicked (the themed page background was fixed z-0, painted over the quiz); ThemedBackground is now -z-10 pointer-events-none (backgrounds unchanged on all 21 pages that use it), and the shared email gate no longer scrolls sideways on phones. Both quizzes clicked through to results in Chrome and Safari. /self-portrait restyled to live (dark page, "The Composite You", progress ring, "N More Brushstrokes Needed" lock until 5 done, live's copy) on our real cookie data; within 3px of live at both widths; tested with 0, 2 and 6 completed. Counts are ours (13 </t>
         </is>
       </c>
       <c r="E278" s="14" t="inlineStr">
@@ -7251,7 +7251,7 @@
       <c r="A279" s="4" t="n"/>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Design change on live, needs a decision</t>
+          <t>Still different from live (needs a yes)</t>
         </is>
       </c>
       <c r="C279" s="15" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>live's story pages now use Cormorant Garamond for titles (ours: Playfair Display), a lighter title weight (400 vs our 700), and a red eyebrow label (#8E1E25, wider letter spacing) instead of our gold. A site-wide font swap is a design call, so not done.</t>
+          <t>blog posts (done) (done 2026-10-07, see Phase 5); /find-my on live hides the site header. /walk-through is a 404 on live now.</t>
         </is>
       </c>
       <c r="E279" s="14" t="inlineStr">
@@ -7274,17 +7274,17 @@
       <c r="A280" s="4" t="n"/>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>Link check across all ported pages (no 404s, no broken internal cross-references)</t>
-        </is>
-      </c>
-      <c r="C280" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design change on live, needs a decision</t>
+        </is>
+      </c>
+      <c r="C280" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>First full pass done 2026-09-29 (510 pages crawled from the sitemap plus every internal link, on a production build). Fixed in code: /brewsoul/coffee/…-tarrazú 404 (the route got the id still percent-encoded), 30+ links that went through the /assessments/* redirects, /find-your-me's dead Homeaglow link, the two root-level Iboga essay links, and the dead FauxTony nav item. Fixed as Sanity drafts (scripts/fix-blog-body-links.ts, 14 posts): broken post links, leaked !… placeholder text, Energy Is Money's split author bio, and scraped WordPress furniture ("Share this / Related / You Might Also Like / Copyright", "Show More / Top News", [mc4wp_form]). Left for a decision: /framework's "Ask FauxTony" button, when-healing-becomes-extraction's two links to a Dr. Lee case file that doesn't exist, and the-clock-keeper-chronicles-part-1's link to the deferred /clock-keeper-part-2. Re-run after the drafts are published. 2026-10-01 re-run (local production build, all 498 sitemap URLs load; 440 unique internal links): 5 broken. Fixed as a Sanity draft: molecule-as-mirror-10-what-the-pioneers-know's "Final installment" link pointed at a non-existent part-10 slug (now part 11; live also shows that line twice, kept). Already fixed in a waiting draft: forever-chemicals-... → /blog/psychedelic-readiness-index. Still the 3 known decisions: /fauxtony (from /framework), /clock-keeper-part-2, /blog/the-case-file-dr-samuel-lee. 2026-10-08 re-run (production build, all 497 sitemap pages, 453 unique i</t>
+          <t>live's story pages now use Cormorant Garamond for titles (ours: Playfair Display), a lighter title weight (400 vs our 700), and a red eyebrow label (#8E1E25, wider letter spacing) instead of our gold. A site-wide font swap is a design call, so not done.</t>
         </is>
       </c>
       <c r="E280" s="14" t="inlineStr">
@@ -7297,7 +7297,7 @@
       <c r="A281" s="4" t="n"/>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Sitemap: no noindex pages (2026-10-08)</t>
+          <t>Link check across all ported pages (no 404s, no broken internal cross-references)</t>
         </is>
       </c>
       <c r="C281" s="13" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>the password-locked /blog/you-are-the-moat was in the sitemap while telling Google not to index it (a Search Console sitemap warning). Gated posts and posts that redirect are now left out (src/app/sitemap.ts); all 497 sitemap addresses return 200 with a matching canonical and no noindex. The 82 warnings Search Console shows are for the old live sitemap, so re-check them after cutover.</t>
+          <t>First full pass done 2026-09-29 (510 pages crawled from the sitemap plus every internal link, on a production build). Fixed in code: /brewsoul/coffee/…-tarrazú 404 (the route got the id still percent-encoded), 30+ links that went through the /assessments/* redirects, /find-your-me's dead Homeaglow link, the two root-level Iboga essay links, and the dead FauxTony nav item. Fixed as Sanity drafts (scripts/fix-blog-body-links.ts, 14 posts): broken post links, leaked !… placeholder text, Energy Is Money's split author bio, and scraped WordPress furniture ("Share this / Related / You Might Also Like / Copyright", "Show More / Top News", [mc4wp_form]). Left for a decision: /framework's "Ask FauxTony" button, when-healing-becomes-extraction's two links to a Dr. Lee case file that doesn't exist, and the-clock-keeper-chronicles-part-1's link to the deferred /clock-keeper-part-2. Re-run after the drafts are published. 2026-10-01 re-run (local production build, all 498 sitemap URLs load; 440 unique internal links): 5 broken. Fixed as a Sanity draft: molecule-as-mirror-10-what-the-pioneers-know's "Final installment" link pointed at a non-existent part-10 slug (now part 11; live also shows that line twice, kept). Already fixed in a waiting draft: forever-chemicals-... → /blog/psychedelic-readiness-index. Still the 3 known decisions: /fauxtony (from /framework), /clock-keeper-part-2, /blog/the-case-file-dr-samuel-lee. 2026-10-08 re-run (production build, all 497 sitemap pages, 453 unique i</t>
         </is>
       </c>
       <c r="E281" s="14" t="inlineStr">
@@ -7320,17 +7320,17 @@
       <c r="A282" s="4" t="n"/>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>Lighthouse pass (performance/accessibility/SEO) on top 20 pages by traffic 2026-09-30, 20 key pages (no traffic data yet), local production …</t>
-        </is>
-      </c>
-      <c r="C282" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Sitemap: no noindex pages (2026-10-08)</t>
+        </is>
+      </c>
+      <c r="C282" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>build, mobile: averages performance 87, accessibility 99→100, best practices 100, SEO 92→100, CLS 0 everywhere. Fixed: public/robots.txt had an LLMs: line (not a real directive) that made Google treat the whole file as invalid, now a comment; h3/h4 headings skipping a level on /assessments, /kava, /peptide-watch (same look, right tag); the Kava and /attention-theft back-arrow links had no accessible name on phones; two small phone-width contrast misses. Left: performance is local-machine only (±10-15 points, see CONTRIBUTING.md); the slowest were / 76 (LCP 5.2 s), /psychedelic-readiness-index 82, /iboga-ibogaine 83. Re-run against the Netlify deploy before launch. 2026-10-06 re-run against the Netlify deploy (14 key pages, mobile): accessibility 100 and CLS 0 on every page, SEO clean (only the expected netlify.app noindex), performance 77-97 held back by 3-4 s LCP. Fixed: all 21 hero images moved off the deprecated priority prop to fetchPriority="high" + loading="eager" (Next 16); /iboga-ibogaine hero and the first card on /blog and category pages no longer lazy-loaded; sizes on the Four Doors cards (~150 KiB per page), /humanos diagram (~100 KiB) and /about headshot; urlFor no longer imports the Sanity client, so ~115 KB of Sanity client code stopped loading on / and /blog; React hydration error #418 on / and /blog (post dates) gone, checked in two time zones; /blog is static again; empty icon &lt;th&gt;s on /iboga-ibogaine labelled; category page reads use sanityFetch(). Left: se</t>
+          <t>the password-locked /blog/you-are-the-moat was in the sitemap while telling Google not to index it (a Search Console sitemap warning). Gated posts and posts that redirect are now left out (src/app/sitemap.ts); all 497 sitemap addresses return 200 with a matching canonical and no noindex. The 82 warnings Search Console shows are for the old live sitemap, so re-check them after cutover.</t>
         </is>
       </c>
       <c r="E282" s="14" t="inlineStr">
@@ -7343,17 +7343,17 @@
       <c r="A283" s="4" t="n"/>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Error pages (2026-10-09, owner asked)</t>
-        </is>
-      </c>
-      <c r="C283" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Lighthouse pass (performance/accessibility/SEO) on top 20 pages by traffic 2026-09-30, 20 key pages (no traffic data yet), local production …</t>
+        </is>
+      </c>
+      <c r="C283" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>404 page now sets its own title ("Page not found") as a server page around live's 3-second redirect (not-found.tsx + components/not-found-redirect.tsx), arrow as an icon; page error screen (error.tsx) uses Next 16's retry (re-fetches), shows a reference code for the server logs, links home and to the site index; new global-error.tsx for failures in the root layout itself (own &lt;html&gt;, plain links). Verified on a production build: missing page, missing essay and missing Kava page return 404 with the right title; a test page that throws returns 500 with the error screen, "Try again" re-fetches; phone and laptop, no sideways scroll (test page removed).</t>
+          <t>build, mobile: averages performance 87, accessibility 99→100, best practices 100, SEO 92→100, CLS 0 everywhere. Fixed: public/robots.txt had an LLMs: line (not a real directive) that made Google treat the whole file as invalid, now a comment; h3/h4 headings skipping a level on /assessments, /kava, /peptide-watch (same look, right tag); the Kava and /attention-theft back-arrow links had no accessible name on phones; two small phone-width contrast misses. Left: performance is local-machine only (±10-15 points, see CONTRIBUTING.md); the slowest were / 76 (LCP 5.2 s), /psychedelic-readiness-index 82, /iboga-ibogaine 83. Re-run against the Netlify deploy before launch. 2026-10-06 re-run against the Netlify deploy (14 key pages, mobile): accessibility 100 and CLS 0 on every page, SEO clean (only the expected netlify.app noindex), performance 77-97 held back by 3-4 s LCP. Fixed: all 21 hero images moved off the deprecated priority prop to fetchPriority="high" + loading="eager" (Next 16); /iboga-ibogaine hero and the first card on /blog and category pages no longer lazy-loaded; sizes on the Four Doors cards (~150 KiB per page), /humanos diagram (~100 KiB) and /about headshot; urlFor no longer imports the Sanity client, so ~115 KB of Sanity client code stopped loading on / and /blog; React hydration error #418 on / and /blog (post dates) gone, checked in two time zones; /blog is static again; empty icon &lt;th&gt;s on /iboga-ibogaine labelled; category page reads use sanityFetch(). Left: se</t>
         </is>
       </c>
       <c r="E283" s="14" t="inlineStr">
@@ -7366,7 +7366,7 @@
       <c r="A284" s="4" t="n"/>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>SEO audit fixes (2026-10-06)</t>
+          <t>Error pages (2026-10-09, owner asked)</t>
         </is>
       </c>
       <c r="C284" s="13" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
+          <t>404 page now sets its own title ("Page not found") as a server page around live's 3-second redirect (not-found.tsx + components/not-found-redirect.tsx), arrow as an icon; page error screen (error.tsx) uses Next 16's retry (re-fetches), shows a reference code for the server logs, links home and to the site index; new global-error.tsx for failures in the root layout itself (own &lt;html&gt;, plain links). Verified on a production build: missing page, missing essay and missing Kava page return 404 with the right title; a test page that throws returns 500 with the error screen, "Try again" re-fetches; phone and laptop, no sideways scroll (test page removed).</t>
         </is>
       </c>
       <c r="E284" s="14" t="inlineStr">
@@ -7389,17 +7389,17 @@
       <c r="A285" s="4" t="n"/>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>SEO audit items needing a yes (2026-10-06)</t>
-        </is>
-      </c>
-      <c r="C285" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>SEO audit fixes (2026-10-06)</t>
+        </is>
+      </c>
+      <c r="C285" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+          <t>Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
         </is>
       </c>
       <c r="E285" s="14" t="inlineStr">
@@ -7412,7 +7412,7 @@
       <c r="A286" s="4" t="n"/>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+          <t>SEO audit items needing a yes (2026-10-06)</t>
         </is>
       </c>
       <c r="C286" s="15" t="inlineStr">
@@ -7420,7 +7420,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D286" s="4" t="inlineStr"/>
+      <c r="D286" s="4" t="inlineStr">
+        <is>
+          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+        </is>
+      </c>
       <c r="E286" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -7431,19 +7435,15 @@
       <c r="A287" s="4" t="n"/>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
-        </is>
-      </c>
-      <c r="C287" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D287" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
-        </is>
-      </c>
+          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+        </is>
+      </c>
+      <c r="C287" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D287" s="4" t="inlineStr"/>
       <c r="E287" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -7454,7 +7454,7 @@
       <c r="A288" s="4" t="n"/>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>"Keep going" strip above the footer on every page (2026-10-07)</t>
+          <t>Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
         </is>
       </c>
       <c r="C288" s="13" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>legacy's WhereNext (deferred in Phase 3, never picked up) with its per-page suggestions, Home · Site Index · All Assessments; links pointed at current routes.</t>
+          <t>2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
         </is>
       </c>
       <c r="E288" s="14" t="inlineStr">
@@ -7477,7 +7477,7 @@
       <c r="A289" s="4" t="n"/>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Live-only and redesigned pages from the 2026-10-07 page sweep (188 pages compared with live)</t>
+          <t>"Keep going" strip above the footer on every page (2026-10-07)</t>
         </is>
       </c>
       <c r="C289" s="13" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>/the-index rebuilt from live's code (20 concepts, related-word search across essays and site pages, full-text search on the server, "three related places to go next"; the old redirect to /search removed and its links, including the "Site Index" link in "Keep going", point at it again); /the-mirror (and /life-assessment) opens on live's intro (dark hero, "What We Measure" with the six areas, "The Ecosystem"), rebuilt as a step registry (rule 19); /essays header, order and column like live; /about "What They Say" styled like live (live picks 3 of the same 19 quotes at random; ours shows a fixed 3 so they're in the server HTML); /impact-futurism list titles and subtitles; /supplier-intake is a real page again with live's Stage 1 form; /seven-doors and /projects redirect home like live; /impact, /health, /library, /built-on-manus, /heroes are 404 on live too. Left as is on purpose: /blog stays our archive page (on live it repeats the homepage), the email gates on /framework and /peptide-supply-chain, the attention-theft Wall of Shame.</t>
+          <t>legacy's WhereNext (deferred in Phase 3, never picked up) with its per-page suggestions, Home · Site Index · All Assessments; links pointed at current routes.</t>
         </is>
       </c>
       <c r="E289" s="14" t="inlineStr">
@@ -7500,7 +7500,7 @@
       <c r="A290" s="4" t="n"/>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>/alex-azzi locked like live (2026-10-07, owner said match it)</t>
+          <t>Live-only and redesigned pages from the 2026-10-07 page sweep (188 pages compared with live)</t>
         </is>
       </c>
       <c r="C290" s="13" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>same server-checked password as the locked essay (GATED_POST_PASSWORD, now also set in Netlify), live's "Restricted Access" screen, the report not in the page until unlocked, out of search and the sitemap.</t>
+          <t>/the-index rebuilt from live's code (20 concepts, related-word search across essays and site pages, full-text search on the server, "three related places to go next"; the old redirect to /search removed and its links, including the "Site Index" link in "Keep going", point at it again); /the-mirror (and /life-assessment) opens on live's intro (dark hero, "What We Measure" with the six areas, "The Ecosystem"), rebuilt as a step registry (rule 19); /essays header, order and column like live; /about "What They Say" styled like live (live picks 3 of the same 19 quotes at random; ours shows a fixed 3 so they're in the server HTML); /impact-futurism list titles and subtitles; /supplier-intake is a real page again with live's Stage 1 form; /seven-doors and /projects redirect home like live; /impact, /health, /library, /built-on-manus, /heroes are 404 on live too. Left as is on purpose: /blog stays our archive page (on live it repeats the homepage), the email gates on /framework and /peptide-supply-chain, the attention-theft Wall of Shame.</t>
         </is>
       </c>
       <c r="E290" s="14" t="inlineStr">
@@ -7523,7 +7523,7 @@
       <c r="A291" s="4" t="n"/>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Live's title fonts and sizes (2026-10-07, "fix the style")</t>
+          <t>/alex-azzi locked like live (2026-10-07, owner said match it)</t>
         </is>
       </c>
       <c r="C291" s="13" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>measured every page's title font, weight, size and label colour on live vs ours (136 pages). Now like live: Kava headings in Fraunces, HumanOS in Space Grotesk, the peptide tools / charity scorecard / thesis threads in the system serif, America Unbundled in the Iowan Old Style stack at live's size, /akbar in Fraunces 900, friend-gate and post-intervention in Georgia, and live's title sizes on peptide-matrix, peptide-supply-chain, rip-peptide-sciences and the HumanOS pages. Fonts load only on the pages that use them (src/lib/fonts/page-fonts.ts). Label colours stay the darker AA-contrast versions where live's lighter ones fail on a light background.</t>
+          <t>same server-checked password as the locked essay (GATED_POST_PASSWORD, now also set in Netlify), live's "Restricted Access" screen, the report not in the page until unlocked, out of search and the sitemap.</t>
         </is>
       </c>
       <c r="E291" s="14" t="inlineStr">
@@ -7546,7 +7546,7 @@
       <c r="A292" s="4" t="n"/>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>Peptide page images rescued into Sanity and wired (2026-10-07)</t>
+          <t>Live's title fonts and sizes (2026-10-07, "fix the style")</t>
         </is>
       </c>
       <c r="C292" s="13" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>/peptide-watch hero plus its 11 section banners, /peptide-matrix and /peptide-supply-chain heroes, the /peptide-hall-of-shame hero (scripts/rescue-2026-10-07-peptide-images.ts, logged in docs/ai/manus-media-rescue.md).</t>
+          <t>measured every page's title font, weight, size and label colour on live vs ours (136 pages). Now like live: Kava headings in Fraunces, HumanOS in Space Grotesk, the peptide tools / charity scorecard / thesis threads in the system serif, America Unbundled in the Iowan Old Style stack at live's size, /akbar in Fraunces 900, friend-gate and post-intervention in Georgia, and live's title sizes on peptide-matrix, peptide-supply-chain, rip-peptide-sciences and the HumanOS pages. Fonts load only on the pages that use them (src/lib/fonts/page-fonts.ts). Label colours stay the darker AA-contrast versions where live's lighter ones fail on a light background.</t>
         </is>
       </c>
       <c r="E292" s="14" t="inlineStr">
@@ -7569,7 +7569,7 @@
       <c r="A293" s="4" t="n"/>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Live's editorial redesign, first group (2026-10-07)</t>
+          <t>Peptide page images rescued into Sanity and wired (2026-10-07)</t>
         </is>
       </c>
       <c r="C293" s="13" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
+          <t>/peptide-watch hero plus its 11 section banners, /peptide-matrix and /peptide-supply-chain heroes, the /peptide-hall-of-shame hero (scripts/rescue-2026-10-07-peptide-images.ts, logged in docs/ai/manus-media-rescue.md).</t>
         </is>
       </c>
       <c r="E293" s="14" t="inlineStr">
@@ -7592,7 +7592,7 @@
       <c r="A294" s="4" t="n"/>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Live's redesign, second group (done 2026-10-08)</t>
+          <t>Live's editorial redesign, first group (2026-10-07)</t>
         </is>
       </c>
       <c r="C294" s="13" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>re-measured all 18 pages on live vs a fresh production build (title font/size/weight/colour, labels, hero images). Already matching from 2026-10-07: /the-web, /spirits, /iboga-ibogaine (weight 800), /living-declaration, BrewSoul photo on /brewsoul, /brewsoul/browse, /brewsoul/first-sip (live has none there either), /quiz_25q, /recent-creations. Fixed today: /find-your-journey (64px title, red label), /impact-dashboard (64px title in essay ink, label spacing), red labels on /published and /speaking (plus its "rooms" chips), /soulscore "by ImpactSoul" label, /pri-calibration title (weight 900, solid cream, was a purple gradient), /clients (live's narrow 546px column for the whole page, 56px title, roomier stats band, cards 2 per row; two static inline styles moved to classes), /brewsoul/guest (live's BrewSoul photo on the guest card instead of "SN" initials, labels in capitals), /humanos/connect (cards line up with the title), /peptide-hall-of-shame (stats and label readable light gold; were dark gold on dark). Typed arrows on the touched links are icons now (rule 18). Deliberately not copied from live (new CONTRIBUTING rule 20, owner 2026-10-08): red labels on dark bands use #E07A80 (live's #8E1E25 on black is about 2:1, unreadable); /recent-creations keeps our darker label colours (live's fail contrast on white); /humanos/connect keeps "Start Reading" (that card links to the philosophy page, the quiz live's "Start the Assessment" implies doesn't exist). Checked: type check, l</t>
+          <t>dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
         </is>
       </c>
       <c r="E294" s="14" t="inlineStr">
@@ -7615,7 +7615,7 @@
       <c r="A295" s="4" t="n"/>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>BrewSoul top of page (2026-10-08, owner: "button in the center at the top doesn't look good")</t>
+          <t>Live's redesign, second group (done 2026-10-08)</t>
         </is>
       </c>
       <c r="C295" s="13" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>the category badge ("Deep Research" etc.) sat centred in an empty strip, squeezed against the hero, because we copied live's doubled 52px top gap. Now one gap everywhere and the badge floats in the top-left corner, lined up with the BrewSoul logo (brewsoul-main.tsx, category-badge.tsx); checked on all 26 badge pages at 3 widths that it covers nothing. BrewSoul menu: on tablets (768-1023px) the links were cut off and "More" was hidden with no menu button at all; now the menu button shows below 1024px, 5 links + "More" from 1024px, all 8 from 1280px, "More" always visible.</t>
+          <t>re-measured all 18 pages on live vs a fresh production build (title font/size/weight/colour, labels, hero images). Already matching from 2026-10-07: /the-web, /spirits, /iboga-ibogaine (weight 800), /living-declaration, BrewSoul photo on /brewsoul, /brewsoul/browse, /brewsoul/first-sip (live has none there either), /quiz_25q, /recent-creations. Fixed today: /find-your-journey (64px title, red label), /impact-dashboard (64px title in essay ink, label spacing), red labels on /published and /speaking (plus its "rooms" chips), /soulscore "by ImpactSoul" label, /pri-calibration title (weight 900, solid cream, was a purple gradient), /clients (live's narrow 546px column for the whole page, 56px title, roomier stats band, cards 2 per row; two static inline styles moved to classes), /brewsoul/guest (live's BrewSoul photo on the guest card instead of "SN" initials, labels in capitals), /humanos/connect (cards line up with the title), /peptide-hall-of-shame (stats and label readable light gold; were dark gold on dark). Typed arrows on the touched links are icons now (rule 18). Deliberately not copied from live (new CONTRIBUTING rule 20, owner 2026-10-08): red labels on dark bands use #E07A80 (live's #8E1E25 on black is about 2:1, unreadable); /recent-creations keeps our darker label colours (live's fail contrast on white); /humanos/connect keeps "Start Reading" (that card links to the philosophy page, the quiz live's "Start the Assessment" implies doesn't exist). Checked: type check, l</t>
         </is>
       </c>
       <c r="E295" s="14" t="inlineStr">
@@ -7638,7 +7638,7 @@
       <c r="A296" s="4" t="n"/>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>/pri-efficacy's "Simulation / Live Calibrations" switch like live (2026-10-08)</t>
+          <t>BrewSoul top of page (2026-10-08, owner: "button in the center at the top doesn't look good")</t>
         </is>
       </c>
       <c r="C296" s="13" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>shadcn Tabs, both panels in the server HTML (forceMount). The Live tab reads real aggregate numbers from pri_calibrations (getPriLiveStats() in src/lib/pri-research.ts: totals, opt-ins, average score per dimension; no rows leave the server), page stays static and refreshes every 10 minutes. Until the Supabase scripts are run (Phase 2) it says the numbers "aren't available just now" instead of a fake zero. Checked: build (○, 10m), server HTML has both tabs, tab switch at 390/1280px, no JS errors. Re-check with real numbers once the table exists.</t>
+          <t>the category badge ("Deep Research" etc.) sat centred in an empty strip, squeezed against the hero, because we copied live's doubled 52px top gap. Now one gap everywhere and the badge floats in the top-left corner, lined up with the BrewSoul logo (brewsoul-main.tsx, category-badge.tsx); checked on all 26 badge pages at 3 widths that it covers nothing. BrewSoul menu: on tablets (768-1023px) the links were cut off and "More" was hidden with no menu button at all; now the menu button shows below 1024px, 5 links + "More" from 1024px, all 8 from 1280px, "More" always visible.</t>
         </is>
       </c>
       <c r="E296" s="14" t="inlineStr">
@@ -7661,63 +7661,63 @@
       <c r="A297" s="4" t="n"/>
       <c r="B297" s="4" t="inlineStr">
         <is>
+          <t>/pri-efficacy's "Simulation / Live Calibrations" switch like live (2026-10-08)</t>
+        </is>
+      </c>
+      <c r="C297" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D297" s="4" t="inlineStr">
+        <is>
+          <t>shadcn Tabs, both panels in the server HTML (forceMount). The Live tab reads real aggregate numbers from pri_calibrations (getPriLiveStats() in src/lib/pri-research.ts: totals, opt-ins, average score per dimension; no rows leave the server), page stays static and refreshes every 10 minutes. Until the Supabase scripts are run (Phase 2) it says the numbers "aren't available just now" instead of a fake zero. Checked: build (○, 10m), server HTML has both tabs, tab switch at 390/1280px, no JS errors. Re-check with real numbers once the table exists.</t>
+        </is>
+      </c>
+      <c r="E297" s="14" t="inlineStr">
+        <is>
+          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="4" t="n"/>
+      <c r="B298" s="4" t="inlineStr">
+        <is>
           <t>/brewsoul/browse hero readable (2026-10-08, owner said go ahead)</t>
         </is>
       </c>
-      <c r="C297" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D297" s="4" t="inlineStr">
+      <c r="C298" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D298" s="4" t="inlineStr">
         <is>
           <t>a soft cream glow behind the title block so "The Catalog", the subtitle and the stat labels read clearly over the coffee photo (live is hard to read there too; rule 20). Photo still shows around the edges. Checked at 390/1280px.</t>
         </is>
       </c>
-      <c r="E297" s="14" t="inlineStr">
+      <c r="E298" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
         </is>
       </c>
     </row>
-    <row r="298">
-      <c r="A298" s="10" t="inlineStr">
+    <row r="299">
+      <c r="A299" s="10" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
-      <c r="B298" s="11" t="n"/>
-      <c r="C298" s="11" t="n"/>
-      <c r="D298" s="12" t="n"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="4" t="n"/>
-      <c r="B299" s="4" t="inlineStr">
-        <is>
-          <t>Manus media rescue (2026-09-29)</t>
-        </is>
-      </c>
-      <c r="C299" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D299" s="4" t="inlineStr">
-        <is>
-          <t>all 94 Manus-hosted image/video references in the legacy source (/api/img/, /manus-storage/) were checked live. 91 were still downloadable, including the /akbar photos the entry below calls "permanently lost", and all 91 are now Sanity assets (scripts/rescue-manus-media.ts; Sanity dedupes by SHA-1). 3 were gone (HTTP 502). The manifest docs/ai/manus-media-rescue.md maps each one to the legacy files that used it and its Sanity URL. They are not wired into pages yet: go page by page, with real alt text. /facilitator-index's two diagrams are done (scripts/rescue-facilitator-images.ts).</t>
-        </is>
-      </c>
-      <c r="E299" s="14" t="inlineStr">
-        <is>
-          <t>Phase 13 — Images Needed in Sanity</t>
-        </is>
-      </c>
+      <c r="B299" s="11" t="n"/>
+      <c r="C299" s="11" t="n"/>
+      <c r="D299" s="12" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="4" t="n"/>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>Favicon</t>
+          <t>Manus media rescue (2026-09-29)</t>
         </is>
       </c>
       <c r="C300" s="13" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>real "G" brand mark generated from the header's actual wordmark treatment (src/app/icon.tsx), see Phase 3</t>
+          <t>all 94 Manus-hosted image/video references in the legacy source (/api/img/, /manus-storage/) were checked live. 91 were still downloadable, including the /akbar photos the entry below calls "permanently lost", and all 91 are now Sanity assets (scripts/rescue-manus-media.ts; Sanity dedupes by SHA-1). 3 were gone (HTTP 502). The manifest docs/ai/manus-media-rescue.md maps each one to the legacy files that used it and its Sanity URL. They are not wired into pages yet: go page by page, with real alt text. /facilitator-index's two diagrams are done (scripts/rescue-facilitator-images.ts).</t>
         </is>
       </c>
       <c r="E300" s="14" t="inlineStr">
@@ -7740,17 +7740,17 @@
       <c r="A301" s="4" t="n"/>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
-        </is>
-      </c>
-      <c r="C301" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Favicon</t>
+        </is>
+      </c>
+      <c r="C301" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
+          <t>real "G" brand mark generated from the header's actual wordmark treatment (src/app/icon.tsx), see Phase 3</t>
         </is>
       </c>
       <c r="E301" s="14" t="inlineStr">
@@ -7763,17 +7763,17 @@
       <c r="A302" s="4" t="n"/>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>Author photo(s) for blog author schema (Tony Greenberg headshot at minimum)</t>
-        </is>
-      </c>
-      <c r="C302" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
+        </is>
+      </c>
+      <c r="C302" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: the rescued headshot is already the author avatar in Sanity; now also in every post's Article JSON-LD (author image + url /about). The JSON-LD publisher logo pointed at /favicon.ico, a 404 here; now /icon.</t>
+          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
         </is>
       </c>
       <c r="E302" s="14" t="inlineStr">
@@ -7786,7 +7786,7 @@
       <c r="A303" s="4" t="n"/>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Blog hero images</t>
+          <t>Author photo(s) for blog author schema (Tony Greenberg headshot at minimum)</t>
         </is>
       </c>
       <c r="C303" s="13" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>audited, then migrated. Final state:</t>
+          <t>2026-10-02: the rescued headshot is already the author avatar in Sanity; now also in every post's Article JSON-LD (author image + url /about). The JSON-LD publisher logo pointed at /favicon.ico, a 404 here; now /icon.</t>
         </is>
       </c>
       <c r="E303" s="14" t="inlineStr">
@@ -7809,7 +7809,7 @@
       <c r="A304" s="4" t="n"/>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>22 posts have a real hero image, now live in Sanity (17 already on RampRate's own CloudFront + 4 rescued from the legacy /api/img/ proxy + 1…</t>
+          <t>Blog hero images</t>
         </is>
       </c>
       <c r="C304" s="13" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> rescued from /manus-storage/, all pulled over by migrate-blog-posts.ts before Manus is decommissioned)</t>
+          <t>audited, then migrated. Final state:</t>
         </is>
       </c>
       <c r="E304" s="14" t="inlineStr">
@@ -7832,7 +7832,7 @@
       <c r="A305" s="4" t="n"/>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>7 more posts got a real, unique hero image rescued from the live legacy site's newly-added art this pass (scripts/rescue-2026-09-blog-images…</t>
+          <t>22 posts have a real hero image, now live in Sanity (17 already on RampRate's own CloudFront + 4 rescued from the legacy /api/img/ proxy + 1…</t>
         </is>
       </c>
       <c r="C305" s="13" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>.ts — see the correction note above): california-toll-roads-legalized-scam, the-1000-hour-hold, conscious-capital-partnership-ecosystem, the-peptide-truth-65m-fraud-industry-vs-life-changing-medicine, clear-communication, building-services-market-transhuman-era, heart-protocol-addendum.</t>
+          <t xml:space="preserve"> rescued from /manus-storage/, all pulled over by migrate-blog-posts.ts before Manus is decommissioned)</t>
         </is>
       </c>
       <c r="E305" s="14" t="inlineStr">
@@ -7855,17 +7855,17 @@
       <c r="A306" s="4" t="n"/>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>92 posts still need a real, unique hero image</t>
-        </is>
-      </c>
-      <c r="C306" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>7 more posts got a real, unique hero image rescued from the live legacy site's newly-added art this pass (scripts/rescue-2026-09-blog-images…</t>
+        </is>
+      </c>
+      <c r="C306" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
+          <t>.ts — see the correction note above): california-toll-roads-legalized-scam, the-1000-hour-hold, conscious-capital-partnership-ecosystem, the-peptide-truth-65m-fraud-industry-vs-life-changing-medicine, clear-communication, building-services-market-transhuman-era, heart-protocol-addendum.</t>
         </is>
       </c>
       <c r="E306" s="14" t="inlineStr">
@@ -7878,17 +7878,17 @@
       <c r="A307" s="4" t="n"/>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Blog: per-post OG image if different from hero (many posts can reuse hero as OG)</t>
-        </is>
-      </c>
-      <c r="C307" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>92 posts still need a real, unique hero image</t>
+        </is>
+      </c>
+      <c r="C307" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>Confirmed 2026-10-02: generateMetadata uses seo.ogImage, else the hero, else the default OG image.</t>
+          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
         </is>
       </c>
       <c r="E307" s="14" t="inlineStr">
@@ -7901,7 +7901,7 @@
       <c r="A308" s="4" t="n"/>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>Marketing pages</t>
+          <t>Blog: per-post OG image if different from hero (many posts can reuse hero as OG)</t>
         </is>
       </c>
       <c r="C308" s="13" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>hero/section images for /the-letter, /the-territory, /engine-room, /the-body, /the-nightstand, /recent-creations (portfolio thumbnails), /published (publication logos), /clients (client logos — confirm licensing before re-hosting). Checked against live 2026-10-02: same image count on every one; /the-territory, /engine-room, /recent-creations, /published, /clients have no images on live either.</t>
+          <t>Confirmed 2026-10-02: generateMetadata uses seo.ogImage, else the hero, else the default OG image.</t>
         </is>
       </c>
       <c r="E308" s="14" t="inlineStr">
@@ -7924,7 +7924,7 @@
       <c r="A309" s="4" t="n"/>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>/akbar essay images</t>
+          <t>Marketing pages</t>
         </is>
       </c>
       <c r="C309" s="13" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>not lost after all: 20 of the 21 were rescued into Sanity by scripts/rescue-manus-media.ts (2026-09-28) and are wired back in legacy's layout (hero mosaic, JC portrait, 2x2 grid, 3 full-bleeds, 3-up strip, footer gallery) as of 2026-09-29. Only slider-3 was gone (HTTP 502); the hero mosaic is 4 tiles instead of 5.</t>
+          <t>hero/section images for /the-letter, /the-territory, /engine-room, /the-body, /the-nightstand, /recent-creations (portfolio thumbnails), /published (publication logos), /clients (client logos — confirm licensing before re-hosting). Checked against live 2026-10-02: same image count on every one; /the-territory, /engine-room, /recent-creations, /published, /clients have no images on live either.</t>
         </is>
       </c>
       <c r="E309" s="14" t="inlineStr">
@@ -7947,7 +7947,7 @@
       <c r="A310" s="4" t="n"/>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>Rescued page images wired back in (2026-09-29)</t>
+          <t>/akbar essay images</t>
         </is>
       </c>
       <c r="C310" s="13" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>/living-declaration hero, hand image and Clarisse Abelarde artwork; /impact-dashboard earth hero; /find-my banner; /find-your-coffee dark photo landing (legacy copy restored, replacing an intro that wasn't in legacy). Also wired (second pass): /consciousness-scale (legacy's hero-first flow restored, the invented intro screen removed), /find-your-me hero, /humanos hero, the HumanOS nav logo, and all 12 HumanOS people headshots (/humanos/ecosystem, /humanos/philosophy). Blog-body images (2026-09-29): all 19 the migration dropped are restored by scripts/restore-blog-body-images.ts as Sanity drafts on 4 posts (Clarisse Abelarde 7, You Are the Moat 4, FRQNCY 6, Energy Is Money 2), waiting to be published in Studio; the other blog-listed assets were heroes already set. Still unwired from docs/ai/manus-media-rescue.md: and /alex-azzi's subject photo (a photo of a real person on an accusation page: needs Tony's yes first).</t>
+          <t>not lost after all: 20 of the 21 were rescued into Sanity by scripts/rescue-manus-media.ts (2026-09-28) and are wired back in legacy's layout (hero mosaic, JC portrait, 2x2 grid, 3 full-bleeds, 3-up strip, footer gallery) as of 2026-09-29. Only slider-3 was gone (HTTP 502); the hero mosaic is 4 tiles instead of 5.</t>
         </is>
       </c>
       <c r="E310" s="14" t="inlineStr">
@@ -7970,7 +7970,7 @@
       <c r="A311" s="4" t="n"/>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>BrewSoul: coffee/product images (brewsoul-coffees-expanded.ts likely has image refs</t>
+          <t>Rescued page images wired back in (2026-09-29)</t>
         </is>
       </c>
       <c r="C311" s="13" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>audit), city guide header images, roaster directory photos. Audited 2026-09-09 (status spreadsheet), confirmed 2026-10-02: city guides already have photos; coffees, chains and roasters have no image field in legacy or here (text-only by design); farms got real photos.</t>
+          <t>/living-declaration hero, hand image and Clarisse Abelarde artwork; /impact-dashboard earth hero; /find-my banner; /find-your-coffee dark photo landing (legacy copy restored, replacing an intro that wasn't in legacy). Also wired (second pass): /consciousness-scale (legacy's hero-first flow restored, the invented intro screen removed), /find-your-me hero, /humanos hero, the HumanOS nav logo, and all 12 HumanOS people headshots (/humanos/ecosystem, /humanos/philosophy). Blog-body images (2026-09-29): all 19 the migration dropped are restored by scripts/restore-blog-body-images.ts as Sanity drafts on 4 posts (Clarisse Abelarde 7, You Are the Moat 4, FRQNCY 6, Energy Is Money 2), waiting to be published in Studio; the other blog-listed assets were heroes already set. Still unwired from docs/ai/manus-media-rescue.md: and /alex-azzi's subject photo (a photo of a real person on an accusation page: needs Tony's yes first).</t>
         </is>
       </c>
       <c r="E311" s="14" t="inlineStr">
@@ -7993,7 +7993,7 @@
       <c r="A312" s="4" t="n"/>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>65 page images moved off the Manus storage copy into Sanity (2026-10-02)</t>
+          <t>BrewSoul: coffee/product images (brewsoul-coffees-expanded.ts likely has image refs</t>
         </is>
       </c>
       <c r="C312" s="13" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>every image the code loaded from d2xsxph8kpxj0f.cloudfront.net (PRI medicine images, Iboga module, facilitator index, /attention-theft, /alex-azzi, /protecting-your-business, /peyote-mescaline, HumanOS, the peptide quiz). Notes called it "RampRate's own CloudFront", but every file sits in the legacy Manus project's folder and its owner couldn't be confirmed. All 65 uploaded (scripts/rescue-cloudfront-images.ts), code rewritten, host removed from images.remotePatterns, no Sanity document used it. Table in docs/ai/manus-media-rescue.md.</t>
+          <t>audit), city guide header images, roaster directory photos. Audited 2026-09-09 (status spreadsheet), confirmed 2026-10-02: city guides already have photos; coffees, chains and roasters have no image field in legacy or here (text-only by design); farms got real photos.</t>
         </is>
       </c>
       <c r="E312" s="14" t="inlineStr">
@@ -8016,7 +8016,7 @@
       <c r="A313" s="4" t="n"/>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>PRI/Kava: medicine reference images (medicine-images.ts), facility images for /facilitator-index</t>
+          <t>65 page images moved off the Manus storage copy into Sanity (2026-10-02)</t>
         </is>
       </c>
       <c r="C313" s="13" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: all in Sanity; image counts match live on PRI, Kava, Iboga, Peyote, facilitator pages.</t>
+          <t>every image the code loaded from d2xsxph8kpxj0f.cloudfront.net (PRI medicine images, Iboga module, facilitator index, /attention-theft, /alex-azzi, /protecting-your-business, /peyote-mescaline, HumanOS, the peptide quiz). Notes called it "RampRate's own CloudFront", but every file sits in the legacy Manus project's folder and its owner couldn't be confirmed. All 65 uploaded (scripts/rescue-cloudfront-images.ts), code rewritten, host removed from images.remotePatterns, no Sanity document used it. Table in docs/ai/manus-media-rescue.md.</t>
         </is>
       </c>
       <c r="E313" s="14" t="inlineStr">
@@ -8039,7 +8039,7 @@
       <c r="A314" s="4" t="n"/>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>Manifesto/Attention Theft: any diagram/illustration assets used on the mega-page</t>
+          <t>PRI/Kava: medicine reference images (medicine-images.ts), facility images for /facilitator-index</t>
         </is>
       </c>
       <c r="C314" s="13" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: 6 of live's 7 are in (now in Sanity); the 7th belongs to the Wall of Shame section left out on purpose.</t>
+          <t>2026-10-02: all in Sanity; image counts match live on PRI, Kava, Iboga, Peyote, facilitator pages.</t>
         </is>
       </c>
       <c r="E314" s="14" t="inlineStr">
@@ -8062,17 +8062,17 @@
       <c r="A315" s="4" t="n"/>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
-        </is>
-      </c>
-      <c r="C315" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Manifesto/Attention Theft: any diagram/illustration assets used on the mega-page</t>
+        </is>
+      </c>
+      <c r="C315" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
+          <t>2026-10-02: 6 of live's 7 are in (now in Sanity); the 7th belongs to the Wall of Shame section left out on purpose.</t>
         </is>
       </c>
       <c r="E315" s="14" t="inlineStr">
@@ -8085,17 +8085,17 @@
       <c r="A316" s="4" t="n"/>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>Chatbot: FauxTony avatar/icon</t>
-        </is>
-      </c>
-      <c r="C316" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
+        </is>
+      </c>
+      <c r="C316" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
         <is>
-          <t>Not needed (2026-10-02): the chatbot phase (Phase 10) was cancelled.</t>
+          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
         </is>
       </c>
       <c r="E316" s="14" t="inlineStr">
@@ -8108,73 +8108,73 @@
       <c r="A317" s="4" t="n"/>
       <c r="B317" s="4" t="inlineStr">
         <is>
+          <t>Chatbot: FauxTony avatar/icon</t>
+        </is>
+      </c>
+      <c r="C317" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D317" s="4" t="inlineStr">
+        <is>
+          <t>Not needed (2026-10-02): the chatbot phase (Phase 10) was cancelled.</t>
+        </is>
+      </c>
+      <c r="E317" s="14" t="inlineStr">
+        <is>
+          <t>Phase 13 — Images Needed in Sanity</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="4" t="n"/>
+      <c r="B318" s="4" t="inlineStr">
+        <is>
           <t>Audit client/public/ (including alex-azzi/, brewsoul/ subfolders) for any static assets already sitting there unused that should be pulled i…</t>
         </is>
       </c>
-      <c r="C317" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D317" s="4" t="inlineStr">
+      <c r="C318" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D318" s="4" t="inlineStr">
         <is>
           <t>n rather than re-created. Done 2026-10-02: no images there at all (only llms.txt, a BrewSoul catalog, Manus debug files, design-options.html). Found and fixed a cutover risk instead: live serves two Google site-verification files (/google6881a0411c48b301.html, /alex-azzi/googleedff0185753a4a1f.html) that the new site returned 404 for, so Search Console could lose verification at DNS cutover. Both copied to public/ byte for byte. Not copied: site.webmanifest (its icons don't exist here; Next's app/icon.tsx covers the favicon).</t>
         </is>
       </c>
-      <c r="E317" s="14" t="inlineStr">
+      <c r="E318" s="14" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" s="10" t="inlineStr">
+    <row r="319">
+      <c r="A319" s="10" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
         </is>
       </c>
-      <c r="B318" s="11" t="n"/>
-      <c r="C318" s="11" t="n"/>
-      <c r="D318" s="12" t="n"/>
-    </row>
-    <row r="319">
-      <c r="A319" s="4" t="n"/>
-      <c r="B319" s="4" t="inlineStr">
-        <is>
-          <t>Mobile responsive pass on every ported section</t>
-        </is>
-      </c>
-      <c r="C319" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D319" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid).</t>
-        </is>
-      </c>
-      <c r="E319" s="14" t="inlineStr">
-        <is>
-          <t>Phase 14 — QA &amp; Launch</t>
-        </is>
-      </c>
+      <c r="B319" s="11" t="n"/>
+      <c r="C319" s="11" t="n"/>
+      <c r="D319" s="12" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="4" t="n"/>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>Accessibility pass (WCAG AA contrast, 44px touch targets, keyboard nav)</t>
-        </is>
-      </c>
-      <c r="C320" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Mobile responsive pass on every ported section</t>
+        </is>
+      </c>
+      <c r="C320" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy QA_MASTER_PROMPT.md. 2026-09-29 axe-core pass (WCAG 2.1 AA, same 114 pages, production build): all unlabeled dropdowns/inputs and unnamed links fixed; contrast down from 1,453 failing items on 106 pages to 1,038 on 70 (43 pages fully clean). Shared fixes: brand gold #8b6914 → #836311 site-wide (was 4.3:1 on cream, AA needs 4.5), header "⌘K"/social icons, BrewSoul nav and footer, HumanOS footer, Kava footer, assessment intro footnote, post-card image links. 2026-09-30: contrast finished, 0 axe color-contrast failures left on the same 114 pages (production build). Token changes: --kava-saffron #b86a28 → #8e521f, --pri-purple-light #a855f7 → #b87bf9 (on-dark purple only), --crusade-teal #0e7c7c → #0d7373; PriEyebrow goes light purple inside a dark PriSection via group-data-dark/pri; /find-your-me and the journey tracker's dark glass panels 60-70% → 90% (legacy's own 60% glass on beige rendered gray, cream text failed). Everything else: nearest passing shade of the same hue, or gold ↔ gold-light on the wrong background. Left: 18 links inside text marked only by color (need an underline), 44px tap targets, keyboard nav. 2026-09-30: 18 color-only in-text links underlined (axe link-in-text-block: 0 left); keyboard focus visible on every focusable item on 8 sampled pages (two form fields had none, fixed). 2026-10-02 re-run (axe WCAG 2.2 AA, 142 pages × 375/1280px, production build, plus Tab through 40 stops per page): found 1,370 contrast failures (mostly BrewSoul'</t>
+          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid).</t>
         </is>
       </c>
       <c r="E320" s="14" t="inlineStr">
@@ -8187,17 +8187,17 @@
       <c r="A321" s="4" t="n"/>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>No dead-end pages (every page links to 2+ others)</t>
-        </is>
-      </c>
-      <c r="C321" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Accessibility pass (WCAG AA contrast, 44px touch targets, keyboard nav)</t>
+        </is>
+      </c>
+      <c r="C321" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
+          <t>same bar as legacy QA_MASTER_PROMPT.md. 2026-09-29 axe-core pass (WCAG 2.1 AA, same 114 pages, production build): all unlabeled dropdowns/inputs and unnamed links fixed; contrast down from 1,453 failing items on 106 pages to 1,038 on 70 (43 pages fully clean). Shared fixes: brand gold #8b6914 → #836311 site-wide (was 4.3:1 on cream, AA needs 4.5), header "⌘K"/social icons, BrewSoul nav and footer, HumanOS footer, Kava footer, assessment intro footnote, post-card image links. 2026-09-30: contrast finished, 0 axe color-contrast failures left on the same 114 pages (production build). Token changes: --kava-saffron #b86a28 → #8e521f, --pri-purple-light #a855f7 → #b87bf9 (on-dark purple only), --crusade-teal #0e7c7c → #0d7373; PriEyebrow goes light purple inside a dark PriSection via group-data-dark/pri; /find-your-me and the journey tracker's dark glass panels 60-70% → 90% (legacy's own 60% glass on beige rendered gray, cream text failed). Everything else: nearest passing shade of the same hue, or gold ↔ gold-light on the wrong background. Left: 18 links inside text marked only by color (need an underline), 44px tap targets, keyboard nav. 2026-09-30: 18 color-only in-text links underlined (axe link-in-text-block: 0 left); keyboard focus visible on every focusable item on 8 sampled pages (two form fields had none, fixed). 2026-10-02 re-run (axe WCAG 2.2 AA, 142 pages × 375/1280px, production build, plus Tab through 40 stops per page): found 1,370 contrast failures (mostly BrewSoul'</t>
         </is>
       </c>
       <c r="E321" s="14" t="inlineStr">
@@ -8210,7 +8210,7 @@
       <c r="A322" s="4" t="n"/>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
+          <t>No dead-end pages (every page links to 2+ others)</t>
         </is>
       </c>
       <c r="C322" s="15" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
+          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
         </is>
       </c>
       <c r="E322" s="14" t="inlineStr">
@@ -8233,7 +8233,7 @@
       <c r="A323" s="4" t="n"/>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>Remove noindex only when sign-off is given</t>
+          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
         </is>
       </c>
       <c r="C323" s="15" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
         </is>
       </c>
       <c r="E323" s="14" t="inlineStr">
@@ -8256,7 +8256,7 @@
       <c r="A324" s="4" t="n"/>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
+          <t>Remove noindex only when sign-off is given</t>
         </is>
       </c>
       <c r="C324" s="15" t="inlineStr">
@@ -8264,7 +8264,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D324" s="4" t="inlineStr"/>
+      <c r="D324" s="4" t="inlineStr">
+        <is>
+          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+        </is>
+      </c>
       <c r="E324" s="14" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
@@ -8275,7 +8279,7 @@
       <c r="A325" s="4" t="n"/>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
         </is>
       </c>
       <c r="C325" s="15" t="inlineStr">
@@ -8290,23 +8294,42 @@
         </is>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" s="4" t="n"/>
+      <c r="B326" s="4" t="inlineStr">
+        <is>
+          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+        </is>
+      </c>
+      <c r="C326" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D326" s="4" t="inlineStr"/>
+      <c r="E326" s="14" t="inlineStr">
+        <is>
+          <t>Phase 14 — QA &amp; Launch</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D325"/>
+  <autoFilter ref="A1:D326"/>
   <mergeCells count="14">
     <mergeCell ref="A150:D150"/>
     <mergeCell ref="A237:D237"/>
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A258:D258"/>
+    <mergeCell ref="A319:D319"/>
     <mergeCell ref="A209:D209"/>
     <mergeCell ref="A205:D205"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A318:D318"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A299:D299"/>
     <mergeCell ref="A183:D183"/>
     <mergeCell ref="A32:D32"/>
     <mergeCell ref="A123:D123"/>
-    <mergeCell ref="A298:D298"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Migration-Status-Report.xlsx
+++ b/Migration-Status-Report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Remaining Work" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$326</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$327</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Remaining Work'!$A$1:$D$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -639,15 +639,15 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A5,'Full Detail'!$C$2:$C$326,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A5,'Full Detail'!$C$2:$C$327,"Done")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A5,'Full Detail'!$C$2:$C$326,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A5,'Full Detail'!$C$2:$C$327,"Remaining")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A5,'Full Detail'!$C$2:$C$326,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A5,'Full Detail'!$C$2:$C$327,"Deferred")</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -666,15 +666,15 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A6,'Full Detail'!$C$2:$C$326,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A6,'Full Detail'!$C$2:$C$327,"Done")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A6,'Full Detail'!$C$2:$C$326,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A6,'Full Detail'!$C$2:$C$327,"Remaining")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A6,'Full Detail'!$C$2:$C$326,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A6,'Full Detail'!$C$2:$C$327,"Deferred")</f>
         <v/>
       </c>
       <c r="E6" s="5">
@@ -693,15 +693,15 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A7,'Full Detail'!$C$2:$C$326,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A7,'Full Detail'!$C$2:$C$327,"Done")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A7,'Full Detail'!$C$2:$C$326,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A7,'Full Detail'!$C$2:$C$327,"Remaining")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A7,'Full Detail'!$C$2:$C$326,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A7,'Full Detail'!$C$2:$C$327,"Deferred")</f>
         <v/>
       </c>
       <c r="E7" s="5">
@@ -720,15 +720,15 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A8,'Full Detail'!$C$2:$C$326,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A8,'Full Detail'!$C$2:$C$327,"Done")</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A8,'Full Detail'!$C$2:$C$326,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A8,'Full Detail'!$C$2:$C$327,"Remaining")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A8,'Full Detail'!$C$2:$C$326,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A8,'Full Detail'!$C$2:$C$327,"Deferred")</f>
         <v/>
       </c>
       <c r="E8" s="5">
@@ -747,15 +747,15 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A9,'Full Detail'!$C$2:$C$326,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A9,'Full Detail'!$C$2:$C$327,"Done")</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A9,'Full Detail'!$C$2:$C$326,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A9,'Full Detail'!$C$2:$C$327,"Remaining")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A9,'Full Detail'!$C$2:$C$326,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A9,'Full Detail'!$C$2:$C$327,"Deferred")</f>
         <v/>
       </c>
       <c r="E9" s="5">
@@ -774,15 +774,15 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A10,'Full Detail'!$C$2:$C$326,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A10,'Full Detail'!$C$2:$C$327,"Done")</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A10,'Full Detail'!$C$2:$C$326,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A10,'Full Detail'!$C$2:$C$327,"Remaining")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A10,'Full Detail'!$C$2:$C$326,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A10,'Full Detail'!$C$2:$C$327,"Deferred")</f>
         <v/>
       </c>
       <c r="E10" s="5">
@@ -801,15 +801,15 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A11,'Full Detail'!$C$2:$C$326,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A11,'Full Detail'!$C$2:$C$327,"Done")</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A11,'Full Detail'!$C$2:$C$326,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A11,'Full Detail'!$C$2:$C$327,"Remaining")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A11,'Full Detail'!$C$2:$C$326,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A11,'Full Detail'!$C$2:$C$327,"Deferred")</f>
         <v/>
       </c>
       <c r="E11" s="5">
@@ -828,15 +828,15 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A12,'Full Detail'!$C$2:$C$326,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A12,'Full Detail'!$C$2:$C$327,"Done")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A12,'Full Detail'!$C$2:$C$326,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A12,'Full Detail'!$C$2:$C$327,"Remaining")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A12,'Full Detail'!$C$2:$C$326,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A12,'Full Detail'!$C$2:$C$327,"Deferred")</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -855,15 +855,15 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A13,'Full Detail'!$C$2:$C$326,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A13,'Full Detail'!$C$2:$C$327,"Done")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A13,'Full Detail'!$C$2:$C$326,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A13,'Full Detail'!$C$2:$C$327,"Remaining")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A13,'Full Detail'!$C$2:$C$326,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A13,'Full Detail'!$C$2:$C$327,"Deferred")</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -882,15 +882,15 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A14,'Full Detail'!$C$2:$C$326,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A14,'Full Detail'!$C$2:$C$327,"Done")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A14,'Full Detail'!$C$2:$C$326,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A14,'Full Detail'!$C$2:$C$327,"Remaining")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A14,'Full Detail'!$C$2:$C$326,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A14,'Full Detail'!$C$2:$C$327,"Deferred")</f>
         <v/>
       </c>
       <c r="E14" s="5">
@@ -909,15 +909,15 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A15,'Full Detail'!$C$2:$C$326,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A15,'Full Detail'!$C$2:$C$327,"Done")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A15,'Full Detail'!$C$2:$C$326,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A15,'Full Detail'!$C$2:$C$327,"Remaining")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A15,'Full Detail'!$C$2:$C$326,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A15,'Full Detail'!$C$2:$C$327,"Deferred")</f>
         <v/>
       </c>
       <c r="E15" s="5">
@@ -936,15 +936,15 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A16,'Full Detail'!$C$2:$C$326,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A16,'Full Detail'!$C$2:$C$327,"Done")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A16,'Full Detail'!$C$2:$C$326,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A16,'Full Detail'!$C$2:$C$327,"Remaining")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A16,'Full Detail'!$C$2:$C$326,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A16,'Full Detail'!$C$2:$C$327,"Deferred")</f>
         <v/>
       </c>
       <c r="E16" s="5">
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A17,'Full Detail'!$C$2:$C$326,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A17,'Full Detail'!$C$2:$C$327,"Done")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A17,'Full Detail'!$C$2:$C$326,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A17,'Full Detail'!$C$2:$C$327,"Remaining")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A17,'Full Detail'!$C$2:$C$326,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A17,'Full Detail'!$C$2:$C$327,"Deferred")</f>
         <v/>
       </c>
       <c r="E17" s="5">
@@ -990,15 +990,15 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A18,'Full Detail'!$C$2:$C$326,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A18,'Full Detail'!$C$2:$C$327,"Done")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A18,'Full Detail'!$C$2:$C$326,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A18,'Full Detail'!$C$2:$C$327,"Remaining")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A18,'Full Detail'!$C$2:$C$326,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A18,'Full Detail'!$C$2:$C$327,"Deferred")</f>
         <v/>
       </c>
       <c r="E18" s="5">
@@ -1017,15 +1017,15 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A19,'Full Detail'!$C$2:$C$326,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A19,'Full Detail'!$C$2:$C$327,"Done")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A19,'Full Detail'!$C$2:$C$326,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A19,'Full Detail'!$C$2:$C$327,"Remaining")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$326,$A19,'Full Detail'!$C$2:$C$326,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A19,'Full Detail'!$C$2:$C$327,"Deferred")</f>
         <v/>
       </c>
       <c r="E19" s="5">
@@ -1075,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E326"/>
+  <dimension ref="A1:E327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7366,7 +7366,7 @@
       <c r="A284" s="4" t="n"/>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>Error pages (2026-10-09, owner asked)</t>
+          <t>Category pages pre-built (2026-10-09)</t>
         </is>
       </c>
       <c r="C284" s="13" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>404 page now sets its own title ("Page not found") as a server page around live's 3-second redirect (not-found.tsx + components/not-found-redirect.tsx), arrow as an icon; page error screen (error.tsx) uses Next 16's retry (re-fetches), shows a reference code for the server logs, links home and to the site index; new global-error.tsx for failures in the root layout itself (own &lt;html&gt;, plain links). Verified on a production build: missing page, missing essay and missing Kava page return 404 with the right title; a test page that throws returns 500 with the error screen, "Try again" re-fetches; phone and laptop, no sideways scroll (test page removed).</t>
+          <t>/blog/category/[slug] read ?page=N, so every category page was rendered on each request (slower first byte, flagged in the Lighthouse notes). Page numbers are now part of the address (/blog/category/&lt;slug&gt;/page/&lt;n&gt;, generateStaticParams, dynamicParams = false), shared code in src/components/blog/category-listing.tsx; old ?page=N links 308 to the new address (pages 2+ only, so no loop), /page/1 308s to the plain address, a page past the end is a 404; "All essays" back link uses an icon. Verified on a production build: route table shows every category page as pre-built (9 page-1s, 7 later pages), titles and canonicals per page, Previous/Next links, the redirects and the 404s.</t>
         </is>
       </c>
       <c r="E284" s="14" t="inlineStr">
@@ -7389,7 +7389,7 @@
       <c r="A285" s="4" t="n"/>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>SEO audit fixes (2026-10-06)</t>
+          <t>Error pages (2026-10-09, owner asked)</t>
         </is>
       </c>
       <c r="C285" s="13" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
+          <t>404 page now sets its own title ("Page not found") as a server page around live's 3-second redirect (not-found.tsx + components/not-found-redirect.tsx), arrow as an icon; page error screen (error.tsx) uses Next 16's retry (re-fetches), shows a reference code for the server logs, links home and to the site index; new global-error.tsx for failures in the root layout itself (own &lt;html&gt;, plain links). Verified on a production build: missing page, missing essay and missing Kava page return 404 with the right title; a test page that throws returns 500 with the error screen, "Try again" re-fetches; phone and laptop, no sideways scroll (test page removed).</t>
         </is>
       </c>
       <c r="E285" s="14" t="inlineStr">
@@ -7412,17 +7412,17 @@
       <c r="A286" s="4" t="n"/>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>SEO audit items needing a yes (2026-10-06)</t>
-        </is>
-      </c>
-      <c r="C286" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>SEO audit fixes (2026-10-06)</t>
+        </is>
+      </c>
+      <c r="C286" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+          <t>Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
         </is>
       </c>
       <c r="E286" s="14" t="inlineStr">
@@ -7435,7 +7435,7 @@
       <c r="A287" s="4" t="n"/>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+          <t>SEO audit items needing a yes (2026-10-06)</t>
         </is>
       </c>
       <c r="C287" s="15" t="inlineStr">
@@ -7443,7 +7443,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D287" s="4" t="inlineStr"/>
+      <c r="D287" s="4" t="inlineStr">
+        <is>
+          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+        </is>
+      </c>
       <c r="E287" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -7454,19 +7458,15 @@
       <c r="A288" s="4" t="n"/>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
-        </is>
-      </c>
-      <c r="C288" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D288" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
-        </is>
-      </c>
+          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+        </is>
+      </c>
+      <c r="C288" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D288" s="4" t="inlineStr"/>
       <c r="E288" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -7477,7 +7477,7 @@
       <c r="A289" s="4" t="n"/>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>"Keep going" strip above the footer on every page (2026-10-07)</t>
+          <t>Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
         </is>
       </c>
       <c r="C289" s="13" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>legacy's WhereNext (deferred in Phase 3, never picked up) with its per-page suggestions, Home · Site Index · All Assessments; links pointed at current routes.</t>
+          <t>2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
         </is>
       </c>
       <c r="E289" s="14" t="inlineStr">
@@ -7500,7 +7500,7 @@
       <c r="A290" s="4" t="n"/>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>Live-only and redesigned pages from the 2026-10-07 page sweep (188 pages compared with live)</t>
+          <t>"Keep going" strip above the footer on every page (2026-10-07)</t>
         </is>
       </c>
       <c r="C290" s="13" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>/the-index rebuilt from live's code (20 concepts, related-word search across essays and site pages, full-text search on the server, "three related places to go next"; the old redirect to /search removed and its links, including the "Site Index" link in "Keep going", point at it again); /the-mirror (and /life-assessment) opens on live's intro (dark hero, "What We Measure" with the six areas, "The Ecosystem"), rebuilt as a step registry (rule 19); /essays header, order and column like live; /about "What They Say" styled like live (live picks 3 of the same 19 quotes at random; ours shows a fixed 3 so they're in the server HTML); /impact-futurism list titles and subtitles; /supplier-intake is a real page again with live's Stage 1 form; /seven-doors and /projects redirect home like live; /impact, /health, /library, /built-on-manus, /heroes are 404 on live too. Left as is on purpose: /blog stays our archive page (on live it repeats the homepage), the email gates on /framework and /peptide-supply-chain, the attention-theft Wall of Shame.</t>
+          <t>legacy's WhereNext (deferred in Phase 3, never picked up) with its per-page suggestions, Home · Site Index · All Assessments; links pointed at current routes.</t>
         </is>
       </c>
       <c r="E290" s="14" t="inlineStr">
@@ -7523,7 +7523,7 @@
       <c r="A291" s="4" t="n"/>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>/alex-azzi locked like live (2026-10-07, owner said match it)</t>
+          <t>Live-only and redesigned pages from the 2026-10-07 page sweep (188 pages compared with live)</t>
         </is>
       </c>
       <c r="C291" s="13" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>same server-checked password as the locked essay (GATED_POST_PASSWORD, now also set in Netlify), live's "Restricted Access" screen, the report not in the page until unlocked, out of search and the sitemap.</t>
+          <t>/the-index rebuilt from live's code (20 concepts, related-word search across essays and site pages, full-text search on the server, "three related places to go next"; the old redirect to /search removed and its links, including the "Site Index" link in "Keep going", point at it again); /the-mirror (and /life-assessment) opens on live's intro (dark hero, "What We Measure" with the six areas, "The Ecosystem"), rebuilt as a step registry (rule 19); /essays header, order and column like live; /about "What They Say" styled like live (live picks 3 of the same 19 quotes at random; ours shows a fixed 3 so they're in the server HTML); /impact-futurism list titles and subtitles; /supplier-intake is a real page again with live's Stage 1 form; /seven-doors and /projects redirect home like live; /impact, /health, /library, /built-on-manus, /heroes are 404 on live too. Left as is on purpose: /blog stays our archive page (on live it repeats the homepage), the email gates on /framework and /peptide-supply-chain, the attention-theft Wall of Shame.</t>
         </is>
       </c>
       <c r="E291" s="14" t="inlineStr">
@@ -7546,7 +7546,7 @@
       <c r="A292" s="4" t="n"/>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>Live's title fonts and sizes (2026-10-07, "fix the style")</t>
+          <t>/alex-azzi locked like live (2026-10-07, owner said match it)</t>
         </is>
       </c>
       <c r="C292" s="13" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>measured every page's title font, weight, size and label colour on live vs ours (136 pages). Now like live: Kava headings in Fraunces, HumanOS in Space Grotesk, the peptide tools / charity scorecard / thesis threads in the system serif, America Unbundled in the Iowan Old Style stack at live's size, /akbar in Fraunces 900, friend-gate and post-intervention in Georgia, and live's title sizes on peptide-matrix, peptide-supply-chain, rip-peptide-sciences and the HumanOS pages. Fonts load only on the pages that use them (src/lib/fonts/page-fonts.ts). Label colours stay the darker AA-contrast versions where live's lighter ones fail on a light background.</t>
+          <t>same server-checked password as the locked essay (GATED_POST_PASSWORD, now also set in Netlify), live's "Restricted Access" screen, the report not in the page until unlocked, out of search and the sitemap.</t>
         </is>
       </c>
       <c r="E292" s="14" t="inlineStr">
@@ -7569,7 +7569,7 @@
       <c r="A293" s="4" t="n"/>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Peptide page images rescued into Sanity and wired (2026-10-07)</t>
+          <t>Live's title fonts and sizes (2026-10-07, "fix the style")</t>
         </is>
       </c>
       <c r="C293" s="13" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>/peptide-watch hero plus its 11 section banners, /peptide-matrix and /peptide-supply-chain heroes, the /peptide-hall-of-shame hero (scripts/rescue-2026-10-07-peptide-images.ts, logged in docs/ai/manus-media-rescue.md).</t>
+          <t>measured every page's title font, weight, size and label colour on live vs ours (136 pages). Now like live: Kava headings in Fraunces, HumanOS in Space Grotesk, the peptide tools / charity scorecard / thesis threads in the system serif, America Unbundled in the Iowan Old Style stack at live's size, /akbar in Fraunces 900, friend-gate and post-intervention in Georgia, and live's title sizes on peptide-matrix, peptide-supply-chain, rip-peptide-sciences and the HumanOS pages. Fonts load only on the pages that use them (src/lib/fonts/page-fonts.ts). Label colours stay the darker AA-contrast versions where live's lighter ones fail on a light background.</t>
         </is>
       </c>
       <c r="E293" s="14" t="inlineStr">
@@ -7592,7 +7592,7 @@
       <c r="A294" s="4" t="n"/>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Live's editorial redesign, first group (2026-10-07)</t>
+          <t>Peptide page images rescued into Sanity and wired (2026-10-07)</t>
         </is>
       </c>
       <c r="C294" s="13" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
+          <t>/peptide-watch hero plus its 11 section banners, /peptide-matrix and /peptide-supply-chain heroes, the /peptide-hall-of-shame hero (scripts/rescue-2026-10-07-peptide-images.ts, logged in docs/ai/manus-media-rescue.md).</t>
         </is>
       </c>
       <c r="E294" s="14" t="inlineStr">
@@ -7615,7 +7615,7 @@
       <c r="A295" s="4" t="n"/>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Live's redesign, second group (done 2026-10-08)</t>
+          <t>Live's editorial redesign, first group (2026-10-07)</t>
         </is>
       </c>
       <c r="C295" s="13" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>re-measured all 18 pages on live vs a fresh production build (title font/size/weight/colour, labels, hero images). Already matching from 2026-10-07: /the-web, /spirits, /iboga-ibogaine (weight 800), /living-declaration, BrewSoul photo on /brewsoul, /brewsoul/browse, /brewsoul/first-sip (live has none there either), /quiz_25q, /recent-creations. Fixed today: /find-your-journey (64px title, red label), /impact-dashboard (64px title in essay ink, label spacing), red labels on /published and /speaking (plus its "rooms" chips), /soulscore "by ImpactSoul" label, /pri-calibration title (weight 900, solid cream, was a purple gradient), /clients (live's narrow 546px column for the whole page, 56px title, roomier stats band, cards 2 per row; two static inline styles moved to classes), /brewsoul/guest (live's BrewSoul photo on the guest card instead of "SN" initials, labels in capitals), /humanos/connect (cards line up with the title), /peptide-hall-of-shame (stats and label readable light gold; were dark gold on dark). Typed arrows on the touched links are icons now (rule 18). Deliberately not copied from live (new CONTRIBUTING rule 20, owner 2026-10-08): red labels on dark bands use #E07A80 (live's #8E1E25 on black is about 2:1, unreadable); /recent-creations keeps our darker label colours (live's fail contrast on white); /humanos/connect keeps "Start Reading" (that card links to the philosophy page, the quiz live's "Start the Assessment" implies doesn't exist). Checked: type check, l</t>
+          <t>dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
         </is>
       </c>
       <c r="E295" s="14" t="inlineStr">
@@ -7638,7 +7638,7 @@
       <c r="A296" s="4" t="n"/>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>BrewSoul top of page (2026-10-08, owner: "button in the center at the top doesn't look good")</t>
+          <t>Live's redesign, second group (done 2026-10-08)</t>
         </is>
       </c>
       <c r="C296" s="13" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>the category badge ("Deep Research" etc.) sat centred in an empty strip, squeezed against the hero, because we copied live's doubled 52px top gap. Now one gap everywhere and the badge floats in the top-left corner, lined up with the BrewSoul logo (brewsoul-main.tsx, category-badge.tsx); checked on all 26 badge pages at 3 widths that it covers nothing. BrewSoul menu: on tablets (768-1023px) the links were cut off and "More" was hidden with no menu button at all; now the menu button shows below 1024px, 5 links + "More" from 1024px, all 8 from 1280px, "More" always visible.</t>
+          <t>re-measured all 18 pages on live vs a fresh production build (title font/size/weight/colour, labels, hero images). Already matching from 2026-10-07: /the-web, /spirits, /iboga-ibogaine (weight 800), /living-declaration, BrewSoul photo on /brewsoul, /brewsoul/browse, /brewsoul/first-sip (live has none there either), /quiz_25q, /recent-creations. Fixed today: /find-your-journey (64px title, red label), /impact-dashboard (64px title in essay ink, label spacing), red labels on /published and /speaking (plus its "rooms" chips), /soulscore "by ImpactSoul" label, /pri-calibration title (weight 900, solid cream, was a purple gradient), /clients (live's narrow 546px column for the whole page, 56px title, roomier stats band, cards 2 per row; two static inline styles moved to classes), /brewsoul/guest (live's BrewSoul photo on the guest card instead of "SN" initials, labels in capitals), /humanos/connect (cards line up with the title), /peptide-hall-of-shame (stats and label readable light gold; were dark gold on dark). Typed arrows on the touched links are icons now (rule 18). Deliberately not copied from live (new CONTRIBUTING rule 20, owner 2026-10-08): red labels on dark bands use #E07A80 (live's #8E1E25 on black is about 2:1, unreadable); /recent-creations keeps our darker label colours (live's fail contrast on white); /humanos/connect keeps "Start Reading" (that card links to the philosophy page, the quiz live's "Start the Assessment" implies doesn't exist). Checked: type check, l</t>
         </is>
       </c>
       <c r="E296" s="14" t="inlineStr">
@@ -7661,7 +7661,7 @@
       <c r="A297" s="4" t="n"/>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>/pri-efficacy's "Simulation / Live Calibrations" switch like live (2026-10-08)</t>
+          <t>BrewSoul top of page (2026-10-08, owner: "button in the center at the top doesn't look good")</t>
         </is>
       </c>
       <c r="C297" s="13" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>shadcn Tabs, both panels in the server HTML (forceMount). The Live tab reads real aggregate numbers from pri_calibrations (getPriLiveStats() in src/lib/pri-research.ts: totals, opt-ins, average score per dimension; no rows leave the server), page stays static and refreshes every 10 minutes. Until the Supabase scripts are run (Phase 2) it says the numbers "aren't available just now" instead of a fake zero. Checked: build (○, 10m), server HTML has both tabs, tab switch at 390/1280px, no JS errors. Re-check with real numbers once the table exists.</t>
+          <t>the category badge ("Deep Research" etc.) sat centred in an empty strip, squeezed against the hero, because we copied live's doubled 52px top gap. Now one gap everywhere and the badge floats in the top-left corner, lined up with the BrewSoul logo (brewsoul-main.tsx, category-badge.tsx); checked on all 26 badge pages at 3 widths that it covers nothing. BrewSoul menu: on tablets (768-1023px) the links were cut off and "More" was hidden with no menu button at all; now the menu button shows below 1024px, 5 links + "More" from 1024px, all 8 from 1280px, "More" always visible.</t>
         </is>
       </c>
       <c r="E297" s="14" t="inlineStr">
@@ -7684,63 +7684,63 @@
       <c r="A298" s="4" t="n"/>
       <c r="B298" s="4" t="inlineStr">
         <is>
+          <t>/pri-efficacy's "Simulation / Live Calibrations" switch like live (2026-10-08)</t>
+        </is>
+      </c>
+      <c r="C298" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D298" s="4" t="inlineStr">
+        <is>
+          <t>shadcn Tabs, both panels in the server HTML (forceMount). The Live tab reads real aggregate numbers from pri_calibrations (getPriLiveStats() in src/lib/pri-research.ts: totals, opt-ins, average score per dimension; no rows leave the server), page stays static and refreshes every 10 minutes. Until the Supabase scripts are run (Phase 2) it says the numbers "aren't available just now" instead of a fake zero. Checked: build (○, 10m), server HTML has both tabs, tab switch at 390/1280px, no JS errors. Re-check with real numbers once the table exists.</t>
+        </is>
+      </c>
+      <c r="E298" s="14" t="inlineStr">
+        <is>
+          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="4" t="n"/>
+      <c r="B299" s="4" t="inlineStr">
+        <is>
           <t>/brewsoul/browse hero readable (2026-10-08, owner said go ahead)</t>
         </is>
       </c>
-      <c r="C298" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D298" s="4" t="inlineStr">
+      <c r="C299" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D299" s="4" t="inlineStr">
         <is>
           <t>a soft cream glow behind the title block so "The Catalog", the subtitle and the stat labels read clearly over the coffee photo (live is hard to read there too; rule 20). Photo still shows around the edges. Checked at 390/1280px.</t>
         </is>
       </c>
-      <c r="E298" s="14" t="inlineStr">
+      <c r="E299" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
         </is>
       </c>
     </row>
-    <row r="299">
-      <c r="A299" s="10" t="inlineStr">
+    <row r="300">
+      <c r="A300" s="10" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
-      <c r="B299" s="11" t="n"/>
-      <c r="C299" s="11" t="n"/>
-      <c r="D299" s="12" t="n"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="4" t="n"/>
-      <c r="B300" s="4" t="inlineStr">
-        <is>
-          <t>Manus media rescue (2026-09-29)</t>
-        </is>
-      </c>
-      <c r="C300" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D300" s="4" t="inlineStr">
-        <is>
-          <t>all 94 Manus-hosted image/video references in the legacy source (/api/img/, /manus-storage/) were checked live. 91 were still downloadable, including the /akbar photos the entry below calls "permanently lost", and all 91 are now Sanity assets (scripts/rescue-manus-media.ts; Sanity dedupes by SHA-1). 3 were gone (HTTP 502). The manifest docs/ai/manus-media-rescue.md maps each one to the legacy files that used it and its Sanity URL. They are not wired into pages yet: go page by page, with real alt text. /facilitator-index's two diagrams are done (scripts/rescue-facilitator-images.ts).</t>
-        </is>
-      </c>
-      <c r="E300" s="14" t="inlineStr">
-        <is>
-          <t>Phase 13 — Images Needed in Sanity</t>
-        </is>
-      </c>
+      <c r="B300" s="11" t="n"/>
+      <c r="C300" s="11" t="n"/>
+      <c r="D300" s="12" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="4" t="n"/>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Favicon</t>
+          <t>Manus media rescue (2026-09-29)</t>
         </is>
       </c>
       <c r="C301" s="13" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>real "G" brand mark generated from the header's actual wordmark treatment (src/app/icon.tsx), see Phase 3</t>
+          <t>all 94 Manus-hosted image/video references in the legacy source (/api/img/, /manus-storage/) were checked live. 91 were still downloadable, including the /akbar photos the entry below calls "permanently lost", and all 91 are now Sanity assets (scripts/rescue-manus-media.ts; Sanity dedupes by SHA-1). 3 were gone (HTTP 502). The manifest docs/ai/manus-media-rescue.md maps each one to the legacy files that used it and its Sanity URL. They are not wired into pages yet: go page by page, with real alt text. /facilitator-index's two diagrams are done (scripts/rescue-facilitator-images.ts).</t>
         </is>
       </c>
       <c r="E301" s="14" t="inlineStr">
@@ -7763,17 +7763,17 @@
       <c r="A302" s="4" t="n"/>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
-        </is>
-      </c>
-      <c r="C302" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Favicon</t>
+        </is>
+      </c>
+      <c r="C302" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
+          <t>real "G" brand mark generated from the header's actual wordmark treatment (src/app/icon.tsx), see Phase 3</t>
         </is>
       </c>
       <c r="E302" s="14" t="inlineStr">
@@ -7786,17 +7786,17 @@
       <c r="A303" s="4" t="n"/>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Author photo(s) for blog author schema (Tony Greenberg headshot at minimum)</t>
-        </is>
-      </c>
-      <c r="C303" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
+        </is>
+      </c>
+      <c r="C303" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: the rescued headshot is already the author avatar in Sanity; now also in every post's Article JSON-LD (author image + url /about). The JSON-LD publisher logo pointed at /favicon.ico, a 404 here; now /icon.</t>
+          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
         </is>
       </c>
       <c r="E303" s="14" t="inlineStr">
@@ -7809,7 +7809,7 @@
       <c r="A304" s="4" t="n"/>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>Blog hero images</t>
+          <t>Author photo(s) for blog author schema (Tony Greenberg headshot at minimum)</t>
         </is>
       </c>
       <c r="C304" s="13" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>audited, then migrated. Final state:</t>
+          <t>2026-10-02: the rescued headshot is already the author avatar in Sanity; now also in every post's Article JSON-LD (author image + url /about). The JSON-LD publisher logo pointed at /favicon.ico, a 404 here; now /icon.</t>
         </is>
       </c>
       <c r="E304" s="14" t="inlineStr">
@@ -7832,7 +7832,7 @@
       <c r="A305" s="4" t="n"/>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>22 posts have a real hero image, now live in Sanity (17 already on RampRate's own CloudFront + 4 rescued from the legacy /api/img/ proxy + 1…</t>
+          <t>Blog hero images</t>
         </is>
       </c>
       <c r="C305" s="13" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> rescued from /manus-storage/, all pulled over by migrate-blog-posts.ts before Manus is decommissioned)</t>
+          <t>audited, then migrated. Final state:</t>
         </is>
       </c>
       <c r="E305" s="14" t="inlineStr">
@@ -7855,7 +7855,7 @@
       <c r="A306" s="4" t="n"/>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>7 more posts got a real, unique hero image rescued from the live legacy site's newly-added art this pass (scripts/rescue-2026-09-blog-images…</t>
+          <t>22 posts have a real hero image, now live in Sanity (17 already on RampRate's own CloudFront + 4 rescued from the legacy /api/img/ proxy + 1…</t>
         </is>
       </c>
       <c r="C306" s="13" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>.ts — see the correction note above): california-toll-roads-legalized-scam, the-1000-hour-hold, conscious-capital-partnership-ecosystem, the-peptide-truth-65m-fraud-industry-vs-life-changing-medicine, clear-communication, building-services-market-transhuman-era, heart-protocol-addendum.</t>
+          <t xml:space="preserve"> rescued from /manus-storage/, all pulled over by migrate-blog-posts.ts before Manus is decommissioned)</t>
         </is>
       </c>
       <c r="E306" s="14" t="inlineStr">
@@ -7878,17 +7878,17 @@
       <c r="A307" s="4" t="n"/>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>92 posts still need a real, unique hero image</t>
-        </is>
-      </c>
-      <c r="C307" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>7 more posts got a real, unique hero image rescued from the live legacy site's newly-added art this pass (scripts/rescue-2026-09-blog-images…</t>
+        </is>
+      </c>
+      <c r="C307" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
+          <t>.ts — see the correction note above): california-toll-roads-legalized-scam, the-1000-hour-hold, conscious-capital-partnership-ecosystem, the-peptide-truth-65m-fraud-industry-vs-life-changing-medicine, clear-communication, building-services-market-transhuman-era, heart-protocol-addendum.</t>
         </is>
       </c>
       <c r="E307" s="14" t="inlineStr">
@@ -7901,17 +7901,17 @@
       <c r="A308" s="4" t="n"/>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>Blog: per-post OG image if different from hero (many posts can reuse hero as OG)</t>
-        </is>
-      </c>
-      <c r="C308" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>92 posts still need a real, unique hero image</t>
+        </is>
+      </c>
+      <c r="C308" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>Confirmed 2026-10-02: generateMetadata uses seo.ogImage, else the hero, else the default OG image.</t>
+          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
         </is>
       </c>
       <c r="E308" s="14" t="inlineStr">
@@ -7924,7 +7924,7 @@
       <c r="A309" s="4" t="n"/>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>Marketing pages</t>
+          <t>Blog: per-post OG image if different from hero (many posts can reuse hero as OG)</t>
         </is>
       </c>
       <c r="C309" s="13" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>hero/section images for /the-letter, /the-territory, /engine-room, /the-body, /the-nightstand, /recent-creations (portfolio thumbnails), /published (publication logos), /clients (client logos — confirm licensing before re-hosting). Checked against live 2026-10-02: same image count on every one; /the-territory, /engine-room, /recent-creations, /published, /clients have no images on live either.</t>
+          <t>Confirmed 2026-10-02: generateMetadata uses seo.ogImage, else the hero, else the default OG image.</t>
         </is>
       </c>
       <c r="E309" s="14" t="inlineStr">
@@ -7947,7 +7947,7 @@
       <c r="A310" s="4" t="n"/>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>/akbar essay images</t>
+          <t>Marketing pages</t>
         </is>
       </c>
       <c r="C310" s="13" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>not lost after all: 20 of the 21 were rescued into Sanity by scripts/rescue-manus-media.ts (2026-09-28) and are wired back in legacy's layout (hero mosaic, JC portrait, 2x2 grid, 3 full-bleeds, 3-up strip, footer gallery) as of 2026-09-29. Only slider-3 was gone (HTTP 502); the hero mosaic is 4 tiles instead of 5.</t>
+          <t>hero/section images for /the-letter, /the-territory, /engine-room, /the-body, /the-nightstand, /recent-creations (portfolio thumbnails), /published (publication logos), /clients (client logos — confirm licensing before re-hosting). Checked against live 2026-10-02: same image count on every one; /the-territory, /engine-room, /recent-creations, /published, /clients have no images on live either.</t>
         </is>
       </c>
       <c r="E310" s="14" t="inlineStr">
@@ -7970,7 +7970,7 @@
       <c r="A311" s="4" t="n"/>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Rescued page images wired back in (2026-09-29)</t>
+          <t>/akbar essay images</t>
         </is>
       </c>
       <c r="C311" s="13" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>/living-declaration hero, hand image and Clarisse Abelarde artwork; /impact-dashboard earth hero; /find-my banner; /find-your-coffee dark photo landing (legacy copy restored, replacing an intro that wasn't in legacy). Also wired (second pass): /consciousness-scale (legacy's hero-first flow restored, the invented intro screen removed), /find-your-me hero, /humanos hero, the HumanOS nav logo, and all 12 HumanOS people headshots (/humanos/ecosystem, /humanos/philosophy). Blog-body images (2026-09-29): all 19 the migration dropped are restored by scripts/restore-blog-body-images.ts as Sanity drafts on 4 posts (Clarisse Abelarde 7, You Are the Moat 4, FRQNCY 6, Energy Is Money 2), waiting to be published in Studio; the other blog-listed assets were heroes already set. Still unwired from docs/ai/manus-media-rescue.md: and /alex-azzi's subject photo (a photo of a real person on an accusation page: needs Tony's yes first).</t>
+          <t>not lost after all: 20 of the 21 were rescued into Sanity by scripts/rescue-manus-media.ts (2026-09-28) and are wired back in legacy's layout (hero mosaic, JC portrait, 2x2 grid, 3 full-bleeds, 3-up strip, footer gallery) as of 2026-09-29. Only slider-3 was gone (HTTP 502); the hero mosaic is 4 tiles instead of 5.</t>
         </is>
       </c>
       <c r="E311" s="14" t="inlineStr">
@@ -7993,7 +7993,7 @@
       <c r="A312" s="4" t="n"/>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>BrewSoul: coffee/product images (brewsoul-coffees-expanded.ts likely has image refs</t>
+          <t>Rescued page images wired back in (2026-09-29)</t>
         </is>
       </c>
       <c r="C312" s="13" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>audit), city guide header images, roaster directory photos. Audited 2026-09-09 (status spreadsheet), confirmed 2026-10-02: city guides already have photos; coffees, chains and roasters have no image field in legacy or here (text-only by design); farms got real photos.</t>
+          <t>/living-declaration hero, hand image and Clarisse Abelarde artwork; /impact-dashboard earth hero; /find-my banner; /find-your-coffee dark photo landing (legacy copy restored, replacing an intro that wasn't in legacy). Also wired (second pass): /consciousness-scale (legacy's hero-first flow restored, the invented intro screen removed), /find-your-me hero, /humanos hero, the HumanOS nav logo, and all 12 HumanOS people headshots (/humanos/ecosystem, /humanos/philosophy). Blog-body images (2026-09-29): all 19 the migration dropped are restored by scripts/restore-blog-body-images.ts as Sanity drafts on 4 posts (Clarisse Abelarde 7, You Are the Moat 4, FRQNCY 6, Energy Is Money 2), waiting to be published in Studio; the other blog-listed assets were heroes already set. Still unwired from docs/ai/manus-media-rescue.md: and /alex-azzi's subject photo (a photo of a real person on an accusation page: needs Tony's yes first).</t>
         </is>
       </c>
       <c r="E312" s="14" t="inlineStr">
@@ -8016,7 +8016,7 @@
       <c r="A313" s="4" t="n"/>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>65 page images moved off the Manus storage copy into Sanity (2026-10-02)</t>
+          <t>BrewSoul: coffee/product images (brewsoul-coffees-expanded.ts likely has image refs</t>
         </is>
       </c>
       <c r="C313" s="13" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>every image the code loaded from d2xsxph8kpxj0f.cloudfront.net (PRI medicine images, Iboga module, facilitator index, /attention-theft, /alex-azzi, /protecting-your-business, /peyote-mescaline, HumanOS, the peptide quiz). Notes called it "RampRate's own CloudFront", but every file sits in the legacy Manus project's folder and its owner couldn't be confirmed. All 65 uploaded (scripts/rescue-cloudfront-images.ts), code rewritten, host removed from images.remotePatterns, no Sanity document used it. Table in docs/ai/manus-media-rescue.md.</t>
+          <t>audit), city guide header images, roaster directory photos. Audited 2026-09-09 (status spreadsheet), confirmed 2026-10-02: city guides already have photos; coffees, chains and roasters have no image field in legacy or here (text-only by design); farms got real photos.</t>
         </is>
       </c>
       <c r="E313" s="14" t="inlineStr">
@@ -8039,7 +8039,7 @@
       <c r="A314" s="4" t="n"/>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>PRI/Kava: medicine reference images (medicine-images.ts), facility images for /facilitator-index</t>
+          <t>65 page images moved off the Manus storage copy into Sanity (2026-10-02)</t>
         </is>
       </c>
       <c r="C314" s="13" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: all in Sanity; image counts match live on PRI, Kava, Iboga, Peyote, facilitator pages.</t>
+          <t>every image the code loaded from d2xsxph8kpxj0f.cloudfront.net (PRI medicine images, Iboga module, facilitator index, /attention-theft, /alex-azzi, /protecting-your-business, /peyote-mescaline, HumanOS, the peptide quiz). Notes called it "RampRate's own CloudFront", but every file sits in the legacy Manus project's folder and its owner couldn't be confirmed. All 65 uploaded (scripts/rescue-cloudfront-images.ts), code rewritten, host removed from images.remotePatterns, no Sanity document used it. Table in docs/ai/manus-media-rescue.md.</t>
         </is>
       </c>
       <c r="E314" s="14" t="inlineStr">
@@ -8062,7 +8062,7 @@
       <c r="A315" s="4" t="n"/>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>Manifesto/Attention Theft: any diagram/illustration assets used on the mega-page</t>
+          <t>PRI/Kava: medicine reference images (medicine-images.ts), facility images for /facilitator-index</t>
         </is>
       </c>
       <c r="C315" s="13" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: 6 of live's 7 are in (now in Sanity); the 7th belongs to the Wall of Shame section left out on purpose.</t>
+          <t>2026-10-02: all in Sanity; image counts match live on PRI, Kava, Iboga, Peyote, facilitator pages.</t>
         </is>
       </c>
       <c r="E315" s="14" t="inlineStr">
@@ -8085,17 +8085,17 @@
       <c r="A316" s="4" t="n"/>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
-        </is>
-      </c>
-      <c r="C316" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Manifesto/Attention Theft: any diagram/illustration assets used on the mega-page</t>
+        </is>
+      </c>
+      <c r="C316" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
         <is>
-          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
+          <t>2026-10-02: 6 of live's 7 are in (now in Sanity); the 7th belongs to the Wall of Shame section left out on purpose.</t>
         </is>
       </c>
       <c r="E316" s="14" t="inlineStr">
@@ -8108,17 +8108,17 @@
       <c r="A317" s="4" t="n"/>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>Chatbot: FauxTony avatar/icon</t>
-        </is>
-      </c>
-      <c r="C317" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
+        </is>
+      </c>
+      <c r="C317" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>Not needed (2026-10-02): the chatbot phase (Phase 10) was cancelled.</t>
+          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
         </is>
       </c>
       <c r="E317" s="14" t="inlineStr">
@@ -8131,73 +8131,73 @@
       <c r="A318" s="4" t="n"/>
       <c r="B318" s="4" t="inlineStr">
         <is>
+          <t>Chatbot: FauxTony avatar/icon</t>
+        </is>
+      </c>
+      <c r="C318" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D318" s="4" t="inlineStr">
+        <is>
+          <t>Not needed (2026-10-02): the chatbot phase (Phase 10) was cancelled.</t>
+        </is>
+      </c>
+      <c r="E318" s="14" t="inlineStr">
+        <is>
+          <t>Phase 13 — Images Needed in Sanity</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="4" t="n"/>
+      <c r="B319" s="4" t="inlineStr">
+        <is>
           <t>Audit client/public/ (including alex-azzi/, brewsoul/ subfolders) for any static assets already sitting there unused that should be pulled i…</t>
         </is>
       </c>
-      <c r="C318" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D318" s="4" t="inlineStr">
+      <c r="C319" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D319" s="4" t="inlineStr">
         <is>
           <t>n rather than re-created. Done 2026-10-02: no images there at all (only llms.txt, a BrewSoul catalog, Manus debug files, design-options.html). Found and fixed a cutover risk instead: live serves two Google site-verification files (/google6881a0411c48b301.html, /alex-azzi/googleedff0185753a4a1f.html) that the new site returned 404 for, so Search Console could lose verification at DNS cutover. Both copied to public/ byte for byte. Not copied: site.webmanifest (its icons don't exist here; Next's app/icon.tsx covers the favicon).</t>
         </is>
       </c>
-      <c r="E318" s="14" t="inlineStr">
+      <c r="E319" s="14" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" s="10" t="inlineStr">
+    <row r="320">
+      <c r="A320" s="10" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
         </is>
       </c>
-      <c r="B319" s="11" t="n"/>
-      <c r="C319" s="11" t="n"/>
-      <c r="D319" s="12" t="n"/>
-    </row>
-    <row r="320">
-      <c r="A320" s="4" t="n"/>
-      <c r="B320" s="4" t="inlineStr">
-        <is>
-          <t>Mobile responsive pass on every ported section</t>
-        </is>
-      </c>
-      <c r="C320" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D320" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid).</t>
-        </is>
-      </c>
-      <c r="E320" s="14" t="inlineStr">
-        <is>
-          <t>Phase 14 — QA &amp; Launch</t>
-        </is>
-      </c>
+      <c r="B320" s="11" t="n"/>
+      <c r="C320" s="11" t="n"/>
+      <c r="D320" s="12" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="4" t="n"/>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>Accessibility pass (WCAG AA contrast, 44px touch targets, keyboard nav)</t>
-        </is>
-      </c>
-      <c r="C321" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Mobile responsive pass on every ported section</t>
+        </is>
+      </c>
+      <c r="C321" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy QA_MASTER_PROMPT.md. 2026-09-29 axe-core pass (WCAG 2.1 AA, same 114 pages, production build): all unlabeled dropdowns/inputs and unnamed links fixed; contrast down from 1,453 failing items on 106 pages to 1,038 on 70 (43 pages fully clean). Shared fixes: brand gold #8b6914 → #836311 site-wide (was 4.3:1 on cream, AA needs 4.5), header "⌘K"/social icons, BrewSoul nav and footer, HumanOS footer, Kava footer, assessment intro footnote, post-card image links. 2026-09-30: contrast finished, 0 axe color-contrast failures left on the same 114 pages (production build). Token changes: --kava-saffron #b86a28 → #8e521f, --pri-purple-light #a855f7 → #b87bf9 (on-dark purple only), --crusade-teal #0e7c7c → #0d7373; PriEyebrow goes light purple inside a dark PriSection via group-data-dark/pri; /find-your-me and the journey tracker's dark glass panels 60-70% → 90% (legacy's own 60% glass on beige rendered gray, cream text failed). Everything else: nearest passing shade of the same hue, or gold ↔ gold-light on the wrong background. Left: 18 links inside text marked only by color (need an underline), 44px tap targets, keyboard nav. 2026-09-30: 18 color-only in-text links underlined (axe link-in-text-block: 0 left); keyboard focus visible on every focusable item on 8 sampled pages (two form fields had none, fixed). 2026-10-02 re-run (axe WCAG 2.2 AA, 142 pages × 375/1280px, production build, plus Tab through 40 stops per page): found 1,370 contrast failures (mostly BrewSoul'</t>
+          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid). Fixed 2026-10-09: the bar is now solid (bg-[#2C1810], was 92% plus backdrop-blur-md), so nothing can show through even where the blur isn't drawn; checked in WebKit (iPhone 13 profile) and Chrome: background rgb(44, 24, 16), no text behind the buttons. A real iPhone check is still part of Phase 14.</t>
         </is>
       </c>
       <c r="E321" s="14" t="inlineStr">
@@ -8210,17 +8210,17 @@
       <c r="A322" s="4" t="n"/>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>No dead-end pages (every page links to 2+ others)</t>
-        </is>
-      </c>
-      <c r="C322" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Accessibility pass (WCAG AA contrast, 44px touch targets, keyboard nav)</t>
+        </is>
+      </c>
+      <c r="C322" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
+          <t>same bar as legacy QA_MASTER_PROMPT.md. 2026-09-29 axe-core pass (WCAG 2.1 AA, same 114 pages, production build): all unlabeled dropdowns/inputs and unnamed links fixed; contrast down from 1,453 failing items on 106 pages to 1,038 on 70 (43 pages fully clean). Shared fixes: brand gold #8b6914 → #836311 site-wide (was 4.3:1 on cream, AA needs 4.5), header "⌘K"/social icons, BrewSoul nav and footer, HumanOS footer, Kava footer, assessment intro footnote, post-card image links. 2026-09-30: contrast finished, 0 axe color-contrast failures left on the same 114 pages (production build). Token changes: --kava-saffron #b86a28 → #8e521f, --pri-purple-light #a855f7 → #b87bf9 (on-dark purple only), --crusade-teal #0e7c7c → #0d7373; PriEyebrow goes light purple inside a dark PriSection via group-data-dark/pri; /find-your-me and the journey tracker's dark glass panels 60-70% → 90% (legacy's own 60% glass on beige rendered gray, cream text failed). Everything else: nearest passing shade of the same hue, or gold ↔ gold-light on the wrong background. Left: 18 links inside text marked only by color (need an underline), 44px tap targets, keyboard nav. 2026-09-30: 18 color-only in-text links underlined (axe link-in-text-block: 0 left); keyboard focus visible on every focusable item on 8 sampled pages (two form fields had none, fixed). 2026-10-02 re-run (axe WCAG 2.2 AA, 142 pages × 375/1280px, production build, plus Tab through 40 stops per page): found 1,370 contrast failures (mostly BrewSoul'</t>
         </is>
       </c>
       <c r="E322" s="14" t="inlineStr">
@@ -8233,7 +8233,7 @@
       <c r="A323" s="4" t="n"/>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
+          <t>No dead-end pages (every page links to 2+ others)</t>
         </is>
       </c>
       <c r="C323" s="15" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
+          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
         </is>
       </c>
       <c r="E323" s="14" t="inlineStr">
@@ -8256,7 +8256,7 @@
       <c r="A324" s="4" t="n"/>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>Remove noindex only when sign-off is given</t>
+          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
         </is>
       </c>
       <c r="C324" s="15" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="D324" s="4" t="inlineStr">
         <is>
-          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
         </is>
       </c>
       <c r="E324" s="14" t="inlineStr">
@@ -8279,7 +8279,7 @@
       <c r="A325" s="4" t="n"/>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
+          <t>Remove noindex only when sign-off is given</t>
         </is>
       </c>
       <c r="C325" s="15" t="inlineStr">
@@ -8287,7 +8287,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D325" s="4" t="inlineStr"/>
+      <c r="D325" s="4" t="inlineStr">
+        <is>
+          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+        </is>
+      </c>
       <c r="E325" s="14" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
@@ -8298,7 +8302,7 @@
       <c r="A326" s="4" t="n"/>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
         </is>
       </c>
       <c r="C326" s="15" t="inlineStr">
@@ -8313,21 +8317,40 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" s="4" t="n"/>
+      <c r="B327" s="4" t="inlineStr">
+        <is>
+          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+        </is>
+      </c>
+      <c r="C327" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D327" s="4" t="inlineStr"/>
+      <c r="E327" s="14" t="inlineStr">
+        <is>
+          <t>Phase 14 — QA &amp; Launch</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D326"/>
+  <autoFilter ref="A1:D327"/>
   <mergeCells count="14">
     <mergeCell ref="A150:D150"/>
+    <mergeCell ref="A320:D320"/>
     <mergeCell ref="A237:D237"/>
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A258:D258"/>
-    <mergeCell ref="A319:D319"/>
     <mergeCell ref="A209:D209"/>
     <mergeCell ref="A205:D205"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A299:D299"/>
     <mergeCell ref="A183:D183"/>
+    <mergeCell ref="A300:D300"/>
     <mergeCell ref="A32:D32"/>
     <mergeCell ref="A123:D123"/>
   </mergeCells>
@@ -8789,7 +8812,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid).</t>
+          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid). Fixed 2026-10-09: the bar is now solid (bg-[#2C1810], was 92% plus backdrop-blur-md), so nothing can show through even where the blur isn't drawn; checked in WebKit (iPhone 13 profile) and Chrome: background rgb(44, 24, 16), no text behind the buttons. A real iPhone check is still part of Phase 14.</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">

--- a/Migration-Status-Report.xlsx
+++ b/Migration-Status-Report.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Remaining Work" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$327</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Remaining Work'!$A$1:$D$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Remaining Work'!$A$1:$D$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -639,15 +639,15 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A5,'Full Detail'!$C$2:$C$327,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A5,'Full Detail'!$C$2:$C$328,"Done")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A5,'Full Detail'!$C$2:$C$327,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A5,'Full Detail'!$C$2:$C$328,"Remaining")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A5,'Full Detail'!$C$2:$C$327,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A5,'Full Detail'!$C$2:$C$328,"Deferred")</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -666,15 +666,15 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A6,'Full Detail'!$C$2:$C$327,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A6,'Full Detail'!$C$2:$C$328,"Done")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A6,'Full Detail'!$C$2:$C$327,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A6,'Full Detail'!$C$2:$C$328,"Remaining")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A6,'Full Detail'!$C$2:$C$327,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A6,'Full Detail'!$C$2:$C$328,"Deferred")</f>
         <v/>
       </c>
       <c r="E6" s="5">
@@ -693,15 +693,15 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A7,'Full Detail'!$C$2:$C$327,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A7,'Full Detail'!$C$2:$C$328,"Done")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A7,'Full Detail'!$C$2:$C$327,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A7,'Full Detail'!$C$2:$C$328,"Remaining")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A7,'Full Detail'!$C$2:$C$327,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A7,'Full Detail'!$C$2:$C$328,"Deferred")</f>
         <v/>
       </c>
       <c r="E7" s="5">
@@ -720,15 +720,15 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A8,'Full Detail'!$C$2:$C$327,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A8,'Full Detail'!$C$2:$C$328,"Done")</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A8,'Full Detail'!$C$2:$C$327,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A8,'Full Detail'!$C$2:$C$328,"Remaining")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A8,'Full Detail'!$C$2:$C$327,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A8,'Full Detail'!$C$2:$C$328,"Deferred")</f>
         <v/>
       </c>
       <c r="E8" s="5">
@@ -747,15 +747,15 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A9,'Full Detail'!$C$2:$C$327,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A9,'Full Detail'!$C$2:$C$328,"Done")</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A9,'Full Detail'!$C$2:$C$327,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A9,'Full Detail'!$C$2:$C$328,"Remaining")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A9,'Full Detail'!$C$2:$C$327,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A9,'Full Detail'!$C$2:$C$328,"Deferred")</f>
         <v/>
       </c>
       <c r="E9" s="5">
@@ -774,15 +774,15 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A10,'Full Detail'!$C$2:$C$327,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A10,'Full Detail'!$C$2:$C$328,"Done")</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A10,'Full Detail'!$C$2:$C$327,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A10,'Full Detail'!$C$2:$C$328,"Remaining")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A10,'Full Detail'!$C$2:$C$327,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A10,'Full Detail'!$C$2:$C$328,"Deferred")</f>
         <v/>
       </c>
       <c r="E10" s="5">
@@ -801,15 +801,15 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A11,'Full Detail'!$C$2:$C$327,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A11,'Full Detail'!$C$2:$C$328,"Done")</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A11,'Full Detail'!$C$2:$C$327,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A11,'Full Detail'!$C$2:$C$328,"Remaining")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A11,'Full Detail'!$C$2:$C$327,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A11,'Full Detail'!$C$2:$C$328,"Deferred")</f>
         <v/>
       </c>
       <c r="E11" s="5">
@@ -828,15 +828,15 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A12,'Full Detail'!$C$2:$C$327,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A12,'Full Detail'!$C$2:$C$328,"Done")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A12,'Full Detail'!$C$2:$C$327,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A12,'Full Detail'!$C$2:$C$328,"Remaining")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A12,'Full Detail'!$C$2:$C$327,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A12,'Full Detail'!$C$2:$C$328,"Deferred")</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -855,15 +855,15 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A13,'Full Detail'!$C$2:$C$327,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A13,'Full Detail'!$C$2:$C$328,"Done")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A13,'Full Detail'!$C$2:$C$327,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A13,'Full Detail'!$C$2:$C$328,"Remaining")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A13,'Full Detail'!$C$2:$C$327,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A13,'Full Detail'!$C$2:$C$328,"Deferred")</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -882,15 +882,15 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A14,'Full Detail'!$C$2:$C$327,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A14,'Full Detail'!$C$2:$C$328,"Done")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A14,'Full Detail'!$C$2:$C$327,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A14,'Full Detail'!$C$2:$C$328,"Remaining")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A14,'Full Detail'!$C$2:$C$327,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A14,'Full Detail'!$C$2:$C$328,"Deferred")</f>
         <v/>
       </c>
       <c r="E14" s="5">
@@ -909,15 +909,15 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A15,'Full Detail'!$C$2:$C$327,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A15,'Full Detail'!$C$2:$C$328,"Done")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A15,'Full Detail'!$C$2:$C$327,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A15,'Full Detail'!$C$2:$C$328,"Remaining")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A15,'Full Detail'!$C$2:$C$327,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A15,'Full Detail'!$C$2:$C$328,"Deferred")</f>
         <v/>
       </c>
       <c r="E15" s="5">
@@ -936,15 +936,15 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A16,'Full Detail'!$C$2:$C$327,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A16,'Full Detail'!$C$2:$C$328,"Done")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A16,'Full Detail'!$C$2:$C$327,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A16,'Full Detail'!$C$2:$C$328,"Remaining")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A16,'Full Detail'!$C$2:$C$327,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A16,'Full Detail'!$C$2:$C$328,"Deferred")</f>
         <v/>
       </c>
       <c r="E16" s="5">
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A17,'Full Detail'!$C$2:$C$327,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A17,'Full Detail'!$C$2:$C$328,"Done")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A17,'Full Detail'!$C$2:$C$327,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A17,'Full Detail'!$C$2:$C$328,"Remaining")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A17,'Full Detail'!$C$2:$C$327,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A17,'Full Detail'!$C$2:$C$328,"Deferred")</f>
         <v/>
       </c>
       <c r="E17" s="5">
@@ -990,15 +990,15 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A18,'Full Detail'!$C$2:$C$327,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A18,'Full Detail'!$C$2:$C$328,"Done")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A18,'Full Detail'!$C$2:$C$327,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A18,'Full Detail'!$C$2:$C$328,"Remaining")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A18,'Full Detail'!$C$2:$C$327,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A18,'Full Detail'!$C$2:$C$328,"Deferred")</f>
         <v/>
       </c>
       <c r="E18" s="5">
@@ -1017,15 +1017,15 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A19,'Full Detail'!$C$2:$C$327,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A19,'Full Detail'!$C$2:$C$328,"Done")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A19,'Full Detail'!$C$2:$C$327,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A19,'Full Detail'!$C$2:$C$328,"Remaining")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$327,$A19,'Full Detail'!$C$2:$C$327,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A19,'Full Detail'!$C$2:$C$328,"Deferred")</f>
         <v/>
       </c>
       <c r="E19" s="5">
@@ -1075,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E327"/>
+  <dimension ref="A1:E328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7251,17 +7251,17 @@
       <c r="A279" s="4" t="n"/>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Still different from live (needs a yes)</t>
-        </is>
-      </c>
-      <c r="C279" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Still different from live (decided 2026-10-09)</t>
+        </is>
+      </c>
+      <c r="C279" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>blog posts (done) (done 2026-10-07, see Phase 5); /find-my on live hides the site header. /walk-through is a 404 on live now.</t>
+          <t>blog posts (done) (done 2026-10-07, see Phase 5); /find-my on live hides the site header. /walk-through is a 404 on live now. Owner: keep our site menu on /find-my (visitors can still reach the rest of the site); nothing left to change.</t>
         </is>
       </c>
       <c r="E279" s="14" t="inlineStr">
@@ -7274,17 +7274,17 @@
       <c r="A280" s="4" t="n"/>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>Design change on live, needs a decision</t>
-        </is>
-      </c>
-      <c r="C280" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Design change on live (owner: "match live", 2026-10-09)</t>
+        </is>
+      </c>
+      <c r="C280" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>live's story pages now use Cormorant Garamond for titles (ours: Playfair Display), a lighter title weight (400 vs our 700), and a red eyebrow label (#8E1E25, wider letter spacing) instead of our gold. A site-wide font swap is a design call, so not done.</t>
+          <t>live's story pages now use Cormorant Garamond for titles (ours: Playfair Display), a lighter title weight (400 vs our 700), and a red eyebrow label (#8E1E25, wider letter spacing) instead of our gold. A site-wide font swap is a design call, so not done. Done 2026-10-09: a fresh sweep of 163 live pages found live has since dropped Cormorant from the story pages (only /living-declaration uses it, ours already matched) and mostly uses Playfair; the real differences were fixed: every heading on /attention-theft in Fraunces 700 (section-wide, like Kava), /supplier-intake title in the system serif, and live's fluid title sizes on /about, /articles, /the-letter, /the-philosophy, /clock-keeper-part-2, /living-declaration (measured at 375/640/820/1024/1280, now identical). Label colours stay darker than live on purpose (contrast, rule 20).</t>
         </is>
       </c>
       <c r="E280" s="14" t="inlineStr">
@@ -7366,7 +7366,7 @@
       <c r="A284" s="4" t="n"/>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>Category pages pre-built (2026-10-09)</t>
+          <t>Arrows in buttons and links are icons (2026-10-09, owner said yes)</t>
         </is>
       </c>
       <c r="C284" s="13" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>/blog/category/[slug] read ?page=N, so every category page was rendered on each request (slower first byte, flagged in the Lighthouse notes). Page numbers are now part of the address (/blog/category/&lt;slug&gt;/page/&lt;n&gt;, generateStaticParams, dynamicParams = false), shared code in src/components/blog/category-listing.tsx; old ?page=N links 308 to the new address (pages 2+ only, so no loop), /page/1 308s to the plain address, a page past the end is a 404; "All essays" back link uses an icon. Verified on a production build: route table shows every category page as pre-built (9 page-1s, 7 later pages), titles and canonicals per page, Previous/Next links, the redirects and the 404s.</t>
+          <t>113 typed arrows in 52 files (button and link labels, "Next"/"See My Results" toggles, decorative arrow spans, the walk-through "See the..." labels, the Letter's "I'm in" button) replaced with lucide ArrowRight/ArrowLeft (size-[1em], inside inline-flex items-center gap-1.5, so the parent layout is untouched). Left as content on purpose: arrows inside Tony's text and data (health findings, origins, iboga compass options, process flows like "Inherit → Wake → Choose → Act", share text), the "← you" marker on the consciousness scale, and &lt;option&gt; sort labels (an option can't hold an icon). Checked on 16 pages at 375 and 1280: no typed arrow left in any link or button, no sideways scroll, no JS errors; close-up screenshots of the new icons.</t>
         </is>
       </c>
       <c r="E284" s="14" t="inlineStr">
@@ -7389,7 +7389,7 @@
       <c r="A285" s="4" t="n"/>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Error pages (2026-10-09, owner asked)</t>
+          <t>Category pages pre-built (2026-10-09)</t>
         </is>
       </c>
       <c r="C285" s="13" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>404 page now sets its own title ("Page not found") as a server page around live's 3-second redirect (not-found.tsx + components/not-found-redirect.tsx), arrow as an icon; page error screen (error.tsx) uses Next 16's retry (re-fetches), shows a reference code for the server logs, links home and to the site index; new global-error.tsx for failures in the root layout itself (own &lt;html&gt;, plain links). Verified on a production build: missing page, missing essay and missing Kava page return 404 with the right title; a test page that throws returns 500 with the error screen, "Try again" re-fetches; phone and laptop, no sideways scroll (test page removed).</t>
+          <t>/blog/category/[slug] read ?page=N, so every category page was rendered on each request (slower first byte, flagged in the Lighthouse notes). Page numbers are now part of the address (/blog/category/&lt;slug&gt;/page/&lt;n&gt;, generateStaticParams, dynamicParams = false), shared code in src/components/blog/category-listing.tsx; old ?page=N links 308 to the new address (pages 2+ only, so no loop), /page/1 308s to the plain address, a page past the end is a 404; "All essays" back link uses an icon. Verified on a production build: route table shows every category page as pre-built (9 page-1s, 7 later pages), titles and canonicals per page, Previous/Next links, the redirects and the 404s.</t>
         </is>
       </c>
       <c r="E285" s="14" t="inlineStr">
@@ -7412,7 +7412,7 @@
       <c r="A286" s="4" t="n"/>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>SEO audit fixes (2026-10-06)</t>
+          <t>Error pages (2026-10-09, owner asked)</t>
         </is>
       </c>
       <c r="C286" s="13" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
+          <t>404 page now sets its own title ("Page not found") as a server page around live's 3-second redirect (not-found.tsx + components/not-found-redirect.tsx), arrow as an icon; page error screen (error.tsx) uses Next 16's retry (re-fetches), shows a reference code for the server logs, links home and to the site index; new global-error.tsx for failures in the root layout itself (own &lt;html&gt;, plain links). Verified on a production build: missing page, missing essay and missing Kava page return 404 with the right title; a test page that throws returns 500 with the error screen, "Try again" re-fetches; phone and laptop, no sideways scroll (test page removed).</t>
         </is>
       </c>
       <c r="E286" s="14" t="inlineStr">
@@ -7435,17 +7435,17 @@
       <c r="A287" s="4" t="n"/>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>SEO audit items needing a yes (2026-10-06)</t>
-        </is>
-      </c>
-      <c r="C287" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>SEO audit fixes (2026-10-06)</t>
+        </is>
+      </c>
+      <c r="C287" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+          <t>Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
         </is>
       </c>
       <c r="E287" s="14" t="inlineStr">
@@ -7458,7 +7458,7 @@
       <c r="A288" s="4" t="n"/>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+          <t>SEO audit items needing a yes (2026-10-06)</t>
         </is>
       </c>
       <c r="C288" s="15" t="inlineStr">
@@ -7466,7 +7466,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D288" s="4" t="inlineStr"/>
+      <c r="D288" s="4" t="inlineStr">
+        <is>
+          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+        </is>
+      </c>
       <c r="E288" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -7477,19 +7481,15 @@
       <c r="A289" s="4" t="n"/>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
-        </is>
-      </c>
-      <c r="C289" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D289" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
-        </is>
-      </c>
+          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+        </is>
+      </c>
+      <c r="C289" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D289" s="4" t="inlineStr"/>
       <c r="E289" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -7500,7 +7500,7 @@
       <c r="A290" s="4" t="n"/>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>"Keep going" strip above the footer on every page (2026-10-07)</t>
+          <t>Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
         </is>
       </c>
       <c r="C290" s="13" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>legacy's WhereNext (deferred in Phase 3, never picked up) with its per-page suggestions, Home · Site Index · All Assessments; links pointed at current routes.</t>
+          <t>2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
         </is>
       </c>
       <c r="E290" s="14" t="inlineStr">
@@ -7523,7 +7523,7 @@
       <c r="A291" s="4" t="n"/>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Live-only and redesigned pages from the 2026-10-07 page sweep (188 pages compared with live)</t>
+          <t>"Keep going" strip above the footer on every page (2026-10-07)</t>
         </is>
       </c>
       <c r="C291" s="13" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>/the-index rebuilt from live's code (20 concepts, related-word search across essays and site pages, full-text search on the server, "three related places to go next"; the old redirect to /search removed and its links, including the "Site Index" link in "Keep going", point at it again); /the-mirror (and /life-assessment) opens on live's intro (dark hero, "What We Measure" with the six areas, "The Ecosystem"), rebuilt as a step registry (rule 19); /essays header, order and column like live; /about "What They Say" styled like live (live picks 3 of the same 19 quotes at random; ours shows a fixed 3 so they're in the server HTML); /impact-futurism list titles and subtitles; /supplier-intake is a real page again with live's Stage 1 form; /seven-doors and /projects redirect home like live; /impact, /health, /library, /built-on-manus, /heroes are 404 on live too. Left as is on purpose: /blog stays our archive page (on live it repeats the homepage), the email gates on /framework and /peptide-supply-chain, the attention-theft Wall of Shame.</t>
+          <t>legacy's WhereNext (deferred in Phase 3, never picked up) with its per-page suggestions, Home · Site Index · All Assessments; links pointed at current routes.</t>
         </is>
       </c>
       <c r="E291" s="14" t="inlineStr">
@@ -7546,7 +7546,7 @@
       <c r="A292" s="4" t="n"/>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>/alex-azzi locked like live (2026-10-07, owner said match it)</t>
+          <t>Live-only and redesigned pages from the 2026-10-07 page sweep (188 pages compared with live)</t>
         </is>
       </c>
       <c r="C292" s="13" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>same server-checked password as the locked essay (GATED_POST_PASSWORD, now also set in Netlify), live's "Restricted Access" screen, the report not in the page until unlocked, out of search and the sitemap.</t>
+          <t>/the-index rebuilt from live's code (20 concepts, related-word search across essays and site pages, full-text search on the server, "three related places to go next"; the old redirect to /search removed and its links, including the "Site Index" link in "Keep going", point at it again); /the-mirror (and /life-assessment) opens on live's intro (dark hero, "What We Measure" with the six areas, "The Ecosystem"), rebuilt as a step registry (rule 19); /essays header, order and column like live; /about "What They Say" styled like live (live picks 3 of the same 19 quotes at random; ours shows a fixed 3 so they're in the server HTML); /impact-futurism list titles and subtitles; /supplier-intake is a real page again with live's Stage 1 form; /seven-doors and /projects redirect home like live; /impact, /health, /library, /built-on-manus, /heroes are 404 on live too. Left as is on purpose: /blog stays our archive page (on live it repeats the homepage), the email gates on /framework and /peptide-supply-chain, the attention-theft Wall of Shame.</t>
         </is>
       </c>
       <c r="E292" s="14" t="inlineStr">
@@ -7569,7 +7569,7 @@
       <c r="A293" s="4" t="n"/>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Live's title fonts and sizes (2026-10-07, "fix the style")</t>
+          <t>/alex-azzi locked like live (2026-10-07, owner said match it)</t>
         </is>
       </c>
       <c r="C293" s="13" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>measured every page's title font, weight, size and label colour on live vs ours (136 pages). Now like live: Kava headings in Fraunces, HumanOS in Space Grotesk, the peptide tools / charity scorecard / thesis threads in the system serif, America Unbundled in the Iowan Old Style stack at live's size, /akbar in Fraunces 900, friend-gate and post-intervention in Georgia, and live's title sizes on peptide-matrix, peptide-supply-chain, rip-peptide-sciences and the HumanOS pages. Fonts load only on the pages that use them (src/lib/fonts/page-fonts.ts). Label colours stay the darker AA-contrast versions where live's lighter ones fail on a light background.</t>
+          <t>same server-checked password as the locked essay (GATED_POST_PASSWORD, now also set in Netlify), live's "Restricted Access" screen, the report not in the page until unlocked, out of search and the sitemap.</t>
         </is>
       </c>
       <c r="E293" s="14" t="inlineStr">
@@ -7592,7 +7592,7 @@
       <c r="A294" s="4" t="n"/>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Peptide page images rescued into Sanity and wired (2026-10-07)</t>
+          <t>Live's title fonts and sizes (2026-10-07, "fix the style")</t>
         </is>
       </c>
       <c r="C294" s="13" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>/peptide-watch hero plus its 11 section banners, /peptide-matrix and /peptide-supply-chain heroes, the /peptide-hall-of-shame hero (scripts/rescue-2026-10-07-peptide-images.ts, logged in docs/ai/manus-media-rescue.md).</t>
+          <t>measured every page's title font, weight, size and label colour on live vs ours (136 pages). Now like live: Kava headings in Fraunces, HumanOS in Space Grotesk, the peptide tools / charity scorecard / thesis threads in the system serif, America Unbundled in the Iowan Old Style stack at live's size, /akbar in Fraunces 900, friend-gate and post-intervention in Georgia, and live's title sizes on peptide-matrix, peptide-supply-chain, rip-peptide-sciences and the HumanOS pages. Fonts load only on the pages that use them (src/lib/fonts/page-fonts.ts). Label colours stay the darker AA-contrast versions where live's lighter ones fail on a light background.</t>
         </is>
       </c>
       <c r="E294" s="14" t="inlineStr">
@@ -7615,7 +7615,7 @@
       <c r="A295" s="4" t="n"/>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Live's editorial redesign, first group (2026-10-07)</t>
+          <t>Peptide page images rescued into Sanity and wired (2026-10-07)</t>
         </is>
       </c>
       <c r="C295" s="13" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
+          <t>/peptide-watch hero plus its 11 section banners, /peptide-matrix and /peptide-supply-chain heroes, the /peptide-hall-of-shame hero (scripts/rescue-2026-10-07-peptide-images.ts, logged in docs/ai/manus-media-rescue.md).</t>
         </is>
       </c>
       <c r="E295" s="14" t="inlineStr">
@@ -7638,7 +7638,7 @@
       <c r="A296" s="4" t="n"/>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>Live's redesign, second group (done 2026-10-08)</t>
+          <t>Live's editorial redesign, first group (2026-10-07)</t>
         </is>
       </c>
       <c r="C296" s="13" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>re-measured all 18 pages on live vs a fresh production build (title font/size/weight/colour, labels, hero images). Already matching from 2026-10-07: /the-web, /spirits, /iboga-ibogaine (weight 800), /living-declaration, BrewSoul photo on /brewsoul, /brewsoul/browse, /brewsoul/first-sip (live has none there either), /quiz_25q, /recent-creations. Fixed today: /find-your-journey (64px title, red label), /impact-dashboard (64px title in essay ink, label spacing), red labels on /published and /speaking (plus its "rooms" chips), /soulscore "by ImpactSoul" label, /pri-calibration title (weight 900, solid cream, was a purple gradient), /clients (live's narrow 546px column for the whole page, 56px title, roomier stats band, cards 2 per row; two static inline styles moved to classes), /brewsoul/guest (live's BrewSoul photo on the guest card instead of "SN" initials, labels in capitals), /humanos/connect (cards line up with the title), /peptide-hall-of-shame (stats and label readable light gold; were dark gold on dark). Typed arrows on the touched links are icons now (rule 18). Deliberately not copied from live (new CONTRIBUTING rule 20, owner 2026-10-08): red labels on dark bands use #E07A80 (live's #8E1E25 on black is about 2:1, unreadable); /recent-creations keeps our darker label colours (live's fail contrast on white); /humanos/connect keeps "Start Reading" (that card links to the philosophy page, the quiz live's "Start the Assessment" implies doesn't exist). Checked: type check, l</t>
+          <t>dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
         </is>
       </c>
       <c r="E296" s="14" t="inlineStr">
@@ -7661,7 +7661,7 @@
       <c r="A297" s="4" t="n"/>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>BrewSoul top of page (2026-10-08, owner: "button in the center at the top doesn't look good")</t>
+          <t>Live's redesign, second group (done 2026-10-08)</t>
         </is>
       </c>
       <c r="C297" s="13" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>the category badge ("Deep Research" etc.) sat centred in an empty strip, squeezed against the hero, because we copied live's doubled 52px top gap. Now one gap everywhere and the badge floats in the top-left corner, lined up with the BrewSoul logo (brewsoul-main.tsx, category-badge.tsx); checked on all 26 badge pages at 3 widths that it covers nothing. BrewSoul menu: on tablets (768-1023px) the links were cut off and "More" was hidden with no menu button at all; now the menu button shows below 1024px, 5 links + "More" from 1024px, all 8 from 1280px, "More" always visible.</t>
+          <t>re-measured all 18 pages on live vs a fresh production build (title font/size/weight/colour, labels, hero images). Already matching from 2026-10-07: /the-web, /spirits, /iboga-ibogaine (weight 800), /living-declaration, BrewSoul photo on /brewsoul, /brewsoul/browse, /brewsoul/first-sip (live has none there either), /quiz_25q, /recent-creations. Fixed today: /find-your-journey (64px title, red label), /impact-dashboard (64px title in essay ink, label spacing), red labels on /published and /speaking (plus its "rooms" chips), /soulscore "by ImpactSoul" label, /pri-calibration title (weight 900, solid cream, was a purple gradient), /clients (live's narrow 546px column for the whole page, 56px title, roomier stats band, cards 2 per row; two static inline styles moved to classes), /brewsoul/guest (live's BrewSoul photo on the guest card instead of "SN" initials, labels in capitals), /humanos/connect (cards line up with the title), /peptide-hall-of-shame (stats and label readable light gold; were dark gold on dark). Typed arrows on the touched links are icons now (rule 18). Deliberately not copied from live (new CONTRIBUTING rule 20, owner 2026-10-08): red labels on dark bands use #E07A80 (live's #8E1E25 on black is about 2:1, unreadable); /recent-creations keeps our darker label colours (live's fail contrast on white); /humanos/connect keeps "Start Reading" (that card links to the philosophy page, the quiz live's "Start the Assessment" implies doesn't exist). Checked: type check, l</t>
         </is>
       </c>
       <c r="E297" s="14" t="inlineStr">
@@ -7684,7 +7684,7 @@
       <c r="A298" s="4" t="n"/>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>/pri-efficacy's "Simulation / Live Calibrations" switch like live (2026-10-08)</t>
+          <t>BrewSoul top of page (2026-10-08, owner: "button in the center at the top doesn't look good")</t>
         </is>
       </c>
       <c r="C298" s="13" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>shadcn Tabs, both panels in the server HTML (forceMount). The Live tab reads real aggregate numbers from pri_calibrations (getPriLiveStats() in src/lib/pri-research.ts: totals, opt-ins, average score per dimension; no rows leave the server), page stays static and refreshes every 10 minutes. Until the Supabase scripts are run (Phase 2) it says the numbers "aren't available just now" instead of a fake zero. Checked: build (○, 10m), server HTML has both tabs, tab switch at 390/1280px, no JS errors. Re-check with real numbers once the table exists.</t>
+          <t>the category badge ("Deep Research" etc.) sat centred in an empty strip, squeezed against the hero, because we copied live's doubled 52px top gap. Now one gap everywhere and the badge floats in the top-left corner, lined up with the BrewSoul logo (brewsoul-main.tsx, category-badge.tsx); checked on all 26 badge pages at 3 widths that it covers nothing. BrewSoul menu: on tablets (768-1023px) the links were cut off and "More" was hidden with no menu button at all; now the menu button shows below 1024px, 5 links + "More" from 1024px, all 8 from 1280px, "More" always visible.</t>
         </is>
       </c>
       <c r="E298" s="14" t="inlineStr">
@@ -7707,63 +7707,63 @@
       <c r="A299" s="4" t="n"/>
       <c r="B299" s="4" t="inlineStr">
         <is>
+          <t>/pri-efficacy's "Simulation / Live Calibrations" switch like live (2026-10-08)</t>
+        </is>
+      </c>
+      <c r="C299" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D299" s="4" t="inlineStr">
+        <is>
+          <t>shadcn Tabs, both panels in the server HTML (forceMount). The Live tab reads real aggregate numbers from pri_calibrations (getPriLiveStats() in src/lib/pri-research.ts: totals, opt-ins, average score per dimension; no rows leave the server), page stays static and refreshes every 10 minutes. Until the Supabase scripts are run (Phase 2) it says the numbers "aren't available just now" instead of a fake zero. Checked: build (○, 10m), server HTML has both tabs, tab switch at 390/1280px, no JS errors. Re-check with real numbers once the table exists.</t>
+        </is>
+      </c>
+      <c r="E299" s="14" t="inlineStr">
+        <is>
+          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="4" t="n"/>
+      <c r="B300" s="4" t="inlineStr">
+        <is>
           <t>/brewsoul/browse hero readable (2026-10-08, owner said go ahead)</t>
         </is>
       </c>
-      <c r="C299" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D299" s="4" t="inlineStr">
+      <c r="C300" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="inlineStr">
         <is>
           <t>a soft cream glow behind the title block so "The Catalog", the subtitle and the stat labels read clearly over the coffee photo (live is hard to read there too; rule 20). Photo still shows around the edges. Checked at 390/1280px.</t>
         </is>
       </c>
-      <c r="E299" s="14" t="inlineStr">
+      <c r="E300" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
         </is>
       </c>
     </row>
-    <row r="300">
-      <c r="A300" s="10" t="inlineStr">
+    <row r="301">
+      <c r="A301" s="10" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
-      <c r="B300" s="11" t="n"/>
-      <c r="C300" s="11" t="n"/>
-      <c r="D300" s="12" t="n"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="4" t="n"/>
-      <c r="B301" s="4" t="inlineStr">
-        <is>
-          <t>Manus media rescue (2026-09-29)</t>
-        </is>
-      </c>
-      <c r="C301" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D301" s="4" t="inlineStr">
-        <is>
-          <t>all 94 Manus-hosted image/video references in the legacy source (/api/img/, /manus-storage/) were checked live. 91 were still downloadable, including the /akbar photos the entry below calls "permanently lost", and all 91 are now Sanity assets (scripts/rescue-manus-media.ts; Sanity dedupes by SHA-1). 3 were gone (HTTP 502). The manifest docs/ai/manus-media-rescue.md maps each one to the legacy files that used it and its Sanity URL. They are not wired into pages yet: go page by page, with real alt text. /facilitator-index's two diagrams are done (scripts/rescue-facilitator-images.ts).</t>
-        </is>
-      </c>
-      <c r="E301" s="14" t="inlineStr">
-        <is>
-          <t>Phase 13 — Images Needed in Sanity</t>
-        </is>
-      </c>
+      <c r="B301" s="11" t="n"/>
+      <c r="C301" s="11" t="n"/>
+      <c r="D301" s="12" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="4" t="n"/>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>Favicon</t>
+          <t>Manus media rescue (2026-09-29)</t>
         </is>
       </c>
       <c r="C302" s="13" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>real "G" brand mark generated from the header's actual wordmark treatment (src/app/icon.tsx), see Phase 3</t>
+          <t>all 94 Manus-hosted image/video references in the legacy source (/api/img/, /manus-storage/) were checked live. 91 were still downloadable, including the /akbar photos the entry below calls "permanently lost", and all 91 are now Sanity assets (scripts/rescue-manus-media.ts; Sanity dedupes by SHA-1). 3 were gone (HTTP 502). The manifest docs/ai/manus-media-rescue.md maps each one to the legacy files that used it and its Sanity URL. They are not wired into pages yet: go page by page, with real alt text. /facilitator-index's two diagrams are done (scripts/rescue-facilitator-images.ts).</t>
         </is>
       </c>
       <c r="E302" s="14" t="inlineStr">
@@ -7786,17 +7786,17 @@
       <c r="A303" s="4" t="n"/>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
-        </is>
-      </c>
-      <c r="C303" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Favicon</t>
+        </is>
+      </c>
+      <c r="C303" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
+          <t>real "G" brand mark generated from the header's actual wordmark treatment (src/app/icon.tsx), see Phase 3</t>
         </is>
       </c>
       <c r="E303" s="14" t="inlineStr">
@@ -7809,17 +7809,17 @@
       <c r="A304" s="4" t="n"/>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>Author photo(s) for blog author schema (Tony Greenberg headshot at minimum)</t>
-        </is>
-      </c>
-      <c r="C304" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
+        </is>
+      </c>
+      <c r="C304" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: the rescued headshot is already the author avatar in Sanity; now also in every post's Article JSON-LD (author image + url /about). The JSON-LD publisher logo pointed at /favicon.ico, a 404 here; now /icon.</t>
+          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
         </is>
       </c>
       <c r="E304" s="14" t="inlineStr">
@@ -7832,7 +7832,7 @@
       <c r="A305" s="4" t="n"/>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Blog hero images</t>
+          <t>Author photo(s) for blog author schema (Tony Greenberg headshot at minimum)</t>
         </is>
       </c>
       <c r="C305" s="13" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>audited, then migrated. Final state:</t>
+          <t>2026-10-02: the rescued headshot is already the author avatar in Sanity; now also in every post's Article JSON-LD (author image + url /about). The JSON-LD publisher logo pointed at /favicon.ico, a 404 here; now /icon.</t>
         </is>
       </c>
       <c r="E305" s="14" t="inlineStr">
@@ -7855,7 +7855,7 @@
       <c r="A306" s="4" t="n"/>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>22 posts have a real hero image, now live in Sanity (17 already on RampRate's own CloudFront + 4 rescued from the legacy /api/img/ proxy + 1…</t>
+          <t>Blog hero images</t>
         </is>
       </c>
       <c r="C306" s="13" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> rescued from /manus-storage/, all pulled over by migrate-blog-posts.ts before Manus is decommissioned)</t>
+          <t>audited, then migrated. Final state:</t>
         </is>
       </c>
       <c r="E306" s="14" t="inlineStr">
@@ -7878,7 +7878,7 @@
       <c r="A307" s="4" t="n"/>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>7 more posts got a real, unique hero image rescued from the live legacy site's newly-added art this pass (scripts/rescue-2026-09-blog-images…</t>
+          <t>22 posts have a real hero image, now live in Sanity (17 already on RampRate's own CloudFront + 4 rescued from the legacy /api/img/ proxy + 1…</t>
         </is>
       </c>
       <c r="C307" s="13" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>.ts — see the correction note above): california-toll-roads-legalized-scam, the-1000-hour-hold, conscious-capital-partnership-ecosystem, the-peptide-truth-65m-fraud-industry-vs-life-changing-medicine, clear-communication, building-services-market-transhuman-era, heart-protocol-addendum.</t>
+          <t xml:space="preserve"> rescued from /manus-storage/, all pulled over by migrate-blog-posts.ts before Manus is decommissioned)</t>
         </is>
       </c>
       <c r="E307" s="14" t="inlineStr">
@@ -7901,17 +7901,17 @@
       <c r="A308" s="4" t="n"/>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>92 posts still need a real, unique hero image</t>
-        </is>
-      </c>
-      <c r="C308" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>7 more posts got a real, unique hero image rescued from the live legacy site's newly-added art this pass (scripts/rescue-2026-09-blog-images…</t>
+        </is>
+      </c>
+      <c r="C308" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
+          <t>.ts — see the correction note above): california-toll-roads-legalized-scam, the-1000-hour-hold, conscious-capital-partnership-ecosystem, the-peptide-truth-65m-fraud-industry-vs-life-changing-medicine, clear-communication, building-services-market-transhuman-era, heart-protocol-addendum.</t>
         </is>
       </c>
       <c r="E308" s="14" t="inlineStr">
@@ -7924,17 +7924,17 @@
       <c r="A309" s="4" t="n"/>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>Blog: per-post OG image if different from hero (many posts can reuse hero as OG)</t>
-        </is>
-      </c>
-      <c r="C309" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>92 posts still need a real, unique hero image</t>
+        </is>
+      </c>
+      <c r="C309" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>Confirmed 2026-10-02: generateMetadata uses seo.ogImage, else the hero, else the default OG image.</t>
+          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
         </is>
       </c>
       <c r="E309" s="14" t="inlineStr">
@@ -7947,7 +7947,7 @@
       <c r="A310" s="4" t="n"/>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>Marketing pages</t>
+          <t>Blog: per-post OG image if different from hero (many posts can reuse hero as OG)</t>
         </is>
       </c>
       <c r="C310" s="13" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>hero/section images for /the-letter, /the-territory, /engine-room, /the-body, /the-nightstand, /recent-creations (portfolio thumbnails), /published (publication logos), /clients (client logos — confirm licensing before re-hosting). Checked against live 2026-10-02: same image count on every one; /the-territory, /engine-room, /recent-creations, /published, /clients have no images on live either.</t>
+          <t>Confirmed 2026-10-02: generateMetadata uses seo.ogImage, else the hero, else the default OG image.</t>
         </is>
       </c>
       <c r="E310" s="14" t="inlineStr">
@@ -7970,7 +7970,7 @@
       <c r="A311" s="4" t="n"/>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>/akbar essay images</t>
+          <t>Marketing pages</t>
         </is>
       </c>
       <c r="C311" s="13" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>not lost after all: 20 of the 21 were rescued into Sanity by scripts/rescue-manus-media.ts (2026-09-28) and are wired back in legacy's layout (hero mosaic, JC portrait, 2x2 grid, 3 full-bleeds, 3-up strip, footer gallery) as of 2026-09-29. Only slider-3 was gone (HTTP 502); the hero mosaic is 4 tiles instead of 5.</t>
+          <t>hero/section images for /the-letter, /the-territory, /engine-room, /the-body, /the-nightstand, /recent-creations (portfolio thumbnails), /published (publication logos), /clients (client logos — confirm licensing before re-hosting). Checked against live 2026-10-02: same image count on every one; /the-territory, /engine-room, /recent-creations, /published, /clients have no images on live either.</t>
         </is>
       </c>
       <c r="E311" s="14" t="inlineStr">
@@ -7993,7 +7993,7 @@
       <c r="A312" s="4" t="n"/>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>Rescued page images wired back in (2026-09-29)</t>
+          <t>/akbar essay images</t>
         </is>
       </c>
       <c r="C312" s="13" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>/living-declaration hero, hand image and Clarisse Abelarde artwork; /impact-dashboard earth hero; /find-my banner; /find-your-coffee dark photo landing (legacy copy restored, replacing an intro that wasn't in legacy). Also wired (second pass): /consciousness-scale (legacy's hero-first flow restored, the invented intro screen removed), /find-your-me hero, /humanos hero, the HumanOS nav logo, and all 12 HumanOS people headshots (/humanos/ecosystem, /humanos/philosophy). Blog-body images (2026-09-29): all 19 the migration dropped are restored by scripts/restore-blog-body-images.ts as Sanity drafts on 4 posts (Clarisse Abelarde 7, You Are the Moat 4, FRQNCY 6, Energy Is Money 2), waiting to be published in Studio; the other blog-listed assets were heroes already set. Still unwired from docs/ai/manus-media-rescue.md: and /alex-azzi's subject photo (a photo of a real person on an accusation page: needs Tony's yes first).</t>
+          <t>not lost after all: 20 of the 21 were rescued into Sanity by scripts/rescue-manus-media.ts (2026-09-28) and are wired back in legacy's layout (hero mosaic, JC portrait, 2x2 grid, 3 full-bleeds, 3-up strip, footer gallery) as of 2026-09-29. Only slider-3 was gone (HTTP 502); the hero mosaic is 4 tiles instead of 5.</t>
         </is>
       </c>
       <c r="E312" s="14" t="inlineStr">
@@ -8016,7 +8016,7 @@
       <c r="A313" s="4" t="n"/>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>BrewSoul: coffee/product images (brewsoul-coffees-expanded.ts likely has image refs</t>
+          <t>Rescued page images wired back in (2026-09-29)</t>
         </is>
       </c>
       <c r="C313" s="13" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>audit), city guide header images, roaster directory photos. Audited 2026-09-09 (status spreadsheet), confirmed 2026-10-02: city guides already have photos; coffees, chains and roasters have no image field in legacy or here (text-only by design); farms got real photos.</t>
+          <t>/living-declaration hero, hand image and Clarisse Abelarde artwork; /impact-dashboard earth hero; /find-my banner; /find-your-coffee dark photo landing (legacy copy restored, replacing an intro that wasn't in legacy). Also wired (second pass): /consciousness-scale (legacy's hero-first flow restored, the invented intro screen removed), /find-your-me hero, /humanos hero, the HumanOS nav logo, and all 12 HumanOS people headshots (/humanos/ecosystem, /humanos/philosophy). Blog-body images (2026-09-29): all 19 the migration dropped are restored by scripts/restore-blog-body-images.ts as Sanity drafts on 4 posts (Clarisse Abelarde 7, You Are the Moat 4, FRQNCY 6, Energy Is Money 2), waiting to be published in Studio; the other blog-listed assets were heroes already set. Still unwired from docs/ai/manus-media-rescue.md: and /alex-azzi's subject photo (a photo of a real person on an accusation page: needs Tony's yes first).</t>
         </is>
       </c>
       <c r="E313" s="14" t="inlineStr">
@@ -8039,7 +8039,7 @@
       <c r="A314" s="4" t="n"/>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>65 page images moved off the Manus storage copy into Sanity (2026-10-02)</t>
+          <t>BrewSoul: coffee/product images (brewsoul-coffees-expanded.ts likely has image refs</t>
         </is>
       </c>
       <c r="C314" s="13" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>every image the code loaded from d2xsxph8kpxj0f.cloudfront.net (PRI medicine images, Iboga module, facilitator index, /attention-theft, /alex-azzi, /protecting-your-business, /peyote-mescaline, HumanOS, the peptide quiz). Notes called it "RampRate's own CloudFront", but every file sits in the legacy Manus project's folder and its owner couldn't be confirmed. All 65 uploaded (scripts/rescue-cloudfront-images.ts), code rewritten, host removed from images.remotePatterns, no Sanity document used it. Table in docs/ai/manus-media-rescue.md.</t>
+          <t>audit), city guide header images, roaster directory photos. Audited 2026-09-09 (status spreadsheet), confirmed 2026-10-02: city guides already have photos; coffees, chains and roasters have no image field in legacy or here (text-only by design); farms got real photos.</t>
         </is>
       </c>
       <c r="E314" s="14" t="inlineStr">
@@ -8062,7 +8062,7 @@
       <c r="A315" s="4" t="n"/>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>PRI/Kava: medicine reference images (medicine-images.ts), facility images for /facilitator-index</t>
+          <t>65 page images moved off the Manus storage copy into Sanity (2026-10-02)</t>
         </is>
       </c>
       <c r="C315" s="13" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: all in Sanity; image counts match live on PRI, Kava, Iboga, Peyote, facilitator pages.</t>
+          <t>every image the code loaded from d2xsxph8kpxj0f.cloudfront.net (PRI medicine images, Iboga module, facilitator index, /attention-theft, /alex-azzi, /protecting-your-business, /peyote-mescaline, HumanOS, the peptide quiz). Notes called it "RampRate's own CloudFront", but every file sits in the legacy Manus project's folder and its owner couldn't be confirmed. All 65 uploaded (scripts/rescue-cloudfront-images.ts), code rewritten, host removed from images.remotePatterns, no Sanity document used it. Table in docs/ai/manus-media-rescue.md.</t>
         </is>
       </c>
       <c r="E315" s="14" t="inlineStr">
@@ -8085,7 +8085,7 @@
       <c r="A316" s="4" t="n"/>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>Manifesto/Attention Theft: any diagram/illustration assets used on the mega-page</t>
+          <t>PRI/Kava: medicine reference images (medicine-images.ts), facility images for /facilitator-index</t>
         </is>
       </c>
       <c r="C316" s="13" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="D316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: 6 of live's 7 are in (now in Sanity); the 7th belongs to the Wall of Shame section left out on purpose.</t>
+          <t>2026-10-02: all in Sanity; image counts match live on PRI, Kava, Iboga, Peyote, facilitator pages.</t>
         </is>
       </c>
       <c r="E316" s="14" t="inlineStr">
@@ -8108,17 +8108,17 @@
       <c r="A317" s="4" t="n"/>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
-        </is>
-      </c>
-      <c r="C317" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Manifesto/Attention Theft: any diagram/illustration assets used on the mega-page</t>
+        </is>
+      </c>
+      <c r="C317" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
+          <t>2026-10-02: 6 of live's 7 are in (now in Sanity); the 7th belongs to the Wall of Shame section left out on purpose.</t>
         </is>
       </c>
       <c r="E317" s="14" t="inlineStr">
@@ -8131,17 +8131,17 @@
       <c r="A318" s="4" t="n"/>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>Chatbot: FauxTony avatar/icon</t>
-        </is>
-      </c>
-      <c r="C318" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
+        </is>
+      </c>
+      <c r="C318" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
         <is>
-          <t>Not needed (2026-10-02): the chatbot phase (Phase 10) was cancelled.</t>
+          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
         </is>
       </c>
       <c r="E318" s="14" t="inlineStr">
@@ -8154,73 +8154,73 @@
       <c r="A319" s="4" t="n"/>
       <c r="B319" s="4" t="inlineStr">
         <is>
+          <t>Chatbot: FauxTony avatar/icon</t>
+        </is>
+      </c>
+      <c r="C319" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D319" s="4" t="inlineStr">
+        <is>
+          <t>Not needed (2026-10-02): the chatbot phase (Phase 10) was cancelled.</t>
+        </is>
+      </c>
+      <c r="E319" s="14" t="inlineStr">
+        <is>
+          <t>Phase 13 — Images Needed in Sanity</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="4" t="n"/>
+      <c r="B320" s="4" t="inlineStr">
+        <is>
           <t>Audit client/public/ (including alex-azzi/, brewsoul/ subfolders) for any static assets already sitting there unused that should be pulled i…</t>
         </is>
       </c>
-      <c r="C319" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D319" s="4" t="inlineStr">
+      <c r="C320" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D320" s="4" t="inlineStr">
         <is>
           <t>n rather than re-created. Done 2026-10-02: no images there at all (only llms.txt, a BrewSoul catalog, Manus debug files, design-options.html). Found and fixed a cutover risk instead: live serves two Google site-verification files (/google6881a0411c48b301.html, /alex-azzi/googleedff0185753a4a1f.html) that the new site returned 404 for, so Search Console could lose verification at DNS cutover. Both copied to public/ byte for byte. Not copied: site.webmanifest (its icons don't exist here; Next's app/icon.tsx covers the favicon).</t>
         </is>
       </c>
-      <c r="E319" s="14" t="inlineStr">
+      <c r="E320" s="14" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
     </row>
-    <row r="320">
-      <c r="A320" s="10" t="inlineStr">
+    <row r="321">
+      <c r="A321" s="10" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
         </is>
       </c>
-      <c r="B320" s="11" t="n"/>
-      <c r="C320" s="11" t="n"/>
-      <c r="D320" s="12" t="n"/>
-    </row>
-    <row r="321">
-      <c r="A321" s="4" t="n"/>
-      <c r="B321" s="4" t="inlineStr">
-        <is>
-          <t>Mobile responsive pass on every ported section</t>
-        </is>
-      </c>
-      <c r="C321" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D321" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid). Fixed 2026-10-09: the bar is now solid (bg-[#2C1810], was 92% plus backdrop-blur-md), so nothing can show through even where the blur isn't drawn; checked in WebKit (iPhone 13 profile) and Chrome: background rgb(44, 24, 16), no text behind the buttons. A real iPhone check is still part of Phase 14.</t>
-        </is>
-      </c>
-      <c r="E321" s="14" t="inlineStr">
-        <is>
-          <t>Phase 14 — QA &amp; Launch</t>
-        </is>
-      </c>
+      <c r="B321" s="11" t="n"/>
+      <c r="C321" s="11" t="n"/>
+      <c r="D321" s="12" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="4" t="n"/>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>Accessibility pass (WCAG AA contrast, 44px touch targets, keyboard nav)</t>
-        </is>
-      </c>
-      <c r="C322" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Mobile responsive pass on every ported section</t>
+        </is>
+      </c>
+      <c r="C322" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy QA_MASTER_PROMPT.md. 2026-09-29 axe-core pass (WCAG 2.1 AA, same 114 pages, production build): all unlabeled dropdowns/inputs and unnamed links fixed; contrast down from 1,453 failing items on 106 pages to 1,038 on 70 (43 pages fully clean). Shared fixes: brand gold #8b6914 → #836311 site-wide (was 4.3:1 on cream, AA needs 4.5), header "⌘K"/social icons, BrewSoul nav and footer, HumanOS footer, Kava footer, assessment intro footnote, post-card image links. 2026-09-30: contrast finished, 0 axe color-contrast failures left on the same 114 pages (production build). Token changes: --kava-saffron #b86a28 → #8e521f, --pri-purple-light #a855f7 → #b87bf9 (on-dark purple only), --crusade-teal #0e7c7c → #0d7373; PriEyebrow goes light purple inside a dark PriSection via group-data-dark/pri; /find-your-me and the journey tracker's dark glass panels 60-70% → 90% (legacy's own 60% glass on beige rendered gray, cream text failed). Everything else: nearest passing shade of the same hue, or gold ↔ gold-light on the wrong background. Left: 18 links inside text marked only by color (need an underline), 44px tap targets, keyboard nav. 2026-09-30: 18 color-only in-text links underlined (axe link-in-text-block: 0 left); keyboard focus visible on every focusable item on 8 sampled pages (two form fields had none, fixed). 2026-10-02 re-run (axe WCAG 2.2 AA, 142 pages × 375/1280px, production build, plus Tab through 40 stops per page): found 1,370 contrast failures (mostly BrewSoul'</t>
+          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid). Fixed 2026-10-09: the bar is now solid (bg-[#2C1810], was 92% plus backdrop-blur-md), so nothing can show through even where the blur isn't drawn; checked in WebKit (iPhone 13 profile) and Chrome: background rgb(44, 24, 16), no text behind the buttons. A real iPhone check is still part of Phase 14.</t>
         </is>
       </c>
       <c r="E322" s="14" t="inlineStr">
@@ -8233,17 +8233,17 @@
       <c r="A323" s="4" t="n"/>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>No dead-end pages (every page links to 2+ others)</t>
-        </is>
-      </c>
-      <c r="C323" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Accessibility pass (WCAG AA contrast, 44px touch targets, keyboard nav)</t>
+        </is>
+      </c>
+      <c r="C323" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
+          <t>same bar as legacy QA_MASTER_PROMPT.md. 2026-09-29 axe-core pass (WCAG 2.1 AA, same 114 pages, production build): all unlabeled dropdowns/inputs and unnamed links fixed; contrast down from 1,453 failing items on 106 pages to 1,038 on 70 (43 pages fully clean). Shared fixes: brand gold #8b6914 → #836311 site-wide (was 4.3:1 on cream, AA needs 4.5), header "⌘K"/social icons, BrewSoul nav and footer, HumanOS footer, Kava footer, assessment intro footnote, post-card image links. 2026-09-30: contrast finished, 0 axe color-contrast failures left on the same 114 pages (production build). Token changes: --kava-saffron #b86a28 → #8e521f, --pri-purple-light #a855f7 → #b87bf9 (on-dark purple only), --crusade-teal #0e7c7c → #0d7373; PriEyebrow goes light purple inside a dark PriSection via group-data-dark/pri; /find-your-me and the journey tracker's dark glass panels 60-70% → 90% (legacy's own 60% glass on beige rendered gray, cream text failed). Everything else: nearest passing shade of the same hue, or gold ↔ gold-light on the wrong background. Left: 18 links inside text marked only by color (need an underline), 44px tap targets, keyboard nav. 2026-09-30: 18 color-only in-text links underlined (axe link-in-text-block: 0 left); keyboard focus visible on every focusable item on 8 sampled pages (two form fields had none, fixed). 2026-10-02 re-run (axe WCAG 2.2 AA, 142 pages × 375/1280px, production build, plus Tab through 40 stops per page): found 1,370 contrast failures (mostly BrewSoul'</t>
         </is>
       </c>
       <c r="E323" s="14" t="inlineStr">
@@ -8256,7 +8256,7 @@
       <c r="A324" s="4" t="n"/>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
+          <t>No dead-end pages (every page links to 2+ others)</t>
         </is>
       </c>
       <c r="C324" s="15" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="D324" s="4" t="inlineStr">
         <is>
-          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
+          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
         </is>
       </c>
       <c r="E324" s="14" t="inlineStr">
@@ -8279,7 +8279,7 @@
       <c r="A325" s="4" t="n"/>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>Remove noindex only when sign-off is given</t>
+          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
         </is>
       </c>
       <c r="C325" s="15" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
         </is>
       </c>
       <c r="E325" s="14" t="inlineStr">
@@ -8302,7 +8302,7 @@
       <c r="A326" s="4" t="n"/>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
+          <t>Remove noindex only when sign-off is given</t>
         </is>
       </c>
       <c r="C326" s="15" t="inlineStr">
@@ -8310,7 +8310,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D326" s="4" t="inlineStr"/>
+      <c r="D326" s="4" t="inlineStr">
+        <is>
+          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+        </is>
+      </c>
       <c r="E326" s="14" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
@@ -8321,7 +8325,7 @@
       <c r="A327" s="4" t="n"/>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
         </is>
       </c>
       <c r="C327" s="15" t="inlineStr">
@@ -8336,21 +8340,40 @@
         </is>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" s="4" t="n"/>
+      <c r="B328" s="4" t="inlineStr">
+        <is>
+          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+        </is>
+      </c>
+      <c r="C328" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D328" s="4" t="inlineStr"/>
+      <c r="E328" s="14" t="inlineStr">
+        <is>
+          <t>Phase 14 — QA &amp; Launch</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D327"/>
+  <autoFilter ref="A1:D328"/>
   <mergeCells count="14">
     <mergeCell ref="A150:D150"/>
-    <mergeCell ref="A320:D320"/>
+    <mergeCell ref="A321:D321"/>
     <mergeCell ref="A237:D237"/>
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A258:D258"/>
     <mergeCell ref="A209:D209"/>
     <mergeCell ref="A205:D205"/>
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A301:D301"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A183:D183"/>
-    <mergeCell ref="A300:D300"/>
     <mergeCell ref="A32:D32"/>
     <mergeCell ref="A123:D123"/>
   </mergeCells>
@@ -8364,7 +8387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8602,7 +8625,7 @@
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Still different from live (needs a yes)</t>
+          <t>Lighthouse pass (performance/accessibility/SEO) on top 20 pages by traffic 2026-09-30, 20 key pages (no traffic data yet), local production …</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -8612,7 +8635,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>blog posts (done) (done 2026-10-07, see Phase 5); /find-my on live hides the site header. /walk-through is a 404 on live now.</t>
+          <t>build, mobile: averages performance 87, accessibility 99→100, best practices 100, SEO 92→100, CLS 0 everywhere. Fixed: public/robots.txt had an LLMs: line (not a real directive) that made Google treat the whole file as invalid, now a comment; h3/h4 headings skipping a level on /assessments, /kava, /peptide-watch (same look, right tag); the Kava and /attention-theft back-arrow links had no accessible name on phones; two small phone-width contrast misses. Left: performance is local-machine only (±10-15 points, see CONTRIBUTING.md); the slowest were / 76 (LCP 5.2 s), /psychedelic-readiness-index 82, /iboga-ibogaine 83. Re-run against the Netlify deploy before launch. 2026-10-06 re-run against the Netlify deploy (14 key pages, mobile): accessibility 100 and CLS 0 on every page, SEO clean (only the expected netlify.app noindex), performance 77-97 held back by 3-4 s LCP. Fixed: all 21 hero images moved off the deprecated priority prop to fetchPriority="high" + loading="eager" (Next 16); /iboga-ibogaine hero and the first card on /blog and category pages no longer lazy-loaded; sizes on the Four Doors cards (~150 KiB per page), /humanos diagram (~100 KiB) and /about headshot; urlFor no longer imports the Sanity client, so ~115 KB of Sanity client code stopped loading on / and /blog; React hydration error #418 on / and /blog (post dates) gone, checked in two time zones; /blog is static again; empty icon &lt;th&gt;s on /iboga-ibogaine labelled; category page reads use sanityFetch(). Left: se</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -8625,7 +8648,7 @@
       <c r="A14" s="4" t="n"/>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Design change on live, needs a decision</t>
+          <t>SEO audit items needing a yes (2026-10-06)</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -8635,7 +8658,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>live's story pages now use Cormorant Garamond for titles (ours: Playfair Display), a lighter title weight (400 vs our 700), and a red eyebrow label (#8E1E25, wider letter spacing) instead of our gold. A site-wide font swap is a design call, so not done.</t>
+          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -8648,7 +8671,7 @@
       <c r="A15" s="4" t="n"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Lighthouse pass (performance/accessibility/SEO) on top 20 pages by traffic 2026-09-30, 20 key pages (no traffic data yet), local production …</t>
+          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -8656,11 +8679,7 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>build, mobile: averages performance 87, accessibility 99→100, best practices 100, SEO 92→100, CLS 0 everywhere. Fixed: public/robots.txt had an LLMs: line (not a real directive) that made Google treat the whole file as invalid, now a comment; h3/h4 headings skipping a level on /assessments, /kava, /peptide-watch (same look, right tag); the Kava and /attention-theft back-arrow links had no accessible name on phones; two small phone-width contrast misses. Left: performance is local-machine only (±10-15 points, see CONTRIBUTING.md); the slowest were / 76 (LCP 5.2 s), /psychedelic-readiness-index 82, /iboga-ibogaine 83. Re-run against the Netlify deploy before launch. 2026-10-06 re-run against the Netlify deploy (14 key pages, mobile): accessibility 100 and CLS 0 on every page, SEO clean (only the expected netlify.app noindex), performance 77-97 held back by 3-4 s LCP. Fixed: all 21 hero images moved off the deprecated priority prop to fetchPriority="high" + loading="eager" (Next 16); /iboga-ibogaine hero and the first card on /blog and category pages no longer lazy-loaded; sizes on the Four Doors cards (~150 KiB per page), /humanos diagram (~100 KiB) and /about headshot; urlFor no longer imports the Sanity client, so ~115 KB of Sanity client code stopped loading on / and /blog; React hydration error #418 on / and /blog (post dates) gone, checked in two time zones; /blog is static again; empty icon &lt;th&gt;s on /iboga-ibogaine labelled; category page reads use sanityFetch(). Left: se</t>
-        </is>
-      </c>
+      <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -8668,33 +8687,20 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>SEO audit items needing a yes (2026-10-06)</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
-        </is>
-      </c>
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Phase 13 — Images Needed in Sanity</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -8702,28 +8708,45 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
+        </is>
+      </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
+          <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>92 posts still need a real, unique hero image</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
+          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -8733,7 +8756,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
+          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -8743,33 +8766,20 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>92 posts still need a real, unique hero image</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>Phase 13 — Images Needed in Sanity</t>
-        </is>
-      </c>
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Phase 14 — QA &amp; Launch</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
+          <t>Mobile responsive pass on every ported section</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -8779,30 +8789,43 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
+          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid). Fixed 2026-10-09: the bar is now solid (bg-[#2C1810], was 92% plus backdrop-blur-md), so nothing can show through even where the blur isn't drawn; checked in WebKit (iPhone 13 profile) and Chrome: background rgb(44, 24, 16), no text behind the buttons. A real iPhone check is still part of Phase 14.</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>Phase 13 — Images Needed in Sanity</t>
+          <t>Phase 14 — QA &amp; Launch</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>No dead-end pages (every page links to 2+ others)</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Mobile responsive pass on every ported section</t>
+          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
@@ -8812,7 +8835,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid). Fixed 2026-10-09: the bar is now solid (bg-[#2C1810], was 92% plus backdrop-blur-md), so nothing can show through even where the blur isn't drawn; checked in WebKit (iPhone 13 profile) and Chrome: background rgb(44, 24, 16), no text behind the buttons. A real iPhone check is still part of Phase 14.</t>
+          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -8825,7 +8848,7 @@
       <c r="A24" s="4" t="n"/>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>No dead-end pages (every page links to 2+ others)</t>
+          <t>Remove noindex only when sign-off is given</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -8835,7 +8858,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
+          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
@@ -8848,7 +8871,7 @@
       <c r="A25" s="4" t="n"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
+          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
@@ -8856,11 +8879,7 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
-        </is>
-      </c>
+      <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="14" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
@@ -8871,7 +8890,7 @@
       <c r="A26" s="4" t="n"/>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Remove noindex only when sign-off is given</t>
+          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -8879,64 +8898,22 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
-        </is>
-      </c>
+      <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="14" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>Phase 14 — QA &amp; Launch</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Phase 14 — QA &amp; Launch</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D28"/>
+  <autoFilter ref="A1:D26"/>
   <mergeCells count="6">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A22:D22"/>
     <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A16:D16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Migration-Status-Report.xlsx
+++ b/Migration-Status-Report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Remaining Work" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$329</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Remaining Work'!$A$1:$D$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -639,15 +639,15 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A5,'Full Detail'!$C$2:$C$328,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A5,'Full Detail'!$C$2:$C$329,"Done")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A5,'Full Detail'!$C$2:$C$328,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A5,'Full Detail'!$C$2:$C$329,"Remaining")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A5,'Full Detail'!$C$2:$C$328,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A5,'Full Detail'!$C$2:$C$329,"Deferred")</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -666,15 +666,15 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A6,'Full Detail'!$C$2:$C$328,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A6,'Full Detail'!$C$2:$C$329,"Done")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A6,'Full Detail'!$C$2:$C$328,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A6,'Full Detail'!$C$2:$C$329,"Remaining")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A6,'Full Detail'!$C$2:$C$328,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A6,'Full Detail'!$C$2:$C$329,"Deferred")</f>
         <v/>
       </c>
       <c r="E6" s="5">
@@ -693,15 +693,15 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A7,'Full Detail'!$C$2:$C$328,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A7,'Full Detail'!$C$2:$C$329,"Done")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A7,'Full Detail'!$C$2:$C$328,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A7,'Full Detail'!$C$2:$C$329,"Remaining")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A7,'Full Detail'!$C$2:$C$328,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A7,'Full Detail'!$C$2:$C$329,"Deferred")</f>
         <v/>
       </c>
       <c r="E7" s="5">
@@ -720,15 +720,15 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A8,'Full Detail'!$C$2:$C$328,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A8,'Full Detail'!$C$2:$C$329,"Done")</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A8,'Full Detail'!$C$2:$C$328,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A8,'Full Detail'!$C$2:$C$329,"Remaining")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A8,'Full Detail'!$C$2:$C$328,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A8,'Full Detail'!$C$2:$C$329,"Deferred")</f>
         <v/>
       </c>
       <c r="E8" s="5">
@@ -747,15 +747,15 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A9,'Full Detail'!$C$2:$C$328,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A9,'Full Detail'!$C$2:$C$329,"Done")</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A9,'Full Detail'!$C$2:$C$328,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A9,'Full Detail'!$C$2:$C$329,"Remaining")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A9,'Full Detail'!$C$2:$C$328,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A9,'Full Detail'!$C$2:$C$329,"Deferred")</f>
         <v/>
       </c>
       <c r="E9" s="5">
@@ -774,15 +774,15 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A10,'Full Detail'!$C$2:$C$328,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A10,'Full Detail'!$C$2:$C$329,"Done")</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A10,'Full Detail'!$C$2:$C$328,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A10,'Full Detail'!$C$2:$C$329,"Remaining")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A10,'Full Detail'!$C$2:$C$328,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A10,'Full Detail'!$C$2:$C$329,"Deferred")</f>
         <v/>
       </c>
       <c r="E10" s="5">
@@ -801,15 +801,15 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A11,'Full Detail'!$C$2:$C$328,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A11,'Full Detail'!$C$2:$C$329,"Done")</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A11,'Full Detail'!$C$2:$C$328,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A11,'Full Detail'!$C$2:$C$329,"Remaining")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A11,'Full Detail'!$C$2:$C$328,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A11,'Full Detail'!$C$2:$C$329,"Deferred")</f>
         <v/>
       </c>
       <c r="E11" s="5">
@@ -828,15 +828,15 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A12,'Full Detail'!$C$2:$C$328,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A12,'Full Detail'!$C$2:$C$329,"Done")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A12,'Full Detail'!$C$2:$C$328,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A12,'Full Detail'!$C$2:$C$329,"Remaining")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A12,'Full Detail'!$C$2:$C$328,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A12,'Full Detail'!$C$2:$C$329,"Deferred")</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -855,15 +855,15 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A13,'Full Detail'!$C$2:$C$328,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A13,'Full Detail'!$C$2:$C$329,"Done")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A13,'Full Detail'!$C$2:$C$328,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A13,'Full Detail'!$C$2:$C$329,"Remaining")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A13,'Full Detail'!$C$2:$C$328,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A13,'Full Detail'!$C$2:$C$329,"Deferred")</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -882,15 +882,15 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A14,'Full Detail'!$C$2:$C$328,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A14,'Full Detail'!$C$2:$C$329,"Done")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A14,'Full Detail'!$C$2:$C$328,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A14,'Full Detail'!$C$2:$C$329,"Remaining")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A14,'Full Detail'!$C$2:$C$328,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A14,'Full Detail'!$C$2:$C$329,"Deferred")</f>
         <v/>
       </c>
       <c r="E14" s="5">
@@ -909,15 +909,15 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A15,'Full Detail'!$C$2:$C$328,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A15,'Full Detail'!$C$2:$C$329,"Done")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A15,'Full Detail'!$C$2:$C$328,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A15,'Full Detail'!$C$2:$C$329,"Remaining")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A15,'Full Detail'!$C$2:$C$328,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A15,'Full Detail'!$C$2:$C$329,"Deferred")</f>
         <v/>
       </c>
       <c r="E15" s="5">
@@ -936,15 +936,15 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A16,'Full Detail'!$C$2:$C$328,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A16,'Full Detail'!$C$2:$C$329,"Done")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A16,'Full Detail'!$C$2:$C$328,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A16,'Full Detail'!$C$2:$C$329,"Remaining")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A16,'Full Detail'!$C$2:$C$328,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A16,'Full Detail'!$C$2:$C$329,"Deferred")</f>
         <v/>
       </c>
       <c r="E16" s="5">
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A17,'Full Detail'!$C$2:$C$328,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A17,'Full Detail'!$C$2:$C$329,"Done")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A17,'Full Detail'!$C$2:$C$328,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A17,'Full Detail'!$C$2:$C$329,"Remaining")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A17,'Full Detail'!$C$2:$C$328,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A17,'Full Detail'!$C$2:$C$329,"Deferred")</f>
         <v/>
       </c>
       <c r="E17" s="5">
@@ -990,15 +990,15 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A18,'Full Detail'!$C$2:$C$328,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A18,'Full Detail'!$C$2:$C$329,"Done")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A18,'Full Detail'!$C$2:$C$328,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A18,'Full Detail'!$C$2:$C$329,"Remaining")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A18,'Full Detail'!$C$2:$C$328,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A18,'Full Detail'!$C$2:$C$329,"Deferred")</f>
         <v/>
       </c>
       <c r="E18" s="5">
@@ -1017,15 +1017,15 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A19,'Full Detail'!$C$2:$C$328,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A19,'Full Detail'!$C$2:$C$329,"Done")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A19,'Full Detail'!$C$2:$C$328,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A19,'Full Detail'!$C$2:$C$329,"Remaining")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$328,$A19,'Full Detail'!$C$2:$C$328,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A19,'Full Detail'!$C$2:$C$329,"Deferred")</f>
         <v/>
       </c>
       <c r="E19" s="5">
@@ -1075,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E328"/>
+  <dimension ref="A1:E329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7366,7 +7366,7 @@
       <c r="A284" s="4" t="n"/>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>Arrows in buttons and links are icons (2026-10-09, owner said yes)</t>
+          <t>Owner answers, round 2 (2026-10-09)</t>
         </is>
       </c>
       <c r="C284" s="13" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>113 typed arrows in 52 files (button and link labels, "Next"/"See My Results" toggles, decorative arrow spans, the walk-through "See the..." labels, the Letter's "I'm in" button) replaced with lucide ArrowRight/ArrowLeft (size-[1em], inside inline-flex items-center gap-1.5, so the parent layout is untouched). Left as content on purpose: arrows inside Tony's text and data (health findings, origins, iboga compass options, process flows like "Inherit → Wake → Choose → Act", share text), the "← you" marker on the consciousness scale, and &lt;option&gt; sort labels (an option can't hold an icon). Checked on 16 pages at 375 and 1280: no typed arrow left in any link or button, no sideways scroll, no JS errors; close-up screenshots of the new icons.</t>
+          <t>(1) real counts instead of live's typed numbers: /charity-scorecard intro and description ("98"/"Ninety-eight" → STATS.totalCharities = 103), /impact-dashboard ("100" → passed in from the page so the browser doesn't load the charity list), /the-index (prop), search directory coffees 103 → 107 (typed, with a note, since it ships to the search pop-up); (2) The Mirror results no longer list the 4 *.manus.space apps (the "Explore further" section hides when empty); (3) /framework's "Ask FauxTony" button and its lead-in line removed; the Dr. Lee case-file link (4 places in when-healing-becomes-extraction, original and updated versions) renders as plain text through a DEAD_INTERNAL_LINKS list in lib/sanity/portable-text.tsx (no Sanity draft needed); (4) B Corp: checked live, nothing shown on either site, no change. Verified on a production build: the counts read 103, /framework has no FauxTony block, the essay has 0 links to the case file and keeps the words, /the-index shows "103 charities" when searching "charity".</t>
         </is>
       </c>
       <c r="E284" s="14" t="inlineStr">
@@ -7389,7 +7389,7 @@
       <c r="A285" s="4" t="n"/>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Category pages pre-built (2026-10-09)</t>
+          <t>Arrows in buttons and links are icons (2026-10-09, owner said yes)</t>
         </is>
       </c>
       <c r="C285" s="13" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>/blog/category/[slug] read ?page=N, so every category page was rendered on each request (slower first byte, flagged in the Lighthouse notes). Page numbers are now part of the address (/blog/category/&lt;slug&gt;/page/&lt;n&gt;, generateStaticParams, dynamicParams = false), shared code in src/components/blog/category-listing.tsx; old ?page=N links 308 to the new address (pages 2+ only, so no loop), /page/1 308s to the plain address, a page past the end is a 404; "All essays" back link uses an icon. Verified on a production build: route table shows every category page as pre-built (9 page-1s, 7 later pages), titles and canonicals per page, Previous/Next links, the redirects and the 404s.</t>
+          <t>113 typed arrows in 52 files (button and link labels, "Next"/"See My Results" toggles, decorative arrow spans, the walk-through "See the..." labels, the Letter's "I'm in" button) replaced with lucide ArrowRight/ArrowLeft (size-[1em], inside inline-flex items-center gap-1.5, so the parent layout is untouched). Left as content on purpose: arrows inside Tony's text and data (health findings, origins, iboga compass options, process flows like "Inherit → Wake → Choose → Act", share text), the "← you" marker on the consciousness scale, and &lt;option&gt; sort labels (an option can't hold an icon). Checked on 16 pages at 375 and 1280: no typed arrow left in any link or button, no sideways scroll, no JS errors; close-up screenshots of the new icons.</t>
         </is>
       </c>
       <c r="E285" s="14" t="inlineStr">
@@ -7412,7 +7412,7 @@
       <c r="A286" s="4" t="n"/>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>Error pages (2026-10-09, owner asked)</t>
+          <t>Category pages pre-built (2026-10-09)</t>
         </is>
       </c>
       <c r="C286" s="13" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>404 page now sets its own title ("Page not found") as a server page around live's 3-second redirect (not-found.tsx + components/not-found-redirect.tsx), arrow as an icon; page error screen (error.tsx) uses Next 16's retry (re-fetches), shows a reference code for the server logs, links home and to the site index; new global-error.tsx for failures in the root layout itself (own &lt;html&gt;, plain links). Verified on a production build: missing page, missing essay and missing Kava page return 404 with the right title; a test page that throws returns 500 with the error screen, "Try again" re-fetches; phone and laptop, no sideways scroll (test page removed).</t>
+          <t>/blog/category/[slug] read ?page=N, so every category page was rendered on each request (slower first byte, flagged in the Lighthouse notes). Page numbers are now part of the address (/blog/category/&lt;slug&gt;/page/&lt;n&gt;, generateStaticParams, dynamicParams = false), shared code in src/components/blog/category-listing.tsx; old ?page=N links 308 to the new address (pages 2+ only, so no loop), /page/1 308s to the plain address, a page past the end is a 404; "All essays" back link uses an icon. Verified on a production build: route table shows every category page as pre-built (9 page-1s, 7 later pages), titles and canonicals per page, Previous/Next links, the redirects and the 404s.</t>
         </is>
       </c>
       <c r="E286" s="14" t="inlineStr">
@@ -7435,7 +7435,7 @@
       <c r="A287" s="4" t="n"/>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>SEO audit fixes (2026-10-06)</t>
+          <t>Error pages (2026-10-09, owner asked)</t>
         </is>
       </c>
       <c r="C287" s="13" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
+          <t>404 page now sets its own title ("Page not found") as a server page around live's 3-second redirect (not-found.tsx + components/not-found-redirect.tsx), arrow as an icon; page error screen (error.tsx) uses Next 16's retry (re-fetches), shows a reference code for the server logs, links home and to the site index; new global-error.tsx for failures in the root layout itself (own &lt;html&gt;, plain links). Verified on a production build: missing page, missing essay and missing Kava page return 404 with the right title; a test page that throws returns 500 with the error screen, "Try again" re-fetches; phone and laptop, no sideways scroll (test page removed).</t>
         </is>
       </c>
       <c r="E287" s="14" t="inlineStr">
@@ -7458,17 +7458,17 @@
       <c r="A288" s="4" t="n"/>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>SEO audit items needing a yes (2026-10-06)</t>
-        </is>
-      </c>
-      <c r="C288" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>SEO audit fixes (2026-10-06)</t>
+        </is>
+      </c>
+      <c r="C288" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+          <t>Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
         </is>
       </c>
       <c r="E288" s="14" t="inlineStr">
@@ -7481,7 +7481,7 @@
       <c r="A289" s="4" t="n"/>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+          <t>SEO audit items needing a yes (2026-10-06)</t>
         </is>
       </c>
       <c r="C289" s="15" t="inlineStr">
@@ -7489,7 +7489,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D289" s="4" t="inlineStr"/>
+      <c r="D289" s="4" t="inlineStr">
+        <is>
+          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+        </is>
+      </c>
       <c r="E289" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -7500,19 +7504,15 @@
       <c r="A290" s="4" t="n"/>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
-        </is>
-      </c>
-      <c r="C290" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D290" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
-        </is>
-      </c>
+          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+        </is>
+      </c>
+      <c r="C290" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D290" s="4" t="inlineStr"/>
       <c r="E290" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -7523,7 +7523,7 @@
       <c r="A291" s="4" t="n"/>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>"Keep going" strip above the footer on every page (2026-10-07)</t>
+          <t>Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
         </is>
       </c>
       <c r="C291" s="13" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>legacy's WhereNext (deferred in Phase 3, never picked up) with its per-page suggestions, Home · Site Index · All Assessments; links pointed at current routes.</t>
+          <t>2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
         </is>
       </c>
       <c r="E291" s="14" t="inlineStr">
@@ -7546,7 +7546,7 @@
       <c r="A292" s="4" t="n"/>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>Live-only and redesigned pages from the 2026-10-07 page sweep (188 pages compared with live)</t>
+          <t>"Keep going" strip above the footer on every page (2026-10-07)</t>
         </is>
       </c>
       <c r="C292" s="13" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>/the-index rebuilt from live's code (20 concepts, related-word search across essays and site pages, full-text search on the server, "three related places to go next"; the old redirect to /search removed and its links, including the "Site Index" link in "Keep going", point at it again); /the-mirror (and /life-assessment) opens on live's intro (dark hero, "What We Measure" with the six areas, "The Ecosystem"), rebuilt as a step registry (rule 19); /essays header, order and column like live; /about "What They Say" styled like live (live picks 3 of the same 19 quotes at random; ours shows a fixed 3 so they're in the server HTML); /impact-futurism list titles and subtitles; /supplier-intake is a real page again with live's Stage 1 form; /seven-doors and /projects redirect home like live; /impact, /health, /library, /built-on-manus, /heroes are 404 on live too. Left as is on purpose: /blog stays our archive page (on live it repeats the homepage), the email gates on /framework and /peptide-supply-chain, the attention-theft Wall of Shame.</t>
+          <t>legacy's WhereNext (deferred in Phase 3, never picked up) with its per-page suggestions, Home · Site Index · All Assessments; links pointed at current routes.</t>
         </is>
       </c>
       <c r="E292" s="14" t="inlineStr">
@@ -7569,7 +7569,7 @@
       <c r="A293" s="4" t="n"/>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>/alex-azzi locked like live (2026-10-07, owner said match it)</t>
+          <t>Live-only and redesigned pages from the 2026-10-07 page sweep (188 pages compared with live)</t>
         </is>
       </c>
       <c r="C293" s="13" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>same server-checked password as the locked essay (GATED_POST_PASSWORD, now also set in Netlify), live's "Restricted Access" screen, the report not in the page until unlocked, out of search and the sitemap.</t>
+          <t>/the-index rebuilt from live's code (20 concepts, related-word search across essays and site pages, full-text search on the server, "three related places to go next"; the old redirect to /search removed and its links, including the "Site Index" link in "Keep going", point at it again); /the-mirror (and /life-assessment) opens on live's intro (dark hero, "What We Measure" with the six areas, "The Ecosystem"), rebuilt as a step registry (rule 19); /essays header, order and column like live; /about "What They Say" styled like live (live picks 3 of the same 19 quotes at random; ours shows a fixed 3 so they're in the server HTML); /impact-futurism list titles and subtitles; /supplier-intake is a real page again with live's Stage 1 form; /seven-doors and /projects redirect home like live; /impact, /health, /library, /built-on-manus, /heroes are 404 on live too. Left as is on purpose: /blog stays our archive page (on live it repeats the homepage), the email gates on /framework and /peptide-supply-chain, the attention-theft Wall of Shame.</t>
         </is>
       </c>
       <c r="E293" s="14" t="inlineStr">
@@ -7592,7 +7592,7 @@
       <c r="A294" s="4" t="n"/>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Live's title fonts and sizes (2026-10-07, "fix the style")</t>
+          <t>/alex-azzi locked like live (2026-10-07, owner said match it)</t>
         </is>
       </c>
       <c r="C294" s="13" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>measured every page's title font, weight, size and label colour on live vs ours (136 pages). Now like live: Kava headings in Fraunces, HumanOS in Space Grotesk, the peptide tools / charity scorecard / thesis threads in the system serif, America Unbundled in the Iowan Old Style stack at live's size, /akbar in Fraunces 900, friend-gate and post-intervention in Georgia, and live's title sizes on peptide-matrix, peptide-supply-chain, rip-peptide-sciences and the HumanOS pages. Fonts load only on the pages that use them (src/lib/fonts/page-fonts.ts). Label colours stay the darker AA-contrast versions where live's lighter ones fail on a light background.</t>
+          <t>same server-checked password as the locked essay (GATED_POST_PASSWORD, now also set in Netlify), live's "Restricted Access" screen, the report not in the page until unlocked, out of search and the sitemap.</t>
         </is>
       </c>
       <c r="E294" s="14" t="inlineStr">
@@ -7615,7 +7615,7 @@
       <c r="A295" s="4" t="n"/>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Peptide page images rescued into Sanity and wired (2026-10-07)</t>
+          <t>Live's title fonts and sizes (2026-10-07, "fix the style")</t>
         </is>
       </c>
       <c r="C295" s="13" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>/peptide-watch hero plus its 11 section banners, /peptide-matrix and /peptide-supply-chain heroes, the /peptide-hall-of-shame hero (scripts/rescue-2026-10-07-peptide-images.ts, logged in docs/ai/manus-media-rescue.md).</t>
+          <t>measured every page's title font, weight, size and label colour on live vs ours (136 pages). Now like live: Kava headings in Fraunces, HumanOS in Space Grotesk, the peptide tools / charity scorecard / thesis threads in the system serif, America Unbundled in the Iowan Old Style stack at live's size, /akbar in Fraunces 900, friend-gate and post-intervention in Georgia, and live's title sizes on peptide-matrix, peptide-supply-chain, rip-peptide-sciences and the HumanOS pages. Fonts load only on the pages that use them (src/lib/fonts/page-fonts.ts). Label colours stay the darker AA-contrast versions where live's lighter ones fail on a light background.</t>
         </is>
       </c>
       <c r="E295" s="14" t="inlineStr">
@@ -7638,7 +7638,7 @@
       <c r="A296" s="4" t="n"/>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>Live's editorial redesign, first group (2026-10-07)</t>
+          <t>Peptide page images rescued into Sanity and wired (2026-10-07)</t>
         </is>
       </c>
       <c r="C296" s="13" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
+          <t>/peptide-watch hero plus its 11 section banners, /peptide-matrix and /peptide-supply-chain heroes, the /peptide-hall-of-shame hero (scripts/rescue-2026-10-07-peptide-images.ts, logged in docs/ai/manus-media-rescue.md).</t>
         </is>
       </c>
       <c r="E296" s="14" t="inlineStr">
@@ -7661,7 +7661,7 @@
       <c r="A297" s="4" t="n"/>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Live's redesign, second group (done 2026-10-08)</t>
+          <t>Live's editorial redesign, first group (2026-10-07)</t>
         </is>
       </c>
       <c r="C297" s="13" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>re-measured all 18 pages on live vs a fresh production build (title font/size/weight/colour, labels, hero images). Already matching from 2026-10-07: /the-web, /spirits, /iboga-ibogaine (weight 800), /living-declaration, BrewSoul photo on /brewsoul, /brewsoul/browse, /brewsoul/first-sip (live has none there either), /quiz_25q, /recent-creations. Fixed today: /find-your-journey (64px title, red label), /impact-dashboard (64px title in essay ink, label spacing), red labels on /published and /speaking (plus its "rooms" chips), /soulscore "by ImpactSoul" label, /pri-calibration title (weight 900, solid cream, was a purple gradient), /clients (live's narrow 546px column for the whole page, 56px title, roomier stats band, cards 2 per row; two static inline styles moved to classes), /brewsoul/guest (live's BrewSoul photo on the guest card instead of "SN" initials, labels in capitals), /humanos/connect (cards line up with the title), /peptide-hall-of-shame (stats and label readable light gold; were dark gold on dark). Typed arrows on the touched links are icons now (rule 18). Deliberately not copied from live (new CONTRIBUTING rule 20, owner 2026-10-08): red labels on dark bands use #E07A80 (live's #8E1E25 on black is about 2:1, unreadable); /recent-creations keeps our darker label colours (live's fail contrast on white); /humanos/connect keeps "Start Reading" (that card links to the philosophy page, the quiz live's "Start the Assessment" implies doesn't exist). Checked: type check, l</t>
+          <t>dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
         </is>
       </c>
       <c r="E297" s="14" t="inlineStr">
@@ -7684,7 +7684,7 @@
       <c r="A298" s="4" t="n"/>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>BrewSoul top of page (2026-10-08, owner: "button in the center at the top doesn't look good")</t>
+          <t>Live's redesign, second group (done 2026-10-08)</t>
         </is>
       </c>
       <c r="C298" s="13" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>the category badge ("Deep Research" etc.) sat centred in an empty strip, squeezed against the hero, because we copied live's doubled 52px top gap. Now one gap everywhere and the badge floats in the top-left corner, lined up with the BrewSoul logo (brewsoul-main.tsx, category-badge.tsx); checked on all 26 badge pages at 3 widths that it covers nothing. BrewSoul menu: on tablets (768-1023px) the links were cut off and "More" was hidden with no menu button at all; now the menu button shows below 1024px, 5 links + "More" from 1024px, all 8 from 1280px, "More" always visible.</t>
+          <t>re-measured all 18 pages on live vs a fresh production build (title font/size/weight/colour, labels, hero images). Already matching from 2026-10-07: /the-web, /spirits, /iboga-ibogaine (weight 800), /living-declaration, BrewSoul photo on /brewsoul, /brewsoul/browse, /brewsoul/first-sip (live has none there either), /quiz_25q, /recent-creations. Fixed today: /find-your-journey (64px title, red label), /impact-dashboard (64px title in essay ink, label spacing), red labels on /published and /speaking (plus its "rooms" chips), /soulscore "by ImpactSoul" label, /pri-calibration title (weight 900, solid cream, was a purple gradient), /clients (live's narrow 546px column for the whole page, 56px title, roomier stats band, cards 2 per row; two static inline styles moved to classes), /brewsoul/guest (live's BrewSoul photo on the guest card instead of "SN" initials, labels in capitals), /humanos/connect (cards line up with the title), /peptide-hall-of-shame (stats and label readable light gold; were dark gold on dark). Typed arrows on the touched links are icons now (rule 18). Deliberately not copied from live (new CONTRIBUTING rule 20, owner 2026-10-08): red labels on dark bands use #E07A80 (live's #8E1E25 on black is about 2:1, unreadable); /recent-creations keeps our darker label colours (live's fail contrast on white); /humanos/connect keeps "Start Reading" (that card links to the philosophy page, the quiz live's "Start the Assessment" implies doesn't exist). Checked: type check, l</t>
         </is>
       </c>
       <c r="E298" s="14" t="inlineStr">
@@ -7707,7 +7707,7 @@
       <c r="A299" s="4" t="n"/>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>/pri-efficacy's "Simulation / Live Calibrations" switch like live (2026-10-08)</t>
+          <t>BrewSoul top of page (2026-10-08, owner: "button in the center at the top doesn't look good")</t>
         </is>
       </c>
       <c r="C299" s="13" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>shadcn Tabs, both panels in the server HTML (forceMount). The Live tab reads real aggregate numbers from pri_calibrations (getPriLiveStats() in src/lib/pri-research.ts: totals, opt-ins, average score per dimension; no rows leave the server), page stays static and refreshes every 10 minutes. Until the Supabase scripts are run (Phase 2) it says the numbers "aren't available just now" instead of a fake zero. Checked: build (○, 10m), server HTML has both tabs, tab switch at 390/1280px, no JS errors. Re-check with real numbers once the table exists.</t>
+          <t>the category badge ("Deep Research" etc.) sat centred in an empty strip, squeezed against the hero, because we copied live's doubled 52px top gap. Now one gap everywhere and the badge floats in the top-left corner, lined up with the BrewSoul logo (brewsoul-main.tsx, category-badge.tsx); checked on all 26 badge pages at 3 widths that it covers nothing. BrewSoul menu: on tablets (768-1023px) the links were cut off and "More" was hidden with no menu button at all; now the menu button shows below 1024px, 5 links + "More" from 1024px, all 8 from 1280px, "More" always visible.</t>
         </is>
       </c>
       <c r="E299" s="14" t="inlineStr">
@@ -7730,63 +7730,63 @@
       <c r="A300" s="4" t="n"/>
       <c r="B300" s="4" t="inlineStr">
         <is>
+          <t>/pri-efficacy's "Simulation / Live Calibrations" switch like live (2026-10-08)</t>
+        </is>
+      </c>
+      <c r="C300" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="inlineStr">
+        <is>
+          <t>shadcn Tabs, both panels in the server HTML (forceMount). The Live tab reads real aggregate numbers from pri_calibrations (getPriLiveStats() in src/lib/pri-research.ts: totals, opt-ins, average score per dimension; no rows leave the server), page stays static and refreshes every 10 minutes. Until the Supabase scripts are run (Phase 2) it says the numbers "aren't available just now" instead of a fake zero. Checked: build (○, 10m), server HTML has both tabs, tab switch at 390/1280px, no JS errors. Re-check with real numbers once the table exists.</t>
+        </is>
+      </c>
+      <c r="E300" s="14" t="inlineStr">
+        <is>
+          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="4" t="n"/>
+      <c r="B301" s="4" t="inlineStr">
+        <is>
           <t>/brewsoul/browse hero readable (2026-10-08, owner said go ahead)</t>
         </is>
       </c>
-      <c r="C300" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D300" s="4" t="inlineStr">
+      <c r="C301" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D301" s="4" t="inlineStr">
         <is>
           <t>a soft cream glow behind the title block so "The Catalog", the subtitle and the stat labels read clearly over the coffee photo (live is hard to read there too; rule 20). Photo still shows around the edges. Checked at 390/1280px.</t>
         </is>
       </c>
-      <c r="E300" s="14" t="inlineStr">
+      <c r="E301" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
         </is>
       </c>
     </row>
-    <row r="301">
-      <c r="A301" s="10" t="inlineStr">
+    <row r="302">
+      <c r="A302" s="10" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
-      <c r="B301" s="11" t="n"/>
-      <c r="C301" s="11" t="n"/>
-      <c r="D301" s="12" t="n"/>
-    </row>
-    <row r="302">
-      <c r="A302" s="4" t="n"/>
-      <c r="B302" s="4" t="inlineStr">
-        <is>
-          <t>Manus media rescue (2026-09-29)</t>
-        </is>
-      </c>
-      <c r="C302" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D302" s="4" t="inlineStr">
-        <is>
-          <t>all 94 Manus-hosted image/video references in the legacy source (/api/img/, /manus-storage/) were checked live. 91 were still downloadable, including the /akbar photos the entry below calls "permanently lost", and all 91 are now Sanity assets (scripts/rescue-manus-media.ts; Sanity dedupes by SHA-1). 3 were gone (HTTP 502). The manifest docs/ai/manus-media-rescue.md maps each one to the legacy files that used it and its Sanity URL. They are not wired into pages yet: go page by page, with real alt text. /facilitator-index's two diagrams are done (scripts/rescue-facilitator-images.ts).</t>
-        </is>
-      </c>
-      <c r="E302" s="14" t="inlineStr">
-        <is>
-          <t>Phase 13 — Images Needed in Sanity</t>
-        </is>
-      </c>
+      <c r="B302" s="11" t="n"/>
+      <c r="C302" s="11" t="n"/>
+      <c r="D302" s="12" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="4" t="n"/>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Favicon</t>
+          <t>Manus media rescue (2026-09-29)</t>
         </is>
       </c>
       <c r="C303" s="13" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>real "G" brand mark generated from the header's actual wordmark treatment (src/app/icon.tsx), see Phase 3</t>
+          <t>all 94 Manus-hosted image/video references in the legacy source (/api/img/, /manus-storage/) were checked live. 91 were still downloadable, including the /akbar photos the entry below calls "permanently lost", and all 91 are now Sanity assets (scripts/rescue-manus-media.ts; Sanity dedupes by SHA-1). 3 were gone (HTTP 502). The manifest docs/ai/manus-media-rescue.md maps each one to the legacy files that used it and its Sanity URL. They are not wired into pages yet: go page by page, with real alt text. /facilitator-index's two diagrams are done (scripts/rescue-facilitator-images.ts).</t>
         </is>
       </c>
       <c r="E303" s="14" t="inlineStr">
@@ -7809,17 +7809,17 @@
       <c r="A304" s="4" t="n"/>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
-        </is>
-      </c>
-      <c r="C304" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Favicon</t>
+        </is>
+      </c>
+      <c r="C304" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
+          <t>real "G" brand mark generated from the header's actual wordmark treatment (src/app/icon.tsx), see Phase 3</t>
         </is>
       </c>
       <c r="E304" s="14" t="inlineStr">
@@ -7832,17 +7832,17 @@
       <c r="A305" s="4" t="n"/>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Author photo(s) for blog author schema (Tony Greenberg headshot at minimum)</t>
-        </is>
-      </c>
-      <c r="C305" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
+        </is>
+      </c>
+      <c r="C305" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: the rescued headshot is already the author avatar in Sanity; now also in every post's Article JSON-LD (author image + url /about). The JSON-LD publisher logo pointed at /favicon.ico, a 404 here; now /icon.</t>
+          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
         </is>
       </c>
       <c r="E305" s="14" t="inlineStr">
@@ -7855,7 +7855,7 @@
       <c r="A306" s="4" t="n"/>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>Blog hero images</t>
+          <t>Author photo(s) for blog author schema (Tony Greenberg headshot at minimum)</t>
         </is>
       </c>
       <c r="C306" s="13" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>audited, then migrated. Final state:</t>
+          <t>2026-10-02: the rescued headshot is already the author avatar in Sanity; now also in every post's Article JSON-LD (author image + url /about). The JSON-LD publisher logo pointed at /favicon.ico, a 404 here; now /icon.</t>
         </is>
       </c>
       <c r="E306" s="14" t="inlineStr">
@@ -7878,7 +7878,7 @@
       <c r="A307" s="4" t="n"/>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>22 posts have a real hero image, now live in Sanity (17 already on RampRate's own CloudFront + 4 rescued from the legacy /api/img/ proxy + 1…</t>
+          <t>Blog hero images</t>
         </is>
       </c>
       <c r="C307" s="13" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> rescued from /manus-storage/, all pulled over by migrate-blog-posts.ts before Manus is decommissioned)</t>
+          <t>audited, then migrated. Final state:</t>
         </is>
       </c>
       <c r="E307" s="14" t="inlineStr">
@@ -7901,7 +7901,7 @@
       <c r="A308" s="4" t="n"/>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>7 more posts got a real, unique hero image rescued from the live legacy site's newly-added art this pass (scripts/rescue-2026-09-blog-images…</t>
+          <t>22 posts have a real hero image, now live in Sanity (17 already on RampRate's own CloudFront + 4 rescued from the legacy /api/img/ proxy + 1…</t>
         </is>
       </c>
       <c r="C308" s="13" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>.ts — see the correction note above): california-toll-roads-legalized-scam, the-1000-hour-hold, conscious-capital-partnership-ecosystem, the-peptide-truth-65m-fraud-industry-vs-life-changing-medicine, clear-communication, building-services-market-transhuman-era, heart-protocol-addendum.</t>
+          <t xml:space="preserve"> rescued from /manus-storage/, all pulled over by migrate-blog-posts.ts before Manus is decommissioned)</t>
         </is>
       </c>
       <c r="E308" s="14" t="inlineStr">
@@ -7924,17 +7924,17 @@
       <c r="A309" s="4" t="n"/>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>92 posts still need a real, unique hero image</t>
-        </is>
-      </c>
-      <c r="C309" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>7 more posts got a real, unique hero image rescued from the live legacy site's newly-added art this pass (scripts/rescue-2026-09-blog-images…</t>
+        </is>
+      </c>
+      <c r="C309" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
+          <t>.ts — see the correction note above): california-toll-roads-legalized-scam, the-1000-hour-hold, conscious-capital-partnership-ecosystem, the-peptide-truth-65m-fraud-industry-vs-life-changing-medicine, clear-communication, building-services-market-transhuman-era, heart-protocol-addendum.</t>
         </is>
       </c>
       <c r="E309" s="14" t="inlineStr">
@@ -7947,17 +7947,17 @@
       <c r="A310" s="4" t="n"/>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>Blog: per-post OG image if different from hero (many posts can reuse hero as OG)</t>
-        </is>
-      </c>
-      <c r="C310" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>92 posts still need a real, unique hero image</t>
+        </is>
+      </c>
+      <c r="C310" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>Confirmed 2026-10-02: generateMetadata uses seo.ogImage, else the hero, else the default OG image.</t>
+          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
         </is>
       </c>
       <c r="E310" s="14" t="inlineStr">
@@ -7970,7 +7970,7 @@
       <c r="A311" s="4" t="n"/>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Marketing pages</t>
+          <t>Blog: per-post OG image if different from hero (many posts can reuse hero as OG)</t>
         </is>
       </c>
       <c r="C311" s="13" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>hero/section images for /the-letter, /the-territory, /engine-room, /the-body, /the-nightstand, /recent-creations (portfolio thumbnails), /published (publication logos), /clients (client logos — confirm licensing before re-hosting). Checked against live 2026-10-02: same image count on every one; /the-territory, /engine-room, /recent-creations, /published, /clients have no images on live either.</t>
+          <t>Confirmed 2026-10-02: generateMetadata uses seo.ogImage, else the hero, else the default OG image.</t>
         </is>
       </c>
       <c r="E311" s="14" t="inlineStr">
@@ -7993,7 +7993,7 @@
       <c r="A312" s="4" t="n"/>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>/akbar essay images</t>
+          <t>Marketing pages</t>
         </is>
       </c>
       <c r="C312" s="13" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>not lost after all: 20 of the 21 were rescued into Sanity by scripts/rescue-manus-media.ts (2026-09-28) and are wired back in legacy's layout (hero mosaic, JC portrait, 2x2 grid, 3 full-bleeds, 3-up strip, footer gallery) as of 2026-09-29. Only slider-3 was gone (HTTP 502); the hero mosaic is 4 tiles instead of 5.</t>
+          <t>hero/section images for /the-letter, /the-territory, /engine-room, /the-body, /the-nightstand, /recent-creations (portfolio thumbnails), /published (publication logos), /clients (client logos — confirm licensing before re-hosting). Checked against live 2026-10-02: same image count on every one; /the-territory, /engine-room, /recent-creations, /published, /clients have no images on live either.</t>
         </is>
       </c>
       <c r="E312" s="14" t="inlineStr">
@@ -8016,7 +8016,7 @@
       <c r="A313" s="4" t="n"/>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Rescued page images wired back in (2026-09-29)</t>
+          <t>/akbar essay images</t>
         </is>
       </c>
       <c r="C313" s="13" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>/living-declaration hero, hand image and Clarisse Abelarde artwork; /impact-dashboard earth hero; /find-my banner; /find-your-coffee dark photo landing (legacy copy restored, replacing an intro that wasn't in legacy). Also wired (second pass): /consciousness-scale (legacy's hero-first flow restored, the invented intro screen removed), /find-your-me hero, /humanos hero, the HumanOS nav logo, and all 12 HumanOS people headshots (/humanos/ecosystem, /humanos/philosophy). Blog-body images (2026-09-29): all 19 the migration dropped are restored by scripts/restore-blog-body-images.ts as Sanity drafts on 4 posts (Clarisse Abelarde 7, You Are the Moat 4, FRQNCY 6, Energy Is Money 2), waiting to be published in Studio; the other blog-listed assets were heroes already set. Still unwired from docs/ai/manus-media-rescue.md: and /alex-azzi's subject photo (a photo of a real person on an accusation page: needs Tony's yes first).</t>
+          <t>not lost after all: 20 of the 21 were rescued into Sanity by scripts/rescue-manus-media.ts (2026-09-28) and are wired back in legacy's layout (hero mosaic, JC portrait, 2x2 grid, 3 full-bleeds, 3-up strip, footer gallery) as of 2026-09-29. Only slider-3 was gone (HTTP 502); the hero mosaic is 4 tiles instead of 5.</t>
         </is>
       </c>
       <c r="E313" s="14" t="inlineStr">
@@ -8039,7 +8039,7 @@
       <c r="A314" s="4" t="n"/>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>BrewSoul: coffee/product images (brewsoul-coffees-expanded.ts likely has image refs</t>
+          <t>Rescued page images wired back in (2026-09-29)</t>
         </is>
       </c>
       <c r="C314" s="13" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>audit), city guide header images, roaster directory photos. Audited 2026-09-09 (status spreadsheet), confirmed 2026-10-02: city guides already have photos; coffees, chains and roasters have no image field in legacy or here (text-only by design); farms got real photos.</t>
+          <t>/living-declaration hero, hand image and Clarisse Abelarde artwork; /impact-dashboard earth hero; /find-my banner; /find-your-coffee dark photo landing (legacy copy restored, replacing an intro that wasn't in legacy). Also wired (second pass): /consciousness-scale (legacy's hero-first flow restored, the invented intro screen removed), /find-your-me hero, /humanos hero, the HumanOS nav logo, and all 12 HumanOS people headshots (/humanos/ecosystem, /humanos/philosophy). Blog-body images (2026-09-29): all 19 the migration dropped are restored by scripts/restore-blog-body-images.ts as Sanity drafts on 4 posts (Clarisse Abelarde 7, You Are the Moat 4, FRQNCY 6, Energy Is Money 2), waiting to be published in Studio; the other blog-listed assets were heroes already set. Still unwired from docs/ai/manus-media-rescue.md: and /alex-azzi's subject photo (a photo of a real person on an accusation page: needs Tony's yes first).</t>
         </is>
       </c>
       <c r="E314" s="14" t="inlineStr">
@@ -8062,7 +8062,7 @@
       <c r="A315" s="4" t="n"/>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>65 page images moved off the Manus storage copy into Sanity (2026-10-02)</t>
+          <t>BrewSoul: coffee/product images (brewsoul-coffees-expanded.ts likely has image refs</t>
         </is>
       </c>
       <c r="C315" s="13" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>every image the code loaded from d2xsxph8kpxj0f.cloudfront.net (PRI medicine images, Iboga module, facilitator index, /attention-theft, /alex-azzi, /protecting-your-business, /peyote-mescaline, HumanOS, the peptide quiz). Notes called it "RampRate's own CloudFront", but every file sits in the legacy Manus project's folder and its owner couldn't be confirmed. All 65 uploaded (scripts/rescue-cloudfront-images.ts), code rewritten, host removed from images.remotePatterns, no Sanity document used it. Table in docs/ai/manus-media-rescue.md.</t>
+          <t>audit), city guide header images, roaster directory photos. Audited 2026-09-09 (status spreadsheet), confirmed 2026-10-02: city guides already have photos; coffees, chains and roasters have no image field in legacy or here (text-only by design); farms got real photos.</t>
         </is>
       </c>
       <c r="E315" s="14" t="inlineStr">
@@ -8085,7 +8085,7 @@
       <c r="A316" s="4" t="n"/>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>PRI/Kava: medicine reference images (medicine-images.ts), facility images for /facilitator-index</t>
+          <t>65 page images moved off the Manus storage copy into Sanity (2026-10-02)</t>
         </is>
       </c>
       <c r="C316" s="13" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="D316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: all in Sanity; image counts match live on PRI, Kava, Iboga, Peyote, facilitator pages.</t>
+          <t>every image the code loaded from d2xsxph8kpxj0f.cloudfront.net (PRI medicine images, Iboga module, facilitator index, /attention-theft, /alex-azzi, /protecting-your-business, /peyote-mescaline, HumanOS, the peptide quiz). Notes called it "RampRate's own CloudFront", but every file sits in the legacy Manus project's folder and its owner couldn't be confirmed. All 65 uploaded (scripts/rescue-cloudfront-images.ts), code rewritten, host removed from images.remotePatterns, no Sanity document used it. Table in docs/ai/manus-media-rescue.md.</t>
         </is>
       </c>
       <c r="E316" s="14" t="inlineStr">
@@ -8108,7 +8108,7 @@
       <c r="A317" s="4" t="n"/>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>Manifesto/Attention Theft: any diagram/illustration assets used on the mega-page</t>
+          <t>PRI/Kava: medicine reference images (medicine-images.ts), facility images for /facilitator-index</t>
         </is>
       </c>
       <c r="C317" s="13" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: 6 of live's 7 are in (now in Sanity); the 7th belongs to the Wall of Shame section left out on purpose.</t>
+          <t>2026-10-02: all in Sanity; image counts match live on PRI, Kava, Iboga, Peyote, facilitator pages.</t>
         </is>
       </c>
       <c r="E317" s="14" t="inlineStr">
@@ -8131,17 +8131,17 @@
       <c r="A318" s="4" t="n"/>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
-        </is>
-      </c>
-      <c r="C318" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Manifesto/Attention Theft: any diagram/illustration assets used on the mega-page</t>
+        </is>
+      </c>
+      <c r="C318" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
         <is>
-          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
+          <t>2026-10-02: 6 of live's 7 are in (now in Sanity); the 7th belongs to the Wall of Shame section left out on purpose.</t>
         </is>
       </c>
       <c r="E318" s="14" t="inlineStr">
@@ -8154,17 +8154,17 @@
       <c r="A319" s="4" t="n"/>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Chatbot: FauxTony avatar/icon</t>
-        </is>
-      </c>
-      <c r="C319" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
+        </is>
+      </c>
+      <c r="C319" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>Not needed (2026-10-02): the chatbot phase (Phase 10) was cancelled.</t>
+          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
         </is>
       </c>
       <c r="E319" s="14" t="inlineStr">
@@ -8177,73 +8177,73 @@
       <c r="A320" s="4" t="n"/>
       <c r="B320" s="4" t="inlineStr">
         <is>
+          <t>Chatbot: FauxTony avatar/icon</t>
+        </is>
+      </c>
+      <c r="C320" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D320" s="4" t="inlineStr">
+        <is>
+          <t>Not needed (2026-10-02): the chatbot phase (Phase 10) was cancelled.</t>
+        </is>
+      </c>
+      <c r="E320" s="14" t="inlineStr">
+        <is>
+          <t>Phase 13 — Images Needed in Sanity</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="4" t="n"/>
+      <c r="B321" s="4" t="inlineStr">
+        <is>
           <t>Audit client/public/ (including alex-azzi/, brewsoul/ subfolders) for any static assets already sitting there unused that should be pulled i…</t>
         </is>
       </c>
-      <c r="C320" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D320" s="4" t="inlineStr">
+      <c r="C321" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D321" s="4" t="inlineStr">
         <is>
           <t>n rather than re-created. Done 2026-10-02: no images there at all (only llms.txt, a BrewSoul catalog, Manus debug files, design-options.html). Found and fixed a cutover risk instead: live serves two Google site-verification files (/google6881a0411c48b301.html, /alex-azzi/googleedff0185753a4a1f.html) that the new site returned 404 for, so Search Console could lose verification at DNS cutover. Both copied to public/ byte for byte. Not copied: site.webmanifest (its icons don't exist here; Next's app/icon.tsx covers the favicon).</t>
         </is>
       </c>
-      <c r="E320" s="14" t="inlineStr">
+      <c r="E321" s="14" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
     </row>
-    <row r="321">
-      <c r="A321" s="10" t="inlineStr">
+    <row r="322">
+      <c r="A322" s="10" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
         </is>
       </c>
-      <c r="B321" s="11" t="n"/>
-      <c r="C321" s="11" t="n"/>
-      <c r="D321" s="12" t="n"/>
-    </row>
-    <row r="322">
-      <c r="A322" s="4" t="n"/>
-      <c r="B322" s="4" t="inlineStr">
-        <is>
-          <t>Mobile responsive pass on every ported section</t>
-        </is>
-      </c>
-      <c r="C322" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D322" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid). Fixed 2026-10-09: the bar is now solid (bg-[#2C1810], was 92% plus backdrop-blur-md), so nothing can show through even where the blur isn't drawn; checked in WebKit (iPhone 13 profile) and Chrome: background rgb(44, 24, 16), no text behind the buttons. A real iPhone check is still part of Phase 14.</t>
-        </is>
-      </c>
-      <c r="E322" s="14" t="inlineStr">
-        <is>
-          <t>Phase 14 — QA &amp; Launch</t>
-        </is>
-      </c>
+      <c r="B322" s="11" t="n"/>
+      <c r="C322" s="11" t="n"/>
+      <c r="D322" s="12" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="4" t="n"/>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>Accessibility pass (WCAG AA contrast, 44px touch targets, keyboard nav)</t>
-        </is>
-      </c>
-      <c r="C323" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Mobile responsive pass on every ported section</t>
+        </is>
+      </c>
+      <c r="C323" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy QA_MASTER_PROMPT.md. 2026-09-29 axe-core pass (WCAG 2.1 AA, same 114 pages, production build): all unlabeled dropdowns/inputs and unnamed links fixed; contrast down from 1,453 failing items on 106 pages to 1,038 on 70 (43 pages fully clean). Shared fixes: brand gold #8b6914 → #836311 site-wide (was 4.3:1 on cream, AA needs 4.5), header "⌘K"/social icons, BrewSoul nav and footer, HumanOS footer, Kava footer, assessment intro footnote, post-card image links. 2026-09-30: contrast finished, 0 axe color-contrast failures left on the same 114 pages (production build). Token changes: --kava-saffron #b86a28 → #8e521f, --pri-purple-light #a855f7 → #b87bf9 (on-dark purple only), --crusade-teal #0e7c7c → #0d7373; PriEyebrow goes light purple inside a dark PriSection via group-data-dark/pri; /find-your-me and the journey tracker's dark glass panels 60-70% → 90% (legacy's own 60% glass on beige rendered gray, cream text failed). Everything else: nearest passing shade of the same hue, or gold ↔ gold-light on the wrong background. Left: 18 links inside text marked only by color (need an underline), 44px tap targets, keyboard nav. 2026-09-30: 18 color-only in-text links underlined (axe link-in-text-block: 0 left); keyboard focus visible on every focusable item on 8 sampled pages (two form fields had none, fixed). 2026-10-02 re-run (axe WCAG 2.2 AA, 142 pages × 375/1280px, production build, plus Tab through 40 stops per page): found 1,370 contrast failures (mostly BrewSoul'</t>
+          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid). Fixed 2026-10-09: the bar is now solid (bg-[#2C1810], was 92% plus backdrop-blur-md), so nothing can show through even where the blur isn't drawn; checked in WebKit (iPhone 13 profile) and Chrome: background rgb(44, 24, 16), no text behind the buttons. A real iPhone check is still part of Phase 14.</t>
         </is>
       </c>
       <c r="E323" s="14" t="inlineStr">
@@ -8256,17 +8256,17 @@
       <c r="A324" s="4" t="n"/>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>No dead-end pages (every page links to 2+ others)</t>
-        </is>
-      </c>
-      <c r="C324" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Accessibility pass (WCAG AA contrast, 44px touch targets, keyboard nav)</t>
+        </is>
+      </c>
+      <c r="C324" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
+          <t>same bar as legacy QA_MASTER_PROMPT.md. 2026-09-29 axe-core pass (WCAG 2.1 AA, same 114 pages, production build): all unlabeled dropdowns/inputs and unnamed links fixed; contrast down from 1,453 failing items on 106 pages to 1,038 on 70 (43 pages fully clean). Shared fixes: brand gold #8b6914 → #836311 site-wide (was 4.3:1 on cream, AA needs 4.5), header "⌘K"/social icons, BrewSoul nav and footer, HumanOS footer, Kava footer, assessment intro footnote, post-card image links. 2026-09-30: contrast finished, 0 axe color-contrast failures left on the same 114 pages (production build). Token changes: --kava-saffron #b86a28 → #8e521f, --pri-purple-light #a855f7 → #b87bf9 (on-dark purple only), --crusade-teal #0e7c7c → #0d7373; PriEyebrow goes light purple inside a dark PriSection via group-data-dark/pri; /find-your-me and the journey tracker's dark glass panels 60-70% → 90% (legacy's own 60% glass on beige rendered gray, cream text failed). Everything else: nearest passing shade of the same hue, or gold ↔ gold-light on the wrong background. Left: 18 links inside text marked only by color (need an underline), 44px tap targets, keyboard nav. 2026-09-30: 18 color-only in-text links underlined (axe link-in-text-block: 0 left); keyboard focus visible on every focusable item on 8 sampled pages (two form fields had none, fixed). 2026-10-02 re-run (axe WCAG 2.2 AA, 142 pages × 375/1280px, production build, plus Tab through 40 stops per page): found 1,370 contrast failures (mostly BrewSoul'</t>
         </is>
       </c>
       <c r="E324" s="14" t="inlineStr">
@@ -8279,7 +8279,7 @@
       <c r="A325" s="4" t="n"/>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
+          <t>No dead-end pages (every page links to 2+ others)</t>
         </is>
       </c>
       <c r="C325" s="15" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
+          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
         </is>
       </c>
       <c r="E325" s="14" t="inlineStr">
@@ -8302,7 +8302,7 @@
       <c r="A326" s="4" t="n"/>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>Remove noindex only when sign-off is given</t>
+          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
         </is>
       </c>
       <c r="C326" s="15" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
         </is>
       </c>
       <c r="E326" s="14" t="inlineStr">
@@ -8325,7 +8325,7 @@
       <c r="A327" s="4" t="n"/>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
+          <t>Remove noindex only when sign-off is given</t>
         </is>
       </c>
       <c r="C327" s="15" t="inlineStr">
@@ -8333,7 +8333,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D327" s="4" t="inlineStr"/>
+      <c r="D327" s="4" t="inlineStr">
+        <is>
+          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+        </is>
+      </c>
       <c r="E327" s="14" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
@@ -8344,7 +8348,7 @@
       <c r="A328" s="4" t="n"/>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
         </is>
       </c>
       <c r="C328" s="15" t="inlineStr">
@@ -8359,18 +8363,37 @@
         </is>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" s="4" t="n"/>
+      <c r="B329" s="4" t="inlineStr">
+        <is>
+          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+        </is>
+      </c>
+      <c r="C329" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D329" s="4" t="inlineStr"/>
+      <c r="E329" s="14" t="inlineStr">
+        <is>
+          <t>Phase 14 — QA &amp; Launch</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D328"/>
+  <autoFilter ref="A1:D329"/>
   <mergeCells count="14">
     <mergeCell ref="A150:D150"/>
-    <mergeCell ref="A321:D321"/>
+    <mergeCell ref="A322:D322"/>
     <mergeCell ref="A237:D237"/>
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A258:D258"/>
     <mergeCell ref="A209:D209"/>
     <mergeCell ref="A205:D205"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A301:D301"/>
+    <mergeCell ref="A302:D302"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A183:D183"/>

--- a/Migration-Status-Report.xlsx
+++ b/Migration-Status-Report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Remaining Work" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$329</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$330</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Remaining Work'!$A$1:$D$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -639,15 +639,15 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A5,'Full Detail'!$C$2:$C$329,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A5,'Full Detail'!$C$2:$C$330,"Done")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A5,'Full Detail'!$C$2:$C$329,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A5,'Full Detail'!$C$2:$C$330,"Remaining")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A5,'Full Detail'!$C$2:$C$329,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A5,'Full Detail'!$C$2:$C$330,"Deferred")</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -666,15 +666,15 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A6,'Full Detail'!$C$2:$C$329,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A6,'Full Detail'!$C$2:$C$330,"Done")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A6,'Full Detail'!$C$2:$C$329,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A6,'Full Detail'!$C$2:$C$330,"Remaining")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A6,'Full Detail'!$C$2:$C$329,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A6,'Full Detail'!$C$2:$C$330,"Deferred")</f>
         <v/>
       </c>
       <c r="E6" s="5">
@@ -693,15 +693,15 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A7,'Full Detail'!$C$2:$C$329,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A7,'Full Detail'!$C$2:$C$330,"Done")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A7,'Full Detail'!$C$2:$C$329,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A7,'Full Detail'!$C$2:$C$330,"Remaining")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A7,'Full Detail'!$C$2:$C$329,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A7,'Full Detail'!$C$2:$C$330,"Deferred")</f>
         <v/>
       </c>
       <c r="E7" s="5">
@@ -720,15 +720,15 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A8,'Full Detail'!$C$2:$C$329,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A8,'Full Detail'!$C$2:$C$330,"Done")</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A8,'Full Detail'!$C$2:$C$329,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A8,'Full Detail'!$C$2:$C$330,"Remaining")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A8,'Full Detail'!$C$2:$C$329,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A8,'Full Detail'!$C$2:$C$330,"Deferred")</f>
         <v/>
       </c>
       <c r="E8" s="5">
@@ -747,15 +747,15 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A9,'Full Detail'!$C$2:$C$329,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A9,'Full Detail'!$C$2:$C$330,"Done")</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A9,'Full Detail'!$C$2:$C$329,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A9,'Full Detail'!$C$2:$C$330,"Remaining")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A9,'Full Detail'!$C$2:$C$329,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A9,'Full Detail'!$C$2:$C$330,"Deferred")</f>
         <v/>
       </c>
       <c r="E9" s="5">
@@ -774,15 +774,15 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A10,'Full Detail'!$C$2:$C$329,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A10,'Full Detail'!$C$2:$C$330,"Done")</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A10,'Full Detail'!$C$2:$C$329,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A10,'Full Detail'!$C$2:$C$330,"Remaining")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A10,'Full Detail'!$C$2:$C$329,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A10,'Full Detail'!$C$2:$C$330,"Deferred")</f>
         <v/>
       </c>
       <c r="E10" s="5">
@@ -801,15 +801,15 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A11,'Full Detail'!$C$2:$C$329,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A11,'Full Detail'!$C$2:$C$330,"Done")</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A11,'Full Detail'!$C$2:$C$329,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A11,'Full Detail'!$C$2:$C$330,"Remaining")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A11,'Full Detail'!$C$2:$C$329,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A11,'Full Detail'!$C$2:$C$330,"Deferred")</f>
         <v/>
       </c>
       <c r="E11" s="5">
@@ -828,15 +828,15 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A12,'Full Detail'!$C$2:$C$329,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A12,'Full Detail'!$C$2:$C$330,"Done")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A12,'Full Detail'!$C$2:$C$329,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A12,'Full Detail'!$C$2:$C$330,"Remaining")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A12,'Full Detail'!$C$2:$C$329,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A12,'Full Detail'!$C$2:$C$330,"Deferred")</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -855,15 +855,15 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A13,'Full Detail'!$C$2:$C$329,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A13,'Full Detail'!$C$2:$C$330,"Done")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A13,'Full Detail'!$C$2:$C$329,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A13,'Full Detail'!$C$2:$C$330,"Remaining")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A13,'Full Detail'!$C$2:$C$329,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A13,'Full Detail'!$C$2:$C$330,"Deferred")</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -882,15 +882,15 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A14,'Full Detail'!$C$2:$C$329,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A14,'Full Detail'!$C$2:$C$330,"Done")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A14,'Full Detail'!$C$2:$C$329,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A14,'Full Detail'!$C$2:$C$330,"Remaining")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A14,'Full Detail'!$C$2:$C$329,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A14,'Full Detail'!$C$2:$C$330,"Deferred")</f>
         <v/>
       </c>
       <c r="E14" s="5">
@@ -909,15 +909,15 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A15,'Full Detail'!$C$2:$C$329,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A15,'Full Detail'!$C$2:$C$330,"Done")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A15,'Full Detail'!$C$2:$C$329,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A15,'Full Detail'!$C$2:$C$330,"Remaining")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A15,'Full Detail'!$C$2:$C$329,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A15,'Full Detail'!$C$2:$C$330,"Deferred")</f>
         <v/>
       </c>
       <c r="E15" s="5">
@@ -936,15 +936,15 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A16,'Full Detail'!$C$2:$C$329,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A16,'Full Detail'!$C$2:$C$330,"Done")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A16,'Full Detail'!$C$2:$C$329,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A16,'Full Detail'!$C$2:$C$330,"Remaining")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A16,'Full Detail'!$C$2:$C$329,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A16,'Full Detail'!$C$2:$C$330,"Deferred")</f>
         <v/>
       </c>
       <c r="E16" s="5">
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A17,'Full Detail'!$C$2:$C$329,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A17,'Full Detail'!$C$2:$C$330,"Done")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A17,'Full Detail'!$C$2:$C$329,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A17,'Full Detail'!$C$2:$C$330,"Remaining")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A17,'Full Detail'!$C$2:$C$329,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A17,'Full Detail'!$C$2:$C$330,"Deferred")</f>
         <v/>
       </c>
       <c r="E17" s="5">
@@ -990,15 +990,15 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A18,'Full Detail'!$C$2:$C$329,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A18,'Full Detail'!$C$2:$C$330,"Done")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A18,'Full Detail'!$C$2:$C$329,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A18,'Full Detail'!$C$2:$C$330,"Remaining")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A18,'Full Detail'!$C$2:$C$329,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A18,'Full Detail'!$C$2:$C$330,"Deferred")</f>
         <v/>
       </c>
       <c r="E18" s="5">
@@ -1017,15 +1017,15 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A19,'Full Detail'!$C$2:$C$329,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A19,'Full Detail'!$C$2:$C$330,"Done")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A19,'Full Detail'!$C$2:$C$329,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A19,'Full Detail'!$C$2:$C$330,"Remaining")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$329,$A19,'Full Detail'!$C$2:$C$329,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A19,'Full Detail'!$C$2:$C$330,"Deferred")</f>
         <v/>
       </c>
       <c r="E19" s="5">
@@ -1075,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E329"/>
+  <dimension ref="A1:E330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7366,7 +7366,7 @@
       <c r="A284" s="4" t="n"/>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>Owner answers, round 2 (2026-10-09)</t>
+          <t>No Manus links anywhere (2026-10-09, owner: "drop them everywhere")</t>
         </is>
       </c>
       <c r="C284" s="13" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>(1) real counts instead of live's typed numbers: /charity-scorecard intro and description ("98"/"Ninety-eight" → STATS.totalCharities = 103), /impact-dashboard ("100" → passed in from the page so the browser doesn't load the charity list), /the-index (prop), search directory coffees 103 → 107 (typed, with a note, since it ships to the search pop-up); (2) The Mirror results no longer list the 4 *.manus.space apps (the "Explore further" section hides when empty); (3) /framework's "Ask FauxTony" button and its lead-in line removed; the Dr. Lee case-file link (4 places in when-healing-becomes-extraction, original and updated versions) renders as plain text through a DEAD_INTERNAL_LINKS list in lib/sanity/portable-text.tsx (no Sanity draft needed); (4) B Corp: checked live, nothing shown on either site, no change. Verified on a production build: the counts read 103, /framework has no FauxTony block, the essay has 0 links to the case file and keeps the words, /the-index shows "103 charities" when searching "charity".</t>
+          <t>every *.manus.space link removed from code and essays. Lists of "try this next" apps lose those entries (journey tracker, Find Your Me results and next steps, /find-my, search directory, Sake and Grant Study results, BrewSoul footer, The Mirror); The Magnetic Partner's and The Temple Keeper's next step now go to their first in-site assessment (/grant-study, /consciousness-scale); their empty "Find Your _" section hides itself; /recent-creations, /spirits and /ecosystem-map keep the cards, unlinked. Clarisse Abelarde now links to her own site clarisseartist.com (owner gave it) on /about and in essays. Essays: lib/sanity/portable-text.tsx rewrites tonygreenberg.manus.space/&lt;path&gt; to /&lt;path&gt;, clarisseart.manus.space to clarisseartist.com (same paths), and renders other Manus app links as plain text (no Sanity drafts). Verified on a production build: no clickable *.manus.space link in any page, no manus.space in any browser script; 13 affected pages load (200).</t>
         </is>
       </c>
       <c r="E284" s="14" t="inlineStr">
@@ -7389,7 +7389,7 @@
       <c r="A285" s="4" t="n"/>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Arrows in buttons and links are icons (2026-10-09, owner said yes)</t>
+          <t>Owner answers, round 2 (2026-10-09)</t>
         </is>
       </c>
       <c r="C285" s="13" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>113 typed arrows in 52 files (button and link labels, "Next"/"See My Results" toggles, decorative arrow spans, the walk-through "See the..." labels, the Letter's "I'm in" button) replaced with lucide ArrowRight/ArrowLeft (size-[1em], inside inline-flex items-center gap-1.5, so the parent layout is untouched). Left as content on purpose: arrows inside Tony's text and data (health findings, origins, iboga compass options, process flows like "Inherit → Wake → Choose → Act", share text), the "← you" marker on the consciousness scale, and &lt;option&gt; sort labels (an option can't hold an icon). Checked on 16 pages at 375 and 1280: no typed arrow left in any link or button, no sideways scroll, no JS errors; close-up screenshots of the new icons.</t>
+          <t>(1) real counts instead of live's typed numbers: /charity-scorecard intro and description ("98"/"Ninety-eight" → STATS.totalCharities = 103), /impact-dashboard ("100" → passed in from the page so the browser doesn't load the charity list), /the-index (prop), search directory coffees 103 → 107 (typed, with a note, since it ships to the search pop-up); (2) The Mirror results no longer list the 4 *.manus.space apps (the "Explore further" section hides when empty); (3) /framework's "Ask FauxTony" button and its lead-in line removed; the Dr. Lee case-file link (4 places in when-healing-becomes-extraction, original and updated versions) renders as plain text through a DEAD_INTERNAL_LINKS list in lib/sanity/portable-text.tsx (no Sanity draft needed); (4) B Corp: checked live, nothing shown on either site, no change. Verified on a production build: the counts read 103, /framework has no FauxTony block, the essay has 0 links to the case file and keeps the words, /the-index shows "103 charities" when searching "charity".</t>
         </is>
       </c>
       <c r="E285" s="14" t="inlineStr">
@@ -7412,7 +7412,7 @@
       <c r="A286" s="4" t="n"/>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>Category pages pre-built (2026-10-09)</t>
+          <t>Arrows in buttons and links are icons (2026-10-09, owner said yes)</t>
         </is>
       </c>
       <c r="C286" s="13" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>/blog/category/[slug] read ?page=N, so every category page was rendered on each request (slower first byte, flagged in the Lighthouse notes). Page numbers are now part of the address (/blog/category/&lt;slug&gt;/page/&lt;n&gt;, generateStaticParams, dynamicParams = false), shared code in src/components/blog/category-listing.tsx; old ?page=N links 308 to the new address (pages 2+ only, so no loop), /page/1 308s to the plain address, a page past the end is a 404; "All essays" back link uses an icon. Verified on a production build: route table shows every category page as pre-built (9 page-1s, 7 later pages), titles and canonicals per page, Previous/Next links, the redirects and the 404s.</t>
+          <t>113 typed arrows in 52 files (button and link labels, "Next"/"See My Results" toggles, decorative arrow spans, the walk-through "See the..." labels, the Letter's "I'm in" button) replaced with lucide ArrowRight/ArrowLeft (size-[1em], inside inline-flex items-center gap-1.5, so the parent layout is untouched). Left as content on purpose: arrows inside Tony's text and data (health findings, origins, iboga compass options, process flows like "Inherit → Wake → Choose → Act", share text), the "← you" marker on the consciousness scale, and &lt;option&gt; sort labels (an option can't hold an icon). Checked on 16 pages at 375 and 1280: no typed arrow left in any link or button, no sideways scroll, no JS errors; close-up screenshots of the new icons.</t>
         </is>
       </c>
       <c r="E286" s="14" t="inlineStr">
@@ -7435,7 +7435,7 @@
       <c r="A287" s="4" t="n"/>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Error pages (2026-10-09, owner asked)</t>
+          <t>Category pages pre-built (2026-10-09)</t>
         </is>
       </c>
       <c r="C287" s="13" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>404 page now sets its own title ("Page not found") as a server page around live's 3-second redirect (not-found.tsx + components/not-found-redirect.tsx), arrow as an icon; page error screen (error.tsx) uses Next 16's retry (re-fetches), shows a reference code for the server logs, links home and to the site index; new global-error.tsx for failures in the root layout itself (own &lt;html&gt;, plain links). Verified on a production build: missing page, missing essay and missing Kava page return 404 with the right title; a test page that throws returns 500 with the error screen, "Try again" re-fetches; phone and laptop, no sideways scroll (test page removed).</t>
+          <t>/blog/category/[slug] read ?page=N, so every category page was rendered on each request (slower first byte, flagged in the Lighthouse notes). Page numbers are now part of the address (/blog/category/&lt;slug&gt;/page/&lt;n&gt;, generateStaticParams, dynamicParams = false), shared code in src/components/blog/category-listing.tsx; old ?page=N links 308 to the new address (pages 2+ only, so no loop), /page/1 308s to the plain address, a page past the end is a 404; "All essays" back link uses an icon. Verified on a production build: route table shows every category page as pre-built (9 page-1s, 7 later pages), titles and canonicals per page, Previous/Next links, the redirects and the 404s.</t>
         </is>
       </c>
       <c r="E287" s="14" t="inlineStr">
@@ -7458,7 +7458,7 @@
       <c r="A288" s="4" t="n"/>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>SEO audit fixes (2026-10-06)</t>
+          <t>Error pages (2026-10-09, owner asked)</t>
         </is>
       </c>
       <c r="C288" s="13" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
+          <t>404 page now sets its own title ("Page not found") as a server page around live's 3-second redirect (not-found.tsx + components/not-found-redirect.tsx), arrow as an icon; page error screen (error.tsx) uses Next 16's retry (re-fetches), shows a reference code for the server logs, links home and to the site index; new global-error.tsx for failures in the root layout itself (own &lt;html&gt;, plain links). Verified on a production build: missing page, missing essay and missing Kava page return 404 with the right title; a test page that throws returns 500 with the error screen, "Try again" re-fetches; phone and laptop, no sideways scroll (test page removed).</t>
         </is>
       </c>
       <c r="E288" s="14" t="inlineStr">
@@ -7481,17 +7481,17 @@
       <c r="A289" s="4" t="n"/>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>SEO audit items needing a yes (2026-10-06)</t>
-        </is>
-      </c>
-      <c r="C289" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>SEO audit fixes (2026-10-06)</t>
+        </is>
+      </c>
+      <c r="C289" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+          <t>Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
         </is>
       </c>
       <c r="E289" s="14" t="inlineStr">
@@ -7504,7 +7504,7 @@
       <c r="A290" s="4" t="n"/>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+          <t>SEO audit items needing a yes (2026-10-06)</t>
         </is>
       </c>
       <c r="C290" s="15" t="inlineStr">
@@ -7512,7 +7512,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D290" s="4" t="inlineStr"/>
+      <c r="D290" s="4" t="inlineStr">
+        <is>
+          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+        </is>
+      </c>
       <c r="E290" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -7523,19 +7527,15 @@
       <c r="A291" s="4" t="n"/>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
-        </is>
-      </c>
-      <c r="C291" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D291" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
-        </is>
-      </c>
+          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+        </is>
+      </c>
+      <c r="C291" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D291" s="4" t="inlineStr"/>
       <c r="E291" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -7546,7 +7546,7 @@
       <c r="A292" s="4" t="n"/>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>"Keep going" strip above the footer on every page (2026-10-07)</t>
+          <t>Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
         </is>
       </c>
       <c r="C292" s="13" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>legacy's WhereNext (deferred in Phase 3, never picked up) with its per-page suggestions, Home · Site Index · All Assessments; links pointed at current routes.</t>
+          <t>2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
         </is>
       </c>
       <c r="E292" s="14" t="inlineStr">
@@ -7569,7 +7569,7 @@
       <c r="A293" s="4" t="n"/>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Live-only and redesigned pages from the 2026-10-07 page sweep (188 pages compared with live)</t>
+          <t>"Keep going" strip above the footer on every page (2026-10-07)</t>
         </is>
       </c>
       <c r="C293" s="13" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>/the-index rebuilt from live's code (20 concepts, related-word search across essays and site pages, full-text search on the server, "three related places to go next"; the old redirect to /search removed and its links, including the "Site Index" link in "Keep going", point at it again); /the-mirror (and /life-assessment) opens on live's intro (dark hero, "What We Measure" with the six areas, "The Ecosystem"), rebuilt as a step registry (rule 19); /essays header, order and column like live; /about "What They Say" styled like live (live picks 3 of the same 19 quotes at random; ours shows a fixed 3 so they're in the server HTML); /impact-futurism list titles and subtitles; /supplier-intake is a real page again with live's Stage 1 form; /seven-doors and /projects redirect home like live; /impact, /health, /library, /built-on-manus, /heroes are 404 on live too. Left as is on purpose: /blog stays our archive page (on live it repeats the homepage), the email gates on /framework and /peptide-supply-chain, the attention-theft Wall of Shame.</t>
+          <t>legacy's WhereNext (deferred in Phase 3, never picked up) with its per-page suggestions, Home · Site Index · All Assessments; links pointed at current routes.</t>
         </is>
       </c>
       <c r="E293" s="14" t="inlineStr">
@@ -7592,7 +7592,7 @@
       <c r="A294" s="4" t="n"/>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>/alex-azzi locked like live (2026-10-07, owner said match it)</t>
+          <t>Live-only and redesigned pages from the 2026-10-07 page sweep (188 pages compared with live)</t>
         </is>
       </c>
       <c r="C294" s="13" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>same server-checked password as the locked essay (GATED_POST_PASSWORD, now also set in Netlify), live's "Restricted Access" screen, the report not in the page until unlocked, out of search and the sitemap.</t>
+          <t>/the-index rebuilt from live's code (20 concepts, related-word search across essays and site pages, full-text search on the server, "three related places to go next"; the old redirect to /search removed and its links, including the "Site Index" link in "Keep going", point at it again); /the-mirror (and /life-assessment) opens on live's intro (dark hero, "What We Measure" with the six areas, "The Ecosystem"), rebuilt as a step registry (rule 19); /essays header, order and column like live; /about "What They Say" styled like live (live picks 3 of the same 19 quotes at random; ours shows a fixed 3 so they're in the server HTML); /impact-futurism list titles and subtitles; /supplier-intake is a real page again with live's Stage 1 form; /seven-doors and /projects redirect home like live; /impact, /health, /library, /built-on-manus, /heroes are 404 on live too. Left as is on purpose: /blog stays our archive page (on live it repeats the homepage), the email gates on /framework and /peptide-supply-chain, the attention-theft Wall of Shame.</t>
         </is>
       </c>
       <c r="E294" s="14" t="inlineStr">
@@ -7615,7 +7615,7 @@
       <c r="A295" s="4" t="n"/>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Live's title fonts and sizes (2026-10-07, "fix the style")</t>
+          <t>/alex-azzi locked like live (2026-10-07, owner said match it)</t>
         </is>
       </c>
       <c r="C295" s="13" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>measured every page's title font, weight, size and label colour on live vs ours (136 pages). Now like live: Kava headings in Fraunces, HumanOS in Space Grotesk, the peptide tools / charity scorecard / thesis threads in the system serif, America Unbundled in the Iowan Old Style stack at live's size, /akbar in Fraunces 900, friend-gate and post-intervention in Georgia, and live's title sizes on peptide-matrix, peptide-supply-chain, rip-peptide-sciences and the HumanOS pages. Fonts load only on the pages that use them (src/lib/fonts/page-fonts.ts). Label colours stay the darker AA-contrast versions where live's lighter ones fail on a light background.</t>
+          <t>same server-checked password as the locked essay (GATED_POST_PASSWORD, now also set in Netlify), live's "Restricted Access" screen, the report not in the page until unlocked, out of search and the sitemap.</t>
         </is>
       </c>
       <c r="E295" s="14" t="inlineStr">
@@ -7638,7 +7638,7 @@
       <c r="A296" s="4" t="n"/>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>Peptide page images rescued into Sanity and wired (2026-10-07)</t>
+          <t>Live's title fonts and sizes (2026-10-07, "fix the style")</t>
         </is>
       </c>
       <c r="C296" s="13" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>/peptide-watch hero plus its 11 section banners, /peptide-matrix and /peptide-supply-chain heroes, the /peptide-hall-of-shame hero (scripts/rescue-2026-10-07-peptide-images.ts, logged in docs/ai/manus-media-rescue.md).</t>
+          <t>measured every page's title font, weight, size and label colour on live vs ours (136 pages). Now like live: Kava headings in Fraunces, HumanOS in Space Grotesk, the peptide tools / charity scorecard / thesis threads in the system serif, America Unbundled in the Iowan Old Style stack at live's size, /akbar in Fraunces 900, friend-gate and post-intervention in Georgia, and live's title sizes on peptide-matrix, peptide-supply-chain, rip-peptide-sciences and the HumanOS pages. Fonts load only on the pages that use them (src/lib/fonts/page-fonts.ts). Label colours stay the darker AA-contrast versions where live's lighter ones fail on a light background.</t>
         </is>
       </c>
       <c r="E296" s="14" t="inlineStr">
@@ -7661,7 +7661,7 @@
       <c r="A297" s="4" t="n"/>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Live's editorial redesign, first group (2026-10-07)</t>
+          <t>Peptide page images rescued into Sanity and wired (2026-10-07)</t>
         </is>
       </c>
       <c r="C297" s="13" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
+          <t>/peptide-watch hero plus its 11 section banners, /peptide-matrix and /peptide-supply-chain heroes, the /peptide-hall-of-shame hero (scripts/rescue-2026-10-07-peptide-images.ts, logged in docs/ai/manus-media-rescue.md).</t>
         </is>
       </c>
       <c r="E297" s="14" t="inlineStr">
@@ -7684,7 +7684,7 @@
       <c r="A298" s="4" t="n"/>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>Live's redesign, second group (done 2026-10-08)</t>
+          <t>Live's editorial redesign, first group (2026-10-07)</t>
         </is>
       </c>
       <c r="C298" s="13" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>re-measured all 18 pages on live vs a fresh production build (title font/size/weight/colour, labels, hero images). Already matching from 2026-10-07: /the-web, /spirits, /iboga-ibogaine (weight 800), /living-declaration, BrewSoul photo on /brewsoul, /brewsoul/browse, /brewsoul/first-sip (live has none there either), /quiz_25q, /recent-creations. Fixed today: /find-your-journey (64px title, red label), /impact-dashboard (64px title in essay ink, label spacing), red labels on /published and /speaking (plus its "rooms" chips), /soulscore "by ImpactSoul" label, /pri-calibration title (weight 900, solid cream, was a purple gradient), /clients (live's narrow 546px column for the whole page, 56px title, roomier stats band, cards 2 per row; two static inline styles moved to classes), /brewsoul/guest (live's BrewSoul photo on the guest card instead of "SN" initials, labels in capitals), /humanos/connect (cards line up with the title), /peptide-hall-of-shame (stats and label readable light gold; were dark gold on dark). Typed arrows on the touched links are icons now (rule 18). Deliberately not copied from live (new CONTRIBUTING rule 20, owner 2026-10-08): red labels on dark bands use #E07A80 (live's #8E1E25 on black is about 2:1, unreadable); /recent-creations keeps our darker label colours (live's fail contrast on white); /humanos/connect keeps "Start Reading" (that card links to the philosophy page, the quiz live's "Start the Assessment" implies doesn't exist). Checked: type check, l</t>
+          <t>dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
         </is>
       </c>
       <c r="E298" s="14" t="inlineStr">
@@ -7707,7 +7707,7 @@
       <c r="A299" s="4" t="n"/>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>BrewSoul top of page (2026-10-08, owner: "button in the center at the top doesn't look good")</t>
+          <t>Live's redesign, second group (done 2026-10-08)</t>
         </is>
       </c>
       <c r="C299" s="13" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>the category badge ("Deep Research" etc.) sat centred in an empty strip, squeezed against the hero, because we copied live's doubled 52px top gap. Now one gap everywhere and the badge floats in the top-left corner, lined up with the BrewSoul logo (brewsoul-main.tsx, category-badge.tsx); checked on all 26 badge pages at 3 widths that it covers nothing. BrewSoul menu: on tablets (768-1023px) the links were cut off and "More" was hidden with no menu button at all; now the menu button shows below 1024px, 5 links + "More" from 1024px, all 8 from 1280px, "More" always visible.</t>
+          <t>re-measured all 18 pages on live vs a fresh production build (title font/size/weight/colour, labels, hero images). Already matching from 2026-10-07: /the-web, /spirits, /iboga-ibogaine (weight 800), /living-declaration, BrewSoul photo on /brewsoul, /brewsoul/browse, /brewsoul/first-sip (live has none there either), /quiz_25q, /recent-creations. Fixed today: /find-your-journey (64px title, red label), /impact-dashboard (64px title in essay ink, label spacing), red labels on /published and /speaking (plus its "rooms" chips), /soulscore "by ImpactSoul" label, /pri-calibration title (weight 900, solid cream, was a purple gradient), /clients (live's narrow 546px column for the whole page, 56px title, roomier stats band, cards 2 per row; two static inline styles moved to classes), /brewsoul/guest (live's BrewSoul photo on the guest card instead of "SN" initials, labels in capitals), /humanos/connect (cards line up with the title), /peptide-hall-of-shame (stats and label readable light gold; were dark gold on dark). Typed arrows on the touched links are icons now (rule 18). Deliberately not copied from live (new CONTRIBUTING rule 20, owner 2026-10-08): red labels on dark bands use #E07A80 (live's #8E1E25 on black is about 2:1, unreadable); /recent-creations keeps our darker label colours (live's fail contrast on white); /humanos/connect keeps "Start Reading" (that card links to the philosophy page, the quiz live's "Start the Assessment" implies doesn't exist). Checked: type check, l</t>
         </is>
       </c>
       <c r="E299" s="14" t="inlineStr">
@@ -7730,7 +7730,7 @@
       <c r="A300" s="4" t="n"/>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>/pri-efficacy's "Simulation / Live Calibrations" switch like live (2026-10-08)</t>
+          <t>BrewSoul top of page (2026-10-08, owner: "button in the center at the top doesn't look good")</t>
         </is>
       </c>
       <c r="C300" s="13" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>shadcn Tabs, both panels in the server HTML (forceMount). The Live tab reads real aggregate numbers from pri_calibrations (getPriLiveStats() in src/lib/pri-research.ts: totals, opt-ins, average score per dimension; no rows leave the server), page stays static and refreshes every 10 minutes. Until the Supabase scripts are run (Phase 2) it says the numbers "aren't available just now" instead of a fake zero. Checked: build (○, 10m), server HTML has both tabs, tab switch at 390/1280px, no JS errors. Re-check with real numbers once the table exists.</t>
+          <t>the category badge ("Deep Research" etc.) sat centred in an empty strip, squeezed against the hero, because we copied live's doubled 52px top gap. Now one gap everywhere and the badge floats in the top-left corner, lined up with the BrewSoul logo (brewsoul-main.tsx, category-badge.tsx); checked on all 26 badge pages at 3 widths that it covers nothing. BrewSoul menu: on tablets (768-1023px) the links were cut off and "More" was hidden with no menu button at all; now the menu button shows below 1024px, 5 links + "More" from 1024px, all 8 from 1280px, "More" always visible.</t>
         </is>
       </c>
       <c r="E300" s="14" t="inlineStr">
@@ -7753,63 +7753,63 @@
       <c r="A301" s="4" t="n"/>
       <c r="B301" s="4" t="inlineStr">
         <is>
+          <t>/pri-efficacy's "Simulation / Live Calibrations" switch like live (2026-10-08)</t>
+        </is>
+      </c>
+      <c r="C301" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D301" s="4" t="inlineStr">
+        <is>
+          <t>shadcn Tabs, both panels in the server HTML (forceMount). The Live tab reads real aggregate numbers from pri_calibrations (getPriLiveStats() in src/lib/pri-research.ts: totals, opt-ins, average score per dimension; no rows leave the server), page stays static and refreshes every 10 minutes. Until the Supabase scripts are run (Phase 2) it says the numbers "aren't available just now" instead of a fake zero. Checked: build (○, 10m), server HTML has both tabs, tab switch at 390/1280px, no JS errors. Re-check with real numbers once the table exists.</t>
+        </is>
+      </c>
+      <c r="E301" s="14" t="inlineStr">
+        <is>
+          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="4" t="n"/>
+      <c r="B302" s="4" t="inlineStr">
+        <is>
           <t>/brewsoul/browse hero readable (2026-10-08, owner said go ahead)</t>
         </is>
       </c>
-      <c r="C301" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D301" s="4" t="inlineStr">
+      <c r="C302" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D302" s="4" t="inlineStr">
         <is>
           <t>a soft cream glow behind the title block so "The Catalog", the subtitle and the stat labels read clearly over the coffee photo (live is hard to read there too; rule 20). Photo still shows around the edges. Checked at 390/1280px.</t>
         </is>
       </c>
-      <c r="E301" s="14" t="inlineStr">
+      <c r="E302" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
         </is>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" s="10" t="inlineStr">
+    <row r="303">
+      <c r="A303" s="10" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
-      <c r="B302" s="11" t="n"/>
-      <c r="C302" s="11" t="n"/>
-      <c r="D302" s="12" t="n"/>
-    </row>
-    <row r="303">
-      <c r="A303" s="4" t="n"/>
-      <c r="B303" s="4" t="inlineStr">
-        <is>
-          <t>Manus media rescue (2026-09-29)</t>
-        </is>
-      </c>
-      <c r="C303" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D303" s="4" t="inlineStr">
-        <is>
-          <t>all 94 Manus-hosted image/video references in the legacy source (/api/img/, /manus-storage/) were checked live. 91 were still downloadable, including the /akbar photos the entry below calls "permanently lost", and all 91 are now Sanity assets (scripts/rescue-manus-media.ts; Sanity dedupes by SHA-1). 3 were gone (HTTP 502). The manifest docs/ai/manus-media-rescue.md maps each one to the legacy files that used it and its Sanity URL. They are not wired into pages yet: go page by page, with real alt text. /facilitator-index's two diagrams are done (scripts/rescue-facilitator-images.ts).</t>
-        </is>
-      </c>
-      <c r="E303" s="14" t="inlineStr">
-        <is>
-          <t>Phase 13 — Images Needed in Sanity</t>
-        </is>
-      </c>
+      <c r="B303" s="11" t="n"/>
+      <c r="C303" s="11" t="n"/>
+      <c r="D303" s="12" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="4" t="n"/>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>Favicon</t>
+          <t>Manus media rescue (2026-09-29)</t>
         </is>
       </c>
       <c r="C304" s="13" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>real "G" brand mark generated from the header's actual wordmark treatment (src/app/icon.tsx), see Phase 3</t>
+          <t>all 94 Manus-hosted image/video references in the legacy source (/api/img/, /manus-storage/) were checked live. 91 were still downloadable, including the /akbar photos the entry below calls "permanently lost", and all 91 are now Sanity assets (scripts/rescue-manus-media.ts; Sanity dedupes by SHA-1). 3 were gone (HTTP 502). The manifest docs/ai/manus-media-rescue.md maps each one to the legacy files that used it and its Sanity URL. They are not wired into pages yet: go page by page, with real alt text. /facilitator-index's two diagrams are done (scripts/rescue-facilitator-images.ts).</t>
         </is>
       </c>
       <c r="E304" s="14" t="inlineStr">
@@ -7832,17 +7832,17 @@
       <c r="A305" s="4" t="n"/>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
-        </is>
-      </c>
-      <c r="C305" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Favicon</t>
+        </is>
+      </c>
+      <c r="C305" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
+          <t>real "G" brand mark generated from the header's actual wordmark treatment (src/app/icon.tsx), see Phase 3</t>
         </is>
       </c>
       <c r="E305" s="14" t="inlineStr">
@@ -7855,17 +7855,17 @@
       <c r="A306" s="4" t="n"/>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>Author photo(s) for blog author schema (Tony Greenberg headshot at minimum)</t>
-        </is>
-      </c>
-      <c r="C306" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
+        </is>
+      </c>
+      <c r="C306" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: the rescued headshot is already the author avatar in Sanity; now also in every post's Article JSON-LD (author image + url /about). The JSON-LD publisher logo pointed at /favicon.ico, a 404 here; now /icon.</t>
+          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
         </is>
       </c>
       <c r="E306" s="14" t="inlineStr">
@@ -7878,7 +7878,7 @@
       <c r="A307" s="4" t="n"/>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Blog hero images</t>
+          <t>Author photo(s) for blog author schema (Tony Greenberg headshot at minimum)</t>
         </is>
       </c>
       <c r="C307" s="13" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>audited, then migrated. Final state:</t>
+          <t>2026-10-02: the rescued headshot is already the author avatar in Sanity; now also in every post's Article JSON-LD (author image + url /about). The JSON-LD publisher logo pointed at /favicon.ico, a 404 here; now /icon.</t>
         </is>
       </c>
       <c r="E307" s="14" t="inlineStr">
@@ -7901,7 +7901,7 @@
       <c r="A308" s="4" t="n"/>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>22 posts have a real hero image, now live in Sanity (17 already on RampRate's own CloudFront + 4 rescued from the legacy /api/img/ proxy + 1…</t>
+          <t>Blog hero images</t>
         </is>
       </c>
       <c r="C308" s="13" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> rescued from /manus-storage/, all pulled over by migrate-blog-posts.ts before Manus is decommissioned)</t>
+          <t>audited, then migrated. Final state:</t>
         </is>
       </c>
       <c r="E308" s="14" t="inlineStr">
@@ -7924,7 +7924,7 @@
       <c r="A309" s="4" t="n"/>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>7 more posts got a real, unique hero image rescued from the live legacy site's newly-added art this pass (scripts/rescue-2026-09-blog-images…</t>
+          <t>22 posts have a real hero image, now live in Sanity (17 already on RampRate's own CloudFront + 4 rescued from the legacy /api/img/ proxy + 1…</t>
         </is>
       </c>
       <c r="C309" s="13" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>.ts — see the correction note above): california-toll-roads-legalized-scam, the-1000-hour-hold, conscious-capital-partnership-ecosystem, the-peptide-truth-65m-fraud-industry-vs-life-changing-medicine, clear-communication, building-services-market-transhuman-era, heart-protocol-addendum.</t>
+          <t xml:space="preserve"> rescued from /manus-storage/, all pulled over by migrate-blog-posts.ts before Manus is decommissioned)</t>
         </is>
       </c>
       <c r="E309" s="14" t="inlineStr">
@@ -7947,17 +7947,17 @@
       <c r="A310" s="4" t="n"/>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>92 posts still need a real, unique hero image</t>
-        </is>
-      </c>
-      <c r="C310" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>7 more posts got a real, unique hero image rescued from the live legacy site's newly-added art this pass (scripts/rescue-2026-09-blog-images…</t>
+        </is>
+      </c>
+      <c r="C310" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
+          <t>.ts — see the correction note above): california-toll-roads-legalized-scam, the-1000-hour-hold, conscious-capital-partnership-ecosystem, the-peptide-truth-65m-fraud-industry-vs-life-changing-medicine, clear-communication, building-services-market-transhuman-era, heart-protocol-addendum.</t>
         </is>
       </c>
       <c r="E310" s="14" t="inlineStr">
@@ -7970,17 +7970,17 @@
       <c r="A311" s="4" t="n"/>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Blog: per-post OG image if different from hero (many posts can reuse hero as OG)</t>
-        </is>
-      </c>
-      <c r="C311" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>92 posts still need a real, unique hero image</t>
+        </is>
+      </c>
+      <c r="C311" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>Confirmed 2026-10-02: generateMetadata uses seo.ogImage, else the hero, else the default OG image.</t>
+          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
         </is>
       </c>
       <c r="E311" s="14" t="inlineStr">
@@ -7993,7 +7993,7 @@
       <c r="A312" s="4" t="n"/>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>Marketing pages</t>
+          <t>Blog: per-post OG image if different from hero (many posts can reuse hero as OG)</t>
         </is>
       </c>
       <c r="C312" s="13" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>hero/section images for /the-letter, /the-territory, /engine-room, /the-body, /the-nightstand, /recent-creations (portfolio thumbnails), /published (publication logos), /clients (client logos — confirm licensing before re-hosting). Checked against live 2026-10-02: same image count on every one; /the-territory, /engine-room, /recent-creations, /published, /clients have no images on live either.</t>
+          <t>Confirmed 2026-10-02: generateMetadata uses seo.ogImage, else the hero, else the default OG image.</t>
         </is>
       </c>
       <c r="E312" s="14" t="inlineStr">
@@ -8016,7 +8016,7 @@
       <c r="A313" s="4" t="n"/>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>/akbar essay images</t>
+          <t>Marketing pages</t>
         </is>
       </c>
       <c r="C313" s="13" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>not lost after all: 20 of the 21 were rescued into Sanity by scripts/rescue-manus-media.ts (2026-09-28) and are wired back in legacy's layout (hero mosaic, JC portrait, 2x2 grid, 3 full-bleeds, 3-up strip, footer gallery) as of 2026-09-29. Only slider-3 was gone (HTTP 502); the hero mosaic is 4 tiles instead of 5.</t>
+          <t>hero/section images for /the-letter, /the-territory, /engine-room, /the-body, /the-nightstand, /recent-creations (portfolio thumbnails), /published (publication logos), /clients (client logos — confirm licensing before re-hosting). Checked against live 2026-10-02: same image count on every one; /the-territory, /engine-room, /recent-creations, /published, /clients have no images on live either.</t>
         </is>
       </c>
       <c r="E313" s="14" t="inlineStr">
@@ -8039,7 +8039,7 @@
       <c r="A314" s="4" t="n"/>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>Rescued page images wired back in (2026-09-29)</t>
+          <t>/akbar essay images</t>
         </is>
       </c>
       <c r="C314" s="13" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>/living-declaration hero, hand image and Clarisse Abelarde artwork; /impact-dashboard earth hero; /find-my banner; /find-your-coffee dark photo landing (legacy copy restored, replacing an intro that wasn't in legacy). Also wired (second pass): /consciousness-scale (legacy's hero-first flow restored, the invented intro screen removed), /find-your-me hero, /humanos hero, the HumanOS nav logo, and all 12 HumanOS people headshots (/humanos/ecosystem, /humanos/philosophy). Blog-body images (2026-09-29): all 19 the migration dropped are restored by scripts/restore-blog-body-images.ts as Sanity drafts on 4 posts (Clarisse Abelarde 7, You Are the Moat 4, FRQNCY 6, Energy Is Money 2), waiting to be published in Studio; the other blog-listed assets were heroes already set. Still unwired from docs/ai/manus-media-rescue.md: and /alex-azzi's subject photo (a photo of a real person on an accusation page: needs Tony's yes first).</t>
+          <t>not lost after all: 20 of the 21 were rescued into Sanity by scripts/rescue-manus-media.ts (2026-09-28) and are wired back in legacy's layout (hero mosaic, JC portrait, 2x2 grid, 3 full-bleeds, 3-up strip, footer gallery) as of 2026-09-29. Only slider-3 was gone (HTTP 502); the hero mosaic is 4 tiles instead of 5.</t>
         </is>
       </c>
       <c r="E314" s="14" t="inlineStr">
@@ -8062,7 +8062,7 @@
       <c r="A315" s="4" t="n"/>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>BrewSoul: coffee/product images (brewsoul-coffees-expanded.ts likely has image refs</t>
+          <t>Rescued page images wired back in (2026-09-29)</t>
         </is>
       </c>
       <c r="C315" s="13" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>audit), city guide header images, roaster directory photos. Audited 2026-09-09 (status spreadsheet), confirmed 2026-10-02: city guides already have photos; coffees, chains and roasters have no image field in legacy or here (text-only by design); farms got real photos.</t>
+          <t>/living-declaration hero, hand image and Clarisse Abelarde artwork; /impact-dashboard earth hero; /find-my banner; /find-your-coffee dark photo landing (legacy copy restored, replacing an intro that wasn't in legacy). Also wired (second pass): /consciousness-scale (legacy's hero-first flow restored, the invented intro screen removed), /find-your-me hero, /humanos hero, the HumanOS nav logo, and all 12 HumanOS people headshots (/humanos/ecosystem, /humanos/philosophy). Blog-body images (2026-09-29): all 19 the migration dropped are restored by scripts/restore-blog-body-images.ts as Sanity drafts on 4 posts (Clarisse Abelarde 7, You Are the Moat 4, FRQNCY 6, Energy Is Money 2), waiting to be published in Studio; the other blog-listed assets were heroes already set. Still unwired from docs/ai/manus-media-rescue.md: and /alex-azzi's subject photo (a photo of a real person on an accusation page: needs Tony's yes first).</t>
         </is>
       </c>
       <c r="E315" s="14" t="inlineStr">
@@ -8085,7 +8085,7 @@
       <c r="A316" s="4" t="n"/>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>65 page images moved off the Manus storage copy into Sanity (2026-10-02)</t>
+          <t>BrewSoul: coffee/product images (brewsoul-coffees-expanded.ts likely has image refs</t>
         </is>
       </c>
       <c r="C316" s="13" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="D316" s="4" t="inlineStr">
         <is>
-          <t>every image the code loaded from d2xsxph8kpxj0f.cloudfront.net (PRI medicine images, Iboga module, facilitator index, /attention-theft, /alex-azzi, /protecting-your-business, /peyote-mescaline, HumanOS, the peptide quiz). Notes called it "RampRate's own CloudFront", but every file sits in the legacy Manus project's folder and its owner couldn't be confirmed. All 65 uploaded (scripts/rescue-cloudfront-images.ts), code rewritten, host removed from images.remotePatterns, no Sanity document used it. Table in docs/ai/manus-media-rescue.md.</t>
+          <t>audit), city guide header images, roaster directory photos. Audited 2026-09-09 (status spreadsheet), confirmed 2026-10-02: city guides already have photos; coffees, chains and roasters have no image field in legacy or here (text-only by design); farms got real photos.</t>
         </is>
       </c>
       <c r="E316" s="14" t="inlineStr">
@@ -8108,7 +8108,7 @@
       <c r="A317" s="4" t="n"/>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>PRI/Kava: medicine reference images (medicine-images.ts), facility images for /facilitator-index</t>
+          <t>65 page images moved off the Manus storage copy into Sanity (2026-10-02)</t>
         </is>
       </c>
       <c r="C317" s="13" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: all in Sanity; image counts match live on PRI, Kava, Iboga, Peyote, facilitator pages.</t>
+          <t>every image the code loaded from d2xsxph8kpxj0f.cloudfront.net (PRI medicine images, Iboga module, facilitator index, /attention-theft, /alex-azzi, /protecting-your-business, /peyote-mescaline, HumanOS, the peptide quiz). Notes called it "RampRate's own CloudFront", but every file sits in the legacy Manus project's folder and its owner couldn't be confirmed. All 65 uploaded (scripts/rescue-cloudfront-images.ts), code rewritten, host removed from images.remotePatterns, no Sanity document used it. Table in docs/ai/manus-media-rescue.md.</t>
         </is>
       </c>
       <c r="E317" s="14" t="inlineStr">
@@ -8131,7 +8131,7 @@
       <c r="A318" s="4" t="n"/>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>Manifesto/Attention Theft: any diagram/illustration assets used on the mega-page</t>
+          <t>PRI/Kava: medicine reference images (medicine-images.ts), facility images for /facilitator-index</t>
         </is>
       </c>
       <c r="C318" s="13" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="D318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: 6 of live's 7 are in (now in Sanity); the 7th belongs to the Wall of Shame section left out on purpose.</t>
+          <t>2026-10-02: all in Sanity; image counts match live on PRI, Kava, Iboga, Peyote, facilitator pages.</t>
         </is>
       </c>
       <c r="E318" s="14" t="inlineStr">
@@ -8154,17 +8154,17 @@
       <c r="A319" s="4" t="n"/>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
-        </is>
-      </c>
-      <c r="C319" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Manifesto/Attention Theft: any diagram/illustration assets used on the mega-page</t>
+        </is>
+      </c>
+      <c r="C319" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
+          <t>2026-10-02: 6 of live's 7 are in (now in Sanity); the 7th belongs to the Wall of Shame section left out on purpose.</t>
         </is>
       </c>
       <c r="E319" s="14" t="inlineStr">
@@ -8177,17 +8177,17 @@
       <c r="A320" s="4" t="n"/>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>Chatbot: FauxTony avatar/icon</t>
-        </is>
-      </c>
-      <c r="C320" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
+        </is>
+      </c>
+      <c r="C320" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>Not needed (2026-10-02): the chatbot phase (Phase 10) was cancelled.</t>
+          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
         </is>
       </c>
       <c r="E320" s="14" t="inlineStr">
@@ -8200,73 +8200,73 @@
       <c r="A321" s="4" t="n"/>
       <c r="B321" s="4" t="inlineStr">
         <is>
+          <t>Chatbot: FauxTony avatar/icon</t>
+        </is>
+      </c>
+      <c r="C321" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D321" s="4" t="inlineStr">
+        <is>
+          <t>Not needed (2026-10-02): the chatbot phase (Phase 10) was cancelled.</t>
+        </is>
+      </c>
+      <c r="E321" s="14" t="inlineStr">
+        <is>
+          <t>Phase 13 — Images Needed in Sanity</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="4" t="n"/>
+      <c r="B322" s="4" t="inlineStr">
+        <is>
           <t>Audit client/public/ (including alex-azzi/, brewsoul/ subfolders) for any static assets already sitting there unused that should be pulled i…</t>
         </is>
       </c>
-      <c r="C321" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D321" s="4" t="inlineStr">
+      <c r="C322" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D322" s="4" t="inlineStr">
         <is>
           <t>n rather than re-created. Done 2026-10-02: no images there at all (only llms.txt, a BrewSoul catalog, Manus debug files, design-options.html). Found and fixed a cutover risk instead: live serves two Google site-verification files (/google6881a0411c48b301.html, /alex-azzi/googleedff0185753a4a1f.html) that the new site returned 404 for, so Search Console could lose verification at DNS cutover. Both copied to public/ byte for byte. Not copied: site.webmanifest (its icons don't exist here; Next's app/icon.tsx covers the favicon).</t>
         </is>
       </c>
-      <c r="E321" s="14" t="inlineStr">
+      <c r="E322" s="14" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" s="10" t="inlineStr">
+    <row r="323">
+      <c r="A323" s="10" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
         </is>
       </c>
-      <c r="B322" s="11" t="n"/>
-      <c r="C322" s="11" t="n"/>
-      <c r="D322" s="12" t="n"/>
-    </row>
-    <row r="323">
-      <c r="A323" s="4" t="n"/>
-      <c r="B323" s="4" t="inlineStr">
-        <is>
-          <t>Mobile responsive pass on every ported section</t>
-        </is>
-      </c>
-      <c r="C323" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D323" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid). Fixed 2026-10-09: the bar is now solid (bg-[#2C1810], was 92% plus backdrop-blur-md), so nothing can show through even where the blur isn't drawn; checked in WebKit (iPhone 13 profile) and Chrome: background rgb(44, 24, 16), no text behind the buttons. A real iPhone check is still part of Phase 14.</t>
-        </is>
-      </c>
-      <c r="E323" s="14" t="inlineStr">
-        <is>
-          <t>Phase 14 — QA &amp; Launch</t>
-        </is>
-      </c>
+      <c r="B323" s="11" t="n"/>
+      <c r="C323" s="11" t="n"/>
+      <c r="D323" s="12" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="4" t="n"/>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>Accessibility pass (WCAG AA contrast, 44px touch targets, keyboard nav)</t>
-        </is>
-      </c>
-      <c r="C324" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Mobile responsive pass on every ported section</t>
+        </is>
+      </c>
+      <c r="C324" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy QA_MASTER_PROMPT.md. 2026-09-29 axe-core pass (WCAG 2.1 AA, same 114 pages, production build): all unlabeled dropdowns/inputs and unnamed links fixed; contrast down from 1,453 failing items on 106 pages to 1,038 on 70 (43 pages fully clean). Shared fixes: brand gold #8b6914 → #836311 site-wide (was 4.3:1 on cream, AA needs 4.5), header "⌘K"/social icons, BrewSoul nav and footer, HumanOS footer, Kava footer, assessment intro footnote, post-card image links. 2026-09-30: contrast finished, 0 axe color-contrast failures left on the same 114 pages (production build). Token changes: --kava-saffron #b86a28 → #8e521f, --pri-purple-light #a855f7 → #b87bf9 (on-dark purple only), --crusade-teal #0e7c7c → #0d7373; PriEyebrow goes light purple inside a dark PriSection via group-data-dark/pri; /find-your-me and the journey tracker's dark glass panels 60-70% → 90% (legacy's own 60% glass on beige rendered gray, cream text failed). Everything else: nearest passing shade of the same hue, or gold ↔ gold-light on the wrong background. Left: 18 links inside text marked only by color (need an underline), 44px tap targets, keyboard nav. 2026-09-30: 18 color-only in-text links underlined (axe link-in-text-block: 0 left); keyboard focus visible on every focusable item on 8 sampled pages (two form fields had none, fixed). 2026-10-02 re-run (axe WCAG 2.2 AA, 142 pages × 375/1280px, production build, plus Tab through 40 stops per page): found 1,370 contrast failures (mostly BrewSoul'</t>
+          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid). Fixed 2026-10-09: the bar is now solid (bg-[#2C1810], was 92% plus backdrop-blur-md), so nothing can show through even where the blur isn't drawn; checked in WebKit (iPhone 13 profile) and Chrome: background rgb(44, 24, 16), no text behind the buttons. A real iPhone check is still part of Phase 14.</t>
         </is>
       </c>
       <c r="E324" s="14" t="inlineStr">
@@ -8279,17 +8279,17 @@
       <c r="A325" s="4" t="n"/>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>No dead-end pages (every page links to 2+ others)</t>
-        </is>
-      </c>
-      <c r="C325" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Accessibility pass (WCAG AA contrast, 44px touch targets, keyboard nav)</t>
+        </is>
+      </c>
+      <c r="C325" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
+          <t>same bar as legacy QA_MASTER_PROMPT.md. 2026-09-29 axe-core pass (WCAG 2.1 AA, same 114 pages, production build): all unlabeled dropdowns/inputs and unnamed links fixed; contrast down from 1,453 failing items on 106 pages to 1,038 on 70 (43 pages fully clean). Shared fixes: brand gold #8b6914 → #836311 site-wide (was 4.3:1 on cream, AA needs 4.5), header "⌘K"/social icons, BrewSoul nav and footer, HumanOS footer, Kava footer, assessment intro footnote, post-card image links. 2026-09-30: contrast finished, 0 axe color-contrast failures left on the same 114 pages (production build). Token changes: --kava-saffron #b86a28 → #8e521f, --pri-purple-light #a855f7 → #b87bf9 (on-dark purple only), --crusade-teal #0e7c7c → #0d7373; PriEyebrow goes light purple inside a dark PriSection via group-data-dark/pri; /find-your-me and the journey tracker's dark glass panels 60-70% → 90% (legacy's own 60% glass on beige rendered gray, cream text failed). Everything else: nearest passing shade of the same hue, or gold ↔ gold-light on the wrong background. Left: 18 links inside text marked only by color (need an underline), 44px tap targets, keyboard nav. 2026-09-30: 18 color-only in-text links underlined (axe link-in-text-block: 0 left); keyboard focus visible on every focusable item on 8 sampled pages (two form fields had none, fixed). 2026-10-02 re-run (axe WCAG 2.2 AA, 142 pages × 375/1280px, production build, plus Tab through 40 stops per page): found 1,370 contrast failures (mostly BrewSoul'</t>
         </is>
       </c>
       <c r="E325" s="14" t="inlineStr">
@@ -8302,7 +8302,7 @@
       <c r="A326" s="4" t="n"/>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
+          <t>No dead-end pages (every page links to 2+ others)</t>
         </is>
       </c>
       <c r="C326" s="15" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
+          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
         </is>
       </c>
       <c r="E326" s="14" t="inlineStr">
@@ -8325,7 +8325,7 @@
       <c r="A327" s="4" t="n"/>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>Remove noindex only when sign-off is given</t>
+          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
         </is>
       </c>
       <c r="C327" s="15" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
         </is>
       </c>
       <c r="E327" s="14" t="inlineStr">
@@ -8348,7 +8348,7 @@
       <c r="A328" s="4" t="n"/>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
+          <t>Remove noindex only when sign-off is given</t>
         </is>
       </c>
       <c r="C328" s="15" t="inlineStr">
@@ -8356,7 +8356,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D328" s="4" t="inlineStr"/>
+      <c r="D328" s="4" t="inlineStr">
+        <is>
+          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+        </is>
+      </c>
       <c r="E328" s="14" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
@@ -8367,7 +8371,7 @@
       <c r="A329" s="4" t="n"/>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
         </is>
       </c>
       <c r="C329" s="15" t="inlineStr">
@@ -8382,20 +8386,39 @@
         </is>
       </c>
     </row>
+    <row r="330">
+      <c r="A330" s="4" t="n"/>
+      <c r="B330" s="4" t="inlineStr">
+        <is>
+          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+        </is>
+      </c>
+      <c r="C330" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D330" s="4" t="inlineStr"/>
+      <c r="E330" s="14" t="inlineStr">
+        <is>
+          <t>Phase 14 — QA &amp; Launch</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D329"/>
+  <autoFilter ref="A1:D330"/>
   <mergeCells count="14">
     <mergeCell ref="A150:D150"/>
-    <mergeCell ref="A322:D322"/>
+    <mergeCell ref="A303:D303"/>
     <mergeCell ref="A237:D237"/>
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A258:D258"/>
     <mergeCell ref="A209:D209"/>
     <mergeCell ref="A205:D205"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A302:D302"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A323:D323"/>
     <mergeCell ref="A183:D183"/>
     <mergeCell ref="A32:D32"/>
     <mergeCell ref="A123:D123"/>

--- a/Migration-Status-Report.xlsx
+++ b/Migration-Status-Report.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Remaining Work" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$330</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Remaining Work'!$A$1:$D$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$331</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Remaining Work'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -639,15 +639,15 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A5,'Full Detail'!$C$2:$C$330,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A5,'Full Detail'!$C$2:$C$331,"Done")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A5,'Full Detail'!$C$2:$C$330,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A5,'Full Detail'!$C$2:$C$331,"Remaining")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A5,'Full Detail'!$C$2:$C$330,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A5,'Full Detail'!$C$2:$C$331,"Deferred")</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -666,15 +666,15 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A6,'Full Detail'!$C$2:$C$330,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A6,'Full Detail'!$C$2:$C$331,"Done")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A6,'Full Detail'!$C$2:$C$330,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A6,'Full Detail'!$C$2:$C$331,"Remaining")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A6,'Full Detail'!$C$2:$C$330,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A6,'Full Detail'!$C$2:$C$331,"Deferred")</f>
         <v/>
       </c>
       <c r="E6" s="5">
@@ -693,15 +693,15 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A7,'Full Detail'!$C$2:$C$330,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A7,'Full Detail'!$C$2:$C$331,"Done")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A7,'Full Detail'!$C$2:$C$330,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A7,'Full Detail'!$C$2:$C$331,"Remaining")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A7,'Full Detail'!$C$2:$C$330,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A7,'Full Detail'!$C$2:$C$331,"Deferred")</f>
         <v/>
       </c>
       <c r="E7" s="5">
@@ -720,15 +720,15 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A8,'Full Detail'!$C$2:$C$330,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A8,'Full Detail'!$C$2:$C$331,"Done")</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A8,'Full Detail'!$C$2:$C$330,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A8,'Full Detail'!$C$2:$C$331,"Remaining")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A8,'Full Detail'!$C$2:$C$330,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A8,'Full Detail'!$C$2:$C$331,"Deferred")</f>
         <v/>
       </c>
       <c r="E8" s="5">
@@ -747,15 +747,15 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A9,'Full Detail'!$C$2:$C$330,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A9,'Full Detail'!$C$2:$C$331,"Done")</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A9,'Full Detail'!$C$2:$C$330,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A9,'Full Detail'!$C$2:$C$331,"Remaining")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A9,'Full Detail'!$C$2:$C$330,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A9,'Full Detail'!$C$2:$C$331,"Deferred")</f>
         <v/>
       </c>
       <c r="E9" s="5">
@@ -774,15 +774,15 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A10,'Full Detail'!$C$2:$C$330,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A10,'Full Detail'!$C$2:$C$331,"Done")</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A10,'Full Detail'!$C$2:$C$330,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A10,'Full Detail'!$C$2:$C$331,"Remaining")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A10,'Full Detail'!$C$2:$C$330,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A10,'Full Detail'!$C$2:$C$331,"Deferred")</f>
         <v/>
       </c>
       <c r="E10" s="5">
@@ -801,15 +801,15 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A11,'Full Detail'!$C$2:$C$330,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A11,'Full Detail'!$C$2:$C$331,"Done")</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A11,'Full Detail'!$C$2:$C$330,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A11,'Full Detail'!$C$2:$C$331,"Remaining")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A11,'Full Detail'!$C$2:$C$330,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A11,'Full Detail'!$C$2:$C$331,"Deferred")</f>
         <v/>
       </c>
       <c r="E11" s="5">
@@ -828,15 +828,15 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A12,'Full Detail'!$C$2:$C$330,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A12,'Full Detail'!$C$2:$C$331,"Done")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A12,'Full Detail'!$C$2:$C$330,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A12,'Full Detail'!$C$2:$C$331,"Remaining")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A12,'Full Detail'!$C$2:$C$330,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A12,'Full Detail'!$C$2:$C$331,"Deferred")</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -855,15 +855,15 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A13,'Full Detail'!$C$2:$C$330,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A13,'Full Detail'!$C$2:$C$331,"Done")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A13,'Full Detail'!$C$2:$C$330,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A13,'Full Detail'!$C$2:$C$331,"Remaining")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A13,'Full Detail'!$C$2:$C$330,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A13,'Full Detail'!$C$2:$C$331,"Deferred")</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -882,15 +882,15 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A14,'Full Detail'!$C$2:$C$330,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A14,'Full Detail'!$C$2:$C$331,"Done")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A14,'Full Detail'!$C$2:$C$330,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A14,'Full Detail'!$C$2:$C$331,"Remaining")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A14,'Full Detail'!$C$2:$C$330,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A14,'Full Detail'!$C$2:$C$331,"Deferred")</f>
         <v/>
       </c>
       <c r="E14" s="5">
@@ -909,15 +909,15 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A15,'Full Detail'!$C$2:$C$330,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A15,'Full Detail'!$C$2:$C$331,"Done")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A15,'Full Detail'!$C$2:$C$330,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A15,'Full Detail'!$C$2:$C$331,"Remaining")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A15,'Full Detail'!$C$2:$C$330,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A15,'Full Detail'!$C$2:$C$331,"Deferred")</f>
         <v/>
       </c>
       <c r="E15" s="5">
@@ -936,15 +936,15 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A16,'Full Detail'!$C$2:$C$330,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A16,'Full Detail'!$C$2:$C$331,"Done")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A16,'Full Detail'!$C$2:$C$330,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A16,'Full Detail'!$C$2:$C$331,"Remaining")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A16,'Full Detail'!$C$2:$C$330,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A16,'Full Detail'!$C$2:$C$331,"Deferred")</f>
         <v/>
       </c>
       <c r="E16" s="5">
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A17,'Full Detail'!$C$2:$C$330,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A17,'Full Detail'!$C$2:$C$331,"Done")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A17,'Full Detail'!$C$2:$C$330,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A17,'Full Detail'!$C$2:$C$331,"Remaining")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A17,'Full Detail'!$C$2:$C$330,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A17,'Full Detail'!$C$2:$C$331,"Deferred")</f>
         <v/>
       </c>
       <c r="E17" s="5">
@@ -990,15 +990,15 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A18,'Full Detail'!$C$2:$C$330,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A18,'Full Detail'!$C$2:$C$331,"Done")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A18,'Full Detail'!$C$2:$C$330,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A18,'Full Detail'!$C$2:$C$331,"Remaining")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A18,'Full Detail'!$C$2:$C$330,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A18,'Full Detail'!$C$2:$C$331,"Deferred")</f>
         <v/>
       </c>
       <c r="E18" s="5">
@@ -1017,15 +1017,15 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A19,'Full Detail'!$C$2:$C$330,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A19,'Full Detail'!$C$2:$C$331,"Done")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A19,'Full Detail'!$C$2:$C$330,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A19,'Full Detail'!$C$2:$C$331,"Remaining")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$330,$A19,'Full Detail'!$C$2:$C$330,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A19,'Full Detail'!$C$2:$C$331,"Deferred")</f>
         <v/>
       </c>
       <c r="E19" s="5">
@@ -1075,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E330"/>
+  <dimension ref="A1:E331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1953,63 +1953,63 @@
       <c r="A42" s="4" t="n"/>
       <c r="B42" s="4" t="inlineStr">
         <is>
+          <t>Copy the old site's visitor data from the Manus database (owner asked, 2026-10-09)</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>The legacy app keeps ~55 MySQL tables on Manus (_legacy-manus-app/drizzle/schema.ts); they go away with Manus. Owner has the connection details: put them in .env.local as LEGACY_DATABASE_URL (never in chat or a commit). Plan: (1) read row counts for every table (read-only, a throwaway pymysql reader outside the project, no new package); (2) after the two Supabase scripts below are run, copy the 12 tables that already have a home: blog_comments, blog_ratings, post_reactions → blog_reactions, micro_commitments → blog_commitments, highlights, referral_codes, referrals, clock_keeper_responses, post_intervention_assessments, friend_gate_sessions, friend_gate_slots, pri_calibrations (account-linked rows can only be matched to new accounts by email); (3) email_subscribers go to Kit, not Supabase; (4) owner picks which of the rest need new tables (facilitator submissions/votes, assessment results, journey progress, community, vendor intake, page views...). Billing (purchases, subscriptions) and spam tracking stay out of scope. Blocked on: LEGACY_DATABASE_URL, and the Supabase scripts being run.</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Phase 2 — Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
           <t>Run the database scripts once, in order</t>
         </is>
       </c>
-      <c r="C42" s="15" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>(supabase/migrations/0001_member_features.sql, then 0002_blog_engagement.sql for essay comments, reactions, ratings and micro-commitments; 0001: highlights, referral codes/referrals, Clock Keeper responses, post-intervention, friend gate, PRI calibrations, all with row-level security) in Supabase: SQL Editor &gt; New query &gt; paste &gt; Run. Also in Supabase: Authentication &gt; URL Configuration &gt; Site URL https://tonygreenberg.com and Redirect URLs https://tonygreenberg.com/auth/callback, https://*--tonygreenberg-website.netlify.app/auth/callback, http://localhost:3000/auth/callback. Then set NEXT_PUBLIC_SUPABASE_URL, NEXT_PUBLIC_SUPABASE_ANON_KEY, SUPABASE_SERVICE_ROLE_KEY, ADMIN_EMAILS in Netlify.</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="E43" s="14" t="inlineStr">
         <is>
           <t>Phase 2 — Supabase</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>Phase 3 — Shared Layout &amp; Design System</t>
         </is>
       </c>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="12" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="n"/>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Root layout (web/src/app/layout.tsx)</t>
-        </is>
-      </c>
-      <c r="C44" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>fonts (Playfair Display / DM Mono / Source Sans 3 via next/font/google), &lt;TooltipProvider&gt;, theme provider (next-themes, class strategy), global &lt;Toaster /&gt; (sonner), skip-to-content link</t>
-        </is>
-      </c>
-      <c r="E44" s="14" t="inlineStr">
-        <is>
-          <t>Phase 3 — Shared Layout &amp; Design System</t>
-        </is>
-      </c>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n"/>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Global metadata defaults in root layout (metadataBase, title template, default OG/Twitter card)</t>
+          <t>Root layout (web/src/app/layout.tsx)</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
@@ -2017,7 +2017,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>fonts (Playfair Display / DM Mono / Source Sans 3 via next/font/google), &lt;TooltipProvider&gt;, theme provider (next-themes, class strategy), global &lt;Toaster /&gt; (sonner), skip-to-content link</t>
+        </is>
+      </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
           <t>Phase 3 — Shared Layout &amp; Design System</t>
@@ -2028,7 +2032,7 @@
       <c r="A46" s="4" t="n"/>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Favicon (src/app/icon.tsx)</t>
+          <t>Global metadata defaults in root layout (metadataBase, title template, default OG/Twitter card)</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -2036,11 +2040,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>real brand mark, not the default Next.js icon: a generated 32×32 PNG of the "G" from the header's actual "TonyG" wordmark (Playfair Display, brand-gold), since the full wordmark doesn't read at favicon scale. Deleted the stale default favicon.ico.</t>
-        </is>
-      </c>
+      <c r="D46" s="4" t="inlineStr"/>
       <c r="E46" s="14" t="inlineStr">
         <is>
           <t>Phase 3 — Shared Layout &amp; Design System</t>
@@ -2051,7 +2051,7 @@
       <c r="A47" s="4" t="n"/>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Header/nav component (site-header.tsx)</t>
+          <t>Favicon (src/app/icon.tsx)</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>real nav structure ported from legacy Layout.tsx (primary links, "Fix Myself"/"Explore" mega-menus, socials, theme toggle), built with shadcn NavigationMenu. Deliberately not ported: StartHereBanner, ExitIntentTony, TonyAvatarTrigger, NotificationBell, ReadingStreakBadge, WhereNext — separate behavioral/engagement features, not core layout, out of scope for this phase</t>
+          <t>real brand mark, not the default Next.js icon: a generated 32×32 PNG of the "G" from the header's actual "TonyG" wordmark (Playfair Display, brand-gold), since the full wordmark doesn't read at favicon scale. Deleted the stale default favicon.ico.</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
@@ -2074,7 +2074,7 @@
       <c r="A48" s="4" t="n"/>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Mobile nav (shadcn Sheet + Accordion, real nav content, no framer-motion)</t>
+          <t>Header/nav component (site-header.tsx)</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
@@ -2082,7 +2082,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>real nav structure ported from legacy Layout.tsx (primary links, "Fix Myself"/"Explore" mega-menus, socials, theme toggle), built with shadcn NavigationMenu. Deliberately not ported: StartHereBanner, ExitIntentTony, TonyAvatarTrigger, NotificationBell, ReadingStreakBadge, WhereNext — separate behavioral/engagement features, not core layout, out of scope for this phase</t>
+        </is>
+      </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
           <t>Phase 3 — Shared Layout &amp; Design System</t>
@@ -2093,7 +2097,7 @@
       <c r="A49" s="4" t="n"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Footer component (site-footer.tsx)</t>
+          <t>Mobile nav (shadcn Sheet + Accordion, real nav content, no framer-motion)</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
@@ -2101,11 +2105,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>real content ported from Layout.tsx's footer JSX (quote, contact, BioChain routing note, socials, CTAs, bio line, legal/copyright). Note: footerData.json turned out to be per-post article-footer data (exercise/related/riddle/CTA), not site footer content — that belongs in Phase 5, not here</t>
-        </is>
-      </c>
+      <c r="D49" s="4" t="inlineStr"/>
       <c r="E49" s="14" t="inlineStr">
         <is>
           <t>Phase 3 — Shared Layout &amp; Design System</t>
@@ -2116,7 +2116,7 @@
       <c r="A50" s="4" t="n"/>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Brand design tokens in globals.css (--brand-gold/--brand-gold-light/backgrounds/borders) ported from the real site palette (#8B6914, #D4B96A…</t>
+          <t>Footer component (site-footer.tsx)</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>, #0A0A10, #FAFAF7, purple-tinted borders) instead of shadcn's default grayscale theme</t>
+          <t>real content ported from Layout.tsx's footer JSX (quote, contact, BioChain routing note, socials, CTAs, bio line, legal/copyright). Note: footerData.json turned out to be per-post article-footer data (exercise/related/riddle/CTA), not site footer content — that belongs in Phase 5, not here</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
@@ -2139,7 +2139,7 @@
       <c r="A51" s="4" t="n"/>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Shared typography components</t>
+          <t>Brand design tokens in globals.css (--brand-gold/--brand-gold-light/backgrounds/borders) ported from the real site palette (#8B6914, #D4B96A…</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>ended up built directly in Phase 5 (portable-text.tsx, drop-cap CSS, pull-quote block) rather than as a separate Phase 3 deliverable, since that's where they're actually consumed</t>
+          <t>, #0A0A10, #FAFAF7, purple-tinted borders) instead of shadcn's default grayscale theme</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
@@ -2162,7 +2162,7 @@
       <c r="A52" s="4" t="n"/>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>robots.ts (AI crawlers explicitly allowed per the current SEO plan, scraper bots blocked) and sitemap.ts (live from Sanity post slugs alread…</t>
+          <t>Shared typography components</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>y, extended per-section in later phases)</t>
+          <t>ended up built directly in Phase 5 (portable-text.tsx, drop-cap CSS, pull-quote block) rather than as a separate Phase 3 deliverable, since that's where they're actually consumed</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
@@ -2185,7 +2185,7 @@
       <c r="A53" s="4" t="n"/>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Error boundary (error.tsx) and not-found.tsx (real legacy 404 copy + countdown-redirect behavior ported from pages/NotFound.tsx)</t>
+          <t>robots.ts (AI crawlers explicitly allowed per the current SEO plan, scraper bots blocked) and sitemap.ts (live from Sanity post slugs alread…</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
@@ -2193,7 +2193,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr"/>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>y, extended per-section in later phases)</t>
+        </is>
+      </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
           <t>Phase 3 — Shared Layout &amp; Design System</t>
@@ -2204,7 +2208,7 @@
       <c r="A54" s="4" t="n"/>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Loading UI (loading.tsx) using shadcn Skeleton</t>
+          <t>Error boundary (error.tsx) and not-found.tsx (real legacy 404 copy + countdown-redirect behavior ported from pages/NotFound.tsx)</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
@@ -2223,7 +2227,7 @@
       <c r="A55" s="4" t="n"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Icon library decision</t>
+          <t>Loading UI (loading.tsx) using shadcn Skeleton</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
@@ -2231,11 +2235,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>lucide-react for all standard UI icons (menu, sun/moon, chevrons); react-icons/fa6 only for the X/LinkedIn brand marks, since lucide-react v1 dropped brand/logo icons entirely</t>
-        </is>
-      </c>
+      <c r="D55" s="4" t="inlineStr"/>
       <c r="E55" s="14" t="inlineStr">
         <is>
           <t>Phase 3 — Shared Layout &amp; Design System</t>
@@ -2246,7 +2246,7 @@
       <c r="A56" s="4" t="n"/>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Top-of-page navigation progress bar (nav-progress-bar.tsx)</t>
+          <t>Icon library decision</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>visible feedback on route transitions, built on the Navigation API (window.navigation) rather than a dependency like nprogress; progressive enhancement, renders nothing where unsupported</t>
+          <t>lucide-react for all standard UI icons (menu, sun/moon, chevrons); react-icons/fa6 only for the X/LinkedIn brand marks, since lucide-react v1 dropped brand/logo icons entirely</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
@@ -2269,63 +2269,63 @@
       <c r="A57" s="4" t="n"/>
       <c r="B57" s="4" t="inlineStr">
         <is>
+          <t>Top-of-page navigation progress bar (nav-progress-bar.tsx)</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>visible feedback on route transitions, built on the Navigation API (window.navigation) rather than a dependency like nprogress; progressive enhancement, renders nothing where unsupported</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>Phase 3 — Shared Layout &amp; Design System</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n"/>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
           <t>Verify header/footer/nav visually in a real browser</t>
         </is>
       </c>
-      <c r="C57" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>Done 2026-09-29 with side-by-side Playwright screenshots against the live tonygreenberg.com at 1280/1536px. The header was rebuilt to match legacy Layout.tsx: full-width translucent cream bar, purple hairline, 0.78rem semi-bold mono nav right-aligned, gold active link, tagline at legacy's breakpoints, and the "Ask Tony ⌘K" pill (legacy TonyDiscovery; it opens site search because the FauxTony chat half was cancelled), plus X/LinkedIn icons and the theme toggle. Also matched from the live site: the Four Doors modal (legacy FourDoorsModal.tsx: image header, Door badge, ochre rule, dark CTA, bottom sheet on mobile), the homepage BrewSoul "Intelligence Engine" band (legacy BrewSoulHero.tsx, background photo rescued into Sanity), and the default theme, now light and not following the OS, same as legacy's ThemeContext. The "New here? 90-second tour" banner (StartHereBanner) is still intentionally not ported.</t>
         </is>
       </c>
-      <c r="E57" s="14" t="inlineStr">
+      <c r="E58" s="14" t="inlineStr">
         <is>
           <t>Phase 3 — Shared Layout &amp; Design System</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>Phase 4 — Marketing Core Pages (30 routes)</t>
         </is>
       </c>
-      <c r="B58" s="11" t="n"/>
-      <c r="C58" s="11" t="n"/>
-      <c r="D58" s="12" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="n"/>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>/ (homepage)</t>
-        </is>
-      </c>
-      <c r="C59" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>Blog.tsx. Not the same page as /the-letter — legacy actually routes path="/" to the Blog component, not Home.tsx (Home.tsx is legacy's /the-letter, already ported separately below); this had briefly regressed to a plain paginated post list before this pass corrected it. Real content ported: hero (headline, stats line, essay count/nav line), Four Doors (Read/Diagnose/Engage/Verify — reusing the shared FourDoors component built for /the-letter; its icon-tile fallback path stays in four-doors.tsx for resilience, but all 4 real source photos are now live — see the follow-up pass note below), Editor's Picks (5 real curated posts), GemSpark Strip (a real, small editorial motif — only 3 posts in the whole corpus reference it; hand-ported subtitles since Portable Text has no raw-heading string left to regex the way legacy did), Case File banner, Latest Thinking, Positioning Statement, Core Themes (4 theme cards linking to /?theme=X#essays-archive, read by the archive below), Ecosystem CTA (essay count now live from Sanity instead of legacy's stale hardcoded "ninety-one"), and the full searchable/filterable archive + sidebar (Curated Journeys, Tip Me Off, Follow). Intentionally not ported: the ABIT waitlist email-capture form (posts to a tRPC subscribe mutation — a backend/CRM feature, out of this migration's "no backend features" scope, not a content gap) and legacy's "Most Read"/"Most Provocative" sidebar widgets (both ranked by a reads count that defaulted to a flat placeholder val</t>
-        </is>
-      </c>
-      <c r="E59" s="14" t="inlineStr">
-        <is>
-          <t>Phase 4 — Marketing Core Pages (30 routes)</t>
-        </is>
-      </c>
+      <c r="B59" s="11" t="n"/>
+      <c r="C59" s="11" t="n"/>
+      <c r="D59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n"/>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>/the-letter</t>
+          <t>/ (homepage)</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Home.tsx. Real content/links/data ported (hero, Three Paths, Start Here essays, Four Doors as a shadcn Dialog instead of the legacy custom modal, Featured Essay pulled live from Sanity, How Tony Works, Investment Thesis, Open Questions, What I Build, Most Read, BrewSoul teaser). Deliberately not reproduced: floating-particle animation, glowing-bowl gradients, glitch text, magnetic-hover physics, typewriter intro — decorative flourishes, same judgment call as Phase 3's engagement widgets. Rescued 5 images (hero + 4 door photos) from the still-live legacy /api/img/ proxy into Sanity before porting (scripts/rescue-homepage-images.ts) rather than reference the fragile path. Fixed 2 legacy bugs found while porting: /ramprate and /human-os linked to routes that don't exist (corrected to https://ramprate.com and /humanos); "Most Read"'s 5 items all pointed at the same generic /blog placeholder instead of each post's real slug — corrected using the real migrated post slugs. Verified live: 200 OK, real content, fixed links, real images, no leaked inline styles, lint+typecheck clean.</t>
+          <t>Blog.tsx. Not the same page as /the-letter — legacy actually routes path="/" to the Blog component, not Home.tsx (Home.tsx is legacy's /the-letter, already ported separately below); this had briefly regressed to a plain paginated post list before this pass corrected it. Real content ported: hero (headline, stats line, essay count/nav line), Four Doors (Read/Diagnose/Engage/Verify — reusing the shared FourDoors component built for /the-letter; its icon-tile fallback path stays in four-doors.tsx for resilience, but all 4 real source photos are now live — see the follow-up pass note below), Editor's Picks (5 real curated posts), GemSpark Strip (a real, small editorial motif — only 3 posts in the whole corpus reference it; hand-ported subtitles since Portable Text has no raw-heading string left to regex the way legacy did), Case File banner, Latest Thinking, Positioning Statement, Core Themes (4 theme cards linking to /?theme=X#essays-archive, read by the archive below), Ecosystem CTA (essay count now live from Sanity instead of legacy's stale hardcoded "ninety-one"), and the full searchable/filterable archive + sidebar (Curated Journeys, Tip Me Off, Follow). Intentionally not ported: the ABIT waitlist email-capture form (posts to a tRPC subscribe mutation — a backend/CRM feature, out of this migration's "no backend features" scope, not a content gap) and legacy's "Most Read"/"Most Provocative" sidebar widgets (both ranked by a reads count that defaulted to a flat placeholder val</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
@@ -2348,7 +2348,7 @@
       <c r="A61" s="4" t="n"/>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>/walk-through</t>
+          <t>/the-letter</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>WalkThrough.tsx. Real content ported (7 doors, entity pills w/ real named investments, "Ask me about" lines, cross-links, pull quotes, "The Lesson" callout). Hero reuses the Tony headshot already rescued to Sanity (Phase 12 JSON-LD work) rather than re-fetching. Not ported: AutoLinkedText's automatic entity hyperlinking — that's driven by the site-wide linkMap.ts, a genuine cross-cutting feature affecting many pages, not a one-off for this page; folded into the existing "preserve internal cross-link structure" open item in Phase 5. Verified live: 200 OK, real content, real image, correct next-page link.</t>
+          <t>Home.tsx. Real content/links/data ported (hero, Three Paths, Start Here essays, Four Doors as a shadcn Dialog instead of the legacy custom modal, Featured Essay pulled live from Sanity, How Tony Works, Investment Thesis, Open Questions, What I Build, Most Read, BrewSoul teaser). Deliberately not reproduced: floating-particle animation, glowing-bowl gradients, glitch text, magnetic-hover physics, typewriter intro — decorative flourishes, same judgment call as Phase 3's engagement widgets. Rescued 5 images (hero + 4 door photos) from the still-live legacy /api/img/ proxy into Sanity before porting (scripts/rescue-homepage-images.ts) rather than reference the fragile path. Fixed 2 legacy bugs found while porting: /ramprate and /human-os linked to routes that don't exist (corrected to https://ramprate.com and /humanos); "Most Read"'s 5 items all pointed at the same generic /blog placeholder instead of each post's real slug — corrected using the real migrated post slugs. Verified live: 200 OK, real content, fixed links, real images, no leaked inline styles, lint+typecheck clean.</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
@@ -2371,7 +2371,7 @@
       <c r="A62" s="4" t="n"/>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>/the-territory</t>
+          <t>/walk-through</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Territory.tsx. Real content ported (10 heroes/influences with full notes, Operating Philosophy, pull quote, "The Lesson" callout, next-page link). Verified live: 200 OK, real content, correct next-page link.</t>
+          <t>WalkThrough.tsx. Real content ported (7 doors, entity pills w/ real named investments, "Ask me about" lines, cross-links, pull quotes, "The Lesson" callout). Hero reuses the Tony headshot already rescued to Sanity (Phase 12 JSON-LD work) rather than re-fetching. Not ported: AutoLinkedText's automatic entity hyperlinking — that's driven by the site-wide linkMap.ts, a genuine cross-cutting feature affecting many pages, not a one-off for this page; folded into the existing "preserve internal cross-link structure" open item in Phase 5. Verified live: 200 OK, real content, real image, correct next-page link.</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
@@ -2394,7 +2394,7 @@
       <c r="A63" s="4" t="n"/>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>/engine-room</t>
+          <t>/the-territory</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>EngineRoom.tsx. Real content ported (6 active ventures, 4 active engagements, pull quote, "The Lesson" callout, next-page link). Verified live: 200 OK, real content, correct next-page link.</t>
+          <t>Territory.tsx. Real content ported (10 heroes/influences with full notes, Operating Philosophy, pull quote, "The Lesson" callout, next-page link). Verified live: 200 OK, real content, correct next-page link.</t>
         </is>
       </c>
       <c r="E63" s="14" t="inlineStr">
@@ -2417,7 +2417,7 @@
       <c r="A64" s="4" t="n"/>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>/under-nda</t>
+          <t>/engine-room</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>UnderNDA.tsx. Real content ported (Corridor overview, pull quote, "What We're Building" list, inline quote, "The Lesson", next-page link). Verified live: 200 OK.</t>
+          <t>EngineRoom.tsx. Real content ported (6 active ventures, 4 active engagements, pull quote, "The Lesson" callout, next-page link). Verified live: 200 OK, real content, correct next-page link.</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
@@ -2440,7 +2440,7 @@
       <c r="A65" s="4" t="n"/>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>/the-body</t>
+          <t>/under-nda</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>TheBody.tsx. Real content ported (Alt Therapy Scorecard, Current Protocols, Peptide Research Tools links, pull quote, "The Lesson"). Hero image rescued from legacy /api/img/ into Sanity before porting. Verified live: 200 OK, real image.</t>
+          <t>UnderNDA.tsx. Real content ported (Corridor overview, pull quote, "What We're Building" list, inline quote, "The Lesson", next-page link). Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E65" s="14" t="inlineStr">
@@ -2463,7 +2463,7 @@
       <c r="A66" s="4" t="n"/>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>/the-nightstand</t>
+          <t>/the-body</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Nightstand.tsx. Real content ported (7 books, 5 key concepts, pull quote, "The Lesson"). Hero image rescued into Sanity. Verified live: 200 OK, real image.</t>
+          <t>TheBody.tsx. Real content ported (Alt Therapy Scorecard, Current Protocols, Peptide Research Tools links, pull quote, "The Lesson"). Hero image rescued from legacy /api/img/ into Sanity before porting. Verified live: 200 OK, real image.</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
@@ -2486,7 +2486,7 @@
       <c r="A67" s="4" t="n"/>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>/the-web</t>
+          <t>/the-nightstand</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>TheWeb.tsx. Real content ported (20 client badges, 4 key partnerships, pull quote, adage strip, "The Lesson"). Hero image rescued into Sanity. Verified live: 200 OK, real image.</t>
+          <t>Nightstand.tsx. Real content ported (7 books, 5 key concepts, pull quote, "The Lesson"). Hero image rescued into Sanity. Verified live: 200 OK, real image.</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
@@ -2509,7 +2509,7 @@
       <c r="A68" s="4" t="n"/>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>/pick-up-the-phone</t>
+          <t>/the-web</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>PickUp.tsx. Real content ported (Engagement Audit CTA to /engage, email/location, "What to Talk About" topics, social links, pull quote, "The Lesson"). Verified live: 200 OK.</t>
+          <t>TheWeb.tsx. Real content ported (20 client badges, 4 key partnerships, pull quote, adage strip, "The Lesson"). Hero image rescued into Sanity. Verified live: 200 OK, real image.</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
@@ -2532,7 +2532,7 @@
       <c r="A69" s="4" t="n"/>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>/journeys</t>
+          <t>/pick-up-the-phone</t>
         </is>
       </c>
       <c r="C69" s="13" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Journeys.tsx. Real content ported (7 curated journeys, all real stops/teasers), rebuilt as a proper shadcn Accordion instead of hand-rolled expand state. Fixed 2 legacy bugs: stops pointing at / meant the old homepage — remapped to /the-letter since / is now the blog index; 3 "Crusade Files" stops pointed at the generic /blog placeholder instead of the specific post — corrected to real slugs. Also caught a real SEO issue: shadcn's AccordionContent doesn't render collapsed-panel children into the DOM at all by default — every internal link on this link-heavy page was invisible to crawlers until a user clicked to expand it. Fixed with forceMount (documented inline). Worth checking any other page that ends up using Accordion for real content, not just decoration. Verified live: 200 OK, all links (including the corrected ones) present in the raw server-rendered HTML, not just after hydration.</t>
+          <t>PickUp.tsx. Real content ported (Engagement Audit CTA to /engage, email/location, "What to Talk About" topics, social links, pull quote, "The Lesson"). Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
@@ -2555,7 +2555,7 @@
       <c r="A70" s="4" t="n"/>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>/recent-creations</t>
+          <t>/journeys</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Portfolio.tsx. Real content ported (11 project cards, real accent colors — the one legitimate per-item inline-style exception, static Tailwind classes can't express 11 runtime hex values). Fixed a dead internal link (Homeaglow Exposed pointed at a route that doesn't exist anywhere; corrected to the real external homeaglowexposed.com already used consistently on other ported pages) and remapped / → /the-letter. Flagged but did NOT fix: "FusionRamp / STRATUM" points at /humanos, same as the unrelated Human OS card — looks like a copy-paste bug but there's no confirmed correct destination anywhere in the codebase, so ported as-is with a comment rather than guessed; worth a content-team check. Verified live: 200 OK, fixed links present.</t>
+          <t>Journeys.tsx. Real content ported (7 curated journeys, all real stops/teasers), rebuilt as a proper shadcn Accordion instead of hand-rolled expand state. Fixed 2 legacy bugs: stops pointing at / meant the old homepage — remapped to /the-letter since / is now the blog index; 3 "Crusade Files" stops pointed at the generic /blog placeholder instead of the specific post — corrected to real slugs. Also caught a real SEO issue: shadcn's AccordionContent doesn't render collapsed-panel children into the DOM at all by default — every internal link on this link-heavy page was invisible to crawlers until a user clicked to expand it. Fixed with forceMount (documented inline). Worth checking any other page that ends up using Accordion for real content, not just decoration. Verified live: 200 OK, all links (including the corrected ones) present in the raw server-rendered HTML, not just after hydration.</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
@@ -2578,7 +2578,7 @@
       <c r="A71" s="4" t="n"/>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>/intel</t>
+          <t>/recent-creations</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Intel.tsx. Real content ported in full (9 portfolio companies, each with investment thesis, three gates, 7-dimension compass scores, full iRR framework, competitive landscape). Rebuilt as a shadcn Accordion with forceMount from the start (learned from /journeys), verified live that investment-thesis/competitor text is present in the raw SSR HTML, not just after a click. Verified live: 200 OK.</t>
+          <t>Portfolio.tsx. Real content ported (11 project cards, real accent colors — the one legitimate per-item inline-style exception, static Tailwind classes can't express 11 runtime hex values). Fixed a dead internal link (Homeaglow Exposed pointed at a route that doesn't exist anywhere; corrected to the real external homeaglowexposed.com already used consistently on other ported pages) and remapped / → /the-letter. Flagged but did NOT fix: "FusionRamp / STRATUM" points at /humanos, same as the unrelated Human OS card — looks like a copy-paste bug but there's no confirmed correct destination anywhere in the codebase, so ported as-is with a comment rather than guessed; worth a content-team check. Verified live: 200 OK, fixed links present.</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
@@ -2601,7 +2601,7 @@
       <c r="A72" s="4" t="n"/>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>/about</t>
+          <t>/intel</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>About.tsx. Real content ported in full (3 narrative chapters, "The Receipts" stats, "What I'm Thinking Now", The Muse, Featured In, closing CTA). Built partner-quotes.tsx as a proper shared component (19 real client testimonials — Disney, Microsoft, eBay, Sony, etc.) since it's a cross-page resource, not a one-off; made it deterministic instead of the legacy Math.random() shuffle so quotes are actually in the SSR HTML. Reused the headshot + homepage hero images already rescued to Sanity. Correctly left this page's "Back to the Essays" link at / as-is (unlike other pages, this one genuinely means the blog/essays index). Verified live: 200 OK, both images, real quotes.</t>
+          <t>Intel.tsx. Real content ported in full (9 portfolio companies, each with investment thesis, three gates, 7-dimension compass scores, full iRR framework, competitive landscape). Rebuilt as a shadcn Accordion with forceMount from the start (learned from /journeys), verified live that investment-thesis/competitor text is present in the raw SSR HTML, not just after a click. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
@@ -2624,7 +2624,7 @@
       <c r="A73" s="4" t="n"/>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>/speaking</t>
+          <t>/about</t>
         </is>
       </c>
       <c r="C73" s="13" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Speaking.tsx. Real content ported (4 speaking topics, 4 formats, rooms spoken at, CTA). Verified live: 200 OK.</t>
+          <t>About.tsx. Real content ported in full (3 narrative chapters, "The Receipts" stats, "What I'm Thinking Now", The Muse, Featured In, closing CTA). Built partner-quotes.tsx as a proper shared component (19 real client testimonials — Disney, Microsoft, eBay, Sony, etc.) since it's a cross-page resource, not a one-off; made it deterministic instead of the legacy Math.random() shuffle so quotes are actually in the SSR HTML. Reused the headshot + homepage hero images already rescued to Sanity. Correctly left this page's "Back to the Essays" link at / as-is (unlike other pages, this one genuinely means the blog/essays index). Verified live: 200 OK, both images, real quotes.</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
@@ -2647,7 +2647,7 @@
       <c r="A74" s="4" t="n"/>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>/ecosystem</t>
+          <t>/speaking</t>
         </is>
       </c>
       <c r="C74" s="13" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Ecosystem.tsx. Real content ported (What It Is, Who It's For, What Members Receive, invitation CTA). Verified live: 200 OK.</t>
+          <t>Speaking.tsx. Real content ported (4 speaking topics, 4 formats, rooms spoken at, CTA). Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
@@ -2670,7 +2670,7 @@
       <c r="A75" s="4" t="n"/>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>/start-here</t>
+          <t>/ecosystem</t>
         </is>
       </c>
       <c r="C75" s="13" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>StartHere.tsx. Real content ported (5 curated essay cards, "After the Foundation" CTA). Found all 5 curated essays have no real hero image — a subset of the 99 in BLOG-IMAGE-BRIEFS.md, but higher priority since this is the site's own "read these first" page; renders a graceful tag-colored number panel instead of a broken image meanwhile. Verified live: 200 OK.</t>
+          <t>Ecosystem.tsx. Real content ported (What It Is, Who It's For, What Members Receive, invitation CTA). Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
@@ -2693,7 +2693,7 @@
       <c r="A76" s="4" t="n"/>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>/published</t>
+          <t>/start-here</t>
         </is>
       </c>
       <c r="C76" s="13" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Published.tsx. Real content ported in full (5 publication badges, 30 real bylines with real external URLs across 6 categories, speaking/podcast list). Caught two real Tailwind bugs before shipping: (1) building class names via hover:${c.border} / ${c.border}/20 template-literal concatenation doesn't work — Tailwind's scanner needs the complete literal string present in source, so those never would have generated any CSS; fixed by precomposing every exact variant as a full literal string. (2) mixing an all-sides border-[color] with a directional border-l-4 would have fought the base border-border on other sides — fixed using directional border-l-[color] utilities instead. Verified the fix by running a full production build and grepping the compiled CSS chunk directly for border-l-[#2563eb]/30 and hover:border-l-[#2563eb] — both present as real rules, not just present as strings in the HTML. Also ran pnpm build clean across all 16 pages shipped so far (154 static pages total) as a broader checkpoint.</t>
+          <t>StartHere.tsx. Real content ported (5 curated essay cards, "After the Foundation" CTA). Found all 5 curated essays have no real hero image — a subset of the 99 in BLOG-IMAGE-BRIEFS.md, but higher priority since this is the site's own "read these first" page; renders a graceful tag-colored number panel instead of a broken image meanwhile. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
@@ -2716,7 +2716,7 @@
       <c r="A77" s="4" t="n"/>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>/clients</t>
+          <t>/published</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Clients.tsx. Real content ported in full (90 real client names with industry + Hawkins-score data, real filter/sort interactivity rebuilt in a small client component, Hawkins scale legend, CTA). Caught another real React bug before shipping: FilterButton was defined inside ClientsGrid's render body (react-hooks/static-components — recreates the component type every render, resetting its state); moved to module scope. Verified live: 200 OK, real client names present.</t>
+          <t>Published.tsx. Real content ported in full (5 publication badges, 30 real bylines with real external URLs across 6 categories, speaking/podcast list). Caught two real Tailwind bugs before shipping: (1) building class names via hover:${c.border} / ${c.border}/20 template-literal concatenation doesn't work — Tailwind's scanner needs the complete literal string present in source, so those never would have generated any CSS; fixed by precomposing every exact variant as a full literal string. (2) mixing an all-sides border-[color] with a directional border-l-4 would have fought the base border-border on other sides — fixed using directional border-l-[color] utilities instead. Verified the fix by running a full production build and grepping the compiled CSS chunk directly for border-l-[#2563eb]/30 and hover:border-l-[#2563eb] — both present as real rules, not just present as strings in the HTML. Also ran pnpm build clean across all 16 pages shipped so far (154 static pages total) as a broader checkpoint.</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
@@ -2739,7 +2739,7 @@
       <c r="A78" s="4" t="n"/>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>/series</t>
+          <t>/clients</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Series.tsx ("The Collections"). Real content ported in full (11 real curated essay series with real, already-migrated post slugs, 6 legacy category colors as precomposed literal Tailwind classes per the /published pattern — not fragment-assembled). Episode titles/hero images now fetched live from Sanity via a new postsBySlugsQuery instead of the legacy static blogData.json import, so they stay in sync as posts get real hero images added. Fixed a dead legacy link: /the-index (not a real route, not in nav) → /search (the label "Search All Essays" clearly describes this app's planned search page). Verified live: 200 OK, all 11 series titles present, 49 real post links, real Sanity hero images rendering where the linked post has one.</t>
+          <t>Clients.tsx. Real content ported in full (90 real client names with industry + Hawkins-score data, real filter/sort interactivity rebuilt in a small client component, Hawkins scale legend, CTA). Caught another real React bug before shipping: FilterButton was defined inside ClientsGrid's render body (react-hooks/static-components — recreates the component type every render, resetting its state); moved to module scope. Verified live: 200 OK, real client names present.</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
@@ -2762,7 +2762,7 @@
       <c r="A79" s="4" t="n"/>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>/framework</t>
+          <t>/series</t>
         </is>
       </c>
       <c r="C79" s="13" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>LeadMagnet.tsx ("How I'd Approach Your Problem"). Real content ported in full (5-step framework, each with real description/prompt/real-world example). Rebuilt the per-step "see real-world example" toggle as shadcn Collapsible with forceMount (same crawlability rule as /journeys//intel — verified the example text is in the raw SSR HTML, not just after a click), installed via pnpm dlx shadcn add collapsible since it wasn't in the project yet. Intentionally not ported: the email-gated "download the worksheet" form — it posted to a tRPC subscribe mutation and didn't actually attach/send a real PDF even in the legacy source (just showed a success message), a backend feature with no real deliverable behind it, out of scope. Replaced with a direct CTA to /pick-up-the-phone. Verified live: 200 OK, all 5 steps + real-world examples present in SSR HTML, lint+typecheck clean.</t>
+          <t>Series.tsx ("The Collections"). Real content ported in full (11 real curated essay series with real, already-migrated post slugs, 6 legacy category colors as precomposed literal Tailwind classes per the /published pattern — not fragment-assembled). Episode titles/hero images now fetched live from Sanity via a new postsBySlugsQuery instead of the legacy static blogData.json import, so they stay in sync as posts get real hero images added. Fixed a dead legacy link: /the-index (not a real route, not in nav) → /search (the label "Search All Essays" clearly describes this app's planned search page). Verified live: 200 OK, all 11 series titles present, 49 real post links, real Sanity hero images rendering where the linked post has one.</t>
         </is>
       </c>
       <c r="E79" s="14" t="inlineStr">
@@ -2785,7 +2785,7 @@
       <c r="A80" s="4" t="n"/>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>/spirits</t>
+          <t>/framework</t>
         </is>
       </c>
       <c r="C80" s="13" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Spirits.tsx ("The Liquid Library"). Real content ported in full (5 categories — Mezcal, Tequila, Sake, Coffee, Wine — each with philosophy, obsessions list, pullquote; Tequila's 5-item "Agave Matchmaker" newsletter digest; Sake's "coming soon" note). Caught two dead external links: the Mezcal and Tequila companion sites (SoulSmoke, LiquidSun) were hosted on *.manus.space — confirmed 503 along with the rest of Manus, not just the primary domain. Rendered as a non-linked "no longer live" card instead of a broken outbound link, keeping the real descriptive copy. Coffee's /brewsoul link kept as-is (real future internal route, Phase 6, not yet built). Verified live: 200 OK, all 5 categories + digest content present, dead external links correctly not rendered as &lt;a&gt; tags.</t>
+          <t>LeadMagnet.tsx ("How I'd Approach Your Problem"). Real content ported in full (5-step framework, each with real description/prompt/real-world example). Rebuilt the per-step "see real-world example" toggle as shadcn Collapsible with forceMount (same crawlability rule as /journeys//intel — verified the example text is in the raw SSR HTML, not just after a click), installed via pnpm dlx shadcn add collapsible since it wasn't in the project yet. Intentionally not ported: the email-gated "download the worksheet" form — it posted to a tRPC subscribe mutation and didn't actually attach/send a real PDF even in the legacy source (just showed a success message), a backend feature with no real deliverable behind it, out of scope. Replaced with a direct CTA to /pick-up-the-phone. Verified live: 200 OK, all 5 steps + real-world examples present in SSR HTML, lint+typecheck clean.</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
@@ -2808,7 +2808,7 @@
       <c r="A81" s="4" t="n"/>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>/community (+ /find-my-tribe → 308 redirect, next.config.ts)</t>
+          <t>/spirits</t>
         </is>
       </c>
       <c r="C81" s="13" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Community.tsx. Legacy is almost entirely a functional community/CRM platform (auth-gated profile editing, CSV contact upload, email invites, member directory) backed by tRPC + a custom auth system — a backend feature, not a content page, out of this migration's scope. Ported the only real editorial content (hero copy, closing manifesto quote/link) and replaced the auth-gated CRUD tabs with an honest "still being built" note + a real CTA to /pick-up-the-phone, rather than reproducing a non-functional sign-in gate. Verified live: 200 OK, redirect confirmed 308.</t>
+          <t>Spirits.tsx ("The Liquid Library"). Real content ported in full (5 categories — Mezcal, Tequila, Sake, Coffee, Wine — each with philosophy, obsessions list, pullquote; Tequila's 5-item "Agave Matchmaker" newsletter digest; Sake's "coming soon" note). Caught two dead external links: the Mezcal and Tequila companion sites (SoulSmoke, LiquidSun) were hosted on *.manus.space — confirmed 503 along with the rest of Manus, not just the primary domain. Rendered as a non-linked "no longer live" card instead of a broken outbound link, keeping the real descriptive copy. Coffee's /brewsoul link kept as-is (real future internal route, Phase 6, not yet built). Verified live: 200 OK, all 5 categories + digest content present, dead external links correctly not rendered as &lt;a&gt; tags.</t>
         </is>
       </c>
       <c r="E81" s="14" t="inlineStr">
@@ -2831,7 +2831,7 @@
       <c r="A82" s="4" t="n"/>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>/engage</t>
+          <t>/community (+ /find-my-tribe → 308 redirect, next.config.ts)</t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Engage.tsx ("The Gate"). The qualification quiz itself (5 real questions, the exact scoring heuristic, all 3 result screens — qualified/not-ready/wrong-fit, the real Calendly link, the 2× guarantee copy) is genuinely client-side logic already in legacy (scored by a pure regex/word-count function, no server round-trip needed to decide the outcome) — ported in full as real assessment logic per the CMS-boundary rule. Not ported: the tRPC engage.submit mutation that logged each submission for Tony's own records — a lead-tracking write, out of scope; dropping it doesn't change the visitor's experience, the gate still scores and unlocks the real Calendly link correctly. Verified live: 200 OK, full quiz flow present, lint+typecheck clean.</t>
+          <t>Community.tsx. Legacy is almost entirely a functional community/CRM platform (auth-gated profile editing, CSV contact upload, email invites, member directory) backed by tRPC + a custom auth system — a backend feature, not a content page, out of this migration's scope. Ported the only real editorial content (hero copy, closing manifesto quote/link) and replaced the auth-gated CRUD tabs with an honest "still being built" note + a real CTA to /pick-up-the-phone, rather than reproducing a non-functional sign-in gate. Verified live: 200 OK, redirect confirmed 308.</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
@@ -2854,7 +2854,7 @@
       <c r="A83" s="4" t="n"/>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>/amplifier</t>
+          <t>/engage</t>
         </is>
       </c>
       <c r="C83" s="13" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Amplifier.tsx. Real content ported in full and unreduced (Matt Mochary note, 5 pillars, unfair advantage, 2× guarantee, 4 real pricing tiers, prep-doc requirements, "what Tony will not do" list). No backend dependency at all — every CTA is either an internal /engage link or a real mailto:. Verified live: 200 OK, all sections + both CTA link types present.</t>
+          <t>Engage.tsx ("The Gate"). The qualification quiz itself (5 real questions, the exact scoring heuristic, all 3 result screens — qualified/not-ready/wrong-fit, the real Calendly link, the 2× guarantee copy) is genuinely client-side logic already in legacy (scored by a pure regex/word-count function, no server round-trip needed to decide the outcome) — ported in full as real assessment logic per the CMS-boundary rule. Not ported: the tRPC engage.submit mutation that logged each submission for Tony's own records — a lead-tracking write, out of scope; dropping it doesn't change the visitor's experience, the gate still scores and unlocks the real Calendly link correctly. Verified live: 200 OK, full quiz flow present, lint+typecheck clean.</t>
         </is>
       </c>
       <c r="E83" s="14" t="inlineStr">
@@ -2877,7 +2877,7 @@
       <c r="A84" s="4" t="n"/>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>/diamond-cut</t>
+          <t>/amplifier</t>
         </is>
       </c>
       <c r="C84" s="13" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>DiamondCut.tsx. Real content ported in full (Honest Note re: Matt Mochary, 5 cuts, 2× guarantee, 4 real pricing tiers). Legacy's 3 non-"Setting" tiers used a live StripeCheckoutButton — checkout/billing is deferred per this migration's scope, so those now route to /engage instead (pricing/copy unchanged, matching how /amplifier's tiers already work), rather than wiring up a real payment flow this pass. Verified live: 200 OK, all sections + tiers present.</t>
+          <t>Amplifier.tsx. Real content ported in full and unreduced (Matt Mochary note, 5 pillars, unfair advantage, 2× guarantee, 4 real pricing tiers, prep-doc requirements, "what Tony will not do" list). No backend dependency at all — every CTA is either an internal /engage link or a real mailto:. Verified live: 200 OK, all sections + both CTA link types present.</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
@@ -2900,7 +2900,7 @@
       <c r="A85" s="4" t="n"/>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>/essays</t>
+          <t>/diamond-cut</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Essays.tsx. A second, distinct essay index from the homepage's archive — filters by "archetype" (Builder/Crusader/Investor, ported from client/src/data/archetypes.ts as src/lib/content/archetypes.ts) instead of Core Themes, compact list layout instead of a card grid. Not linked from current nav (legacy didn't link it from nav either — it's a real destination referenced by other not-yet-built pages like SkippyMap/CheshireGrin). Posts now fetched live from Sanity instead of the static blogData.json import. Verified live: 200 OK, archetype/category filters + real post list present.</t>
+          <t>DiamondCut.tsx. Real content ported in full (Honest Note re: Matt Mochary, 5 cuts, 2× guarantee, 4 real pricing tiers). Legacy's 3 non-"Setting" tiers used a live StripeCheckoutButton — checkout/billing is deferred per this migration's scope, so those now route to /engage instead (pricing/copy unchanged, matching how /amplifier's tiers already work), rather than wiring up a real payment flow this pass. Verified live: 200 OK, all sections + tiers present.</t>
         </is>
       </c>
       <c r="E85" s="14" t="inlineStr">
@@ -2923,7 +2923,7 @@
       <c r="A86" s="4" t="n"/>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>/invest</t>
+          <t>/essays</t>
         </is>
       </c>
       <c r="C86" s="13" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Invest.tsx ("Invest in the Thesis"). Real content ported in full — 6 portfolio categories, 32 real named companies with role/note, "and many more" teaser → /engage, ABIT waitlist section. The waitlist is a real outbound link to impactsoul.is (confirmed live, a separate real site) — no backend/email-capture on this page at all. Verified live: 200 OK, all 6 categories + companies + outbound link present.</t>
+          <t>Essays.tsx. A second, distinct essay index from the homepage's archive — filters by "archetype" (Builder/Crusader/Investor, ported from client/src/data/archetypes.ts as src/lib/content/archetypes.ts) instead of Core Themes, compact list layout instead of a card grid. Not linked from current nav (legacy didn't link it from nav either — it's a real destination referenced by other not-yet-built pages like SkippyMap/CheshireGrin). Posts now fetched live from Sanity instead of the static blogData.json import. Verified live: 200 OK, archetype/category filters + real post list present.</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
@@ -2946,7 +2946,7 @@
       <c r="A87" s="4" t="n"/>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>/akbar</t>
+          <t>/invest</t>
         </is>
       </c>
       <c r="C87" s="13" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>AkbarEssay.tsx ("Los Angeles Is Losing Its Memory"). Real essay prose ported in full, unchanged (every section, every pull quote, all 6 wine pairings, the 3 reframe terms). Legacy was a ~20-image photo essay entirely on the now-fully-dead Manus /api/img/ host — none recoverable, confirmed 404/503. Rather than fabricate placeholder imagery for a piece about specific real photographs, ported as a clean long-form article and tracked the loss explicitly (see Phase 13) instead of pretending it's not there. Kept the deliberately dark, fixed palette (this is a one-off bespoke essay design, not site chrome, so a permanent dark mood is the real intent) but reused the site's existing loaded fonts instead of the 3 extra webfonts legacy imported for just this page. Verified live: 200 OK, full essay text present.</t>
+          <t>Invest.tsx ("Invest in the Thesis"). Real content ported in full — 6 portfolio categories, 32 real named companies with role/note, "and many more" teaser → /engage, ABIT waitlist section. The waitlist is a real outbound link to impactsoul.is (confirmed live, a separate real site) — no backend/email-capture on this page at all. Verified live: 200 OK, all 6 categories + companies + outbound link present.</t>
         </is>
       </c>
       <c r="E87" s="14" t="inlineStr">
@@ -2969,7 +2969,7 @@
       <c r="A88" s="4" t="n"/>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>/living-declaration (+ /manifesto → 308 redirect, next.config.ts)</t>
+          <t>/akbar</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Manifesto.tsx ("A Living Declaration — The Measurement of Becoming"). Real essay prose ported in full: the premise, "Boiling the Human" retrospective, 4 real pull quotes (Tristan Harris, Toffler, Harari, Eisenstein), the original 6 numbered practices + exceptions + specific steps, Phase 2/Balaji Srinivasan section, The Puzzle Pieces (acknowledgments), the 6 Roman-numeral principles, and the closing CTAs. Legacy's hero photo, "hand breakthrough" image, and Clarisse Abelarde's artwork photo are all on the now-fully-dead Manus host — dropped (real text credit to her kept), not fabricated. The "Ecosystem Map" 6-card grid originally linked to 6 other Manus-hosted micro-sites (Gem Spark, Regenerative Protocol, SoulSmoke, LiquidSun, Sacred Waters, Intimacy Assessment) plus a "Vancefolio" site — confirmed all 503; those link chips dropped, keeping only chips to pages actually live in this app (or genuinely planned, like /humanos//flow-circuit, already referenced elsewhere in this migration). The interactive questionnaire (trpc.manifesto.submit — unlike /engage's audit, this one has no logic that works without a backend) replaced with a direct, real mailto: invitation instead of a form that would go nowhere. Corrected /assessment → /assessments (the real legacy route name, confirmed in App.tsx; the singular looks like a typo in the original). Verified live: 200 OK, all sections + quotes present, redirect confirmed 308.</t>
+          <t>AkbarEssay.tsx ("Los Angeles Is Losing Its Memory"). Real essay prose ported in full, unchanged (every section, every pull quote, all 6 wine pairings, the 3 reframe terms). Legacy was a ~20-image photo essay entirely on the now-fully-dead Manus /api/img/ host — none recoverable, confirmed 404/503. Rather than fabricate placeholder imagery for a piece about specific real photographs, ported as a clean long-form article and tracked the loss explicitly (see Phase 13) instead of pretending it's not there. Kept the deliberately dark, fixed palette (this is a one-off bespoke essay design, not site chrome, so a permanent dark mood is the real intent) but reused the site's existing loaded fonts instead of the 3 extra webfonts legacy imported for just this page. Verified live: 200 OK, full essay text present.</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
@@ -2992,7 +2992,7 @@
       <c r="A89" s="4" t="n"/>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>/protecting-your-business</t>
+          <t>/living-declaration (+ /manifesto → 308 redirect, next.config.ts)</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>ProtectingYourBusiness.tsx. Real documented fraud case file (Kristi Klawiter) ported in full — every factual claim, citation, the fact/opinion separation (AlertBox/OpinionBox), all quoted correspondence, the 13-section structure, and the full Legal Notice preserved verbatim; already-published, court-record-cited content, not new allegations authored here. Not ported: the "Submit Your Story" form (trpc.cheshire.submit — a lead-intake backend feature with no client-side logic of its own) replaced with a real mailto:; the closing SEO keyword-stuffing footer (bare repeated-name list, no informational content) dropped as an actual SEO improvement — modern search engines penalize that pattern, and the same keywords already live correctly in page metadata. Simplified the floating hamburger/TOC overlay to a plain inline jump-to-section list. Verified live: 200 OK, all sections + full legal notice present.</t>
+          <t>Manifesto.tsx ("A Living Declaration — The Measurement of Becoming"). Real essay prose ported in full: the premise, "Boiling the Human" retrospective, 4 real pull quotes (Tristan Harris, Toffler, Harari, Eisenstein), the original 6 numbered practices + exceptions + specific steps, Phase 2/Balaji Srinivasan section, The Puzzle Pieces (acknowledgments), the 6 Roman-numeral principles, and the closing CTAs. Legacy's hero photo, "hand breakthrough" image, and Clarisse Abelarde's artwork photo are all on the now-fully-dead Manus host — dropped (real text credit to her kept), not fabricated. The "Ecosystem Map" 6-card grid originally linked to 6 other Manus-hosted micro-sites (Gem Spark, Regenerative Protocol, SoulSmoke, LiquidSun, Sacred Waters, Intimacy Assessment) plus a "Vancefolio" site — confirmed all 503; those link chips dropped, keeping only chips to pages actually live in this app (or genuinely planned, like /humanos//flow-circuit, already referenced elsewhere in this migration). The interactive questionnaire (trpc.manifesto.submit — unlike /engage's audit, this one has no logic that works without a backend) replaced with a direct, real mailto: invitation instead of a form that would go nowhere. Corrected /assessment → /assessments (the real legacy route name, confirmed in App.tsx; the singular looks like a typo in the original). Verified live: 200 OK, all sections + quotes present, redirect confirmed 308.</t>
         </is>
       </c>
       <c r="E89" s="14" t="inlineStr">
@@ -3015,7 +3015,7 @@
       <c r="A90" s="4" t="n"/>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>/alex-azzi (+ /cheshire-grin, 308-redirected to it)</t>
+          <t>/protecting-your-business</t>
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>ported from legacy CheshireGrin.tsx (2608 lines), the VerifiedTribe Community Protection Report on Alex Azzi (CEO, XRWorkout). Site owner explicitly confirmed porting this, same content class as /protecting-your-business and following its established conventions (Tailwind instead of legacy's inline-style system, plain jump-to-section TOC, real generateMetadata + Article/FAQPage JSON-LD). Legacy registered the identical component at both /alex-azzi and /cheshire-grin with no redirect between them; picked /alex-azzi as canonical (the name people search for) and 308-redirected the other, matching the /find-my-tribe-style duplicate-route pattern already used throughout next.config.ts. Every dollar figure, date, case number, and quoted admission ported verbatim into lib/content/alex-azzi.ts — independently spot-checked against the legacy source (not just the port's own self-report) and confirmed exact matches on $137,000+/$75,000+/$15,000/CPR-2026-001/etc. Dropped 3 backend-dependent legacy features with no live tRPC to power them, matching /protecting-your-business's own precedent: the Submission Form (replaced with a real mailto: CTA), the Byron Katie Verification Gate modal (only existed to gate the removed form), and the Endorsement/"Ring the Bell" counter — its "7 testimonials received" claim was dropped rather than ported as fact, since it can't be verified without the backend that produced it. Real dead-link bug fixed: 2 of 20 "Ecosystem Interlinks" pointed to /assessment?t</t>
+          <t>ProtectingYourBusiness.tsx. Real documented fraud case file (Kristi Klawiter) ported in full — every factual claim, citation, the fact/opinion separation (AlertBox/OpinionBox), all quoted correspondence, the 13-section structure, and the full Legal Notice preserved verbatim; already-published, court-record-cited content, not new allegations authored here. Not ported: the "Submit Your Story" form (trpc.cheshire.submit — a lead-intake backend feature with no client-side logic of its own) replaced with a real mailto:; the closing SEO keyword-stuffing footer (bare repeated-name list, no informational content) dropped as an actual SEO improvement — modern search engines penalize that pattern, and the same keywords already live correctly in page metadata. Simplified the floating hamburger/TOC overlay to a plain inline jump-to-section list. Verified live: 200 OK, all sections + full legal notice present.</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
@@ -3038,7 +3038,7 @@
       <c r="A91" s="4" t="n"/>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Real bug found and fixed</t>
+          <t>/alex-azzi (+ /cheshire-grin, 308-redirected to it)</t>
         </is>
       </c>
       <c r="C91" s="13" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>(while verifying the above): a Core Themes selection (e.g. "The Crusades") often shares its display name with a real post category — showing it as a separate floating chip next to the category pill row (rather than merging into the matching pill) read as two disconnected, contradictory controls. Fixed HomeArchive so an active theme lights up the matching category pill directly (with the same click-to-clear ✕ affordance) instead of a separate chip; a theme with no same-named category still falls back to its own chip.</t>
+          <t>ported from legacy CheshireGrin.tsx (2608 lines), the VerifiedTribe Community Protection Report on Alex Azzi (CEO, XRWorkout). Site owner explicitly confirmed porting this, same content class as /protecting-your-business and following its established conventions (Tailwind instead of legacy's inline-style system, plain jump-to-section TOC, real generateMetadata + Article/FAQPage JSON-LD). Legacy registered the identical component at both /alex-azzi and /cheshire-grin with no redirect between them; picked /alex-azzi as canonical (the name people search for) and 308-redirected the other, matching the /find-my-tribe-style duplicate-route pattern already used throughout next.config.ts. Every dollar figure, date, case number, and quoted admission ported verbatim into lib/content/alex-azzi.ts — independently spot-checked against the legacy source (not just the port's own self-report) and confirmed exact matches on $137,000+/$75,000+/$15,000/CPR-2026-001/etc. Dropped 3 backend-dependent legacy features with no live tRPC to power them, matching /protecting-your-business's own precedent: the Submission Form (replaced with a real mailto: CTA), the Byron Katie Verification Gate modal (only existed to gate the removed form), and the Endorsement/"Ring the Bell" counter — its "7 testimonials received" claim was dropped rather than ported as fact, since it can't be verified without the backend that produced it. Real dead-link bug fixed: 2 of 20 "Ecosystem Interlinks" pointed to /assessment?t</t>
         </is>
       </c>
       <c r="E91" s="14" t="inlineStr">
@@ -3061,7 +3061,7 @@
       <c r="A92" s="4" t="n"/>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>/rip-peptide-sciences</t>
+          <t>Real bug found and fixed</t>
         </is>
       </c>
       <c r="C92" s="13" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>RipPeptideSciences.tsx. Real content ported in full (7-event timeline, 3 shutdown-reason cards, COA explainer, 9-vendor sortable scorecard, Tony's quote). Built components/marketing/biochain-cta.tsx — a shared CTA used across every peptide/bio-sourcing page, real static outbound links to RampRate's own BioChain site (confirmed live), no backend on this side. Installed formik+yup this pass for upcoming multi-field forms (peptide quiz, etc.) — documented as the house convention in CONTRIBUTING.md. Verified live: 200 OK, timeline/reasons/vendors/quote all present.</t>
+          <t>(while verifying the above): a Core Themes selection (e.g. "The Crusades") often shares its display name with a real post category — showing it as a separate floating chip next to the category pill row (rather than merging into the matching pill) read as two disconnected, contradictory controls. Fixed HomeArchive so an active theme lights up the matching category pill directly (with the same click-to-clear ✕ affordance) instead of a separate chip; a theme with no same-named category still falls back to its own chip.</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
@@ -3084,7 +3084,7 @@
       <c r="A93" s="4" t="n"/>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>/whats-legal</t>
+          <t>/rip-peptide-sciences</t>
         </is>
       </c>
       <c r="C93" s="13" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>WhatsLegal.tsx. Real content ported in full — 17 real compounds with real US/UK/Australia regulatory status, searchable/risk-filterable table, the 3 "key distinctions" callouts. No backend dependency. Verified live: 200 OK, full table + all real compounds present.</t>
+          <t>RipPeptideSciences.tsx. Real content ported in full (7-event timeline, 3 shutdown-reason cards, COA explainer, 9-vendor sortable scorecard, Tony's quote). Built components/marketing/biochain-cta.tsx — a shared CTA used across every peptide/bio-sourcing page, real static outbound links to RampRate's own BioChain site (confirmed live), no backend on this side. Installed formik+yup this pass for upcoming multi-field forms (peptide quiz, etc.) — documented as the house convention in CONTRIBUTING.md. Verified live: 200 OK, timeline/reasons/vendors/quote all present.</t>
         </is>
       </c>
       <c r="E93" s="14" t="inlineStr">
@@ -3107,7 +3107,7 @@
       <c r="A94" s="4" t="n"/>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>/verify-your-coa</t>
+          <t>/whats-legal</t>
         </is>
       </c>
       <c r="C94" s="13" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>VerifyYourCoa.tsx. Real content ported in full (interactive 7-point checklist with live score, 4-step Janoshik verification walkthrough). Extracted components/marketing/peptide-shutdown-banner.tsx (shared FDA-shutdown banner, was duplicated inline on /whats-legal, now both use the one component) and components/marketing/coa-checklist.tsx. Also caught and fixed 3 duplicated EyebrowLabel component definitions (identical code in /amplifier, /diamond-cut, /living-declaration) — extracted to components/marketing/eyebrow-label.tsx. Verified live: 200 OK, full checklist + walkthrough present.</t>
+          <t>WhatsLegal.tsx. Real content ported in full — 17 real compounds with real US/UK/Australia regulatory status, searchable/risk-filterable table, the 3 "key distinctions" callouts. No backend dependency. Verified live: 200 OK, full table + all real compounds present.</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
@@ -3130,7 +3130,7 @@
       <c r="A95" s="4" t="n"/>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>/price-tracker</t>
+          <t>/verify-your-coa</t>
         </is>
       </c>
       <c r="C95" s="13" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>PriceTracker.tsx. Real content ported in full — 14 real compounds with research-vendor vs. telehealth price ranges, Tony's takes, sortable table, and the interactive up-to-4 stack cost calculator. Reused PeptideShutdownBanner. Verified live: 200 OK, full price table + calculator present.</t>
+          <t>VerifyYourCoa.tsx. Real content ported in full (interactive 7-point checklist with live score, 4-step Janoshik verification walkthrough). Extracted components/marketing/peptide-shutdown-banner.tsx (shared FDA-shutdown banner, was duplicated inline on /whats-legal, now both use the one component) and components/marketing/coa-checklist.tsx. Also caught and fixed 3 duplicated EyebrowLabel component definitions (identical code in /amplifier, /diamond-cut, /living-declaration) — extracted to components/marketing/eyebrow-label.tsx. Verified live: 200 OK, full checklist + walkthrough present.</t>
         </is>
       </c>
       <c r="E95" s="14" t="inlineStr">
@@ -3153,7 +3153,7 @@
       <c r="A96" s="4" t="n"/>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>/test-your-peptides</t>
+          <t>/price-tracker</t>
         </is>
       </c>
       <c r="C96" s="13" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>TestYourPeptides.tsx. Real content ported in full — 4 real independent-verification options (Janoshik, r/Peptides, Eroids, telehealth route) with real sites, costs, and Tony's notes. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, all 4 options present. Also renamed /blog's heading from "The Blog" to "Essays" per feedback (matches /essays and the site's own voice).</t>
+          <t>PriceTracker.tsx. Real content ported in full — 14 real compounds with research-vendor vs. telehealth price ranges, Tony's takes, sortable table, and the interactive up-to-4 stack cost calculator. Reused PeptideShutdownBanner. Verified live: 200 OK, full price table + calculator present.</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
@@ -3176,7 +3176,7 @@
       <c r="A97" s="4" t="n"/>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>/peptide-library</t>
+          <t>/test-your-peptides</t>
         </is>
       </c>
       <c r="C97" s="13" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>PeptideLibrary.tsx. Real content ported in full — 20 real compound profiles across 8 categories, each with mechanism, safety tier, evidence score, regulatory status, pricing, stack partners, Oura tracking, key study, and Tony's take; expandable cards with category filter. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, all 20 compounds present.</t>
+          <t>TestYourPeptides.tsx. Real content ported in full — 4 real independent-verification options (Janoshik, r/Peptides, Eroids, telehealth route) with real sites, costs, and Tony's notes. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, all 4 options present. Also renamed /blog's heading from "The Blog" to "Essays" per feedback (matches /essays and the site's own voice).</t>
         </is>
       </c>
       <c r="E97" s="14" t="inlineStr">
@@ -3199,7 +3199,7 @@
       <c r="A98" s="4" t="n"/>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>/peptide-hall-of-shame</t>
+          <t>/peptide-library</t>
         </is>
       </c>
       <c r="C98" s="13" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>PeptideHallOfShame.tsx. Real content ported in full — 20 real named clinics/providers audited on 6 weighted clinical criteria, sortable rankings with expandable weaknesses/strengths, comparison callout for the site's own assessment, methodology note. Reused PeptideShutdownBanner + BioChainCTA; built ClinicRankings (components/marketing/clinic-rankings.tsx). Real bug caught and fixed: CRITERIA was defined and exported from clinic-rankings.tsx (a "use client" file) and imported directly into the Server Component page.tsx, which crashed at runtime (CRITERIA.map is not a function) — a plain data re-export doesn't survive the Client→Server boundary. Fixed by moving CRITERIA to a new shared plain module, lib/content/peptide-criteria.ts, imported by both. Verified live: 200 OK, no error digest, all 20 clinic names and both methodology-card criteria present in rendered HTML.</t>
+          <t>PeptideLibrary.tsx. Real content ported in full — 20 real compound profiles across 8 categories, each with mechanism, safety tier, evidence score, regulatory status, pricing, stack partners, Oura tracking, key study, and Tony's take; expandable cards with category filter. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, all 20 compounds present.</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
@@ -3222,7 +3222,7 @@
       <c r="A99" s="4" t="n"/>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>/peptide-supply-chain</t>
+          <t>/peptide-hall-of-shame</t>
         </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>PeptideSupplyChain.tsx. Real content ported in full — 12 real named providers audited on a 7-category cost breakdown (manufacturing/marketing/compliance/physician/R&amp;D/shipping/profit) with a derived credibility score, sortable rankings, expandable per-provider dollar breakdown + red-flag tags, green/red-flag guidance, methodology note. Built SupplyChainRankings (components/marketing/supply-chain-rankings.tsx) + shared lib/content/supply-chain-providers.ts (kept data out of the client file per the same Client→Server export pitfall fixed on /peptide-hall-of-shame). Dropped the legacy EmailGate (trpc.subscribe.add backend mutation) — full analysis now renders directly with no gate, matching /peptide-library and /price-tracker. Legacy hero background image (CloudFront) confirmed 403, same host/failure as /peptide-hall-of-shame — dropped for a CSS gradient. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, all 12 providers present.</t>
+          <t>PeptideHallOfShame.tsx. Real content ported in full — 20 real named clinics/providers audited on 6 weighted clinical criteria, sortable rankings with expandable weaknesses/strengths, comparison callout for the site's own assessment, methodology note. Reused PeptideShutdownBanner + BioChainCTA; built ClinicRankings (components/marketing/clinic-rankings.tsx). Real bug caught and fixed: CRITERIA was defined and exported from clinic-rankings.tsx (a "use client" file) and imported directly into the Server Component page.tsx, which crashed at runtime (CRITERIA.map is not a function) — a plain data re-export doesn't survive the Client→Server boundary. Fixed by moving CRITERIA to a new shared plain module, lib/content/peptide-criteria.ts, imported by both. Verified live: 200 OK, no error digest, all 20 clinic names and both methodology-card criteria present in rendered HTML.</t>
         </is>
       </c>
       <c r="E99" s="14" t="inlineStr">
@@ -3245,7 +3245,7 @@
       <c r="A100" s="4" t="n"/>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>/peptide-matrix</t>
+          <t>/peptide-supply-chain</t>
         </is>
       </c>
       <c r="C100" s="13" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>PeptideMatrix.tsx. Real content ported in full — interactive canvas scatter plot (review score vs. scientific evidence score) mapping 8 real named entities (influencers, clinics, a vendor, doctors, USADA as regulatory) across 4 quadrants, sortable/clickable entity table with selected-entity detail, 5 danger-zone psychology mechanisms, evidence-scoring methodology (crawlable via forceMount), full fair-comment/appeals legal framework. Built PeptideMatrixExplorer (canvas + table, client) and PeptideMatrixMethodology (client) + shared lib/content/peptide-matrix.ts (plain data module, not re-exported from either client file — same pattern as the /peptide-hall-of-shame CRITERIA fix). Converted every legacy emoji (🧠🔄⏰📊💰🧬🏚️📝🛡️📰✓✕▶) to lucide icons. Legacy hero background image (CloudFront) confirmed 403, same as the other peptide pages — dropped for a CSS gradient. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, all entities, quadrants, and legal-framework text present.</t>
+          <t>PeptideSupplyChain.tsx. Real content ported in full — 12 real named providers audited on a 7-category cost breakdown (manufacturing/marketing/compliance/physician/R&amp;D/shipping/profit) with a derived credibility score, sortable rankings, expandable per-provider dollar breakdown + red-flag tags, green/red-flag guidance, methodology note. Built SupplyChainRankings (components/marketing/supply-chain-rankings.tsx) + shared lib/content/supply-chain-providers.ts (kept data out of the client file per the same Client→Server export pitfall fixed on /peptide-hall-of-shame). Dropped the legacy EmailGate (trpc.subscribe.add backend mutation) — full analysis now renders directly with no gate, matching /peptide-library and /price-tracker. Legacy hero background image (CloudFront) confirmed 403, same host/failure as /peptide-hall-of-shame — dropped for a CSS gradient. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, all 12 providers present.</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
@@ -3268,7 +3268,7 @@
       <c r="A101" s="4" t="n"/>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>/peptide-watch</t>
+          <t>/peptide-matrix</t>
         </is>
       </c>
       <c r="C101" s="13" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>PeptideWatch.tsx. Real content ported in full across all 10 legacy sections — 3 market tiers, a 2024–26 enforcement timeline, an 18-entry wall-of-shame table with real FDA/DOJ/FTC/ITC/state/NAD citations, 12 recurring fraud patterns, 5 role-based checklists, a 10-question buyer test, a 10-category/50-point vendor scorecard, a Finnrick Analytics section, the proposed PeptideWatch Foundation, whistleblower reporting channels, and the closing "chain of custody" argument. Built PeptideWatchFraudPatterns, PeptideWatchRoleChecklist, PeptideWatchScorecard (all client) + shared lib/content/peptide-watch.ts (plain data module, same Client/Server-safe pattern as the other peptide pages). Fixed two real legacy crawlability gaps: fraud-pattern bodies and all 5 role checklists were conditionally unmounted (never in the DOM until clicked) — now always server-rendered and toggled via hidden instead, verified present in raw HTML. Dropped the legacy page's own duplicate &lt;footer&gt; (site already renders one global SiteFooter). Legacy per-section hero images (CloudFront) confirmed 403, same dead host as every other peptide page. Reused BioChainCTA. Verified live: 200 OK, all content present including collapsed sections.</t>
+          <t>PeptideMatrix.tsx. Real content ported in full — interactive canvas scatter plot (review score vs. scientific evidence score) mapping 8 real named entities (influencers, clinics, a vendor, doctors, USADA as regulatory) across 4 quadrants, sortable/clickable entity table with selected-entity detail, 5 danger-zone psychology mechanisms, evidence-scoring methodology (crawlable via forceMount), full fair-comment/appeals legal framework. Built PeptideMatrixExplorer (canvas + table, client) and PeptideMatrixMethodology (client) + shared lib/content/peptide-matrix.ts (plain data module, not re-exported from either client file — same pattern as the /peptide-hall-of-shame CRITERIA fix). Converted every legacy emoji (🧠🔄⏰📊💰🧬🏚️📝🛡️📰✓✕▶) to lucide icons. Legacy hero background image (CloudFront) confirmed 403, same as the other peptide pages — dropped for a CSS gradient. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, all entities, quadrants, and legal-framework text present.</t>
         </is>
       </c>
       <c r="E101" s="14" t="inlineStr">
@@ -3291,7 +3291,7 @@
       <c r="A102" s="4" t="n"/>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>/quiz_25q</t>
+          <t>/peptide-watch</t>
         </is>
       </c>
       <c r="C102" s="13" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>PeptideQuiz25.tsx. Real content ported in full — all 25 questions across 5 scoring dimensions (Science Literacy, Red Flag Detection, Provider Evaluation, Regulatory Awareness, Personal Risk Assessment), all 4 answer choices with real feedback text per question, all 5 result profiles with real recommendations. Built PeptideQuiz (client component, components/marketing/peptide-quiz.tsx) matching the existing single-file precedent set by engage-audit.tsx. The email-gate phase's "GET MY REPORT" never posted anywhere even in the legacy source (no backend call in its handler) — kept as real client-only gating. AssessmentResultActions's "Send to Tony"/"Keep Private" (a tRPC CRM write) was dropped; "Download PDF" (window.print) kept since it's real and backend-free. Legacy hero image (CloudFront) confirmed 403. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, intro copy/dimensions present, typecheck/lint/production-build clean.</t>
+          <t>PeptideWatch.tsx. Real content ported in full across all 10 legacy sections — 3 market tiers, a 2024–26 enforcement timeline, an 18-entry wall-of-shame table with real FDA/DOJ/FTC/ITC/state/NAD citations, 12 recurring fraud patterns, 5 role-based checklists, a 10-question buyer test, a 10-category/50-point vendor scorecard, a Finnrick Analytics section, the proposed PeptideWatch Foundation, whistleblower reporting channels, and the closing "chain of custody" argument. Built PeptideWatchFraudPatterns, PeptideWatchRoleChecklist, PeptideWatchScorecard (all client) + shared lib/content/peptide-watch.ts (plain data module, same Client/Server-safe pattern as the other peptide pages). Fixed two real legacy crawlability gaps: fraud-pattern bodies and all 5 role checklists were conditionally unmounted (never in the DOM until clicked) — now always server-rendered and toggled via hidden instead, verified present in raw HTML. Dropped the legacy page's own duplicate &lt;footer&gt; (site already renders one global SiteFooter). Legacy per-section hero images (CloudFront) confirmed 403, same dead host as every other peptide page. Reused BioChainCTA. Verified live: 200 OK, all content present including collapsed sections.</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
@@ -3314,7 +3314,7 @@
       <c r="A103" s="4" t="n"/>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>/clock-keeper-part-2</t>
+          <t>/quiz_25q</t>
         </is>
       </c>
       <c r="C103" s="13" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>ClockKeeperPartII.tsx. Built 2026-10-06: hero, intro, 5 modes, the 5 questions, optional name/email; saves to Supabase clock_keeper_responses (anonymous allowed; server-validated), response count in the hero. Fixes the dead link from the Part I essay. Saving works once the database script is run. Was: Deferred, not skipped. A companion response-collection form for the /blog/the-clock-keeper-chronicles-part-1 essay — 5 questions + alternate "modes" (reframe/meta/jazz/minimum), posts to trpc.clockKeeper.submit, displays a live trpc.clockKeeper.count response counter. Unlike /post-intervention, this doesn't promise anonymity, so a mailto: fallback (matching newsletter-popup.tsx's pattern) could work for the submit action — but the live response counter has no honest fallback without a real backend. Lower priority than the rest of Phase 4 (a companion piece to one specific post, not a core marketing page); revisit with a mailto-based submit and the counter dropped.</t>
+          <t>PeptideQuiz25.tsx. Real content ported in full — all 25 questions across 5 scoring dimensions (Science Literacy, Red Flag Detection, Provider Evaluation, Regulatory Awareness, Personal Risk Assessment), all 4 answer choices with real feedback text per question, all 5 result profiles with real recommendations. Built PeptideQuiz (client component, components/marketing/peptide-quiz.tsx) matching the existing single-file precedent set by engage-audit.tsx. The email-gate phase's "GET MY REPORT" never posted anywhere even in the legacy source (no backend call in its handler) — kept as real client-only gating. AssessmentResultActions's "Send to Tony"/"Keep Private" (a tRPC CRM write) was dropped; "Download PDF" (window.print) kept since it's real and backend-free. Legacy hero image (CloudFront) confirmed 403. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, intro copy/dimensions present, typecheck/lint/production-build clean.</t>
         </is>
       </c>
       <c r="E103" s="14" t="inlineStr">
@@ -3337,7 +3337,7 @@
       <c r="A104" s="4" t="n"/>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>/charity-scorecard + /charity-scorecard/:slug</t>
+          <t>/clock-keeper-part-2</t>
         </is>
       </c>
       <c r="C104" s="13" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>CharityScorecard.tsx, CharityProfile.tsx (uses charityData.ts). Real content ported in full — 98 real named charities scored across 7 weighted dimensions unifying GiveWell/Charity Navigator/CharityWatch/Candid ratings plus a proprietary Cloak-vs-Clear transparency score; 3-tab explorer (Rankings with search/filter/sort/expand, Scorecard, Evaluators) and a full per-charity profile page with an SVG radar chart, score breakdown, quick facts, external ratings, and similar-charity cross-links. No backend dependency in the legacy source at all. Built CharityScorecardExplorer (client) + shared components/marketing/charity-badges.tsx (GradeBadge/CloakBadge/CloakPanel/ScoreBar/RadarChart/EvaluatorBadges, plain presentational, safe in both Server and Client contexts) + lib/content/charity-data.ts. /charity-scorecard/[slug] is a full Server Component (legacy had zero client state on that page) with generateStaticParams for all 98 slugs — confirmed all 98 statically generated in pnpm build. Fixed a real crawlability gap: the Scorecard/Evaluators tabs were conditionally unmounted until clicked (same pattern as the peptide-watch fix) — now always server-rendered, toggled via hidden, verified present in raw HTML. Verified live: 200 OK on both the index and a profile page, all real charity names present.</t>
+          <t>ClockKeeperPartII.tsx. Built 2026-10-06: hero, intro, 5 modes, the 5 questions, optional name/email; saves to Supabase clock_keeper_responses (anonymous allowed; server-validated), response count in the hero. Fixes the dead link from the Part I essay. Saving works once the database script is run. Was: Deferred, not skipped. A companion response-collection form for the /blog/the-clock-keeper-chronicles-part-1 essay — 5 questions + alternate "modes" (reframe/meta/jazz/minimum), posts to trpc.clockKeeper.submit, displays a live trpc.clockKeeper.count response counter. Unlike /post-intervention, this doesn't promise anonymity, so a mailto: fallback (matching newsletter-popup.tsx's pattern) could work for the submit action — but the live response counter has no honest fallback without a real backend. Lower priority than the rest of Phase 4 (a companion piece to one specific post, not a core marketing page); revisit with a mailto-based submit and the counter dropped.</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
@@ -3360,7 +3360,7 @@
       <c r="A105" s="4" t="n"/>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>/find-your-journey</t>
+          <t>/charity-scorecard + /charity-scorecard/:slug</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>JourneyFinder.tsx. Real content ported in full — all 5 NLP-style questions with real weighted choices, all 6 journey archetypes (Thinker/Operator/Relationship/Body/Impact/Crusade) with real curated article lists linking to real /blog/[slug] posts. Built JourneyFinder (single client component, data + UI together, matching the engage-audit.tsx/peptide-quiz.tsx precedent). Converted legacy's plain Unicode glyph icons (◉⬡∞◈◎⚔) to lucide-react icons. Dropped the "relationship" journey's external link to intimacyassess-tcir3hon.manus.space — confirmed dead, same fully-decommissioned Manus host as everywhere else in this migration. AssessmentResultActions's backend save dropped; retake kept (real, client-only). Verified live: 200 OK, intro copy present, typecheck/lint/production-build clean.</t>
+          <t>CharityScorecard.tsx, CharityProfile.tsx (uses charityData.ts). Real content ported in full — 98 real named charities scored across 7 weighted dimensions unifying GiveWell/Charity Navigator/CharityWatch/Candid ratings plus a proprietary Cloak-vs-Clear transparency score; 3-tab explorer (Rankings with search/filter/sort/expand, Scorecard, Evaluators) and a full per-charity profile page with an SVG radar chart, score breakdown, quick facts, external ratings, and similar-charity cross-links. No backend dependency in the legacy source at all. Built CharityScorecardExplorer (client) + shared components/marketing/charity-badges.tsx (GradeBadge/CloakBadge/CloakPanel/ScoreBar/RadarChart/EvaluatorBadges, plain presentational, safe in both Server and Client contexts) + lib/content/charity-data.ts. /charity-scorecard/[slug] is a full Server Component (legacy had zero client state on that page) with generateStaticParams for all 98 slugs — confirmed all 98 statically generated in pnpm build. Fixed a real crawlability gap: the Scorecard/Evaluators tabs were conditionally unmounted until clicked (same pattern as the peptide-watch fix) — now always server-rendered, toggled via hidden, verified present in raw HTML. Verified live: 200 OK on both the index and a profile page, all real charity names present.</t>
         </is>
       </c>
       <c r="E105" s="14" t="inlineStr">
@@ -3383,7 +3383,7 @@
       <c r="A106" s="4" t="n"/>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>/skippy</t>
+          <t>/find-your-journey</t>
         </is>
       </c>
       <c r="C106" s="13" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>SkippyMap.tsx. Ported 2026-09-29 from the legacy source, full destination list and copy unchanged. It was unblocked because 34 of its 38 destinations now exist. The other 4 (/friend-gate, /post-intervention, /pri-research, /thought-cloud) show "Coming Soon" instead of a broken link. /the-index, /cheshire-grin and /life-assessment now link straight to their redirect targets. Progress is kept in localStorage under legacy's key, read hydration-safely. Emoji are replaced with Lucide icons. noindex because it's a personal page for one named person, and legacy had no SEO tags on it. A Manus branch had its own version with a trimmed list and rewritten copy, not used (see docs/ai/project_production_restoration_branch.md). Verified with a production build: 200, noindex, and every non-null link resolves to a real route.</t>
+          <t>JourneyFinder.tsx. Real content ported in full — all 5 NLP-style questions with real weighted choices, all 6 journey archetypes (Thinker/Operator/Relationship/Body/Impact/Crusade) with real curated article lists linking to real /blog/[slug] posts. Built JourneyFinder (single client component, data + UI together, matching the engage-audit.tsx/peptide-quiz.tsx precedent). Converted legacy's plain Unicode glyph icons (◉⬡∞◈◎⚔) to lucide-react icons. Dropped the "relationship" journey's external link to intimacyassess-tcir3hon.manus.space — confirmed dead, same fully-decommissioned Manus host as everywhere else in this migration. AssessmentResultActions's backend save dropped; retake kept (real, client-only). Verified live: 200 OK, intro copy present, typecheck/lint/production-build clean.</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
@@ -3406,7 +3406,7 @@
       <c r="A107" s="4" t="n"/>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>/ecosystem-map</t>
+          <t>/skippy</t>
         </is>
       </c>
       <c r="C107" s="13" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>EcosystemMap.tsx. Ported 2026-09-29 with legacy copy (6 phases, 18 experience descriptions, closing CTA). URLs and completion come from the shared JOURNEY_MAP/useJourneyProgress in components/assessments/journey-tracker.tsx. All 18 IDs resolve. Collapsed phases are hidden with CSS rather than unmounted, so all descriptions are in the server HTML. 6 experiences still link to Tony's own *.manus.space apps, same as /my-journey; that's an owner decision. Verified with a production build: 200, all copy in the server HTML.</t>
+          <t>SkippyMap.tsx. Ported 2026-09-29 from the legacy source, full destination list and copy unchanged. It was unblocked because 34 of its 38 destinations now exist. The other 4 (/friend-gate, /post-intervention, /pri-research, /thought-cloud) show "Coming Soon" instead of a broken link. /the-index, /cheshire-grin and /life-assessment now link straight to their redirect targets. Progress is kept in localStorage under legacy's key, read hydration-safely. Emoji are replaced with Lucide icons. noindex because it's a personal page for one named person, and legacy had no SEO tags on it. A Manus branch had its own version with a trimmed list and rewritten copy, not used (see docs/ai/project_production_restoration_branch.md). Verified with a production build: 200, noindex, and every non-null link resolves to a real route.</t>
         </is>
       </c>
       <c r="E107" s="14" t="inlineStr">
@@ -3429,7 +3429,7 @@
       <c r="A108" s="4" t="n"/>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>/my-highlights</t>
+          <t>/ecosystem-map</t>
         </is>
       </c>
       <c r="C108" s="13" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>MyHighlights.tsx. Built 2026-10-06: select 10-2,000 characters in any essay and a "Save Highlight" button appears (no login code on essay pages; signed-out readers get a sign-in link; essays stay statically built); "Your Commonplace Book" lists saved passages by essay with real titles, remove button per passage; RLS keeps each member to their own rows. Saving works once the database script is run. Was: Deferred, not skipped. Entirely an authenticated account feature — gated behind useAuth(), reads/deletes saved text highlights via trpc.highlights.list/highlights.delete. No real content exists to show a signed-out visitor beyond a "Sign In" prompt; the underlying "select text in an essay to save it" feature isn't built anywhere else in this migration either. Blocked on real auth + a highlights backend (Phase 5+), not a content-porting task.</t>
+          <t>EcosystemMap.tsx. Ported 2026-09-29 with legacy copy (6 phases, 18 experience descriptions, closing CTA). URLs and completion come from the shared JOURNEY_MAP/useJourneyProgress in components/assessments/journey-tracker.tsx. All 18 IDs resolve. Collapsed phases are hidden with CSS rather than unmounted, so all descriptions are in the server HTML. 6 experiences still link to Tony's own *.manus.space apps, same as /my-journey; that's an owner decision. Verified with a production build: 200, all copy in the server HTML.</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
@@ -3452,7 +3452,7 @@
       <c r="A109" s="4" t="n"/>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>/my-impact</t>
+          <t>/my-highlights</t>
         </is>
       </c>
       <c r="C109" s="13" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>MyReferrals.tsx. Built 2026-10-06: invite link (/signup?ref=CODE, code created on first visit), people referred, depth score, referrals list; a referral is recorded when the invited member confirms their email. Depth = passages the referred member saved (legacy added essays read, assessments and chats per member, which this site doesn't track). Works once the database script is run. Was: Deferred, not skipped — same reasoning as /my-highlights. Entirely an authenticated referral-tracking dashboard (trpc.referral.stats, a depth-scored referral graph). No content to port without real auth + a referrals backend.</t>
+          <t>MyHighlights.tsx. Built 2026-10-06: select 10-2,000 characters in any essay and a "Save Highlight" button appears (no login code on essay pages; signed-out readers get a sign-in link; essays stay statically built); "Your Commonplace Book" lists saved passages by essay with real titles, remove button per passage; RLS keeps each member to their own rows. Saving works once the database script is run. Was: Deferred, not skipped. Entirely an authenticated account feature — gated behind useAuth(), reads/deletes saved text highlights via trpc.highlights.list/highlights.delete. No real content exists to show a signed-out visitor beyond a "Sign In" prompt; the underlying "select text in an essay to save it" feature isn't built anywhere else in this migration either. Blocked on real auth + a highlights backend (Phase 5+), not a content-porting task.</t>
         </is>
       </c>
       <c r="E109" s="14" t="inlineStr">
@@ -3475,7 +3475,7 @@
       <c r="A110" s="4" t="n"/>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>/friend-gate</t>
+          <t>/my-impact</t>
         </is>
       </c>
       <c r="C110" s="13" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>FriendGate.tsx. Built 2026-10-06 (email only, owner chose Resend): intro, nominate 3 friends (Formik + Yup, disposable/duplicate emails refused), invites emailed via Resend's HTTP API (src/lib/email.ts, no new package), bookmarkable seeker page /friend-gate/[token] (auto-refreshes; opens after 72h; 2+ "wait" blocks), anonymous messages shown sorted, not in friend order. Was: Deferred, not skipped. Real backend workflow (3 tRPC calls) — generates invite links for three friends, tracks their responses, enforces a 72-hour wait. No client-side-only version makes sense; the entire feature is the backend coordination. Blocked on real auth/backend (Phase 5+).</t>
+          <t>MyReferrals.tsx. Built 2026-10-06: invite link (/signup?ref=CODE, code created on first visit), people referred, depth score, referrals list; a referral is recorded when the invited member confirms their email. Depth = passages the referred member saved (legacy added essays read, assessments and chats per member, which this site doesn't track). Works once the database script is run. Was: Deferred, not skipped — same reasoning as /my-highlights. Entirely an authenticated referral-tracking dashboard (trpc.referral.stats, a depth-scored referral graph). No content to port without real auth + a referrals backend.</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
@@ -3498,7 +3498,7 @@
       <c r="A111" s="4" t="n"/>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>/friend-survey/:token</t>
+          <t>/friend-gate</t>
         </is>
       </c>
       <c r="C111" s="13" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>FriendSurvey.tsx. Built 2026-10-06: identity check (email must match the invite) &gt; 6-digit code by email (15 min, max 5 tries, new safeguard) &gt; the six questions &gt; thanks; invalid/used links handled. Was: Deferred, not skipped — the token-gated survey a friend fills out after being invited via /friend-gate (5 tRPC calls). Depends entirely on /friend-gate existing first.</t>
+          <t>FriendGate.tsx. Built 2026-10-06 (email only, owner chose Resend): intro, nominate 3 friends (Formik + Yup, disposable/duplicate emails refused), invites emailed via Resend's HTTP API (src/lib/email.ts, no new package), bookmarkable seeker page /friend-gate/[token] (auto-refreshes; opens after 72h; 2+ "wait" blocks), anonymous messages shown sorted, not in friend order. Was: Deferred, not skipped. Real backend workflow (3 tRPC calls) — generates invite links for three friends, tracks their responses, enforces a 72-hour wait. No client-side-only version makes sense; the entire feature is the backend coordination. Blocked on real auth/backend (Phase 5+).</t>
         </is>
       </c>
       <c r="E111" s="14" t="inlineStr">
@@ -3521,7 +3521,7 @@
       <c r="A112" s="4" t="n"/>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>/impact-dashboard</t>
+          <t>/friend-survey/:token</t>
         </is>
       </c>
       <c r="C112" s="13" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>ImpactDashboard.tsx (built, not yet pushed — pending local review). Real content ported in full across all 6 tabs (Overview, Token Ecosystems, Portfolio Impact, SoulScore, Charity Index, iRR Framework) — the 4 real ImpactSoul token ecosystems (BEYOND/REX/SPACE/BEING), 8 portfolio categories, all 12 SoulScore dimensions, the charity index summary, and the full iRR/Hawkins framework explanation. Built ImpactDashboardExplorer (client) + lib/content/impact-dashboard.ts. Dropped the canvas particle field and scroll-linked parallax hero (decoration not worth the runtime cost, same reasoning used throughout this migration) and the legacy hero images, which used the banned /api/img/ Manus path — replaced with a plain gradient hero. The 3 "LAUNCH SOULSCORE ENGINE"/"LAUNCH C-NPV CALCULATOR" links pointed to /soulscore, which doesn't exist yet — rendered as a "Coming Soon" badge instead of a broken link or a silently-dropped promise. All 6 tabs render always in SSR HTML (crawlability fix, same pattern as charity-scorecard/peptide-watch) — verified live: 200 OK, all tab content present including "Coming Soon" state, typecheck/lint/production-build clean.</t>
+          <t>FriendSurvey.tsx. Built 2026-10-06: identity check (email must match the invite) &gt; 6-digit code by email (15 min, max 5 tries, new safeguard) &gt; the six questions &gt; thanks; invalid/used links handled. Was: Deferred, not skipped — the token-gated survey a friend fills out after being invited via /friend-gate (5 tRPC calls). Depends entirely on /friend-gate existing first.</t>
         </is>
       </c>
       <c r="E112" s="14" t="inlineStr">
@@ -3544,7 +3544,7 @@
       <c r="A113" s="4" t="n"/>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>/medicine-sequencing</t>
+          <t>/impact-dashboard</t>
         </is>
       </c>
       <c r="C113" s="13" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>MedicineSequencing.tsx. Unblocked once /psychedelic-readiness-index and /facilitator-index shipped. The shared MEDICINES dataset was already in lib/content/pri-data.ts, so this renders from it directly. Real content ported in full: the six-rung ladder, its philosophy passage, every medicine's "why this rung" note, overview, therapeutic uses, readiness requirements and tradition, plus the level filter. Built MedicineSequencingLadder (components/pri/medicine-sequencing-ladder.tsx, client) with each card on a shadcn Collapsible using forceMount. The level filter hides rungs instead of unmounting them, so all 39 cards' text is in the raw SSR HTML. Legacy's inline styles object was rebuilt as one full literal Tailwind class string per rung. The intensity bar width is the one style exception. Real legacy bug fixed: Mambe's complexityLevel was "Gentle Entry", which isn't one of the six rungs, so legacy counted it in "All (39)" but never rendered its card. Normalized to "Entry" in the dataset (nothing else read that field). The hero's hardcoded "38 medicines" now reads the real count. Also re-linked /the-philosophy's Instruments: PRI, Facilitator Index and Medicine Sequencing are now real links, and Three Friends Gate keeps "Coming Soon" until /friend-gate exists. Verified live: 200 OK, 39 collapsible panels in SSR HTML, typecheck/lint clean.</t>
+          <t>ImpactDashboard.tsx (built, not yet pushed — pending local review). Real content ported in full across all 6 tabs (Overview, Token Ecosystems, Portfolio Impact, SoulScore, Charity Index, iRR Framework) — the 4 real ImpactSoul token ecosystems (BEYOND/REX/SPACE/BEING), 8 portfolio categories, all 12 SoulScore dimensions, the charity index summary, and the full iRR/Hawkins framework explanation. Built ImpactDashboardExplorer (client) + lib/content/impact-dashboard.ts. Dropped the canvas particle field and scroll-linked parallax hero (decoration not worth the runtime cost, same reasoning used throughout this migration) and the legacy hero images, which used the banned /api/img/ Manus path — replaced with a plain gradient hero. The 3 "LAUNCH SOULSCORE ENGINE"/"LAUNCH C-NPV CALCULATOR" links pointed to /soulscore, which doesn't exist yet — rendered as a "Coming Soon" badge instead of a broken link or a silently-dropped promise. All 6 tabs render always in SSR HTML (crawlability fix, same pattern as charity-scorecard/peptide-watch) — verified live: 200 OK, all tab content present including "Coming Soon" state, typecheck/lint/production-build clean.</t>
         </is>
       </c>
       <c r="E113" s="14" t="inlineStr">
@@ -3567,7 +3567,7 @@
       <c r="A114" s="4" t="n"/>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>/the-philosophy</t>
+          <t>/medicine-sequencing</t>
         </is>
       </c>
       <c r="C114" s="13" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>ThePhilosophy.tsx (built, not yet pushed — pending local review). Real content ported in full — the complete "Diode of Perception" passage and all 5 "What This Means" interpretive sections. No backend dependency in the legacy source. The 4 "Instruments" links (Psychedelic Readiness Index, Facilitator Index, Medicine Sequencing, Three Friends Gate) don't exist yet — rendered as "Coming Soon" badges instead of broken links, same pattern as /impact-dashboard's SoulScore links; revisit and re-link as each destination gets built. Verified live: 200 OK, full passage + interpretation present, typecheck/lint/production-build clean.</t>
+          <t>MedicineSequencing.tsx. Unblocked once /psychedelic-readiness-index and /facilitator-index shipped. The shared MEDICINES dataset was already in lib/content/pri-data.ts, so this renders from it directly. Real content ported in full: the six-rung ladder, its philosophy passage, every medicine's "why this rung" note, overview, therapeutic uses, readiness requirements and tradition, plus the level filter. Built MedicineSequencingLadder (components/pri/medicine-sequencing-ladder.tsx, client) with each card on a shadcn Collapsible using forceMount. The level filter hides rungs instead of unmounting them, so all 39 cards' text is in the raw SSR HTML. Legacy's inline styles object was rebuilt as one full literal Tailwind class string per rung. The intensity bar width is the one style exception. Real legacy bug fixed: Mambe's complexityLevel was "Gentle Entry", which isn't one of the six rungs, so legacy counted it in "All (39)" but never rendered its card. Normalized to "Entry" in the dataset (nothing else read that field). The hero's hardcoded "38 medicines" now reads the real count. Also re-linked /the-philosophy's Instruments: PRI, Facilitator Index and Medicine Sequencing are now real links, and Three Friends Gate keeps "Coming Soon" until /friend-gate exists. Verified live: 200 OK, 39 collapsible panels in SSR HTML, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E114" s="14" t="inlineStr">
@@ -3590,7 +3590,7 @@
       <c r="A115" s="4" t="n"/>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>/post-intervention</t>
+          <t>/the-philosophy</t>
         </is>
       </c>
       <c r="C115" s="13" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>PostIntervention.tsx. Built 2026-10-06 as a step registry (day, type, survey, done); saves to Supabase post_intervention_assessments, server-validated. Live's copy says results "go to tony@tonygreenberg.com"; that needs an email service (none connected yet), so for now they are only saved in Supabase. Saving works once the database script is run. Was: Deferred, not skipped. Unlike other single-tRPC-call pages in this migration, this one can't be honestly reduced to a mailto: fallback: the page's entire value proposition, stated three times in its own copy ("Anonymous", "No one can see your name. No one can see your email.", results routed anonymously), is that the facilitator never sees who submitted it. A mailto: would expose the visitor's own email address the moment they hit send in their mail client — actively contradicting the one promise the page makes, not just a missing nice-to-have. Blocked on a real anonymous-submission backend (Phase 5+).</t>
+          <t>ThePhilosophy.tsx (built, not yet pushed — pending local review). Real content ported in full — the complete "Diode of Perception" passage and all 5 "What This Means" interpretive sections. No backend dependency in the legacy source. The 4 "Instruments" links (Psychedelic Readiness Index, Facilitator Index, Medicine Sequencing, Three Friends Gate) don't exist yet — rendered as "Coming Soon" badges instead of broken links, same pattern as /impact-dashboard's SoulScore links; revisit and re-link as each destination gets built. Verified live: 200 OK, full passage + interpretation present, typecheck/lint/production-build clean.</t>
         </is>
       </c>
       <c r="E115" s="14" t="inlineStr">
@@ -3613,7 +3613,7 @@
       <c r="A116" s="4" t="n"/>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>/flow-circuit</t>
+          <t>/post-intervention</t>
         </is>
       </c>
       <c r="C116" s="13" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>redirect stub to flow.tonygreenberg.com (built, not yet pushed — pending local review). Legacy did this client-side via window.location.replace(...) with a flash of "Loading Flow Circuit..." text; ported as a real next.config.ts redirects() entry instead — a genuine 308, no JS required, no flash. Confirmed flow.tonygreenberg.com is live (200) before wiring it. Verified live: curl -I /flow-circuit returns 308 with location: https://flow.tonygreenberg.com/, typecheck/lint/production-build clean.</t>
+          <t>PostIntervention.tsx. Built 2026-10-06 as a step registry (day, type, survey, done); saves to Supabase post_intervention_assessments, server-validated. Live's copy says results "go to tony@tonygreenberg.com"; that needs an email service (none connected yet), so for now they are only saved in Supabase. Saving works once the database script is run. Was: Deferred, not skipped. Unlike other single-tRPC-call pages in this migration, this one can't be honestly reduced to a mailto: fallback: the page's entire value proposition, stated three times in its own copy ("Anonymous", "No one can see your name. No one can see your email.", results routed anonymously), is that the facilitator never sees who submitted it. A mailto: would expose the visitor's own email address the moment they hit send in their mail client — actively contradicting the one promise the page makes, not just a missing nice-to-have. Blocked on a real anonymous-submission backend (Phase 5+).</t>
         </is>
       </c>
       <c r="E116" s="14" t="inlineStr">
@@ -3636,7 +3636,7 @@
       <c r="A117" s="4" t="n"/>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>/supplier-intake + /supplier-intake-long/:token</t>
+          <t>/flow-circuit</t>
         </is>
       </c>
       <c r="C117" s="13" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>SupplierIntakeForm.tsx, SupplierIntakeLong.tsx (built, not yet pushed — pending local review). Plan revised: the original note said "keep pointed at legacy backend," but that backend (trpc.vendor.submitStage1/submitStage2, token-gated file uploads) ran on the now-fully-dead Manus host — there's nothing left to point to. Found a real, active bug in the process: 5 already-ported pages ("Become a Supply Partner" CTAs — peptide-hall-of-shame, peptide-supply-chain, peptide-matrix, whats-legal, etc.) link to /supplier-intake, which didn't exist, so those were live 404s. Fixed by redirecting both /supplier-intake and /supplier-intake-long/:token to RampRate's own real, live supplier intake at ramprate.com/biochain/supplier-intake (confirmed reachable) — the same real destination BioChainCTA already links to elsewhere in this migration, rather than rebuilding a form whose only working backend no longer exists. Verified live: both routes return real 308s to the correct destination, typecheck/lint/production-build clean.</t>
+          <t>redirect stub to flow.tonygreenberg.com (built, not yet pushed — pending local review). Legacy did this client-side via window.location.replace(...) with a flash of "Loading Flow Circuit..." text; ported as a real next.config.ts redirects() entry instead — a genuine 308, no JS required, no flash. Confirmed flow.tonygreenberg.com is live (200) before wiring it. Verified live: curl -I /flow-circuit returns 308 with location: https://flow.tonygreenberg.com/, typecheck/lint/production-build clean.</t>
         </is>
       </c>
       <c r="E117" s="14" t="inlineStr">
@@ -3659,7 +3659,7 @@
       <c r="A118" s="4" t="n"/>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>/subscribe</t>
+          <t>/supplier-intake + /supplier-intake-long/:token</t>
         </is>
       </c>
       <c r="C118" s="13" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Subscribe.tsx. Ported 2026-09-29: legacy copy, a working free signup through /api/subscribe (Kit, with a mailto fallback, same as the popup), and the $99/yr membership and $27 compilation shown as information only with no checkout. This fixed a live 404, because /the-letter already linked here. /api/subscribe also got input length caps.</t>
+          <t>SupplierIntakeForm.tsx, SupplierIntakeLong.tsx (built, not yet pushed — pending local review). Plan revised: the original note said "keep pointed at legacy backend," but that backend (trpc.vendor.submitStage1/submitStage2, token-gated file uploads) ran on the now-fully-dead Manus host — there's nothing left to point to. Found a real, active bug in the process: 5 already-ported pages ("Become a Supply Partner" CTAs — peptide-hall-of-shame, peptide-supply-chain, peptide-matrix, whats-legal, etc.) link to /supplier-intake, which didn't exist, so those were live 404s. Fixed by redirecting both /supplier-intake and /supplier-intake-long/:token to RampRate's own real, live supplier intake at ramprate.com/biochain/supplier-intake (confirmed reachable) — the same real destination BioChainCTA already links to elsewhere in this migration, rather than rebuilding a form whose only working backend no longer exists. Verified live: both routes return real 308s to the correct destination, typecheck/lint/production-build clean.</t>
         </is>
       </c>
       <c r="E118" s="14" t="inlineStr">
@@ -3682,17 +3682,17 @@
       <c r="A119" s="4" t="n"/>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>/shop, /payment-success, /payment-cancel</t>
-        </is>
-      </c>
-      <c r="C119" s="16" t="inlineStr">
-        <is>
-          <t>Deferred</t>
+          <t>/subscribe</t>
+        </is>
+      </c>
+      <c r="C119" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>defer: these are Stripe-backed; flag for the later billing-migration phase, do not port checkout logic yet, static/informational content only if ported now</t>
+          <t>Subscribe.tsx. Ported 2026-09-29: legacy copy, a working free signup through /api/subscribe (Kit, with a mailto fallback, same as the popup), and the $99/yr membership and $27 compilation shown as information only with no checkout. This fixed a live 404, because /the-letter already linked here. /api/subscribe also got input length caps.</t>
         </is>
       </c>
       <c r="E119" s="14" t="inlineStr">
@@ -3705,17 +3705,17 @@
       <c r="A120" s="4" t="n"/>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Drop dead code, do not port</t>
-        </is>
-      </c>
-      <c r="C120" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>/shop, /payment-success, /payment-cancel</t>
+        </is>
+      </c>
+      <c r="C120" s="16" t="inlineStr">
+        <is>
+          <t>Deferred</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>HumanOS.tsx, ComponentShowcase.tsx, VendorIntakeForm.tsx, VendorIntakeLong.tsx, pre-consolidation manifesto sub-pages (AttentionEconomics.tsx, BlockerFinder.tsx, LegalDatabase.tsx, TenWeapons.tsx, ReportSpammer.tsx). Effectively satisfied by the repo-wide flatten: the entire legacy Vite/Express app (including all of these) now lives only under _legacy-manus-app/, outside src/app/ entirely — none of them are part of the deployed Next.js app or its build.</t>
+          <t>defer: these are Stripe-backed; flag for the later billing-migration phase, do not port checkout logic yet, static/informational content only if ported now</t>
         </is>
       </c>
       <c r="E120" s="14" t="inlineStr">
@@ -3728,7 +3728,7 @@
       <c r="A121" s="4" t="n"/>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>/america-unbundled-field-guide</t>
+          <t>Drop dead code, do not port</t>
         </is>
       </c>
       <c r="C121" s="13" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>live-only (no legacy file; added to the live site after the _legacy-manus-app/ snapshot). Ported 2026-10-01 from the live page: copy, links, title/description/OG and Article JSON-LD verbatim; hero image from Sanity (rescued age-of-ai-no-party). The 10 "90-day commitment" questions are a small client island (components/america-unbundled/field-guide-responses.tsx) that saves to localStorage under live's key, copies, or downloads a .txt; nothing is sent anywhere. Sits inside the normal site chrome (live has its own standalone masthead; kept in-page). Part One /america-unbundled is ported too (next line); its temporary 307 to / is gone. /connect → / 308 added (matches live).</t>
+          <t>HumanOS.tsx, ComponentShowcase.tsx, VendorIntakeForm.tsx, VendorIntakeLong.tsx, pre-consolidation manifesto sub-pages (AttentionEconomics.tsx, BlockerFinder.tsx, LegalDatabase.tsx, TenWeapons.tsx, ReportSpammer.tsx). Effectively satisfied by the repo-wide flatten: the entire legacy Vite/Express app (including all of these) now lives only under _legacy-manus-app/, outside src/app/ entirely — none of them are part of the deployed Next.js app or its build.</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
@@ -3751,63 +3751,63 @@
       <c r="A122" s="4" t="n"/>
       <c r="B122" s="4" t="inlineStr">
         <is>
+          <t>/america-unbundled-field-guide</t>
+        </is>
+      </c>
+      <c r="C122" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>live-only (no legacy file; added to the live site after the _legacy-manus-app/ snapshot). Ported 2026-10-01 from the live page: copy, links, title/description/OG and Article JSON-LD verbatim; hero image from Sanity (rescued age-of-ai-no-party). The 10 "90-day commitment" questions are a small client island (components/america-unbundled/field-guide-responses.tsx) that saves to localStorage under live's key, copies, or downloads a .txt; nothing is sent anywhere. Sits inside the normal site chrome (live has its own standalone masthead; kept in-page). Part One /america-unbundled is ported too (next line); its temporary 307 to / is gone. /connect → / 308 added (matches live).</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="inlineStr">
+        <is>
+          <t>Phase 4 — Marketing Core Pages (30 routes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="n"/>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
           <t>/america-unbundled</t>
         </is>
       </c>
-      <c r="C122" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D122" s="4" t="inlineStr">
+      <c r="C123" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
         <is>
           <t>live-only Part One, "AI Does Not Have a Candidate" (no legacy file). Ported 2026-10-01 from the live page: copy, links, title/description/keywords/OG and Article JSON-LD verbatim; same series masthead and styling as Part Two; hero is the same rescued Sanity image (age-of-ai-no-party). The "Share the question" rail is a tiny client island (components/america-unbundled/share-rail.tsx: copy link + device share; X/LinkedIn are plain links). #sources anchor kept for Part Two's link. Temporary /america-unbundled → / redirect removed from next.config.ts.</t>
         </is>
       </c>
-      <c r="E122" s="14" t="inlineStr">
+      <c r="E123" s="14" t="inlineStr">
         <is>
           <t>Phase 4 — Marketing Core Pages (30 routes)</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="10" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
         <is>
           <t>Phase 5 — Blog Engine (Sanity-backed)</t>
         </is>
       </c>
-      <c r="B123" s="11" t="n"/>
-      <c r="C123" s="11" t="n"/>
-      <c r="D123" s="12" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="4" t="n"/>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>/ and /blog</t>
-        </is>
-      </c>
-      <c r="C124" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D124" s="4" t="inlineStr">
-        <is>
-          <t>blog index, paginated (12/page), category filter pills, real Sanity data — verified live: 200 OK, real post links, real category links</t>
-        </is>
-      </c>
-      <c r="E124" s="14" t="inlineStr">
-        <is>
-          <t>Phase 5 — Blog Engine (Sanity-backed)</t>
-        </is>
-      </c>
+      <c r="B124" s="11" t="n"/>
+      <c r="C124" s="11" t="n"/>
+      <c r="D124" s="12" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n"/>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>/blog/[slug]</t>
+          <t>/ and /blog</t>
         </is>
       </c>
       <c r="C125" s="13" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>post template: hero image (next/image), portable text renderer, byline/reading time, pull quote (added pullQuote field to the post schema + backfilled 15 posts that had one — wasn't in the original schema, would've been silently dropped otherwise), drop caps (CSS ::first-letter on the article's first paragraph, in globals.css — position-based, not per-post data, so it works for every post automatically), related posts (same-category, falling back to most-recent) — verified live against a real post: correct &lt;title&gt;, correct read time, body rendered</t>
+          <t>blog index, paginated (12/page), category filter pills, real Sanity data — verified live: 200 OK, real post links, real category links</t>
         </is>
       </c>
       <c r="E125" s="14" t="inlineStr">
@@ -3830,7 +3830,7 @@
       <c r="A126" s="4" t="n"/>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>/blog/category/[slug]</t>
+          <t>/blog/[slug]</t>
         </is>
       </c>
       <c r="C126" s="13" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>category listing + pagination (not explicitly in the original phase list, but linked from the index's category pills — built so that link isn't a 404; own quality bar already requires "every page links to 2+", not dead links)</t>
+          <t>post template: hero image (next/image), portable text renderer, byline/reading time, pull quote (added pullQuote field to the post schema + backfilled 15 posts that had one — wasn't in the original schema, would've been silently dropped otherwise), drop caps (CSS ::first-letter on the article's first paragraph, in globals.css — position-based, not per-post data, so it works for every post automatically), related posts (same-category, falling back to most-recent) — verified live against a real post: correct &lt;title&gt;, correct read time, body rendered</t>
         </is>
       </c>
       <c r="E126" s="14" t="inlineStr">
@@ -3853,7 +3853,7 @@
       <c r="A127" s="4" t="n"/>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>generateStaticParams for all post slugs and category slugs (SSG)</t>
+          <t>/blog/category/[slug]</t>
         </is>
       </c>
       <c r="C127" s="13" t="inlineStr">
@@ -3861,7 +3861,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D127" s="4" t="inlineStr"/>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>category listing + pagination (not explicitly in the original phase list, but linked from the index's category pills — built so that link isn't a 404; own quality bar already requires "every page links to 2+", not dead links)</t>
+        </is>
+      </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
           <t>Phase 5 — Blog Engine (Sanity-backed)</t>
@@ -3872,7 +3876,7 @@
       <c r="A128" s="4" t="n"/>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>sitemap.ts already live from real Sanity data (122 URLs verified</t>
+          <t>generateStaticParams for all post slugs and category slugs (SSG)</t>
         </is>
       </c>
       <c r="C128" s="13" t="inlineStr">
@@ -3880,11 +3884,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D128" s="4" t="inlineStr">
-        <is>
-          <t>homepage + 121 posts)</t>
-        </is>
-      </c>
+      <c r="D128" s="4" t="inlineStr"/>
       <c r="E128" s="14" t="inlineStr">
         <is>
           <t>Phase 5 — Blog Engine (Sanity-backed)</t>
@@ -3895,7 +3895,7 @@
       <c r="A129" s="4" t="n"/>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>/search</t>
+          <t>sitemap.ts already live from real Sanity data (122 URLs verified</t>
         </is>
       </c>
       <c r="C129" s="13" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>full-text search across posts (built, not yet pushed — pending local review). No legacy Search.tsx ever existed — this is a genuinely new page, not a port (Phase 5's plan noted the GROQ query searchPostsQuery was already written but the page wasn't). Built as a pure Server Component: a plain GET &lt;form&gt; to /search?q=... needs no client JS at all, sanityFetch(searchPostsQuery, ...) runs server-side per this repo's data-fetching rule, results render with the existing PostCard. Was an orphan page (only reachable via /series' already-corrected link) — added a search icon to site-header.tsx (desktop + mobile) linking to /search so it has a real, discoverable entry point. Verified live: 200 OK empty state, ?q=trust returns 30 real matched posts (capped by the query's own [0...30]), typecheck/lint/production-build clean.</t>
+          <t>homepage + 121 posts)</t>
         </is>
       </c>
       <c r="E129" s="14" t="inlineStr">
@@ -3918,7 +3918,7 @@
       <c r="A130" s="4" t="n"/>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Header search icon → command-palette modal, matching legacy's real SearchPalette.tsx UX (a page-navigation link before this)</t>
+          <t>/search</t>
         </is>
       </c>
       <c r="C130" s="13" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Ported the real ~121-entry PAGES directory (data/searchablePages.ts is a grep-confirmed-dead older duplicate, not used) into lib/content/search-directory.ts, and the real word-frequency/multi-word-AND relevance scoring from lib/searchEngine.ts into lib/search-engine.ts. Fixed 3 stale /assessments/* hrefs to their real canonical routes, repointed the dead /the-index link to /search, and repointed 5 pre-consolidation Attention Theft sub-page links to real in-page anchors on the consolidated /attention-theft. Dropped 4 entries with no real route and no documented deferral (FauxTony, The Open Door, Alex Azzi, Spamtoast — Alex Azzi has since been ported, see below; should be re-added to the directory in a follow-up). Built components/search-modal.tsx on the existing shadcn Dialog (no cmdk, no framer-motion, no new dependency) with a real global Cmd/Ctrl+K shortcut, arrow-key nav + Enter-to-open, and Escape/backdrop close (free from Radix). Blog-post search is a debounced (250ms) fetch to a new app/api/search/route.ts, reusing /search's existing searchPostsQuery/sanityFetch rather than adding a new GROQ query, re-ranked server-side with the same relevance scorer used for static pages — legacy's TF-IDF body-density scoring wasn't portable since Sanity content isn't bundled client-side the way legacy's blogData.json was. Real Loader2 spinner during the fetch, no "..." text. Replaced both header &lt;Link href="/search"&gt; search icons (desktop + mobile) with buttons that open the modal; /s</t>
+          <t>full-text search across posts (built, not yet pushed — pending local review). No legacy Search.tsx ever existed — this is a genuinely new page, not a port (Phase 5's plan noted the GROQ query searchPostsQuery was already written but the page wasn't). Built as a pure Server Component: a plain GET &lt;form&gt; to /search?q=... needs no client JS at all, sanityFetch(searchPostsQuery, ...) runs server-side per this repo's data-fetching rule, results render with the existing PostCard. Was an orphan page (only reachable via /series' already-corrected link) — added a search icon to site-header.tsx (desktop + mobile) linking to /search so it has a real, discoverable entry point. Verified live: 200 OK empty state, ?q=trust returns 30 real matched posts (capped by the query's own [0...30]), typecheck/lint/production-build clean.</t>
         </is>
       </c>
       <c r="E130" s="14" t="inlineStr">
@@ -3941,7 +3941,7 @@
       <c r="A131" s="4" t="n"/>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>/articles</t>
+          <t>Header search icon → command-palette modal, matching legacy's real SearchPalette.tsx UX (a page-navigation link before this)</t>
         </is>
       </c>
       <c r="C131" s="13" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>full archive grouped by category (built, not yet pushed — pending local review). Real content ported in full — all 6 discovery-mode curations (Start Here, Short Reads, Deep Dives, Contrarian, Changed His Mind, Surprise Me) with their real curated slug lists, all 8 real category descriptions, category-grouped default view, search. Built ArticlesExplorer (client, components/blog/articles-explorer.tsx) + lib/content/articles-discovery.ts. Posts now come live from Sanity (allPostsForArchiveQuery) instead of the static blogData.json import. Caught and fixed a real legacy bug: 3 of the curated discovery-mode slugs (psychedelics-could-become-extractive-capitalism-unless, enterprise-blockchain-can-big-business-co-opt-an-existing-technology, an-ode-to-kusaki-where-plants-become-culinary-art) didn't match any real post slug — verified against blogData.json, corrected to the real slugs, same class of stale-slug bug already fixed on /journeys//recent-creations//series. Footer "SUBSCRIBE" CTA linked to /subscribe (Stripe-backed, deferred) — replaced with a link to /blog. Verified live: 200 OK, all discovery modes + categories present, both corrected slugs render as real working links, typecheck/lint/production-build clean.</t>
+          <t>Ported the real ~121-entry PAGES directory (data/searchablePages.ts is a grep-confirmed-dead older duplicate, not used) into lib/content/search-directory.ts, and the real word-frequency/multi-word-AND relevance scoring from lib/searchEngine.ts into lib/search-engine.ts. Fixed 3 stale /assessments/* hrefs to their real canonical routes, repointed the dead /the-index link to /search, and repointed 5 pre-consolidation Attention Theft sub-page links to real in-page anchors on the consolidated /attention-theft. Dropped 4 entries with no real route and no documented deferral (FauxTony, The Open Door, Alex Azzi, Spamtoast — Alex Azzi has since been ported, see below; should be re-added to the directory in a follow-up). Built components/search-modal.tsx on the existing shadcn Dialog (no cmdk, no framer-motion, no new dependency) with a real global Cmd/Ctrl+K shortcut, arrow-key nav + Enter-to-open, and Escape/backdrop close (free from Radix). Blog-post search is a debounced (250ms) fetch to a new app/api/search/route.ts, reusing /search's existing searchPostsQuery/sanityFetch rather than adding a new GROQ query, re-ranked server-side with the same relevance scorer used for static pages — legacy's TF-IDF body-density scoring wasn't portable since Sanity content isn't bundled client-side the way legacy's blogData.json was. Real Loader2 spinner during the fetch, no "..." text. Replaced both header &lt;Link href="/search"&gt; search icons (desktop + mobile) with buttons that open the modal; /s</t>
         </is>
       </c>
       <c r="E131" s="14" t="inlineStr">
@@ -3964,7 +3964,7 @@
       <c r="A132" s="4" t="n"/>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>/thesis-threads</t>
+          <t>/articles</t>
         </is>
       </c>
       <c r="C132" s="13" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>curated-by-thread view (built, not yet pushed — pending local review). No legacy port of a data file was needed — lib/content/thesis-threads.ts (Tony's own newsletter-curation "content DNA" document, ported from legacy client/src/data/sitePrompt.ts) already existed from an earlier pass with all 69 articleSlugs pre-verified against the real post corpus. Built ThesisThreadsExplorer (client, components/blog/thesis-threads-explorer.tsx) + app/thesis-threads/page.tsx (Server Component, sanityFetch(allPostsForArchiveQuery)). 4 tabs ported in full: Thesis Threads (6 threads, thread selector, per-thread article list with real THESIS_CONNECTORS pull-quotes, unmapped-articles section), Section Map (5 section-to-thesis cards), Research Library (6 citations + 4 LP comparables), Content Rules (voice, 6 content rules, "never use" word list). Fixed legacy's /read/[slug] links to this site's real /blog/[slug] pattern. Two decorative simplifications, matching calls already made elsewhere in this migration: canvas-based floating particles dropped (same as home-hero.tsx), and the legacy hero's generic Unsplash stock photo + scroll-parallax dropped for a plain dark band (not a real editorial image worth rescuing into Sanity, same call as the peptide pages' dead CloudFront heroes). Was an orphan page — added to site-nav-data.ts's "Read" mega-menu category, next to "All Essays". Verified live: 200 OK, stats strip shows real counts (121 essays, 69 mapped, 52 unmapped — matches the data module's own</t>
+          <t>full archive grouped by category (built, not yet pushed — pending local review). Real content ported in full — all 6 discovery-mode curations (Start Here, Short Reads, Deep Dives, Contrarian, Changed His Mind, Surprise Me) with their real curated slug lists, all 8 real category descriptions, category-grouped default view, search. Built ArticlesExplorer (client, components/blog/articles-explorer.tsx) + lib/content/articles-discovery.ts. Posts now come live from Sanity (allPostsForArchiveQuery) instead of the static blogData.json import. Caught and fixed a real legacy bug: 3 of the curated discovery-mode slugs (psychedelics-could-become-extractive-capitalism-unless, enterprise-blockchain-can-big-business-co-opt-an-existing-technology, an-ode-to-kusaki-where-plants-become-culinary-art) didn't match any real post slug — verified against blogData.json, corrected to the real slugs, same class of stale-slug bug already fixed on /journeys//recent-creations//series. Footer "SUBSCRIBE" CTA linked to /subscribe (Stripe-backed, deferred) — replaced with a link to /blog. Verified live: 200 OK, all discovery modes + categories present, both corrected slugs render as real working links, typecheck/lint/production-build clean.</t>
         </is>
       </c>
       <c r="E132" s="14" t="inlineStr">
@@ -3987,7 +3987,7 @@
       <c r="A133" s="4" t="n"/>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>/impact-futurism</t>
+          <t>/thesis-threads</t>
         </is>
       </c>
       <c r="C133" s="13" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>curated category view (built, not yet pushed — pending local review). Real content ported in full — all 7 real essays (3 featured + 4 more) across 5 tags (Health Systems, AI &amp; Energy, Psychedelic Medicine, Infrastructure, Trust &amp; Verification), curated teaser copy, tag filter. Built ImpactFuturismExplorer (client, components/blog/impact-futurism-explorer.tsx) + lib/content/impact-futurism.ts (curated tag/teaser only — real title/date/hero-image/read-time now come live from Sanity via allPostsForArchiveQuery, same content-boundary split as articles-discovery.ts/thesis-threads.ts). Legacy's per-article hero images (/manus-storage/... — banned Manus host — plus one dead CloudFront URL) dropped in favor of each real post's own Sanity heroImage, already present per post, no rescue needed. Both "Get the Dispatch" CTAs linked to /subscribe (Stripe-backed, deferred) — replaced with /blog, same fix already applied on /articles. Fixed legacy's stale hardcoded "All 121 Essays" to a live posts.length. Was an orphan page — added to site-nav-data.ts's "Read" mega-menu category. Verified live: 200 OK, all 7 real titles + real Sanity hero images render, live essay count (121) confirmed in SSR HTML, typecheck/lint clean.</t>
+          <t>curated-by-thread view (built, not yet pushed — pending local review). No legacy port of a data file was needed — lib/content/thesis-threads.ts (Tony's own newsletter-curation "content DNA" document, ported from legacy client/src/data/sitePrompt.ts) already existed from an earlier pass with all 69 articleSlugs pre-verified against the real post corpus. Built ThesisThreadsExplorer (client, components/blog/thesis-threads-explorer.tsx) + app/thesis-threads/page.tsx (Server Component, sanityFetch(allPostsForArchiveQuery)). 4 tabs ported in full: Thesis Threads (6 threads, thread selector, per-thread article list with real THESIS_CONNECTORS pull-quotes, unmapped-articles section), Section Map (5 section-to-thesis cards), Research Library (6 citations + 4 LP comparables), Content Rules (voice, 6 content rules, "never use" word list). Fixed legacy's /read/[slug] links to this site's real /blog/[slug] pattern. Two decorative simplifications, matching calls already made elsewhere in this migration: canvas-based floating particles dropped (same as home-hero.tsx), and the legacy hero's generic Unsplash stock photo + scroll-parallax dropped for a plain dark band (not a real editorial image worth rescuing into Sanity, same call as the peptide pages' dead CloudFront heroes). Was an orphan page — added to site-nav-data.ts's "Read" mega-menu category, next to "All Essays". Verified live: 200 OK, stats strip shows real counts (121 essays, 69 mapped, 52 unmapped — matches the data module's own</t>
         </is>
       </c>
       <c r="E133" s="14" t="inlineStr">
@@ -4010,7 +4010,7 @@
       <c r="A134" s="4" t="n"/>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>On-demand webhook-triggered revalidation on Sanity publish (built, not yet pushed</t>
+          <t>/impact-futurism</t>
         </is>
       </c>
       <c r="C134" s="13" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>pending local review). Corrected mislabel: the old note here said "Phase 11", but Phase 11 is the unrelated Publish-Approval Workflow (Supabase dashboard) — this is its own small piece of infra, not part of that phase. Built app/api/revalidate/route.ts: a Route Handler using next-sanity/webhook's parseBody (wraps @sanity/webhook's isValidSignature — already a transitive dep via next-sanity, no new package needed) to verify the request against SANITY_WEBHOOK_SECRET (already reserved in .env.local.example from an earlier pass, never actually wired up). On a valid signature, calls revalidateTag("sanity", { expire: 0 }) — every sanityFetch() call already tags its cache entry "sanity" (see lib/sanity/client.ts), so one tag covers every Sanity-backed page, no per-route path list to maintain. Real Next.js 16 breaking change caught: revalidateTag(tag) (single-argument) is deprecated and now a type error — the second argument is required. Read node_modules/next/dist/docs/.../revalidateTag.md rather than assuming the old signature; its own webhook example calls out { expire: 0 } specifically for "webhooks or third-party services that need immediate expiration" (the default recommended profile: "max" only refreshes on next visit, wrong for this case). Still needs a human step this migration can't do: creating the actual webhook in Sanity's project dashboard (manage.sanity.io → API → Webhooks) pointing at /api/revalidate with a matching secret — documented in the route's own file comment</t>
+          <t>curated category view (built, not yet pushed — pending local review). Real content ported in full — all 7 real essays (3 featured + 4 more) across 5 tags (Health Systems, AI &amp; Energy, Psychedelic Medicine, Infrastructure, Trust &amp; Verification), curated teaser copy, tag filter. Built ImpactFuturismExplorer (client, components/blog/impact-futurism-explorer.tsx) + lib/content/impact-futurism.ts (curated tag/teaser only — real title/date/hero-image/read-time now come live from Sanity via allPostsForArchiveQuery, same content-boundary split as articles-discovery.ts/thesis-threads.ts). Legacy's per-article hero images (/manus-storage/... — banned Manus host — plus one dead CloudFront URL) dropped in favor of each real post's own Sanity heroImage, already present per post, no rescue needed. Both "Get the Dispatch" CTAs linked to /subscribe (Stripe-backed, deferred) — replaced with /blog, same fix already applied on /articles. Fixed legacy's stale hardcoded "All 121 Essays" to a live posts.length. Was an orphan page — added to site-nav-data.ts's "Read" mega-menu category. Verified live: 200 OK, all 7 real titles + real Sanity hero images render, live essay count (121) confirmed in SSR HTML, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E134" s="14" t="inlineStr">
@@ -4033,7 +4033,7 @@
       <c r="A135" s="4" t="n"/>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Article footer standardization (built, not yet pushed</t>
+          <t>On-demand webhook-triggered revalidation on Sanity publish (built, not yet pushed</t>
         </is>
       </c>
       <c r="C135" s="13" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pending local review). Real content ported for all 121 entries from footerData.json (exercise / 2-4 curated related links with hand-written reasons / riddle / further reading), keyed by slug. Built ArticleFooter (components/blog/article-footer.tsx) + lib/content/article-footers.ts, wired into app/blog/[slug]/page.tsx after the "Read next" section. Fetched all 121 real post slugs from Sanity to cross-check every related[].slug reference — found and fixed 3 real stale slugs across 2 renamed posts (the Bentley/EV piece and the Butcher's Daughter piece each had a different stale slug pointing at them), same class of bug already fixed on /journeys//articles//series. Also found: (1) one entry used a relatedArticles key instead of related — the key BlogPost.tsx actually reads — meaning that post's related-links block silently never rendered even in legacy; normalized to related. (2) a trueSelfCTA field in one entry that BlogPost.tsx never reads at all (grepped — zero usages) — dead data, dropped rather than ported. (3) an exercise.steps checklist in one entry that legacy authored but never rendered (component only reads exercise.title/.description) — real content, so rendered here instead of repeating the oversight. The one slug: "manifesto" sentinel (legacy's in-code special case for "link to the manifesto, not a post") resolved to a real href: "/living-declaration" in the data itself. The hardcoded "TrueSelf Soul Print Assessment" CTA (identical on every legacy post) is kept, but </t>
+          <t>pending local review). Corrected mislabel: the old note here said "Phase 11", but Phase 11 is the unrelated Publish-Approval Workflow (Supabase dashboard) — this is its own small piece of infra, not part of that phase. Built app/api/revalidate/route.ts: a Route Handler using next-sanity/webhook's parseBody (wraps @sanity/webhook's isValidSignature — already a transitive dep via next-sanity, no new package needed) to verify the request against SANITY_WEBHOOK_SECRET (already reserved in .env.local.example from an earlier pass, never actually wired up). On a valid signature, calls revalidateTag("sanity", { expire: 0 }) — every sanityFetch() call already tags its cache entry "sanity" (see lib/sanity/client.ts), so one tag covers every Sanity-backed page, no per-route path list to maintain. Real Next.js 16 breaking change caught: revalidateTag(tag) (single-argument) is deprecated and now a type error — the second argument is required. Read node_modules/next/dist/docs/.../revalidateTag.md rather than assuming the old signature; its own webhook example calls out { expire: 0 } specifically for "webhooks or third-party services that need immediate expiration" (the default recommended profile: "max" only refreshes on next visit, wrong for this case). Still needs a human step this migration can't do: creating the actual webhook in Sanity's project dashboard (manage.sanity.io → API → Webhooks) pointing at /api/revalidate with a matching secret — documented in the route's own file comment</t>
         </is>
       </c>
       <c r="E135" s="14" t="inlineStr">
@@ -4056,7 +4056,7 @@
       <c r="A136" s="4" t="n"/>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>Spot-check all 121 migrated posts' body formatting (automated, not a Studio visual pass</t>
+          <t>Article footer standardization (built, not yet pushed</t>
         </is>
       </c>
       <c r="C136" s="13" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>see note below on what that still leaves open). Wrote a one-off script fetching every post's body from Sanity and scanning for markdown-conversion artifacts (unconverted bold/text/headings/bullets, leaked HTML tags, empty text blocks, link marks with no href). Flagged 12 of 121. Two real bugs found and one fixed: (1) ~8 posts have link marks with href: "" — traced to the actual root cause by reading blogData.json's raw originalContent markdown directly: the source markdown itself has text links with an already-empty URL (predates this migration entirely — e.g. the-tug-of-war-ethical-vs-economic-decisions has subsidy, dairy kills, etc., empty parens in the original text). portable-text.tsx's link renderer was defaulting a missing href to "#", silently turning lost-forever data into a fake dead link on every affected post. Fixed at the renderer level (real code, not data): a link mark with no href now renders its text plain, with no anchor wrapper — verified live on the-tug-of-war-ethical-vs-economic-decisions (zero href="#" in the rendered HTML, previously-"linked" words like "subsidy" and "dairy kills" still read fine as plain text). (2) 4 posts (energy-is-money-money-is-memory, frqncy-the-bus-that-restores-the-world, is-that-a-lot-clarisse-abelarde, you-are-the-moat) had literal un-rendered !alt markdown image syntax visible as plain paragraph text — the markdown→Portable-Text converter (scripts/markdown-to-portable-text.ts) never had image-syntax handling at all. Checked al</t>
+          <t xml:space="preserve">pending local review). Real content ported for all 121 entries from footerData.json (exercise / 2-4 curated related links with hand-written reasons / riddle / further reading), keyed by slug. Built ArticleFooter (components/blog/article-footer.tsx) + lib/content/article-footers.ts, wired into app/blog/[slug]/page.tsx after the "Read next" section. Fetched all 121 real post slugs from Sanity to cross-check every related[].slug reference — found and fixed 3 real stale slugs across 2 renamed posts (the Bentley/EV piece and the Butcher's Daughter piece each had a different stale slug pointing at them), same class of bug already fixed on /journeys//articles//series. Also found: (1) one entry used a relatedArticles key instead of related — the key BlogPost.tsx actually reads — meaning that post's related-links block silently never rendered even in legacy; normalized to related. (2) a trueSelfCTA field in one entry that BlogPost.tsx never reads at all (grepped — zero usages) — dead data, dropped rather than ported. (3) an exercise.steps checklist in one entry that legacy authored but never rendered (component only reads exercise.title/.description) — real content, so rendered here instead of repeating the oversight. The one slug: "manifesto" sentinel (legacy's in-code special case for "link to the manifesto, not a post") resolved to a real href: "/living-declaration" in the data itself. The hardcoded "TrueSelf Soul Print Assessment" CTA (identical on every legacy post) is kept, but </t>
         </is>
       </c>
       <c r="E136" s="14" t="inlineStr">
@@ -4079,7 +4079,7 @@
       <c r="A137" s="4" t="n"/>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Reconcile blogData.json vs. the legacy blogPosts.ts module. Resolved</t>
+          <t>Spot-check all 121 migrated posts' body formatting (automated, not a Studio visual pass</t>
         </is>
       </c>
       <c r="C137" s="13" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>not a duplicate. Traced blogPosts.ts's own header comment ("Blog Post Data — 20 most recent posts... original excerpt, AI-rewritten 'Updated for Today' version") plus its actual 25-entry BlogPost[] array: this is a distinct, unrelated, much smaller dataset (an AI-rewrite/"TonyG Format" exercise with lesson/nextSteps fields) that was never the input to migrate-blog-posts.ts, which reads only blogData.json (confirmed in that script's own top-of-file comment and its LegacyPost type). blogData.json is the sole authoritative source for the 121-post corpus; blogPosts.ts was never a candidate alternate and needs no reconciliation — it's simply out of scope, superseded implicitly by the real 121-post migration.</t>
+          <t>see note below on what that still leaves open). Wrote a one-off script fetching every post's body from Sanity and scanning for markdown-conversion artifacts (unconverted bold/text/headings/bullets, leaked HTML tags, empty text blocks, link marks with no href). Flagged 12 of 121. Two real bugs found and one fixed: (1) ~8 posts have link marks with href: "" — traced to the actual root cause by reading blogData.json's raw originalContent markdown directly: the source markdown itself has text links with an already-empty URL (predates this migration entirely — e.g. the-tug-of-war-ethical-vs-economic-decisions has subsidy, dairy kills, etc., empty parens in the original text). portable-text.tsx's link renderer was defaulting a missing href to "#", silently turning lost-forever data into a fake dead link on every affected post. Fixed at the renderer level (real code, not data): a link mark with no href now renders its text plain, with no anchor wrapper — verified live on the-tug-of-war-ethical-vs-economic-decisions (zero href="#" in the rendered HTML, previously-"linked" words like "subsidy" and "dairy kills" still read fine as plain text). (2) 4 posts (energy-is-money-money-is-memory, frqncy-the-bus-that-restores-the-world, is-that-a-lot-clarisse-abelarde, you-are-the-moat) had literal un-rendered !alt markdown image syntax visible as plain paragraph text — the markdown→Portable-Text converter (scripts/markdown-to-portable-text.ts) never had image-syntax handling at all. Checked al</t>
         </is>
       </c>
       <c r="E137" s="14" t="inlineStr">
@@ -4102,7 +4102,7 @@
       <c r="A138" s="4" t="n"/>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Preserve internal cross-link structure from client/src/data/linkMap.ts / readingPaths.ts (built, not yet pushed</t>
+          <t>Reconcile blogData.json vs. the legacy blogPosts.ts module. Resolved</t>
         </is>
       </c>
       <c r="C138" s="13" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>pending local review). Both ported as real, working features, not just cross-referenced.</t>
+          <t>not a duplicate. Traced blogPosts.ts's own header comment ("Blog Post Data — 20 most recent posts... original excerpt, AI-rewritten 'Updated for Today' version") plus its actual 25-entry BlogPost[] array: this is a distinct, unrelated, much smaller dataset (an AI-rewrite/"TonyG Format" exercise with lesson/nextSteps fields) that was never the input to migrate-blog-posts.ts, which reads only blogData.json (confirmed in that script's own top-of-file comment and its LegacyPost type). blogData.json is the sole authoritative source for the 121-post corpus; blogPosts.ts was never a candidate alternate and needs no reconciliation — it's simply out of scope, superseded implicitly by the real 121-post migration.</t>
         </is>
       </c>
       <c r="E138" s="14" t="inlineStr">
@@ -4125,7 +4125,7 @@
       <c r="A139" s="4" t="n"/>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Post extras from live (2026-10-01)</t>
+          <t>Preserve internal cross-link structure from client/src/data/linkMap.ts / readingPaths.ts (built, not yet pushed</t>
         </is>
       </c>
       <c r="C139" s="13" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>every post now shows the blocks legacy BlogPost.tsx and live render around the essay: format tag, validity score and series badge in the header, the summary, "Before You Read" (Reveal/Hint via &lt;details&gt;, answer in the server HTML), then The Lesson, Next Steps, Further Reading, Voices in This Space / Also involves, Since this was written, and the series reading list. Data ported unchanged into src/lib/content/post-extras.ts (from blogData.json, riddleData.ts, thoughtLeaders.ts), further-reading.ts and essay-series.ts (now shared with /series); component src/components/blog/post-extras.tsx. Checked against live: lesson, next steps and validity match on every post that loaded. Left out on purpose: read counts, reactions/comments/"Rate this thinking" (no backend), and the "Updated for Today" toggle (an AI rewrite; live defaults to the original text, which is what Sanity holds).</t>
+          <t>pending local review). Both ported as real, working features, not just cross-referenced.</t>
         </is>
       </c>
       <c r="E139" s="14" t="inlineStr">
@@ -4148,7 +4148,7 @@
       <c r="A140" s="4" t="n"/>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>Lost tables restored (2026-10-01)</t>
+          <t>Post extras from live (2026-10-01)</t>
         </is>
       </c>
       <c r="C140" s="13" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>the migration's markdown converter had no table case, so all tables in 18 posts (44 tables) were silently dropped; live still shows them. Added a plain dataTable body type (src/sanity/schemas/dataTable.ts, rendered in src/lib/sanity/portable-text.tsx, scrolls inside its own box on phones), a table case in scripts/markdown-to-portable-text.ts, and put every table back after the paragraph that precedes it in the legacy markdown (scripts/restore-blog-tables.ts), as Sanity drafts built on existing drafts. find-my-ev-... had a malformed table showing as raw "|" text; now a real table (draft).</t>
+          <t>every post now shows the blocks legacy BlogPost.tsx and live render around the essay: format tag, validity score and series badge in the header, the summary, "Before You Read" (Reveal/Hint via &lt;details&gt;, answer in the server HTML), then The Lesson, Next Steps, Further Reading, Voices in This Space / Also involves, Since this was written, and the series reading list. Data ported unchanged into src/lib/content/post-extras.ts (from blogData.json, riddleData.ts, thoughtLeaders.ts), further-reading.ts and essay-series.ts (now shared with /series); component src/components/blog/post-extras.tsx. Checked against live: lesson, next steps and validity match on every post that loaded. Left out on purpose: read counts, reactions/comments/"Rate this thinking" (no backend), and the "Updated for Today" toggle (an AI rewrite; live defaults to the original text, which is what Sanity holds).</t>
         </is>
       </c>
       <c r="E140" s="14" t="inlineStr">
@@ -4171,7 +4171,7 @@
       <c r="A141" s="4" t="n"/>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Essays rewritten on live, saved as Sanity drafts (2026-10-01)</t>
+          <t>Lost tables restored (2026-10-01)</t>
         </is>
       </c>
       <c r="C141" s="13" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>(scripts/sync-live-essays.ts, from live's essay body; live images rescued into Sanity): your-blood-lies-without-your-dna, energy-is-money-money-is-memory (kept our fixed author bio), the-way-of-dao, what-solutions-are-best-built-with-blockchain replaced with live's version; the-peptide-truth-... got live's "Provenance and Corrections" note and the new stem cell appendix. Checked: every live paragraph is in the drafts. Not changed: posts where live still shows old WordPress furniture we already cleaned (Davos 2022, Boiling the Human, Mastering BD, and others), and /the-stack links (a "Private review draft" page on live, not ported; text kept, link dropped).</t>
+          <t>the migration's markdown converter had no table case, so all tables in 18 posts (44 tables) were silently dropped; live still shows them. Added a plain dataTable body type (src/sanity/schemas/dataTable.ts, rendered in src/lib/sanity/portable-text.tsx, scrolls inside its own box on phones), a table case in scripts/markdown-to-portable-text.ts, and put every table back after the paragraph that precedes it in the legacy markdown (scripts/restore-blog-tables.ts), as Sanity drafts built on existing drafts. find-my-ev-... had a malformed table showing as raw "|" text; now a real table (draft).</t>
         </is>
       </c>
       <c r="E141" s="14" t="inlineStr">
@@ -4194,7 +4194,7 @@
       <c r="A142" s="4" t="n"/>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Password gate on you-are-the-moat (done 2026-10-06, owner chose a password)</t>
+          <t>Essays rewritten on live, saved as Sanity drafts (2026-10-01)</t>
         </is>
       </c>
       <c r="C142" s="13" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Server-checked: the password is in the GATED_POST_PASSWORD env var (in .env.local; must also be set in Netlify, or the essay stays locked for everyone), compared on the server, and the body is only rendered after a correct entry (checked: the locked page HTML has none of the essay text, and it is noindex, nofollow). Unlock lasts 30 days via an httpOnly cookie scoped to the post; changing the password locks everyone out again. Legacy's lock screen copy ("This One's Behind a Door"). Other posts stay statically built. Tested wrong/right password and reload in Chrome and Safari. Still true: the Sanity dataset is publicly readable, so the raw text is reachable through the Sanity API by someone who knows how. Was: (passwordGate, a browser-side check), but the port renders it openly to everyone. Needs a decision on how to gate it (see status block) before launch.</t>
+          <t>(scripts/sync-live-essays.ts, from live's essay body; live images rescued into Sanity): your-blood-lies-without-your-dna, energy-is-money-money-is-memory (kept our fixed author bio), the-way-of-dao, what-solutions-are-best-built-with-blockchain replaced with live's version; the-peptide-truth-... got live's "Provenance and Corrections" note and the new stem cell appendix. Checked: every live paragraph is in the drafts. Not changed: posts where live still shows old WordPress furniture we already cleaned (Davos 2022, Boiling the Human, Mastering BD, and others), and /the-stack links (a "Private review draft" page on live, not ported; text kept, link dropped).</t>
         </is>
       </c>
       <c r="E142" s="14" t="inlineStr">
@@ -4217,7 +4217,7 @@
       <c r="A143" s="4" t="n"/>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Essay page rebuilt to match live (2026-10-07, asked for by the team)</t>
+          <t>Password gate on you-are-the-moat (done 2026-10-06, owner chose a password)</t>
         </is>
       </c>
       <c r="C143" s="13" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Every post now has live's layout: full-width hero with the title over it (posts without their own photo use live's default arch art, rescued into Sanity, also on post cards), back link, colored format badge, date · category · read time, validity, byline (co-author override field), summary with a rule, labelled share buttons (X, LinkedIn, Facebook, More, Email, Copy link), live's type (Libre Baskerville body with indents, Cormorant Garamond italic section titles, IM Fell English drop cap, Fraunces title; loaded on essays only), red in-text links, the auto pull quote, section breaks, the GemSpark card with "What is this?", and the sticky parchment Contents sidebar (1280px+) that highlights the section being read (IntersectionObserver plus a settle check, so jumps land right; click scrolls there). Checked in Chrome: sidebar stays pinned, highlight follows scrolling, End/Home and clicks, no console errors, every image loads. After the essay, in live's order: The Lesson, Next steps, Further reading, Voices, Also involves (chips), Since this was written, #tags, Did this land?, video moment (Clarisse, FRQNCY), Ask Tony directly (emails Tony), Discourse comments, What's the verdict?, Rate this thinking, diagnostic and ImpactSoul CTAs, The Mirror reflection (85 posts), Try this, Where this leads, riddle, Go deeper, Discover your pattern, Originally published at, Previous/Next (legacy's order, series-aware), Why this matters now, author card, booking box, Subscribe / ABIT, social line,</t>
+          <t>Server-checked: the password is in the GATED_POST_PASSWORD env var (in .env.local; must also be set in Netlify, or the essay stays locked for everyone), compared on the server, and the body is only rendered after a correct entry (checked: the locked page HTML has none of the essay text, and it is noindex, nofollow). Unlock lasts 30 days via an httpOnly cookie scoped to the post; changing the password locks everyone out again. Legacy's lock screen copy ("This One's Behind a Door"). Other posts stay statically built. Tested wrong/right password and reload in Chrome and Safari. Still true: the Sanity dataset is publicly readable, so the raw text is reachable through the Sanity API by someone who knows how. Was: (passwordGate, a browser-side check), but the port renders it openly to everyone. Needs a decision on how to gate it (see status block) before launch.</t>
         </is>
       </c>
       <c r="E143" s="14" t="inlineStr">
@@ -4240,7 +4240,7 @@
       <c r="A144" s="4" t="n"/>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Essay extras moved into Sanity (2026-10-07, owner chose "publish directly")</t>
+          <t>Essay page rebuilt to match live (2026-10-07, asked for by the team)</t>
         </is>
       </c>
       <c r="C144" s="13" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>The per-post blocks that were in code (post-extras.ts, article-footers.ts, reading-paths.ts, deleted) are now fields on each post, "Essay extras" tab in Studio: 152 documents written (every post plus its pending draft), counts checked (105 lessons, 93 riddles, 115 read-next lists). New fields the same day: byline, editorsNote (Forward Health's September 2026 note), provenanceNote (on live's 14 first-hand/accusation posts), videoMoment, updatedBody.</t>
+          <t>Every post now has live's layout: full-width hero with the title over it (posts without their own photo use live's default arch art, rescued into Sanity, also on post cards), back link, colored format badge, date · category · read time, validity, byline (co-author override field), summary with a rule, labelled share buttons (X, LinkedIn, Facebook, More, Email, Copy link), live's type (Libre Baskerville body with indents, Cormorant Garamond italic section titles, IM Fell English drop cap, Fraunces title; loaded on essays only), red in-text links, the auto pull quote, section breaks, the GemSpark card with "What is this?", and the sticky parchment Contents sidebar (1280px+) that highlights the section being read (IntersectionObserver plus a settle check, so jumps land right; click scrolls there). Checked in Chrome: sidebar stays pinned, highlight follows scrolling, End/Home and clicks, no console errors, every image loads. After the essay, in live's order: The Lesson, Next steps, Further reading, Voices, Also involves (chips), Since this was written, #tags, Did this land?, video moment (Clarisse, FRQNCY), Ask Tony directly (emails Tony), Discourse comments, What's the verdict?, Rate this thinking, diagnostic and ImpactSoul CTAs, The Mirror reflection (85 posts), Try this, Where this leads, riddle, Go deeper, Discover your pattern, Originally published at, Previous/Next (legacy's order, series-aware), Why this matters now, author card, booking box, Subscribe / ABIT, social line,</t>
         </is>
       </c>
       <c r="E144" s="14" t="inlineStr">
@@ -4263,7 +4263,7 @@
       <c r="A145" s="4" t="n"/>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>"Original post / Updated for today" switch (2026-10-07; was decision 20)</t>
+          <t>Essay extras moved into Sanity (2026-10-07, owner chose "publish directly")</t>
         </is>
       </c>
       <c r="C145" s="13" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Legacy's updated texts checked against live (98-99% word overlap on 5 posts), imported into updatedBody for 102 essays (scripts/import-2026-10-07-updated-bodies.ts; stray TITLE:/DATE: headers dropped). Skipped: 9 where both versions are identical, 3 whose updated text holds pictures (frqncy, two Molecule as Mirror parts; they show the original only). Both versions are in the page; the switch needs no request, and the Contents sidebar follows it.</t>
+          <t>The per-post blocks that were in code (post-extras.ts, article-footers.ts, reading-paths.ts, deleted) are now fields on each post, "Essay extras" tab in Studio: 152 documents written (every post plus its pending draft), counts checked (105 lessons, 93 riddles, 115 read-next lists). New fields the same day: byline, editorsNote (Forward Health's September 2026 note), provenanceNote (on live's 14 first-hand/accusation posts), videoMoment, updatedBody.</t>
         </is>
       </c>
       <c r="E145" s="14" t="inlineStr">
@@ -4286,7 +4286,7 @@
       <c r="A146" s="4" t="n"/>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>The 2 live-only essays imported (2026-10-07; was decision 8)</t>
+          <t>"Original post / Updated for today" switch (2026-10-07; was decision 20)</t>
         </is>
       </c>
       <c r="C146" s="13" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>the-tollbooth-and-the-alternative (with Alex Veytsel; its own hero rescued; lesson, next steps, Try this, Where this leads, riddle, Go deeper) and what-quest-could-fix, published. Tollbooth's 5 body pictures are broken on live itself (a dark placeholder with unreadable text), so they're listed in BLOG-IMAGE-BRIEFS.md to be made instead.</t>
+          <t>Legacy's updated texts checked against live (98-99% word overlap on 5 posts), imported into updatedBody for 102 essays (scripts/import-2026-10-07-updated-bodies.ts; stray TITLE:/DATE: headers dropped). Skipped: 9 where both versions are identical, 3 whose updated text holds pictures (frqncy, two Molecule as Mirror parts; they show the original only). Both versions are in the page; the switch needs no request, and the Contents sidebar follows it.</t>
         </is>
       </c>
       <c r="E146" s="14" t="inlineStr">
@@ -4309,7 +4309,7 @@
       <c r="A147" s="4" t="n"/>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Pending drafts published (2026-10-07, owner said yes; was decision 18)</t>
+          <t>The 2 live-only essays imported (2026-10-07; was decision 8)</t>
         </is>
       </c>
       <c r="C147" s="13" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>all 31 post drafts (44 tables on 17 posts, the essays brought in line with live including Your Blood's new hero, link and clean-up fixes). No drafts left. Creation dates checked unchanged (the heading rules depend on them).</t>
+          <t>the-tollbooth-and-the-alternative (with Alex Veytsel; its own hero rescued; lesson, next steps, Try this, Where this leads, riddle, Go deeper) and what-quest-could-fix, published. Tollbooth's 5 body pictures are broken on live itself (a dark placeholder with unreadable text), so they're listed in BLOG-IMAGE-BRIEFS.md to be made instead.</t>
         </is>
       </c>
       <c r="E147" s="14" t="inlineStr">
@@ -4332,7 +4332,7 @@
       <c r="A148" s="4" t="n"/>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Per-post fixes from the 2026-10-07 sweep (all 123 live/our posts compared)</t>
+          <t>Pending drafts published (2026-10-07, owner said yes; was decision 18)</t>
         </is>
       </c>
       <c r="C148" s="13" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>heart-protocol-addendum heading showed {#heart-protocol-addendum} (fixed in Sanity); lines starting with "◆ " are section titles again, as on live (five-cups had 4); /blog/akbar-cuisine-restoration-economics now redirects to /akbar like live (was decision 21; out of the sitemap); the Elixir of Life product block (photos and order QR codes rescued into Sanity); Clarisse's video rescued.</t>
+          <t>all 31 post drafts (44 tables on 17 posts, the essays brought in line with live including Your Blood's new hero, link and clean-up fixes). No drafts left. Creation dates checked unchanged (the heading rules depend on them).</t>
         </is>
       </c>
       <c r="E148" s="14" t="inlineStr">
@@ -4355,63 +4355,63 @@
       <c r="A149" s="4" t="n"/>
       <c r="B149" s="4" t="inlineStr">
         <is>
+          <t>Per-post fixes from the 2026-10-07 sweep (all 123 live/our posts compared)</t>
+        </is>
+      </c>
+      <c r="C149" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>heart-protocol-addendum heading showed {#heart-protocol-addendum} (fixed in Sanity); lines starting with "◆ " are section titles again, as on live (five-cups had 4); /blog/akbar-cuisine-restoration-economics now redirects to /akbar like live (was decision 21; out of the sitemap); the Elixir of Life product block (photos and order QR codes rescued into Sanity); Clarisse's video rescued.</t>
+        </is>
+      </c>
+      <c r="E149" s="14" t="inlineStr">
+        <is>
+          <t>Phase 5 — Blog Engine (Sanity-backed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="n"/>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
           <t>Reader engagement (2026-10-07)</t>
         </is>
       </c>
-      <c r="C149" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr">
+      <c r="C150" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
         <is>
           <t>Discourse comments (shown straight away like live, honeypot and a 5-per-10-minutes limit, Tony emailed for each), reactions, Rate this thinking, Micro-commitment: supabase/migrations/0002_blog_engagement.sql, server actions src/app/blog/[slug]/engagement-actions.ts; essays stay prebuilt (the blocks load after the page). Needs the 0002 script run in Supabase (Phase 2) and Resend for the emails; until then the forms say "isn't available just now".</t>
         </is>
       </c>
-      <c r="E149" s="14" t="inlineStr">
+      <c r="E150" s="14" t="inlineStr">
         <is>
           <t>Phase 5 — Blog Engine (Sanity-backed)</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="10" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="10" t="inlineStr">
         <is>
           <t>Phase 6 — BrewSoul (28 routes)</t>
         </is>
       </c>
-      <c r="B150" s="11" t="n"/>
-      <c r="C150" s="11" t="n"/>
-      <c r="D150" s="12" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="4" t="n"/>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>/brewsoul</t>
-        </is>
-      </c>
-      <c r="C151" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr">
-        <is>
-          <t>welcome/landing gate (built, not yet pushed — pending local review), along with the shared foundation the rest of Phase 6 depends on. Ported BrewSoulLayout.tsx → app/brewsoul/layout.tsx + components/brewsoul/brewsoul-nav.tsx (BrewSoulNav/BrewSoulFooter), CategoryBadge.tsx → components/brewsoul/category-badge.tsx, brewsoul-config.ts → lib/content/brewsoul-config.ts, and BrewSoulDirectory.tsx's CATEGORIES/PAGE_CATEGORY_MAP data (not the page itself yet) → lib/content/brewsoul-directory.ts. Real architecture decision: BrewSoul is a self-contained sub-site with its own nav/footer/coffee-brown palette, same as legacy — but this app has one flat root layout with no route groups, so the main site's SiteHeader/SiteFooter needed to be suppressed for this one subtree without restructuring every existing route. Added components/site-chrome.tsx (SiteChrome, a small client wrapper checking pathname.startsWith("/brewsoul")) around both in app/layout.tsx — verified via literal &lt;header&gt;/&lt;footer&gt;/&lt;nav&gt; tag counts in real SSR HTML (not text search, which false-positives on Next dev mode's RSC debug payload) that /brewsoul gets zero main-site chrome and its own real nav+footer, while / still gets exactly one of each. Dropped TonyAvatarTrigger (FauxTony chatbot widget — Phase 10, no backend yet, same "don't fake it" call made elsewhere) from the nav. Ported BrewSoulWelcome.tsx → components/brewsoul/brewsoul-welcome-quiz.tsx (8-screen onboarding quiz, real identity-scoring logic, palate questions</t>
-        </is>
-      </c>
-      <c r="E151" s="14" t="inlineStr">
-        <is>
-          <t>Phase 6 — BrewSoul (28 routes)</t>
-        </is>
-      </c>
+      <c r="B151" s="11" t="n"/>
+      <c r="C151" s="11" t="n"/>
+      <c r="D151" s="12" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n"/>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/first-sip</t>
+          <t>/brewsoul</t>
         </is>
       </c>
       <c r="C152" s="13" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>onboarding intro (built, not yet pushed — pending local review). Ported "The First Sip Is a Vote" in full — the complete manifesto essay (5 sections, 3 pullquotes, the couplets block, the disclosure-demands grid), the 5-tool journey map, 6 related-essay links (real slugs, cross-checked against this session's already-verified corpus), the closing + sources, and the email capture. Built as a Server Component (all static except the email form) + components/brewsoul/next-steps.tsx (shared "what's next" CTA, itself a Server Component — legacy's hover effects were plain CSS-able, no JS state needed) + components/brewsoul/first-sip-email-capture.tsx (client island, mailto: fallback since no subscribe backend exists, same pattern as newsletter-popup.tsx). Dropped the canvas CoffeeDust decoration and the confirmed-dead hero photo (/api/img/brewsoul-orig_84eb4bc9.jpg, 404, same Manus proxy) — with no image left, the scroll-linked parallax that moved it went too. The 5 tool-card links (prescription/health/pairings/economics/compare) point at later Phase 6 routes not built yet — same forward-reference pattern as /find-my. Verified live: 200 OK, full essay text present, CategoryBadge correctly shows "Start Here" (from PAGE_CATEGORY_MAP), zero main-site chrome leaking in, typecheck/lint clean.</t>
+          <t>welcome/landing gate (built, not yet pushed — pending local review), along with the shared foundation the rest of Phase 6 depends on. Ported BrewSoulLayout.tsx → app/brewsoul/layout.tsx + components/brewsoul/brewsoul-nav.tsx (BrewSoulNav/BrewSoulFooter), CategoryBadge.tsx → components/brewsoul/category-badge.tsx, brewsoul-config.ts → lib/content/brewsoul-config.ts, and BrewSoulDirectory.tsx's CATEGORIES/PAGE_CATEGORY_MAP data (not the page itself yet) → lib/content/brewsoul-directory.ts. Real architecture decision: BrewSoul is a self-contained sub-site with its own nav/footer/coffee-brown palette, same as legacy — but this app has one flat root layout with no route groups, so the main site's SiteHeader/SiteFooter needed to be suppressed for this one subtree without restructuring every existing route. Added components/site-chrome.tsx (SiteChrome, a small client wrapper checking pathname.startsWith("/brewsoul")) around both in app/layout.tsx — verified via literal &lt;header&gt;/&lt;footer&gt;/&lt;nav&gt; tag counts in real SSR HTML (not text search, which false-positives on Next dev mode's RSC debug payload) that /brewsoul gets zero main-site chrome and its own real nav+footer, while / still gets exactly one of each. Dropped TonyAvatarTrigger (FauxTony chatbot widget — Phase 10, no backend yet, same "don't fake it" call made elsewhere) from the nav. Ported BrewSoulWelcome.tsx → components/brewsoul/brewsoul-welcome-quiz.tsx (8-screen onboarding quiz, real identity-scoring logic, palate questions</t>
         </is>
       </c>
       <c r="E152" s="14" t="inlineStr">
@@ -4434,7 +4434,7 @@
       <c r="A153" s="4" t="n"/>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/home</t>
+          <t>/brewsoul/first-sip</t>
         </is>
       </c>
       <c r="C153" s="13" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>the real BrewSoul dashboard (distinct from /brewsoul's identity-quiz welcome gate and /brewsoul/first-sip's manifesto): hero + stats, Follow the Dollar teaser, Top QPR coffees (computed live via computeQPR), the 2025 crisis callout, New Drops, a Wall of Shame preview (SHAME_ENTRIES), the research-hub card grid, and a cyclable health-fact ticker (components/brewsoul/health-ticker.tsx, its own small client island so the rest of the page stays a Server Component). Canvas WarmParticles/ParallaxBg decorations and the dead hero photo (/api/img/brewsoul-orig_84eb4bc9.jpg, same confirmed-404 Manus proxy used elsewhere in Phase 6) dropped for CSS gradients. Stats use the real live BREWSOUL_COFFEES.length (107) in place of legacy's stale "103". Verified live: 200 OK.</t>
+          <t>onboarding intro (built, not yet pushed — pending local review). Ported "The First Sip Is a Vote" in full — the complete manifesto essay (5 sections, 3 pullquotes, the couplets block, the disclosure-demands grid), the 5-tool journey map, 6 related-essay links (real slugs, cross-checked against this session's already-verified corpus), the closing + sources, and the email capture. Built as a Server Component (all static except the email form) + components/brewsoul/next-steps.tsx (shared "what's next" CTA, itself a Server Component — legacy's hover effects were plain CSS-able, no JS state needed) + components/brewsoul/first-sip-email-capture.tsx (client island, mailto: fallback since no subscribe backend exists, same pattern as newsletter-popup.tsx). Dropped the canvas CoffeeDust decoration and the confirmed-dead hero photo (/api/img/brewsoul-orig_84eb4bc9.jpg, 404, same Manus proxy) — with no image left, the scroll-linked parallax that moved it went too. The 5 tool-card links (prescription/health/pairings/economics/compare) point at later Phase 6 routes not built yet — same forward-reference pattern as /find-my. Verified live: 200 OK, full essay text present, CategoryBadge correctly shows "Start Here" (from PAGE_CATEGORY_MAP), zero main-site chrome leaking in, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E153" s="14" t="inlineStr">
@@ -4457,7 +4457,7 @@
       <c r="A154" s="4" t="n"/>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/browse</t>
+          <t>/brewsoul/home</t>
         </is>
       </c>
       <c r="C154" s="13" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>coffee listing (components/brewsoul/browse-explorer.tsx), real filter/search over the full BREWSOUL_COFFEES catalog. Verified live: 200 OK.</t>
+          <t>the real BrewSoul dashboard (distinct from /brewsoul's identity-quiz welcome gate and /brewsoul/first-sip's manifesto): hero + stats, Follow the Dollar teaser, Top QPR coffees (computed live via computeQPR), the 2025 crisis callout, New Drops, a Wall of Shame preview (SHAME_ENTRIES), the research-hub card grid, and a cyclable health-fact ticker (components/brewsoul/health-ticker.tsx, its own small client island so the rest of the page stays a Server Component). Canvas WarmParticles/ParallaxBg decorations and the dead hero photo (/api/img/brewsoul-orig_84eb4bc9.jpg, same confirmed-404 Manus proxy used elsewhere in Phase 6) dropped for CSS gradients. Stats use the real live BREWSOUL_COFFEES.length (107) in place of legacy's stale "103". Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E154" s="14" t="inlineStr">
@@ -4480,7 +4480,7 @@
       <c r="A155" s="4" t="n"/>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/coffee/[id]</t>
+          <t>/brewsoul/browse</t>
         </is>
       </c>
       <c r="C155" s="13" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>coffee detail page (breadcrumb, QPR + tier header, quick stats, tasting notes, flavor-profile bars, the 4 intelligence scores, transparency/ethics data, buy links, competition wins, similar-coffees cross-links, journey CTAs), server-rendered with generateStaticParams over all 107 real coffees (this repo's bounded-dynamic-route convention, same as /blog/[slug]) instead of legacy's client-side useParams lookup. Verified live: 200 OK.</t>
+          <t>coffee listing (components/brewsoul/browse-explorer.tsx), real filter/search over the full BREWSOUL_COFFEES catalog. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E155" s="14" t="inlineStr">
@@ -4503,7 +4503,7 @@
       <c r="A156" s="4" t="n"/>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/quiz</t>
+          <t>/brewsoul/coffee/[id]</t>
         </is>
       </c>
       <c r="C156" s="13" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>matching quiz (built, not yet pushed — pending local review), along with the real data/engine foundation most of the rest of Phase 6 depends on. Ported lib/intelligence-engine/{types,scoring}.ts verbatim (generic scoring engine — QPR/availability/scarcity/wow/tier/freshness — reusable beyond BrewSoul) and the full coffee catalog (legacy's 3 files: brewsoul-coffees.ts + -expanded.ts + -expanded2.ts, merged at import time) → one lib/content/brewsoul-coffees.ts, extracted via tsx (not hand-typed — 107 real entries, ~6.5K lines). Caught a real stale count: legacy's own file header claimed "105" and its UI copy said "103", but the actual merged arrays contain 107 — this migration shows the live BREWSOUL_COFFEES.length everywhere instead of a repeated hardcoded number. Ported JourneyBar.tsx (components/brewsoul/journey-bar.tsx) — the fixed bottom "what's next" bar shown on every BrewSoul content page except the identity quiz — and retrofitted it onto /brewsoul/first-sip too (built before JourneyBar existed). Built components/brewsoul/brewsoul-quiz.tsx: real 7-question taste quiz scored against each coffee's real flavorProfile via the real scoring engine, ranking the full catalog by match. Legacy's useMarkVisited was renamed to markVisited (it's a plain localStorage write, not a hook — its old use-prefixed name tripped React's rules-of-hooks lint when called from inside a useEffect). Dropped the canvas WarmParticles decoration and the dead hero photo (same confirmed-404 Manus proxy,</t>
+          <t>coffee detail page (breadcrumb, QPR + tier header, quick stats, tasting notes, flavor-profile bars, the 4 intelligence scores, transparency/ethics data, buy links, competition wins, similar-coffees cross-links, journey CTAs), server-rendered with generateStaticParams over all 107 real coffees (this repo's bounded-dynamic-route convention, same as /blog/[slug]) instead of legacy's client-side useParams lookup. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E156" s="14" t="inlineStr">
@@ -4526,7 +4526,7 @@
       <c r="A157" s="4" t="n"/>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/wall-of-shame</t>
+          <t>/brewsoul/quiz</t>
         </is>
       </c>
       <c r="C157" s="13" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>content page. Real 13 entries (brand/category/evidence/severity/response) from SHAME_ENTRIES, unchanged. Category filter buttons extracted into components/brewsoul/shame-explorer.tsx (the only interactive piece) so the page itself stays a Server Component. Verified live: 200 OK.</t>
+          <t>matching quiz (built, not yet pushed — pending local review), along with the real data/engine foundation most of the rest of Phase 6 depends on. Ported lib/intelligence-engine/{types,scoring}.ts verbatim (generic scoring engine — QPR/availability/scarcity/wow/tier/freshness — reusable beyond BrewSoul) and the full coffee catalog (legacy's 3 files: brewsoul-coffees.ts + -expanded.ts + -expanded2.ts, merged at import time) → one lib/content/brewsoul-coffees.ts, extracted via tsx (not hand-typed — 107 real entries, ~6.5K lines). Caught a real stale count: legacy's own file header claimed "105" and its UI copy said "103", but the actual merged arrays contain 107 — this migration shows the live BREWSOUL_COFFEES.length everywhere instead of a repeated hardcoded number. Ported JourneyBar.tsx (components/brewsoul/journey-bar.tsx) — the fixed bottom "what's next" bar shown on every BrewSoul content page except the identity quiz — and retrofitted it onto /brewsoul/first-sip too (built before JourneyBar existed). Built components/brewsoul/brewsoul-quiz.tsx: real 7-question taste quiz scored against each coffee's real flavorProfile via the real scoring engine, ranking the full catalog by match. Legacy's useMarkVisited was renamed to markVisited (it's a plain localStorage write, not a hook — its old use-prefixed name tripped React's rules-of-hooks lint when called from inside a useEffect). Dropped the canvas WarmParticles decoration and the dead hero photo (same confirmed-404 Manus proxy,</t>
         </is>
       </c>
       <c r="E157" s="14" t="inlineStr">
@@ -4549,7 +4549,7 @@
       <c r="A158" s="4" t="n"/>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/follow-the-dollar</t>
+          <t>/brewsoul/wall-of-shame</t>
         </is>
       </c>
       <c r="C158" s="13" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>supply-chain essay. Real DOLLAR_BREAKDOWNS segment bars (farmer/exporter/importer/roaster/retailer %, real commentary), unchanged. The farmer-segment bar's data-driven color (green/gold/red by threshold) is a small known set of variants — precomposed as 3 literal Tailwind classes rather than an inline style background, per this repo's dynamic-class rule; only the genuinely per-item width stays as style. Fully static, Server Component. Verified live: 200 OK.</t>
+          <t>content page. Real 13 entries (brand/category/evidence/severity/response) from SHAME_ENTRIES, unchanged. Category filter buttons extracted into components/brewsoul/shame-explorer.tsx (the only interactive piece) so the page itself stays a Server Component. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E158" s="14" t="inlineStr">
@@ -4572,7 +4572,7 @@
       <c r="A159" s="4" t="n"/>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/farms</t>
+          <t>/brewsoul/follow-the-dollar</t>
         </is>
       </c>
       <c r="C159" s="13" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>sourcing content ("Farm Passports"). Real FARMS entries (country/region/producer/altitude/story/varieties/certifications), unchanged. Fully static. Verified live: 200 OK.</t>
+          <t>supply-chain essay. Real DOLLAR_BREAKDOWNS segment bars (farmer/exporter/importer/roaster/retailer %, real commentary), unchanged. The farmer-segment bar's data-driven color (green/gold/red by threshold) is a small known set of variants — precomposed as 3 literal Tailwind classes rather than an inline style background, per this repo's dynamic-class rule; only the genuinely per-item width stays as style. Fully static, Server Component. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E159" s="14" t="inlineStr">
@@ -4595,7 +4595,7 @@
       <c r="A160" s="4" t="n"/>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/mold-free</t>
+          <t>/brewsoul/farms</t>
         </is>
       </c>
       <c r="C160" s="13" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>mycotoxin content. Real verified/claims/untested split computed live over the full BREWSOUL_COFFEES catalog by moldTestStatus. Fully static. Verified live: 200 OK.</t>
+          <t>sourcing content ("Farm Passports"). Real FARMS entries (country/region/producer/altitude/story/varieties/certifications), unchanged. Fully static. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E160" s="14" t="inlineStr">
@@ -4618,7 +4618,7 @@
       <c r="A161" s="4" t="n"/>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/experiences</t>
+          <t>/brewsoul/mold-free</t>
         </is>
       </c>
       <c r="C161" s="13" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>experiential content ("Experience Map"). Real EXPERIENCES entries (farm tours, cafés, cupping labs, roastery visits), unchanged. Country filter buttons extracted into components/brewsoul/experiences-explorer.tsx, same split-out-the-interactive-bit pattern as wall-of-shame. Verified live: 200 OK.</t>
+          <t>mycotoxin content. Real verified/claims/untested split computed live over the full BREWSOUL_COFFEES catalog by moldTestStatus. Fully static. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E161" s="14" t="inlineStr">
@@ -4641,7 +4641,7 @@
       <c r="A162" s="4" t="n"/>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/health</t>
+          <t>/brewsoul/experiences</t>
         </is>
       </c>
       <c r="C162" s="13" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>health deep-dive, ported from BrewSoulHealthFull.tsx (the file legacy's own router actually uses for this route — BrewSoulContent.tsx's same-named BrewSoulHealth export is real but genuinely dead/unrouted code in legacy, shadowed by this one). Real 8 longevity findings with real citations/participant counts, 7 real risks with severity ratings, CYP1A2 caffeine-metabolism genetics, a 6-step chronobiology timing schedule, 8 real bioactive compounds, 3 real mycotoxin threats, and a 3-step "simplification protocol," all ported unchanged and verbatim. Dead Manus hero image dropped for a CSS gradient. Legacy's own redundant BrewSoulLayout wrapper dropped — app/brewsoul/layout.tsx already wraps every route. The two real interactive pieces (show-all-risks toggle, per-compound click-to-expand) split into components/brewsoul/health-{risks,compounds}.tsx client islands so the rest stays a Server Component. Legacy's bespoke earthy "science" palette (soil/clay/sage/moss — distinct from the rest of BrewSoul's amber/gold commercial palette) kept as a deliberate one-off sub-identity for this one page, same reasoning as /attention-theft's own "crusade" palette elsewhere in this migration. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>experiential content ("Experience Map"). Real EXPERIENCES entries (farm tours, cafés, cupping labs, roastery visits), unchanged. Country filter buttons extracted into components/brewsoul/experiences-explorer.tsx, same split-out-the-interactive-bit pattern as wall-of-shame. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E162" s="14" t="inlineStr">
@@ -4664,7 +4664,7 @@
       <c r="A163" s="4" t="n"/>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/varieties</t>
+          <t>/brewsoul/health</t>
         </is>
       </c>
       <c r="C163" s="13" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>reference: varieties. Real VARIETIES encyclopedia entries (species/origin/genetics/cup profile/yield/disease resistance), unchanged. Search extracted into components/brewsoul/varieties-explorer.tsx. Verified live: 200 OK.</t>
+          <t>health deep-dive, ported from BrewSoulHealthFull.tsx (the file legacy's own router actually uses for this route — BrewSoulContent.tsx's same-named BrewSoulHealth export is real but genuinely dead/unrouted code in legacy, shadowed by this one). Real 8 longevity findings with real citations/participant counts, 7 real risks with severity ratings, CYP1A2 caffeine-metabolism genetics, a 6-step chronobiology timing schedule, 8 real bioactive compounds, 3 real mycotoxin threats, and a 3-step "simplification protocol," all ported unchanged and verbatim. Dead Manus hero image dropped for a CSS gradient. Legacy's own redundant BrewSoulLayout wrapper dropped — app/brewsoul/layout.tsx already wraps every route. The two real interactive pieces (show-all-risks toggle, per-compound click-to-expand) split into components/brewsoul/health-{risks,compounds}.tsx client islands so the rest stays a Server Component. Legacy's bespoke earthy "science" palette (soil/clay/sage/moss — distinct from the rest of BrewSoul's amber/gold commercial palette) kept as a deliberate one-off sub-identity for this one page, same reasoning as /attention-theft's own "crusade" palette elsewhere in this migration. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E163" s="14" t="inlineStr">
@@ -4687,7 +4687,7 @@
       <c r="A164" s="4" t="n"/>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/processing</t>
+          <t>/brewsoul/varieties</t>
         </is>
       </c>
       <c r="C164" s="13" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>reference: processing. Real PROCESSING_METHODS entries (description/flavor impact/complexity/controversy), unchanged. Fully static. Verified live: 200 OK.</t>
+          <t>reference: varieties. Real VARIETIES encyclopedia entries (species/origin/genetics/cup profile/yield/disease resistance), unchanged. Search extracted into components/brewsoul/varieties-explorer.tsx. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E164" s="14" t="inlineStr">
@@ -4710,7 +4710,7 @@
       <c r="A165" s="4" t="n"/>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/roasters</t>
+          <t>/brewsoul/processing</t>
         </is>
       </c>
       <c r="C165" s="13" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>reference: roaster directory. Real ROASTERS entries (philosophy/quality/transparency/farmer-equity scores), unchanged. Search + tier filter extracted into components/brewsoul/roasters-explorer.tsx. Verified live: 200 OK.</t>
+          <t>reference: processing. Real PROCESSING_METHODS entries (description/flavor impact/complexity/controversy), unchanged. Fully static. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E165" s="14" t="inlineStr">
@@ -4733,7 +4733,7 @@
       <c r="A166" s="4" t="n"/>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/glossary</t>
+          <t>/brewsoul/roasters</t>
         </is>
       </c>
       <c r="C166" s="13" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>reference: glossary. Real GLOSSARY terms, unchanged. Search + alphabetical grouping extracted into components/brewsoul/glossary-explorer.tsx. Verified live: 200 OK.</t>
+          <t>reference: roaster directory. Real ROASTERS entries (philosophy/quality/transparency/farmer-equity scores), unchanged. Search + tier filter extracted into components/brewsoul/roasters-explorer.tsx. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E166" s="14" t="inlineStr">
@@ -4756,7 +4756,7 @@
       <c r="A167" s="4" t="n"/>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/pairings</t>
+          <t>/brewsoul/glossary</t>
         </is>
       </c>
       <c r="C167" s="13" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>reference: pairings. Real PAIRINGS (food/drink pairings by origin) and 3 real curated FLIGHTS (each linking to real coffees in the catalog), unchanged. Fully static. Verified live: 200 OK.</t>
+          <t>reference: glossary. Real GLOSSARY terms, unchanged. Search + alphabetical grouping extracted into components/brewsoul/glossary-explorer.tsx. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E167" s="14" t="inlineStr">
@@ -4779,7 +4779,7 @@
       <c r="A168" s="4" t="n"/>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/economics</t>
+          <t>/brewsoul/pairings</t>
         </is>
       </c>
       <c r="C168" s="13" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>reference: economics. Real live-computed stats (coffee/origin/roaster/variety counts, average price, average farmer share via DOLLAR_BREAKDOWNS), a real price-distribution histogram, and a real top-origins ranking — all computed directly from BREWSOUL_COFFEES at render time, unchanged. Fully static. Verified live: 200 OK.</t>
+          <t>reference: pairings. Real PAIRINGS (food/drink pairings by origin) and 3 real curated FLIGHTS (each linking to real coffees in the catalog), unchanged. Fully static. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr">
@@ -4802,7 +4802,7 @@
       <c r="A169" s="4" t="n"/>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/compare</t>
+          <t>/brewsoul/economics</t>
         </is>
       </c>
       <c r="C169" s="13" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>tool: compare coffees. Real side-by-side comparison of up to 4 coffees across origin/producer/variety/process/price/cupping and the 4 intelligence scores (QPR/availability/wow/overall), unchanged. Interactivity in components/brewsoul/compare-explorer.tsx. Verified live: 200 OK.</t>
+          <t>reference: economics. Real live-computed stats (coffee/origin/roaster/variety counts, average price, average farmer share via DOLLAR_BREAKDOWNS), a real price-distribution histogram, and a real top-origins ranking — all computed directly from BREWSOUL_COFFEES at render time, unchanged. Fully static. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E169" s="14" t="inlineStr">
@@ -4825,7 +4825,7 @@
       <c r="A170" s="4" t="n"/>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/blend-builder</t>
+          <t>/brewsoul/compare</t>
         </is>
       </c>
       <c r="C170" s="13" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>tool: blend builder. Real combine-up-to-5-coffees ratio calculator with weighted-average QPR/Wow/Overall scores via range sliders, unchanged (never persisted anywhere in legacy either — a pure in-session calculator). Interactivity in components/brewsoul/blend-builder-explorer.tsx. Verified live: 200 OK.</t>
+          <t>tool: compare coffees. Real side-by-side comparison of up to 4 coffees across origin/producer/variety/process/price/cupping and the 4 intelligence scores (QPR/availability/wow/overall), unchanged. Interactivity in components/brewsoul/compare-explorer.tsx. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E170" s="14" t="inlineStr">
@@ -4848,7 +4848,7 @@
       <c r="A171" s="4" t="n"/>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/drops</t>
+          <t>/brewsoul/blend-builder</t>
         </is>
       </c>
       <c r="C171" s="13" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>tool: product drops ("Latest Drops"). Real top-12-by-overall-score coffees. No client-side state at all (legacy's own useMemo had no changing dependencies — a pure derived list), so this ships as a plain Server Component. Verified live: 200 OK.</t>
+          <t>tool: blend builder. Real combine-up-to-5-coffees ratio calculator with weighted-average QPR/Wow/Overall scores via range sliders, unchanged (never persisted anywhere in legacy either — a pure in-session calculator). Interactivity in components/brewsoul/blend-builder-explorer.tsx. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E171" s="14" t="inlineStr">
@@ -4871,7 +4871,7 @@
       <c r="A172" s="4" t="n"/>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/collection</t>
+          <t>/brewsoul/drops</t>
         </is>
       </c>
       <c r="C172" s="13" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>tool: personal collection tracker ("My Collection"). Real save/toggle-to-collection behavior, unchanged. Real bug found and fixed: legacy read localStorage directly inside a useState initializer — unsafe during SSR, same hydration-mismatch class already fixed in journey-bar.tsx/journey-tracker.tsx — rebuilt around a module-level external store fed through useSyncExternalStore in components/brewsoul/collection-explorer.tsx. Also found and fixed: the already-ported brewsoul-directory.ts listed this page's path as /brewsoul/my-coffees — a real dead link in legacy's own directory (legacy's actual router only ever served this at /brewsoul/collection, /brewsoul/my-coffees never existed) — corrected to the real path. Verified live: 200 OK.</t>
+          <t>tool: product drops ("Latest Drops"). Real top-12-by-overall-score coffees. No client-side state at all (legacy's own useMemo had no changing dependencies — a pure derived list), so this ships as a plain Server Component. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E172" s="14" t="inlineStr">
@@ -4894,7 +4894,7 @@
       <c r="A173" s="4" t="n"/>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/submit</t>
+          <t>/brewsoul/collection</t>
         </is>
       </c>
       <c r="C173" s="13" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>tool: submit a coffee ("Submit or Appeal"). Real submit-a-coffee / appeal-a-score form, unchanged in structure. Real bug found and fixed: legacy's own comment admitted "In production this would POST to a tRPC endpoint" but in the meantime wrote the submission to localStorage and showed "Received. We'll review your submission" regardless — actively misleading, since nobody would ever see a localStorage-only write. Replaced with a real mailto: fallback pre-filled with the form fields, same honest-degradation pattern as first-sip-email-capture.tsx — no fake success state. Verified live: 200 OK.</t>
+          <t>tool: personal collection tracker ("My Collection"). Real save/toggle-to-collection behavior, unchanged. Real bug found and fixed: legacy read localStorage directly inside a useState initializer — unsafe during SSR, same hydration-mismatch class already fixed in journey-bar.tsx/journey-tracker.tsx — rebuilt around a module-level external store fed through useSyncExternalStore in components/brewsoul/collection-explorer.tsx. Also found and fixed: the already-ported brewsoul-directory.ts listed this page's path as /brewsoul/my-coffees — a real dead link in legacy's own directory (legacy's actual router only ever served this at /brewsoul/collection, /brewsoul/my-coffees never existed) — corrected to the real path. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E173" s="14" t="inlineStr">
@@ -4917,7 +4917,7 @@
       <c r="A174" s="4" t="n"/>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/prescription</t>
+          <t>/brewsoul/submit</t>
         </is>
       </c>
       <c r="C174" s="13" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>personalized "prescription", ported from BrewSoulPrescriptionFull.tsx (the file legacy's router actually uses — BrewSoulTools.tsx's same-named export is dead/unrouted, same shadowed-file trap as /brewsoul/health). Real 5-step questionnaire (genetics/timing/health/flavor/budget) generating a real, deterministic prescription (generatePrescription — real roast/cup-count/brand/pricing/warning logic), all ported unchanged and verbatim. Legacy's trpc.coffeePrescription.generate AI-enhancement mutation doesn't exist in this migration — dropped along with its "AI ANALYSIS LOADING..." block, which would otherwise spin forever and never resolve; the real prescription itself never depended on that call, it's already fully computed client-side. Same bespoke earthy "science" palette as /brewsoul/health kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>tool: submit a coffee ("Submit or Appeal"). Real submit-a-coffee / appeal-a-score form, unchanged in structure. Real bug found and fixed: legacy's own comment admitted "In production this would POST to a tRPC endpoint" but in the meantime wrote the submission to localStorage and showed "Received. We'll review your submission" regardless — actively misleading, since nobody would ever see a localStorage-only write. Replaced with a real mailto: fallback pre-filled with the form fields, same honest-degradation pattern as first-sip-email-capture.tsx — no fake success state. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E174" s="14" t="inlineStr">
@@ -4940,7 +4940,7 @@
       <c r="A175" s="4" t="n"/>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/chains</t>
+          <t>/brewsoul/prescription</t>
         </is>
       </c>
       <c r="C175" s="13" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>"Top 100 Coffee Chains" ranking (not supply-chain visualization — that's /brewsoul/economics//brewsoul/follow-the-dollar; this is chain rankings). Real 100-chain dataset extracted from legacy's computed CHAIN_RANKINGS export (5 real weighted dimensions → aggregate → S-F tier) via a one-off tsx script (same approach as brewsoul-coffees.ts) into lib/content/brewsoul-chains.ts, with a new ChainEntry type added to intelligence-engine/types.ts. Real tier/type filters, search, and per-chain expand, unchanged, extracted into components/brewsoul/chains-explorer.tsx. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>personalized "prescription", ported from BrewSoulPrescriptionFull.tsx (the file legacy's router actually uses — BrewSoulTools.tsx's same-named export is dead/unrouted, same shadowed-file trap as /brewsoul/health). Real 5-step questionnaire (genetics/timing/health/flavor/budget) generating a real, deterministic prescription (generatePrescription — real roast/cup-count/brand/pricing/warning logic), all ported unchanged and verbatim. Legacy's trpc.coffeePrescription.generate AI-enhancement mutation doesn't exist in this migration — dropped along with its "AI ANALYSIS LOADING..." block, which would otherwise spin forever and never resolve; the real prescription itself never depended on that call, it's already fully computed client-side. Same bespoke earthy "science" palette as /brewsoul/health kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E175" s="14" t="inlineStr">
@@ -4963,7 +4963,7 @@
       <c r="A176" s="4" t="n"/>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/biodynamic</t>
+          <t>/brewsoul/chains</t>
         </is>
       </c>
       <c r="C176" s="13" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>biodynamic content. The complete real census of Demeter-certified biodynamic coffee: 3 real source farms, 6 real roasters/brands with real product tables and pricing, real nutritional-science compounds, a real cost calculator, and a real impact/tokenization section, all ported unchanged and verbatim. Dead Manus hero image dropped for a CSS gradient. The 3 genuinely interactive pieces (click-to-expand farms/roasters, cups-per-day cost slider) split into components/brewsoul/{biodynamic-farms,biodynamic-roasters,cost-calculator}.tsx client islands so the rest stays a Server Component. Same bespoke earthy "science" palette as /brewsoul/health and /brewsoul/prescription kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>"Top 100 Coffee Chains" ranking (not supply-chain visualization — that's /brewsoul/economics//brewsoul/follow-the-dollar; this is chain rankings). Real 100-chain dataset extracted from legacy's computed CHAIN_RANKINGS export (5 real weighted dimensions → aggregate → S-F tier) via a one-off tsx script (same approach as brewsoul-coffees.ts) into lib/content/brewsoul-chains.ts, with a new ChainEntry type added to intelligence-engine/types.ts. Real tier/type filters, search, and per-chain expand, unchanged, extracted into components/brewsoul/chains-explorer.tsx. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E176" s="14" t="inlineStr">
@@ -4986,7 +4986,7 @@
       <c r="A177" s="4" t="n"/>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/decaf</t>
+          <t>/brewsoul/biodynamic</t>
         </is>
       </c>
       <c r="C177" s="13" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>decaf content ("Paint Stripper or Pure Water?"). Real 3-process breakdown (methylene chloride/Swiss Water/supercritical CO₂), 13 real clean-decaf brands ("Hall of Fame"), 10 real methylene-chloride brands ("Wall of Shame," with real Clean Label Project lawsuit citations), a real carbon footprint comparison, real decaf health science, and a real price-comparison table, all ported unchanged and verbatim. Legacy's manual document.title/&lt;meta keywords&gt; mutation in a useEffect (a real anti-pattern — Next's generateMetadata already owns the head) dropped for the real metadata export. Real bug found and fixed: the 13-brand FAME dataset was initially exported from the "use client" decaf-fame.tsx component file and imported into the Server Component page for its price-comparison table — non-component exports from a client module aren't available across the RSC boundary, which threw FAME is not iterable at runtime (only caught by live verification, not typecheck/lint). Moved the data to a plain lib/content/brewsoul-decaf.ts module instead. The 2 genuinely interactive pieces (click-to-expand Hall of Fame, reveal-toggle Wall of Shame) split into components/brewsoul/decaf-{fame,shame}.tsx client islands. Same bespoke earthy "science" palette as the other /brewsoul deep-dive pages kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>biodynamic content. The complete real census of Demeter-certified biodynamic coffee: 3 real source farms, 6 real roasters/brands with real product tables and pricing, real nutritional-science compounds, a real cost calculator, and a real impact/tokenization section, all ported unchanged and verbatim. Dead Manus hero image dropped for a CSS gradient. The 3 genuinely interactive pieces (click-to-expand farms/roasters, cups-per-day cost slider) split into components/brewsoul/{biodynamic-farms,biodynamic-roasters,cost-calculator}.tsx client islands so the rest stays a Server Component. Same bespoke earthy "science" palette as /brewsoul/health and /brewsoul/prescription kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E177" s="14" t="inlineStr">
@@ -5009,7 +5009,7 @@
       <c r="A178" s="4" t="n"/>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/esoteric</t>
+          <t>/brewsoul/decaf</t>
         </is>
       </c>
       <c r="C178" s="13" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>rare-coffee content ("Esoteric Coffee Index"). Real 9-coffee index across 2 tiers (Panama Geisha, Yemen Mokha, Liberica, Eugenioides, Wush Wush, Sidra, Pink Bourbon, Bourbon Aji, Sudan Rume) with real tasting notes, rarity scores, and real named buy sources, plus a real acquisition-priority list and explorer scorecard, all ported unchanged and verbatim. Real content gap found, not fixed: legacy's own "Top 10 Acquisition Priority" list and scorecard table both reference "Laurina" as a 10th entry, but no coffee card for it exists anywhere in the source dataset — ported as-is rather than inventing card content that was never written. Zero client-side state anywhere in this page (only CSS-able hover) — ships entirely as a Server Component. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>decaf content ("Paint Stripper or Pure Water?"). Real 3-process breakdown (methylene chloride/Swiss Water/supercritical CO₂), 13 real clean-decaf brands ("Hall of Fame"), 10 real methylene-chloride brands ("Wall of Shame," with real Clean Label Project lawsuit citations), a real carbon footprint comparison, real decaf health science, and a real price-comparison table, all ported unchanged and verbatim. Legacy's manual document.title/&lt;meta keywords&gt; mutation in a useEffect (a real anti-pattern — Next's generateMetadata already owns the head) dropped for the real metadata export. Real bug found and fixed: the 13-brand FAME dataset was initially exported from the "use client" decaf-fame.tsx component file and imported into the Server Component page for its price-comparison table — non-component exports from a client module aren't available across the RSC boundary, which threw FAME is not iterable at runtime (only caught by live verification, not typecheck/lint). Moved the data to a plain lib/content/brewsoul-decaf.ts module instead. The 2 genuinely interactive pieces (click-to-expand Hall of Fame, reveal-toggle Wall of Shame) split into components/brewsoul/decaf-{fame,shame}.tsx client islands. Same bespoke earthy "science" palette as the other /brewsoul deep-dive pages kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E178" s="14" t="inlineStr">
@@ -5032,7 +5032,7 @@
       <c r="A179" s="4" t="n"/>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/cities + /brewsoul/cities/[slug]</t>
+          <t>/brewsoul/esoteric</t>
         </is>
       </c>
       <c r="C179" s="13" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>city directory + detail ("City Intelligence Module"). Real 25-city leaderboard (name/state/grade/score/tagline/verdict/live stats), a real 7-dimension scoring methodology, and real national + universal/nuanced chain report cards, all ported unchanged and verbatim into lib/content/brewsoul-cities.ts. Real data-completeness note, not a bug: legacy's own comment admits only Portland has full shop-by-shop data (25 real best + 5 real worst shops with real blurbs/scores/order-this/skip-this) — the other 24 cities have real city-level stats but empty shop/chain/bridge-drink/non-coffee arrays; legacy's own UI already handles this honestly (a real "Full data coming soon" state on both the card and detail page, not fake data) — preserved exactly, verified for both Portland (full tabs) and Seattle (coming-soon state). Grade filter, methodology modal, and chain-toggle interactivity in components/brewsoul/cities-explorer.tsx; per-city tab switching and per-shop expand in components/brewsoul/city-detail-tabs.tsx. Detail route uses generateStaticParams over all 25 real slugs. Scroll-linked parallax and floating-particle backgrounds dropped, same decoration call made throughout this migration. Real image-hosting gap flagged, not silently worked around: the 25 city hero photos are real, live Unsplash URLs (not a dead Manus proxy) but aren't yet uploaded to Sanity per this repo's own image convention — added images.unsplash.com to next.config.ts's remotePatterns as an interim measure rather th</t>
+          <t>rare-coffee content ("Esoteric Coffee Index"). Real 9-coffee index across 2 tiers (Panama Geisha, Yemen Mokha, Liberica, Eugenioides, Wush Wush, Sidra, Pink Bourbon, Bourbon Aji, Sudan Rume) with real tasting notes, rarity scores, and real named buy sources, plus a real acquisition-priority list and explorer scorecard, all ported unchanged and verbatim. Real content gap found, not fixed: legacy's own "Top 10 Acquisition Priority" list and scorecard table both reference "Laurina" as a 10th entry, but no coffee card for it exists anywhere in the source dataset — ported as-is rather than inventing card content that was never written. Zero client-side state anywhere in this page (only CSS-able hover) — ships entirely as a Server Component. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E179" s="14" t="inlineStr">
@@ -5055,7 +5055,7 @@
       <c r="A180" s="4" t="n"/>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/directory</t>
+          <t>/brewsoul/cities + /brewsoul/cities/[slug]</t>
         </is>
       </c>
       <c r="C180" s="13" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>real master page index ("Everything Inside BrewSoul," not a roaster directory — that's /brewsoul/roasters). Real 6 categories with real page descriptions/icons, unchanged; the underlying data already lived in lib/content/brewsoul-directory.ts (built earlier this phase to power CategoryBadge) — this route is where it finally becomes a real browsable page. Category filter extracted into components/brewsoul/directory-explorer.tsx. Fixed the stale "Browse All 103 Coffees" label (real count is 107) by dropping the hardcoded number from the shared data module — benefits every other consumer of that module too. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>city directory + detail ("City Intelligence Module"). Real 25-city leaderboard (name/state/grade/score/tagline/verdict/live stats), a real 7-dimension scoring methodology, and real national + universal/nuanced chain report cards, all ported unchanged and verbatim into lib/content/brewsoul-cities.ts. Real data-completeness note, not a bug: legacy's own comment admits only Portland has full shop-by-shop data (25 real best + 5 real worst shops with real blurbs/scores/order-this/skip-this) — the other 24 cities have real city-level stats but empty shop/chain/bridge-drink/non-coffee arrays; legacy's own UI already handles this honestly (a real "Full data coming soon" state on both the card and detail page, not fake data) — preserved exactly, verified for both Portland (full tabs) and Seattle (coming-soon state). Grade filter, methodology modal, and chain-toggle interactivity in components/brewsoul/cities-explorer.tsx; per-city tab switching and per-shop expand in components/brewsoul/city-detail-tabs.tsx. Detail route uses generateStaticParams over all 25 real slugs. Scroll-linked parallax and floating-particle backgrounds dropped, same decoration call made throughout this migration. Real image-hosting gap flagged, not silently worked around: the 25 city hero photos are real, live Unsplash URLs (not a dead Manus proxy) but aren't yet uploaded to Sanity per this repo's own image convention — added images.unsplash.com to next.config.ts's remotePatterns as an interim measure rather th</t>
         </is>
       </c>
       <c r="E180" s="14" t="inlineStr">
@@ -5078,7 +5078,7 @@
       <c r="A181" s="4" t="n"/>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/guest + /brewsoul/guest/shanita-nicholas</t>
+          <t>/brewsoul/directory</t>
         </is>
       </c>
       <c r="C181" s="13" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>guest series index + profile ("Tony G Guest Series"). Real single guest entry (Shanita Nicholas — real headline/teaser/tags) on the index, and the real 10-question interview on the detail page (Fair Trade economics, roasting mythology, the C Market, regenerative vs. sustainable, origin-roasting economics vs. Fair Trade, blockchain traceability, pre-harvest financing — real substantive answers with real citations), all ported unchanged and verbatim into components/brewsoul/shanita-interview.tsx. Legacy's guest photo (/api/img/brewsoul-orig_84eb4bc9.jpg) was the same dead Manus proxy confirmed 404 throughout this migration — dropped for a plain initial avatar on both pages rather than a broken headshot. Per-question expand/collapse, "Expand/Collapse All," and the real Twitter/LinkedIn/copy-link share row are genuinely interactive, split into client islands. Verified live: 200 OK on both, typecheck/lint clean.</t>
+          <t>real master page index ("Everything Inside BrewSoul," not a roaster directory — that's /brewsoul/roasters). Real 6 categories with real page descriptions/icons, unchanged; the underlying data already lived in lib/content/brewsoul-directory.ts (built earlier this phase to power CategoryBadge) — this route is where it finally becomes a real browsable page. Category filter extracted into components/brewsoul/directory-explorer.tsx. Fixed the stale "Browse All 103 Coffees" label (real count is 107) by dropping the hardcoded number from the shared data module — benefits every other consumer of that module too. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E181" s="14" t="inlineStr">
@@ -5101,63 +5101,63 @@
       <c r="A182" s="4" t="n"/>
       <c r="B182" s="4" t="inlineStr">
         <is>
+          <t>/brewsoul/guest + /brewsoul/guest/shanita-nicholas</t>
+        </is>
+      </c>
+      <c r="C182" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>guest series index + profile ("Tony G Guest Series"). Real single guest entry (Shanita Nicholas — real headline/teaser/tags) on the index, and the real 10-question interview on the detail page (Fair Trade economics, roasting mythology, the C Market, regenerative vs. sustainable, origin-roasting economics vs. Fair Trade, blockchain traceability, pre-harvest financing — real substantive answers with real citations), all ported unchanged and verbatim into components/brewsoul/shanita-interview.tsx. Legacy's guest photo (/api/img/brewsoul-orig_84eb4bc9.jpg) was the same dead Manus proxy confirmed 404 throughout this migration — dropped for a plain initial avatar on both pages rather than a broken headshot. Per-question expand/collapse, "Expand/Collapse All," and the real Twitter/LinkedIn/copy-link share row are genuinely interactive, split into client islands. Verified live: 200 OK on both, typecheck/lint clean.</t>
+        </is>
+      </c>
+      <c r="E182" s="14" t="inlineStr">
+        <is>
+          <t>Phase 6 — BrewSoul (28 routes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="n"/>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
           <t>Shared: port BrewSoulLayout, CategoryBadge, JourneyBar, NextSteps as Next.js layout/components</t>
         </is>
       </c>
-      <c r="C182" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D182" s="4" t="inlineStr">
+      <c r="C183" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr">
         <is>
           <t>app/brewsoul/layout.tsx + components/brewsoul/{brewsoul-nav,category-badge,journey-bar,next-steps}.tsx, all built and reused by every /brewsoul/* route above.</t>
         </is>
       </c>
-      <c r="E182" s="14" t="inlineStr">
+      <c r="E183" s="14" t="inlineStr">
         <is>
           <t>Phase 6 — BrewSoul (28 routes)</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="10" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="10" t="inlineStr">
         <is>
           <t>Phase 7 — PRI &amp; Kava Encyclopedias (19 routes)</t>
         </is>
       </c>
-      <c r="B183" s="11" t="n"/>
-      <c r="C183" s="11" t="n"/>
-      <c r="D183" s="12" t="n"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="4" t="n"/>
-      <c r="B184" s="4" t="inlineStr">
-        <is>
-          <t>Kava shared foundation</t>
-        </is>
-      </c>
-      <c r="C184" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D184" s="4" t="inlineStr">
-        <is>
-          <t>app/kava/layout.tsx + components/kava/kava-nav.tsx (KavaNav/KavaFooter, 10 real nav items) + components/kava/kava-ui.tsx (KavaHero/KavaSection/KavaSectionTitle/KavaCard/KavaBadge/KavaDivider/KavaDisclaimer, converted from legacy inline style={} to Tailwind + new --kava-* tokens in globals.css). Added /kava to site-chrome.tsx's SUPPRESSED_PREFIXES (self-contained sub-site, same pattern as BrewSoul and /attention-theft). Real dead link fixed: legacy nav pointed at /pri, which legacy's own App.tsx never routed (only /psychedelic-readiness-index exists) — corrected.</t>
-        </is>
-      </c>
-      <c r="E184" s="14" t="inlineStr">
-        <is>
-          <t>Phase 7 — PRI &amp; Kava Encyclopedias (19 routes)</t>
-        </is>
-      </c>
+      <c r="B184" s="11" t="n"/>
+      <c r="C184" s="11" t="n"/>
+      <c r="D184" s="12" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n"/>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>/kava (home)</t>
+          <t>Kava shared foundation</t>
         </is>
       </c>
       <c r="C185" s="13" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>9 module cards, "Threshold Doctrine," "Sacred Masculine Triad" (Mezcal/Kava/Peyote), 4 market stats, all ported unchanged. Verified live: 200 OK, exactly 1 header/1 footer (chrome suppression confirmed), typecheck/lint clean.</t>
+          <t>app/kava/layout.tsx + components/kava/kava-nav.tsx (KavaNav/KavaFooter, 10 real nav items) + components/kava/kava-ui.tsx (KavaHero/KavaSection/KavaSectionTitle/KavaCard/KavaBadge/KavaDivider/KavaDisclaimer, converted from legacy inline style={} to Tailwind + new --kava-* tokens in globals.css). Added /kava to site-chrome.tsx's SUPPRESSED_PREFIXES (self-contained sub-site, same pattern as BrewSoul and /attention-theft). Real dead link fixed: legacy nav pointed at /pri, which legacy's own App.tsx never routed (only /psychedelic-readiness-index exists) — corrected.</t>
         </is>
       </c>
       <c r="E185" s="14" t="inlineStr">
@@ -5180,7 +5180,7 @@
       <c r="A186" s="4" t="n"/>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>/kava/origins</t>
+          <t>/kava (home)</t>
         </is>
       </c>
       <c r="C186" s="13" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>real migration timeline (6 Pacific nations, ~3000 BCE–1000 CE), real 6-island selector (Vanuatu/Fiji/Tonga/Samoa/Hawaii/Pohnpei, each with real facts/ceremony/cultivar/safety content), and the real Noble vs. Tudei safety comparison, all ported unchanged and verbatim. Island-selector interactivity in components/kava/origins-explorer.tsx. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>9 module cards, "Threshold Doctrine," "Sacred Masculine Triad" (Mezcal/Kava/Peyote), 4 market stats, all ported unchanged. Verified live: 200 OK, exactly 1 header/1 footer (chrome suppression confirmed), typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E186" s="14" t="inlineStr">
@@ -5203,7 +5203,7 @@
       <c r="A187" s="4" t="n"/>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>/kava/interactions</t>
+          <t>/kava/origins</t>
         </is>
       </c>
       <c r="C187" s="13" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>real 24-substance drug interaction database (real severity ratings across an 11-value scale, real pharmacological mechanisms, real PRI protocol guidance) and real 5-enzyme CYP450 inhibition profile, ported unchanged and verbatim. Search + severity-filter interactivity in components/kava/interactions-explorer.tsx, using a precomposed SEVERITY_CONFIG class lookup (not string-built classes — same Tailwind static-scanner rule enforced elsewhere this migration). Legacy's unused Download icon import (dead code, no export feature attached to it) not ported. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>real migration timeline (6 Pacific nations, ~3000 BCE–1000 CE), real 6-island selector (Vanuatu/Fiji/Tonga/Samoa/Hawaii/Pohnpei, each with real facts/ceremony/cultivar/safety content), and the real Noble vs. Tudei safety comparison, all ported unchanged and verbatim. Island-selector interactivity in components/kava/origins-explorer.tsx. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E187" s="14" t="inlineStr">
@@ -5226,7 +5226,7 @@
       <c r="A188" s="4" t="n"/>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>/kava/science</t>
+          <t>/kava/interactions</t>
         </is>
       </c>
       <c r="C188" s="13" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>real 6 major kavalactones (real receptor mechanisms, real PRI relevance) and real 11-item combined pharmacological profile, ported unchanged into lib/content/kava-science.ts. RSC-boundary bug caught proactively before shipping: initially drafted KAVALACTONES as an export of the "use client" chemotype-decoder.tsx, which would have thrown the same TypeError: X is not iterable already hit once this migration on /brewsoul/decaf when the Server Component page tried to import it — moved to the plain data module before ever running it. Chemotype decoder tool (enter e.g. 4-2-6-5-3-1, see dominant kavalactones) kept as the real interactive client island. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>real 24-substance drug interaction database (real severity ratings across an 11-value scale, real pharmacological mechanisms, real PRI protocol guidance) and real 5-enzyme CYP450 inhibition profile, ported unchanged and verbatim. Search + severity-filter interactivity in components/kava/interactions-explorer.tsx, using a precomposed SEVERITY_CONFIG class lookup (not string-built classes — same Tailwind static-scanner rule enforced elsewhere this migration). Legacy's unused Download icon import (dead code, no export feature attached to it) not ported. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E188" s="14" t="inlineStr">
@@ -5249,7 +5249,7 @@
       <c r="A189" s="4" t="n"/>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>/kava/assessment</t>
+          <t>/kava/science</t>
         </is>
       </c>
       <c r="C189" s="13" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>real 5-domain, 20-question PRI readiness assessment (somatic/psychological/relational/cultural/integration), real per-domain point weights, and real 4-band recommendation scoring (CLEARED/CONDITIONAL/DEFER/NOT READY), all ported unchanged into components/kava/assessment-quiz.tsx. Fully stateful (domain navigation, per-question answers, results view), so kept as a single client island per this migration's established pattern for multi-step assessments. Domain and recommendation accent colors (5 + 4 distinct hexes, none matching the --kava-* brand palette) precomposed into literal DOMAIN_STYLES/RECOMMENDATION_STYLES lookup objects rather than style={}, avoiding the dynamic-class bug already caught twice this migration (chains-explorer.tsx, biodynamic/page.tsx). Real backend gap, handled honestly: legacy's AssessmentResultActions took sessionId/serialized-answers props feeding a trpc.assessments.submit mutation this migration never built — used the already-simplified, print-only AssessmentResultActions (components/assessments/result-actions.tsx, built during Phase 9) instead of reproducing a submit call with no backend. Verified live: 200 OK, real domain/question content confirmed in rendered HTML, typecheck/lint clean.</t>
+          <t>real 6 major kavalactones (real receptor mechanisms, real PRI relevance) and real 11-item combined pharmacological profile, ported unchanged into lib/content/kava-science.ts. RSC-boundary bug caught proactively before shipping: initially drafted KAVALACTONES as an export of the "use client" chemotype-decoder.tsx, which would have thrown the same TypeError: X is not iterable already hit once this migration on /brewsoul/decaf when the Server Component page tried to import it — moved to the plain data module before ever running it. Chemotype decoder tool (enter e.g. 4-2-6-5-3-1, see dominant kavalactones) kept as the real interactive client island. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E189" s="14" t="inlineStr">
@@ -5272,7 +5272,7 @@
       <c r="A190" s="4" t="n"/>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>/kava/hawaii</t>
+          <t>/kava/assessment</t>
         </is>
       </c>
       <c r="C190" s="13" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>real ICE/meth crisis statistics (Quest Diagnostics 410% figure, Hawaii DOH conviction rates, law enforcement seizure data), real dual crisis/revival timeline (1985–present), the real (explicitly-labeled hypothesis, not proven) pharmacological alignment table, and real recovery resource listings, all ported unchanged and verbatim. Fully static, no client island needed. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>real 5-domain, 20-question PRI readiness assessment (somatic/psychological/relational/cultural/integration), real per-domain point weights, and real 4-band recommendation scoring (CLEARED/CONDITIONAL/DEFER/NOT READY), all ported unchanged into components/kava/assessment-quiz.tsx. Fully stateful (domain navigation, per-question answers, results view), so kept as a single client island per this migration's established pattern for multi-step assessments. Domain and recommendation accent colors (5 + 4 distinct hexes, none matching the --kava-* brand palette) precomposed into literal DOMAIN_STYLES/RECOMMENDATION_STYLES lookup objects rather than style={}, avoiding the dynamic-class bug already caught twice this migration (chains-explorer.tsx, biodynamic/page.tsx). Real backend gap, handled honestly: legacy's AssessmentResultActions took sessionId/serialized-answers props feeding a trpc.assessments.submit mutation this migration never built — used the already-simplified, print-only AssessmentResultActions (components/assessments/result-actions.tsx, built during Phase 9) instead of reproducing a submit call with no backend. Verified live: 200 OK, real domain/question content confirmed in rendered HTML, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E190" s="14" t="inlineStr">
@@ -5295,7 +5295,7 @@
       <c r="A191" s="4" t="n"/>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>/kava/myths</t>
+          <t>/kava/hawaii</t>
         </is>
       </c>
       <c r="C191" s="13" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>real 7-myth evidence review (2002/2014 European kava ban and reversal, WHO findings, CYP2D6 metabolism differences by population, chemotype/preparation distinctions) and the real closing takeaway, ported unchanged. Expand/collapse interactivity in components/kava/myths-explorer.tsx, verdict colors (3-value enum) precomposed into a literal VERDICT_CLASS lookup. Extended shared KavaCard (kava-ui.tsx) with an optional onClick prop to support this — first Kava page needing a clickable card. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>real ICE/meth crisis statistics (Quest Diagnostics 410% figure, Hawaii DOH conviction rates, law enforcement seizure data), real dual crisis/revival timeline (1985–present), the real (explicitly-labeled hypothesis, not proven) pharmacological alignment table, and real recovery resource listings, all ported unchanged and verbatim. Fully static, no client island needed. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E191" s="14" t="inlineStr">
@@ -5318,7 +5318,7 @@
       <c r="A192" s="4" t="n"/>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>/kava/caffeine</t>
+          <t>/kava/myths</t>
         </is>
       </c>
       <c r="C192" s="13" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>real CYP1A2 inhibition mechanism (56%, the same pathway grapefruit juice uses on medications), real caffeine cutoff protocol, and the real kava-vs-coffee comparison table, ported unchanged. Fully static, no client island needed. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>real 7-myth evidence review (2002/2014 European kava ban and reversal, WHO findings, CYP2D6 metabolism differences by population, chemotype/preparation distinctions) and the real closing takeaway, ported unchanged. Expand/collapse interactivity in components/kava/myths-explorer.tsx, verdict colors (3-value enum) precomposed into a literal VERDICT_CLASS lookup. Extended shared KavaCard (kava-ui.tsx) with an optional onClick prop to support this — first Kava page needing a clickable card. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E192" s="14" t="inlineStr">
@@ -5341,7 +5341,7 @@
       <c r="A193" s="4" t="n"/>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>/kava/products</t>
+          <t>/kava/caffeine</t>
         </is>
       </c>
       <c r="C193" s="13" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>real 5-category product index (ceremonial powder, fresh frozen, RTD beverages, supplements, kava bars) with real named vendors/cultivars/chemotypes/pricing/PRI ratings and real outbound buy links (all live vendor domains, not Manus proxies — no image assets on this page to check), ported unchanged into components/kava/products-explorer.tsx. Category-tab interactivity kept as the client island. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>real CYP1A2 inhibition mechanism (56%, the same pathway grapefruit juice uses on medications), real caffeine cutoff protocol, and the real kava-vs-coffee comparison table, ported unchanged. Fully static, no client island needed. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E193" s="14" t="inlineStr">
@@ -5364,7 +5364,7 @@
       <c r="A194" s="4" t="n"/>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>/kava/certification</t>
+          <t>/kava/products</t>
         </is>
       </c>
       <c r="C194" s="13" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>real 12-module, 80-hour facilitator curriculum, real 3-tier certification structure (Practitioner/Threshold Facilitator/Master Facilitator), and real prerequisites list, ported unchanged. Fully static, no client island needed; legacy's wouter cross-links replaced with next/link. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>real 5-category product index (ceremonial powder, fresh frozen, RTD beverages, supplements, kava bars) with real named vendors/cultivars/chemotypes/pricing/PRI ratings and real outbound buy links (all live vendor domains, not Manus proxies — no image assets on this page to check), ported unchanged into components/kava/products-explorer.tsx. Category-tab interactivity kept as the client island. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E194" s="14" t="inlineStr">
@@ -5387,7 +5387,7 @@
       <c r="A195" s="4" t="n"/>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>PRI shared data: lib/content/pri-data.ts (copied verbatim from legacy pri/data.ts</t>
+          <t>/kava/certification</t>
         </is>
       </c>
       <c r="C195" s="13" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>real 39-medicine pharmacopoeia, 50+ questions across 6 domains, MAO-B interaction matrix, medication interaction guide, crisis/integration resources, pathway questions), lib/content/pri-safety-data.ts (verbatim safety data merge source), lib/content/pri-medicine-images.ts (verbatim real CloudFront hero-image map, all spot-checked 200 OK — RampRate's own CDN, already whitelisted, not Manus), lib/content/pri-shared.ts (the real scoring engine — computeScores/READINESS_LEVELS/getMedicineWithSafety — extracted to a plain module per the RSC-boundary lesson from /brewsoul/decaf and /kava/science). Added --pri-* CSS custom properties to globals.css (this subsystem's own purple/parchment/near-black palette, same pattern as --kava-/--crusade-) since Phase 7's PRI section spans 9 more routes.</t>
+          <t>real 12-module, 80-hour facilitator curriculum, real 3-tier certification structure (Practitioner/Threshold Facilitator/Master Facilitator), and real prerequisites list, ported unchanged. Fully static, no client island needed; legacy's wouter cross-links replaced with next/link. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E195" s="14" t="inlineStr">
@@ -5410,7 +5410,7 @@
       <c r="A196" s="4" t="n"/>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>/psychedelic-readiness-index (core tool)</t>
+          <t>PRI shared data: lib/content/pri-data.ts (copied verbatim from legacy pri/data.ts</t>
         </is>
       </c>
       <c r="C196" s="13" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>the real hero, 39-medicine grid with compare/save/bookmark tooling, MAO-B interaction matrix, medication interaction guide, crisis resources, the real 5-state assessment flow (philosophy intro → readiness quiz → pathway &amp; access questions → legal disclaimer gate → results), medicine detail modal (overview/safety/correction tabs), testimonials, and ImpactSoul cross-promotion, all ported unchanged and verbatim into components/pri/psychedelic-readiness-index.tsx plus supporting client islands (disclaimer-gate.tsx, medicine-modal.tsx, safety-section.tsx, correction-form.tsx, share-bar.tsx, cinematic-band.tsx). Kept as one client island — a single state machine drives which section renders, same call made for other large multi-step assessments this migration. Real hero/section photography (8 CloudFront images) kept via next/image; legacy's purely decorative glitch-scanline overlay divs and CSS shimmer/glow @keyframes dropped (no framer-motion — CONTRIBUTING.md rule 5 — and "decoration not worth the cost," same call made throughout this migration).</t>
+          <t>real 39-medicine pharmacopoeia, 50+ questions across 6 domains, MAO-B interaction matrix, medication interaction guide, crisis/integration resources, pathway questions), lib/content/pri-safety-data.ts (verbatim safety data merge source), lib/content/pri-medicine-images.ts (verbatim real CloudFront hero-image map, all spot-checked 200 OK — RampRate's own CDN, already whitelisted, not Manus), lib/content/pri-shared.ts (the real scoring engine — computeScores/READINESS_LEVELS/getMedicineWithSafety — extracted to a plain module per the RSC-boundary lesson from /brewsoul/decaf and /kava/science). Added --pri-* CSS custom properties to globals.css (this subsystem's own purple/parchment/near-black palette, same pattern as --kava-/--crusade-) since Phase 7's PRI section spans 9 more routes.</t>
         </is>
       </c>
       <c r="E196" s="14" t="inlineStr">
@@ -5433,7 +5433,7 @@
       <c r="A197" s="4" t="n"/>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>PRI: /peyote-mescaline</t>
+          <t>/psychedelic-readiness-index (core tool)</t>
         </is>
       </c>
       <c r="C197" s="13" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>MescalineDeepDive, real receptor pharmacology table, the real "Latuda Mirror" same-target-opposite-action comparison, real clinical outcomes (Agin-Liebes et al. 2021, n=452), the real 16-row pharma-to-plant alternatives table, real supplement protocol (pre/day-of/post-integration), real mescaline-specific PRI dimension scores, the real medicine-selector comparison table, and real sources, all ported unchanged and verbatim into lib/content/pri-mescaline-module.ts (copied verbatim) + app/peyote-mescaline/page.tsx. Fully static except the pharma-table expand toggle, extracted into components/pri/pharma-table.tsx; shared PriSection/PriEyebrow wrapper (components/pri/pri-section.tsx) introduced here for reuse by the remaining PRI deep-dive modules. All 8 real section photos (CloudFront) spot-checked live before use; legacy's purely decorative glitch-scanline overlays dropped. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
+          <t>the real hero, 39-medicine grid with compare/save/bookmark tooling, MAO-B interaction matrix, medication interaction guide, crisis resources, the real 5-state assessment flow (philosophy intro → readiness quiz → pathway &amp; access questions → legal disclaimer gate → results), medicine detail modal (overview/safety/correction tabs), testimonials, and ImpactSoul cross-promotion, all ported unchanged and verbatim into components/pri/psychedelic-readiness-index.tsx plus supporting client islands (disclaimer-gate.tsx, medicine-modal.tsx, safety-section.tsx, correction-form.tsx, share-bar.tsx, cinematic-band.tsx). Kept as one client island — a single state machine drives which section renders, same call made for other large multi-step assessments this migration. Real hero/section photography (8 CloudFront images) kept via next/image; legacy's purely decorative glitch-scanline overlay divs and CSS shimmer/glow @keyframes dropped (no framer-motion — CONTRIBUTING.md rule 5 — and "decoration not worth the cost," same call made throughout this migration).</t>
         </is>
       </c>
       <c r="E197" s="14" t="inlineStr">
@@ -5456,7 +5456,7 @@
       <c r="A198" s="4" t="n"/>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>PRI: /iboga-ibogaine</t>
+          <t>PRI: /peyote-mescaline</t>
         </is>
       </c>
       <c r="C198" s="13" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>IbogaDeepDive, "The Plant vs The Isolate": real alkaloid-profile comparison, real receptor pharmacology, real head-to-head iboga-vs-ibogaine table, real clinical outcomes (Mash/Noller/Schenberg/Brown &amp; Alper/Cherian/Williams — including the 2024 Stanford Nature Medicine SOF-veteran data and the 2026 19,071-patient safety analysis), real pharma-to-plant alternatives, real supplement protocol, real dimension thresholds, real medicine selector, Tony's real first-hand account of sitting ibogaine at The Mission Within, real hard-stop contraindications, a real 9-facility directory (with the 2 facilities legacy explicitly removed and why), real Nagoya Protocol / extractive-capitalism argument, real 2026 US legal-status rundown, the embedded Iboga Compass v2 documentation section (components/pri/iboga-compass-section.tsx, its own client island for the question-group toggles), and real sources — all ported unchanged and verbatim into lib/content/pri-iboga-module.ts + lib/content/pri-iboga-compass-data.ts (both copied verbatim) + app/iboga-ibogaine/page.tsx. Fully static except the pharma-table expand toggle (components/pri/iboga-pharma-table.tsx) and the compass section's toggles; reused the shared PriSection/PriEyebrow wrapper from the mescaline module. All 5 real hero/section photos (CloudFront) spot-checked live before use. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
+          <t>MescalineDeepDive, real receptor pharmacology table, the real "Latuda Mirror" same-target-opposite-action comparison, real clinical outcomes (Agin-Liebes et al. 2021, n=452), the real 16-row pharma-to-plant alternatives table, real supplement protocol (pre/day-of/post-integration), real mescaline-specific PRI dimension scores, the real medicine-selector comparison table, and real sources, all ported unchanged and verbatim into lib/content/pri-mescaline-module.ts (copied verbatim) + app/peyote-mescaline/page.tsx. Fully static except the pharma-table expand toggle, extracted into components/pri/pharma-table.tsx; shared PriSection/PriEyebrow wrapper (components/pri/pri-section.tsx) introduced here for reuse by the remaining PRI deep-dive modules. All 8 real section photos (CloudFront) spot-checked live before use; legacy's purely decorative glitch-scanline overlays dropped. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E198" s="14" t="inlineStr">
@@ -5479,7 +5479,7 @@
       <c r="A199" s="4" t="n"/>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>PRI: /iboga-compass</t>
+          <t>PRI: /iboga-ibogaine</t>
         </is>
       </c>
       <c r="C199" s="13" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>IbogaCompassAssessment, the real interactive 28-question / 7-section compass (outcome/medical/approach/logistics/geography/personal/aftercare), the real drag-or-arrow priority-rank step (top dimension ×2.0, bottom ×0.5), the real facility-scoring engine, and the real results view (matched facilities with real "why this matched" reasoning and real elimination reasons), all ported unchanged and verbatim. lib/content/pri-iboga-compass-engine.ts (real scoring logic — weight deltas, hard filters, substance bonuses, priority-rank application, facility scoring) and lib/content/pri-iboga-facility-data.ts (real facility directory + substance-bonus data) both copied verbatim from legacy rather than hand-transcribed, given this is the actual matching algorithm — correctness matters more here than anywhere else in this migration. Uses this site's own brand-gold/foreground/muted-foreground design tokens rather than the pri-* palette — legacy's own hex here (#8B6914) is an exact match for brand-gold, confirming this one page always used the main site identity, not a PRI-specific one. Real backend gap handled honestly: legacy's lead-capture gate posted a rich structured payload (question-by-question answers, top facility matches, primary goal, budget range) to trpc.assessments.submit (no backend built for this migration) — replaced with a mailto: to Tony carrying the same structured summary, same pattern used throughout this migration; the meaningless "Submitting..." pending state and its e</t>
+          <t>IbogaDeepDive, "The Plant vs The Isolate": real alkaloid-profile comparison, real receptor pharmacology, real head-to-head iboga-vs-ibogaine table, real clinical outcomes (Mash/Noller/Schenberg/Brown &amp; Alper/Cherian/Williams — including the 2024 Stanford Nature Medicine SOF-veteran data and the 2026 19,071-patient safety analysis), real pharma-to-plant alternatives, real supplement protocol, real dimension thresholds, real medicine selector, Tony's real first-hand account of sitting ibogaine at The Mission Within, real hard-stop contraindications, a real 9-facility directory (with the 2 facilities legacy explicitly removed and why), real Nagoya Protocol / extractive-capitalism argument, real 2026 US legal-status rundown, the embedded Iboga Compass v2 documentation section (components/pri/iboga-compass-section.tsx, its own client island for the question-group toggles), and real sources — all ported unchanged and verbatim into lib/content/pri-iboga-module.ts + lib/content/pri-iboga-compass-data.ts (both copied verbatim) + app/iboga-ibogaine/page.tsx. Fully static except the pharma-table expand toggle (components/pri/iboga-pharma-table.tsx) and the compass section's toggles; reused the shared PriSection/PriEyebrow wrapper from the mescaline module. All 5 real hero/section photos (CloudFront) spot-checked live before use. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E199" s="14" t="inlineStr">
@@ -5502,7 +5502,7 @@
       <c r="A200" s="4" t="n"/>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>PRI: /pri-calibration</t>
+          <t>PRI: /iboga-compass</t>
         </is>
       </c>
       <c r="C200" s="13" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>forced-rank calibration study, the real Bradley-Terry pairwise-comparison model (all 15 unique pairs of the 6 PRI dimensions), the real drag-or-arrow full ranking step, real methodology copy (acquiescence-bias explanation, the 4 headline validation stats), and the real Monte Carlo validation metrics (lib/content/pri-efficacy-data.json, copied verbatim from legacy — also feeds /pri-efficacy below), all ported unchanged into components/pri/calibration-assessment.tsx. Real backend gap, handled honestly: legacy's "Contribute to Research?" opt-in phase posted to trpc.priCalibration.submit (no backend built for this migration), and the results view's "Community Data" section read a live trpc.priCalibration.stats aggregate query showing other users' scores — neither has an honest backend-free equivalent (a cross-user aggregate can't be faked locally, and a research opt-in toggle with nothing behind it would be dishonest UI, the same call already made dropping the main PRI results page's inert research-pool checkbox). Both dropped; the flow goes straight from ranking to results. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
+          <t>IbogaCompassAssessment, the real interactive 28-question / 7-section compass (outcome/medical/approach/logistics/geography/personal/aftercare), the real drag-or-arrow priority-rank step (top dimension ×2.0, bottom ×0.5), the real facility-scoring engine, and the real results view (matched facilities with real "why this matched" reasoning and real elimination reasons), all ported unchanged and verbatim. lib/content/pri-iboga-compass-engine.ts (real scoring logic — weight deltas, hard filters, substance bonuses, priority-rank application, facility scoring) and lib/content/pri-iboga-facility-data.ts (real facility directory + substance-bonus data) both copied verbatim from legacy rather than hand-transcribed, given this is the actual matching algorithm — correctness matters more here than anywhere else in this migration. Uses this site's own brand-gold/foreground/muted-foreground design tokens rather than the pri-* palette — legacy's own hex here (#8B6914) is an exact match for brand-gold, confirming this one page always used the main site identity, not a PRI-specific one. Real backend gap handled honestly: legacy's lead-capture gate posted a rich structured payload (question-by-question answers, top facility matches, primary goal, budget range) to trpc.assessments.submit (no backend built for this migration) — replaced with a mailto: to Tony carrying the same structured summary, same pattern used throughout this migration; the meaningless "Submitting..." pending state and its e</t>
         </is>
       </c>
       <c r="E200" s="14" t="inlineStr">
@@ -5525,7 +5525,7 @@
       <c r="A201" s="4" t="n"/>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>PRI: /pri-efficacy</t>
+          <t>PRI: /pri-calibration</t>
         </is>
       </c>
       <c r="C201" s="13" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>psychometric validation dashboard, the real Monte Carlo simulation results (10,000 synthetic respondents), real classification-accuracy comparison, real dimension-priority distribution (the real first-dimension-inflation finding), real test-retest reliability and entropy metrics, and the real methodology writeup, all ported unchanged into app/pri-efficacy/page.tsx, reading the same lib/content/pri-efficacy-data.json also used by /pri-calibration. Real backend gap, handled honestly: legacy's "Live Calibrations" tab read a live trpc.priCalibration.stats query — since /pri-calibration's own submit call was already dropped (no backend, see that page's port note), this tab would permanently render "0 total calibrations, no data yet," a dead feature masquerading as a live one. Dropped entirely rather than ship a perpetually-empty tab; only the real, fully-populated Simulation view ships — which also means this page has no state left at all, so it's a plain Server Component now instead of a client one. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
+          <t>forced-rank calibration study, the real Bradley-Terry pairwise-comparison model (all 15 unique pairs of the 6 PRI dimensions), the real drag-or-arrow full ranking step, real methodology copy (acquiescence-bias explanation, the 4 headline validation stats), and the real Monte Carlo validation metrics (lib/content/pri-efficacy-data.json, copied verbatim from legacy — also feeds /pri-efficacy below), all ported unchanged into components/pri/calibration-assessment.tsx. Real backend gap, handled honestly: legacy's "Contribute to Research?" opt-in phase posted to trpc.priCalibration.submit (no backend built for this migration), and the results view's "Community Data" section read a live trpc.priCalibration.stats aggregate query showing other users' scores — neither has an honest backend-free equivalent (a cross-user aggregate can't be faked locally, and a research opt-in toggle with nothing behind it would be dishonest UI, the same call already made dropping the main PRI results page's inert research-pool checkbox). Both dropped; the flow goes straight from ranking to results. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E201" s="14" t="inlineStr">
@@ -5548,7 +5548,7 @@
       <c r="A202" s="4" t="n"/>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>PRI: /pri-research Built 2026-10-06 behind the login: admins are the emails in ADMIN_EMAILS; everyone else gets live's "Access Denied"</t>
+          <t>PRI: /pri-efficacy</t>
         </is>
       </c>
       <c r="C202" s="13" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Totals, anonymized opt-in table, admin-only CSV export (/pri-research/export). /pri-calibration regained legacy's "Contribute to Research?" step and now saves every calibration anonymously to pri_calibrations (opt-ins flagged). Was: — Deferred, not skipped (access-model question resolved by inspection). Read the real legacy source: this is a genuine admin-only dashboard (useAuth() gated to role === "admin") showing trpc.priCalibration.researchData — the same calibration-submission backend already confirmed absent and intentionally not built for /pri-calibration and /pri-efficacy (see their port notes). No admin-auth system exists anywhere in this Next.js migration yet either. So this isn't just an access-control decision — even fully wired up, the page would have zero real data to show, forever. Not worth building an admin dashboard against a backend this migration has twice already decided not to build. Added to "Explicitly deferred" below alongside the other admin dashboards; revisit only if/when both a real admin-auth system and a real calibration-submission backend exist.</t>
+          <t>psychometric validation dashboard, the real Monte Carlo simulation results (10,000 synthetic respondents), real classification-accuracy comparison, real dimension-priority distribution (the real first-dimension-inflation finding), real test-retest reliability and entropy metrics, and the real methodology writeup, all ported unchanged into app/pri-efficacy/page.tsx, reading the same lib/content/pri-efficacy-data.json also used by /pri-calibration. Real backend gap, handled honestly: legacy's "Live Calibrations" tab read a live trpc.priCalibration.stats query — since /pri-calibration's own submit call was already dropped (no backend, see that page's port note), this tab would permanently render "0 total calibrations, no data yet," a dead feature masquerading as a live one. Dropped entirely rather than ship a perpetually-empty tab; only the real, fully-populated Simulation view ships — which also means this page has no state left at all, so it's a plain Server Component now instead of a client one. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E202" s="14" t="inlineStr">
@@ -5571,7 +5571,7 @@
       <c r="A203" s="4" t="n"/>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>PRI: /facilitator-index</t>
+          <t>PRI: /pri-research Built 2026-10-06 behind the login: admins are the emails in ADMIN_EMAILS; everyone else gets live's "Access Denied"</t>
         </is>
       </c>
       <c r="C203" s="13" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>"The Facilitator Index: Know Who You Go With," the real 15-question quick-intake archetype quiz (real Bradley-Terry-style axis derivation, fully client-computed via deriveArchetype()), the real 108-item, 12-band (plus Band 0) practitioner self-assessment instrument, and the real methodology prose (rationale, code/tier system, data-handling policy, Reciprocity Gate, Corroboration token system), all ported unchanged and verbatim into lib/content/facilitator-index-data.ts (single authoritative content source) + components/facilitator/* + app/facilitator-index/page.tsx. Real content-drift bug found and fixed: legacy shipped two divergent copies of the same "108 items" — the on-page JSX and a separate printFacilitatorQuestions() print/PDF export using an older, different set of item numbers and band groupings (missing the on-page "Twenty-Five Traditions and Protocols" band entirely) — the print export was never updated when the on-page instrument was revised. Used the on-page version (the one actually shown to visitors) as the single source of truth and rebuilt the print export to generate from that same data, so the two can never diverge again. Real fake-data found and dropped: legacy's PeerStats component's own comment admits its numbers ("163 practitioners mapped so far," etc.) are "seeded, realistic-feeling" — fabricated, not real — dropped entirely, same principle as BrewSoul's stale "reads" counts; UsageCounter's hardcoded 160-practitioner fallback (shown forever since no ba</t>
+          <t>Totals, anonymized opt-in table, admin-only CSV export (/pri-research/export). /pri-calibration regained legacy's "Contribute to Research?" step and now saves every calibration anonymously to pri_calibrations (opt-ins flagged). Was: — Deferred, not skipped (access-model question resolved by inspection). Read the real legacy source: this is a genuine admin-only dashboard (useAuth() gated to role === "admin") showing trpc.priCalibration.researchData — the same calibration-submission backend already confirmed absent and intentionally not built for /pri-calibration and /pri-efficacy (see their port notes). No admin-auth system exists anywhere in this Next.js migration yet either. So this isn't just an access-control decision — even fully wired up, the page would have zero real data to show, forever. Not worth building an admin dashboard against a backend this migration has twice already decided not to build. Added to "Explicitly deferred" below alongside the other admin dashboards; revisit only if/when both a real admin-auth system and a real calibration-submission backend exist.</t>
         </is>
       </c>
       <c r="E203" s="14" t="inlineStr">
@@ -5594,63 +5594,63 @@
       <c r="A204" s="4" t="n"/>
       <c r="B204" s="4" t="inlineStr">
         <is>
+          <t>PRI: /facilitator-index</t>
+        </is>
+      </c>
+      <c r="C204" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D204" s="4" t="inlineStr">
+        <is>
+          <t>"The Facilitator Index: Know Who You Go With," the real 15-question quick-intake archetype quiz (real Bradley-Terry-style axis derivation, fully client-computed via deriveArchetype()), the real 108-item, 12-band (plus Band 0) practitioner self-assessment instrument, and the real methodology prose (rationale, code/tier system, data-handling policy, Reciprocity Gate, Corroboration token system), all ported unchanged and verbatim into lib/content/facilitator-index-data.ts (single authoritative content source) + components/facilitator/* + app/facilitator-index/page.tsx. Real content-drift bug found and fixed: legacy shipped two divergent copies of the same "108 items" — the on-page JSX and a separate printFacilitatorQuestions() print/PDF export using an older, different set of item numbers and band groupings (missing the on-page "Twenty-Five Traditions and Protocols" band entirely) — the print export was never updated when the on-page instrument was revised. Used the on-page version (the one actually shown to visitors) as the single source of truth and rebuilt the print export to generate from that same data, so the two can never diverge again. Real fake-data found and dropped: legacy's PeerStats component's own comment admits its numbers ("163 practitioners mapped so far," etc.) are "seeded, realistic-feeling" — fabricated, not real — dropped entirely, same principle as BrewSoul's stale "reads" counts; UsageCounter's hardcoded 160-practitioner fallback (shown forever since no ba</t>
+        </is>
+      </c>
+      <c r="E204" s="14" t="inlineStr">
+        <is>
+          <t>Phase 7 — PRI &amp; Kava Encyclopedias (19 routes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="n"/>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
           <t>Port shared safety/medicine data modules (safety-data.ts, medicine-images.ts) as typed .ts content in the new codebase</t>
         </is>
       </c>
-      <c r="C204" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D204" s="4" t="inlineStr">
+      <c r="C205" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr">
         <is>
           <t>done as part of the main PRI page above (lib/content/pri-safety-data.ts, lib/content/pri-medicine-images.ts, both copied verbatim).</t>
         </is>
       </c>
-      <c r="E204" s="14" t="inlineStr">
+      <c r="E205" s="14" t="inlineStr">
         <is>
           <t>Phase 7 — PRI &amp; Kava Encyclopedias (19 routes)</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="10" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="10" t="inlineStr">
         <is>
           <t>Phase 8 — Attention Theft Manifesto (7 routes)</t>
         </is>
       </c>
-      <c r="B205" s="11" t="n"/>
-      <c r="C205" s="11" t="n"/>
-      <c r="D205" s="12" t="n"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="4" t="n"/>
-      <c r="B206" s="4" t="inlineStr">
-        <is>
-          <t>/attention-theft</t>
-        </is>
-      </c>
-      <c r="C206" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D206" s="4" t="inlineStr">
-        <is>
-          <t>consolidated mega-page. Real content ported in full across all 9 sections (hero, The Sacred, The Heresy economics data + full breakdown table + sources, the 10 Weapons, Legal Arsenal w/ filter + letter template, AI Blocker Finder quiz, Report a Spammer, closing vow + related reading) — AttentionTheft.tsx used as the single source, the 5 pre-consolidation sub-pages not resurrected (they never existed in this codebase anyway). Section "glamour" photography is real, live imagery on RampRate's own CloudFront (already whitelisted in next.config.ts as a non-Manus, permanent host — confirmed all 7 URLs 200 before using them), rendered via next/image. Real backend gap found and handled honestly: legacy's Wall of Shame (a live trpc.spam.wallOfShame ranked list) and the Report form's trpc.spam.submit both depended on a spam-tracking backend that this migration explicitly defers (see "Explicitly deferred" list below: "/youve-been-reported, /spamtoast, admin spam tooling") — rather than fake a public database with no real data behind it, the report form now composes a mailto: to Tony (same honest non-fake-success pattern as newsletter-popup.tsx), and the ranked Wall of Shame list isn't reproduced. Two simplifications matching precedent set elsewhere in this migration: legacy's "Fraunces" serif (loaded for this one page only) was dropped for font-heading (Playfair Display, already loaded — same call made on /akbar), and the glitch/VHS/ember-particle/shattered-glass decoration layer was dr</t>
-        </is>
-      </c>
-      <c r="E206" s="14" t="inlineStr">
-        <is>
-          <t>Phase 8 — Attention Theft Manifesto (7 routes)</t>
-        </is>
-      </c>
+      <c r="B206" s="11" t="n"/>
+      <c r="C206" s="11" t="n"/>
+      <c r="D206" s="12" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="n"/>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Legacy anchor redirects</t>
+          <t>/attention-theft</t>
         </is>
       </c>
       <c r="C207" s="13" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>/attention-theft/economics, /blocker-finder, /legal, /weapons, /report → /attention-theft#&lt;anchor&gt; via next.config.ts redirects(). Verified live: all return real 308s to the correct anchor.</t>
+          <t>consolidated mega-page. Real content ported in full across all 9 sections (hero, The Sacred, The Heresy economics data + full breakdown table + sources, the 10 Weapons, Legal Arsenal w/ filter + letter template, AI Blocker Finder quiz, Report a Spammer, closing vow + related reading) — AttentionTheft.tsx used as the single source, the 5 pre-consolidation sub-pages not resurrected (they never existed in this codebase anyway). Section "glamour" photography is real, live imagery on RampRate's own CloudFront (already whitelisted in next.config.ts as a non-Manus, permanent host — confirmed all 7 URLs 200 before using them), rendered via next/image. Real backend gap found and handled honestly: legacy's Wall of Shame (a live trpc.spam.wallOfShame ranked list) and the Report form's trpc.spam.submit both depended on a spam-tracking backend that this migration explicitly defers (see "Explicitly deferred" list below: "/youve-been-reported, /spamtoast, admin spam tooling") — rather than fake a public database with no real data behind it, the report form now composes a mailto: to Tony (same honest non-fake-success pattern as newsletter-popup.tsx), and the ranked Wall of Shame list isn't reproduced. Two simplifications matching precedent set elsewhere in this migration: legacy's "Fraunces" serif (loaded for this one page only) was dropped for font-heading (Playfair Display, already loaded — same call made on /akbar), and the glitch/VHS/ember-particle/shattered-glass decoration layer was dr</t>
         </is>
       </c>
       <c r="E207" s="14" t="inlineStr">
@@ -5673,63 +5673,63 @@
       <c r="A208" s="4" t="n"/>
       <c r="B208" s="4" t="inlineStr">
         <is>
+          <t>Legacy anchor redirects</t>
+        </is>
+      </c>
+      <c r="C208" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D208" s="4" t="inlineStr">
+        <is>
+          <t>/attention-theft/economics, /blocker-finder, /legal, /weapons, /report → /attention-theft#&lt;anchor&gt; via next.config.ts redirects(). Verified live: all return real 308s to the correct anchor.</t>
+        </is>
+      </c>
+      <c r="E208" s="14" t="inlineStr">
+        <is>
+          <t>Phase 8 — Attention Theft Manifesto (7 routes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="n"/>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
           <t>Port ManifestoLayout scroll-tracking wrapper behavior</t>
         </is>
       </c>
-      <c r="C208" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D208" s="4" t="inlineStr">
+      <c r="C209" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="inlineStr">
         <is>
           <t>components/manifesto/manifesto-nav.tsx tracks which section is in view on scroll and highlights the matching nav pill (desktop + mobile), real behavior kept per this line item rather than simplified away.</t>
         </is>
       </c>
-      <c r="E208" s="14" t="inlineStr">
+      <c r="E209" s="14" t="inlineStr">
         <is>
           <t>Phase 8 — Attention Theft Manifesto (7 routes)</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="10" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="10" t="inlineStr">
         <is>
           <t>Phase 9 — Assessments (33 routes)</t>
         </is>
       </c>
-      <c r="B209" s="11" t="n"/>
-      <c r="C209" s="11" t="n"/>
-      <c r="D209" s="12" t="n"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="4" t="n"/>
-      <c r="B210" s="4" t="inlineStr">
-        <is>
-          <t>HumanOS section</t>
-        </is>
-      </c>
-      <c r="C210" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D210" s="4" t="inlineStr">
-        <is>
-          <t>/humanos, /humanos/philosophy, /humanos/ecosystem, /humanos/resources, /humanos/connect, /humanos/path-to-here, ported from _legacy-manus-app/client/src/pages/HumanOS.tsx + humanos/*.tsx. The top-level HumanOS.tsx (an iframe embed of an external manus.space site) turned out to be dead code, never wired into legacy's router — the real, routed implementation is HumanosHome/HumanosPhilosophy/HumanosEcosystem/HumanosResources/HumanosConnect/HumanosPathToHere behind HumanosLayout, which is what got ported, with its own nested layout.tsx (route now added to site-chrome.tsx's SUPPRESSED_PREFIXES so the main SiteHeader/SiteFooter don't double up around HumanOS's own nav/footer). Real content in full: the Maximizer-vs-Satisficer framework and "Boiling the Human"/"Maximizer Trap"/"Conscious Satisficer" philosophy sections, the full ecosystem roster (1 mentor, 8 advisors, 3 partners, 29 clients), all 4 transformation playbooks + 3 daily-practice protocols + 8-book reading list, all 4 connect channels, and the 6-entry "Path to Here" timeline (2010 H+ Summit through 2025). Real bugs fixed: every "Take the Diagnostic" CTA site-wide pointed at /assessment, an 8-question Maximizer/Satisficer quiz that was never actually built anywhere (legacy's real /assessment and /assessments routes are two different, unrelated quiz sets) — redirected to /humanos/philosophy, which delivers the actual promised content; Connect's "Read the Living Declaration" pointed at /manifesto, a dead redirect stub in le</t>
-        </is>
-      </c>
-      <c r="E210" s="14" t="inlineStr">
-        <is>
-          <t>Phase 9 — Assessments (33 routes)</t>
-        </is>
-      </c>
+      <c r="B210" s="11" t="n"/>
+      <c r="C210" s="11" t="n"/>
+      <c r="D210" s="12" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="4" t="n"/>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>/find-your-me (+ /find-my-me, /discover)</t>
+          <t>HumanOS section</t>
         </is>
       </c>
       <c r="C211" s="13" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>"Find My — To Find Your We," the ecosystem hub assessment and by far the largest page in Phase 9. Real 5 NLP-driven questions, 6 dimensions (relationships/purpose/body/truth/tribe/consciousness), and 6 real archetypes (each with a real description, real blog article links, real satellite-site links, real "go deeper" forward-references, and a real share text) ported unchanged and verbatim into a new lib/content/find-your-me.ts data module (kept separate from the component given the file's exceptional size, same pattern as brewsoul-directory.ts). All 17 unique blog article slugs referenced across the 6 archetypes were individually verified live (200 OK) against this migration's real Sanity blog before porting — zero dead article links. Real accuracy fix: legacy's "Full Ecosystem Directory" (26 items across 5 categories, with a real LIVE/COMING pill UI already built for exactly this purpose) marked everything "live," including several routes that don't exist anywhere in this migration yet (/find-my, /the-mirror, /assessments/dharma-finder, /assessments/consciousness-scale, /assessments/grant-study, /flow-circuit) — corrected each item's status to this app's actual current build state rather than shipping false LIVE labels on what would be 404s. Real completeness fix: added Find Your Peptide and Find Your Sexuality to the directory (Body &amp; Temple and Love &amp; Belonging) — both are real, fully-built assessments elsewhere in this migration that didn't exist yet when legacy was writte</t>
+          <t>/humanos, /humanos/philosophy, /humanos/ecosystem, /humanos/resources, /humanos/connect, /humanos/path-to-here, ported from _legacy-manus-app/client/src/pages/HumanOS.tsx + humanos/*.tsx. The top-level HumanOS.tsx (an iframe embed of an external manus.space site) turned out to be dead code, never wired into legacy's router — the real, routed implementation is HumanosHome/HumanosPhilosophy/HumanosEcosystem/HumanosResources/HumanosConnect/HumanosPathToHere behind HumanosLayout, which is what got ported, with its own nested layout.tsx (route now added to site-chrome.tsx's SUPPRESSED_PREFIXES so the main SiteHeader/SiteFooter don't double up around HumanOS's own nav/footer). Real content in full: the Maximizer-vs-Satisficer framework and "Boiling the Human"/"Maximizer Trap"/"Conscious Satisficer" philosophy sections, the full ecosystem roster (1 mentor, 8 advisors, 3 partners, 29 clients), all 4 transformation playbooks + 3 daily-practice protocols + 8-book reading list, all 4 connect channels, and the 6-entry "Path to Here" timeline (2010 H+ Summit through 2025). Real bugs fixed: every "Take the Diagnostic" CTA site-wide pointed at /assessment, an 8-question Maximizer/Satisficer quiz that was never actually built anywhere (legacy's real /assessment and /assessments routes are two different, unrelated quiz sets) — redirected to /humanos/philosophy, which delivers the actual promised content; Connect's "Read the Living Declaration" pointed at /manifesto, a dead redirect stub in le</t>
         </is>
       </c>
       <c r="E211" s="14" t="inlineStr">
@@ -5752,7 +5752,7 @@
       <c r="A212" s="4" t="n"/>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>/find-your-therapy (+ /find-my-therapy)</t>
+          <t>/find-your-me (+ /find-my-me, /discover)</t>
         </is>
       </c>
       <c r="C212" s="13" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real 25 questions across 6 dimensions (Cognitive/Somatic/Relational/Depth-Unconscious/Altered States/Integrative), 6 real therapeutic modalities (each with a real description, "how it works," best-for/not-ideal-for lists, real named pioneers, and real book/directory resources), and the real archetype-matching logic (highest-scoring dimension wins) ported unchanged and verbatim. Three real stale-count bugs found and fixed: legacy's own file-header comment claimed "10 questions," its AssessmentIntro stats prop claimed 20 — neither matches the real 25-item array (the scoring code's own maxPossible = 30 // rough max per dimension with 25 questions comment confirms 25 is correct) — replaced both with live QUESTIONS.length. Real dead-link bug fixed: legacy's "Journey Continues" grid linked "Find Your Spirit"/"Find Your Religion" to external findmyassess-9eekxcob.manus.space stub URLs (dead Manus domain) despite this migration already having real, fully-built internal pages at /find-your-spirit and /find-your-religion — repointed to the real internal routes, and corrected Religion's stale "15 Questions" badge to the real 20. Real accent-color inconsistency fixed: legacy passed accentColor="#7B1FA2" only to the landing screen, then hardcoded brand-gold everywhere on the results screen instead — threaded one ACCENT constant through intro/radar/result-actions consistently, matching every other assessment in this migration. The "Also Worth Exploring" related-modality cards were dropped </t>
+          <t>"Find My — To Find Your We," the ecosystem hub assessment and by far the largest page in Phase 9. Real 5 NLP-driven questions, 6 dimensions (relationships/purpose/body/truth/tribe/consciousness), and 6 real archetypes (each with a real description, real blog article links, real satellite-site links, real "go deeper" forward-references, and a real share text) ported unchanged and verbatim into a new lib/content/find-your-me.ts data module (kept separate from the component given the file's exceptional size, same pattern as brewsoul-directory.ts). All 17 unique blog article slugs referenced across the 6 archetypes were individually verified live (200 OK) against this migration's real Sanity blog before porting — zero dead article links. Real accuracy fix: legacy's "Full Ecosystem Directory" (26 items across 5 categories, with a real LIVE/COMING pill UI already built for exactly this purpose) marked everything "live," including several routes that don't exist anywhere in this migration yet (/find-my, /the-mirror, /assessments/dharma-finder, /assessments/consciousness-scale, /assessments/grant-study, /flow-circuit) — corrected each item's status to this app's actual current build state rather than shipping false LIVE labels on what would be 404s. Real completeness fix: added Find Your Peptide and Find Your Sexuality to the directory (Body &amp; Temple and Love &amp; Belonging) — both are real, fully-built assessments elsewhere in this migration that didn't exist yet when legacy was writte</t>
         </is>
       </c>
       <c r="E212" s="14" t="inlineStr">
@@ -5775,7 +5775,7 @@
       <c r="A213" s="4" t="n"/>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>/find-your-sake</t>
+          <t>/find-your-therapy (+ /find-my-therapy)</t>
         </is>
       </c>
       <c r="C213" s="13" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>Real 20 questions across 5 dimensions (Palate/Ritual/Terroir/Philosophy/Season) and the real 5 sake profiles (each with real Japanese name, tasting notes, food pairings, serving temperature, named producers with region/note, and further-reading resources) ported unchanged and verbatim. Legacy's own AssessmentIntro stats prop claimed "15 questions, 6 dimensions" — didn't match the real 20/5 implementation — replaced with live QUESTIONS.length/DIMENSIONS.length counts, same fix pattern already applied on /find-your-attachment-style and /find-your-sexuality. Two real bugs found and fixed: (1) legacy's "Journey Continues" list read "Find Myzcal" — a literal typo for "Find Your Mezcal" — corrected. (2) legacy's JSX rendered &lt;WhatsNext /&gt; (a full page section) nested inside the small "Retake the Tasting" &lt;button&gt; element — moved to a proper top-level section, same class of nested-interactive-content bug already fixed on /find-your-religion. The dark GlassPanel treatment (near-black translucent cards with light cream text, sitting on the page's own light parchment ThemedBackground) was kept as a real, intentional design choice rather than "fixed" to this migration's usual light-card convention — unlike the light-text-directly-on-light-background contrast bugs found on Style/Sexuality/Peptide/Religion, the text here sits inside its own correctly-contrasted dark card. SacredGeometryBg's canvas-based floating rice-grain particles dropped (same decoration-not-worth-the-JS-cost call made</t>
+          <t xml:space="preserve">Real 25 questions across 6 dimensions (Cognitive/Somatic/Relational/Depth-Unconscious/Altered States/Integrative), 6 real therapeutic modalities (each with a real description, "how it works," best-for/not-ideal-for lists, real named pioneers, and real book/directory resources), and the real archetype-matching logic (highest-scoring dimension wins) ported unchanged and verbatim. Three real stale-count bugs found and fixed: legacy's own file-header comment claimed "10 questions," its AssessmentIntro stats prop claimed 20 — neither matches the real 25-item array (the scoring code's own maxPossible = 30 // rough max per dimension with 25 questions comment confirms 25 is correct) — replaced both with live QUESTIONS.length. Real dead-link bug fixed: legacy's "Journey Continues" grid linked "Find Your Spirit"/"Find Your Religion" to external findmyassess-9eekxcob.manus.space stub URLs (dead Manus domain) despite this migration already having real, fully-built internal pages at /find-your-spirit and /find-your-religion — repointed to the real internal routes, and corrected Religion's stale "15 Questions" badge to the real 20. Real accent-color inconsistency fixed: legacy passed accentColor="#7B1FA2" only to the landing screen, then hardcoded brand-gold everywhere on the results screen instead — threaded one ACCENT constant through intro/radar/result-actions consistently, matching every other assessment in this migration. The "Also Worth Exploring" related-modality cards were dropped </t>
         </is>
       </c>
       <c r="E213" s="14" t="inlineStr">
@@ -5798,7 +5798,7 @@
       <c r="A214" s="4" t="n"/>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>/find-your-spirit (+ /find-my-spirit), along with a shared PDF-export component the rest of Phase 9 can reuse</t>
+          <t>/find-your-sake</t>
         </is>
       </c>
       <c r="C214" s="13" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Real 35 questions, 10 dimensions, and the 6 real spiritual traditions (each with real description/practices/key texts/figures/modern expressions/growth edge) ported unchanged and verbatim — legacy's own file-header comment claimed "12 archetypes," but only 6 TRADITIONS actually exist in the code; ported the real 6, not the stale doc comment. The real weighted tradition-matching logic (top 3 dimensions per tradition, weighted 3/2/1) is unchanged. Ported components/assessments/result-actions.tsx from legacy's AssessmentResultActions — kept only the real, backend-free "Download PDF" action (browser print); the "Send to Tony"/"Keep Private" buttons posted to an unbuilt trpc.assessments.submit and weren't reproduced, same honest-degradation pattern used throughout this migration. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
+          <t>Real 20 questions across 5 dimensions (Palate/Ritual/Terroir/Philosophy/Season) and the real 5 sake profiles (each with real Japanese name, tasting notes, food pairings, serving temperature, named producers with region/note, and further-reading resources) ported unchanged and verbatim. Legacy's own AssessmentIntro stats prop claimed "15 questions, 6 dimensions" — didn't match the real 20/5 implementation — replaced with live QUESTIONS.length/DIMENSIONS.length counts, same fix pattern already applied on /find-your-attachment-style and /find-your-sexuality. Two real bugs found and fixed: (1) legacy's "Journey Continues" list read "Find Myzcal" — a literal typo for "Find Your Mezcal" — corrected. (2) legacy's JSX rendered &lt;WhatsNext /&gt; (a full page section) nested inside the small "Retake the Tasting" &lt;button&gt; element — moved to a proper top-level section, same class of nested-interactive-content bug already fixed on /find-your-religion. The dark GlassPanel treatment (near-black translucent cards with light cream text, sitting on the page's own light parchment ThemedBackground) was kept as a real, intentional design choice rather than "fixed" to this migration's usual light-card convention — unlike the light-text-directly-on-light-background contrast bugs found on Style/Sexuality/Peptide/Religion, the text here sits inside its own correctly-contrasted dark card. SacredGeometryBg's canvas-based floating rice-grain particles dropped (same decoration-not-worth-the-JS-cost call made</t>
         </is>
       </c>
       <c r="E214" s="14" t="inlineStr">
@@ -5821,7 +5821,7 @@
       <c r="A215" s="4" t="n"/>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>/find-your-religion</t>
+          <t>/find-your-spirit (+ /find-my-spirit), along with a shared PDF-export component the rest of Phase 9 can reuse</t>
         </is>
       </c>
       <c r="C215" s="13" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Real 20 questions across 8 dimensions, 8 real spiritual/philosophical archetypes (each with real description/practices/key texts/figures/resonant traditions/growth-edge tensions), and the real scoring/matching logic ported unchanged and verbatim. Real bug found and fixed: legacy's own JSX rendered &lt;AssessmentResultActions&gt; nested inside the "Retake Assessment" &lt;button&gt; element — a button inside a button, invalid HTML — fixed by rendering it as a sibling instead, same fix pattern already applied on /find-your-spirit. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>Real 35 questions, 10 dimensions, and the 6 real spiritual traditions (each with real description/practices/key texts/figures/modern expressions/growth edge) ported unchanged and verbatim — legacy's own file-header comment claimed "12 archetypes," but only 6 TRADITIONS actually exist in the code; ported the real 6, not the stale doc comment. The real weighted tradition-matching logic (top 3 dimensions per tradition, weighted 3/2/1) is unchanged. Ported components/assessments/result-actions.tsx from legacy's AssessmentResultActions — kept only the real, backend-free "Download PDF" action (browser print); the "Send to Tony"/"Keep Private" buttons posted to an unbuilt trpc.assessments.submit and weren't reproduced, same honest-degradation pattern used throughout this migration. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E215" s="14" t="inlineStr">
@@ -5844,7 +5844,7 @@
       <c r="A216" s="4" t="n"/>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>/find-your-diet (+ /find-my-diet)</t>
+          <t>/find-your-religion</t>
         </is>
       </c>
       <c r="C216" s="13" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Real 15 questions, 6 real archetypes (with descriptions), and the real nearest-neighbor archetype-matching logic ported unchanged. Legacy's dead JourneyTracker import wired in for real (see journey-tracker.tsx). /find-my-diet → /find-your-diet redirect added. Verified live: 200 OK, full quiz flow, redirect confirmed 308, typecheck/lint clean.</t>
+          <t>Real 20 questions across 8 dimensions, 8 real spiritual/philosophical archetypes (each with real description/practices/key texts/figures/resonant traditions/growth-edge tensions), and the real scoring/matching logic ported unchanged and verbatim. Real bug found and fixed: legacy's own JSX rendered &lt;AssessmentResultActions&gt; nested inside the "Retake Assessment" &lt;button&gt; element — a button inside a button, invalid HTML — fixed by rendering it as a sibling instead, same fix pattern already applied on /find-your-spirit. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E216" s="14" t="inlineStr">
@@ -5867,7 +5867,7 @@
       <c r="A217" s="4" t="n"/>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>/find-your-movement (+ /find-my-movement), along with the shared assessment foundation the rest of Phase 9 depends on</t>
+          <t>/find-your-diet (+ /find-my-diet)</t>
         </is>
       </c>
       <c r="C217" s="13" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>Ported components/assessments/{themed-background,assessment-intro,email-gate,whats-next}.tsx from legacy's ThemedBackground/AssessmentIntro/EmailGate/WhatsNext — real content/behavior unchanged, with 2 real fixes along the way: (1) EmailGate now posts to the real /api/subscribe Route Handler (built earlier this migration) using the exact find-your-&lt;slug&gt; source keys already defined in lib/content/kit-source-tags.ts's KIT_TAG_MAP — legacy's own assessment-gate:&lt;slug&gt; prefix didn't match any tag in that map, so this is a genuine improvement, not just a port. (2) ThemedBackground's per-theme decorative particle field + SVG sacred-geometry overlay + 2 extra radial-glow layers dropped (same "not worth the cost" call made repeatedly elsewhere) — the real per-theme base gradient (16 themes) is kept, precomposed as one literal Tailwind class per theme rather than assembled from fragments. find-your-movement-quiz.tsx ports all 15 real questions and the real 6-dimension (Strength/Flexibility/Endurance/Mindfulness/Community/Adventure) scoring unchanged; the legacy JourneyTracker/useJourneyProgress import in the source file was dead code (imported, never rendered) and not ported. /find-my-movement → /find-your-movement redirect added (next.config.ts), same duplicate-route pattern as /find-my-tribe. Verified live: 200 OK, full quiz flow renders, redirect confirmed 308, typecheck/lint clean.</t>
+          <t>Real 15 questions, 6 real archetypes (with descriptions), and the real nearest-neighbor archetype-matching logic ported unchanged. Legacy's dead JourneyTracker import wired in for real (see journey-tracker.tsx). /find-my-diet → /find-your-diet redirect added. Verified live: 200 OK, full quiz flow, redirect confirmed 308, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E217" s="14" t="inlineStr">
@@ -5890,7 +5890,7 @@
       <c r="A218" s="4" t="n"/>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>/find-your-sleep (+ /find-my-sleep)</t>
+          <t>/find-your-movement (+ /find-my-movement), along with the shared assessment foundation the rest of Phase 9 depends on</t>
         </is>
       </c>
       <c r="C218" s="13" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Real 15 questions, 6 real archetypes, and the real cascading archetype-match logic ported unchanged, including legacy's own real behavioral quirk of rendering JourneyTracker on every phase (not just results). One real duplicate-destination "Journey Continues" link pair dropped (see file's own port note), the one real distinct link (Find Your Diet) kept. /find-my-sleep → /find-your-sleep redirect added. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
+          <t>Ported components/assessments/{themed-background,assessment-intro,email-gate,whats-next}.tsx from legacy's ThemedBackground/AssessmentIntro/EmailGate/WhatsNext — real content/behavior unchanged, with 2 real fixes along the way: (1) EmailGate now posts to the real /api/subscribe Route Handler (built earlier this migration) using the exact find-your-&lt;slug&gt; source keys already defined in lib/content/kit-source-tags.ts's KIT_TAG_MAP — legacy's own assessment-gate:&lt;slug&gt; prefix didn't match any tag in that map, so this is a genuine improvement, not just a port. (2) ThemedBackground's per-theme decorative particle field + SVG sacred-geometry overlay + 2 extra radial-glow layers dropped (same "not worth the cost" call made repeatedly elsewhere) — the real per-theme base gradient (16 themes) is kept, precomposed as one literal Tailwind class per theme rather than assembled from fragments. find-your-movement-quiz.tsx ports all 15 real questions and the real 6-dimension (Strength/Flexibility/Endurance/Mindfulness/Community/Adventure) scoring unchanged; the legacy JourneyTracker/useJourneyProgress import in the source file was dead code (imported, never rendered) and not ported. /find-my-movement → /find-your-movement redirect added (next.config.ts), same duplicate-route pattern as /find-my-tribe. Verified live: 200 OK, full quiz flow renders, redirect confirmed 308, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E218" s="14" t="inlineStr">
@@ -5913,7 +5913,7 @@
       <c r="A219" s="4" t="n"/>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>/find-your-coffee (+ /find-my-coffee)</t>
+          <t>/find-your-sleep (+ /find-my-sleep)</t>
         </is>
       </c>
       <c r="C219" s="13" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>Real 15 questions, 6 dimensions (Roast Preference/Origin Curiosity/Brewing Ritual/Social Context/Caffeine Sensitivity/Flavor Complexity), 6 real archetypes (each with a real description and 5 real named coffee recommendations — roaster, origin, roast level, tasting notes, real "why" rationale), and the real archetype-matching logic (sum of each archetype's 2 primary dimensions, highest wins) ported unchanged and verbatim. This legacy page predates the shared ThemedBackground/AssessmentIntro component system the rest of Phase 9 is built on — it hand-rolled its own hero-image page shell — so it needed more normalization than most: its hero image (/api/img/coffee-orig_a935f111.jpg) was a dead Manus asset, dropped for the standard ThemedBackground light theme (added a new "coffee" warm-cream entry) instead of reproducing a broken background; the canvas bean-particle field, floating steam-wisp divs, and SVG sacred-geometry overlay all dropped (same decoration-not-worth-the-JS-cost call made repeatedly elsewhere). Real bug found and fixed: legacy read window.innerWidth directly during render (twice — to pick grid columns and flex direction), unsafe during SSR and a real hydration-mismatch source — replaced with responsive Tailwind classes. EmailGate's prop was legacy's assessmentName; ported using this repo's real assessmentSlug="coffee" to match find-your-coffee in KIT_TAG_MAP. Legacy imported useJourneyProgress for markComplete but never rendered a visible JourneyTracker, and nev</t>
+          <t>Real 15 questions, 6 real archetypes, and the real cascading archetype-match logic ported unchanged, including legacy's own real behavioral quirk of rendering JourneyTracker on every phase (not just results). One real duplicate-destination "Journey Continues" link pair dropped (see file's own port note), the one real distinct link (Find Your Diet) kept. /find-my-sleep → /find-your-sleep redirect added. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E219" s="14" t="inlineStr">
@@ -5936,7 +5936,7 @@
       <c r="A220" s="4" t="n"/>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>/find-your-kitchen. Real 15 questions (all rendered on one page at once</t>
+          <t>/find-your-coffee (+ /find-my-coffee)</t>
         </is>
       </c>
       <c r="C220" s="13" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>a genuinely different, legacy-intentional UX from the other paginated quizzes, kept as-is) and the real dual-tracking scoring (answer score keys split into archetype tallies vs. 6 separate radar-chart dimensions) ported unchanged, including the 3 real "Journey Continues" links (one to already-built /find-your-diet, one forward-reference to /find-your-style). Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>Real 15 questions, 6 dimensions (Roast Preference/Origin Curiosity/Brewing Ritual/Social Context/Caffeine Sensitivity/Flavor Complexity), 6 real archetypes (each with a real description and 5 real named coffee recommendations — roaster, origin, roast level, tasting notes, real "why" rationale), and the real archetype-matching logic (sum of each archetype's 2 primary dimensions, highest wins) ported unchanged and verbatim. This legacy page predates the shared ThemedBackground/AssessmentIntro component system the rest of Phase 9 is built on — it hand-rolled its own hero-image page shell — so it needed more normalization than most: its hero image (/api/img/coffee-orig_a935f111.jpg) was a dead Manus asset, dropped for the standard ThemedBackground light theme (added a new "coffee" warm-cream entry) instead of reproducing a broken background; the canvas bean-particle field, floating steam-wisp divs, and SVG sacred-geometry overlay all dropped (same decoration-not-worth-the-JS-cost call made repeatedly elsewhere). Real bug found and fixed: legacy read window.innerWidth directly during render (twice — to pick grid columns and flex direction), unsafe during SSR and a real hydration-mismatch source — replaced with responsive Tailwind classes. EmailGate's prop was legacy's assessmentName; ported using this repo's real assessmentSlug="coffee" to match find-your-coffee in KIT_TAG_MAP. Legacy imported useJourneyProgress for markComplete but never rendered a visible JourneyTracker, and nev</t>
         </is>
       </c>
       <c r="E220" s="14" t="inlineStr">
@@ -5959,7 +5959,7 @@
       <c r="A221" s="4" t="n"/>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>/find-your-style. Real 15 questions, 6 real archetypes, and the real (if crude</t>
+          <t>/find-your-kitchen. Real 15 questions (all rendered on one page at once</t>
         </is>
       </c>
       <c r="C221" s="13" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>legacy's own comment admits "Simple mapping for demonstration") threshold-based archetype match ported unchanged. Two real inconsistencies found and normalized: legacy's own inline styles used near-illegible light text on ThemedBackground's actual light pastel "style" theme (inconsistent with every other assessment in this migration); and legacy rendered &lt;JourneyTracker /&gt; defaulting to variant="dark" on a light results screen instead of the variant="light" every other assessment passes. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>a genuinely different, legacy-intentional UX from the other paginated quizzes, kept as-is) and the real dual-tracking scoring (answer score keys split into archetype tallies vs. 6 separate radar-chart dimensions) ported unchanged, including the 3 real "Journey Continues" links (one to already-built /find-your-diet, one forward-reference to /find-your-style). Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E221" s="14" t="inlineStr">
@@ -5982,7 +5982,7 @@
       <c r="A222" s="4" t="n"/>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>/find-your-attachment-style (+ /find-my-attachment-style, /find-my-we)</t>
+          <t>/find-your-style. Real 15 questions, 6 real archetypes, and the real (if crude</t>
         </is>
       </c>
       <c r="C222" s="13" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Real 18 questions (legacy's own AssessmentIntro stats prop under-reported this as "15" — used the live QUESTIONS.length instead of repeating the stale number, same live-count discipline used elsewhere in this migration), the 4 real archetypes, and the real scoring/selection logic all ported unchanged, including the real closing note on attachment theory. Both alt-path redirects added. Verified live: 200 OK, both redirects confirmed 308, typecheck/lint clean.</t>
+          <t>legacy's own comment admits "Simple mapping for demonstration") threshold-based archetype match ported unchanged. Two real inconsistencies found and normalized: legacy's own inline styles used near-illegible light text on ThemedBackground's actual light pastel "style" theme (inconsistent with every other assessment in this migration); and legacy rendered &lt;JourneyTracker /&gt; defaulting to variant="dark" on a light results screen instead of the variant="light" every other assessment passes. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E222" s="14" t="inlineStr">
@@ -6005,7 +6005,7 @@
       <c r="A223" s="4" t="n"/>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>/find-your-love-language</t>
+          <t>/find-your-attachment-style (+ /find-my-attachment-style, /find-my-we)</t>
         </is>
       </c>
       <c r="C223" s="13" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>Real 15 questions (incl. the negative-score "disconnect" question), 5 real archetypes with descriptions/tips, and Dr. Gary Chapman's real attribution note all ported unchanged. Verified live: 200 OK, full quiz flow, typecheck/lint clean.</t>
+          <t>Real 18 questions (legacy's own AssessmentIntro stats prop under-reported this as "15" — used the live QUESTIONS.length instead of repeating the stale number, same live-count discipline used elsewhere in this migration), the 4 real archetypes, and the real scoring/selection logic all ported unchanged, including the real closing note on attachment theory. Both alt-path redirects added. Verified live: 200 OK, both redirects confirmed 308, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E223" s="14" t="inlineStr">
@@ -6028,7 +6028,7 @@
       <c r="A224" s="4" t="n"/>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>/find-your-peptide (+ /find-my-peptide)</t>
+          <t>/find-your-love-language</t>
         </is>
       </c>
       <c r="C224" s="13" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>"The Peptide Clarity Index™." A real, evidence-cited 10-question assessment across 7 clinical axes, mapping to 16 real peptide archetype profiles — every question (with its real PubMed/journal citation), every profile's real primary/secondary peptides with mechanisms and evidence, suggested lab work, red flags, and stacking notes ported unchanged and verbatim (clinical-adjacent content, not paraphrased). The real Peptide Readiness Score, contraindication-flag screening, share buttons (Twitter/LinkedIn/email/copy — real, backend-free), and the real medical disclaimer are all preserved. Real hero image (CloudFront, confirmed live) kept via next/image. Reused the simplified AssessmentResultActions (PDF-only) built for /find-your-spirit. Same light-text-on-light-background contrast bug already caught elsewhere was fixed here too. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
+          <t>Real 15 questions (incl. the negative-score "disconnect" question), 5 real archetypes with descriptions/tips, and Dr. Gary Chapman's real attribution note all ported unchanged. Verified live: 200 OK, full quiz flow, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E224" s="14" t="inlineStr">
@@ -6051,7 +6051,7 @@
       <c r="A225" s="4" t="n"/>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>/find-your-sexuality (+ /find-my-sexuality)</t>
+          <t>/find-your-peptide (+ /find-my-peptide)</t>
         </is>
       </c>
       <c r="C225" s="13" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>A research-informed assessment across 6 real dimensions, grounded in real cited research (Klein Sexual Orientation Grid 1978, Kinsey Scale 1948, Lisa Diamond 2008, Sari van Anders 2015) — real 16 questions (with per-question research context notes), real 12 archetypes (each with a real description + research note), and the real scoring/selection logic all ported unchanged and verbatim, including the real closing disclaimer. Legacy's own AssessmentIntro stats prop claimed "20 questions, 7 dimensions" — didn't match the real 16/6 implementation, used the live counts instead. Legacy's results screen also used light grey text on the real light pastel theme background (same low-contrast bug already caught on /find-your-style) — normalized to dark ink. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
+          <t>"The Peptide Clarity Index™." A real, evidence-cited 10-question assessment across 7 clinical axes, mapping to 16 real peptide archetype profiles — every question (with its real PubMed/journal citation), every profile's real primary/secondary peptides with mechanisms and evidence, suggested lab work, red flags, and stacking notes ported unchanged and verbatim (clinical-adjacent content, not paraphrased). The real Peptide Readiness Score, contraindication-flag screening, share buttons (Twitter/LinkedIn/email/copy — real, backend-free), and the real medical disclaimer are all preserved. Real hero image (CloudFront, confirmed live) kept via next/image. Reused the simplified AssessmentResultActions (PDF-only) built for /find-your-spirit. Same light-text-on-light-background contrast bug already caught elsewhere was fixed here too. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E225" s="14" t="inlineStr">
@@ -6074,7 +6074,7 @@
       <c r="A226" s="4" t="n"/>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>/find-my</t>
+          <t>/find-your-sexuality (+ /find-my-sexuality)</t>
         </is>
       </c>
       <c r="C226" s="13" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Find What's Yours," the real destination of the homepage's "Diagnose" door (confirmed by grepping lib/content/home-doors.ts's /find-my href) and of whats-next.tsx's "Take Another Assessment" link, both already pointing here as forward-references before this page existed. Legacy's 26-item ALL_LINKS directory (Featured + 6 categories) ported unchanged and verbatim into lib/content/find-my-directory.ts. Real accuracy fix, same pattern as /find-your-me's own port note: cross-checked all 26 destinations against the real route list — /find-your-ev, /life-assessment, and /soulscore (at the time) didn't exist yet, rendered as real "Coming Soon" cards instead of links that would 404 (dharma-finder/consciousness-scale/grant-study have since shipped and now flip to live — see below). Real reuse, not re-derivation: every item whose destination already exists in find-your-me.ts's audited DIRECTORY pulls that entry's real hook text and status at build time via a lookup helper, instead of hand-copying a second, driftable copy of the same facts. Two real live destinations added that legacy linked but find-your-me.ts's directory didn't track: /brewsoul (confirmed 200) and the external findmystem-s3lknc4h.manus.space sibling tool (confirmed live), both using the same "real external sibling product" trust already established for the other manus.space tools. Legacy's dead Manus hero image dropped for ThemedBackground (theme="ecosystem"), same call as /find-your-me. AssessmentProgressBar (never </t>
+          <t>A research-informed assessment across 6 real dimensions, grounded in real cited research (Klein Sexual Orientation Grid 1978, Kinsey Scale 1948, Lisa Diamond 2008, Sari van Anders 2015) — real 16 questions (with per-question research context notes), real 12 archetypes (each with a real description + research note), and the real scoring/selection logic all ported unchanged and verbatim, including the real closing disclaimer. Legacy's own AssessmentIntro stats prop claimed "20 questions, 7 dimensions" — didn't match the real 16/6 implementation, used the live counts instead. Legacy's results screen also used light grey text on the real light pastel theme background (same low-contrast bug already caught on /find-your-style) — normalized to dark ink. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E226" s="14" t="inlineStr">
@@ -6097,7 +6097,7 @@
       <c r="A227" s="4" t="n"/>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>/assessments</t>
+          <t>/find-my</t>
         </is>
       </c>
       <c r="C227" s="13" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>"Three Maps. One Journey," confirmed genuinely distinct from /find-my rather than a duplicate: /find-my is the wide 26-item ecosystem directory, /assessments is its own page for exactly 3 long research-grounded instruments (Dharma Finder / Consciousness Scale / Grant Study) that also happen to appear as one category inside /find-my's directory — legacy kept these as two separate pages, so the port does too. Real title/subtitle/description/time/icon/accent content for all 3 instruments ported unchanged and verbatim into lib/content/assessments-hub.ts, including the full "Why These Three" closing essay (Schmachtenberger/Hawkins/Harvard Grant Study triangulation). All 3 instrument cards now link live (dharma-finder/consciousness-scale/grant-study shipped alongside this page). Legacy's footer claim "Results saved for your return" was dropped — replaced with an honest line since nothing persists results yet. Added a real cross-link to /find-my. JourneyTracker reused unchanged; no EmailGate/AssessmentResultActions — pure preview/hub page with no quiz or results step of its own. Verified live: 200 OK, exactly 1 header/footer, real content in all 3 cards, typecheck/lint clean.</t>
+          <t xml:space="preserve">"Find What's Yours," the real destination of the homepage's "Diagnose" door (confirmed by grepping lib/content/home-doors.ts's /find-my href) and of whats-next.tsx's "Take Another Assessment" link, both already pointing here as forward-references before this page existed. Legacy's 26-item ALL_LINKS directory (Featured + 6 categories) ported unchanged and verbatim into lib/content/find-my-directory.ts. Real accuracy fix, same pattern as /find-your-me's own port note: cross-checked all 26 destinations against the real route list — /find-your-ev, /life-assessment, and /soulscore (at the time) didn't exist yet, rendered as real "Coming Soon" cards instead of links that would 404 (dharma-finder/consciousness-scale/grant-study have since shipped and now flip to live — see below). Real reuse, not re-derivation: every item whose destination already exists in find-your-me.ts's audited DIRECTORY pulls that entry's real hook text and status at build time via a lookup helper, instead of hand-copying a second, driftable copy of the same facts. Two real live destinations added that legacy linked but find-your-me.ts's directory didn't track: /brewsoul (confirmed 200) and the external findmystem-s3lknc4h.manus.space sibling tool (confirmed live), both using the same "real external sibling product" trust already established for the other manus.space tools. Legacy's dead Manus hero image dropped for ThemedBackground (theme="ecosystem"), same call as /find-your-me. AssessmentProgressBar (never </t>
         </is>
       </c>
       <c r="E227" s="14" t="inlineStr">
@@ -6120,7 +6120,7 @@
       <c r="A228" s="4" t="n"/>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>/dharma-finder (+ /assessments/dharma-finder redirect). Structurally different from every other Phase 9 quiz</t>
+          <t>/assessments</t>
         </is>
       </c>
       <c r="C228" s="13" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>legacy's real 25 questions are open-text reflection prompts, not multiple choice, distilled from Daniel Schmachtenberger's Dharma Inquiry and grouped into 4 real sections (Capacities/Values/Propensities/The Shadow Inquiry), each with a real framing quote, plus 3 real interstitial quotes shown between sections with the original 4-second auto-advance. All 25 questions, all quotes, and legacy's own keyword-matching generateDharmaProfile (deriving up to 3 archetypal roles and up to 4 core values from free-text answers, plus a completion-depth percentage) are ported unchanged and verbatim into a new dharma-finder-quiz.tsx. Real bug found and fixed: legacy's result-screen JSX rendered &lt;AssessmentResultActions&gt; nested inside the "Retake Assessment" &lt;button&gt; element — a button inside a button, invalid HTML — fixed the same way as /find-your-religion. Real dead-link bug fixed: "Journey Continues" linked to /assessments/consciousness-scale (repointed to the real /consciousness-scale) and /assessments/grant-study (dropped at the time, now live too). EmailGate (new here; legacy had none) is a real ecosystem-consistency addition. find-your-me.ts's ecosystem-directory status flipped from "coming" to "live" now that this page ships. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>"Three Maps. One Journey," confirmed genuinely distinct from /find-my rather than a duplicate: /find-my is the wide 26-item ecosystem directory, /assessments is its own page for exactly 3 long research-grounded instruments (Dharma Finder / Consciousness Scale / Grant Study) that also happen to appear as one category inside /find-my's directory — legacy kept these as two separate pages, so the port does too. Real title/subtitle/description/time/icon/accent content for all 3 instruments ported unchanged and verbatim into lib/content/assessments-hub.ts, including the full "Why These Three" closing essay (Schmachtenberger/Hawkins/Harvard Grant Study triangulation). All 3 instrument cards now link live (dharma-finder/consciousness-scale/grant-study shipped alongside this page). Legacy's footer claim "Results saved for your return" was dropped — replaced with an honest line since nothing persists results yet. Added a real cross-link to /find-my. JourneyTracker reused unchanged; no EmailGate/AssessmentResultActions — pure preview/hub page with no quiz or results step of its own. Verified live: 200 OK, exactly 1 header/footer, real content in all 3 cards, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E228" s="14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       <c r="A229" s="4" t="n"/>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>/consciousness-scale (+ /assessments/consciousness-scale redirect)</t>
+          <t>/dharma-finder (+ /assessments/dharma-finder redirect). Structurally different from every other Phase 9 quiz</t>
         </is>
       </c>
       <c r="C229" s="13" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Real 25 questions, each scored against David R. Hawkins' real 17-level Map of Consciousness (Shame 20 through Enlightenment 700+, final score = average of all 25 answers) — every question/option, every level's name/emotion/threshold, and getInsight's exact 6 tiers of interpretive copy ported unchanged and verbatim into a new consciousness-scale-quiz.tsx, along with the real live running-average indicator, visual scale gauge, full 17-level map, 6-month reminder, and X/LinkedIn/copy share. Since this assessment produces one composite score on a single axis rather than independent dimensions, a bespoke single-axis gauge replaces AssessmentRadarChart; per-level colors (17 known-at-build-time values) are precomposed literal Tailwind classes rather than assembled from hex fragments. Real Manus-dependency bug found and fixed: legacy's cinematic Q1 hero used a /api/img/consciousness-scale-hero-v2_085e0746.jpg Manus-proxied image — forbidden even temporarily per this migration's Zero-Manus rule — dropped for the plain question-card layout every other assessment uses; a real Sanity-hosted replacement is a tracked follow-up (see BLOG-IMAGE-BRIEFS.md-style tracking). find-your-me.ts's ecosystem-directory status flipped from "coming" to "live" now that this page ships. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>legacy's real 25 questions are open-text reflection prompts, not multiple choice, distilled from Daniel Schmachtenberger's Dharma Inquiry and grouped into 4 real sections (Capacities/Values/Propensities/The Shadow Inquiry), each with a real framing quote, plus 3 real interstitial quotes shown between sections with the original 4-second auto-advance. All 25 questions, all quotes, and legacy's own keyword-matching generateDharmaProfile (deriving up to 3 archetypal roles and up to 4 core values from free-text answers, plus a completion-depth percentage) are ported unchanged and verbatim into a new dharma-finder-quiz.tsx. Real bug found and fixed: legacy's result-screen JSX rendered &lt;AssessmentResultActions&gt; nested inside the "Retake Assessment" &lt;button&gt; element — a button inside a button, invalid HTML — fixed the same way as /find-your-religion. Real dead-link bug fixed: "Journey Continues" linked to /assessments/consciousness-scale (repointed to the real /consciousness-scale) and /assessments/grant-study (dropped at the time, now live too). EmailGate (new here; legacy had none) is a real ecosystem-consistency addition. find-your-me.ts's ecosystem-directory status flipped from "coming" to "live" now that this page ships. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E229" s="14" t="inlineStr">
@@ -6166,7 +6166,7 @@
       <c r="A230" s="4" t="n"/>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>/grant-study (+ /assessments/grant-study redirect)</t>
+          <t>/consciousness-scale (+ /assessments/consciousness-scale redirect)</t>
         </is>
       </c>
       <c r="C230" s="13" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>"Find Your Score," the real 25-question (5 per factor), 5-factor Harvard Grant Study life-satisfaction assessment (724 men, 1938–present, 85+ years — the longest-running study of human happiness). Every question, the 5 real factors (Warm Relationships/Adaptive Coping/Generativity/Career Satisfaction/Physical Vitality), every per-factor/per-tier insight (real named findings — Vaillant's "mature defenses," Erikson's generativity, Waldinger's quote), and the closing "Tony's Note" (Vaillant's "Happiness is love. Full stop." + Waldinger's "good relationships keep us happier and healthier") all ported unchanged and verbatim. Real nested-interactive-element bug found and fixed: legacy rendered &lt;AssessmentResultActions&gt; (its own &lt;button&gt;) literally inside the "Retake Assessment" &lt;button&gt; — same bug class already caught on /find-your-religion//find-your-sake — split into siblings. Real dead-link fix: "Journey Continues" pointed "Find Your Spirit" at a dead external Manus stub despite the real internal /find-your-spirit existing — repointed. Real ecosystem-consistency normalization: unlike every sibling "Find Your X" quiz, legacy skipped EmailGate entirely and went straight to results — added for consistency, plus new find-your-grant-study/find-your-dharma-finder/find-your-consciousness-scale alias keys in kit-source-tags.ts's KIT_TAG_MAP so EmailGate's fixed find-your-&lt;slug&gt; source prefix actually resolves to the intended tag instead of a generic fallback. resultSlug="grant-study" pas</t>
+          <t>Real 25 questions, each scored against David R. Hawkins' real 17-level Map of Consciousness (Shame 20 through Enlightenment 700+, final score = average of all 25 answers) — every question/option, every level's name/emotion/threshold, and getInsight's exact 6 tiers of interpretive copy ported unchanged and verbatim into a new consciousness-scale-quiz.tsx, along with the real live running-average indicator, visual scale gauge, full 17-level map, 6-month reminder, and X/LinkedIn/copy share. Since this assessment produces one composite score on a single axis rather than independent dimensions, a bespoke single-axis gauge replaces AssessmentRadarChart; per-level colors (17 known-at-build-time values) are precomposed literal Tailwind classes rather than assembled from hex fragments. Real Manus-dependency bug found and fixed: legacy's cinematic Q1 hero used a /api/img/consciousness-scale-hero-v2_085e0746.jpg Manus-proxied image — forbidden even temporarily per this migration's Zero-Manus rule — dropped for the plain question-card layout every other assessment uses; a real Sanity-hosted replacement is a tracked follow-up (see BLOG-IMAGE-BRIEFS.md-style tracking). find-your-me.ts's ecosystem-directory status flipped from "coming" to "live" now that this page ships. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E230" s="14" t="inlineStr">
@@ -6189,7 +6189,7 @@
       <c r="A231" s="4" t="n"/>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>/soulscore</t>
+          <t>/grant-study (+ /assessments/grant-study redirect)</t>
         </is>
       </c>
       <c r="C231" s="13" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>SoulScore™, ImpactSoul's 12-dimension impact measurement engine (1231-line legacy file, the largest remaining port). Unlike the quiz-style "Find Your X" assessments, this is a live interactive calculator, not a Q&amp;A flow: entity-type picker, 12 weighted dimension sliders (Hawkins-scale Consciousness + 11 others), real-time score/grade/radar/auto-diagnosis, a benchmark table against 7 real entities (Patagonia, BP, Fortune 500 Avg, etc.), a 6-tier/30-factor supply chain drill-down, 20 "why every impact system failed" entries, a real Consciousness-Adjusted NPV calculator, and the gig-economy 5-layer stack comparison — all real content/formulas ported verbatim. Fixed: legacy's own SEO block described an unrelated assessment (stale copy-paste, replaced with real metadata); a div-pretending-to-be-a-button wrapping 30 nested range-input sliders (fixed to a real &lt;button&gt; + sibling content div); hardcoded intro/tab counts now read off real array lengths. No EmailGate (legacy never had one here — it's an open calculator, not a report unlock), matching /find-your-peptide's precedent. AssessmentResultActions wired with resultSlug="soulscore". journey-tracker.tsx's JOURNEY_MAP and /impact-dashboard's "Launch SoulScore Engine"/"Launch C-NPV Calculator" links (previously a disabled "Coming Soon" note) now point at the real page. This closes the real dead-end referenced from site-nav-data.ts (/soulscore appears twice in nav) and from /impact-dashboard — the last item in the STATUS.md dead-end</t>
+          <t>"Find Your Score," the real 25-question (5 per factor), 5-factor Harvard Grant Study life-satisfaction assessment (724 men, 1938–present, 85+ years — the longest-running study of human happiness). Every question, the 5 real factors (Warm Relationships/Adaptive Coping/Generativity/Career Satisfaction/Physical Vitality), every per-factor/per-tier insight (real named findings — Vaillant's "mature defenses," Erikson's generativity, Waldinger's quote), and the closing "Tony's Note" (Vaillant's "Happiness is love. Full stop." + Waldinger's "good relationships keep us happier and healthier") all ported unchanged and verbatim. Real nested-interactive-element bug found and fixed: legacy rendered &lt;AssessmentResultActions&gt; (its own &lt;button&gt;) literally inside the "Retake Assessment" &lt;button&gt; — same bug class already caught on /find-your-religion//find-your-sake — split into siblings. Real dead-link fix: "Journey Continues" pointed "Find Your Spirit" at a dead external Manus stub despite the real internal /find-your-spirit existing — repointed. Real ecosystem-consistency normalization: unlike every sibling "Find Your X" quiz, legacy skipped EmailGate entirely and went straight to results — added for consistency, plus new find-your-grant-study/find-your-dharma-finder/find-your-consciousness-scale alias keys in kit-source-tags.ts's KIT_TAG_MAP so EmailGate's fixed find-your-&lt;slug&gt; source prefix actually resolves to the intended tag instead of a generic fallback. resultSlug="grant-study" pas</t>
         </is>
       </c>
       <c r="E231" s="14" t="inlineStr">
@@ -6212,7 +6212,7 @@
       <c r="A232" s="4" t="n"/>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>/self-portrait</t>
+          <t>/soulscore</t>
         </is>
       </c>
       <c r="C232" s="13" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>composite of completed assessments. Decision made: local-only (a real cookie, not Supabase — Phase 2 isn't provisioned yet). AssessmentResultActions (components/assessments/result-actions.tsx) takes an optional resultSlug and logs completions to a tg_assessment_results cookie via lib/assessments/result-log.ts, the same real-cookie-read-via-next/headers pattern already established by returning-visitor-hero.tsx/track-last-blog-visit.tsx — the page itself is a Server Component reading that cookie with zero client hydration step. Real, deliberate scope cut, not a silent one: legacy's SelfPortrait.tsx combined each assessment's own per-dimension scores (16 separate localStorage keys) into one composite radar chart across 15 unified dimensions, gated behind "5+ completed." This migration's result log only ever records that an assessment was completed, not its actual scored answers — building the real composite radar would mean threading a second, much larger data channel through every quiz. Shipped the honest subset instead: a real completed-assessments list (title, real completion date, retake link) plus a real "X of N completed" count and a "Still to Explore" section for the rest, via a new lib/content/self-portrait-catalog.ts. Wired resultSlug into the 7 remaining older "Find Your X" quizzes that already call AssessmentResultActions but hadn't been threaded yet (spirit/therapy/religion/sake/coffee/peptide/me) — /self-portrait now tracks 13 real assessments total. /find-my's "Sel</t>
+          <t>SoulScore™, ImpactSoul's 12-dimension impact measurement engine (1231-line legacy file, the largest remaining port). Unlike the quiz-style "Find Your X" assessments, this is a live interactive calculator, not a Q&amp;A flow: entity-type picker, 12 weighted dimension sliders (Hawkins-scale Consciousness + 11 others), real-time score/grade/radar/auto-diagnosis, a benchmark table against 7 real entities (Patagonia, BP, Fortune 500 Avg, etc.), a 6-tier/30-factor supply chain drill-down, 20 "why every impact system failed" entries, a real Consciousness-Adjusted NPV calculator, and the gig-economy 5-layer stack comparison — all real content/formulas ported verbatim. Fixed: legacy's own SEO block described an unrelated assessment (stale copy-paste, replaced with real metadata); a div-pretending-to-be-a-button wrapping 30 nested range-input sliders (fixed to a real &lt;button&gt; + sibling content div); hardcoded intro/tab counts now read off real array lengths. No EmailGate (legacy never had one here — it's an open calculator, not a report unlock), matching /find-your-peptide's precedent. AssessmentResultActions wired with resultSlug="soulscore". journey-tracker.tsx's JOURNEY_MAP and /impact-dashboard's "Launch SoulScore Engine"/"Launch C-NPV Calculator" links (previously a disabled "Coming Soon" note) now point at the real page. This closes the real dead-end referenced from site-nav-data.ts (/soulscore appears twice in nav) and from /impact-dashboard — the last item in the STATUS.md dead-end</t>
         </is>
       </c>
       <c r="E232" s="14" t="inlineStr">
@@ -6235,7 +6235,7 @@
       <c r="A233" s="4" t="n"/>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>/the-mirror (+ /life-assessment)</t>
+          <t>/self-portrait</t>
         </is>
       </c>
       <c r="C233" s="13" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>uses mirrorData.json, real 6-dimension/18-question life assessment ("The Mirror") ported into a typed lib/content/mirror-data.ts. Legacy served the identical component at both paths; /the-mirror is canonical (it's the only URL every existing internal link already pointed to — nav, journey tracker, Find Your Me), /life-assessment permanently redirects there. Real dimension-averaged scoring, radar chart via the shared AssessmentRadarChart, and weakest-dimension article/satellite-site recommendations ported unchanged. A live Sanity check found only 27 of 85 legacy article slugs still resolve; recommendations now resolve server-side and defensively skip missing ones, matching legacy's own behavior. Fixed: a hydration-unsafe typeof window branch computing the share URL, three stale manus.space satellite URLs superseded by their current live counterparts already used elsewhere in this migration, and dead /assessments/*/external-stub links in the "Journey Continues" grid. Added find-your-mirror to kit-source-tags.ts's KIT_TAG_MAP and reconciled journey-tracker.tsx's stale 10-minute estimate to legacy's real "~4 minutes" claim. find-your-me.ts's ecosystem-directory status flipped to "live." Verified live: 200 OK on both paths, redirect confirmed, typecheck/lint clean.</t>
+          <t>composite of completed assessments. Decision made: local-only (a real cookie, not Supabase — Phase 2 isn't provisioned yet). AssessmentResultActions (components/assessments/result-actions.tsx) takes an optional resultSlug and logs completions to a tg_assessment_results cookie via lib/assessments/result-log.ts, the same real-cookie-read-via-next/headers pattern already established by returning-visitor-hero.tsx/track-last-blog-visit.tsx — the page itself is a Server Component reading that cookie with zero client hydration step. Real, deliberate scope cut, not a silent one: legacy's SelfPortrait.tsx combined each assessment's own per-dimension scores (16 separate localStorage keys) into one composite radar chart across 15 unified dimensions, gated behind "5+ completed." This migration's result log only ever records that an assessment was completed, not its actual scored answers — building the real composite radar would mean threading a second, much larger data channel through every quiz. Shipped the honest subset instead: a real completed-assessments list (title, real completion date, retake link) plus a real "X of N completed" count and a "Still to Explore" section for the rest, via a new lib/content/self-portrait-catalog.ts. Wired resultSlug into the 7 remaining older "Find Your X" quizzes that already call AssessmentResultActions but hadn't been threaded yet (spirit/therapy/religion/sake/coffee/peptide/me) — /self-portrait now tracks 13 real assessments total. /find-my's "Sel</t>
         </is>
       </c>
       <c r="E233" s="14" t="inlineStr">
@@ -6258,7 +6258,7 @@
       <c r="A234" s="4" t="n"/>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>/assessment</t>
+          <t>/the-mirror (+ /life-assessment)</t>
         </is>
       </c>
       <c r="C234" s="13" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>confirmed via full legacy read this is not a "Find Your X" quiz (it predates that convention): it's Tony's own 3-way reader-path diagnostic — Builder / Crusader / Investor — 5 real questions, one point per matching answer, highest tally wins. Real questions and real archetype copy ported unchanged, reused from lib/content/archetypes.ts (already ported for /essays's archetype filter) rather than duplicated — added the page's ASSESSMENT_QUESTIONS to that same module since both come from the identical legacy source file. Preserved the real, distinct UX (no landing screen, no ThemedBackground/JourneyTracker — this page sits outside that ecosystem). Real bugs fixed: JS onMouseEnter/onMouseLeave inline-style hover hack replaced with Tailwind hover: classes; literal "..." pending-state text replaced with a real Loader2 spinner per house rule; dead trpc.subscribe.add replaced with a real POST /api/subscribe call. Real link audit: kept /impact-dashboard, /find-your-me, /living-declaration, and the real /blog/boiling-the-human-summit-harvard-kurzweil article as live links; /soulscore and /humanos are established forward-references used repeatedly elsewhere in this migration and both now ship too. The Human OS CTA reuses the border-red-800/30 text-red-800 treatment /living-declaration already established for the identical button instead of a new one-off raw-hex pair. AssessmentResultActions resultSlug="assessment" added (didn't exist when legacy was written). Added assessment-builder/as</t>
+          <t>uses mirrorData.json, real 6-dimension/18-question life assessment ("The Mirror") ported into a typed lib/content/mirror-data.ts. Legacy served the identical component at both paths; /the-mirror is canonical (it's the only URL every existing internal link already pointed to — nav, journey tracker, Find Your Me), /life-assessment permanently redirects there. Real dimension-averaged scoring, radar chart via the shared AssessmentRadarChart, and weakest-dimension article/satellite-site recommendations ported unchanged. A live Sanity check found only 27 of 85 legacy article slugs still resolve; recommendations now resolve server-side and defensively skip missing ones, matching legacy's own behavior. Fixed: a hydration-unsafe typeof window branch computing the share URL, three stale manus.space satellite URLs superseded by their current live counterparts already used elsewhere in this migration, and dead /assessments/*/external-stub links in the "Journey Continues" grid. Added find-your-mirror to kit-source-tags.ts's KIT_TAG_MAP and reconciled journey-tracker.tsx's stale 10-minute estimate to legacy's real "~4 minutes" claim. find-your-me.ts's ecosystem-directory status flipped to "live." Verified live: 200 OK on both paths, redirect confirmed, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E234" s="14" t="inlineStr">
@@ -6281,7 +6281,7 @@
       <c r="A235" s="4" t="n"/>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Fix dead-end pages flagged in STATUS.md</t>
+          <t>/assessment</t>
         </is>
       </c>
       <c r="C235" s="13" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>sake, therapy, and love-language all got real next-step navigation (WhatsNext + real "Journey Continues" links) during their ports — the last remaining one, soulscore, is now built (see above), closing this out.</t>
+          <t>confirmed via full legacy read this is not a "Find Your X" quiz (it predates that convention): it's Tony's own 3-way reader-path diagnostic — Builder / Crusader / Investor — 5 real questions, one point per matching answer, highest tally wins. Real questions and real archetype copy ported unchanged, reused from lib/content/archetypes.ts (already ported for /essays's archetype filter) rather than duplicated — added the page's ASSESSMENT_QUESTIONS to that same module since both come from the identical legacy source file. Preserved the real, distinct UX (no landing screen, no ThemedBackground/JourneyTracker — this page sits outside that ecosystem). Real bugs fixed: JS onMouseEnter/onMouseLeave inline-style hover hack replaced with Tailwind hover: classes; literal "..." pending-state text replaced with a real Loader2 spinner per house rule; dead trpc.subscribe.add replaced with a real POST /api/subscribe call. Real link audit: kept /impact-dashboard, /find-your-me, /living-declaration, and the real /blog/boiling-the-human-summit-harvard-kurzweil article as live links; /soulscore and /humanos are established forward-references used repeatedly elsewhere in this migration and both now ship too. The Human OS CTA reuses the border-red-800/30 text-red-800 treatment /living-declaration already established for the identical button instead of a new one-off raw-hex pair. AssessmentResultActions resultSlug="assessment" added (didn't exist when legacy was written). Added assessment-builder/as</t>
         </is>
       </c>
       <c r="E235" s="14" t="inlineStr">
@@ -6304,63 +6304,63 @@
       <c r="A236" s="4" t="n"/>
       <c r="B236" s="4" t="inlineStr">
         <is>
+          <t>Fix dead-end pages flagged in STATUS.md</t>
+        </is>
+      </c>
+      <c r="C236" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D236" s="4" t="inlineStr">
+        <is>
+          <t>sake, therapy, and love-language all got real next-step navigation (WhatsNext + real "Journey Continues" links) during their ports — the last remaining one, soulscore, is now built (see above), closing this out.</t>
+        </is>
+      </c>
+      <c r="E236" s="14" t="inlineStr">
+        <is>
+          <t>Phase 9 — Assessments (33 routes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="n"/>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
           <t>Port shared radar-chart / PDF-export / email-gate components used across assessments</t>
         </is>
       </c>
-      <c r="C236" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D236" s="4" t="inlineStr">
+      <c r="C237" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D237" s="4" t="inlineStr">
         <is>
           <t>components/assessments/{radar-chart,result-actions,email-gate}.tsx, built during Phase 9 and reused unchanged by all 15 "Find Your X" quizzes plus /find-your-me.</t>
         </is>
       </c>
-      <c r="E236" s="14" t="inlineStr">
+      <c r="E237" s="14" t="inlineStr">
         <is>
           <t>Phase 9 — Assessments (33 routes)</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="10" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="10" t="inlineStr">
         <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
         </is>
       </c>
-      <c r="B237" s="11" t="n"/>
-      <c r="C237" s="11" t="n"/>
-      <c r="D237" s="12" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="4" t="n"/>
-      <c r="B238" s="4" t="inlineStr">
-        <is>
-          <t>src/lib/admin/</t>
-        </is>
-      </c>
-      <c r="C238" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D238" s="4" t="inlineStr">
-        <is>
-          <t>guardrails (fixes the removed version's proxy.ts pattern, which missed the real src/proxy.ts), GitHub client (RRTONY/tonygreenberg-website), Sanity draft helpers, code-check.ts (ESLint + CONTRIBUTING.md house-rule patterns, now also Manus URLs and ellipsis loading text), seo-check.ts, tools.ts, mcp-server.ts, mcp-handler.ts, mcp-tool-context.ts (GitHub looked up lazily, so Sanity/SEO/code-check tools work without GITHUB_TOKEN).</t>
-        </is>
-      </c>
-      <c r="E238" s="14" t="inlineStr">
-        <is>
-          <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
-        </is>
-      </c>
+      <c r="B238" s="11" t="n"/>
+      <c r="C238" s="11" t="n"/>
+      <c r="D238" s="12" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="4" t="n"/>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Per-person access via MCP_ADMIN_USERS (read/edit/write roles, tools filtered per role, calls logged, commits stamped [by &lt;name&gt;])</t>
+          <t>src/lib/admin/</t>
         </is>
       </c>
       <c r="C239" s="13" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>mcp-auth.ts.</t>
+          <t>guardrails (fixes the removed version's proxy.ts pattern, which missed the real src/proxy.ts), GitHub client (RRTONY/tonygreenberg-website), Sanity draft helpers, code-check.ts (ESLint + CONTRIBUTING.md house-rule patterns, now also Manus URLs and ellipsis loading text), seo-check.ts, tools.ts, mcp-server.ts, mcp-handler.ts, mcp-tool-context.ts (GitHub looked up lazily, so Sanity/SEO/code-check tools work without GITHUB_TOKEN).</t>
         </is>
       </c>
       <c r="E239" s="14" t="inlineStr">
@@ -6383,7 +6383,7 @@
       <c r="A240" s="4" t="n"/>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>Rules gate: get_project_rules serves CONTRIBUTING.md + AGENTS.md + docs/ai/ guides with a rulesVersion; all 6 write tools require it</t>
+          <t>Per-person access via MCP_ADMIN_USERS (read/edit/write roles, tools filtered per role, calls logged, commits stamped [by &lt;name&gt;])</t>
         </is>
       </c>
       <c r="C240" s="13" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>project-rules.ts.</t>
+          <t>mcp-auth.ts.</t>
         </is>
       </c>
       <c r="E240" s="14" t="inlineStr">
@@ -6406,7 +6406,7 @@
       <c r="A241" s="4" t="n"/>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>src/app/api/mcp/route.ts (header auth) + src/app/api/mcp/[token]/route.ts (token in URL).</t>
+          <t>Rules gate: get_project_rules serves CONTRIBUTING.md + AGENTS.md + docs/ai/ guides with a rulesVersion; all 6 write tools require it</t>
         </is>
       </c>
       <c r="C241" s="13" t="inlineStr">
@@ -6414,7 +6414,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D241" s="4" t="inlineStr"/>
+      <c r="D241" s="4" t="inlineStr">
+        <is>
+          <t>project-rules.ts.</t>
+        </is>
+      </c>
       <c r="E241" s="14" t="inlineStr">
         <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
@@ -6425,7 +6429,7 @@
       <c r="A242" s="4" t="n"/>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>docs/ai/ knowledge base (README, TASK_GUIDE, PROJECT_STRUCTURE, project_mcp_server), linked from CONTRIBUTING.md.</t>
+          <t>src/app/api/mcp/route.ts (header auth) + src/app/api/mcp/[token]/route.ts (token in URL).</t>
         </is>
       </c>
       <c r="C242" s="13" t="inlineStr">
@@ -6444,7 +6448,7 @@
       <c r="A243" s="4" t="n"/>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>@modelcontextprotocol/sdk ^1.30.0 re-added (approved 2026-09-29); GITHUB_TOKEN/MCP_ADMIN_USERS/MCP_SITE_ORIGIN documented in .env.local.example.</t>
+          <t>docs/ai/ knowledge base (README, TASK_GUIDE, PROJECT_STRUCTURE, project_mcp_server), linked from CONTRIBUTING.md.</t>
         </is>
       </c>
       <c r="C243" s="13" t="inlineStr">
@@ -6463,7 +6467,7 @@
       <c r="A244" s="4" t="n"/>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>Verified locally</t>
+          <t>@modelcontextprotocol/sdk ^1.30.0 re-added (approved 2026-09-29); GITHUB_TOKEN/MCP_ADMIN_USERS/MCP_SITE_ORIGIN documented in .env.local.example.</t>
         </is>
       </c>
       <c r="C244" s="13" t="inlineStr">
@@ -6471,11 +6475,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D244" s="4" t="inlineStr">
-        <is>
-          <t>auth (401/405), role filtering, rules-gate markers, token-in-URL route, code check, Sanity query, SEO check.</t>
-        </is>
-      </c>
+      <c r="D244" s="4" t="inlineStr"/>
       <c r="E244" s="14" t="inlineStr">
         <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
@@ -6486,7 +6486,7 @@
       <c r="A245" s="4" t="n"/>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Sign-in for the MCP server (OAuth 2.1, ported from ramprate-ui, 2026-09-30)</t>
+          <t>Verified locally</t>
         </is>
       </c>
       <c r="C245" s="13" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>/oauth/authorize sign-in page + /.well-known metadata + register/authorize/token endpoints, stateless (signed tokens, no database), no new dependency. Verified end to end on a local production build. See docs/ai/project_mcp_server.md.</t>
+          <t>auth (401/405), role filtering, rules-gate markers, token-in-URL route, code check, Sanity query, SEO check.</t>
         </is>
       </c>
       <c r="E245" s="14" t="inlineStr">
@@ -6509,17 +6509,17 @@
       <c r="A246" s="4" t="n"/>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>Set GITHUB_TOKEN, MCP_ADMIN_USERS, MCP_LOGIN_PASSWORD, MCP_OAUTH_SECRET, MCP_SITE_ORIGIN, MCP_PUBLIC_ORIGIN in Netlify (done) (checked 2026-…</t>
-        </is>
-      </c>
-      <c r="C246" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Sign-in for the MCP server (OAuth 2.1, ported from ramprate-ui, 2026-09-30)</t>
+        </is>
+      </c>
+      <c r="C246" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>10-07: all already set in Netlify). Left: connect Claude.ai to /api/mcp for real, and verify the GitHub flow end to end (branch → PR → deploy preview → publish_changes) against a real PR.</t>
+          <t>/oauth/authorize sign-in page + /.well-known metadata + register/authorize/token endpoints, stateless (signed tokens, no database), no new dependency. Verified end to end on a local production build. See docs/ai/project_mcp_server.md.</t>
         </is>
       </c>
       <c r="E246" s="14" t="inlineStr">
@@ -6532,7 +6532,7 @@
       <c r="A247" s="4" t="n"/>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Commit a team-wide .mcp.json (URL only) once the production URL is settled.</t>
+          <t>Set GITHUB_TOKEN, MCP_ADMIN_USERS, MCP_LOGIN_PASSWORD, MCP_OAUTH_SECRET, MCP_SITE_ORIGIN, MCP_PUBLIC_ORIGIN in Netlify (done) (checked 2026-…</t>
         </is>
       </c>
       <c r="C247" s="15" t="inlineStr">
@@ -6540,7 +6540,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D247" s="4" t="inlineStr"/>
+      <c r="D247" s="4" t="inlineStr">
+        <is>
+          <t>10-07: all already set in Netlify). Left: connect Claude.ai to /api/mcp for real, and verify the GitHub flow end to end (branch → PR → deploy preview → publish_changes) against a real PR.</t>
+        </is>
+      </c>
       <c r="E247" s="14" t="inlineStr">
         <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
@@ -6551,19 +6555,15 @@
       <c r="A248" s="4" t="n"/>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>Google read-only tools added (2026-10-02)</t>
-        </is>
-      </c>
-      <c r="C248" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D248" s="4" t="inlineStr">
-        <is>
-          <t>check_analytics (GA4), search_console_sites / _performance / _inspect_url / _sitemaps (list only, no submit or delete), lighthouse_check_page (PageSpeed Insights). New files google-auth.ts, ga4-client.ts, gsc-client.ts, lighthouse-check.ts; no new dependency. Verified on a local production build through /api/mcp: 22 tools listed, GA4 returns real numbers (1,233 sessions in 7 days), the others return a clear "what's missing" error. Env vars added to .env.local.example.</t>
-        </is>
-      </c>
+          <t>Commit a team-wide .mcp.json (URL only) once the production URL is settled.</t>
+        </is>
+      </c>
+      <c r="C248" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="inlineStr"/>
       <c r="E248" s="14" t="inlineStr">
         <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
@@ -6574,7 +6574,7 @@
       <c r="A249" s="4" t="n"/>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>publish_changes fixed (2026-10-02)</t>
+          <t>Google read-only tools added (2026-10-02)</t>
         </is>
       </c>
       <c r="C249" s="13" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>it published every draft in Sanity (31 waiting for review today), so any one-line fix would have pushed them all live. Now it publishes only the drafts named in draft_ids; unknown ids are refused before anything happens (verified).</t>
+          <t>check_analytics (GA4), search_console_sites / _performance / _inspect_url / _sitemaps (list only, no submit or delete), lighthouse_check_page (PageSpeed Insights). New files google-auth.ts, ga4-client.ts, gsc-client.ts, lighthouse-check.ts; no new dependency. Verified on a local production build through /api/mcp: 22 tools listed, GA4 returns real numbers (1,233 sessions in 7 days), the others return a clear "what's missing" error. Env vars added to .env.local.example.</t>
         </is>
       </c>
       <c r="E249" s="14" t="inlineStr">
@@ -6597,7 +6597,7 @@
       <c r="A250" s="4" t="n"/>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>seo_check_page decoded &amp;#39; but not React's &amp;#x27;, so descriptions showed Tony Greenberg&amp;#x27;s and the length was off</t>
+          <t>publish_changes fixed (2026-10-02)</t>
         </is>
       </c>
       <c r="C250" s="13" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>Fixed and verified (2026-10-02).</t>
+          <t>it published every draft in Sanity (31 waiting for review today), so any one-line fix would have pushed them all live. Now it publishes only the drafts named in draft_ids; unknown ids are refused before anything happens (verified).</t>
         </is>
       </c>
       <c r="E250" s="14" t="inlineStr">
@@ -6620,7 +6620,7 @@
       <c r="A251" s="4" t="n"/>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Search Console access for the service account added by the team (2026-10-02); all four search_console_* tools verified with real tonygreenbe…</t>
+          <t>seo_check_page decoded &amp;#39; but not React's &amp;#x27;, so descriptions showed Tony Greenberg&amp;#x27;s and the length was off</t>
         </is>
       </c>
       <c r="C251" s="13" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>rg.com data (99 clicks / 1,663 impressions in 28 days, homepage indexed, sitemap 284 URLs, 0 errors, 82 warnings).</t>
+          <t>Fixed and verified (2026-10-02).</t>
         </is>
       </c>
       <c r="E251" s="14" t="inlineStr">
@@ -6643,7 +6643,7 @@
       <c r="A252" s="4" t="n"/>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>GOOGLE_GA_CLIENT_EMAIL, GOOGLE_GA_PRIVATE_KEY, GA4_PROPERTY_ID_TONYGREENBERG set in Netlify (2026-10-02, via the Netlify API, values checked…</t>
+          <t>Search Console access for the service account added by the team (2026-10-02); all four search_console_* tools verified with real tonygreenbe…</t>
         </is>
       </c>
       <c r="C252" s="13" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> equal to .env.local; this plan can't limit a variable's scopes, so they're available to builds and functions). Used from the next deploy.</t>
+          <t>rg.com data (99 clicks / 1,663 impressions in 28 days, homepage indexed, sitemap 284 URLs, 0 errors, 82 warnings).</t>
         </is>
       </c>
       <c r="E252" s="14" t="inlineStr">
@@ -6666,7 +6666,7 @@
       <c r="A253" s="4" t="n"/>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Per-request change system ported from ramprate-ui (2026-10-02, owner said yes)</t>
+          <t>GOOGLE_GA_CLIENT_EMAIL, GOOGLE_GA_PRIVATE_KEY, GA4_PROPERTY_ID_TONYGREENBERG set in Netlify (2026-10-02, via the Netlify API, values checked…</t>
         </is>
       </c>
       <c r="C253" s="13" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>, covering the 10 review points the team raised for RampRate's setup: (1) discard_change; (2) one request = one change with its own branch, PR and drafts, so publishing never takes another request live; (3) a review with pages affected, a server-written "what's included" line and preview links; (4) publish needs the review's reviewToken, and the rules make the AI ask "You are about to publish these changes to the live tonygreenberg.com website. Are you sure you want to continue?"; (5) list_change_history, also visible read-only in Studio under "Website change history" (new adminChange type); (6) undo_change; (7) before/after (automatic for Sanity, given by the AI for code); (8) preview_on_devices phone + laptop screenshots (needs GOOGLE_API_KEY); (9) the AI's plain summary plus the server's facts line; (10) Draft → Ready for review → Published / Discarded. Files: change-sets.ts, change-describe.ts, device-preview.ts, mcp-tool-context.ts, mcp-server.ts, github-client.ts (RampRate's full version), src/sanity/schemas/adminChange.ts, sanity.config.ts. Tested end to end with a real throwaway change, then discarded (see docs/ai/project_mcp_server.md).</t>
+          <t xml:space="preserve"> equal to .env.local; this plan can't limit a variable's scopes, so they're available to builds and functions). Used from the next deploy.</t>
         </is>
       </c>
       <c r="E253" s="14" t="inlineStr">
@@ -6689,7 +6689,7 @@
       <c r="A254" s="4" t="n"/>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>Merge the CI fix into main</t>
+          <t>Per-request change system ported from ramprate-ui (2026-10-02, owner said yes)</t>
         </is>
       </c>
       <c r="C254" s="13" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>(done with PR #3; checked 2026-10-06: main's pr-lint.yml runs Node 22 and next typegen before the type check). The test change's GitHub check failed because main still has the old pr-lint.yml (Node 20 crash). Every MCP change will fail its site check, and so can't be published, until this branch's work (or at least .github/workflows/pr-lint.yml) is on main. Then test a real publish and undo_change.</t>
+          <t>, covering the 10 review points the team raised for RampRate's setup: (1) discard_change; (2) one request = one change with its own branch, PR and drafts, so publishing never takes another request live; (3) a review with pages affected, a server-written "what's included" line and preview links; (4) publish needs the review's reviewToken, and the rules make the AI ask "You are about to publish these changes to the live tonygreenberg.com website. Are you sure you want to continue?"; (5) list_change_history, also visible read-only in Studio under "Website change history" (new adminChange type); (6) undo_change; (7) before/after (automatic for Sanity, given by the AI for code); (8) preview_on_devices phone + laptop screenshots (needs GOOGLE_API_KEY); (9) the AI's plain summary plus the server's facts line; (10) Draft → Ready for review → Published / Discarded. Files: change-sets.ts, change-describe.ts, device-preview.ts, mcp-tool-context.ts, mcp-server.ts, github-client.ts (RampRate's full version), src/sanity/schemas/adminChange.ts, sanity.config.ts. Tested end to end with a real throwaway change, then discarded (see docs/ai/project_mcp_server.md).</t>
         </is>
       </c>
       <c r="E254" s="14" t="inlineStr">
@@ -6712,17 +6712,17 @@
       <c r="A255" s="4" t="n"/>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Blocked on you (Google)</t>
-        </is>
-      </c>
-      <c r="C255" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Merge the CI fix into main</t>
+        </is>
+      </c>
+      <c r="C255" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>create a GOOGLE_API_KEY in Google Cloud (project of the vcos-ga4-reader service account, where the PageSpeed Insights API is already on), restricted to the PageSpeed Insights API, then add it to .env.local and Netlify. Creating it from here was blocked by the session's safety check (it would use the service account's credentials to change the Cloud project). Note lighthouse_check_page may time out on Netlify (10 s function limit on the free plan).</t>
+          <t>(done with PR #3; checked 2026-10-06: main's pr-lint.yml runs Node 22 and next typegen before the type check). The test change's GitHub check failed because main still has the old pr-lint.yml (Node 20 crash). Every MCP change will fail its site check, and so can't be published, until this branch's work (or at least .github/workflows/pr-lint.yml) is on main. Then test a real publish and undo_change.</t>
         </is>
       </c>
       <c r="E255" s="14" t="inlineStr">
@@ -6735,17 +6735,17 @@
       <c r="A256" s="4" t="n"/>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Synced with ramprate-ui's MCP server (2026-10-09, owner asked; card included by their choice)</t>
-        </is>
-      </c>
-      <c r="C256" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Blocked on you (Google)</t>
+        </is>
+      </c>
+      <c r="C256" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>the review card for ChatGPT/Claude (one status and next step, Build / Type check / Lint / GitHub / phone-and-laptop checks, "what goes live" and what doesn't, Preview / Discard / Publish / Retry, history with Restore); start_change restates the request (understood_as) and unclear ones wait for the person's OK (confirm_change); before (live) / after (preview) screenshots on phone and laptop; attached images and files (ChatGPT file, or request_upload_link, a private 30-minute upload page at /api/mcp/upload, size and real-type checked); every change result lists the other waiting changes and the AI ends its reply with them (new Status Report line); the server lints changed files itself; ESLint now traced into the deployed function (serverExternalPackages; ramprate's tracing globs crash Turbopack under pnpm, left out). Everything named for tonygreenberg.com only (Netlify tonygreenberg-website, live tonygreenberg.com, card ui://tonygreenberg-admin/...). Verified on a local production build: type check, lint, build; 30 tools listed; card served and its script valid; rules include migrationStatus; list_pending_changes returns other pending changes; check_code_quality runs ESLint; upload page refuses bad links (401). See docs/ai/project_mcp_server.md.</t>
+          <t>create a GOOGLE_API_KEY in Google Cloud (project of the vcos-ga4-reader service account, where the PageSpeed Insights API is already on), restricted to the PageSpeed Insights API, then add it to .env.local and Netlify. Creating it from here was blocked by the session's safety check (it would use the service account's credentials to change the Cloud project). Note lighthouse_check_page may time out on Netlify (10 s function limit on the free plan).</t>
         </is>
       </c>
       <c r="E256" s="14" t="inlineStr">
@@ -6758,63 +6758,63 @@
       <c r="A257" s="4" t="n"/>
       <c r="B257" s="4" t="inlineStr">
         <is>
+          <t>Synced with ramprate-ui's MCP server (2026-10-09, owner asked; card included by their choice)</t>
+        </is>
+      </c>
+      <c r="C257" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D257" s="4" t="inlineStr">
+        <is>
+          <t>the review card for ChatGPT/Claude (one status and next step, Build / Type check / Lint / GitHub / phone-and-laptop checks, "what goes live" and what doesn't, Preview / Discard / Publish / Retry, history with Restore); start_change restates the request (understood_as) and unclear ones wait for the person's OK (confirm_change); before (live) / after (preview) screenshots on phone and laptop; attached images and files (ChatGPT file, or request_upload_link, a private 30-minute upload page at /api/mcp/upload, size and real-type checked); every change result lists the other waiting changes and the AI ends its reply with them (new Status Report line); the server lints changed files itself; ESLint now traced into the deployed function (serverExternalPackages; ramprate's tracing globs crash Turbopack under pnpm, left out). Everything named for tonygreenberg.com only (Netlify tonygreenberg-website, live tonygreenberg.com, card ui://tonygreenberg-admin/...). Verified on a local production build: type check, lint, build; 30 tools listed; card served and its script valid; rules include migrationStatus; list_pending_changes returns other pending changes; check_code_quality runs ESLint; upload page refuses bad links (401). See docs/ai/project_mcp_server.md.</t>
+        </is>
+      </c>
+      <c r="E257" s="14" t="inlineStr">
+        <is>
+          <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="n"/>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
           <t>Test the new review end to end on a deploy preview</t>
         </is>
       </c>
-      <c r="C257" s="15" t="inlineStr">
+      <c r="C258" s="15" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D257" s="4" t="inlineStr">
+      <c r="D258" s="4" t="inlineStr">
         <is>
           <t>(needs a yes, it opens a real pull request): one throwaway change from Claude.ai or ChatGPT: start (unclear request, so the confirm step shows), confirm, edit, review card, screenshots, upload link, then discard.</t>
         </is>
       </c>
-      <c r="E257" s="14" t="inlineStr">
+      <c r="E258" s="14" t="inlineStr">
         <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="10" t="inlineStr">
+    <row r="259">
+      <c r="A259" s="10" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
         </is>
       </c>
-      <c r="B258" s="11" t="n"/>
-      <c r="C258" s="11" t="n"/>
-      <c r="D258" s="12" t="n"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="4" t="n"/>
-      <c r="B259" s="4" t="inlineStr">
-        <is>
-          <t>Per-page generateMetadata (title, description, OG, Twitter Card, canonical) for every ported route, sourced from Sanity seo object where con…</t>
-        </is>
-      </c>
-      <c r="C259" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D259" s="4" t="inlineStr">
-        <is>
-          <t>tent is CMS-backed, static otherwise. Audited all 140 page.tsx files: only /studio has none (correct — it's robots.txt-disallowed, not public content). Real gap found and fixed: /blog/category/[slug] had no alternates.canonical at all, and no page-aware title for its own real pagination (?page=N) — every paginated page was serving an identical title with no canonical, a real duplicate-content signal. Fixed: generateMetadata now reads searchParams too, self-canonicals each page (?page=N pages canonical to themselves, not consolidated to page 1 — genuinely different posts per page, matching Google's current pagination guidance) and appends "— Page N" to the title past page 1. Verified live: page 1 canonicals to the bare URL, ?page=2 canonicals to ?page=2 with a distinct title.</t>
-        </is>
-      </c>
-      <c r="E259" s="14" t="inlineStr">
-        <is>
-          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
-        </is>
-      </c>
+      <c r="B259" s="11" t="n"/>
+      <c r="C259" s="11" t="n"/>
+      <c r="D259" s="12" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="4" t="n"/>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>sitemap.ts generated from real Sanity content + static route list, auto-updates on publish</t>
+          <t>Per-page generateMetadata (title, description, OG, Twitter Card, canonical) for every ported route, sourced from Sanity seo object where con…</t>
         </is>
       </c>
       <c r="C260" s="13" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>Extended from the Phase 5-era version (homepage + blog posts only, 122 URLs) to every real route: the full static route list (130 routes, generated from find src/app -name page.tsx, excluding /studio (robots.txt-disallowed), /(auth)/login (noindex via its own metadata), and /life-assessment (a pure redirect, not distinct content)) plus all 5 real dynamic sources — blog categories (allCategorySlugsQuery), BrewSoul cities (25), BrewSoul coffees (107), and charity-scorecard entries (103) — each pulled from the exact same data source its own page's generateStaticParams already uses, not re-derived. Auto-updates on publish for anything Sanity-backed (blog posts/categories) since it's a live client.fetch on every build; the static route list itself needs a one-line addition whenever a new page ships (same as any other route-registration step). Verified live: 496 real &lt;loc&gt; entries, spot-checked a coffee/city/charity/category URL each, typecheck/lint clean.</t>
+          <t>tent is CMS-backed, static otherwise. Audited all 140 page.tsx files: only /studio has none (correct — it's robots.txt-disallowed, not public content). Real gap found and fixed: /blog/category/[slug] had no alternates.canonical at all, and no page-aware title for its own real pagination (?page=N) — every paginated page was serving an identical title with no canonical, a real duplicate-content signal. Fixed: generateMetadata now reads searchParams too, self-canonicals each page (?page=N pages canonical to themselves, not consolidated to page 1 — genuinely different posts per page, matching Google's current pagination guidance) and appends "— Page N" to the title past page 1. Verified live: page 1 canonicals to the bare URL, ?page=2 canonicals to ?page=2 with a distinct title.</t>
         </is>
       </c>
       <c r="E260" s="14" t="inlineStr">
@@ -6837,7 +6837,7 @@
       <c r="A261" s="4" t="n"/>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>llms.txt</t>
+          <t>sitemap.ts generated from real Sanity content + static route list, auto-updates on publish</t>
         </is>
       </c>
       <c r="C261" s="13" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>fetched verbatim from the still-live site and saved to web/public/llms.txt (real content: Tony's bio, expertise, full article index by category, every product/tool section) — do this before Manus goes away, it won't be recoverable after</t>
+          <t>Extended from the Phase 5-era version (homepage + blog posts only, 122 URLs) to every real route: the full static route list (130 routes, generated from find src/app -name page.tsx, excluding /studio (robots.txt-disallowed), /(auth)/login (noindex via its own metadata), and /life-assessment (a pure redirect, not distinct content)) plus all 5 real dynamic sources — blog categories (allCategorySlugsQuery), BrewSoul cities (25), BrewSoul coffees (107), and charity-scorecard entries (103) — each pulled from the exact same data source its own page's generateStaticParams already uses, not re-derived. Auto-updates on publish for anything Sanity-backed (blog posts/categories) since it's a live client.fetch on every build; the static route list itself needs a one-line addition whenever a new page ships (same as any other route-registration step). Verified live: 496 real &lt;loc&gt; entries, spot-checked a coffee/city/charity/category URL each, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E261" s="14" t="inlineStr">
@@ -6860,7 +6860,7 @@
       <c r="A262" s="4" t="n"/>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>robots.txt</t>
+          <t>llms.txt</t>
         </is>
       </c>
       <c r="C262" s="13" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>same approach: fetched the real live file (not my earlier guessed robots.ts, which has been removed) and saved verbatim to web/public/robots.txt, plus added Disallow: /studio for the new Sanity Studio route. Confirmed live: real AI-crawler allowlist (GPTBot, Claude-Web, PerplexityBot, etc.), scraper blocklist, and the site's non-standard LLMs: directive all intact</t>
+          <t>fetched verbatim from the still-live site and saved to web/public/llms.txt (real content: Tony's bio, expertise, full article index by category, every product/tool section) — do this before Manus goes away, it won't be recoverable after</t>
         </is>
       </c>
       <c r="E262" s="14" t="inlineStr">
@@ -6883,7 +6883,7 @@
       <c r="A263" s="4" t="n"/>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>JSON-LD</t>
+          <t>robots.txt</t>
         </is>
       </c>
       <c r="C263" s="13" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>WebSite + Person schema ported verbatim from the live homepage's actual &lt;script type="application/ld+json"&gt; tags (not reconstructed from memory) — rendered site-wide from src/lib/structured-data.ts in the root layout. The Person image was hardcoded to a /api/img/... legacy proxy path on the live site — rescued that headshot (downloaded it while still live, uploaded to Sanity as the author-tony-greenberg document's avatar) so the new site's JSON-LD has zero Manus dependency instead of just copying the fragile path forward</t>
+          <t>same approach: fetched the real live file (not my earlier guessed robots.ts, which has been removed) and saved verbatim to web/public/robots.txt, plus added Disallow: /studio for the new Sanity Studio route. Confirmed live: real AI-crawler allowlist (GPTBot, Claude-Web, PerplexityBot, etc.), scraper blocklist, and the site's non-standard LLMs: directive all intact</t>
         </is>
       </c>
       <c r="E263" s="14" t="inlineStr">
@@ -6906,7 +6906,7 @@
       <c r="A264" s="4" t="n"/>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>Article JSON-LD on /blog/[slug], built from real per-post Sanity data (headline, image, datePublished/dateModified, author, canonical URL)</t>
+          <t>JSON-LD</t>
         </is>
       </c>
       <c r="C264" s="13" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>verified live on a real post</t>
+          <t>WebSite + Person schema ported verbatim from the live homepage's actual &lt;script type="application/ld+json"&gt; tags (not reconstructed from memory) — rendered site-wide from src/lib/structured-data.ts in the root layout. The Person image was hardcoded to a /api/img/... legacy proxy path on the live site — rescued that headshot (downloaded it while still live, uploaded to Sanity as the author-tony-greenberg document's avatar) so the new site's JSON-LD has zero Manus dependency instead of just copying the fragile path forward</t>
         </is>
       </c>
       <c r="E264" s="14" t="inlineStr">
@@ -6929,7 +6929,7 @@
       <c r="A265" s="4" t="n"/>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Build the full Manus/legacy-URL → Next.js-URL 301 redirect map (next.config.ts redirects() or Sanity redirect documents)</t>
+          <t>Article JSON-LD on /blog/[slug], built from real per-post Sanity data (headline, image, datePublished/dateModified, author, canonical URL)</t>
         </is>
       </c>
       <c r="C265" s="13" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>hard QA gate, nothing proceeds to DNS cutover until this is complete and tested. First real pass done: extracted all 197 real path= routes from legacy's App.tsx router (not guessed — the actual route table), diffed against this app's real current routes (find src/app -maxdepth 1 -name page.tsx) + next.config.ts's existing redirect sources, normalizing :param/[param] syntax to compare like-for-like. Started at 41 real gaps, closed 10 with new redirects: /attention-theft/{blocker-finder,legal,report,weapons} (legacy registered both a bare AND a /attention-theft/-nested path for each, only the bare ones had redirects before), /find-my-car → /find-my, /the-index → /search (matching the fix already applied to other pages' dead links to it), /supplier-intake-long (bare) + /vendor-intake + /vendor-intake-long (+/:token) → the same real ramprate.com/biochain/supplier-intake destination the token'd path already redirected to, and /spamtoast + /youve-been-reported → / (the live half of legacy's "report a spammer" confrontation flow — a fake IP-fingerprinting/countdown-timer page; the other half, ReportSpammer.tsx, was already a documented drop in Phase 4, this is the same call for its sequel). 21 of the remaining 31 gaps need no redirect — they're /admin/*//analytics//edit/frqncy (internal tools never meant for public discovery) or already-documented intentional defers from Phase 4/7/10 (/clock-keeper-part-2, /ecosystem-map, /friend-gate, /friend-survey/:token, /medicine-sequencing, /m</t>
+          <t>verified live on a real post</t>
         </is>
       </c>
       <c r="E265" s="14" t="inlineStr">
@@ -6952,7 +6952,7 @@
       <c r="A266" s="4" t="n"/>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>/path/:archetype (src/app/path/[archetype]/page.tsx)</t>
+          <t>Build the full Manus/legacy-URL → Next.js-URL 301 redirect map (next.config.ts redirects() or Sanity redirect documents)</t>
         </is>
       </c>
       <c r="C266" s="13" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>per-archetype landing page for /assessment's Builder/Crusader/Investor result, reusing lib/content/archetypes.ts. Real content ported in full (top-5 essential-reading list per archetype via allPostsForArchiveQuery, real PathSubscribeForm posting to /api/subscribe, AUTHORITY_ITEMS strip). Real bug fixed vs. legacy: replaced a hand-rolled inline-styled "Path not found" div with a real notFound() (this route's generateStaticParams only ever produces the 3 real keys). Verified live: all 3 archetype routes 200 OK, typecheck/lint clean.</t>
+          <t>hard QA gate, nothing proceeds to DNS cutover until this is complete and tested. First real pass done: extracted all 197 real path= routes from legacy's App.tsx router (not guessed — the actual route table), diffed against this app's real current routes (find src/app -maxdepth 1 -name page.tsx) + next.config.ts's existing redirect sources, normalizing :param/[param] syntax to compare like-for-like. Started at 41 real gaps, closed 10 with new redirects: /attention-theft/{blocker-finder,legal,report,weapons} (legacy registered both a bare AND a /attention-theft/-nested path for each, only the bare ones had redirects before), /find-my-car → /find-my, /the-index → /search (matching the fix already applied to other pages' dead links to it), /supplier-intake-long (bare) + /vendor-intake + /vendor-intake-long (+/:token) → the same real ramprate.com/biochain/supplier-intake destination the token'd path already redirected to, and /spamtoast + /youve-been-reported → / (the live half of legacy's "report a spammer" confrontation flow — a fake IP-fingerprinting/countdown-timer page; the other half, ReportSpammer.tsx, was already a documented drop in Phase 4, this is the same call for its sequel). 21 of the remaining 31 gaps need no redirect — they're /admin/*//analytics//edit/frqncy (internal tools never meant for public discovery) or already-documented intentional defers from Phase 4/7/10 (/clock-keeper-part-2, /ecosystem-map, /friend-gate, /friend-survey/:token, /medicine-sequencing, /m</t>
         </is>
       </c>
       <c r="E266" s="14" t="inlineStr">
@@ -6975,7 +6975,7 @@
       <c r="A267" s="4" t="n"/>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>/my-journey (src/app/my-journey/page.tsx + components/assessments/my-journey-dashboard.tsx)</t>
+          <t>/path/:archetype (src/app/path/[archetype]/page.tsx)</t>
         </is>
       </c>
       <c r="C267" s="13" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>"My Journey Dashboard," real grid/timeline views across all 28 JOURNEY_MAP experiences, category/status filters, phase progress ring, recommended-next card, using the same real useJourneyProgress/JOURNEY_MAP completion tracking every "Find Your X" quiz already writes to (not the narrower tg_assessment_results cookie built for /self-portrait). Legacy's per-quiz scored-result caching (RESULT_KEYS, feeding a mini radar chart) was not ported — no quiz in this migration writes that data either, same honest-degradation call already made for /self-portrait's own composite radar. Fixed a real legacy dead link (/ecosystem-map, a still-unbuilt page) to /self-portrait. Verified live: 200 OK, real content confirmed, typecheck/lint clean.</t>
+          <t>per-archetype landing page for /assessment's Builder/Crusader/Investor result, reusing lib/content/archetypes.ts. Real content ported in full (top-5 essential-reading list per archetype via allPostsForArchiveQuery, real PathSubscribeForm posting to /api/subscribe, AUTHORITY_ITEMS strip). Real bug fixed vs. legacy: replaced a hand-rolled inline-styled "Path not found" div with a real notFound() (this route's generateStaticParams only ever produces the 3 real keys). Verified live: all 3 archetype routes 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E267" s="14" t="inlineStr">
@@ -6998,7 +6998,7 @@
       <c r="A268" s="4" t="n"/>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>/the-open-door (src/app/the-open-door/page.tsx)</t>
+          <t>/my-journey (src/app/my-journey/page.tsx + components/assessments/my-journey-dashboard.tsx)</t>
         </is>
       </c>
       <c r="C268" s="13" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>real press/credibility content: all 10 "Magic Genie" client-pitch prompts (real named targets — Marco Argenti/Goldman Sachs, Adam Smith/Disney, etc.), 18 real client testimonials, all 8 explicitly-labeled satirical "parody" quotes (kept with disclaimers, not presented as real). Real overlap found and reconciled: this page's publications/speaking/podcasts arrays substantially duplicate the already-shipped /published's fuller bibliography — kept only what /published doesn't cover (Forbes + Business Insider bylines, the Clinton Global Initiative keynote, 4 of 5 podcast appearances) and cross-linked to /published for the rest, same reconciliation pattern as /assessments vs /find-my. Real bugs fixed: 3 genie/keynote links pointed externally at tonygreenberg.com/&lt;slug&gt; for posts that are real internal posts in this migration — relinked to /blog/psychedelics-could-become-extractive-capitalism, /blog/boiling-the-human-summit-harvard-kurzweil, /blog/return-on-investment-going-green-going-green-2 (all verified 200); a bare self-link to tonygreenberg.com remapped to /. Ships as a pure Server Component (legacy's FadeIn/Section/editorial-component dependencies don't exist here and weren't needed). Verified live: 200 OK, real content in raw SSR HTML, typecheck/lint clean.</t>
+          <t>"My Journey Dashboard," real grid/timeline views across all 28 JOURNEY_MAP experiences, category/status filters, phase progress ring, recommended-next card, using the same real useJourneyProgress/JOURNEY_MAP completion tracking every "Find Your X" quiz already writes to (not the narrower tg_assessment_results cookie built for /self-portrait). Legacy's per-quiz scored-result caching (RESULT_KEYS, feeding a mini radar chart) was not ported — no quiz in this migration writes that data either, same honest-degradation call already made for /self-portrait's own composite radar. Fixed a real legacy dead link (/ecosystem-map, a still-unbuilt page) to /self-portrait. Verified live: 200 OK, real content confirmed, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E268" s="14" t="inlineStr">
@@ -7021,7 +7021,7 @@
       <c r="A269" s="4" t="n"/>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Homepage "Recent Updates" band (2026-09-29)</t>
+          <t>/the-open-door (src/app/the-open-door/page.tsx)</t>
         </is>
       </c>
       <c r="C269" s="13" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>on the live site (a newer Blog.tsx than _legacy-manus-app/, so rebuilt from the live page's markup), replacing the older "Latest Thinking" pair. Found while doing it: two live essays are missing from Sanity, the-tollbooth-and-the-alternative (Aug 18, 2026, the live site's newest) and what-quest-could-fix. Both were published on live after the legacy snapshot and need importing.</t>
+          <t>real press/credibility content: all 10 "Magic Genie" client-pitch prompts (real named targets — Marco Argenti/Goldman Sachs, Adam Smith/Disney, etc.), 18 real client testimonials, all 8 explicitly-labeled satirical "parody" quotes (kept with disclaimers, not presented as real). Real overlap found and reconciled: this page's publications/speaking/podcasts arrays substantially duplicate the already-shipped /published's fuller bibliography — kept only what /published doesn't cover (Forbes + Business Insider bylines, the Clinton Global Initiative keynote, 4 of 5 podcast appearances) and cross-linked to /published for the rest, same reconciliation pattern as /assessments vs /find-my. Real bugs fixed: 3 genie/keynote links pointed externally at tonygreenberg.com/&lt;slug&gt; for posts that are real internal posts in this migration — relinked to /blog/psychedelics-could-become-extractive-capitalism, /blog/boiling-the-human-summit-harvard-kurzweil, /blog/return-on-investment-going-green-going-green-2 (all verified 200); a bare self-link to tonygreenberg.com remapped to /. Ships as a pure Server Component (legacy's FadeIn/Section/editorial-component dependencies don't exist here and weren't needed). Verified live: 200 OK, real content in raw SSR HTML, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E269" s="14" t="inlineStr">
@@ -7044,7 +7044,7 @@
       <c r="A270" s="4" t="n"/>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>Re-sync the legacy reference</t>
+          <t>Homepage "Recent Updates" band (2026-09-29)</t>
         </is>
       </c>
       <c r="C270" s="13" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>_legacy-manus-app/ is older than what's live (Recent Updates proves it), so visual diffs should be against the live site, not only that folder. Closed 2026-10-08: done the way this item suggests: every comparison since 2026-10-01 is against the live site itself (163 pages + 121 posts on 2026-10-01, 188 pages on 2026-10-07, 18 redesigned pages on 2026-10-08), with _legacy-manus-app/ used only as the code reference.</t>
+          <t>on the live site (a newer Blog.tsx than _legacy-manus-app/, so rebuilt from the live page's markup), replacing the older "Latest Thinking" pair. Found while doing it: two live essays are missing from Sanity, the-tollbooth-and-the-alternative (Aug 18, 2026, the live site's newest) and what-quest-could-fix. Both were published on live after the legacy snapshot and need importing.</t>
         </is>
       </c>
       <c r="E270" s="14" t="inlineStr">
@@ -7067,7 +7067,7 @@
       <c r="A271" s="4" t="n"/>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Visual diff pass: every ported page vs</t>
+          <t>Re-sync the legacy reference</t>
         </is>
       </c>
       <c r="C271" s="13" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>legacy page Closed 2026-10-08: covered by the live-site sweeps above (screenshots and measured title/label/spacing per page, see the 2026-10-01, 10-02, 10-07 and 10-08 entries in this phase). Remaining differences are listed as decisions (Cormorant titles, /find-my header) or deliberate (CONTRIBUTING rule 20).</t>
+          <t>_legacy-manus-app/ is older than what's live (Recent Updates proves it), so visual diffs should be against the live site, not only that folder. Closed 2026-10-08: done the way this item suggests: every comparison since 2026-10-01 is against the live site itself (163 pages + 121 posts on 2026-10-01, 188 pages on 2026-10-07, 18 redesigned pages on 2026-10-08), with _legacy-manus-app/ used only as the code reference.</t>
         </is>
       </c>
       <c r="E271" s="14" t="inlineStr">
@@ -7090,7 +7090,7 @@
       <c r="A272" s="4" t="n"/>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>Padding / spacing on the story pages matched to live (2026-10-01)</t>
+          <t>Visual diff pass: every ported page vs</t>
         </is>
       </c>
       <c r="C272" s="13" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>Measured margins, text column and spacing on 31 pages, live vs a production build, at 375px and 1280px. The "door" story pages were the clear mismatch: live's text column is ~546px (ours was 720px), 20px side margins on phones / 40px on desktop, body text 19px/1.8 on phones and 18px/1.85 on desktop (ours 16px/1.5). Fixed on /the-body, /engine-room, /under-nda, /the-nightstand, /the-web, /the-territory, /about, /intel (Intel uses live's 16.8px/1.9; About's hero line 480px max, 18.4px/1.8). Re-measured: all 8 match live to within 2px (About's column 28px narrower), no sideways scroll at 375px.</t>
+          <t>legacy page Closed 2026-10-08: covered by the live-site sweeps above (screenshots and measured title/label/spacing per page, see the 2026-10-01, 10-02, 10-07 and 10-08 entries in this phase). Remaining differences are listed as decisions (Cormorant titles, /find-my header) or deliberate (CONTRIBUTING rule 20).</t>
         </is>
       </c>
       <c r="E272" s="14" t="inlineStr">
@@ -7113,7 +7113,7 @@
       <c r="A273" s="4" t="n"/>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Header-to-title spacing re-checked (2026-10-02)</t>
+          <t>Padding / spacing on the story pages matched to live (2026-10-01)</t>
         </is>
       </c>
       <c r="C273" s="13" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>The 2026-10-01 note compared different things: live's header wasn't measured (it showed 0), so "96px vs 168px" was really 161px vs 168px from the top of the page. Measured again from the top of the page, live vs a production build, at 375px and 1280px: most pages were already within 10px. Fixed the real gaps: /the-open-door (now live's dark centered hero band, 56px title, 546px text column; title was 72px too high), /start-here (live's 48px/96px top padding; 25px too high on desktop), /invest and /engage (label spacing and live's 32px/51px title; /invest's desktop title was 36px), /impact-dashboard on phones (card edge to edge under the header like live; title was 89px too low). Re-measured: all within 8px of live, no sideways scroll at 375px, no JS errors.</t>
+          <t>Measured margins, text column and spacing on 31 pages, live vs a production build, at 375px and 1280px. The "door" story pages were the clear mismatch: live's text column is ~546px (ours was 720px), 20px side margins on phones / 40px on desktop, body text 19px/1.8 on phones and 18px/1.85 on desktop (ours 16px/1.5). Fixed on /the-body, /engine-room, /under-nda, /the-nightstand, /the-web, /the-territory, /about, /intel (Intel uses live's 16.8px/1.9; About's hero line 480px max, 18.4px/1.8). Re-measured: all 8 match live to within 2px (About's column 28px narrower), no sideways scroll at 375px.</t>
         </is>
       </c>
       <c r="E273" s="14" t="inlineStr">
@@ -7136,7 +7136,7 @@
       <c r="A274" s="4" t="n"/>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>HumanOS headings in capitals like live (2026-10-02, owner said yes)</t>
+          <t>Header-to-title spacing re-checked (2026-10-02)</t>
         </is>
       </c>
       <c r="C274" s="13" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>the 4 headings live capitalises on /humanos (title, "Are you a Maximizer...", "Take the Diagnostic", "The Diagnostic") get uppercase; the words are unchanged. The subpages already matched.</t>
+          <t>The 2026-10-01 note compared different things: live's header wasn't measured (it showed 0), so "96px vs 168px" was really 161px vs 168px from the top of the page. Measured again from the top of the page, live vs a production build, at 375px and 1280px: most pages were already within 10px. Fixed the real gaps: /the-open-door (now live's dark centered hero band, 56px title, 546px text column; title was 72px too high), /start-here (live's 48px/96px top padding; 25px too high on desktop), /invest and /engage (label spacing and live's 32px/51px title; /invest's desktop title was 36px), /impact-dashboard on phones (card edge to edge under the header like live; title was 89px too low). Re-measured: all within 8px of live, no sideways scroll at 375px, no JS errors.</t>
         </is>
       </c>
       <c r="E274" s="14" t="inlineStr">
@@ -7159,7 +7159,7 @@
       <c r="A275" s="4" t="n"/>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>More layout gaps matched to live (2026-10-02)</t>
+          <t>HumanOS headings in capitals like live (2026-10-02, owner said yes)</t>
         </is>
       </c>
       <c r="C275" s="13" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>/series (live's centered 546px column, and a bug fixed: every card kept an empty 240px picture column, squeezing the text; live's per-series picture is one generic placeholder on the Manus proxy, so not copied), /humanos (middle section 900px like live), homepage desktop widths (hero text 804px, Four Doors 1000px, Editor's Picks 1168px, GemSpark edge, section title sizes; live's /blog now shows the homepage), /find-my (photo undimmed and plain background, like live; our site header kept). Re-measured: headings within 3px (/series) to 20px (homepage) of live, no sideways scroll, no JS errors. Note: live's "New here?" tour bar sits over its header and doesn't move the page, so it doesn't affect these numbers.</t>
+          <t>the 4 headings live capitalises on /humanos (title, "Are you a Maximizer...", "Take the Diagnostic", "The Diagnostic") get uppercase; the words are unchanged. The subpages already matched.</t>
         </is>
       </c>
       <c r="E275" s="14" t="inlineStr">
@@ -7182,7 +7182,7 @@
       <c r="A276" s="4" t="n"/>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>Full sweep vs live (2026-10-02)</t>
+          <t>More layout gaps matched to live (2026-10-02)</t>
         </is>
       </c>
       <c r="C276" s="13" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>142 pages (every non-blog page, 3 of each templated set) at 375px and 1280px, title position, text column, title size. Fixed the shared causes: BrewSoul (live wraps most pages in its frame twice, so a second 52px offset plus the category badge; the landing, cities, directory and quiz pages have neither: src/components/brewsoul/brewsoul-main.tsx; intro paragraphs uncapped like live; 38px titles), Kava (live's extra 52px offset), /the-body, /the-nightstand, /the-web (405px top photo like live), the 6 peptide pages (live's 768/896px intro column), /journeys, /pick-up-the-phone, /published, /ecosystem (546px story column and live's text size). Re-measured: 110 of 120 within 40px / 60px of live.</t>
+          <t>/series (live's centered 546px column, and a bug fixed: every card kept an empty 240px picture column, squeezing the text; live's per-series picture is one generic placeholder on the Manus proxy, so not copied), /humanos (middle section 900px like live), homepage desktop widths (hero text 804px, Four Doors 1000px, Editor's Picks 1168px, GemSpark edge, section title sizes; live's /blog now shows the homepage), /find-my (photo undimmed and plain background, like live; our site header kept). Re-measured: headings within 3px (/series) to 20px (homepage) of live, no sideways scroll, no JS errors. Note: live's "New here?" tour bar sits over its header and doesn't move the page, so it doesn't affect these numbers.</t>
         </is>
       </c>
       <c r="E276" s="14" t="inlineStr">
@@ -7205,7 +7205,7 @@
       <c r="A277" s="4" t="n"/>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Sweep leftovers fixed (2026-10-06)</t>
+          <t>Full sweep vs live (2026-10-02)</t>
         </is>
       </c>
       <c r="C277" s="13" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>Ported legacy's exact title sizes, margins and column widths. Measured live vs a production build at 375px and 1280px (H1 distance from the top, H1 size, intro and table widths). Now within 8px and the same title size on /published, /brewsoul/first-sip, /brewsoul/home, /brewsoul/chains (intro 912px like live), /brewsoul/browse, /brewsoul/directory (3-column 952px grid like live), /brewsoul and /brewsoul/quiz (intro 520px), /amplifier (546px column), /diamond-cut, /speaking, /living-declaration, /spirits, /protecting-your-business (tables 730px), and the 5 HumanOS subpages (titles smaller like live, 752px column). No sideways scroll at 375px. Left on purpose: /self-portrait (font matches; our page has a different title and no back link, so it sits 23-57px higher), BrewSoul pages 3-6px off (the shared journey bar row), and the different-layout pages /dharma-finder, /grant-study, /search, /quiz_25q, /soulscore. Also: /brewsoul/quiz rebuilt as a step registry (src/components/brewsoul/brewsoul-quiz/: parent + hook/ + components/step-* + data/), same questions, scoring and look; Back/Skip/Retake use lucide icons. New CONTRIBUTING rule 19 (multi-step flows, FydoPartner pattern). brewsoul-welcome-quiz.tsx (/brewsoul) still has the old shape and text arrows.</t>
+          <t>142 pages (every non-blog page, 3 of each templated set) at 375px and 1280px, title position, text column, title size. Fixed the shared causes: BrewSoul (live wraps most pages in its frame twice, so a second 52px offset plus the category badge; the landing, cities, directory and quiz pages have neither: src/components/brewsoul/brewsoul-main.tsx; intro paragraphs uncapped like live; 38px titles), Kava (live's extra 52px offset), /the-body, /the-nightstand, /the-web (405px top photo like live), the 6 peptide pages (live's 768/896px intro column), /journeys, /pick-up-the-phone, /published, /ecosystem (546px story column and live's text size). Re-measured: 110 of 120 within 40px / 60px of live.</t>
         </is>
       </c>
       <c r="E277" s="14" t="inlineStr">
@@ -7228,7 +7228,7 @@
       <c r="A278" s="4" t="n"/>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>Match live's redesigned pages (2026-10-06, owner said go)</t>
+          <t>Sweep leftovers fixed (2026-10-06)</t>
         </is>
       </c>
       <c r="C278" s="13" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">/self-portrait (live: dark page, progress ring, "N more brushstrokes" lock until 5 assessments), /grant-study and /dharma-finder (live opens straight on question 1, no intro screen), /quiz_25q (live adds a hero picture above the title; rescue it into Sanity first), /search (live: one search box across essays, BrewSoul, peptides, HumanOS, assessments, kava and pages with filter chips). Measure live vs a production build at 375px and 1280px when done. Done 2026-10-06: /grant-study and /dharma-finder open straight on question 1 like live (title block / part header above the first question, live's 546px column, plain page, credit under every question), both rebuilt as step registries (rule 19); measured within 3px of live at the top (dharma's question block within 7px). /quiz_25q's hero rescued into Sanity and placed like live (within 2px). Found and fixed on the way: on the deployed copy /grant-study's answer buttons could not be clicked (the themed page background was fixed z-0, painted over the quiz); ThemedBackground is now -z-10 pointer-events-none (backgrounds unchanged on all 21 pages that use it), and the shared email gate no longer scrolls sideways on phones. Both quizzes clicked through to results in Chrome and Safari. /self-portrait restyled to live (dark page, "The Composite You", progress ring, "N More Brushstrokes Needed" lock until 5 done, live's copy) on our real cookie data; within 3px of live at both widths; tested with 0, 2 and 6 completed. Counts are ours (13 </t>
+          <t>Ported legacy's exact title sizes, margins and column widths. Measured live vs a production build at 375px and 1280px (H1 distance from the top, H1 size, intro and table widths). Now within 8px and the same title size on /published, /brewsoul/first-sip, /brewsoul/home, /brewsoul/chains (intro 912px like live), /brewsoul/browse, /brewsoul/directory (3-column 952px grid like live), /brewsoul and /brewsoul/quiz (intro 520px), /amplifier (546px column), /diamond-cut, /speaking, /living-declaration, /spirits, /protecting-your-business (tables 730px), and the 5 HumanOS subpages (titles smaller like live, 752px column). No sideways scroll at 375px. Left on purpose: /self-portrait (font matches; our page has a different title and no back link, so it sits 23-57px higher), BrewSoul pages 3-6px off (the shared journey bar row), and the different-layout pages /dharma-finder, /grant-study, /search, /quiz_25q, /soulscore. Also: /brewsoul/quiz rebuilt as a step registry (src/components/brewsoul/brewsoul-quiz/: parent + hook/ + components/step-* + data/), same questions, scoring and look; Back/Skip/Retake use lucide icons. New CONTRIBUTING rule 19 (multi-step flows, FydoPartner pattern). brewsoul-welcome-quiz.tsx (/brewsoul) still has the old shape and text arrows.</t>
         </is>
       </c>
       <c r="E278" s="14" t="inlineStr">
@@ -7251,7 +7251,7 @@
       <c r="A279" s="4" t="n"/>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Still different from live (decided 2026-10-09)</t>
+          <t>Match live's redesigned pages (2026-10-06, owner said go)</t>
         </is>
       </c>
       <c r="C279" s="13" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>blog posts (done) (done 2026-10-07, see Phase 5); /find-my on live hides the site header. /walk-through is a 404 on live now. Owner: keep our site menu on /find-my (visitors can still reach the rest of the site); nothing left to change.</t>
+          <t xml:space="preserve">/self-portrait (live: dark page, progress ring, "N more brushstrokes" lock until 5 assessments), /grant-study and /dharma-finder (live opens straight on question 1, no intro screen), /quiz_25q (live adds a hero picture above the title; rescue it into Sanity first), /search (live: one search box across essays, BrewSoul, peptides, HumanOS, assessments, kava and pages with filter chips). Measure live vs a production build at 375px and 1280px when done. Done 2026-10-06: /grant-study and /dharma-finder open straight on question 1 like live (title block / part header above the first question, live's 546px column, plain page, credit under every question), both rebuilt as step registries (rule 19); measured within 3px of live at the top (dharma's question block within 7px). /quiz_25q's hero rescued into Sanity and placed like live (within 2px). Found and fixed on the way: on the deployed copy /grant-study's answer buttons could not be clicked (the themed page background was fixed z-0, painted over the quiz); ThemedBackground is now -z-10 pointer-events-none (backgrounds unchanged on all 21 pages that use it), and the shared email gate no longer scrolls sideways on phones. Both quizzes clicked through to results in Chrome and Safari. /self-portrait restyled to live (dark page, "The Composite You", progress ring, "N More Brushstrokes Needed" lock until 5 done, live's copy) on our real cookie data; within 3px of live at both widths; tested with 0, 2 and 6 completed. Counts are ours (13 </t>
         </is>
       </c>
       <c r="E279" s="14" t="inlineStr">
@@ -7274,7 +7274,7 @@
       <c r="A280" s="4" t="n"/>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>Design change on live (owner: "match live", 2026-10-09)</t>
+          <t>Still different from live (decided 2026-10-09)</t>
         </is>
       </c>
       <c r="C280" s="13" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>live's story pages now use Cormorant Garamond for titles (ours: Playfair Display), a lighter title weight (400 vs our 700), and a red eyebrow label (#8E1E25, wider letter spacing) instead of our gold. A site-wide font swap is a design call, so not done. Done 2026-10-09: a fresh sweep of 163 live pages found live has since dropped Cormorant from the story pages (only /living-declaration uses it, ours already matched) and mostly uses Playfair; the real differences were fixed: every heading on /attention-theft in Fraunces 700 (section-wide, like Kava), /supplier-intake title in the system serif, and live's fluid title sizes on /about, /articles, /the-letter, /the-philosophy, /clock-keeper-part-2, /living-declaration (measured at 375/640/820/1024/1280, now identical). Label colours stay darker than live on purpose (contrast, rule 20).</t>
+          <t>blog posts (done) (done 2026-10-07, see Phase 5); /find-my on live hides the site header. /walk-through is a 404 on live now. Owner: keep our site menu on /find-my (visitors can still reach the rest of the site); nothing left to change.</t>
         </is>
       </c>
       <c r="E280" s="14" t="inlineStr">
@@ -7297,7 +7297,7 @@
       <c r="A281" s="4" t="n"/>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Link check across all ported pages (no 404s, no broken internal cross-references)</t>
+          <t>Design change on live (owner: "match live", 2026-10-09)</t>
         </is>
       </c>
       <c r="C281" s="13" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>First full pass done 2026-09-29 (510 pages crawled from the sitemap plus every internal link, on a production build). Fixed in code: /brewsoul/coffee/…-tarrazú 404 (the route got the id still percent-encoded), 30+ links that went through the /assessments/* redirects, /find-your-me's dead Homeaglow link, the two root-level Iboga essay links, and the dead FauxTony nav item. Fixed as Sanity drafts (scripts/fix-blog-body-links.ts, 14 posts): broken post links, leaked !… placeholder text, Energy Is Money's split author bio, and scraped WordPress furniture ("Share this / Related / You Might Also Like / Copyright", "Show More / Top News", [mc4wp_form]). Left for a decision: /framework's "Ask FauxTony" button, when-healing-becomes-extraction's two links to a Dr. Lee case file that doesn't exist, and the-clock-keeper-chronicles-part-1's link to the deferred /clock-keeper-part-2. Re-run after the drafts are published. 2026-10-01 re-run (local production build, all 498 sitemap URLs load; 440 unique internal links): 5 broken. Fixed as a Sanity draft: molecule-as-mirror-10-what-the-pioneers-know's "Final installment" link pointed at a non-existent part-10 slug (now part 11; live also shows that line twice, kept). Already fixed in a waiting draft: forever-chemicals-... → /blog/psychedelic-readiness-index. Still the 3 known decisions: /fauxtony (from /framework), /clock-keeper-part-2, /blog/the-case-file-dr-samuel-lee. 2026-10-08 re-run (production build, all 497 sitemap pages, 453 unique i</t>
+          <t>live's story pages now use Cormorant Garamond for titles (ours: Playfair Display), a lighter title weight (400 vs our 700), and a red eyebrow label (#8E1E25, wider letter spacing) instead of our gold. A site-wide font swap is a design call, so not done. Done 2026-10-09: a fresh sweep of 163 live pages found live has since dropped Cormorant from the story pages (only /living-declaration uses it, ours already matched) and mostly uses Playfair; the real differences were fixed: every heading on /attention-theft in Fraunces 700 (section-wide, like Kava), /supplier-intake title in the system serif, and live's fluid title sizes on /about, /articles, /the-letter, /the-philosophy, /clock-keeper-part-2, /living-declaration (measured at 375/640/820/1024/1280, now identical). Label colours stay darker than live on purpose (contrast, rule 20).</t>
         </is>
       </c>
       <c r="E281" s="14" t="inlineStr">
@@ -7320,7 +7320,7 @@
       <c r="A282" s="4" t="n"/>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>Sitemap: no noindex pages (2026-10-08)</t>
+          <t>Link check across all ported pages (no 404s, no broken internal cross-references)</t>
         </is>
       </c>
       <c r="C282" s="13" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>the password-locked /blog/you-are-the-moat was in the sitemap while telling Google not to index it (a Search Console sitemap warning). Gated posts and posts that redirect are now left out (src/app/sitemap.ts); all 497 sitemap addresses return 200 with a matching canonical and no noindex. The 82 warnings Search Console shows are for the old live sitemap, so re-check them after cutover.</t>
+          <t>First full pass done 2026-09-29 (510 pages crawled from the sitemap plus every internal link, on a production build). Fixed in code: /brewsoul/coffee/…-tarrazú 404 (the route got the id still percent-encoded), 30+ links that went through the /assessments/* redirects, /find-your-me's dead Homeaglow link, the two root-level Iboga essay links, and the dead FauxTony nav item. Fixed as Sanity drafts (scripts/fix-blog-body-links.ts, 14 posts): broken post links, leaked !… placeholder text, Energy Is Money's split author bio, and scraped WordPress furniture ("Share this / Related / You Might Also Like / Copyright", "Show More / Top News", [mc4wp_form]). Left for a decision: /framework's "Ask FauxTony" button, when-healing-becomes-extraction's two links to a Dr. Lee case file that doesn't exist, and the-clock-keeper-chronicles-part-1's link to the deferred /clock-keeper-part-2. Re-run after the drafts are published. 2026-10-01 re-run (local production build, all 498 sitemap URLs load; 440 unique internal links): 5 broken. Fixed as a Sanity draft: molecule-as-mirror-10-what-the-pioneers-know's "Final installment" link pointed at a non-existent part-10 slug (now part 11; live also shows that line twice, kept). Already fixed in a waiting draft: forever-chemicals-... → /blog/psychedelic-readiness-index. Still the 3 known decisions: /fauxtony (from /framework), /clock-keeper-part-2, /blog/the-case-file-dr-samuel-lee. 2026-10-08 re-run (production build, all 497 sitemap pages, 453 unique i</t>
         </is>
       </c>
       <c r="E282" s="14" t="inlineStr">
@@ -7343,17 +7343,17 @@
       <c r="A283" s="4" t="n"/>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Lighthouse pass (performance/accessibility/SEO) on top 20 pages by traffic 2026-09-30, 20 key pages (no traffic data yet), local production …</t>
-        </is>
-      </c>
-      <c r="C283" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Sitemap: no noindex pages (2026-10-08)</t>
+        </is>
+      </c>
+      <c r="C283" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>build, mobile: averages performance 87, accessibility 99→100, best practices 100, SEO 92→100, CLS 0 everywhere. Fixed: public/robots.txt had an LLMs: line (not a real directive) that made Google treat the whole file as invalid, now a comment; h3/h4 headings skipping a level on /assessments, /kava, /peptide-watch (same look, right tag); the Kava and /attention-theft back-arrow links had no accessible name on phones; two small phone-width contrast misses. Left: performance is local-machine only (±10-15 points, see CONTRIBUTING.md); the slowest were / 76 (LCP 5.2 s), /psychedelic-readiness-index 82, /iboga-ibogaine 83. Re-run against the Netlify deploy before launch. 2026-10-06 re-run against the Netlify deploy (14 key pages, mobile): accessibility 100 and CLS 0 on every page, SEO clean (only the expected netlify.app noindex), performance 77-97 held back by 3-4 s LCP. Fixed: all 21 hero images moved off the deprecated priority prop to fetchPriority="high" + loading="eager" (Next 16); /iboga-ibogaine hero and the first card on /blog and category pages no longer lazy-loaded; sizes on the Four Doors cards (~150 KiB per page), /humanos diagram (~100 KiB) and /about headshot; urlFor no longer imports the Sanity client, so ~115 KB of Sanity client code stopped loading on / and /blog; React hydration error #418 on / and /blog (post dates) gone, checked in two time zones; /blog is static again; empty icon &lt;th&gt;s on /iboga-ibogaine labelled; category page reads use sanityFetch(). Left: se</t>
+          <t>the password-locked /blog/you-are-the-moat was in the sitemap while telling Google not to index it (a Search Console sitemap warning). Gated posts and posts that redirect are now left out (src/app/sitemap.ts); all 497 sitemap addresses return 200 with a matching canonical and no noindex. The 82 warnings Search Console shows are for the old live sitemap, so re-check them after cutover.</t>
         </is>
       </c>
       <c r="E283" s="14" t="inlineStr">
@@ -7366,17 +7366,17 @@
       <c r="A284" s="4" t="n"/>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>No Manus links anywhere (2026-10-09, owner: "drop them everywhere")</t>
-        </is>
-      </c>
-      <c r="C284" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Lighthouse pass (performance/accessibility/SEO) on top 20 pages by traffic 2026-09-30, 20 key pages (no traffic data yet), local production …</t>
+        </is>
+      </c>
+      <c r="C284" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>every *.manus.space link removed from code and essays. Lists of "try this next" apps lose those entries (journey tracker, Find Your Me results and next steps, /find-my, search directory, Sake and Grant Study results, BrewSoul footer, The Mirror); The Magnetic Partner's and The Temple Keeper's next step now go to their first in-site assessment (/grant-study, /consciousness-scale); their empty "Find Your _" section hides itself; /recent-creations, /spirits and /ecosystem-map keep the cards, unlinked. Clarisse Abelarde now links to her own site clarisseartist.com (owner gave it) on /about and in essays. Essays: lib/sanity/portable-text.tsx rewrites tonygreenberg.manus.space/&lt;path&gt; to /&lt;path&gt;, clarisseart.manus.space to clarisseartist.com (same paths), and renders other Manus app links as plain text (no Sanity drafts). Verified on a production build: no clickable *.manus.space link in any page, no manus.space in any browser script; 13 affected pages load (200).</t>
+          <t>build, mobile: averages performance 87, accessibility 99→100, best practices 100, SEO 92→100, CLS 0 everywhere. Fixed: public/robots.txt had an LLMs: line (not a real directive) that made Google treat the whole file as invalid, now a comment; h3/h4 headings skipping a level on /assessments, /kava, /peptide-watch (same look, right tag); the Kava and /attention-theft back-arrow links had no accessible name on phones; two small phone-width contrast misses. Left: performance is local-machine only (±10-15 points, see CONTRIBUTING.md); the slowest were / 76 (LCP 5.2 s), /psychedelic-readiness-index 82, /iboga-ibogaine 83. Re-run against the Netlify deploy before launch. 2026-10-06 re-run against the Netlify deploy (14 key pages, mobile): accessibility 100 and CLS 0 on every page, SEO clean (only the expected netlify.app noindex), performance 77-97 held back by 3-4 s LCP. Fixed: all 21 hero images moved off the deprecated priority prop to fetchPriority="high" + loading="eager" (Next 16); /iboga-ibogaine hero and the first card on /blog and category pages no longer lazy-loaded; sizes on the Four Doors cards (~150 KiB per page), /humanos diagram (~100 KiB) and /about headshot; urlFor no longer imports the Sanity client, so ~115 KB of Sanity client code stopped loading on / and /blog; React hydration error #418 on / and /blog (post dates) gone, checked in two time zones; /blog is static again; empty icon &lt;th&gt;s on /iboga-ibogaine labelled; category page reads use sanityFetch(). Left: se</t>
         </is>
       </c>
       <c r="E284" s="14" t="inlineStr">
@@ -7389,7 +7389,7 @@
       <c r="A285" s="4" t="n"/>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Owner answers, round 2 (2026-10-09)</t>
+          <t>No Manus links anywhere (2026-10-09, owner: "drop them everywhere")</t>
         </is>
       </c>
       <c r="C285" s="13" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>(1) real counts instead of live's typed numbers: /charity-scorecard intro and description ("98"/"Ninety-eight" → STATS.totalCharities = 103), /impact-dashboard ("100" → passed in from the page so the browser doesn't load the charity list), /the-index (prop), search directory coffees 103 → 107 (typed, with a note, since it ships to the search pop-up); (2) The Mirror results no longer list the 4 *.manus.space apps (the "Explore further" section hides when empty); (3) /framework's "Ask FauxTony" button and its lead-in line removed; the Dr. Lee case-file link (4 places in when-healing-becomes-extraction, original and updated versions) renders as plain text through a DEAD_INTERNAL_LINKS list in lib/sanity/portable-text.tsx (no Sanity draft needed); (4) B Corp: checked live, nothing shown on either site, no change. Verified on a production build: the counts read 103, /framework has no FauxTony block, the essay has 0 links to the case file and keeps the words, /the-index shows "103 charities" when searching "charity".</t>
+          <t>every *.manus.space link removed from code and essays. Lists of "try this next" apps lose those entries (journey tracker, Find Your Me results and next steps, /find-my, search directory, Sake and Grant Study results, BrewSoul footer, The Mirror); The Magnetic Partner's and The Temple Keeper's next step now go to their first in-site assessment (/grant-study, /consciousness-scale); their empty "Find Your _" section hides itself; /recent-creations, /spirits and /ecosystem-map keep the cards, unlinked. Clarisse Abelarde now links to her own site clarisseartist.com (owner gave it) on /about and in essays. Essays: lib/sanity/portable-text.tsx rewrites tonygreenberg.manus.space/&lt;path&gt; to /&lt;path&gt;, clarisseart.manus.space to clarisseartist.com (same paths), and renders other Manus app links as plain text (no Sanity drafts). Verified on a production build: no clickable *.manus.space link in any page, no manus.space in any browser script; 13 affected pages load (200).</t>
         </is>
       </c>
       <c r="E285" s="14" t="inlineStr">
@@ -7412,7 +7412,7 @@
       <c r="A286" s="4" t="n"/>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>Arrows in buttons and links are icons (2026-10-09, owner said yes)</t>
+          <t>Owner answers, round 2 (2026-10-09)</t>
         </is>
       </c>
       <c r="C286" s="13" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>113 typed arrows in 52 files (button and link labels, "Next"/"See My Results" toggles, decorative arrow spans, the walk-through "See the..." labels, the Letter's "I'm in" button) replaced with lucide ArrowRight/ArrowLeft (size-[1em], inside inline-flex items-center gap-1.5, so the parent layout is untouched). Left as content on purpose: arrows inside Tony's text and data (health findings, origins, iboga compass options, process flows like "Inherit → Wake → Choose → Act", share text), the "← you" marker on the consciousness scale, and &lt;option&gt; sort labels (an option can't hold an icon). Checked on 16 pages at 375 and 1280: no typed arrow left in any link or button, no sideways scroll, no JS errors; close-up screenshots of the new icons.</t>
+          <t>(1) real counts instead of live's typed numbers: /charity-scorecard intro and description ("98"/"Ninety-eight" → STATS.totalCharities = 103), /impact-dashboard ("100" → passed in from the page so the browser doesn't load the charity list), /the-index (prop), search directory coffees 103 → 107 (typed, with a note, since it ships to the search pop-up); (2) The Mirror results no longer list the 4 *.manus.space apps (the "Explore further" section hides when empty); (3) /framework's "Ask FauxTony" button and its lead-in line removed; the Dr. Lee case-file link (4 places in when-healing-becomes-extraction, original and updated versions) renders as plain text through a DEAD_INTERNAL_LINKS list in lib/sanity/portable-text.tsx (no Sanity draft needed); (4) B Corp: checked live, nothing shown on either site, no change. Verified on a production build: the counts read 103, /framework has no FauxTony block, the essay has 0 links to the case file and keeps the words, /the-index shows "103 charities" when searching "charity".</t>
         </is>
       </c>
       <c r="E286" s="14" t="inlineStr">
@@ -7435,7 +7435,7 @@
       <c r="A287" s="4" t="n"/>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Category pages pre-built (2026-10-09)</t>
+          <t>Arrows in buttons and links are icons (2026-10-09, owner said yes)</t>
         </is>
       </c>
       <c r="C287" s="13" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>/blog/category/[slug] read ?page=N, so every category page was rendered on each request (slower first byte, flagged in the Lighthouse notes). Page numbers are now part of the address (/blog/category/&lt;slug&gt;/page/&lt;n&gt;, generateStaticParams, dynamicParams = false), shared code in src/components/blog/category-listing.tsx; old ?page=N links 308 to the new address (pages 2+ only, so no loop), /page/1 308s to the plain address, a page past the end is a 404; "All essays" back link uses an icon. Verified on a production build: route table shows every category page as pre-built (9 page-1s, 7 later pages), titles and canonicals per page, Previous/Next links, the redirects and the 404s.</t>
+          <t>113 typed arrows in 52 files (button and link labels, "Next"/"See My Results" toggles, decorative arrow spans, the walk-through "See the..." labels, the Letter's "I'm in" button) replaced with lucide ArrowRight/ArrowLeft (size-[1em], inside inline-flex items-center gap-1.5, so the parent layout is untouched). Left as content on purpose: arrows inside Tony's text and data (health findings, origins, iboga compass options, process flows like "Inherit → Wake → Choose → Act", share text), the "← you" marker on the consciousness scale, and &lt;option&gt; sort labels (an option can't hold an icon). Checked on 16 pages at 375 and 1280: no typed arrow left in any link or button, no sideways scroll, no JS errors; close-up screenshots of the new icons.</t>
         </is>
       </c>
       <c r="E287" s="14" t="inlineStr">
@@ -7458,7 +7458,7 @@
       <c r="A288" s="4" t="n"/>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>Error pages (2026-10-09, owner asked)</t>
+          <t>Category pages pre-built (2026-10-09)</t>
         </is>
       </c>
       <c r="C288" s="13" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>404 page now sets its own title ("Page not found") as a server page around live's 3-second redirect (not-found.tsx + components/not-found-redirect.tsx), arrow as an icon; page error screen (error.tsx) uses Next 16's retry (re-fetches), shows a reference code for the server logs, links home and to the site index; new global-error.tsx for failures in the root layout itself (own &lt;html&gt;, plain links). Verified on a production build: missing page, missing essay and missing Kava page return 404 with the right title; a test page that throws returns 500 with the error screen, "Try again" re-fetches; phone and laptop, no sideways scroll (test page removed).</t>
+          <t>/blog/category/[slug] read ?page=N, so every category page was rendered on each request (slower first byte, flagged in the Lighthouse notes). Page numbers are now part of the address (/blog/category/&lt;slug&gt;/page/&lt;n&gt;, generateStaticParams, dynamicParams = false), shared code in src/components/blog/category-listing.tsx; old ?page=N links 308 to the new address (pages 2+ only, so no loop), /page/1 308s to the plain address, a page past the end is a 404; "All essays" back link uses an icon. Verified on a production build: route table shows every category page as pre-built (9 page-1s, 7 later pages), titles and canonicals per page, Previous/Next links, the redirects and the 404s.</t>
         </is>
       </c>
       <c r="E288" s="14" t="inlineStr">
@@ -7481,7 +7481,7 @@
       <c r="A289" s="4" t="n"/>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>SEO audit fixes (2026-10-06)</t>
+          <t>Error pages (2026-10-09, owner asked)</t>
         </is>
       </c>
       <c r="C289" s="13" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
+          <t>404 page now sets its own title ("Page not found") as a server page around live's 3-second redirect (not-found.tsx + components/not-found-redirect.tsx), arrow as an icon; page error screen (error.tsx) uses Next 16's retry (re-fetches), shows a reference code for the server logs, links home and to the site index; new global-error.tsx for failures in the root layout itself (own &lt;html&gt;, plain links). Verified on a production build: missing page, missing essay and missing Kava page return 404 with the right title; a test page that throws returns 500 with the error screen, "Try again" re-fetches; phone and laptop, no sideways scroll (test page removed).</t>
         </is>
       </c>
       <c r="E289" s="14" t="inlineStr">
@@ -7504,17 +7504,17 @@
       <c r="A290" s="4" t="n"/>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>SEO audit items needing a yes (2026-10-06)</t>
-        </is>
-      </c>
-      <c r="C290" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>SEO audit fixes (2026-10-06)</t>
+        </is>
+      </c>
+      <c r="C290" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+          <t>Checked an outside audit point by point against the code. Fixed: Core Themes cards linked to /?theme=…#essays-archive (not crawlable, counts from a stale hand-kept list) and now link to /blog/category/&lt;slug&gt; with real counts (21/25/20/14, matching the archive pills; THEME_MAP and the ?theme= filter removed); Four Doors cards were &lt;button&gt;s, now real links that still open the modal on a plain click; "DIAGNOSE · ENGAGE" now link to /find-my and /engage; one shared formatPostDate (Asia/Kolkata, src/lib/format-post-date.ts) so a post no longer shows two different dates; the title repeated as the first body paragraph is dropped at render time (legacyBodyLayout); essay cards are h3 under a section h2 (archive, Read next), h2 only on category/search; heading glyphs (◆ ✦) hidden from screen readers; posts send BlogPosting with the author tied to the site Person (@id) plus a BreadcrumbList; descriptive alt on the homepage and BrewSoul heroes; homepage OG image cropped to 1200x630 JPEG. Already fine (audit could not see it): Person/Article schema, Netlify noindex, robots.txt, sitemap, header nav and search, Amazon links carry no affiliate tag. Checked on a production build: type check, lint, build, status codes, browser click test at 375px, no console errors. Implementation pack (Mohammad Danish, 2026-10-05) checked the same day: added og:type/og:site_name back on the 6 pages with their own openGraph (a page-level openGraph replaces the layout one), twitter:creator, and on posts og:url</t>
         </is>
       </c>
       <c r="E290" s="14" t="inlineStr">
@@ -7527,7 +7527,7 @@
       <c r="A291" s="4" t="n"/>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+          <t>SEO audit items needing a yes (2026-10-06)</t>
         </is>
       </c>
       <c r="C291" s="15" t="inlineStr">
@@ -7535,7 +7535,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D291" s="4" t="inlineStr"/>
+      <c r="D291" s="4" t="inlineStr">
+        <is>
+          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+        </is>
+      </c>
       <c r="E291" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -7546,19 +7550,15 @@
       <c r="A292" s="4" t="n"/>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
-        </is>
-      </c>
-      <c r="C292" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D292" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
-        </is>
-      </c>
+          <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
+        </is>
+      </c>
+      <c r="C292" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D292" s="4" t="inlineStr"/>
       <c r="E292" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
@@ -7569,7 +7569,7 @@
       <c r="A293" s="4" t="n"/>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>"Keep going" strip above the footer on every page (2026-10-07)</t>
+          <t>Restore/adapt the manus.space triple-layer noindex lockdown pattern for any remaining staging URLs</t>
         </is>
       </c>
       <c r="C293" s="13" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>legacy's WhereNext (deferred in Phase 3, never picked up) with its per-page suggestions, Home · Site Index · All Assessments; links pointed at current routes.</t>
+          <t>2026-10-01: the Netlify copy (tonygreenberg-website.netlify.app) and every deploy preview had no noindex at all, so Google could index a duplicate of the site. next.config.ts headers() now sends X-Robots-Tag: noindex, nofollow on any *.netlify.app host only; tonygreenberg.com is unaffected, so nothing to remove at cutover. Tested with Host headers on a production build.</t>
         </is>
       </c>
       <c r="E293" s="14" t="inlineStr">
@@ -7592,7 +7592,7 @@
       <c r="A294" s="4" t="n"/>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Live-only and redesigned pages from the 2026-10-07 page sweep (188 pages compared with live)</t>
+          <t>"Keep going" strip above the footer on every page (2026-10-07)</t>
         </is>
       </c>
       <c r="C294" s="13" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>/the-index rebuilt from live's code (20 concepts, related-word search across essays and site pages, full-text search on the server, "three related places to go next"; the old redirect to /search removed and its links, including the "Site Index" link in "Keep going", point at it again); /the-mirror (and /life-assessment) opens on live's intro (dark hero, "What We Measure" with the six areas, "The Ecosystem"), rebuilt as a step registry (rule 19); /essays header, order and column like live; /about "What They Say" styled like live (live picks 3 of the same 19 quotes at random; ours shows a fixed 3 so they're in the server HTML); /impact-futurism list titles and subtitles; /supplier-intake is a real page again with live's Stage 1 form; /seven-doors and /projects redirect home like live; /impact, /health, /library, /built-on-manus, /heroes are 404 on live too. Left as is on purpose: /blog stays our archive page (on live it repeats the homepage), the email gates on /framework and /peptide-supply-chain, the attention-theft Wall of Shame.</t>
+          <t>legacy's WhereNext (deferred in Phase 3, never picked up) with its per-page suggestions, Home · Site Index · All Assessments; links pointed at current routes.</t>
         </is>
       </c>
       <c r="E294" s="14" t="inlineStr">
@@ -7615,7 +7615,7 @@
       <c r="A295" s="4" t="n"/>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>/alex-azzi locked like live (2026-10-07, owner said match it)</t>
+          <t>Live-only and redesigned pages from the 2026-10-07 page sweep (188 pages compared with live)</t>
         </is>
       </c>
       <c r="C295" s="13" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>same server-checked password as the locked essay (GATED_POST_PASSWORD, now also set in Netlify), live's "Restricted Access" screen, the report not in the page until unlocked, out of search and the sitemap.</t>
+          <t>/the-index rebuilt from live's code (20 concepts, related-word search across essays and site pages, full-text search on the server, "three related places to go next"; the old redirect to /search removed and its links, including the "Site Index" link in "Keep going", point at it again); /the-mirror (and /life-assessment) opens on live's intro (dark hero, "What We Measure" with the six areas, "The Ecosystem"), rebuilt as a step registry (rule 19); /essays header, order and column like live; /about "What They Say" styled like live (live picks 3 of the same 19 quotes at random; ours shows a fixed 3 so they're in the server HTML); /impact-futurism list titles and subtitles; /supplier-intake is a real page again with live's Stage 1 form; /seven-doors and /projects redirect home like live; /impact, /health, /library, /built-on-manus, /heroes are 404 on live too. Left as is on purpose: /blog stays our archive page (on live it repeats the homepage), the email gates on /framework and /peptide-supply-chain, the attention-theft Wall of Shame.</t>
         </is>
       </c>
       <c r="E295" s="14" t="inlineStr">
@@ -7638,7 +7638,7 @@
       <c r="A296" s="4" t="n"/>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>Live's title fonts and sizes (2026-10-07, "fix the style")</t>
+          <t>/alex-azzi locked like live (2026-10-07, owner said match it)</t>
         </is>
       </c>
       <c r="C296" s="13" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>measured every page's title font, weight, size and label colour on live vs ours (136 pages). Now like live: Kava headings in Fraunces, HumanOS in Space Grotesk, the peptide tools / charity scorecard / thesis threads in the system serif, America Unbundled in the Iowan Old Style stack at live's size, /akbar in Fraunces 900, friend-gate and post-intervention in Georgia, and live's title sizes on peptide-matrix, peptide-supply-chain, rip-peptide-sciences and the HumanOS pages. Fonts load only on the pages that use them (src/lib/fonts/page-fonts.ts). Label colours stay the darker AA-contrast versions where live's lighter ones fail on a light background.</t>
+          <t>same server-checked password as the locked essay (GATED_POST_PASSWORD, now also set in Netlify), live's "Restricted Access" screen, the report not in the page until unlocked, out of search and the sitemap.</t>
         </is>
       </c>
       <c r="E296" s="14" t="inlineStr">
@@ -7661,7 +7661,7 @@
       <c r="A297" s="4" t="n"/>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Peptide page images rescued into Sanity and wired (2026-10-07)</t>
+          <t>Live's title fonts and sizes (2026-10-07, "fix the style")</t>
         </is>
       </c>
       <c r="C297" s="13" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>/peptide-watch hero plus its 11 section banners, /peptide-matrix and /peptide-supply-chain heroes, the /peptide-hall-of-shame hero (scripts/rescue-2026-10-07-peptide-images.ts, logged in docs/ai/manus-media-rescue.md).</t>
+          <t>measured every page's title font, weight, size and label colour on live vs ours (136 pages). Now like live: Kava headings in Fraunces, HumanOS in Space Grotesk, the peptide tools / charity scorecard / thesis threads in the system serif, America Unbundled in the Iowan Old Style stack at live's size, /akbar in Fraunces 900, friend-gate and post-intervention in Georgia, and live's title sizes on peptide-matrix, peptide-supply-chain, rip-peptide-sciences and the HumanOS pages. Fonts load only on the pages that use them (src/lib/fonts/page-fonts.ts). Label colours stay the darker AA-contrast versions where live's lighter ones fail on a light background.</t>
         </is>
       </c>
       <c r="E297" s="14" t="inlineStr">
@@ -7684,7 +7684,7 @@
       <c r="A298" s="4" t="n"/>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>Live's editorial redesign, first group (2026-10-07)</t>
+          <t>Peptide page images rescued into Sanity and wired (2026-10-07)</t>
         </is>
       </c>
       <c r="C298" s="13" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
+          <t>/peptide-watch hero plus its 11 section banners, /peptide-matrix and /peptide-supply-chain heroes, the /peptide-hall-of-shame hero (scripts/rescue-2026-10-07-peptide-images.ts, logged in docs/ai/manus-media-rescue.md).</t>
         </is>
       </c>
       <c r="E298" s="14" t="inlineStr">
@@ -7707,7 +7707,7 @@
       <c r="A299" s="4" t="n"/>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Live's redesign, second group (done 2026-10-08)</t>
+          <t>Live's editorial redesign, first group (2026-10-07)</t>
         </is>
       </c>
       <c r="C299" s="13" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>re-measured all 18 pages on live vs a fresh production build (title font/size/weight/colour, labels, hero images). Already matching from 2026-10-07: /the-web, /spirits, /iboga-ibogaine (weight 800), /living-declaration, BrewSoul photo on /brewsoul, /brewsoul/browse, /brewsoul/first-sip (live has none there either), /quiz_25q, /recent-creations. Fixed today: /find-your-journey (64px title, red label), /impact-dashboard (64px title in essay ink, label spacing), red labels on /published and /speaking (plus its "rooms" chips), /soulscore "by ImpactSoul" label, /pri-calibration title (weight 900, solid cream, was a purple gradient), /clients (live's narrow 546px column for the whole page, 56px title, roomier stats band, cards 2 per row; two static inline styles moved to classes), /brewsoul/guest (live's BrewSoul photo on the guest card instead of "SN" initials, labels in capitals), /humanos/connect (cards line up with the title), /peptide-hall-of-shame (stats and label readable light gold; were dark gold on dark). Typed arrows on the touched links are icons now (rule 18). Deliberately not copied from live (new CONTRIBUTING rule 20, owner 2026-10-08): red labels on dark bands use #E07A80 (live's #8E1E25 on black is about 2:1, unreadable); /recent-creations keeps our darker label colours (live's fail contrast on white); /humanos/connect keeps "Start Reading" (that card links to the philosophy page, the quiz live's "Start the Assessment" implies doesn't exist). Checked: type check, l</t>
+          <t>dark top sections, narrow single text column, short red section rules and dark call-to-action bands on /invest, /amplifier, /community (now "Sign In to Join the Community", linking our real sign-in; live's made-up counters left out), /framework, /the-letter (daily provocation with "Share this thought" and "Search past provocations"), /engage, /diamond-cut, /ecosystem and the homepage's "The thinking doesn't stop here" band. Kept on purpose: AA-contrast colours where live's fail, "Enter the Gate" instead of live's $5,000 checkout on /diamond-cut.</t>
         </is>
       </c>
       <c r="E299" s="14" t="inlineStr">
@@ -7730,7 +7730,7 @@
       <c r="A300" s="4" t="n"/>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>BrewSoul top of page (2026-10-08, owner: "button in the center at the top doesn't look good")</t>
+          <t>Live's redesign, second group (done 2026-10-08)</t>
         </is>
       </c>
       <c r="C300" s="13" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>the category badge ("Deep Research" etc.) sat centred in an empty strip, squeezed against the hero, because we copied live's doubled 52px top gap. Now one gap everywhere and the badge floats in the top-left corner, lined up with the BrewSoul logo (brewsoul-main.tsx, category-badge.tsx); checked on all 26 badge pages at 3 widths that it covers nothing. BrewSoul menu: on tablets (768-1023px) the links were cut off and "More" was hidden with no menu button at all; now the menu button shows below 1024px, 5 links + "More" from 1024px, all 8 from 1280px, "More" always visible.</t>
+          <t>re-measured all 18 pages on live vs a fresh production build (title font/size/weight/colour, labels, hero images). Already matching from 2026-10-07: /the-web, /spirits, /iboga-ibogaine (weight 800), /living-declaration, BrewSoul photo on /brewsoul, /brewsoul/browse, /brewsoul/first-sip (live has none there either), /quiz_25q, /recent-creations. Fixed today: /find-your-journey (64px title, red label), /impact-dashboard (64px title in essay ink, label spacing), red labels on /published and /speaking (plus its "rooms" chips), /soulscore "by ImpactSoul" label, /pri-calibration title (weight 900, solid cream, was a purple gradient), /clients (live's narrow 546px column for the whole page, 56px title, roomier stats band, cards 2 per row; two static inline styles moved to classes), /brewsoul/guest (live's BrewSoul photo on the guest card instead of "SN" initials, labels in capitals), /humanos/connect (cards line up with the title), /peptide-hall-of-shame (stats and label readable light gold; were dark gold on dark). Typed arrows on the touched links are icons now (rule 18). Deliberately not copied from live (new CONTRIBUTING rule 20, owner 2026-10-08): red labels on dark bands use #E07A80 (live's #8E1E25 on black is about 2:1, unreadable); /recent-creations keeps our darker label colours (live's fail contrast on white); /humanos/connect keeps "Start Reading" (that card links to the philosophy page, the quiz live's "Start the Assessment" implies doesn't exist). Checked: type check, l</t>
         </is>
       </c>
       <c r="E300" s="14" t="inlineStr">
@@ -7753,7 +7753,7 @@
       <c r="A301" s="4" t="n"/>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>/pri-efficacy's "Simulation / Live Calibrations" switch like live (2026-10-08)</t>
+          <t>BrewSoul top of page (2026-10-08, owner: "button in the center at the top doesn't look good")</t>
         </is>
       </c>
       <c r="C301" s="13" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>shadcn Tabs, both panels in the server HTML (forceMount). The Live tab reads real aggregate numbers from pri_calibrations (getPriLiveStats() in src/lib/pri-research.ts: totals, opt-ins, average score per dimension; no rows leave the server), page stays static and refreshes every 10 minutes. Until the Supabase scripts are run (Phase 2) it says the numbers "aren't available just now" instead of a fake zero. Checked: build (○, 10m), server HTML has both tabs, tab switch at 390/1280px, no JS errors. Re-check with real numbers once the table exists.</t>
+          <t>the category badge ("Deep Research" etc.) sat centred in an empty strip, squeezed against the hero, because we copied live's doubled 52px top gap. Now one gap everywhere and the badge floats in the top-left corner, lined up with the BrewSoul logo (brewsoul-main.tsx, category-badge.tsx); checked on all 26 badge pages at 3 widths that it covers nothing. BrewSoul menu: on tablets (768-1023px) the links were cut off and "More" was hidden with no menu button at all; now the menu button shows below 1024px, 5 links + "More" from 1024px, all 8 from 1280px, "More" always visible.</t>
         </is>
       </c>
       <c r="E301" s="14" t="inlineStr">
@@ -7776,63 +7776,63 @@
       <c r="A302" s="4" t="n"/>
       <c r="B302" s="4" t="inlineStr">
         <is>
+          <t>/pri-efficacy's "Simulation / Live Calibrations" switch like live (2026-10-08)</t>
+        </is>
+      </c>
+      <c r="C302" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D302" s="4" t="inlineStr">
+        <is>
+          <t>shadcn Tabs, both panels in the server HTML (forceMount). The Live tab reads real aggregate numbers from pri_calibrations (getPriLiveStats() in src/lib/pri-research.ts: totals, opt-ins, average score per dimension; no rows leave the server), page stays static and refreshes every 10 minutes. Until the Supabase scripts are run (Phase 2) it says the numbers "aren't available just now" instead of a fake zero. Checked: build (○, 10m), server HTML has both tabs, tab switch at 390/1280px, no JS errors. Re-check with real numbers once the table exists.</t>
+        </is>
+      </c>
+      <c r="E302" s="14" t="inlineStr">
+        <is>
+          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="n"/>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
           <t>/brewsoul/browse hero readable (2026-10-08, owner said go ahead)</t>
         </is>
       </c>
-      <c r="C302" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D302" s="4" t="inlineStr">
+      <c r="C303" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D303" s="4" t="inlineStr">
         <is>
           <t>a soft cream glow behind the title block so "The Catalog", the subtitle and the stat labels read clearly over the coffee photo (live is hard to read there too; rule 20). Photo still shows around the edges. Checked at 390/1280px.</t>
         </is>
       </c>
-      <c r="E302" s="14" t="inlineStr">
+      <c r="E303" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
         </is>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" s="10" t="inlineStr">
+    <row r="304">
+      <c r="A304" s="10" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
-      <c r="B303" s="11" t="n"/>
-      <c r="C303" s="11" t="n"/>
-      <c r="D303" s="12" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="4" t="n"/>
-      <c r="B304" s="4" t="inlineStr">
-        <is>
-          <t>Manus media rescue (2026-09-29)</t>
-        </is>
-      </c>
-      <c r="C304" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D304" s="4" t="inlineStr">
-        <is>
-          <t>all 94 Manus-hosted image/video references in the legacy source (/api/img/, /manus-storage/) were checked live. 91 were still downloadable, including the /akbar photos the entry below calls "permanently lost", and all 91 are now Sanity assets (scripts/rescue-manus-media.ts; Sanity dedupes by SHA-1). 3 were gone (HTTP 502). The manifest docs/ai/manus-media-rescue.md maps each one to the legacy files that used it and its Sanity URL. They are not wired into pages yet: go page by page, with real alt text. /facilitator-index's two diagrams are done (scripts/rescue-facilitator-images.ts).</t>
-        </is>
-      </c>
-      <c r="E304" s="14" t="inlineStr">
-        <is>
-          <t>Phase 13 — Images Needed in Sanity</t>
-        </is>
-      </c>
+      <c r="B304" s="11" t="n"/>
+      <c r="C304" s="11" t="n"/>
+      <c r="D304" s="12" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="4" t="n"/>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Favicon</t>
+          <t>Manus media rescue (2026-09-29)</t>
         </is>
       </c>
       <c r="C305" s="13" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>real "G" brand mark generated from the header's actual wordmark treatment (src/app/icon.tsx), see Phase 3</t>
+          <t>all 94 Manus-hosted image/video references in the legacy source (/api/img/, /manus-storage/) were checked live. 91 were still downloadable, including the /akbar photos the entry below calls "permanently lost", and all 91 are now Sanity assets (scripts/rescue-manus-media.ts; Sanity dedupes by SHA-1). 3 were gone (HTTP 502). The manifest docs/ai/manus-media-rescue.md maps each one to the legacy files that used it and its Sanity URL. They are not wired into pages yet: go page by page, with real alt text. /facilitator-index's two diagrams are done (scripts/rescue-facilitator-images.ts).</t>
         </is>
       </c>
       <c r="E305" s="14" t="inlineStr">
@@ -7855,17 +7855,17 @@
       <c r="A306" s="4" t="n"/>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
-        </is>
-      </c>
-      <c r="C306" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Favicon</t>
+        </is>
+      </c>
+      <c r="C306" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
+          <t>real "G" brand mark generated from the header's actual wordmark treatment (src/app/icon.tsx), see Phase 3</t>
         </is>
       </c>
       <c r="E306" s="14" t="inlineStr">
@@ -7878,17 +7878,17 @@
       <c r="A307" s="4" t="n"/>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Author photo(s) for blog author schema (Tony Greenberg headshot at minimum)</t>
-        </is>
-      </c>
-      <c r="C307" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
+        </is>
+      </c>
+      <c r="C307" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: the rescued headshot is already the author avatar in Sanity; now also in every post's Article JSON-LD (author image + url /about). The JSON-LD publisher logo pointed at /favicon.ico, a 404 here; now /icon.</t>
+          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
         </is>
       </c>
       <c r="E307" s="14" t="inlineStr">
@@ -7901,7 +7901,7 @@
       <c r="A308" s="4" t="n"/>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>Blog hero images</t>
+          <t>Author photo(s) for blog author schema (Tony Greenberg headshot at minimum)</t>
         </is>
       </c>
       <c r="C308" s="13" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>audited, then migrated. Final state:</t>
+          <t>2026-10-02: the rescued headshot is already the author avatar in Sanity; now also in every post's Article JSON-LD (author image + url /about). The JSON-LD publisher logo pointed at /favicon.ico, a 404 here; now /icon.</t>
         </is>
       </c>
       <c r="E308" s="14" t="inlineStr">
@@ -7924,7 +7924,7 @@
       <c r="A309" s="4" t="n"/>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>22 posts have a real hero image, now live in Sanity (17 already on RampRate's own CloudFront + 4 rescued from the legacy /api/img/ proxy + 1…</t>
+          <t>Blog hero images</t>
         </is>
       </c>
       <c r="C309" s="13" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> rescued from /manus-storage/, all pulled over by migrate-blog-posts.ts before Manus is decommissioned)</t>
+          <t>audited, then migrated. Final state:</t>
         </is>
       </c>
       <c r="E309" s="14" t="inlineStr">
@@ -7947,7 +7947,7 @@
       <c r="A310" s="4" t="n"/>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>7 more posts got a real, unique hero image rescued from the live legacy site's newly-added art this pass (scripts/rescue-2026-09-blog-images…</t>
+          <t>22 posts have a real hero image, now live in Sanity (17 already on RampRate's own CloudFront + 4 rescued from the legacy /api/img/ proxy + 1…</t>
         </is>
       </c>
       <c r="C310" s="13" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>.ts — see the correction note above): california-toll-roads-legalized-scam, the-1000-hour-hold, conscious-capital-partnership-ecosystem, the-peptide-truth-65m-fraud-industry-vs-life-changing-medicine, clear-communication, building-services-market-transhuman-era, heart-protocol-addendum.</t>
+          <t xml:space="preserve"> rescued from /manus-storage/, all pulled over by migrate-blog-posts.ts before Manus is decommissioned)</t>
         </is>
       </c>
       <c r="E310" s="14" t="inlineStr">
@@ -7970,17 +7970,17 @@
       <c r="A311" s="4" t="n"/>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>92 posts still need a real, unique hero image</t>
-        </is>
-      </c>
-      <c r="C311" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>7 more posts got a real, unique hero image rescued from the live legacy site's newly-added art this pass (scripts/rescue-2026-09-blog-images…</t>
+        </is>
+      </c>
+      <c r="C311" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
+          <t>.ts — see the correction note above): california-toll-roads-legalized-scam, the-1000-hour-hold, conscious-capital-partnership-ecosystem, the-peptide-truth-65m-fraud-industry-vs-life-changing-medicine, clear-communication, building-services-market-transhuman-era, heart-protocol-addendum.</t>
         </is>
       </c>
       <c r="E311" s="14" t="inlineStr">
@@ -7993,17 +7993,17 @@
       <c r="A312" s="4" t="n"/>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>Blog: per-post OG image if different from hero (many posts can reuse hero as OG)</t>
-        </is>
-      </c>
-      <c r="C312" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>92 posts still need a real, unique hero image</t>
+        </is>
+      </c>
+      <c r="C312" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>Confirmed 2026-10-02: generateMetadata uses seo.ogImage, else the hero, else the default OG image.</t>
+          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
         </is>
       </c>
       <c r="E312" s="14" t="inlineStr">
@@ -8016,7 +8016,7 @@
       <c r="A313" s="4" t="n"/>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Marketing pages</t>
+          <t>Blog: per-post OG image if different from hero (many posts can reuse hero as OG)</t>
         </is>
       </c>
       <c r="C313" s="13" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>hero/section images for /the-letter, /the-territory, /engine-room, /the-body, /the-nightstand, /recent-creations (portfolio thumbnails), /published (publication logos), /clients (client logos — confirm licensing before re-hosting). Checked against live 2026-10-02: same image count on every one; /the-territory, /engine-room, /recent-creations, /published, /clients have no images on live either.</t>
+          <t>Confirmed 2026-10-02: generateMetadata uses seo.ogImage, else the hero, else the default OG image.</t>
         </is>
       </c>
       <c r="E313" s="14" t="inlineStr">
@@ -8039,7 +8039,7 @@
       <c r="A314" s="4" t="n"/>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>/akbar essay images</t>
+          <t>Marketing pages</t>
         </is>
       </c>
       <c r="C314" s="13" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>not lost after all: 20 of the 21 were rescued into Sanity by scripts/rescue-manus-media.ts (2026-09-28) and are wired back in legacy's layout (hero mosaic, JC portrait, 2x2 grid, 3 full-bleeds, 3-up strip, footer gallery) as of 2026-09-29. Only slider-3 was gone (HTTP 502); the hero mosaic is 4 tiles instead of 5.</t>
+          <t>hero/section images for /the-letter, /the-territory, /engine-room, /the-body, /the-nightstand, /recent-creations (portfolio thumbnails), /published (publication logos), /clients (client logos — confirm licensing before re-hosting). Checked against live 2026-10-02: same image count on every one; /the-territory, /engine-room, /recent-creations, /published, /clients have no images on live either.</t>
         </is>
       </c>
       <c r="E314" s="14" t="inlineStr">
@@ -8062,7 +8062,7 @@
       <c r="A315" s="4" t="n"/>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>Rescued page images wired back in (2026-09-29)</t>
+          <t>/akbar essay images</t>
         </is>
       </c>
       <c r="C315" s="13" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>/living-declaration hero, hand image and Clarisse Abelarde artwork; /impact-dashboard earth hero; /find-my banner; /find-your-coffee dark photo landing (legacy copy restored, replacing an intro that wasn't in legacy). Also wired (second pass): /consciousness-scale (legacy's hero-first flow restored, the invented intro screen removed), /find-your-me hero, /humanos hero, the HumanOS nav logo, and all 12 HumanOS people headshots (/humanos/ecosystem, /humanos/philosophy). Blog-body images (2026-09-29): all 19 the migration dropped are restored by scripts/restore-blog-body-images.ts as Sanity drafts on 4 posts (Clarisse Abelarde 7, You Are the Moat 4, FRQNCY 6, Energy Is Money 2), waiting to be published in Studio; the other blog-listed assets were heroes already set. Still unwired from docs/ai/manus-media-rescue.md: and /alex-azzi's subject photo (a photo of a real person on an accusation page: needs Tony's yes first).</t>
+          <t>not lost after all: 20 of the 21 were rescued into Sanity by scripts/rescue-manus-media.ts (2026-09-28) and are wired back in legacy's layout (hero mosaic, JC portrait, 2x2 grid, 3 full-bleeds, 3-up strip, footer gallery) as of 2026-09-29. Only slider-3 was gone (HTTP 502); the hero mosaic is 4 tiles instead of 5.</t>
         </is>
       </c>
       <c r="E315" s="14" t="inlineStr">
@@ -8085,7 +8085,7 @@
       <c r="A316" s="4" t="n"/>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>BrewSoul: coffee/product images (brewsoul-coffees-expanded.ts likely has image refs</t>
+          <t>Rescued page images wired back in (2026-09-29)</t>
         </is>
       </c>
       <c r="C316" s="13" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="D316" s="4" t="inlineStr">
         <is>
-          <t>audit), city guide header images, roaster directory photos. Audited 2026-09-09 (status spreadsheet), confirmed 2026-10-02: city guides already have photos; coffees, chains and roasters have no image field in legacy or here (text-only by design); farms got real photos.</t>
+          <t>/living-declaration hero, hand image and Clarisse Abelarde artwork; /impact-dashboard earth hero; /find-my banner; /find-your-coffee dark photo landing (legacy copy restored, replacing an intro that wasn't in legacy). Also wired (second pass): /consciousness-scale (legacy's hero-first flow restored, the invented intro screen removed), /find-your-me hero, /humanos hero, the HumanOS nav logo, and all 12 HumanOS people headshots (/humanos/ecosystem, /humanos/philosophy). Blog-body images (2026-09-29): all 19 the migration dropped are restored by scripts/restore-blog-body-images.ts as Sanity drafts on 4 posts (Clarisse Abelarde 7, You Are the Moat 4, FRQNCY 6, Energy Is Money 2), waiting to be published in Studio; the other blog-listed assets were heroes already set. Still unwired from docs/ai/manus-media-rescue.md: and /alex-azzi's subject photo (a photo of a real person on an accusation page: needs Tony's yes first).</t>
         </is>
       </c>
       <c r="E316" s="14" t="inlineStr">
@@ -8108,7 +8108,7 @@
       <c r="A317" s="4" t="n"/>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>65 page images moved off the Manus storage copy into Sanity (2026-10-02)</t>
+          <t>BrewSoul: coffee/product images (brewsoul-coffees-expanded.ts likely has image refs</t>
         </is>
       </c>
       <c r="C317" s="13" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>every image the code loaded from d2xsxph8kpxj0f.cloudfront.net (PRI medicine images, Iboga module, facilitator index, /attention-theft, /alex-azzi, /protecting-your-business, /peyote-mescaline, HumanOS, the peptide quiz). Notes called it "RampRate's own CloudFront", but every file sits in the legacy Manus project's folder and its owner couldn't be confirmed. All 65 uploaded (scripts/rescue-cloudfront-images.ts), code rewritten, host removed from images.remotePatterns, no Sanity document used it. Table in docs/ai/manus-media-rescue.md.</t>
+          <t>audit), city guide header images, roaster directory photos. Audited 2026-09-09 (status spreadsheet), confirmed 2026-10-02: city guides already have photos; coffees, chains and roasters have no image field in legacy or here (text-only by design); farms got real photos.</t>
         </is>
       </c>
       <c r="E317" s="14" t="inlineStr">
@@ -8131,7 +8131,7 @@
       <c r="A318" s="4" t="n"/>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>PRI/Kava: medicine reference images (medicine-images.ts), facility images for /facilitator-index</t>
+          <t>65 page images moved off the Manus storage copy into Sanity (2026-10-02)</t>
         </is>
       </c>
       <c r="C318" s="13" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="D318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: all in Sanity; image counts match live on PRI, Kava, Iboga, Peyote, facilitator pages.</t>
+          <t>every image the code loaded from d2xsxph8kpxj0f.cloudfront.net (PRI medicine images, Iboga module, facilitator index, /attention-theft, /alex-azzi, /protecting-your-business, /peyote-mescaline, HumanOS, the peptide quiz). Notes called it "RampRate's own CloudFront", but every file sits in the legacy Manus project's folder and its owner couldn't be confirmed. All 65 uploaded (scripts/rescue-cloudfront-images.ts), code rewritten, host removed from images.remotePatterns, no Sanity document used it. Table in docs/ai/manus-media-rescue.md.</t>
         </is>
       </c>
       <c r="E318" s="14" t="inlineStr">
@@ -8154,7 +8154,7 @@
       <c r="A319" s="4" t="n"/>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Manifesto/Attention Theft: any diagram/illustration assets used on the mega-page</t>
+          <t>PRI/Kava: medicine reference images (medicine-images.ts), facility images for /facilitator-index</t>
         </is>
       </c>
       <c r="C319" s="13" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02: 6 of live's 7 are in (now in Sanity); the 7th belongs to the Wall of Shame section left out on purpose.</t>
+          <t>2026-10-02: all in Sanity; image counts match live on PRI, Kava, Iboga, Peyote, facilitator pages.</t>
         </is>
       </c>
       <c r="E319" s="14" t="inlineStr">
@@ -8177,17 +8177,17 @@
       <c r="A320" s="4" t="n"/>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
-        </is>
-      </c>
-      <c r="C320" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Manifesto/Attention Theft: any diagram/illustration assets used on the mega-page</t>
+        </is>
+      </c>
+      <c r="C320" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
+          <t>2026-10-02: 6 of live's 7 are in (now in Sanity); the 7th belongs to the Wall of Shame section left out on purpose.</t>
         </is>
       </c>
       <c r="E320" s="14" t="inlineStr">
@@ -8200,17 +8200,17 @@
       <c r="A321" s="4" t="n"/>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>Chatbot: FauxTony avatar/icon</t>
-        </is>
-      </c>
-      <c r="C321" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
+        </is>
+      </c>
+      <c r="C321" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>Not needed (2026-10-02): the chatbot phase (Phase 10) was cancelled.</t>
+          <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
         </is>
       </c>
       <c r="E321" s="14" t="inlineStr">
@@ -8223,73 +8223,73 @@
       <c r="A322" s="4" t="n"/>
       <c r="B322" s="4" t="inlineStr">
         <is>
+          <t>Chatbot: FauxTony avatar/icon</t>
+        </is>
+      </c>
+      <c r="C322" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D322" s="4" t="inlineStr">
+        <is>
+          <t>Not needed (2026-10-02): the chatbot phase (Phase 10) was cancelled.</t>
+        </is>
+      </c>
+      <c r="E322" s="14" t="inlineStr">
+        <is>
+          <t>Phase 13 — Images Needed in Sanity</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="4" t="n"/>
+      <c r="B323" s="4" t="inlineStr">
+        <is>
           <t>Audit client/public/ (including alex-azzi/, brewsoul/ subfolders) for any static assets already sitting there unused that should be pulled i…</t>
         </is>
       </c>
-      <c r="C322" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D322" s="4" t="inlineStr">
+      <c r="C323" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D323" s="4" t="inlineStr">
         <is>
           <t>n rather than re-created. Done 2026-10-02: no images there at all (only llms.txt, a BrewSoul catalog, Manus debug files, design-options.html). Found and fixed a cutover risk instead: live serves two Google site-verification files (/google6881a0411c48b301.html, /alex-azzi/googleedff0185753a4a1f.html) that the new site returned 404 for, so Search Console could lose verification at DNS cutover. Both copied to public/ byte for byte. Not copied: site.webmanifest (its icons don't exist here; Next's app/icon.tsx covers the favicon).</t>
         </is>
       </c>
-      <c r="E322" s="14" t="inlineStr">
+      <c r="E323" s="14" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
     </row>
-    <row r="323">
-      <c r="A323" s="10" t="inlineStr">
+    <row r="324">
+      <c r="A324" s="10" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
         </is>
       </c>
-      <c r="B323" s="11" t="n"/>
-      <c r="C323" s="11" t="n"/>
-      <c r="D323" s="12" t="n"/>
-    </row>
-    <row r="324">
-      <c r="A324" s="4" t="n"/>
-      <c r="B324" s="4" t="inlineStr">
-        <is>
-          <t>Mobile responsive pass on every ported section</t>
-        </is>
-      </c>
-      <c r="C324" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D324" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid). Fixed 2026-10-09: the bar is now solid (bg-[#2C1810], was 92% plus backdrop-blur-md), so nothing can show through even where the blur isn't drawn; checked in WebKit (iPhone 13 profile) and Chrome: background rgb(44, 24, 16), no text behind the buttons. A real iPhone check is still part of Phase 14.</t>
-        </is>
-      </c>
-      <c r="E324" s="14" t="inlineStr">
-        <is>
-          <t>Phase 14 — QA &amp; Launch</t>
-        </is>
-      </c>
+      <c r="B324" s="11" t="n"/>
+      <c r="C324" s="11" t="n"/>
+      <c r="D324" s="12" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="4" t="n"/>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>Accessibility pass (WCAG AA contrast, 44px touch targets, keyboard nav)</t>
-        </is>
-      </c>
-      <c r="C325" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Mobile responsive pass on every ported section</t>
+        </is>
+      </c>
+      <c r="C325" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy QA_MASTER_PROMPT.md. 2026-09-29 axe-core pass (WCAG 2.1 AA, same 114 pages, production build): all unlabeled dropdowns/inputs and unnamed links fixed; contrast down from 1,453 failing items on 106 pages to 1,038 on 70 (43 pages fully clean). Shared fixes: brand gold #8b6914 → #836311 site-wide (was 4.3:1 on cream, AA needs 4.5), header "⌘K"/social icons, BrewSoul nav and footer, HumanOS footer, Kava footer, assessment intro footnote, post-card image links. 2026-09-30: contrast finished, 0 axe color-contrast failures left on the same 114 pages (production build). Token changes: --kava-saffron #b86a28 → #8e521f, --pri-purple-light #a855f7 → #b87bf9 (on-dark purple only), --crusade-teal #0e7c7c → #0d7373; PriEyebrow goes light purple inside a dark PriSection via group-data-dark/pri; /find-your-me and the journey tracker's dark glass panels 60-70% → 90% (legacy's own 60% glass on beige rendered gray, cream text failed). Everything else: nearest passing shade of the same hue, or gold ↔ gold-light on the wrong background. Left: 18 links inside text marked only by color (need an underline), 44px tap targets, keyboard nav. 2026-09-30: 18 color-only in-text links underlined (axe link-in-text-block: 0 left); keyboard focus visible on every focusable item on 8 sampled pages (two form fields had none, fixed). 2026-10-02 re-run (axe WCAG 2.2 AA, 142 pages × 375/1280px, production build, plus Tab through 40 stops per page): found 1,370 contrast failures (mostly BrewSoul'</t>
+          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid). Fixed 2026-10-09: the bar is now solid (bg-[#2C1810], was 92% plus backdrop-blur-md), so nothing can show through even where the blur isn't drawn; checked in WebKit (iPhone 13 profile) and Chrome: background rgb(44, 24, 16), no text behind the buttons. A real iPhone check is still part of Phase 14.</t>
         </is>
       </c>
       <c r="E325" s="14" t="inlineStr">
@@ -8302,17 +8302,17 @@
       <c r="A326" s="4" t="n"/>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>No dead-end pages (every page links to 2+ others)</t>
-        </is>
-      </c>
-      <c r="C326" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Accessibility pass (WCAG AA contrast, 44px touch targets, keyboard nav)</t>
+        </is>
+      </c>
+      <c r="C326" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
+          <t>same bar as legacy QA_MASTER_PROMPT.md. 2026-09-29 axe-core pass (WCAG 2.1 AA, same 114 pages, production build): all unlabeled dropdowns/inputs and unnamed links fixed; contrast down from 1,453 failing items on 106 pages to 1,038 on 70 (43 pages fully clean). Shared fixes: brand gold #8b6914 → #836311 site-wide (was 4.3:1 on cream, AA needs 4.5), header "⌘K"/social icons, BrewSoul nav and footer, HumanOS footer, Kava footer, assessment intro footnote, post-card image links. 2026-09-30: contrast finished, 0 axe color-contrast failures left on the same 114 pages (production build). Token changes: --kava-saffron #b86a28 → #8e521f, --pri-purple-light #a855f7 → #b87bf9 (on-dark purple only), --crusade-teal #0e7c7c → #0d7373; PriEyebrow goes light purple inside a dark PriSection via group-data-dark/pri; /find-your-me and the journey tracker's dark glass panels 60-70% → 90% (legacy's own 60% glass on beige rendered gray, cream text failed). Everything else: nearest passing shade of the same hue, or gold ↔ gold-light on the wrong background. Left: 18 links inside text marked only by color (need an underline), 44px tap targets, keyboard nav. 2026-09-30: 18 color-only in-text links underlined (axe link-in-text-block: 0 left); keyboard focus visible on every focusable item on 8 sampled pages (two form fields had none, fixed). 2026-10-02 re-run (axe WCAG 2.2 AA, 142 pages × 375/1280px, production build, plus Tab through 40 stops per page): found 1,370 contrast failures (mostly BrewSoul'</t>
         </is>
       </c>
       <c r="E326" s="14" t="inlineStr">
@@ -8325,7 +8325,7 @@
       <c r="A327" s="4" t="n"/>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
+          <t>No dead-end pages (every page links to 2+ others)</t>
         </is>
       </c>
       <c r="C327" s="15" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
+          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
         </is>
       </c>
       <c r="E327" s="14" t="inlineStr">
@@ -8348,7 +8348,7 @@
       <c r="A328" s="4" t="n"/>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>Remove noindex only when sign-off is given</t>
+          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
         </is>
       </c>
       <c r="C328" s="15" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="D328" s="4" t="inlineStr">
         <is>
-          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
         </is>
       </c>
       <c r="E328" s="14" t="inlineStr">
@@ -8371,7 +8371,7 @@
       <c r="A329" s="4" t="n"/>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
+          <t>Remove noindex only when sign-off is given</t>
         </is>
       </c>
       <c r="C329" s="15" t="inlineStr">
@@ -8379,7 +8379,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D329" s="4" t="inlineStr"/>
+      <c r="D329" s="4" t="inlineStr">
+        <is>
+          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+        </is>
+      </c>
       <c r="E329" s="14" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
@@ -8390,7 +8394,7 @@
       <c r="A330" s="4" t="n"/>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
         </is>
       </c>
       <c r="C330" s="15" t="inlineStr">
@@ -8405,23 +8409,42 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" s="4" t="n"/>
+      <c r="B331" s="4" t="inlineStr">
+        <is>
+          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+        </is>
+      </c>
+      <c r="C331" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D331" s="4" t="inlineStr"/>
+      <c r="E331" s="14" t="inlineStr">
+        <is>
+          <t>Phase 14 — QA &amp; Launch</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D330"/>
+  <autoFilter ref="A1:D331"/>
   <mergeCells count="14">
-    <mergeCell ref="A150:D150"/>
-    <mergeCell ref="A303:D303"/>
-    <mergeCell ref="A237:D237"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A258:D258"/>
-    <mergeCell ref="A209:D209"/>
-    <mergeCell ref="A205:D205"/>
+    <mergeCell ref="A259:D259"/>
+    <mergeCell ref="A238:D238"/>
+    <mergeCell ref="A184:D184"/>
+    <mergeCell ref="A206:D206"/>
+    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="A210:D210"/>
+    <mergeCell ref="A304:D304"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A324:D324"/>
+    <mergeCell ref="A151:D151"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A323:D323"/>
-    <mergeCell ref="A183:D183"/>
     <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A123:D123"/>
+    <mergeCell ref="A44:D44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8433,7 +8456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8507,96 +8530,96 @@
       <c r="A4" s="4" t="n"/>
       <c r="B4" s="4" t="inlineStr">
         <is>
+          <t>Copy the old site's visitor data from the Manus database (owner asked, 2026-10-09)</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>The legacy app keeps ~55 MySQL tables on Manus (_legacy-manus-app/drizzle/schema.ts); they go away with Manus. Owner has the connection details: put them in .env.local as LEGACY_DATABASE_URL (never in chat or a commit). Plan: (1) read row counts for every table (read-only, a throwaway pymysql reader outside the project, no new package); (2) after the two Supabase scripts below are run, copy the 12 tables that already have a home: blog_comments, blog_ratings, post_reactions → blog_reactions, micro_commitments → blog_commitments, highlights, referral_codes, referrals, clock_keeper_responses, post_intervention_assessments, friend_gate_sessions, friend_gate_slots, pri_calibrations (account-linked rows can only be matched to new accounts by email); (3) email_subscribers go to Kit, not Supabase; (4) owner picks which of the rest need new tables (facilitator submissions/votes, assessment results, journey progress, community, vendor intake, page views...). Billing (purchases, subscriptions) and spam tracking stay out of scope. Blocked on: LEGACY_DATABASE_URL, and the Supabase scripts being run.</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Phase 2 — Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
           <t>Run the database scripts once, in order</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>(supabase/migrations/0001_member_features.sql, then 0002_blog_engagement.sql for essay comments, reactions, ratings and micro-commitments; 0001: highlights, referral codes/referrals, Clock Keeper responses, post-intervention, friend gate, PRI calibrations, all with row-level security) in Supabase: SQL Editor &gt; New query &gt; paste &gt; Run. Also in Supabase: Authentication &gt; URL Configuration &gt; Site URL https://tonygreenberg.com and Redirect URLs https://tonygreenberg.com/auth/callback, https://*--tonygreenberg-website.netlify.app/auth/callback, http://localhost:3000/auth/callback. Then set NEXT_PUBLIC_SUPABASE_URL, NEXT_PUBLIC_SUPABASE_ANON_KEY, SUPABASE_SERVICE_ROLE_KEY, ADMIN_EMAILS in Netlify.</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Phase 2 — Supabase</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Phase 4 — Marketing Core Pages (30 routes)</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="12" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="12" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>/shop, /payment-success, /payment-cancel</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>defer: these are Stripe-backed; flag for the later billing-migration phase, do not port checkout logic yet, static/informational content only if ported now</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Phase 4 — Marketing Core Pages (30 routes)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="12" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Set GITHUB_TOKEN, MCP_ADMIN_USERS, MCP_LOGIN_PASSWORD, MCP_OAUTH_SECRET, MCP_SITE_ORIGIN, MCP_PUBLIC_ORIGIN in Netlify (done) (checked 2026-…</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>10-07: all already set in Netlify). Left: connect Claude.ai to /api/mcp for real, and verify the GitHub flow end to end (branch → PR → deploy preview → publish_changes) against a real PR.</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
-        </is>
-      </c>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Commit a team-wide .mcp.json (URL only) once the production URL is settled.</t>
+          <t>Set GITHUB_TOKEN, MCP_ADMIN_USERS, MCP_LOGIN_PASSWORD, MCP_OAUTH_SECRET, MCP_SITE_ORIGIN, MCP_PUBLIC_ORIGIN in Netlify (done) (checked 2026-…</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
@@ -8604,7 +8627,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>10-07: all already set in Netlify). Left: connect Claude.ai to /api/mcp for real, and verify the GitHub flow end to end (branch → PR → deploy preview → publish_changes) against a real PR.</t>
+        </is>
+      </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
@@ -8615,7 +8642,7 @@
       <c r="A10" s="4" t="n"/>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Blocked on you (Google)</t>
+          <t>Commit a team-wide .mcp.json (URL only) once the production URL is settled.</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
@@ -8623,11 +8650,7 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>create a GOOGLE_API_KEY in Google Cloud (project of the vcos-ga4-reader service account, where the PageSpeed Insights API is already on), restricted to the PageSpeed Insights API, then add it to .env.local and Netlify. Creating it from here was blocked by the session's safety check (it would use the service account's credentials to change the Cloud project). Note lighthouse_check_page may time out on Netlify (10 s function limit on the free plan).</t>
-        </is>
-      </c>
+      <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
@@ -8638,63 +8661,63 @@
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>Blocked on you (Google)</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>create a GOOGLE_API_KEY in Google Cloud (project of the vcos-ga4-reader service account, where the PageSpeed Insights API is already on), restricted to the PageSpeed Insights API, then add it to .env.local and Netlify. Creating it from here was blocked by the session's safety check (it would use the service account's credentials to change the Cloud project). Note lighthouse_check_page may time out on Netlify (10 s function limit on the free plan).</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
           <t>Test the new review end to end on a deploy preview</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>(needs a yes, it opens a real pull request): one throwaway change from Claude.ai or ChatGPT: start (unclear request, so the confirm step shows), confirm, edit, review card, screenshots, upload link, then discard.</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="12" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Lighthouse pass (performance/accessibility/SEO) on top 20 pages by traffic 2026-09-30, 20 key pages (no traffic data yet), local production …</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>build, mobile: averages performance 87, accessibility 99→100, best practices 100, SEO 92→100, CLS 0 everywhere. Fixed: public/robots.txt had an LLMs: line (not a real directive) that made Google treat the whole file as invalid, now a comment; h3/h4 headings skipping a level on /assessments, /kava, /peptide-watch (same look, right tag); the Kava and /attention-theft back-arrow links had no accessible name on phones; two small phone-width contrast misses. Left: performance is local-machine only (±10-15 points, see CONTRIBUTING.md); the slowest were / 76 (LCP 5.2 s), /psychedelic-readiness-index 82, /iboga-ibogaine 83. Re-run against the Netlify deploy before launch. 2026-10-06 re-run against the Netlify deploy (14 key pages, mobile): accessibility 100 and CLS 0 on every page, SEO clean (only the expected netlify.app noindex), performance 77-97 held back by 3-4 s LCP. Fixed: all 21 hero images moved off the deprecated priority prop to fetchPriority="high" + loading="eager" (Next 16); /iboga-ibogaine hero and the first card on /blog and category pages no longer lazy-loaded; sizes on the Four Doors cards (~150 KiB per page), /humanos diagram (~100 KiB) and /about headshot; urlFor no longer imports the Sanity client, so ~115 KB of Sanity client code stopped loading on / and /blog; React hydration error #418 on / and /blog (post dates) gone, checked in two time zones; /blog is static again; empty icon &lt;th&gt;s on /iboga-ibogaine labelled; category page reads use sanityFetch(). Left: se</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
-        </is>
-      </c>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n"/>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SEO audit items needing a yes (2026-10-06)</t>
+          <t>Lighthouse pass (performance/accessibility/SEO) on top 20 pages by traffic 2026-09-30, 20 key pages (no traffic data yet), local production …</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -8704,7 +8727,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+          <t>build, mobile: averages performance 87, accessibility 99→100, best practices 100, SEO 92→100, CLS 0 everywhere. Fixed: public/robots.txt had an LLMs: line (not a real directive) that made Google treat the whole file as invalid, now a comment; h3/h4 headings skipping a level on /assessments, /kava, /peptide-watch (same look, right tag); the Kava and /attention-theft back-arrow links had no accessible name on phones; two small phone-width contrast misses. Left: performance is local-machine only (±10-15 points, see CONTRIBUTING.md); the slowest were / 76 (LCP 5.2 s), /psychedelic-readiness-index 82, /iboga-ibogaine 83. Re-run against the Netlify deploy before launch. 2026-10-06 re-run against the Netlify deploy (14 key pages, mobile): accessibility 100 and CLS 0 on every page, SEO clean (only the expected netlify.app noindex), performance 77-97 held back by 3-4 s LCP. Fixed: all 21 hero images moved off the deprecated priority prop to fetchPriority="high" + loading="eager" (Next 16); /iboga-ibogaine hero and the first card on /blog and category pages no longer lazy-loaded; sizes on the Four Doors cards (~150 KiB per page), /humanos diagram (~100 KiB) and /about headshot; urlFor no longer imports the Sanity client, so ~115 KB of Sanity client code stopped loading on / and /blog; React hydration error #418 on / and /blog (post dates) gone, checked in two time zones; /blog is static again; empty icon &lt;th&gt;s on /iboga-ibogaine labelled; category page reads use sanityFetch(). Left: se</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -8717,59 +8740,59 @@
       <c r="A15" s="4" t="n"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
+          <t>SEO audit items needing a yes (2026-10-06)</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>the pack's new copy (homepage title/description, five-cups title, description, short answer, FAQ, heading rewrites, entity statement, newsletter block, author box, health disclaimer, COA wording); "Further Reading" shown twice on posts (merge the lists?); long post title (84 chars), homepage description length and obsolete keywords tag, slugs (/blog/five-cups, the -2 slug; would need redirects), "Six lenses" over four cards, sources for health claims and proof for "$10B+", "Certified B Corp", "Validity: 91", legal review of the homepage Case File banner, ABIT waitlist disclosures, one contact email, the two one-post categories, fewer homepage CTAs / email signup / table of contents / explaining "COA".</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
           <t>Connect Google Search Console + GA4 to the new deployment on day one of cutover</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="12" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Phase 13 — Images Needed in Sanity</t>
-        </is>
-      </c>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>92 posts still need a real, unique hero image</t>
+          <t>Site-wide: logo (light + dark) beyond the current text wordmark</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -8779,7 +8802,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
+          <t>(Default/fallback OG image 1200×630 exists: public/images/default-og.png, checked 2026-10-02.)</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
@@ -8792,63 +8815,63 @@
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
+          <t>92 posts still need a real, unique hero image</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>(down from 99). Tracked one row per post, with a suggested image-generation prompt, in BLOG-IMAGE-BRIEFS.md — work through that file and check items off there, not here. No image-generation tool was connected in this environment as of this writing; either connect one (e.g. an MCP image-gen extension), source these manually/with a designer then upload via Sanity Studio (/studio), or re-check the live legacy site periodically per the correction note above.</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Phase 13 — Images Needed in Sanity</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>Assessment result-screen background art (flagged in STATUS.md as a known gap</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>18/20 assessments currently have plain black backgrounds; sourcing themed art here also closes that gap)</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>Phase 13 — Images Needed in Sanity</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="12" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Mobile responsive pass on every ported section</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid). Fixed 2026-10-09: the bar is now solid (bg-[#2C1810], was 92% plus backdrop-blur-md), so nothing can show through even where the blur isn't drawn; checked in WebKit (iPhone 13 profile) and Chrome: background rgb(44, 24, 16), no text behind the buttons. A real iPhone check is still part of Phase 14.</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>Phase 14 — QA &amp; Launch</t>
-        </is>
-      </c>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n"/>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>No dead-end pages (every page links to 2+ others)</t>
+          <t>Mobile responsive pass on every ported section</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -8858,7 +8881,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
+          <t>2026-09-29: no page scrolls sideways at 375px any more (114 pages checked in Chrome: every unique page plus 3 of each templated set like blog posts and coffees). Fixed: BrewSoul NextSteps forced 3 columns (and used an inline style), charity-scorecard tab row, /brewsoul/browse filter dropdowns, /the-philosophy hero glow. Still to check by hand: 44px tap targets and Safari iOS. 2026-09-30: 44px tap targets on phones for the shared header, footer, BrewSoul/Kava/HumanOS menus and ~100 standalone links (undersized targets 1,904 → 578; the rest are 24-43px pills/chips that meet WCAG 2.2 AA). axe target-size (WCAG 2.2 AA, with its spacing exception): 0 failures on 114 pages. Safari/iPhone (WebKit, iPhone 14 emulation): all 114 pages load, no sideways scroll, no JS errors; form fields under 16px (iOS zoom-on-tap) fixed site-wide in globals.css. Still to check on a real iPhone: BrewSoul's bottom journey bar showed page text through it in headless WebKit only (taps hit the bar correctly; Chrome renders it solid). Fixed 2026-10-09: the bar is now solid (bg-[#2C1810], was 92% plus backdrop-blur-md), so nothing can show through even where the blur isn't drawn; checked in WebKit (iPhone 13 profile) and Chrome: background rgb(44, 24, 16), no text behind the buttons. A real iPhone check is still part of Phase 14.</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
@@ -8871,7 +8894,7 @@
       <c r="A23" s="4" t="n"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
+          <t>No dead-end pages (every page links to 2+ others)</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
@@ -8881,7 +8904,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
+          <t>same bar as legacy MASTER_QUALITY_PROMPT.md 2026-09-30 scan (496 sitemap pages, header/footer links not counted): every page has a way home (the 6 HumanOS pages had none, in legacy too; added a "← TonyGreenberg.com" footer link). ~17 quiz pages only look like dead ends on their intro screen; their result screens link to related assessments. Left for a content decision: ~20 marketing pages (/akbar, /amplifier, /diamond-cut, /ecosystem, /engage, /engine-room, /intel, /invest, /pick-up-the-phone, /protecting-your-business, /published, /speaking, /the-nightstand, /the-territory, /the-web, /under-nda, /pri-calibration, /charity-scorecard and its detail pages) link to only 0-1 other page in their content. The port matches legacy there (legacy was just as sparse), so adding related links is new content and needs the owner's yes.</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -8894,7 +8917,7 @@
       <c r="A24" s="4" t="n"/>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Remove noindex only when sign-off is given</t>
+          <t>Cross-browser check (Safari iOS in particular, per legacy performance notes) 2026-10-06 WebKit pass (Playwright WebKit, iPhone 13 profile, 1…</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -8904,7 +8927,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+          <t>52 pages: every unique page plus 3 of each templated set, production build): no page pans sideways, no failed requests, no JS errors. Found and fixed on the way: upgrade-insecure-requests in the new CSP made Safari fetch every stylesheet and font over https on localhost (dropped; the site is HTTPS-only via HSTS anyway), and .toLocaleString() without a locale caused a hydration error on /brewsoul/chains in Safari (all number formatting now en-US). Left: a check on a real iPhone (Phase 14).</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
@@ -8917,7 +8940,7 @@
       <c r="A25" s="4" t="n"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
+          <t>Remove noindex only when sign-off is given</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
@@ -8925,7 +8948,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>do not launch indexable by accident (The only noindex is the host-based one for *.netlify.app above, so the real domain is indexable as soon as DNS points at it: sign-off must come before DNS.)</t>
+        </is>
+      </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
@@ -8936,7 +8963,7 @@
       <c r="A26" s="4" t="n"/>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+          <t>Final stakeholder sign-off (Tony/Darryl/Kimberly) on the ported site before DNS cutover</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -8951,15 +8978,34 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Phase 14 — QA &amp; Launch</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D26"/>
+  <autoFilter ref="A1:D27"/>
   <mergeCells count="6">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Migration-Status-Report.xlsx
+++ b/Migration-Status-Report.xlsx
@@ -1953,7 +1953,7 @@
       <c r="A42" s="4" t="n"/>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Copy the old site's visitor data from the Manus database (owner asked, 2026-10-09)</t>
+          <t>Old site's visitor data from the Manus database (owner asked, 2026-10-09)</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>The legacy app keeps ~55 MySQL tables on Manus (_legacy-manus-app/drizzle/schema.ts); they go away with Manus. Owner has the connection details: put them in .env.local as LEGACY_DATABASE_URL (never in chat or a commit). Plan: (1) read row counts for every table (read-only, a throwaway pymysql reader outside the project, no new package); (2) after the two Supabase scripts below are run, copy the 12 tables that already have a home: blog_comments, blog_ratings, post_reactions → blog_reactions, micro_commitments → blog_commitments, highlights, referral_codes, referrals, clock_keeper_responses, post_intervention_assessments, friend_gate_sessions, friend_gate_slots, pri_calibrations (account-linked rows can only be matched to new accounts by email); (3) email_subscribers go to Kit, not Supabase; (4) owner picks which of the rest need new tables (facilitator submissions/votes, assessment results, journey progress, community, vendor intake, page views...). Billing (purchases, subscriptions) and spam tracking stay out of scope. Blocked on: LEGACY_DATABASE_URL, and the Supabase scripts being run.</t>
+          <t>Connection details in .env.local (LEGACY_DATABASE_URL). Done: read-only check of all 56 tables and a full private backup (75,128 rows) to ~/Desktop/tonyg-site-backups/legacy-db-export-2026-10-09/ on the webmaster's Mac (personal data: never commit); most rows are the Manus agent's automated tests (details: docs/ai/project_legacy_database.md); the 198 short share links /s/&lt;code&gt; now redirect (src/lib/content/short-links.ts; 196 land on a page, 2 targets don't exist on live either). Left (needs a yes): add the 36 real email subscribers to Kit (may send Kit's confirmation email); copy the handful of real reactions/ratings/commitment into Supabase after the scripts below are run; decide whether the ~24 real assessment results, ~17 PRI consents, 2 manifesto responses, 8 supplier forms and 1 Cheshire submission stay in the backup only. Then rotate the database password (it was pasted in a chat) and remove LEGACY_DATABASE_URL.</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
@@ -8530,7 +8530,7 @@
       <c r="A4" s="4" t="n"/>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Copy the old site's visitor data from the Manus database (owner asked, 2026-10-09)</t>
+          <t>Old site's visitor data from the Manus database (owner asked, 2026-10-09)</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>The legacy app keeps ~55 MySQL tables on Manus (_legacy-manus-app/drizzle/schema.ts); they go away with Manus. Owner has the connection details: put them in .env.local as LEGACY_DATABASE_URL (never in chat or a commit). Plan: (1) read row counts for every table (read-only, a throwaway pymysql reader outside the project, no new package); (2) after the two Supabase scripts below are run, copy the 12 tables that already have a home: blog_comments, blog_ratings, post_reactions → blog_reactions, micro_commitments → blog_commitments, highlights, referral_codes, referrals, clock_keeper_responses, post_intervention_assessments, friend_gate_sessions, friend_gate_slots, pri_calibrations (account-linked rows can only be matched to new accounts by email); (3) email_subscribers go to Kit, not Supabase; (4) owner picks which of the rest need new tables (facilitator submissions/votes, assessment results, journey progress, community, vendor intake, page views...). Billing (purchases, subscriptions) and spam tracking stay out of scope. Blocked on: LEGACY_DATABASE_URL, and the Supabase scripts being run.</t>
+          <t>Connection details in .env.local (LEGACY_DATABASE_URL). Done: read-only check of all 56 tables and a full private backup (75,128 rows) to ~/Desktop/tonyg-site-backups/legacy-db-export-2026-10-09/ on the webmaster's Mac (personal data: never commit); most rows are the Manus agent's automated tests (details: docs/ai/project_legacy_database.md); the 198 short share links /s/&lt;code&gt; now redirect (src/lib/content/short-links.ts; 196 land on a page, 2 targets don't exist on live either). Left (needs a yes): add the 36 real email subscribers to Kit (may send Kit's confirmation email); copy the handful of real reactions/ratings/commitment into Supabase after the scripts below are run; decide whether the ~24 real assessment results, ~17 PRI consents, 2 manifesto responses, 8 supplier forms and 1 Cheshire submission stay in the backup only. Then rotate the database password (it was pasted in a chat) and remove LEGACY_DATABASE_URL.</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">

--- a/Migration-Status-Report.xlsx
+++ b/Migration-Status-Report.xlsx
@@ -1963,7 +1963,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Connection details in .env.local (LEGACY_DATABASE_URL). Done: read-only check of all 56 tables and a full private backup (75,128 rows) to ~/Desktop/tonyg-site-backups/legacy-db-export-2026-10-09/ on the webmaster's Mac (personal data: never commit); most rows are the Manus agent's automated tests (details: docs/ai/project_legacy_database.md); the 198 short share links /s/&lt;code&gt; now redirect (src/lib/content/short-links.ts; 196 land on a page, 2 targets don't exist on live either). Left (needs a yes): add the 36 real email subscribers to Kit (may send Kit's confirmation email); copy the handful of real reactions/ratings/commitment into Supabase after the scripts below are run; decide whether the ~24 real assessment results, ~17 PRI consents, 2 manifesto responses, 8 supplier forms and 1 Cheshire submission stay in the backup only. Then rotate the database password (it was pasted in a chat) and remove LEGACY_DATABASE_URL.</t>
+          <t>Connection details in .env.local (LEGACY_DATABASE_URL). Done: read-only check of all 56 tables and a full private backup (75,128 rows) to ~/Desktop/tonyg-site-backups/legacy-db-export-2026-10-09/ on the webmaster's Mac (personal data: never commit); most rows are the Manus agent's automated tests (details: docs/ai/project_legacy_database.md); the 198 short share links /s/&lt;code&gt; now redirect (src/lib/content/short-links.ts; 196 land on a page, 2 targets don't exist on live either). Done 2026-10-09 (owner said yes): email subscribers in Kit with no email sent (5 already there, 27 added on the new tag "Legacy site import 2026-10-09", 4 refused by Kit's suppression list); the missing 2026-10-07 Daily Provocation added; supplier forms: table script supabase/migrations/0003_legacy_vendor_intake.sql and scripts/import-legacy-vendor-intake.ts ready (owner: supplier forms to Supabase, everything else stays in the backup). Left: restore the paused Supabase project, run 0001 to 0003, run the import; the few reactions/ratings (optional). Then rotate the database password (it was pasted in a chat) and remove LEGACY_DATABASE_URL.</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
@@ -1976,7 +1976,7 @@
       <c r="A43" s="4" t="n"/>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Run the database scripts once, in order</t>
+          <t>Restore the Supabase project first: it was paused (2026-10-09, its address no longer resolves), so every member feature, comment and reaction is off until someone with the Supabase account clicks "Restore project"</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>(supabase/migrations/0001_member_features.sql, then 0002_blog_engagement.sql for essay comments, reactions, ratings and micro-commitments; 0001: highlights, referral codes/referrals, Clock Keeper responses, post-intervention, friend gate, PRI calibrations, all with row-level security) in Supabase: SQL Editor &gt; New query &gt; paste &gt; Run. Also in Supabase: Authentication &gt; URL Configuration &gt; Site URL https://tonygreenberg.com and Redirect URLs https://tonygreenberg.com/auth/callback, https://*--tonygreenberg-website.netlify.app/auth/callback, http://localhost:3000/auth/callback. Then set NEXT_PUBLIC_SUPABASE_URL, NEXT_PUBLIC_SUPABASE_ANON_KEY, SUPABASE_SERVICE_ROLE_KEY, ADMIN_EMAILS in Netlify.</t>
+          <t>Then run the database scripts once, in order (supabase/migrations/0001_member_features.sql, then 0002_blog_engagement.sql, then 0003_legacy_vendor_intake.sql for essay comments, reactions, ratings and micro-commitments; 0001: highlights, referral codes/referrals, Clock Keeper responses, post-intervention, friend gate, PRI calibrations, all with row-level security) in Supabase: SQL Editor &gt; New query &gt; paste &gt; Run. Also in Supabase: Authentication &gt; URL Configuration &gt; Site URL https://tonygreenberg.com and Redirect URLs https://tonygreenberg.com/auth/callback, https://*--tonygreenberg-website.netlify.app/auth/callback, http://localhost:3000/auth/callback. Then set NEXT_PUBLIC_SUPABASE_URL, NEXT_PUBLIC_SUPABASE_ANON_KEY, SUPABASE_SERVICE_ROLE_KEY, ADMIN_EMAILS in Netlify.</t>
         </is>
       </c>
       <c r="E43" s="14" t="inlineStr">
@@ -8413,7 +8413,7 @@
       <c r="A331" s="4" t="n"/>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+          <t>DNS cutover, legacy app decommissioned only after a stable overlap window Checked 2026-10-09 (owner wants to go live and switch off Manus)</t>
         </is>
       </c>
       <c r="C331" s="15" t="inlineStr">
@@ -8421,7 +8421,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D331" s="4" t="inlineStr"/>
+      <c r="D331" s="4" t="inlineStr">
+        <is>
+          <t>DNS for tonygreenberg.com is at Hostinger (name servers ns1/ns2.dns-parking.com); www is a CNAME to cname.manus.space, the bare domain points at Manus's addresses (104.19.168.112 / .169.112); the Netlify site tonygreenberg-website has no custom domain yet (production branch main). Order: (1) merge the three open pull requests into main and check the Netlify copy; (2) restore Supabase and run 0001 to 0003, or launch without member features (they say "isn't available just now"); (3) owner sign-off; (4) add tonygreenberg.com + www in Netlify (Domain management), then at Hostinger point the bare domain at Netlify (A record 75.2.60.5, or Netlify DNS) and www CNAME at tonygreenberg-website.netlify.app; Netlify issues the HTTPS certificate; (5) re-run scripts/check-search-console-urls.ts https://tonygreenberg.com and submit the sitemap in Search Console; (6) only after a few stable days: switch off the Manus site (the database is already backed up, docs/ai/project_legacy_database.md) and rotate the old database password.</t>
+        </is>
+      </c>
       <c r="E331" s="14" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>
@@ -8540,7 +8544,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Connection details in .env.local (LEGACY_DATABASE_URL). Done: read-only check of all 56 tables and a full private backup (75,128 rows) to ~/Desktop/tonyg-site-backups/legacy-db-export-2026-10-09/ on the webmaster's Mac (personal data: never commit); most rows are the Manus agent's automated tests (details: docs/ai/project_legacy_database.md); the 198 short share links /s/&lt;code&gt; now redirect (src/lib/content/short-links.ts; 196 land on a page, 2 targets don't exist on live either). Left (needs a yes): add the 36 real email subscribers to Kit (may send Kit's confirmation email); copy the handful of real reactions/ratings/commitment into Supabase after the scripts below are run; decide whether the ~24 real assessment results, ~17 PRI consents, 2 manifesto responses, 8 supplier forms and 1 Cheshire submission stay in the backup only. Then rotate the database password (it was pasted in a chat) and remove LEGACY_DATABASE_URL.</t>
+          <t>Connection details in .env.local (LEGACY_DATABASE_URL). Done: read-only check of all 56 tables and a full private backup (75,128 rows) to ~/Desktop/tonyg-site-backups/legacy-db-export-2026-10-09/ on the webmaster's Mac (personal data: never commit); most rows are the Manus agent's automated tests (details: docs/ai/project_legacy_database.md); the 198 short share links /s/&lt;code&gt; now redirect (src/lib/content/short-links.ts; 196 land on a page, 2 targets don't exist on live either). Done 2026-10-09 (owner said yes): email subscribers in Kit with no email sent (5 already there, 27 added on the new tag "Legacy site import 2026-10-09", 4 refused by Kit's suppression list); the missing 2026-10-07 Daily Provocation added; supplier forms: table script supabase/migrations/0003_legacy_vendor_intake.sql and scripts/import-legacy-vendor-intake.ts ready (owner: supplier forms to Supabase, everything else stays in the backup). Left: restore the paused Supabase project, run 0001 to 0003, run the import; the few reactions/ratings (optional). Then rotate the database password (it was pasted in a chat) and remove LEGACY_DATABASE_URL.</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
@@ -8553,7 +8557,7 @@
       <c r="A5" s="4" t="n"/>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Run the database scripts once, in order</t>
+          <t>Restore the Supabase project first: it was paused (2026-10-09, its address no longer resolves), so every member feature, comment and reaction is off until someone with the Supabase account clicks "Restore project"</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -8563,7 +8567,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>(supabase/migrations/0001_member_features.sql, then 0002_blog_engagement.sql for essay comments, reactions, ratings and micro-commitments; 0001: highlights, referral codes/referrals, Clock Keeper responses, post-intervention, friend gate, PRI calibrations, all with row-level security) in Supabase: SQL Editor &gt; New query &gt; paste &gt; Run. Also in Supabase: Authentication &gt; URL Configuration &gt; Site URL https://tonygreenberg.com and Redirect URLs https://tonygreenberg.com/auth/callback, https://*--tonygreenberg-website.netlify.app/auth/callback, http://localhost:3000/auth/callback. Then set NEXT_PUBLIC_SUPABASE_URL, NEXT_PUBLIC_SUPABASE_ANON_KEY, SUPABASE_SERVICE_ROLE_KEY, ADMIN_EMAILS in Netlify.</t>
+          <t>Then run the database scripts once, in order (supabase/migrations/0001_member_features.sql, then 0002_blog_engagement.sql, then 0003_legacy_vendor_intake.sql for essay comments, reactions, ratings and micro-commitments; 0001: highlights, referral codes/referrals, Clock Keeper responses, post-intervention, friend gate, PRI calibrations, all with row-level security) in Supabase: SQL Editor &gt; New query &gt; paste &gt; Run. Also in Supabase: Authentication &gt; URL Configuration &gt; Site URL https://tonygreenberg.com and Redirect URLs https://tonygreenberg.com/auth/callback, https://*--tonygreenberg-website.netlify.app/auth/callback, http://localhost:3000/auth/callback. Then set NEXT_PUBLIC_SUPABASE_URL, NEXT_PUBLIC_SUPABASE_ANON_KEY, SUPABASE_SERVICE_ROLE_KEY, ADMIN_EMAILS in Netlify.</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -8982,7 +8986,7 @@
       <c r="A27" s="4" t="n"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>DNS cutover, legacy app decommissioned only after a stable overlap window</t>
+          <t>DNS cutover, legacy app decommissioned only after a stable overlap window Checked 2026-10-09 (owner wants to go live and switch off Manus)</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -8990,7 +8994,11 @@
           <t>Remaining</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>DNS for tonygreenberg.com is at Hostinger (name servers ns1/ns2.dns-parking.com); www is a CNAME to cname.manus.space, the bare domain points at Manus's addresses (104.19.168.112 / .169.112); the Netlify site tonygreenberg-website has no custom domain yet (production branch main). Order: (1) merge the three open pull requests into main and check the Netlify copy; (2) restore Supabase and run 0001 to 0003, or launch without member features (they say "isn't available just now"); (3) owner sign-off; (4) add tonygreenberg.com + www in Netlify (Domain management), then at Hostinger point the bare domain at Netlify (A record 75.2.60.5, or Netlify DNS) and www CNAME at tonygreenberg-website.netlify.app; Netlify issues the HTTPS certificate; (5) re-run scripts/check-search-console-urls.ts https://tonygreenberg.com and submit the sitemap in Search Console; (6) only after a few stable days: switch off the Manus site (the database is already backed up, docs/ai/project_legacy_database.md) and rotate the old database password.</t>
+        </is>
+      </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
           <t>Phase 14 — QA &amp; Launch</t>

--- a/Migration-Status-Report.xlsx
+++ b/Migration-Status-Report.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Remaining Work" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$331</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Remaining Work'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Full Detail'!$A$1:$D$333</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Remaining Work'!$A$1:$D$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -639,15 +639,15 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A5,'Full Detail'!$C$2:$C$331,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A5,'Full Detail'!$C$2:$C$333,"Done")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A5,'Full Detail'!$C$2:$C$331,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A5,'Full Detail'!$C$2:$C$333,"Remaining")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A5,'Full Detail'!$C$2:$C$331,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A5,'Full Detail'!$C$2:$C$333,"Deferred")</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -666,15 +666,15 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A6,'Full Detail'!$C$2:$C$331,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A6,'Full Detail'!$C$2:$C$333,"Done")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A6,'Full Detail'!$C$2:$C$331,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A6,'Full Detail'!$C$2:$C$333,"Remaining")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A6,'Full Detail'!$C$2:$C$331,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A6,'Full Detail'!$C$2:$C$333,"Deferred")</f>
         <v/>
       </c>
       <c r="E6" s="5">
@@ -693,15 +693,15 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A7,'Full Detail'!$C$2:$C$331,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A7,'Full Detail'!$C$2:$C$333,"Done")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A7,'Full Detail'!$C$2:$C$331,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A7,'Full Detail'!$C$2:$C$333,"Remaining")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A7,'Full Detail'!$C$2:$C$331,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A7,'Full Detail'!$C$2:$C$333,"Deferred")</f>
         <v/>
       </c>
       <c r="E7" s="5">
@@ -720,15 +720,15 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A8,'Full Detail'!$C$2:$C$331,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A8,'Full Detail'!$C$2:$C$333,"Done")</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A8,'Full Detail'!$C$2:$C$331,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A8,'Full Detail'!$C$2:$C$333,"Remaining")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A8,'Full Detail'!$C$2:$C$331,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A8,'Full Detail'!$C$2:$C$333,"Deferred")</f>
         <v/>
       </c>
       <c r="E8" s="5">
@@ -747,15 +747,15 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A9,'Full Detail'!$C$2:$C$331,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A9,'Full Detail'!$C$2:$C$333,"Done")</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A9,'Full Detail'!$C$2:$C$331,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A9,'Full Detail'!$C$2:$C$333,"Remaining")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A9,'Full Detail'!$C$2:$C$331,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A9,'Full Detail'!$C$2:$C$333,"Deferred")</f>
         <v/>
       </c>
       <c r="E9" s="5">
@@ -774,15 +774,15 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A10,'Full Detail'!$C$2:$C$331,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A10,'Full Detail'!$C$2:$C$333,"Done")</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A10,'Full Detail'!$C$2:$C$331,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A10,'Full Detail'!$C$2:$C$333,"Remaining")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A10,'Full Detail'!$C$2:$C$331,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A10,'Full Detail'!$C$2:$C$333,"Deferred")</f>
         <v/>
       </c>
       <c r="E10" s="5">
@@ -801,15 +801,15 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A11,'Full Detail'!$C$2:$C$331,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A11,'Full Detail'!$C$2:$C$333,"Done")</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A11,'Full Detail'!$C$2:$C$331,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A11,'Full Detail'!$C$2:$C$333,"Remaining")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A11,'Full Detail'!$C$2:$C$331,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A11,'Full Detail'!$C$2:$C$333,"Deferred")</f>
         <v/>
       </c>
       <c r="E11" s="5">
@@ -828,15 +828,15 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A12,'Full Detail'!$C$2:$C$331,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A12,'Full Detail'!$C$2:$C$333,"Done")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A12,'Full Detail'!$C$2:$C$331,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A12,'Full Detail'!$C$2:$C$333,"Remaining")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A12,'Full Detail'!$C$2:$C$331,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A12,'Full Detail'!$C$2:$C$333,"Deferred")</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -855,15 +855,15 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A13,'Full Detail'!$C$2:$C$331,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A13,'Full Detail'!$C$2:$C$333,"Done")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A13,'Full Detail'!$C$2:$C$331,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A13,'Full Detail'!$C$2:$C$333,"Remaining")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A13,'Full Detail'!$C$2:$C$331,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A13,'Full Detail'!$C$2:$C$333,"Deferred")</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -882,15 +882,15 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A14,'Full Detail'!$C$2:$C$331,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A14,'Full Detail'!$C$2:$C$333,"Done")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A14,'Full Detail'!$C$2:$C$331,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A14,'Full Detail'!$C$2:$C$333,"Remaining")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A14,'Full Detail'!$C$2:$C$331,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A14,'Full Detail'!$C$2:$C$333,"Deferred")</f>
         <v/>
       </c>
       <c r="E14" s="5">
@@ -909,15 +909,15 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A15,'Full Detail'!$C$2:$C$331,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A15,'Full Detail'!$C$2:$C$333,"Done")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A15,'Full Detail'!$C$2:$C$331,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A15,'Full Detail'!$C$2:$C$333,"Remaining")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A15,'Full Detail'!$C$2:$C$331,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A15,'Full Detail'!$C$2:$C$333,"Deferred")</f>
         <v/>
       </c>
       <c r="E15" s="5">
@@ -936,15 +936,15 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A16,'Full Detail'!$C$2:$C$331,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A16,'Full Detail'!$C$2:$C$333,"Done")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A16,'Full Detail'!$C$2:$C$331,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A16,'Full Detail'!$C$2:$C$333,"Remaining")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A16,'Full Detail'!$C$2:$C$331,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A16,'Full Detail'!$C$2:$C$333,"Deferred")</f>
         <v/>
       </c>
       <c r="E16" s="5">
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A17,'Full Detail'!$C$2:$C$331,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A17,'Full Detail'!$C$2:$C$333,"Done")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A17,'Full Detail'!$C$2:$C$331,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A17,'Full Detail'!$C$2:$C$333,"Remaining")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A17,'Full Detail'!$C$2:$C$331,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A17,'Full Detail'!$C$2:$C$333,"Deferred")</f>
         <v/>
       </c>
       <c r="E17" s="5">
@@ -990,15 +990,15 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A18,'Full Detail'!$C$2:$C$331,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A18,'Full Detail'!$C$2:$C$333,"Done")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A18,'Full Detail'!$C$2:$C$331,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A18,'Full Detail'!$C$2:$C$333,"Remaining")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A18,'Full Detail'!$C$2:$C$331,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A18,'Full Detail'!$C$2:$C$333,"Deferred")</f>
         <v/>
       </c>
       <c r="E18" s="5">
@@ -1017,15 +1017,15 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A19,'Full Detail'!$C$2:$C$331,"Done")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A19,'Full Detail'!$C$2:$C$333,"Done")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A19,'Full Detail'!$C$2:$C$331,"Remaining")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A19,'Full Detail'!$C$2:$C$333,"Remaining")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Full Detail'!$E$2:$E$331,$A19,'Full Detail'!$C$2:$C$331,"Deferred")</f>
+        <f>COUNTIFS('Full Detail'!$E$2:$E$333,$A19,'Full Detail'!$C$2:$C$333,"Deferred")</f>
         <v/>
       </c>
       <c r="E19" s="5">
@@ -1075,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E331"/>
+  <dimension ref="A1:E333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1930,7 +1930,7 @@
       <c r="A41" s="4" t="n"/>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Email for the Three Friends Gate</t>
+          <t>Fix the Supabase secret key (found 2026-10-09)</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>create a free account at resend.com, verify a sending domain (adds DNS records on tonygreenberg.com, so whoever manages DNS), then set RESEND_API_KEY and EMAIL_FROM (e.g. Only Time Buys Trust &lt;trust@tonygreenberg.com&gt;) in Netlify and .env.local. Until then invites and codes are not sent (logged on the server instead).</t>
+          <t>SUPABASE_SERVICE_ROLE_KEY in .env.local and in Netlify is a damaged copy of the project's secret key (44 characters, the real sb_secret_… key has 41), so every server-side Supabase call fails ("Invalid API key"): comments, reactions, ratings, Ask Tony, highlights, invites, Clock Keeper, post-intervention, friend gate, the /pri-efficacy Live tab. Fix: Supabase dashboard &gt; Project Settings &gt; API Keys &gt; Secret keys &gt; copy the default key, paste it as SUPABASE_SERVICE_ROLE_KEY in .env.local and in Netlify (all scopes), redeploy. (The AI session wasn't allowed to write secrets.) The publishable key (NEXT_PUBLIC_SUPABASE_ANON_KEY) is correct.</t>
         </is>
       </c>
       <c r="E41" s="14" t="inlineStr">
@@ -1953,7 +1953,7 @@
       <c r="A42" s="4" t="n"/>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Old site's visitor data from the Manus database (owner asked, 2026-10-09)</t>
+          <t>Set SANITY_WEBHOOK_SECRET (found 2026-10-09)</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Connection details in .env.local (LEGACY_DATABASE_URL). Done: read-only check of all 56 tables and a full private backup (75,128 rows) to ~/Desktop/tonyg-site-backups/legacy-db-export-2026-10-09/ on the webmaster's Mac (personal data: never commit); most rows are the Manus agent's automated tests (details: docs/ai/project_legacy_database.md); the 198 short share links /s/&lt;code&gt; now redirect (src/lib/content/short-links.ts; 196 land on a page, 2 targets don't exist on live either). Done 2026-10-09 (owner said yes): email subscribers in Kit with no email sent (5 already there, 27 added on the new tag "Legacy site import 2026-10-09", 4 refused by Kit's suppression list); the missing 2026-10-07 Daily Provocation added; supplier forms: table script supabase/migrations/0003_legacy_vendor_intake.sql and scripts/import-legacy-vendor-intake.ts ready (owner: supplier forms to Supabase, everything else stays in the backup). Left: restore the paused Supabase project, run 0001 to 0003, run the import; the few reactions/ratings (optional). Then rotate the database password (it was pasted in a chat) and remove LEGACY_DATABASE_URL.</t>
+          <t>missing in Netlify and .env.local, so Sanity's publish webhook to /api/revalidate is refused and edits appear only after the 60-second refresh. Create the webhook secret in Sanity (manage &gt; API &gt; Webhooks) and add it to Netlify.</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
@@ -1976,7 +1976,7 @@
       <c r="A43" s="4" t="n"/>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Restore the Supabase project first: it was paused (2026-10-09, its address no longer resolves), so every member feature, comment and reaction is off until someone with the Supabase account clicks "Restore project"</t>
+          <t>Email for the Three Friends Gate</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Then run the database scripts once, in order (supabase/migrations/0001_member_features.sql, then 0002_blog_engagement.sql, then 0003_legacy_vendor_intake.sql for essay comments, reactions, ratings and micro-commitments; 0001: highlights, referral codes/referrals, Clock Keeper responses, post-intervention, friend gate, PRI calibrations, all with row-level security) in Supabase: SQL Editor &gt; New query &gt; paste &gt; Run. Also in Supabase: Authentication &gt; URL Configuration &gt; Site URL https://tonygreenberg.com and Redirect URLs https://tonygreenberg.com/auth/callback, https://*--tonygreenberg-website.netlify.app/auth/callback, http://localhost:3000/auth/callback. Then set NEXT_PUBLIC_SUPABASE_URL, NEXT_PUBLIC_SUPABASE_ANON_KEY, SUPABASE_SERVICE_ROLE_KEY, ADMIN_EMAILS in Netlify.</t>
+          <t>create a free account at resend.com, verify a sending domain (adds DNS records on tonygreenberg.com, so whoever manages DNS), then set RESEND_API_KEY and EMAIL_FROM (e.g. Only Time Buys Trust &lt;trust@tonygreenberg.com&gt;) in Netlify and .env.local. Until then invites and codes are not sent (logged on the server instead).</t>
         </is>
       </c>
       <c r="E43" s="14" t="inlineStr">
@@ -1996,20 +1996,33 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>Phase 3 — Shared Layout &amp; Design System</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="11" t="n"/>
-      <c r="D44" s="12" t="n"/>
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Old site's visitor data from the Manus database (owner asked, 2026-10-09)</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Connection details in .env.local (LEGACY_DATABASE_URL). Done: read-only check of all 56 tables and a full private backup (75,128 rows) to ~/Desktop/tonyg-site-backups/legacy-db-export-2026-10-09/ on the webmaster's Mac (personal data: never commit); most rows are the Manus agent's automated tests (details: docs/ai/project_legacy_database.md); the 198 short share links /s/&lt;code&gt; now redirect (src/lib/content/short-links.ts; 196 land on a page, 2 targets don't exist on live either). Done 2026-10-09 (owner said yes): email subscribers in Kit with no email sent (5 already there, 27 added on the new tag "Legacy site import 2026-10-09", 4 refused by Kit's suppression list); the missing 2026-10-07 Daily Provocation added; supplier forms: table script supabase/migrations/0003_legacy_vendor_intake.sql and scripts/import-legacy-vendor-intake.ts ready (owner: supplier forms to Supabase, everything else stays in the backup). Done 2026-10-09 (owner: "add all data in old db to new supabase"): every legacy table copied into a private legacy schema in Supabase (55 tables, 75,089 rows, counts match; the old app's migration log skipped), row-level security on, not exposed to the site's API, no access for anon/authenticated; the 8 supplier forms also in public.legacy_vendor_intake. Left: the site's Supabase secret key is wrong (see Phase 2); rotate the old database password and remove LEGACY_DATABASE_URL; remove SUPABASE_ACCESS_TOKEN from .env.local when setup is done. Then rotate the database </t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Phase 2 — Supabase</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n"/>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Root layout (web/src/app/layout.tsx)</t>
+          <t>Database scripts run (2026-10-09, through a Supabase access token the owner added)</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
@@ -2019,39 +2032,30 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>fonts (Playfair Display / DM Mono / Source Sans 3 via next/font/google), &lt;TooltipProvider&gt;, theme provider (next-themes, class strategy), global &lt;Toaster /&gt; (sonner), skip-to-content link</t>
+          <t>0001, 0002 and 0003, 13 tables, row-level security on, 5 policies; checked through the Management API. (Correction: the project was never paused; this Mac's DNS briefly failed to resolve its address.) Original item: run the database scripts once, in order (supabase/migrations/0001_member_features.sql, then 0002_blog_engagement.sql, then 0003_legacy_vendor_intake.sql for essay comments, reactions, ratings and micro-commitments; 0001: highlights, referral codes/referrals, Clock Keeper responses, post-intervention, friend gate, PRI calibrations, all with row-level security) in Supabase: SQL Editor &gt; New query &gt; paste &gt; Run. Also in Supabase: Authentication &gt; URL Configuration &gt; Site URL https://tonygreenberg.com and Redirect URLs https://tonygreenberg.com/auth/callback, https://*--tonygreenberg-website.netlify.app/auth/callback, http://localhost:3000/auth/callback. Then set NEXT_PUBLIC_SUPABASE_URL, NEXT_PUBLIC_SUPABASE_ANON_KEY, SUPABASE_SERVICE_ROLE_KEY, ADMIN_EMAILS in Netlify.</t>
         </is>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
+          <t>Phase 2 — Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
           <t>Phase 3 — Shared Layout &amp; Design System</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n"/>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Global metadata defaults in root layout (metadataBase, title template, default OG/Twitter card)</t>
-        </is>
-      </c>
-      <c r="C46" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr"/>
-      <c r="E46" s="14" t="inlineStr">
-        <is>
-          <t>Phase 3 — Shared Layout &amp; Design System</t>
-        </is>
-      </c>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n"/>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Favicon (src/app/icon.tsx)</t>
+          <t>Root layout (web/src/app/layout.tsx)</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
@@ -2061,7 +2065,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>real brand mark, not the default Next.js icon: a generated 32×32 PNG of the "G" from the header's actual "TonyG" wordmark (Playfair Display, brand-gold), since the full wordmark doesn't read at favicon scale. Deleted the stale default favicon.ico.</t>
+          <t>fonts (Playfair Display / DM Mono / Source Sans 3 via next/font/google), &lt;TooltipProvider&gt;, theme provider (next-themes, class strategy), global &lt;Toaster /&gt; (sonner), skip-to-content link</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
@@ -2074,7 +2078,7 @@
       <c r="A48" s="4" t="n"/>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Header/nav component (site-header.tsx)</t>
+          <t>Global metadata defaults in root layout (metadataBase, title template, default OG/Twitter card)</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
@@ -2082,11 +2086,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>real nav structure ported from legacy Layout.tsx (primary links, "Fix Myself"/"Explore" mega-menus, socials, theme toggle), built with shadcn NavigationMenu. Deliberately not ported: StartHereBanner, ExitIntentTony, TonyAvatarTrigger, NotificationBell, ReadingStreakBadge, WhereNext — separate behavioral/engagement features, not core layout, out of scope for this phase</t>
-        </is>
-      </c>
+      <c r="D48" s="4" t="inlineStr"/>
       <c r="E48" s="14" t="inlineStr">
         <is>
           <t>Phase 3 — Shared Layout &amp; Design System</t>
@@ -2097,7 +2097,7 @@
       <c r="A49" s="4" t="n"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Mobile nav (shadcn Sheet + Accordion, real nav content, no framer-motion)</t>
+          <t>Favicon (src/app/icon.tsx)</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
@@ -2105,7 +2105,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr"/>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>real brand mark, not the default Next.js icon: a generated 32×32 PNG of the "G" from the header's actual "TonyG" wordmark (Playfair Display, brand-gold), since the full wordmark doesn't read at favicon scale. Deleted the stale default favicon.ico.</t>
+        </is>
+      </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
           <t>Phase 3 — Shared Layout &amp; Design System</t>
@@ -2116,7 +2120,7 @@
       <c r="A50" s="4" t="n"/>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Footer component (site-footer.tsx)</t>
+          <t>Header/nav component (site-header.tsx)</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -2126,7 +2130,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>real content ported from Layout.tsx's footer JSX (quote, contact, BioChain routing note, socials, CTAs, bio line, legal/copyright). Note: footerData.json turned out to be per-post article-footer data (exercise/related/riddle/CTA), not site footer content — that belongs in Phase 5, not here</t>
+          <t>real nav structure ported from legacy Layout.tsx (primary links, "Fix Myself"/"Explore" mega-menus, socials, theme toggle), built with shadcn NavigationMenu. Deliberately not ported: StartHereBanner, ExitIntentTony, TonyAvatarTrigger, NotificationBell, ReadingStreakBadge, WhereNext — separate behavioral/engagement features, not core layout, out of scope for this phase</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
@@ -2139,7 +2143,7 @@
       <c r="A51" s="4" t="n"/>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Brand design tokens in globals.css (--brand-gold/--brand-gold-light/backgrounds/borders) ported from the real site palette (#8B6914, #D4B96A…</t>
+          <t>Mobile nav (shadcn Sheet + Accordion, real nav content, no framer-motion)</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
@@ -2147,11 +2151,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>, #0A0A10, #FAFAF7, purple-tinted borders) instead of shadcn's default grayscale theme</t>
-        </is>
-      </c>
+      <c r="D51" s="4" t="inlineStr"/>
       <c r="E51" s="14" t="inlineStr">
         <is>
           <t>Phase 3 — Shared Layout &amp; Design System</t>
@@ -2162,7 +2162,7 @@
       <c r="A52" s="4" t="n"/>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Shared typography components</t>
+          <t>Footer component (site-footer.tsx)</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>ended up built directly in Phase 5 (portable-text.tsx, drop-cap CSS, pull-quote block) rather than as a separate Phase 3 deliverable, since that's where they're actually consumed</t>
+          <t>real content ported from Layout.tsx's footer JSX (quote, contact, BioChain routing note, socials, CTAs, bio line, legal/copyright). Note: footerData.json turned out to be per-post article-footer data (exercise/related/riddle/CTA), not site footer content — that belongs in Phase 5, not here</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
@@ -2185,7 +2185,7 @@
       <c r="A53" s="4" t="n"/>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>robots.ts (AI crawlers explicitly allowed per the current SEO plan, scraper bots blocked) and sitemap.ts (live from Sanity post slugs alread…</t>
+          <t>Brand design tokens in globals.css (--brand-gold/--brand-gold-light/backgrounds/borders) ported from the real site palette (#8B6914, #D4B96A…</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>y, extended per-section in later phases)</t>
+          <t>, #0A0A10, #FAFAF7, purple-tinted borders) instead of shadcn's default grayscale theme</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
@@ -2208,7 +2208,7 @@
       <c r="A54" s="4" t="n"/>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Error boundary (error.tsx) and not-found.tsx (real legacy 404 copy + countdown-redirect behavior ported from pages/NotFound.tsx)</t>
+          <t>Shared typography components</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
@@ -2216,7 +2216,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>ended up built directly in Phase 5 (portable-text.tsx, drop-cap CSS, pull-quote block) rather than as a separate Phase 3 deliverable, since that's where they're actually consumed</t>
+        </is>
+      </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
           <t>Phase 3 — Shared Layout &amp; Design System</t>
@@ -2227,7 +2231,7 @@
       <c r="A55" s="4" t="n"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Loading UI (loading.tsx) using shadcn Skeleton</t>
+          <t>robots.ts (AI crawlers explicitly allowed per the current SEO plan, scraper bots blocked) and sitemap.ts (live from Sanity post slugs alread…</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
@@ -2235,7 +2239,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>y, extended per-section in later phases)</t>
+        </is>
+      </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
           <t>Phase 3 — Shared Layout &amp; Design System</t>
@@ -2246,7 +2254,7 @@
       <c r="A56" s="4" t="n"/>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Icon library decision</t>
+          <t>Error boundary (error.tsx) and not-found.tsx (real legacy 404 copy + countdown-redirect behavior ported from pages/NotFound.tsx)</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
@@ -2254,11 +2262,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>lucide-react for all standard UI icons (menu, sun/moon, chevrons); react-icons/fa6 only for the X/LinkedIn brand marks, since lucide-react v1 dropped brand/logo icons entirely</t>
-        </is>
-      </c>
+      <c r="D56" s="4" t="inlineStr"/>
       <c r="E56" s="14" t="inlineStr">
         <is>
           <t>Phase 3 — Shared Layout &amp; Design System</t>
@@ -2269,7 +2273,7 @@
       <c r="A57" s="4" t="n"/>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Top-of-page navigation progress bar (nav-progress-bar.tsx)</t>
+          <t>Loading UI (loading.tsx) using shadcn Skeleton</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
@@ -2277,11 +2281,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>visible feedback on route transitions, built on the Navigation API (window.navigation) rather than a dependency like nprogress; progressive enhancement, renders nothing where unsupported</t>
-        </is>
-      </c>
+      <c r="D57" s="4" t="inlineStr"/>
       <c r="E57" s="14" t="inlineStr">
         <is>
           <t>Phase 3 — Shared Layout &amp; Design System</t>
@@ -2292,7 +2292,7 @@
       <c r="A58" s="4" t="n"/>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Verify header/footer/nav visually in a real browser</t>
+          <t>Icon library decision</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Done 2026-09-29 with side-by-side Playwright screenshots against the live tonygreenberg.com at 1280/1536px. The header was rebuilt to match legacy Layout.tsx: full-width translucent cream bar, purple hairline, 0.78rem semi-bold mono nav right-aligned, gold active link, tagline at legacy's breakpoints, and the "Ask Tony ⌘K" pill (legacy TonyDiscovery; it opens site search because the FauxTony chat half was cancelled), plus X/LinkedIn icons and the theme toggle. Also matched from the live site: the Four Doors modal (legacy FourDoorsModal.tsx: image header, Door badge, ochre rule, dark CTA, bottom sheet on mobile), the homepage BrewSoul "Intelligence Engine" band (legacy BrewSoulHero.tsx, background photo rescued into Sanity), and the default theme, now light and not following the OS, same as legacy's ThemeContext. The "New here? 90-second tour" banner (StartHereBanner) is still intentionally not ported.</t>
+          <t>lucide-react for all standard UI icons (menu, sun/moon, chevrons); react-icons/fa6 only for the X/LinkedIn brand marks, since lucide-react v1 dropped brand/logo icons entirely</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
@@ -2312,20 +2312,33 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>Phase 4 — Marketing Core Pages (30 routes)</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="n"/>
-      <c r="C59" s="11" t="n"/>
-      <c r="D59" s="12" t="n"/>
+      <c r="A59" s="4" t="n"/>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Top-of-page navigation progress bar (nav-progress-bar.tsx)</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>visible feedback on route transitions, built on the Navigation API (window.navigation) rather than a dependency like nprogress; progressive enhancement, renders nothing where unsupported</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>Phase 3 — Shared Layout &amp; Design System</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n"/>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>/ (homepage)</t>
+          <t>Verify header/footer/nav visually in a real browser</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
@@ -2335,43 +2348,30 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Blog.tsx. Not the same page as /the-letter — legacy actually routes path="/" to the Blog component, not Home.tsx (Home.tsx is legacy's /the-letter, already ported separately below); this had briefly regressed to a plain paginated post list before this pass corrected it. Real content ported: hero (headline, stats line, essay count/nav line), Four Doors (Read/Diagnose/Engage/Verify — reusing the shared FourDoors component built for /the-letter; its icon-tile fallback path stays in four-doors.tsx for resilience, but all 4 real source photos are now live — see the follow-up pass note below), Editor's Picks (5 real curated posts), GemSpark Strip (a real, small editorial motif — only 3 posts in the whole corpus reference it; hand-ported subtitles since Portable Text has no raw-heading string left to regex the way legacy did), Case File banner, Latest Thinking, Positioning Statement, Core Themes (4 theme cards linking to /?theme=X#essays-archive, read by the archive below), Ecosystem CTA (essay count now live from Sanity instead of legacy's stale hardcoded "ninety-one"), and the full searchable/filterable archive + sidebar (Curated Journeys, Tip Me Off, Follow). Intentionally not ported: the ABIT waitlist email-capture form (posts to a tRPC subscribe mutation — a backend/CRM feature, out of this migration's "no backend features" scope, not a content gap) and legacy's "Most Read"/"Most Provocative" sidebar widgets (both ranked by a reads count that defaulted to a flat placeholder val</t>
+          <t>Done 2026-09-29 with side-by-side Playwright screenshots against the live tonygreenberg.com at 1280/1536px. The header was rebuilt to match legacy Layout.tsx: full-width translucent cream bar, purple hairline, 0.78rem semi-bold mono nav right-aligned, gold active link, tagline at legacy's breakpoints, and the "Ask Tony ⌘K" pill (legacy TonyDiscovery; it opens site search because the FauxTony chat half was cancelled), plus X/LinkedIn icons and the theme toggle. Also matched from the live site: the Four Doors modal (legacy FourDoorsModal.tsx: image header, Door badge, ochre rule, dark CTA, bottom sheet on mobile), the homepage BrewSoul "Intelligence Engine" band (legacy BrewSoulHero.tsx, background photo rescued into Sanity), and the default theme, now light and not following the OS, same as legacy's ThemeContext. The "New here? 90-second tour" banner (StartHereBanner) is still intentionally not ported.</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
+          <t>Phase 3 — Shared Layout &amp; Design System</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
           <t>Phase 4 — Marketing Core Pages (30 routes)</t>
         </is>
       </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="n"/>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>/the-letter</t>
-        </is>
-      </c>
-      <c r="C61" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>Home.tsx. Real content/links/data ported (hero, Three Paths, Start Here essays, Four Doors as a shadcn Dialog instead of the legacy custom modal, Featured Essay pulled live from Sanity, How Tony Works, Investment Thesis, Open Questions, What I Build, Most Read, BrewSoul teaser). Deliberately not reproduced: floating-particle animation, glowing-bowl gradients, glitch text, magnetic-hover physics, typewriter intro — decorative flourishes, same judgment call as Phase 3's engagement widgets. Rescued 5 images (hero + 4 door photos) from the still-live legacy /api/img/ proxy into Sanity before porting (scripts/rescue-homepage-images.ts) rather than reference the fragile path. Fixed 2 legacy bugs found while porting: /ramprate and /human-os linked to routes that don't exist (corrected to https://ramprate.com and /humanos); "Most Read"'s 5 items all pointed at the same generic /blog placeholder instead of each post's real slug — corrected using the real migrated post slugs. Verified live: 200 OK, real content, fixed links, real images, no leaked inline styles, lint+typecheck clean.</t>
-        </is>
-      </c>
-      <c r="E61" s="14" t="inlineStr">
-        <is>
-          <t>Phase 4 — Marketing Core Pages (30 routes)</t>
-        </is>
-      </c>
+      <c r="B61" s="11" t="n"/>
+      <c r="C61" s="11" t="n"/>
+      <c r="D61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n"/>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>/walk-through</t>
+          <t>/ (homepage)</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>WalkThrough.tsx. Real content ported (7 doors, entity pills w/ real named investments, "Ask me about" lines, cross-links, pull quotes, "The Lesson" callout). Hero reuses the Tony headshot already rescued to Sanity (Phase 12 JSON-LD work) rather than re-fetching. Not ported: AutoLinkedText's automatic entity hyperlinking — that's driven by the site-wide linkMap.ts, a genuine cross-cutting feature affecting many pages, not a one-off for this page; folded into the existing "preserve internal cross-link structure" open item in Phase 5. Verified live: 200 OK, real content, real image, correct next-page link.</t>
+          <t>Blog.tsx. Not the same page as /the-letter — legacy actually routes path="/" to the Blog component, not Home.tsx (Home.tsx is legacy's /the-letter, already ported separately below); this had briefly regressed to a plain paginated post list before this pass corrected it. Real content ported: hero (headline, stats line, essay count/nav line), Four Doors (Read/Diagnose/Engage/Verify — reusing the shared FourDoors component built for /the-letter; its icon-tile fallback path stays in four-doors.tsx for resilience, but all 4 real source photos are now live — see the follow-up pass note below), Editor's Picks (5 real curated posts), GemSpark Strip (a real, small editorial motif — only 3 posts in the whole corpus reference it; hand-ported subtitles since Portable Text has no raw-heading string left to regex the way legacy did), Case File banner, Latest Thinking, Positioning Statement, Core Themes (4 theme cards linking to /?theme=X#essays-archive, read by the archive below), Ecosystem CTA (essay count now live from Sanity instead of legacy's stale hardcoded "ninety-one"), and the full searchable/filterable archive + sidebar (Curated Journeys, Tip Me Off, Follow). Intentionally not ported: the ABIT waitlist email-capture form (posts to a tRPC subscribe mutation — a backend/CRM feature, out of this migration's "no backend features" scope, not a content gap) and legacy's "Most Read"/"Most Provocative" sidebar widgets (both ranked by a reads count that defaulted to a flat placeholder val</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
@@ -2394,7 +2394,7 @@
       <c r="A63" s="4" t="n"/>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>/the-territory</t>
+          <t>/the-letter</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Territory.tsx. Real content ported (10 heroes/influences with full notes, Operating Philosophy, pull quote, "The Lesson" callout, next-page link). Verified live: 200 OK, real content, correct next-page link.</t>
+          <t>Home.tsx. Real content/links/data ported (hero, Three Paths, Start Here essays, Four Doors as a shadcn Dialog instead of the legacy custom modal, Featured Essay pulled live from Sanity, How Tony Works, Investment Thesis, Open Questions, What I Build, Most Read, BrewSoul teaser). Deliberately not reproduced: floating-particle animation, glowing-bowl gradients, glitch text, magnetic-hover physics, typewriter intro — decorative flourishes, same judgment call as Phase 3's engagement widgets. Rescued 5 images (hero + 4 door photos) from the still-live legacy /api/img/ proxy into Sanity before porting (scripts/rescue-homepage-images.ts) rather than reference the fragile path. Fixed 2 legacy bugs found while porting: /ramprate and /human-os linked to routes that don't exist (corrected to https://ramprate.com and /humanos); "Most Read"'s 5 items all pointed at the same generic /blog placeholder instead of each post's real slug — corrected using the real migrated post slugs. Verified live: 200 OK, real content, fixed links, real images, no leaked inline styles, lint+typecheck clean.</t>
         </is>
       </c>
       <c r="E63" s="14" t="inlineStr">
@@ -2417,7 +2417,7 @@
       <c r="A64" s="4" t="n"/>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>/engine-room</t>
+          <t>/walk-through</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>EngineRoom.tsx. Real content ported (6 active ventures, 4 active engagements, pull quote, "The Lesson" callout, next-page link). Verified live: 200 OK, real content, correct next-page link.</t>
+          <t>WalkThrough.tsx. Real content ported (7 doors, entity pills w/ real named investments, "Ask me about" lines, cross-links, pull quotes, "The Lesson" callout). Hero reuses the Tony headshot already rescued to Sanity (Phase 12 JSON-LD work) rather than re-fetching. Not ported: AutoLinkedText's automatic entity hyperlinking — that's driven by the site-wide linkMap.ts, a genuine cross-cutting feature affecting many pages, not a one-off for this page; folded into the existing "preserve internal cross-link structure" open item in Phase 5. Verified live: 200 OK, real content, real image, correct next-page link.</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
@@ -2440,7 +2440,7 @@
       <c r="A65" s="4" t="n"/>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>/under-nda</t>
+          <t>/the-territory</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>UnderNDA.tsx. Real content ported (Corridor overview, pull quote, "What We're Building" list, inline quote, "The Lesson", next-page link). Verified live: 200 OK.</t>
+          <t>Territory.tsx. Real content ported (10 heroes/influences with full notes, Operating Philosophy, pull quote, "The Lesson" callout, next-page link). Verified live: 200 OK, real content, correct next-page link.</t>
         </is>
       </c>
       <c r="E65" s="14" t="inlineStr">
@@ -2463,7 +2463,7 @@
       <c r="A66" s="4" t="n"/>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>/the-body</t>
+          <t>/engine-room</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>TheBody.tsx. Real content ported (Alt Therapy Scorecard, Current Protocols, Peptide Research Tools links, pull quote, "The Lesson"). Hero image rescued from legacy /api/img/ into Sanity before porting. Verified live: 200 OK, real image.</t>
+          <t>EngineRoom.tsx. Real content ported (6 active ventures, 4 active engagements, pull quote, "The Lesson" callout, next-page link). Verified live: 200 OK, real content, correct next-page link.</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
@@ -2486,7 +2486,7 @@
       <c r="A67" s="4" t="n"/>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>/the-nightstand</t>
+          <t>/under-nda</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Nightstand.tsx. Real content ported (7 books, 5 key concepts, pull quote, "The Lesson"). Hero image rescued into Sanity. Verified live: 200 OK, real image.</t>
+          <t>UnderNDA.tsx. Real content ported (Corridor overview, pull quote, "What We're Building" list, inline quote, "The Lesson", next-page link). Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
@@ -2509,7 +2509,7 @@
       <c r="A68" s="4" t="n"/>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>/the-web</t>
+          <t>/the-body</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>TheWeb.tsx. Real content ported (20 client badges, 4 key partnerships, pull quote, adage strip, "The Lesson"). Hero image rescued into Sanity. Verified live: 200 OK, real image.</t>
+          <t>TheBody.tsx. Real content ported (Alt Therapy Scorecard, Current Protocols, Peptide Research Tools links, pull quote, "The Lesson"). Hero image rescued from legacy /api/img/ into Sanity before porting. Verified live: 200 OK, real image.</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
@@ -2532,7 +2532,7 @@
       <c r="A69" s="4" t="n"/>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>/pick-up-the-phone</t>
+          <t>/the-nightstand</t>
         </is>
       </c>
       <c r="C69" s="13" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>PickUp.tsx. Real content ported (Engagement Audit CTA to /engage, email/location, "What to Talk About" topics, social links, pull quote, "The Lesson"). Verified live: 200 OK.</t>
+          <t>Nightstand.tsx. Real content ported (7 books, 5 key concepts, pull quote, "The Lesson"). Hero image rescued into Sanity. Verified live: 200 OK, real image.</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
@@ -2555,7 +2555,7 @@
       <c r="A70" s="4" t="n"/>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>/journeys</t>
+          <t>/the-web</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Journeys.tsx. Real content ported (7 curated journeys, all real stops/teasers), rebuilt as a proper shadcn Accordion instead of hand-rolled expand state. Fixed 2 legacy bugs: stops pointing at / meant the old homepage — remapped to /the-letter since / is now the blog index; 3 "Crusade Files" stops pointed at the generic /blog placeholder instead of the specific post — corrected to real slugs. Also caught a real SEO issue: shadcn's AccordionContent doesn't render collapsed-panel children into the DOM at all by default — every internal link on this link-heavy page was invisible to crawlers until a user clicked to expand it. Fixed with forceMount (documented inline). Worth checking any other page that ends up using Accordion for real content, not just decoration. Verified live: 200 OK, all links (including the corrected ones) present in the raw server-rendered HTML, not just after hydration.</t>
+          <t>TheWeb.tsx. Real content ported (20 client badges, 4 key partnerships, pull quote, adage strip, "The Lesson"). Hero image rescued into Sanity. Verified live: 200 OK, real image.</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
@@ -2578,7 +2578,7 @@
       <c r="A71" s="4" t="n"/>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>/recent-creations</t>
+          <t>/pick-up-the-phone</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Portfolio.tsx. Real content ported (11 project cards, real accent colors — the one legitimate per-item inline-style exception, static Tailwind classes can't express 11 runtime hex values). Fixed a dead internal link (Homeaglow Exposed pointed at a route that doesn't exist anywhere; corrected to the real external homeaglowexposed.com already used consistently on other ported pages) and remapped / → /the-letter. Flagged but did NOT fix: "FusionRamp / STRATUM" points at /humanos, same as the unrelated Human OS card — looks like a copy-paste bug but there's no confirmed correct destination anywhere in the codebase, so ported as-is with a comment rather than guessed; worth a content-team check. Verified live: 200 OK, fixed links present.</t>
+          <t>PickUp.tsx. Real content ported (Engagement Audit CTA to /engage, email/location, "What to Talk About" topics, social links, pull quote, "The Lesson"). Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
@@ -2601,7 +2601,7 @@
       <c r="A72" s="4" t="n"/>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>/intel</t>
+          <t>/journeys</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Intel.tsx. Real content ported in full (9 portfolio companies, each with investment thesis, three gates, 7-dimension compass scores, full iRR framework, competitive landscape). Rebuilt as a shadcn Accordion with forceMount from the start (learned from /journeys), verified live that investment-thesis/competitor text is present in the raw SSR HTML, not just after a click. Verified live: 200 OK.</t>
+          <t>Journeys.tsx. Real content ported (7 curated journeys, all real stops/teasers), rebuilt as a proper shadcn Accordion instead of hand-rolled expand state. Fixed 2 legacy bugs: stops pointing at / meant the old homepage — remapped to /the-letter since / is now the blog index; 3 "Crusade Files" stops pointed at the generic /blog placeholder instead of the specific post — corrected to real slugs. Also caught a real SEO issue: shadcn's AccordionContent doesn't render collapsed-panel children into the DOM at all by default — every internal link on this link-heavy page was invisible to crawlers until a user clicked to expand it. Fixed with forceMount (documented inline). Worth checking any other page that ends up using Accordion for real content, not just decoration. Verified live: 200 OK, all links (including the corrected ones) present in the raw server-rendered HTML, not just after hydration.</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
@@ -2624,7 +2624,7 @@
       <c r="A73" s="4" t="n"/>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>/about</t>
+          <t>/recent-creations</t>
         </is>
       </c>
       <c r="C73" s="13" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>About.tsx. Real content ported in full (3 narrative chapters, "The Receipts" stats, "What I'm Thinking Now", The Muse, Featured In, closing CTA). Built partner-quotes.tsx as a proper shared component (19 real client testimonials — Disney, Microsoft, eBay, Sony, etc.) since it's a cross-page resource, not a one-off; made it deterministic instead of the legacy Math.random() shuffle so quotes are actually in the SSR HTML. Reused the headshot + homepage hero images already rescued to Sanity. Correctly left this page's "Back to the Essays" link at / as-is (unlike other pages, this one genuinely means the blog/essays index). Verified live: 200 OK, both images, real quotes.</t>
+          <t>Portfolio.tsx. Real content ported (11 project cards, real accent colors — the one legitimate per-item inline-style exception, static Tailwind classes can't express 11 runtime hex values). Fixed a dead internal link (Homeaglow Exposed pointed at a route that doesn't exist anywhere; corrected to the real external homeaglowexposed.com already used consistently on other ported pages) and remapped / → /the-letter. Flagged but did NOT fix: "FusionRamp / STRATUM" points at /humanos, same as the unrelated Human OS card — looks like a copy-paste bug but there's no confirmed correct destination anywhere in the codebase, so ported as-is with a comment rather than guessed; worth a content-team check. Verified live: 200 OK, fixed links present.</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
@@ -2647,7 +2647,7 @@
       <c r="A74" s="4" t="n"/>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>/speaking</t>
+          <t>/intel</t>
         </is>
       </c>
       <c r="C74" s="13" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Speaking.tsx. Real content ported (4 speaking topics, 4 formats, rooms spoken at, CTA). Verified live: 200 OK.</t>
+          <t>Intel.tsx. Real content ported in full (9 portfolio companies, each with investment thesis, three gates, 7-dimension compass scores, full iRR framework, competitive landscape). Rebuilt as a shadcn Accordion with forceMount from the start (learned from /journeys), verified live that investment-thesis/competitor text is present in the raw SSR HTML, not just after a click. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
@@ -2670,7 +2670,7 @@
       <c r="A75" s="4" t="n"/>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>/ecosystem</t>
+          <t>/about</t>
         </is>
       </c>
       <c r="C75" s="13" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Ecosystem.tsx. Real content ported (What It Is, Who It's For, What Members Receive, invitation CTA). Verified live: 200 OK.</t>
+          <t>About.tsx. Real content ported in full (3 narrative chapters, "The Receipts" stats, "What I'm Thinking Now", The Muse, Featured In, closing CTA). Built partner-quotes.tsx as a proper shared component (19 real client testimonials — Disney, Microsoft, eBay, Sony, etc.) since it's a cross-page resource, not a one-off; made it deterministic instead of the legacy Math.random() shuffle so quotes are actually in the SSR HTML. Reused the headshot + homepage hero images already rescued to Sanity. Correctly left this page's "Back to the Essays" link at / as-is (unlike other pages, this one genuinely means the blog/essays index). Verified live: 200 OK, both images, real quotes.</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
@@ -2693,7 +2693,7 @@
       <c r="A76" s="4" t="n"/>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>/start-here</t>
+          <t>/speaking</t>
         </is>
       </c>
       <c r="C76" s="13" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>StartHere.tsx. Real content ported (5 curated essay cards, "After the Foundation" CTA). Found all 5 curated essays have no real hero image — a subset of the 99 in BLOG-IMAGE-BRIEFS.md, but higher priority since this is the site's own "read these first" page; renders a graceful tag-colored number panel instead of a broken image meanwhile. Verified live: 200 OK.</t>
+          <t>Speaking.tsx. Real content ported (4 speaking topics, 4 formats, rooms spoken at, CTA). Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
@@ -2716,7 +2716,7 @@
       <c r="A77" s="4" t="n"/>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>/published</t>
+          <t>/ecosystem</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Published.tsx. Real content ported in full (5 publication badges, 30 real bylines with real external URLs across 6 categories, speaking/podcast list). Caught two real Tailwind bugs before shipping: (1) building class names via hover:${c.border} / ${c.border}/20 template-literal concatenation doesn't work — Tailwind's scanner needs the complete literal string present in source, so those never would have generated any CSS; fixed by precomposing every exact variant as a full literal string. (2) mixing an all-sides border-[color] with a directional border-l-4 would have fought the base border-border on other sides — fixed using directional border-l-[color] utilities instead. Verified the fix by running a full production build and grepping the compiled CSS chunk directly for border-l-[#2563eb]/30 and hover:border-l-[#2563eb] — both present as real rules, not just present as strings in the HTML. Also ran pnpm build clean across all 16 pages shipped so far (154 static pages total) as a broader checkpoint.</t>
+          <t>Ecosystem.tsx. Real content ported (What It Is, Who It's For, What Members Receive, invitation CTA). Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
@@ -2739,7 +2739,7 @@
       <c r="A78" s="4" t="n"/>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>/clients</t>
+          <t>/start-here</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Clients.tsx. Real content ported in full (90 real client names with industry + Hawkins-score data, real filter/sort interactivity rebuilt in a small client component, Hawkins scale legend, CTA). Caught another real React bug before shipping: FilterButton was defined inside ClientsGrid's render body (react-hooks/static-components — recreates the component type every render, resetting its state); moved to module scope. Verified live: 200 OK, real client names present.</t>
+          <t>StartHere.tsx. Real content ported (5 curated essay cards, "After the Foundation" CTA). Found all 5 curated essays have no real hero image — a subset of the 99 in BLOG-IMAGE-BRIEFS.md, but higher priority since this is the site's own "read these first" page; renders a graceful tag-colored number panel instead of a broken image meanwhile. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
@@ -2762,7 +2762,7 @@
       <c r="A79" s="4" t="n"/>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>/series</t>
+          <t>/published</t>
         </is>
       </c>
       <c r="C79" s="13" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Series.tsx ("The Collections"). Real content ported in full (11 real curated essay series with real, already-migrated post slugs, 6 legacy category colors as precomposed literal Tailwind classes per the /published pattern — not fragment-assembled). Episode titles/hero images now fetched live from Sanity via a new postsBySlugsQuery instead of the legacy static blogData.json import, so they stay in sync as posts get real hero images added. Fixed a dead legacy link: /the-index (not a real route, not in nav) → /search (the label "Search All Essays" clearly describes this app's planned search page). Verified live: 200 OK, all 11 series titles present, 49 real post links, real Sanity hero images rendering where the linked post has one.</t>
+          <t>Published.tsx. Real content ported in full (5 publication badges, 30 real bylines with real external URLs across 6 categories, speaking/podcast list). Caught two real Tailwind bugs before shipping: (1) building class names via hover:${c.border} / ${c.border}/20 template-literal concatenation doesn't work — Tailwind's scanner needs the complete literal string present in source, so those never would have generated any CSS; fixed by precomposing every exact variant as a full literal string. (2) mixing an all-sides border-[color] with a directional border-l-4 would have fought the base border-border on other sides — fixed using directional border-l-[color] utilities instead. Verified the fix by running a full production build and grepping the compiled CSS chunk directly for border-l-[#2563eb]/30 and hover:border-l-[#2563eb] — both present as real rules, not just present as strings in the HTML. Also ran pnpm build clean across all 16 pages shipped so far (154 static pages total) as a broader checkpoint.</t>
         </is>
       </c>
       <c r="E79" s="14" t="inlineStr">
@@ -2785,7 +2785,7 @@
       <c r="A80" s="4" t="n"/>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>/framework</t>
+          <t>/clients</t>
         </is>
       </c>
       <c r="C80" s="13" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>LeadMagnet.tsx ("How I'd Approach Your Problem"). Real content ported in full (5-step framework, each with real description/prompt/real-world example). Rebuilt the per-step "see real-world example" toggle as shadcn Collapsible with forceMount (same crawlability rule as /journeys//intel — verified the example text is in the raw SSR HTML, not just after a click), installed via pnpm dlx shadcn add collapsible since it wasn't in the project yet. Intentionally not ported: the email-gated "download the worksheet" form — it posted to a tRPC subscribe mutation and didn't actually attach/send a real PDF even in the legacy source (just showed a success message), a backend feature with no real deliverable behind it, out of scope. Replaced with a direct CTA to /pick-up-the-phone. Verified live: 200 OK, all 5 steps + real-world examples present in SSR HTML, lint+typecheck clean.</t>
+          <t>Clients.tsx. Real content ported in full (90 real client names with industry + Hawkins-score data, real filter/sort interactivity rebuilt in a small client component, Hawkins scale legend, CTA). Caught another real React bug before shipping: FilterButton was defined inside ClientsGrid's render body (react-hooks/static-components — recreates the component type every render, resetting its state); moved to module scope. Verified live: 200 OK, real client names present.</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
@@ -2808,7 +2808,7 @@
       <c r="A81" s="4" t="n"/>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>/spirits</t>
+          <t>/series</t>
         </is>
       </c>
       <c r="C81" s="13" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Spirits.tsx ("The Liquid Library"). Real content ported in full (5 categories — Mezcal, Tequila, Sake, Coffee, Wine — each with philosophy, obsessions list, pullquote; Tequila's 5-item "Agave Matchmaker" newsletter digest; Sake's "coming soon" note). Caught two dead external links: the Mezcal and Tequila companion sites (SoulSmoke, LiquidSun) were hosted on *.manus.space — confirmed 503 along with the rest of Manus, not just the primary domain. Rendered as a non-linked "no longer live" card instead of a broken outbound link, keeping the real descriptive copy. Coffee's /brewsoul link kept as-is (real future internal route, Phase 6, not yet built). Verified live: 200 OK, all 5 categories + digest content present, dead external links correctly not rendered as &lt;a&gt; tags.</t>
+          <t>Series.tsx ("The Collections"). Real content ported in full (11 real curated essay series with real, already-migrated post slugs, 6 legacy category colors as precomposed literal Tailwind classes per the /published pattern — not fragment-assembled). Episode titles/hero images now fetched live from Sanity via a new postsBySlugsQuery instead of the legacy static blogData.json import, so they stay in sync as posts get real hero images added. Fixed a dead legacy link: /the-index (not a real route, not in nav) → /search (the label "Search All Essays" clearly describes this app's planned search page). Verified live: 200 OK, all 11 series titles present, 49 real post links, real Sanity hero images rendering where the linked post has one.</t>
         </is>
       </c>
       <c r="E81" s="14" t="inlineStr">
@@ -2831,7 +2831,7 @@
       <c r="A82" s="4" t="n"/>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>/community (+ /find-my-tribe → 308 redirect, next.config.ts)</t>
+          <t>/framework</t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Community.tsx. Legacy is almost entirely a functional community/CRM platform (auth-gated profile editing, CSV contact upload, email invites, member directory) backed by tRPC + a custom auth system — a backend feature, not a content page, out of this migration's scope. Ported the only real editorial content (hero copy, closing manifesto quote/link) and replaced the auth-gated CRUD tabs with an honest "still being built" note + a real CTA to /pick-up-the-phone, rather than reproducing a non-functional sign-in gate. Verified live: 200 OK, redirect confirmed 308.</t>
+          <t>LeadMagnet.tsx ("How I'd Approach Your Problem"). Real content ported in full (5-step framework, each with real description/prompt/real-world example). Rebuilt the per-step "see real-world example" toggle as shadcn Collapsible with forceMount (same crawlability rule as /journeys//intel — verified the example text is in the raw SSR HTML, not just after a click), installed via pnpm dlx shadcn add collapsible since it wasn't in the project yet. Intentionally not ported: the email-gated "download the worksheet" form — it posted to a tRPC subscribe mutation and didn't actually attach/send a real PDF even in the legacy source (just showed a success message), a backend feature with no real deliverable behind it, out of scope. Replaced with a direct CTA to /pick-up-the-phone. Verified live: 200 OK, all 5 steps + real-world examples present in SSR HTML, lint+typecheck clean.</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
@@ -2854,7 +2854,7 @@
       <c r="A83" s="4" t="n"/>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>/engage</t>
+          <t>/spirits</t>
         </is>
       </c>
       <c r="C83" s="13" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Engage.tsx ("The Gate"). The qualification quiz itself (5 real questions, the exact scoring heuristic, all 3 result screens — qualified/not-ready/wrong-fit, the real Calendly link, the 2× guarantee copy) is genuinely client-side logic already in legacy (scored by a pure regex/word-count function, no server round-trip needed to decide the outcome) — ported in full as real assessment logic per the CMS-boundary rule. Not ported: the tRPC engage.submit mutation that logged each submission for Tony's own records — a lead-tracking write, out of scope; dropping it doesn't change the visitor's experience, the gate still scores and unlocks the real Calendly link correctly. Verified live: 200 OK, full quiz flow present, lint+typecheck clean.</t>
+          <t>Spirits.tsx ("The Liquid Library"). Real content ported in full (5 categories — Mezcal, Tequila, Sake, Coffee, Wine — each with philosophy, obsessions list, pullquote; Tequila's 5-item "Agave Matchmaker" newsletter digest; Sake's "coming soon" note). Caught two dead external links: the Mezcal and Tequila companion sites (SoulSmoke, LiquidSun) were hosted on *.manus.space — confirmed 503 along with the rest of Manus, not just the primary domain. Rendered as a non-linked "no longer live" card instead of a broken outbound link, keeping the real descriptive copy. Coffee's /brewsoul link kept as-is (real future internal route, Phase 6, not yet built). Verified live: 200 OK, all 5 categories + digest content present, dead external links correctly not rendered as &lt;a&gt; tags.</t>
         </is>
       </c>
       <c r="E83" s="14" t="inlineStr">
@@ -2877,7 +2877,7 @@
       <c r="A84" s="4" t="n"/>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>/amplifier</t>
+          <t>/community (+ /find-my-tribe → 308 redirect, next.config.ts)</t>
         </is>
       </c>
       <c r="C84" s="13" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Amplifier.tsx. Real content ported in full and unreduced (Matt Mochary note, 5 pillars, unfair advantage, 2× guarantee, 4 real pricing tiers, prep-doc requirements, "what Tony will not do" list). No backend dependency at all — every CTA is either an internal /engage link or a real mailto:. Verified live: 200 OK, all sections + both CTA link types present.</t>
+          <t>Community.tsx. Legacy is almost entirely a functional community/CRM platform (auth-gated profile editing, CSV contact upload, email invites, member directory) backed by tRPC + a custom auth system — a backend feature, not a content page, out of this migration's scope. Ported the only real editorial content (hero copy, closing manifesto quote/link) and replaced the auth-gated CRUD tabs with an honest "still being built" note + a real CTA to /pick-up-the-phone, rather than reproducing a non-functional sign-in gate. Verified live: 200 OK, redirect confirmed 308.</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
@@ -2900,7 +2900,7 @@
       <c r="A85" s="4" t="n"/>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>/diamond-cut</t>
+          <t>/engage</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>DiamondCut.tsx. Real content ported in full (Honest Note re: Matt Mochary, 5 cuts, 2× guarantee, 4 real pricing tiers). Legacy's 3 non-"Setting" tiers used a live StripeCheckoutButton — checkout/billing is deferred per this migration's scope, so those now route to /engage instead (pricing/copy unchanged, matching how /amplifier's tiers already work), rather than wiring up a real payment flow this pass. Verified live: 200 OK, all sections + tiers present.</t>
+          <t>Engage.tsx ("The Gate"). The qualification quiz itself (5 real questions, the exact scoring heuristic, all 3 result screens — qualified/not-ready/wrong-fit, the real Calendly link, the 2× guarantee copy) is genuinely client-side logic already in legacy (scored by a pure regex/word-count function, no server round-trip needed to decide the outcome) — ported in full as real assessment logic per the CMS-boundary rule. Not ported: the tRPC engage.submit mutation that logged each submission for Tony's own records — a lead-tracking write, out of scope; dropping it doesn't change the visitor's experience, the gate still scores and unlocks the real Calendly link correctly. Verified live: 200 OK, full quiz flow present, lint+typecheck clean.</t>
         </is>
       </c>
       <c r="E85" s="14" t="inlineStr">
@@ -2923,7 +2923,7 @@
       <c r="A86" s="4" t="n"/>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>/essays</t>
+          <t>/amplifier</t>
         </is>
       </c>
       <c r="C86" s="13" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Essays.tsx. A second, distinct essay index from the homepage's archive — filters by "archetype" (Builder/Crusader/Investor, ported from client/src/data/archetypes.ts as src/lib/content/archetypes.ts) instead of Core Themes, compact list layout instead of a card grid. Not linked from current nav (legacy didn't link it from nav either — it's a real destination referenced by other not-yet-built pages like SkippyMap/CheshireGrin). Posts now fetched live from Sanity instead of the static blogData.json import. Verified live: 200 OK, archetype/category filters + real post list present.</t>
+          <t>Amplifier.tsx. Real content ported in full and unreduced (Matt Mochary note, 5 pillars, unfair advantage, 2× guarantee, 4 real pricing tiers, prep-doc requirements, "what Tony will not do" list). No backend dependency at all — every CTA is either an internal /engage link or a real mailto:. Verified live: 200 OK, all sections + both CTA link types present.</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
@@ -2946,7 +2946,7 @@
       <c r="A87" s="4" t="n"/>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>/invest</t>
+          <t>/diamond-cut</t>
         </is>
       </c>
       <c r="C87" s="13" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Invest.tsx ("Invest in the Thesis"). Real content ported in full — 6 portfolio categories, 32 real named companies with role/note, "and many more" teaser → /engage, ABIT waitlist section. The waitlist is a real outbound link to impactsoul.is (confirmed live, a separate real site) — no backend/email-capture on this page at all. Verified live: 200 OK, all 6 categories + companies + outbound link present.</t>
+          <t>DiamondCut.tsx. Real content ported in full (Honest Note re: Matt Mochary, 5 cuts, 2× guarantee, 4 real pricing tiers). Legacy's 3 non-"Setting" tiers used a live StripeCheckoutButton — checkout/billing is deferred per this migration's scope, so those now route to /engage instead (pricing/copy unchanged, matching how /amplifier's tiers already work), rather than wiring up a real payment flow this pass. Verified live: 200 OK, all sections + tiers present.</t>
         </is>
       </c>
       <c r="E87" s="14" t="inlineStr">
@@ -2969,7 +2969,7 @@
       <c r="A88" s="4" t="n"/>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>/akbar</t>
+          <t>/essays</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>AkbarEssay.tsx ("Los Angeles Is Losing Its Memory"). Real essay prose ported in full, unchanged (every section, every pull quote, all 6 wine pairings, the 3 reframe terms). Legacy was a ~20-image photo essay entirely on the now-fully-dead Manus /api/img/ host — none recoverable, confirmed 404/503. Rather than fabricate placeholder imagery for a piece about specific real photographs, ported as a clean long-form article and tracked the loss explicitly (see Phase 13) instead of pretending it's not there. Kept the deliberately dark, fixed palette (this is a one-off bespoke essay design, not site chrome, so a permanent dark mood is the real intent) but reused the site's existing loaded fonts instead of the 3 extra webfonts legacy imported for just this page. Verified live: 200 OK, full essay text present.</t>
+          <t>Essays.tsx. A second, distinct essay index from the homepage's archive — filters by "archetype" (Builder/Crusader/Investor, ported from client/src/data/archetypes.ts as src/lib/content/archetypes.ts) instead of Core Themes, compact list layout instead of a card grid. Not linked from current nav (legacy didn't link it from nav either — it's a real destination referenced by other not-yet-built pages like SkippyMap/CheshireGrin). Posts now fetched live from Sanity instead of the static blogData.json import. Verified live: 200 OK, archetype/category filters + real post list present.</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
@@ -2992,7 +2992,7 @@
       <c r="A89" s="4" t="n"/>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>/living-declaration (+ /manifesto → 308 redirect, next.config.ts)</t>
+          <t>/invest</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Manifesto.tsx ("A Living Declaration — The Measurement of Becoming"). Real essay prose ported in full: the premise, "Boiling the Human" retrospective, 4 real pull quotes (Tristan Harris, Toffler, Harari, Eisenstein), the original 6 numbered practices + exceptions + specific steps, Phase 2/Balaji Srinivasan section, The Puzzle Pieces (acknowledgments), the 6 Roman-numeral principles, and the closing CTAs. Legacy's hero photo, "hand breakthrough" image, and Clarisse Abelarde's artwork photo are all on the now-fully-dead Manus host — dropped (real text credit to her kept), not fabricated. The "Ecosystem Map" 6-card grid originally linked to 6 other Manus-hosted micro-sites (Gem Spark, Regenerative Protocol, SoulSmoke, LiquidSun, Sacred Waters, Intimacy Assessment) plus a "Vancefolio" site — confirmed all 503; those link chips dropped, keeping only chips to pages actually live in this app (or genuinely planned, like /humanos//flow-circuit, already referenced elsewhere in this migration). The interactive questionnaire (trpc.manifesto.submit — unlike /engage's audit, this one has no logic that works without a backend) replaced with a direct, real mailto: invitation instead of a form that would go nowhere. Corrected /assessment → /assessments (the real legacy route name, confirmed in App.tsx; the singular looks like a typo in the original). Verified live: 200 OK, all sections + quotes present, redirect confirmed 308.</t>
+          <t>Invest.tsx ("Invest in the Thesis"). Real content ported in full — 6 portfolio categories, 32 real named companies with role/note, "and many more" teaser → /engage, ABIT waitlist section. The waitlist is a real outbound link to impactsoul.is (confirmed live, a separate real site) — no backend/email-capture on this page at all. Verified live: 200 OK, all 6 categories + companies + outbound link present.</t>
         </is>
       </c>
       <c r="E89" s="14" t="inlineStr">
@@ -3015,7 +3015,7 @@
       <c r="A90" s="4" t="n"/>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>/protecting-your-business</t>
+          <t>/akbar</t>
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>ProtectingYourBusiness.tsx. Real documented fraud case file (Kristi Klawiter) ported in full — every factual claim, citation, the fact/opinion separation (AlertBox/OpinionBox), all quoted correspondence, the 13-section structure, and the full Legal Notice preserved verbatim; already-published, court-record-cited content, not new allegations authored here. Not ported: the "Submit Your Story" form (trpc.cheshire.submit — a lead-intake backend feature with no client-side logic of its own) replaced with a real mailto:; the closing SEO keyword-stuffing footer (bare repeated-name list, no informational content) dropped as an actual SEO improvement — modern search engines penalize that pattern, and the same keywords already live correctly in page metadata. Simplified the floating hamburger/TOC overlay to a plain inline jump-to-section list. Verified live: 200 OK, all sections + full legal notice present.</t>
+          <t>AkbarEssay.tsx ("Los Angeles Is Losing Its Memory"). Real essay prose ported in full, unchanged (every section, every pull quote, all 6 wine pairings, the 3 reframe terms). Legacy was a ~20-image photo essay entirely on the now-fully-dead Manus /api/img/ host — none recoverable, confirmed 404/503. Rather than fabricate placeholder imagery for a piece about specific real photographs, ported as a clean long-form article and tracked the loss explicitly (see Phase 13) instead of pretending it's not there. Kept the deliberately dark, fixed palette (this is a one-off bespoke essay design, not site chrome, so a permanent dark mood is the real intent) but reused the site's existing loaded fonts instead of the 3 extra webfonts legacy imported for just this page. Verified live: 200 OK, full essay text present.</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
@@ -3038,7 +3038,7 @@
       <c r="A91" s="4" t="n"/>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>/alex-azzi (+ /cheshire-grin, 308-redirected to it)</t>
+          <t>/living-declaration (+ /manifesto → 308 redirect, next.config.ts)</t>
         </is>
       </c>
       <c r="C91" s="13" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>ported from legacy CheshireGrin.tsx (2608 lines), the VerifiedTribe Community Protection Report on Alex Azzi (CEO, XRWorkout). Site owner explicitly confirmed porting this, same content class as /protecting-your-business and following its established conventions (Tailwind instead of legacy's inline-style system, plain jump-to-section TOC, real generateMetadata + Article/FAQPage JSON-LD). Legacy registered the identical component at both /alex-azzi and /cheshire-grin with no redirect between them; picked /alex-azzi as canonical (the name people search for) and 308-redirected the other, matching the /find-my-tribe-style duplicate-route pattern already used throughout next.config.ts. Every dollar figure, date, case number, and quoted admission ported verbatim into lib/content/alex-azzi.ts — independently spot-checked against the legacy source (not just the port's own self-report) and confirmed exact matches on $137,000+/$75,000+/$15,000/CPR-2026-001/etc. Dropped 3 backend-dependent legacy features with no live tRPC to power them, matching /protecting-your-business's own precedent: the Submission Form (replaced with a real mailto: CTA), the Byron Katie Verification Gate modal (only existed to gate the removed form), and the Endorsement/"Ring the Bell" counter — its "7 testimonials received" claim was dropped rather than ported as fact, since it can't be verified without the backend that produced it. Real dead-link bug fixed: 2 of 20 "Ecosystem Interlinks" pointed to /assessment?t</t>
+          <t>Manifesto.tsx ("A Living Declaration — The Measurement of Becoming"). Real essay prose ported in full: the premise, "Boiling the Human" retrospective, 4 real pull quotes (Tristan Harris, Toffler, Harari, Eisenstein), the original 6 numbered practices + exceptions + specific steps, Phase 2/Balaji Srinivasan section, The Puzzle Pieces (acknowledgments), the 6 Roman-numeral principles, and the closing CTAs. Legacy's hero photo, "hand breakthrough" image, and Clarisse Abelarde's artwork photo are all on the now-fully-dead Manus host — dropped (real text credit to her kept), not fabricated. The "Ecosystem Map" 6-card grid originally linked to 6 other Manus-hosted micro-sites (Gem Spark, Regenerative Protocol, SoulSmoke, LiquidSun, Sacred Waters, Intimacy Assessment) plus a "Vancefolio" site — confirmed all 503; those link chips dropped, keeping only chips to pages actually live in this app (or genuinely planned, like /humanos//flow-circuit, already referenced elsewhere in this migration). The interactive questionnaire (trpc.manifesto.submit — unlike /engage's audit, this one has no logic that works without a backend) replaced with a direct, real mailto: invitation instead of a form that would go nowhere. Corrected /assessment → /assessments (the real legacy route name, confirmed in App.tsx; the singular looks like a typo in the original). Verified live: 200 OK, all sections + quotes present, redirect confirmed 308.</t>
         </is>
       </c>
       <c r="E91" s="14" t="inlineStr">
@@ -3061,7 +3061,7 @@
       <c r="A92" s="4" t="n"/>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Real bug found and fixed</t>
+          <t>/protecting-your-business</t>
         </is>
       </c>
       <c r="C92" s="13" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>(while verifying the above): a Core Themes selection (e.g. "The Crusades") often shares its display name with a real post category — showing it as a separate floating chip next to the category pill row (rather than merging into the matching pill) read as two disconnected, contradictory controls. Fixed HomeArchive so an active theme lights up the matching category pill directly (with the same click-to-clear ✕ affordance) instead of a separate chip; a theme with no same-named category still falls back to its own chip.</t>
+          <t>ProtectingYourBusiness.tsx. Real documented fraud case file (Kristi Klawiter) ported in full — every factual claim, citation, the fact/opinion separation (AlertBox/OpinionBox), all quoted correspondence, the 13-section structure, and the full Legal Notice preserved verbatim; already-published, court-record-cited content, not new allegations authored here. Not ported: the "Submit Your Story" form (trpc.cheshire.submit — a lead-intake backend feature with no client-side logic of its own) replaced with a real mailto:; the closing SEO keyword-stuffing footer (bare repeated-name list, no informational content) dropped as an actual SEO improvement — modern search engines penalize that pattern, and the same keywords already live correctly in page metadata. Simplified the floating hamburger/TOC overlay to a plain inline jump-to-section list. Verified live: 200 OK, all sections + full legal notice present.</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
@@ -3084,7 +3084,7 @@
       <c r="A93" s="4" t="n"/>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>/rip-peptide-sciences</t>
+          <t>/alex-azzi (+ /cheshire-grin, 308-redirected to it)</t>
         </is>
       </c>
       <c r="C93" s="13" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>RipPeptideSciences.tsx. Real content ported in full (7-event timeline, 3 shutdown-reason cards, COA explainer, 9-vendor sortable scorecard, Tony's quote). Built components/marketing/biochain-cta.tsx — a shared CTA used across every peptide/bio-sourcing page, real static outbound links to RampRate's own BioChain site (confirmed live), no backend on this side. Installed formik+yup this pass for upcoming multi-field forms (peptide quiz, etc.) — documented as the house convention in CONTRIBUTING.md. Verified live: 200 OK, timeline/reasons/vendors/quote all present.</t>
+          <t>ported from legacy CheshireGrin.tsx (2608 lines), the VerifiedTribe Community Protection Report on Alex Azzi (CEO, XRWorkout). Site owner explicitly confirmed porting this, same content class as /protecting-your-business and following its established conventions (Tailwind instead of legacy's inline-style system, plain jump-to-section TOC, real generateMetadata + Article/FAQPage JSON-LD). Legacy registered the identical component at both /alex-azzi and /cheshire-grin with no redirect between them; picked /alex-azzi as canonical (the name people search for) and 308-redirected the other, matching the /find-my-tribe-style duplicate-route pattern already used throughout next.config.ts. Every dollar figure, date, case number, and quoted admission ported verbatim into lib/content/alex-azzi.ts — independently spot-checked against the legacy source (not just the port's own self-report) and confirmed exact matches on $137,000+/$75,000+/$15,000/CPR-2026-001/etc. Dropped 3 backend-dependent legacy features with no live tRPC to power them, matching /protecting-your-business's own precedent: the Submission Form (replaced with a real mailto: CTA), the Byron Katie Verification Gate modal (only existed to gate the removed form), and the Endorsement/"Ring the Bell" counter — its "7 testimonials received" claim was dropped rather than ported as fact, since it can't be verified without the backend that produced it. Real dead-link bug fixed: 2 of 20 "Ecosystem Interlinks" pointed to /assessment?t</t>
         </is>
       </c>
       <c r="E93" s="14" t="inlineStr">
@@ -3107,7 +3107,7 @@
       <c r="A94" s="4" t="n"/>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>/whats-legal</t>
+          <t>Real bug found and fixed</t>
         </is>
       </c>
       <c r="C94" s="13" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>WhatsLegal.tsx. Real content ported in full — 17 real compounds with real US/UK/Australia regulatory status, searchable/risk-filterable table, the 3 "key distinctions" callouts. No backend dependency. Verified live: 200 OK, full table + all real compounds present.</t>
+          <t>(while verifying the above): a Core Themes selection (e.g. "The Crusades") often shares its display name with a real post category — showing it as a separate floating chip next to the category pill row (rather than merging into the matching pill) read as two disconnected, contradictory controls. Fixed HomeArchive so an active theme lights up the matching category pill directly (with the same click-to-clear ✕ affordance) instead of a separate chip; a theme with no same-named category still falls back to its own chip.</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
@@ -3130,7 +3130,7 @@
       <c r="A95" s="4" t="n"/>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>/verify-your-coa</t>
+          <t>/rip-peptide-sciences</t>
         </is>
       </c>
       <c r="C95" s="13" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>VerifyYourCoa.tsx. Real content ported in full (interactive 7-point checklist with live score, 4-step Janoshik verification walkthrough). Extracted components/marketing/peptide-shutdown-banner.tsx (shared FDA-shutdown banner, was duplicated inline on /whats-legal, now both use the one component) and components/marketing/coa-checklist.tsx. Also caught and fixed 3 duplicated EyebrowLabel component definitions (identical code in /amplifier, /diamond-cut, /living-declaration) — extracted to components/marketing/eyebrow-label.tsx. Verified live: 200 OK, full checklist + walkthrough present.</t>
+          <t>RipPeptideSciences.tsx. Real content ported in full (7-event timeline, 3 shutdown-reason cards, COA explainer, 9-vendor sortable scorecard, Tony's quote). Built components/marketing/biochain-cta.tsx — a shared CTA used across every peptide/bio-sourcing page, real static outbound links to RampRate's own BioChain site (confirmed live), no backend on this side. Installed formik+yup this pass for upcoming multi-field forms (peptide quiz, etc.) — documented as the house convention in CONTRIBUTING.md. Verified live: 200 OK, timeline/reasons/vendors/quote all present.</t>
         </is>
       </c>
       <c r="E95" s="14" t="inlineStr">
@@ -3153,7 +3153,7 @@
       <c r="A96" s="4" t="n"/>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>/price-tracker</t>
+          <t>/whats-legal</t>
         </is>
       </c>
       <c r="C96" s="13" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>PriceTracker.tsx. Real content ported in full — 14 real compounds with research-vendor vs. telehealth price ranges, Tony's takes, sortable table, and the interactive up-to-4 stack cost calculator. Reused PeptideShutdownBanner. Verified live: 200 OK, full price table + calculator present.</t>
+          <t>WhatsLegal.tsx. Real content ported in full — 17 real compounds with real US/UK/Australia regulatory status, searchable/risk-filterable table, the 3 "key distinctions" callouts. No backend dependency. Verified live: 200 OK, full table + all real compounds present.</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
@@ -3176,7 +3176,7 @@
       <c r="A97" s="4" t="n"/>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>/test-your-peptides</t>
+          <t>/verify-your-coa</t>
         </is>
       </c>
       <c r="C97" s="13" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>TestYourPeptides.tsx. Real content ported in full — 4 real independent-verification options (Janoshik, r/Peptides, Eroids, telehealth route) with real sites, costs, and Tony's notes. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, all 4 options present. Also renamed /blog's heading from "The Blog" to "Essays" per feedback (matches /essays and the site's own voice).</t>
+          <t>VerifyYourCoa.tsx. Real content ported in full (interactive 7-point checklist with live score, 4-step Janoshik verification walkthrough). Extracted components/marketing/peptide-shutdown-banner.tsx (shared FDA-shutdown banner, was duplicated inline on /whats-legal, now both use the one component) and components/marketing/coa-checklist.tsx. Also caught and fixed 3 duplicated EyebrowLabel component definitions (identical code in /amplifier, /diamond-cut, /living-declaration) — extracted to components/marketing/eyebrow-label.tsx. Verified live: 200 OK, full checklist + walkthrough present.</t>
         </is>
       </c>
       <c r="E97" s="14" t="inlineStr">
@@ -3199,7 +3199,7 @@
       <c r="A98" s="4" t="n"/>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>/peptide-library</t>
+          <t>/price-tracker</t>
         </is>
       </c>
       <c r="C98" s="13" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>PeptideLibrary.tsx. Real content ported in full — 20 real compound profiles across 8 categories, each with mechanism, safety tier, evidence score, regulatory status, pricing, stack partners, Oura tracking, key study, and Tony's take; expandable cards with category filter. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, all 20 compounds present.</t>
+          <t>PriceTracker.tsx. Real content ported in full — 14 real compounds with research-vendor vs. telehealth price ranges, Tony's takes, sortable table, and the interactive up-to-4 stack cost calculator. Reused PeptideShutdownBanner. Verified live: 200 OK, full price table + calculator present.</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
@@ -3222,7 +3222,7 @@
       <c r="A99" s="4" t="n"/>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>/peptide-hall-of-shame</t>
+          <t>/test-your-peptides</t>
         </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>PeptideHallOfShame.tsx. Real content ported in full — 20 real named clinics/providers audited on 6 weighted clinical criteria, sortable rankings with expandable weaknesses/strengths, comparison callout for the site's own assessment, methodology note. Reused PeptideShutdownBanner + BioChainCTA; built ClinicRankings (components/marketing/clinic-rankings.tsx). Real bug caught and fixed: CRITERIA was defined and exported from clinic-rankings.tsx (a "use client" file) and imported directly into the Server Component page.tsx, which crashed at runtime (CRITERIA.map is not a function) — a plain data re-export doesn't survive the Client→Server boundary. Fixed by moving CRITERIA to a new shared plain module, lib/content/peptide-criteria.ts, imported by both. Verified live: 200 OK, no error digest, all 20 clinic names and both methodology-card criteria present in rendered HTML.</t>
+          <t>TestYourPeptides.tsx. Real content ported in full — 4 real independent-verification options (Janoshik, r/Peptides, Eroids, telehealth route) with real sites, costs, and Tony's notes. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, all 4 options present. Also renamed /blog's heading from "The Blog" to "Essays" per feedback (matches /essays and the site's own voice).</t>
         </is>
       </c>
       <c r="E99" s="14" t="inlineStr">
@@ -3245,7 +3245,7 @@
       <c r="A100" s="4" t="n"/>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>/peptide-supply-chain</t>
+          <t>/peptide-library</t>
         </is>
       </c>
       <c r="C100" s="13" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>PeptideSupplyChain.tsx. Real content ported in full — 12 real named providers audited on a 7-category cost breakdown (manufacturing/marketing/compliance/physician/R&amp;D/shipping/profit) with a derived credibility score, sortable rankings, expandable per-provider dollar breakdown + red-flag tags, green/red-flag guidance, methodology note. Built SupplyChainRankings (components/marketing/supply-chain-rankings.tsx) + shared lib/content/supply-chain-providers.ts (kept data out of the client file per the same Client→Server export pitfall fixed on /peptide-hall-of-shame). Dropped the legacy EmailGate (trpc.subscribe.add backend mutation) — full analysis now renders directly with no gate, matching /peptide-library and /price-tracker. Legacy hero background image (CloudFront) confirmed 403, same host/failure as /peptide-hall-of-shame — dropped for a CSS gradient. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, all 12 providers present.</t>
+          <t>PeptideLibrary.tsx. Real content ported in full — 20 real compound profiles across 8 categories, each with mechanism, safety tier, evidence score, regulatory status, pricing, stack partners, Oura tracking, key study, and Tony's take; expandable cards with category filter. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, all 20 compounds present.</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
@@ -3268,7 +3268,7 @@
       <c r="A101" s="4" t="n"/>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>/peptide-matrix</t>
+          <t>/peptide-hall-of-shame</t>
         </is>
       </c>
       <c r="C101" s="13" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>PeptideMatrix.tsx. Real content ported in full — interactive canvas scatter plot (review score vs. scientific evidence score) mapping 8 real named entities (influencers, clinics, a vendor, doctors, USADA as regulatory) across 4 quadrants, sortable/clickable entity table with selected-entity detail, 5 danger-zone psychology mechanisms, evidence-scoring methodology (crawlable via forceMount), full fair-comment/appeals legal framework. Built PeptideMatrixExplorer (canvas + table, client) and PeptideMatrixMethodology (client) + shared lib/content/peptide-matrix.ts (plain data module, not re-exported from either client file — same pattern as the /peptide-hall-of-shame CRITERIA fix). Converted every legacy emoji (🧠🔄⏰📊💰🧬🏚️📝🛡️📰✓✕▶) to lucide icons. Legacy hero background image (CloudFront) confirmed 403, same as the other peptide pages — dropped for a CSS gradient. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, all entities, quadrants, and legal-framework text present.</t>
+          <t>PeptideHallOfShame.tsx. Real content ported in full — 20 real named clinics/providers audited on 6 weighted clinical criteria, sortable rankings with expandable weaknesses/strengths, comparison callout for the site's own assessment, methodology note. Reused PeptideShutdownBanner + BioChainCTA; built ClinicRankings (components/marketing/clinic-rankings.tsx). Real bug caught and fixed: CRITERIA was defined and exported from clinic-rankings.tsx (a "use client" file) and imported directly into the Server Component page.tsx, which crashed at runtime (CRITERIA.map is not a function) — a plain data re-export doesn't survive the Client→Server boundary. Fixed by moving CRITERIA to a new shared plain module, lib/content/peptide-criteria.ts, imported by both. Verified live: 200 OK, no error digest, all 20 clinic names and both methodology-card criteria present in rendered HTML.</t>
         </is>
       </c>
       <c r="E101" s="14" t="inlineStr">
@@ -3291,7 +3291,7 @@
       <c r="A102" s="4" t="n"/>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>/peptide-watch</t>
+          <t>/peptide-supply-chain</t>
         </is>
       </c>
       <c r="C102" s="13" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>PeptideWatch.tsx. Real content ported in full across all 10 legacy sections — 3 market tiers, a 2024–26 enforcement timeline, an 18-entry wall-of-shame table with real FDA/DOJ/FTC/ITC/state/NAD citations, 12 recurring fraud patterns, 5 role-based checklists, a 10-question buyer test, a 10-category/50-point vendor scorecard, a Finnrick Analytics section, the proposed PeptideWatch Foundation, whistleblower reporting channels, and the closing "chain of custody" argument. Built PeptideWatchFraudPatterns, PeptideWatchRoleChecklist, PeptideWatchScorecard (all client) + shared lib/content/peptide-watch.ts (plain data module, same Client/Server-safe pattern as the other peptide pages). Fixed two real legacy crawlability gaps: fraud-pattern bodies and all 5 role checklists were conditionally unmounted (never in the DOM until clicked) — now always server-rendered and toggled via hidden instead, verified present in raw HTML. Dropped the legacy page's own duplicate &lt;footer&gt; (site already renders one global SiteFooter). Legacy per-section hero images (CloudFront) confirmed 403, same dead host as every other peptide page. Reused BioChainCTA. Verified live: 200 OK, all content present including collapsed sections.</t>
+          <t>PeptideSupplyChain.tsx. Real content ported in full — 12 real named providers audited on a 7-category cost breakdown (manufacturing/marketing/compliance/physician/R&amp;D/shipping/profit) with a derived credibility score, sortable rankings, expandable per-provider dollar breakdown + red-flag tags, green/red-flag guidance, methodology note. Built SupplyChainRankings (components/marketing/supply-chain-rankings.tsx) + shared lib/content/supply-chain-providers.ts (kept data out of the client file per the same Client→Server export pitfall fixed on /peptide-hall-of-shame). Dropped the legacy EmailGate (trpc.subscribe.add backend mutation) — full analysis now renders directly with no gate, matching /peptide-library and /price-tracker. Legacy hero background image (CloudFront) confirmed 403, same host/failure as /peptide-hall-of-shame — dropped for a CSS gradient. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, all 12 providers present.</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
@@ -3314,7 +3314,7 @@
       <c r="A103" s="4" t="n"/>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>/quiz_25q</t>
+          <t>/peptide-matrix</t>
         </is>
       </c>
       <c r="C103" s="13" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>PeptideQuiz25.tsx. Real content ported in full — all 25 questions across 5 scoring dimensions (Science Literacy, Red Flag Detection, Provider Evaluation, Regulatory Awareness, Personal Risk Assessment), all 4 answer choices with real feedback text per question, all 5 result profiles with real recommendations. Built PeptideQuiz (client component, components/marketing/peptide-quiz.tsx) matching the existing single-file precedent set by engage-audit.tsx. The email-gate phase's "GET MY REPORT" never posted anywhere even in the legacy source (no backend call in its handler) — kept as real client-only gating. AssessmentResultActions's "Send to Tony"/"Keep Private" (a tRPC CRM write) was dropped; "Download PDF" (window.print) kept since it's real and backend-free. Legacy hero image (CloudFront) confirmed 403. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, intro copy/dimensions present, typecheck/lint/production-build clean.</t>
+          <t>PeptideMatrix.tsx. Real content ported in full — interactive canvas scatter plot (review score vs. scientific evidence score) mapping 8 real named entities (influencers, clinics, a vendor, doctors, USADA as regulatory) across 4 quadrants, sortable/clickable entity table with selected-entity detail, 5 danger-zone psychology mechanisms, evidence-scoring methodology (crawlable via forceMount), full fair-comment/appeals legal framework. Built PeptideMatrixExplorer (canvas + table, client) and PeptideMatrixMethodology (client) + shared lib/content/peptide-matrix.ts (plain data module, not re-exported from either client file — same pattern as the /peptide-hall-of-shame CRITERIA fix). Converted every legacy emoji (🧠🔄⏰📊💰🧬🏚️📝🛡️📰✓✕▶) to lucide icons. Legacy hero background image (CloudFront) confirmed 403, same as the other peptide pages — dropped for a CSS gradient. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, all entities, quadrants, and legal-framework text present.</t>
         </is>
       </c>
       <c r="E103" s="14" t="inlineStr">
@@ -3337,7 +3337,7 @@
       <c r="A104" s="4" t="n"/>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>/clock-keeper-part-2</t>
+          <t>/peptide-watch</t>
         </is>
       </c>
       <c r="C104" s="13" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>ClockKeeperPartII.tsx. Built 2026-10-06: hero, intro, 5 modes, the 5 questions, optional name/email; saves to Supabase clock_keeper_responses (anonymous allowed; server-validated), response count in the hero. Fixes the dead link from the Part I essay. Saving works once the database script is run. Was: Deferred, not skipped. A companion response-collection form for the /blog/the-clock-keeper-chronicles-part-1 essay — 5 questions + alternate "modes" (reframe/meta/jazz/minimum), posts to trpc.clockKeeper.submit, displays a live trpc.clockKeeper.count response counter. Unlike /post-intervention, this doesn't promise anonymity, so a mailto: fallback (matching newsletter-popup.tsx's pattern) could work for the submit action — but the live response counter has no honest fallback without a real backend. Lower priority than the rest of Phase 4 (a companion piece to one specific post, not a core marketing page); revisit with a mailto-based submit and the counter dropped.</t>
+          <t>PeptideWatch.tsx. Real content ported in full across all 10 legacy sections — 3 market tiers, a 2024–26 enforcement timeline, an 18-entry wall-of-shame table with real FDA/DOJ/FTC/ITC/state/NAD citations, 12 recurring fraud patterns, 5 role-based checklists, a 10-question buyer test, a 10-category/50-point vendor scorecard, a Finnrick Analytics section, the proposed PeptideWatch Foundation, whistleblower reporting channels, and the closing "chain of custody" argument. Built PeptideWatchFraudPatterns, PeptideWatchRoleChecklist, PeptideWatchScorecard (all client) + shared lib/content/peptide-watch.ts (plain data module, same Client/Server-safe pattern as the other peptide pages). Fixed two real legacy crawlability gaps: fraud-pattern bodies and all 5 role checklists were conditionally unmounted (never in the DOM until clicked) — now always server-rendered and toggled via hidden instead, verified present in raw HTML. Dropped the legacy page's own duplicate &lt;footer&gt; (site already renders one global SiteFooter). Legacy per-section hero images (CloudFront) confirmed 403, same dead host as every other peptide page. Reused BioChainCTA. Verified live: 200 OK, all content present including collapsed sections.</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
@@ -3360,7 +3360,7 @@
       <c r="A105" s="4" t="n"/>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>/charity-scorecard + /charity-scorecard/:slug</t>
+          <t>/quiz_25q</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>CharityScorecard.tsx, CharityProfile.tsx (uses charityData.ts). Real content ported in full — 98 real named charities scored across 7 weighted dimensions unifying GiveWell/Charity Navigator/CharityWatch/Candid ratings plus a proprietary Cloak-vs-Clear transparency score; 3-tab explorer (Rankings with search/filter/sort/expand, Scorecard, Evaluators) and a full per-charity profile page with an SVG radar chart, score breakdown, quick facts, external ratings, and similar-charity cross-links. No backend dependency in the legacy source at all. Built CharityScorecardExplorer (client) + shared components/marketing/charity-badges.tsx (GradeBadge/CloakBadge/CloakPanel/ScoreBar/RadarChart/EvaluatorBadges, plain presentational, safe in both Server and Client contexts) + lib/content/charity-data.ts. /charity-scorecard/[slug] is a full Server Component (legacy had zero client state on that page) with generateStaticParams for all 98 slugs — confirmed all 98 statically generated in pnpm build. Fixed a real crawlability gap: the Scorecard/Evaluators tabs were conditionally unmounted until clicked (same pattern as the peptide-watch fix) — now always server-rendered, toggled via hidden, verified present in raw HTML. Verified live: 200 OK on both the index and a profile page, all real charity names present.</t>
+          <t>PeptideQuiz25.tsx. Real content ported in full — all 25 questions across 5 scoring dimensions (Science Literacy, Red Flag Detection, Provider Evaluation, Regulatory Awareness, Personal Risk Assessment), all 4 answer choices with real feedback text per question, all 5 result profiles with real recommendations. Built PeptideQuiz (client component, components/marketing/peptide-quiz.tsx) matching the existing single-file precedent set by engage-audit.tsx. The email-gate phase's "GET MY REPORT" never posted anywhere even in the legacy source (no backend call in its handler) — kept as real client-only gating. AssessmentResultActions's "Send to Tony"/"Keep Private" (a tRPC CRM write) was dropped; "Download PDF" (window.print) kept since it's real and backend-free. Legacy hero image (CloudFront) confirmed 403. Reused PeptideShutdownBanner + BioChainCTA. Verified live: 200 OK, intro copy/dimensions present, typecheck/lint/production-build clean.</t>
         </is>
       </c>
       <c r="E105" s="14" t="inlineStr">
@@ -3383,7 +3383,7 @@
       <c r="A106" s="4" t="n"/>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>/find-your-journey</t>
+          <t>/clock-keeper-part-2</t>
         </is>
       </c>
       <c r="C106" s="13" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>JourneyFinder.tsx. Real content ported in full — all 5 NLP-style questions with real weighted choices, all 6 journey archetypes (Thinker/Operator/Relationship/Body/Impact/Crusade) with real curated article lists linking to real /blog/[slug] posts. Built JourneyFinder (single client component, data + UI together, matching the engage-audit.tsx/peptide-quiz.tsx precedent). Converted legacy's plain Unicode glyph icons (◉⬡∞◈◎⚔) to lucide-react icons. Dropped the "relationship" journey's external link to intimacyassess-tcir3hon.manus.space — confirmed dead, same fully-decommissioned Manus host as everywhere else in this migration. AssessmentResultActions's backend save dropped; retake kept (real, client-only). Verified live: 200 OK, intro copy present, typecheck/lint/production-build clean.</t>
+          <t>ClockKeeperPartII.tsx. Built 2026-10-06: hero, intro, 5 modes, the 5 questions, optional name/email; saves to Supabase clock_keeper_responses (anonymous allowed; server-validated), response count in the hero. Fixes the dead link from the Part I essay. Saving works once the database script is run. Was: Deferred, not skipped. A companion response-collection form for the /blog/the-clock-keeper-chronicles-part-1 essay — 5 questions + alternate "modes" (reframe/meta/jazz/minimum), posts to trpc.clockKeeper.submit, displays a live trpc.clockKeeper.count response counter. Unlike /post-intervention, this doesn't promise anonymity, so a mailto: fallback (matching newsletter-popup.tsx's pattern) could work for the submit action — but the live response counter has no honest fallback without a real backend. Lower priority than the rest of Phase 4 (a companion piece to one specific post, not a core marketing page); revisit with a mailto-based submit and the counter dropped.</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
@@ -3406,7 +3406,7 @@
       <c r="A107" s="4" t="n"/>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>/skippy</t>
+          <t>/charity-scorecard + /charity-scorecard/:slug</t>
         </is>
       </c>
       <c r="C107" s="13" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>SkippyMap.tsx. Ported 2026-09-29 from the legacy source, full destination list and copy unchanged. It was unblocked because 34 of its 38 destinations now exist. The other 4 (/friend-gate, /post-intervention, /pri-research, /thought-cloud) show "Coming Soon" instead of a broken link. /the-index, /cheshire-grin and /life-assessment now link straight to their redirect targets. Progress is kept in localStorage under legacy's key, read hydration-safely. Emoji are replaced with Lucide icons. noindex because it's a personal page for one named person, and legacy had no SEO tags on it. A Manus branch had its own version with a trimmed list and rewritten copy, not used (see docs/ai/project_production_restoration_branch.md). Verified with a production build: 200, noindex, and every non-null link resolves to a real route.</t>
+          <t>CharityScorecard.tsx, CharityProfile.tsx (uses charityData.ts). Real content ported in full — 98 real named charities scored across 7 weighted dimensions unifying GiveWell/Charity Navigator/CharityWatch/Candid ratings plus a proprietary Cloak-vs-Clear transparency score; 3-tab explorer (Rankings with search/filter/sort/expand, Scorecard, Evaluators) and a full per-charity profile page with an SVG radar chart, score breakdown, quick facts, external ratings, and similar-charity cross-links. No backend dependency in the legacy source at all. Built CharityScorecardExplorer (client) + shared components/marketing/charity-badges.tsx (GradeBadge/CloakBadge/CloakPanel/ScoreBar/RadarChart/EvaluatorBadges, plain presentational, safe in both Server and Client contexts) + lib/content/charity-data.ts. /charity-scorecard/[slug] is a full Server Component (legacy had zero client state on that page) with generateStaticParams for all 98 slugs — confirmed all 98 statically generated in pnpm build. Fixed a real crawlability gap: the Scorecard/Evaluators tabs were conditionally unmounted until clicked (same pattern as the peptide-watch fix) — now always server-rendered, toggled via hidden, verified present in raw HTML. Verified live: 200 OK on both the index and a profile page, all real charity names present.</t>
         </is>
       </c>
       <c r="E107" s="14" t="inlineStr">
@@ -3429,7 +3429,7 @@
       <c r="A108" s="4" t="n"/>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>/ecosystem-map</t>
+          <t>/find-your-journey</t>
         </is>
       </c>
       <c r="C108" s="13" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>EcosystemMap.tsx. Ported 2026-09-29 with legacy copy (6 phases, 18 experience descriptions, closing CTA). URLs and completion come from the shared JOURNEY_MAP/useJourneyProgress in components/assessments/journey-tracker.tsx. All 18 IDs resolve. Collapsed phases are hidden with CSS rather than unmounted, so all descriptions are in the server HTML. 6 experiences still link to Tony's own *.manus.space apps, same as /my-journey; that's an owner decision. Verified with a production build: 200, all copy in the server HTML.</t>
+          <t>JourneyFinder.tsx. Real content ported in full — all 5 NLP-style questions with real weighted choices, all 6 journey archetypes (Thinker/Operator/Relationship/Body/Impact/Crusade) with real curated article lists linking to real /blog/[slug] posts. Built JourneyFinder (single client component, data + UI together, matching the engage-audit.tsx/peptide-quiz.tsx precedent). Converted legacy's plain Unicode glyph icons (◉⬡∞◈◎⚔) to lucide-react icons. Dropped the "relationship" journey's external link to intimacyassess-tcir3hon.manus.space — confirmed dead, same fully-decommissioned Manus host as everywhere else in this migration. AssessmentResultActions's backend save dropped; retake kept (real, client-only). Verified live: 200 OK, intro copy present, typecheck/lint/production-build clean.</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
@@ -3452,7 +3452,7 @@
       <c r="A109" s="4" t="n"/>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>/my-highlights</t>
+          <t>/skippy</t>
         </is>
       </c>
       <c r="C109" s="13" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>MyHighlights.tsx. Built 2026-10-06: select 10-2,000 characters in any essay and a "Save Highlight" button appears (no login code on essay pages; signed-out readers get a sign-in link; essays stay statically built); "Your Commonplace Book" lists saved passages by essay with real titles, remove button per passage; RLS keeps each member to their own rows. Saving works once the database script is run. Was: Deferred, not skipped. Entirely an authenticated account feature — gated behind useAuth(), reads/deletes saved text highlights via trpc.highlights.list/highlights.delete. No real content exists to show a signed-out visitor beyond a "Sign In" prompt; the underlying "select text in an essay to save it" feature isn't built anywhere else in this migration either. Blocked on real auth + a highlights backend (Phase 5+), not a content-porting task.</t>
+          <t>SkippyMap.tsx. Ported 2026-09-29 from the legacy source, full destination list and copy unchanged. It was unblocked because 34 of its 38 destinations now exist. The other 4 (/friend-gate, /post-intervention, /pri-research, /thought-cloud) show "Coming Soon" instead of a broken link. /the-index, /cheshire-grin and /life-assessment now link straight to their redirect targets. Progress is kept in localStorage under legacy's key, read hydration-safely. Emoji are replaced with Lucide icons. noindex because it's a personal page for one named person, and legacy had no SEO tags on it. A Manus branch had its own version with a trimmed list and rewritten copy, not used (see docs/ai/project_production_restoration_branch.md). Verified with a production build: 200, noindex, and every non-null link resolves to a real route.</t>
         </is>
       </c>
       <c r="E109" s="14" t="inlineStr">
@@ -3475,7 +3475,7 @@
       <c r="A110" s="4" t="n"/>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>/my-impact</t>
+          <t>/ecosystem-map</t>
         </is>
       </c>
       <c r="C110" s="13" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>MyReferrals.tsx. Built 2026-10-06: invite link (/signup?ref=CODE, code created on first visit), people referred, depth score, referrals list; a referral is recorded when the invited member confirms their email. Depth = passages the referred member saved (legacy added essays read, assessments and chats per member, which this site doesn't track). Works once the database script is run. Was: Deferred, not skipped — same reasoning as /my-highlights. Entirely an authenticated referral-tracking dashboard (trpc.referral.stats, a depth-scored referral graph). No content to port without real auth + a referrals backend.</t>
+          <t>EcosystemMap.tsx. Ported 2026-09-29 with legacy copy (6 phases, 18 experience descriptions, closing CTA). URLs and completion come from the shared JOURNEY_MAP/useJourneyProgress in components/assessments/journey-tracker.tsx. All 18 IDs resolve. Collapsed phases are hidden with CSS rather than unmounted, so all descriptions are in the server HTML. 6 experiences still link to Tony's own *.manus.space apps, same as /my-journey; that's an owner decision. Verified with a production build: 200, all copy in the server HTML.</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
@@ -3498,7 +3498,7 @@
       <c r="A111" s="4" t="n"/>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>/friend-gate</t>
+          <t>/my-highlights</t>
         </is>
       </c>
       <c r="C111" s="13" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>FriendGate.tsx. Built 2026-10-06 (email only, owner chose Resend): intro, nominate 3 friends (Formik + Yup, disposable/duplicate emails refused), invites emailed via Resend's HTTP API (src/lib/email.ts, no new package), bookmarkable seeker page /friend-gate/[token] (auto-refreshes; opens after 72h; 2+ "wait" blocks), anonymous messages shown sorted, not in friend order. Was: Deferred, not skipped. Real backend workflow (3 tRPC calls) — generates invite links for three friends, tracks their responses, enforces a 72-hour wait. No client-side-only version makes sense; the entire feature is the backend coordination. Blocked on real auth/backend (Phase 5+).</t>
+          <t>MyHighlights.tsx. Built 2026-10-06: select 10-2,000 characters in any essay and a "Save Highlight" button appears (no login code on essay pages; signed-out readers get a sign-in link; essays stay statically built); "Your Commonplace Book" lists saved passages by essay with real titles, remove button per passage; RLS keeps each member to their own rows. Saving works once the database script is run. Was: Deferred, not skipped. Entirely an authenticated account feature — gated behind useAuth(), reads/deletes saved text highlights via trpc.highlights.list/highlights.delete. No real content exists to show a signed-out visitor beyond a "Sign In" prompt; the underlying "select text in an essay to save it" feature isn't built anywhere else in this migration either. Blocked on real auth + a highlights backend (Phase 5+), not a content-porting task.</t>
         </is>
       </c>
       <c r="E111" s="14" t="inlineStr">
@@ -3521,7 +3521,7 @@
       <c r="A112" s="4" t="n"/>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>/friend-survey/:token</t>
+          <t>/my-impact</t>
         </is>
       </c>
       <c r="C112" s="13" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>FriendSurvey.tsx. Built 2026-10-06: identity check (email must match the invite) &gt; 6-digit code by email (15 min, max 5 tries, new safeguard) &gt; the six questions &gt; thanks; invalid/used links handled. Was: Deferred, not skipped — the token-gated survey a friend fills out after being invited via /friend-gate (5 tRPC calls). Depends entirely on /friend-gate existing first.</t>
+          <t>MyReferrals.tsx. Built 2026-10-06: invite link (/signup?ref=CODE, code created on first visit), people referred, depth score, referrals list; a referral is recorded when the invited member confirms their email. Depth = passages the referred member saved (legacy added essays read, assessments and chats per member, which this site doesn't track). Works once the database script is run. Was: Deferred, not skipped — same reasoning as /my-highlights. Entirely an authenticated referral-tracking dashboard (trpc.referral.stats, a depth-scored referral graph). No content to port without real auth + a referrals backend.</t>
         </is>
       </c>
       <c r="E112" s="14" t="inlineStr">
@@ -3544,7 +3544,7 @@
       <c r="A113" s="4" t="n"/>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>/impact-dashboard</t>
+          <t>/friend-gate</t>
         </is>
       </c>
       <c r="C113" s="13" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>ImpactDashboard.tsx (built, not yet pushed — pending local review). Real content ported in full across all 6 tabs (Overview, Token Ecosystems, Portfolio Impact, SoulScore, Charity Index, iRR Framework) — the 4 real ImpactSoul token ecosystems (BEYOND/REX/SPACE/BEING), 8 portfolio categories, all 12 SoulScore dimensions, the charity index summary, and the full iRR/Hawkins framework explanation. Built ImpactDashboardExplorer (client) + lib/content/impact-dashboard.ts. Dropped the canvas particle field and scroll-linked parallax hero (decoration not worth the runtime cost, same reasoning used throughout this migration) and the legacy hero images, which used the banned /api/img/ Manus path — replaced with a plain gradient hero. The 3 "LAUNCH SOULSCORE ENGINE"/"LAUNCH C-NPV CALCULATOR" links pointed to /soulscore, which doesn't exist yet — rendered as a "Coming Soon" badge instead of a broken link or a silently-dropped promise. All 6 tabs render always in SSR HTML (crawlability fix, same pattern as charity-scorecard/peptide-watch) — verified live: 200 OK, all tab content present including "Coming Soon" state, typecheck/lint/production-build clean.</t>
+          <t>FriendGate.tsx. Built 2026-10-06 (email only, owner chose Resend): intro, nominate 3 friends (Formik + Yup, disposable/duplicate emails refused), invites emailed via Resend's HTTP API (src/lib/email.ts, no new package), bookmarkable seeker page /friend-gate/[token] (auto-refreshes; opens after 72h; 2+ "wait" blocks), anonymous messages shown sorted, not in friend order. Was: Deferred, not skipped. Real backend workflow (3 tRPC calls) — generates invite links for three friends, tracks their responses, enforces a 72-hour wait. No client-side-only version makes sense; the entire feature is the backend coordination. Blocked on real auth/backend (Phase 5+).</t>
         </is>
       </c>
       <c r="E113" s="14" t="inlineStr">
@@ -3567,7 +3567,7 @@
       <c r="A114" s="4" t="n"/>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>/medicine-sequencing</t>
+          <t>/friend-survey/:token</t>
         </is>
       </c>
       <c r="C114" s="13" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>MedicineSequencing.tsx. Unblocked once /psychedelic-readiness-index and /facilitator-index shipped. The shared MEDICINES dataset was already in lib/content/pri-data.ts, so this renders from it directly. Real content ported in full: the six-rung ladder, its philosophy passage, every medicine's "why this rung" note, overview, therapeutic uses, readiness requirements and tradition, plus the level filter. Built MedicineSequencingLadder (components/pri/medicine-sequencing-ladder.tsx, client) with each card on a shadcn Collapsible using forceMount. The level filter hides rungs instead of unmounting them, so all 39 cards' text is in the raw SSR HTML. Legacy's inline styles object was rebuilt as one full literal Tailwind class string per rung. The intensity bar width is the one style exception. Real legacy bug fixed: Mambe's complexityLevel was "Gentle Entry", which isn't one of the six rungs, so legacy counted it in "All (39)" but never rendered its card. Normalized to "Entry" in the dataset (nothing else read that field). The hero's hardcoded "38 medicines" now reads the real count. Also re-linked /the-philosophy's Instruments: PRI, Facilitator Index and Medicine Sequencing are now real links, and Three Friends Gate keeps "Coming Soon" until /friend-gate exists. Verified live: 200 OK, 39 collapsible panels in SSR HTML, typecheck/lint clean.</t>
+          <t>FriendSurvey.tsx. Built 2026-10-06: identity check (email must match the invite) &gt; 6-digit code by email (15 min, max 5 tries, new safeguard) &gt; the six questions &gt; thanks; invalid/used links handled. Was: Deferred, not skipped — the token-gated survey a friend fills out after being invited via /friend-gate (5 tRPC calls). Depends entirely on /friend-gate existing first.</t>
         </is>
       </c>
       <c r="E114" s="14" t="inlineStr">
@@ -3590,7 +3590,7 @@
       <c r="A115" s="4" t="n"/>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>/the-philosophy</t>
+          <t>/impact-dashboard</t>
         </is>
       </c>
       <c r="C115" s="13" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>ThePhilosophy.tsx (built, not yet pushed — pending local review). Real content ported in full — the complete "Diode of Perception" passage and all 5 "What This Means" interpretive sections. No backend dependency in the legacy source. The 4 "Instruments" links (Psychedelic Readiness Index, Facilitator Index, Medicine Sequencing, Three Friends Gate) don't exist yet — rendered as "Coming Soon" badges instead of broken links, same pattern as /impact-dashboard's SoulScore links; revisit and re-link as each destination gets built. Verified live: 200 OK, full passage + interpretation present, typecheck/lint/production-build clean.</t>
+          <t>ImpactDashboard.tsx (built, not yet pushed — pending local review). Real content ported in full across all 6 tabs (Overview, Token Ecosystems, Portfolio Impact, SoulScore, Charity Index, iRR Framework) — the 4 real ImpactSoul token ecosystems (BEYOND/REX/SPACE/BEING), 8 portfolio categories, all 12 SoulScore dimensions, the charity index summary, and the full iRR/Hawkins framework explanation. Built ImpactDashboardExplorer (client) + lib/content/impact-dashboard.ts. Dropped the canvas particle field and scroll-linked parallax hero (decoration not worth the runtime cost, same reasoning used throughout this migration) and the legacy hero images, which used the banned /api/img/ Manus path — replaced with a plain gradient hero. The 3 "LAUNCH SOULSCORE ENGINE"/"LAUNCH C-NPV CALCULATOR" links pointed to /soulscore, which doesn't exist yet — rendered as a "Coming Soon" badge instead of a broken link or a silently-dropped promise. All 6 tabs render always in SSR HTML (crawlability fix, same pattern as charity-scorecard/peptide-watch) — verified live: 200 OK, all tab content present including "Coming Soon" state, typecheck/lint/production-build clean.</t>
         </is>
       </c>
       <c r="E115" s="14" t="inlineStr">
@@ -3613,7 +3613,7 @@
       <c r="A116" s="4" t="n"/>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>/post-intervention</t>
+          <t>/medicine-sequencing</t>
         </is>
       </c>
       <c r="C116" s="13" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>PostIntervention.tsx. Built 2026-10-06 as a step registry (day, type, survey, done); saves to Supabase post_intervention_assessments, server-validated. Live's copy says results "go to tony@tonygreenberg.com"; that needs an email service (none connected yet), so for now they are only saved in Supabase. Saving works once the database script is run. Was: Deferred, not skipped. Unlike other single-tRPC-call pages in this migration, this one can't be honestly reduced to a mailto: fallback: the page's entire value proposition, stated three times in its own copy ("Anonymous", "No one can see your name. No one can see your email.", results routed anonymously), is that the facilitator never sees who submitted it. A mailto: would expose the visitor's own email address the moment they hit send in their mail client — actively contradicting the one promise the page makes, not just a missing nice-to-have. Blocked on a real anonymous-submission backend (Phase 5+).</t>
+          <t>MedicineSequencing.tsx. Unblocked once /psychedelic-readiness-index and /facilitator-index shipped. The shared MEDICINES dataset was already in lib/content/pri-data.ts, so this renders from it directly. Real content ported in full: the six-rung ladder, its philosophy passage, every medicine's "why this rung" note, overview, therapeutic uses, readiness requirements and tradition, plus the level filter. Built MedicineSequencingLadder (components/pri/medicine-sequencing-ladder.tsx, client) with each card on a shadcn Collapsible using forceMount. The level filter hides rungs instead of unmounting them, so all 39 cards' text is in the raw SSR HTML. Legacy's inline styles object was rebuilt as one full literal Tailwind class string per rung. The intensity bar width is the one style exception. Real legacy bug fixed: Mambe's complexityLevel was "Gentle Entry", which isn't one of the six rungs, so legacy counted it in "All (39)" but never rendered its card. Normalized to "Entry" in the dataset (nothing else read that field). The hero's hardcoded "38 medicines" now reads the real count. Also re-linked /the-philosophy's Instruments: PRI, Facilitator Index and Medicine Sequencing are now real links, and Three Friends Gate keeps "Coming Soon" until /friend-gate exists. Verified live: 200 OK, 39 collapsible panels in SSR HTML, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E116" s="14" t="inlineStr">
@@ -3636,7 +3636,7 @@
       <c r="A117" s="4" t="n"/>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>/flow-circuit</t>
+          <t>/the-philosophy</t>
         </is>
       </c>
       <c r="C117" s="13" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>redirect stub to flow.tonygreenberg.com (built, not yet pushed — pending local review). Legacy did this client-side via window.location.replace(...) with a flash of "Loading Flow Circuit..." text; ported as a real next.config.ts redirects() entry instead — a genuine 308, no JS required, no flash. Confirmed flow.tonygreenberg.com is live (200) before wiring it. Verified live: curl -I /flow-circuit returns 308 with location: https://flow.tonygreenberg.com/, typecheck/lint/production-build clean.</t>
+          <t>ThePhilosophy.tsx (built, not yet pushed — pending local review). Real content ported in full — the complete "Diode of Perception" passage and all 5 "What This Means" interpretive sections. No backend dependency in the legacy source. The 4 "Instruments" links (Psychedelic Readiness Index, Facilitator Index, Medicine Sequencing, Three Friends Gate) don't exist yet — rendered as "Coming Soon" badges instead of broken links, same pattern as /impact-dashboard's SoulScore links; revisit and re-link as each destination gets built. Verified live: 200 OK, full passage + interpretation present, typecheck/lint/production-build clean.</t>
         </is>
       </c>
       <c r="E117" s="14" t="inlineStr">
@@ -3659,7 +3659,7 @@
       <c r="A118" s="4" t="n"/>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>/supplier-intake + /supplier-intake-long/:token</t>
+          <t>/post-intervention</t>
         </is>
       </c>
       <c r="C118" s="13" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>SupplierIntakeForm.tsx, SupplierIntakeLong.tsx (built, not yet pushed — pending local review). Plan revised: the original note said "keep pointed at legacy backend," but that backend (trpc.vendor.submitStage1/submitStage2, token-gated file uploads) ran on the now-fully-dead Manus host — there's nothing left to point to. Found a real, active bug in the process: 5 already-ported pages ("Become a Supply Partner" CTAs — peptide-hall-of-shame, peptide-supply-chain, peptide-matrix, whats-legal, etc.) link to /supplier-intake, which didn't exist, so those were live 404s. Fixed by redirecting both /supplier-intake and /supplier-intake-long/:token to RampRate's own real, live supplier intake at ramprate.com/biochain/supplier-intake (confirmed reachable) — the same real destination BioChainCTA already links to elsewhere in this migration, rather than rebuilding a form whose only working backend no longer exists. Verified live: both routes return real 308s to the correct destination, typecheck/lint/production-build clean.</t>
+          <t>PostIntervention.tsx. Built 2026-10-06 as a step registry (day, type, survey, done); saves to Supabase post_intervention_assessments, server-validated. Live's copy says results "go to tony@tonygreenberg.com"; that needs an email service (none connected yet), so for now they are only saved in Supabase. Saving works once the database script is run. Was: Deferred, not skipped. Unlike other single-tRPC-call pages in this migration, this one can't be honestly reduced to a mailto: fallback: the page's entire value proposition, stated three times in its own copy ("Anonymous", "No one can see your name. No one can see your email.", results routed anonymously), is that the facilitator never sees who submitted it. A mailto: would expose the visitor's own email address the moment they hit send in their mail client — actively contradicting the one promise the page makes, not just a missing nice-to-have. Blocked on a real anonymous-submission backend (Phase 5+).</t>
         </is>
       </c>
       <c r="E118" s="14" t="inlineStr">
@@ -3682,7 +3682,7 @@
       <c r="A119" s="4" t="n"/>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>/subscribe</t>
+          <t>/flow-circuit</t>
         </is>
       </c>
       <c r="C119" s="13" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Subscribe.tsx. Ported 2026-09-29: legacy copy, a working free signup through /api/subscribe (Kit, with a mailto fallback, same as the popup), and the $99/yr membership and $27 compilation shown as information only with no checkout. This fixed a live 404, because /the-letter already linked here. /api/subscribe also got input length caps.</t>
+          <t>redirect stub to flow.tonygreenberg.com (built, not yet pushed — pending local review). Legacy did this client-side via window.location.replace(...) with a flash of "Loading Flow Circuit..." text; ported as a real next.config.ts redirects() entry instead — a genuine 308, no JS required, no flash. Confirmed flow.tonygreenberg.com is live (200) before wiring it. Verified live: curl -I /flow-circuit returns 308 with location: https://flow.tonygreenberg.com/, typecheck/lint/production-build clean.</t>
         </is>
       </c>
       <c r="E119" s="14" t="inlineStr">
@@ -3705,17 +3705,17 @@
       <c r="A120" s="4" t="n"/>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>/shop, /payment-success, /payment-cancel</t>
-        </is>
-      </c>
-      <c r="C120" s="16" t="inlineStr">
-        <is>
-          <t>Deferred</t>
+          <t>/supplier-intake + /supplier-intake-long/:token</t>
+        </is>
+      </c>
+      <c r="C120" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>defer: these are Stripe-backed; flag for the later billing-migration phase, do not port checkout logic yet, static/informational content only if ported now</t>
+          <t>SupplierIntakeForm.tsx, SupplierIntakeLong.tsx (built, not yet pushed — pending local review). Plan revised: the original note said "keep pointed at legacy backend," but that backend (trpc.vendor.submitStage1/submitStage2, token-gated file uploads) ran on the now-fully-dead Manus host — there's nothing left to point to. Found a real, active bug in the process: 5 already-ported pages ("Become a Supply Partner" CTAs — peptide-hall-of-shame, peptide-supply-chain, peptide-matrix, whats-legal, etc.) link to /supplier-intake, which didn't exist, so those were live 404s. Fixed by redirecting both /supplier-intake and /supplier-intake-long/:token to RampRate's own real, live supplier intake at ramprate.com/biochain/supplier-intake (confirmed reachable) — the same real destination BioChainCTA already links to elsewhere in this migration, rather than rebuilding a form whose only working backend no longer exists. Verified live: both routes return real 308s to the correct destination, typecheck/lint/production-build clean.</t>
         </is>
       </c>
       <c r="E120" s="14" t="inlineStr">
@@ -3728,7 +3728,7 @@
       <c r="A121" s="4" t="n"/>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Drop dead code, do not port</t>
+          <t>/subscribe</t>
         </is>
       </c>
       <c r="C121" s="13" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>HumanOS.tsx, ComponentShowcase.tsx, VendorIntakeForm.tsx, VendorIntakeLong.tsx, pre-consolidation manifesto sub-pages (AttentionEconomics.tsx, BlockerFinder.tsx, LegalDatabase.tsx, TenWeapons.tsx, ReportSpammer.tsx). Effectively satisfied by the repo-wide flatten: the entire legacy Vite/Express app (including all of these) now lives only under _legacy-manus-app/, outside src/app/ entirely — none of them are part of the deployed Next.js app or its build.</t>
+          <t>Subscribe.tsx. Ported 2026-09-29: legacy copy, a working free signup through /api/subscribe (Kit, with a mailto fallback, same as the popup), and the $99/yr membership and $27 compilation shown as information only with no checkout. This fixed a live 404, because /the-letter already linked here. /api/subscribe also got input length caps.</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
@@ -3751,17 +3751,17 @@
       <c r="A122" s="4" t="n"/>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>/america-unbundled-field-guide</t>
-        </is>
-      </c>
-      <c r="C122" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>/shop, /payment-success, /payment-cancel</t>
+        </is>
+      </c>
+      <c r="C122" s="16" t="inlineStr">
+        <is>
+          <t>Deferred</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>live-only (no legacy file; added to the live site after the _legacy-manus-app/ snapshot). Ported 2026-10-01 from the live page: copy, links, title/description/OG and Article JSON-LD verbatim; hero image from Sanity (rescued age-of-ai-no-party). The 10 "90-day commitment" questions are a small client island (components/america-unbundled/field-guide-responses.tsx) that saves to localStorage under live's key, copies, or downloads a .txt; nothing is sent anywhere. Sits inside the normal site chrome (live has its own standalone masthead; kept in-page). Part One /america-unbundled is ported too (next line); its temporary 307 to / is gone. /connect → / 308 added (matches live).</t>
+          <t>defer: these are Stripe-backed; flag for the later billing-migration phase, do not port checkout logic yet, static/informational content only if ported now</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
@@ -3774,7 +3774,7 @@
       <c r="A123" s="4" t="n"/>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>/america-unbundled</t>
+          <t>Drop dead code, do not port</t>
         </is>
       </c>
       <c r="C123" s="13" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>live-only Part One, "AI Does Not Have a Candidate" (no legacy file). Ported 2026-10-01 from the live page: copy, links, title/description/keywords/OG and Article JSON-LD verbatim; same series masthead and styling as Part Two; hero is the same rescued Sanity image (age-of-ai-no-party). The "Share the question" rail is a tiny client island (components/america-unbundled/share-rail.tsx: copy link + device share; X/LinkedIn are plain links). #sources anchor kept for Part Two's link. Temporary /america-unbundled → / redirect removed from next.config.ts.</t>
+          <t>HumanOS.tsx, ComponentShowcase.tsx, VendorIntakeForm.tsx, VendorIntakeLong.tsx, pre-consolidation manifesto sub-pages (AttentionEconomics.tsx, BlockerFinder.tsx, LegalDatabase.tsx, TenWeapons.tsx, ReportSpammer.tsx). Effectively satisfied by the repo-wide flatten: the entire legacy Vite/Express app (including all of these) now lives only under _legacy-manus-app/, outside src/app/ entirely — none of them are part of the deployed Next.js app or its build.</t>
         </is>
       </c>
       <c r="E123" s="14" t="inlineStr">
@@ -3794,20 +3794,33 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="10" t="inlineStr">
-        <is>
-          <t>Phase 5 — Blog Engine (Sanity-backed)</t>
-        </is>
-      </c>
-      <c r="B124" s="11" t="n"/>
-      <c r="C124" s="11" t="n"/>
-      <c r="D124" s="12" t="n"/>
+      <c r="A124" s="4" t="n"/>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>/america-unbundled-field-guide</t>
+        </is>
+      </c>
+      <c r="C124" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>live-only (no legacy file; added to the live site after the _legacy-manus-app/ snapshot). Ported 2026-10-01 from the live page: copy, links, title/description/OG and Article JSON-LD verbatim; hero image from Sanity (rescued age-of-ai-no-party). The 10 "90-day commitment" questions are a small client island (components/america-unbundled/field-guide-responses.tsx) that saves to localStorage under live's key, copies, or downloads a .txt; nothing is sent anywhere. Sits inside the normal site chrome (live has its own standalone masthead; kept in-page). Part One /america-unbundled is ported too (next line); its temporary 307 to / is gone. /connect → / 308 added (matches live).</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="inlineStr">
+        <is>
+          <t>Phase 4 — Marketing Core Pages (30 routes)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n"/>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>/ and /blog</t>
+          <t>/america-unbundled</t>
         </is>
       </c>
       <c r="C125" s="13" t="inlineStr">
@@ -3817,43 +3830,30 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>blog index, paginated (12/page), category filter pills, real Sanity data — verified live: 200 OK, real post links, real category links</t>
+          <t>live-only Part One, "AI Does Not Have a Candidate" (no legacy file). Ported 2026-10-01 from the live page: copy, links, title/description/keywords/OG and Article JSON-LD verbatim; same series masthead and styling as Part Two; hero is the same rescued Sanity image (age-of-ai-no-party). The "Share the question" rail is a tiny client island (components/america-unbundled/share-rail.tsx: copy link + device share; X/LinkedIn are plain links). #sources anchor kept for Part Two's link. Temporary /america-unbundled → / redirect removed from next.config.ts.</t>
         </is>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
+          <t>Phase 4 — Marketing Core Pages (30 routes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
           <t>Phase 5 — Blog Engine (Sanity-backed)</t>
         </is>
       </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="4" t="n"/>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>/blog/[slug]</t>
-        </is>
-      </c>
-      <c r="C126" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D126" s="4" t="inlineStr">
-        <is>
-          <t>post template: hero image (next/image), portable text renderer, byline/reading time, pull quote (added pullQuote field to the post schema + backfilled 15 posts that had one — wasn't in the original schema, would've been silently dropped otherwise), drop caps (CSS ::first-letter on the article's first paragraph, in globals.css — position-based, not per-post data, so it works for every post automatically), related posts (same-category, falling back to most-recent) — verified live against a real post: correct &lt;title&gt;, correct read time, body rendered</t>
-        </is>
-      </c>
-      <c r="E126" s="14" t="inlineStr">
-        <is>
-          <t>Phase 5 — Blog Engine (Sanity-backed)</t>
-        </is>
-      </c>
+      <c r="B126" s="11" t="n"/>
+      <c r="C126" s="11" t="n"/>
+      <c r="D126" s="12" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n"/>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>/blog/category/[slug]</t>
+          <t>/ and /blog</t>
         </is>
       </c>
       <c r="C127" s="13" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>category listing + pagination (not explicitly in the original phase list, but linked from the index's category pills — built so that link isn't a 404; own quality bar already requires "every page links to 2+", not dead links)</t>
+          <t>blog index, paginated (12/page), category filter pills, real Sanity data — verified live: 200 OK, real post links, real category links</t>
         </is>
       </c>
       <c r="E127" s="14" t="inlineStr">
@@ -3876,7 +3876,7 @@
       <c r="A128" s="4" t="n"/>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>generateStaticParams for all post slugs and category slugs (SSG)</t>
+          <t>/blog/[slug]</t>
         </is>
       </c>
       <c r="C128" s="13" t="inlineStr">
@@ -3884,7 +3884,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D128" s="4" t="inlineStr"/>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>post template: hero image (next/image), portable text renderer, byline/reading time, pull quote (added pullQuote field to the post schema + backfilled 15 posts that had one — wasn't in the original schema, would've been silently dropped otherwise), drop caps (CSS ::first-letter on the article's first paragraph, in globals.css — position-based, not per-post data, so it works for every post automatically), related posts (same-category, falling back to most-recent) — verified live against a real post: correct &lt;title&gt;, correct read time, body rendered</t>
+        </is>
+      </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
           <t>Phase 5 — Blog Engine (Sanity-backed)</t>
@@ -3895,7 +3899,7 @@
       <c r="A129" s="4" t="n"/>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>sitemap.ts already live from real Sanity data (122 URLs verified</t>
+          <t>/blog/category/[slug]</t>
         </is>
       </c>
       <c r="C129" s="13" t="inlineStr">
@@ -3905,7 +3909,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>homepage + 121 posts)</t>
+          <t>category listing + pagination (not explicitly in the original phase list, but linked from the index's category pills — built so that link isn't a 404; own quality bar already requires "every page links to 2+", not dead links)</t>
         </is>
       </c>
       <c r="E129" s="14" t="inlineStr">
@@ -3918,7 +3922,7 @@
       <c r="A130" s="4" t="n"/>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>/search</t>
+          <t>generateStaticParams for all post slugs and category slugs (SSG)</t>
         </is>
       </c>
       <c r="C130" s="13" t="inlineStr">
@@ -3926,11 +3930,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>full-text search across posts (built, not yet pushed — pending local review). No legacy Search.tsx ever existed — this is a genuinely new page, not a port (Phase 5's plan noted the GROQ query searchPostsQuery was already written but the page wasn't). Built as a pure Server Component: a plain GET &lt;form&gt; to /search?q=... needs no client JS at all, sanityFetch(searchPostsQuery, ...) runs server-side per this repo's data-fetching rule, results render with the existing PostCard. Was an orphan page (only reachable via /series' already-corrected link) — added a search icon to site-header.tsx (desktop + mobile) linking to /search so it has a real, discoverable entry point. Verified live: 200 OK empty state, ?q=trust returns 30 real matched posts (capped by the query's own [0...30]), typecheck/lint/production-build clean.</t>
-        </is>
-      </c>
+      <c r="D130" s="4" t="inlineStr"/>
       <c r="E130" s="14" t="inlineStr">
         <is>
           <t>Phase 5 — Blog Engine (Sanity-backed)</t>
@@ -3941,7 +3941,7 @@
       <c r="A131" s="4" t="n"/>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Header search icon → command-palette modal, matching legacy's real SearchPalette.tsx UX (a page-navigation link before this)</t>
+          <t>sitemap.ts already live from real Sanity data (122 URLs verified</t>
         </is>
       </c>
       <c r="C131" s="13" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Ported the real ~121-entry PAGES directory (data/searchablePages.ts is a grep-confirmed-dead older duplicate, not used) into lib/content/search-directory.ts, and the real word-frequency/multi-word-AND relevance scoring from lib/searchEngine.ts into lib/search-engine.ts. Fixed 3 stale /assessments/* hrefs to their real canonical routes, repointed the dead /the-index link to /search, and repointed 5 pre-consolidation Attention Theft sub-page links to real in-page anchors on the consolidated /attention-theft. Dropped 4 entries with no real route and no documented deferral (FauxTony, The Open Door, Alex Azzi, Spamtoast — Alex Azzi has since been ported, see below; should be re-added to the directory in a follow-up). Built components/search-modal.tsx on the existing shadcn Dialog (no cmdk, no framer-motion, no new dependency) with a real global Cmd/Ctrl+K shortcut, arrow-key nav + Enter-to-open, and Escape/backdrop close (free from Radix). Blog-post search is a debounced (250ms) fetch to a new app/api/search/route.ts, reusing /search's existing searchPostsQuery/sanityFetch rather than adding a new GROQ query, re-ranked server-side with the same relevance scorer used for static pages — legacy's TF-IDF body-density scoring wasn't portable since Sanity content isn't bundled client-side the way legacy's blogData.json was. Real Loader2 spinner during the fetch, no "..." text. Replaced both header &lt;Link href="/search"&gt; search icons (desktop + mobile) with buttons that open the modal; /s</t>
+          <t>homepage + 121 posts)</t>
         </is>
       </c>
       <c r="E131" s="14" t="inlineStr">
@@ -3964,7 +3964,7 @@
       <c r="A132" s="4" t="n"/>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>/articles</t>
+          <t>/search</t>
         </is>
       </c>
       <c r="C132" s="13" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>full archive grouped by category (built, not yet pushed — pending local review). Real content ported in full — all 6 discovery-mode curations (Start Here, Short Reads, Deep Dives, Contrarian, Changed His Mind, Surprise Me) with their real curated slug lists, all 8 real category descriptions, category-grouped default view, search. Built ArticlesExplorer (client, components/blog/articles-explorer.tsx) + lib/content/articles-discovery.ts. Posts now come live from Sanity (allPostsForArchiveQuery) instead of the static blogData.json import. Caught and fixed a real legacy bug: 3 of the curated discovery-mode slugs (psychedelics-could-become-extractive-capitalism-unless, enterprise-blockchain-can-big-business-co-opt-an-existing-technology, an-ode-to-kusaki-where-plants-become-culinary-art) didn't match any real post slug — verified against blogData.json, corrected to the real slugs, same class of stale-slug bug already fixed on /journeys//recent-creations//series. Footer "SUBSCRIBE" CTA linked to /subscribe (Stripe-backed, deferred) — replaced with a link to /blog. Verified live: 200 OK, all discovery modes + categories present, both corrected slugs render as real working links, typecheck/lint/production-build clean.</t>
+          <t>full-text search across posts (built, not yet pushed — pending local review). No legacy Search.tsx ever existed — this is a genuinely new page, not a port (Phase 5's plan noted the GROQ query searchPostsQuery was already written but the page wasn't). Built as a pure Server Component: a plain GET &lt;form&gt; to /search?q=... needs no client JS at all, sanityFetch(searchPostsQuery, ...) runs server-side per this repo's data-fetching rule, results render with the existing PostCard. Was an orphan page (only reachable via /series' already-corrected link) — added a search icon to site-header.tsx (desktop + mobile) linking to /search so it has a real, discoverable entry point. Verified live: 200 OK empty state, ?q=trust returns 30 real matched posts (capped by the query's own [0...30]), typecheck/lint/production-build clean.</t>
         </is>
       </c>
       <c r="E132" s="14" t="inlineStr">
@@ -3987,7 +3987,7 @@
       <c r="A133" s="4" t="n"/>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>/thesis-threads</t>
+          <t>Header search icon → command-palette modal, matching legacy's real SearchPalette.tsx UX (a page-navigation link before this)</t>
         </is>
       </c>
       <c r="C133" s="13" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>curated-by-thread view (built, not yet pushed — pending local review). No legacy port of a data file was needed — lib/content/thesis-threads.ts (Tony's own newsletter-curation "content DNA" document, ported from legacy client/src/data/sitePrompt.ts) already existed from an earlier pass with all 69 articleSlugs pre-verified against the real post corpus. Built ThesisThreadsExplorer (client, components/blog/thesis-threads-explorer.tsx) + app/thesis-threads/page.tsx (Server Component, sanityFetch(allPostsForArchiveQuery)). 4 tabs ported in full: Thesis Threads (6 threads, thread selector, per-thread article list with real THESIS_CONNECTORS pull-quotes, unmapped-articles section), Section Map (5 section-to-thesis cards), Research Library (6 citations + 4 LP comparables), Content Rules (voice, 6 content rules, "never use" word list). Fixed legacy's /read/[slug] links to this site's real /blog/[slug] pattern. Two decorative simplifications, matching calls already made elsewhere in this migration: canvas-based floating particles dropped (same as home-hero.tsx), and the legacy hero's generic Unsplash stock photo + scroll-parallax dropped for a plain dark band (not a real editorial image worth rescuing into Sanity, same call as the peptide pages' dead CloudFront heroes). Was an orphan page — added to site-nav-data.ts's "Read" mega-menu category, next to "All Essays". Verified live: 200 OK, stats strip shows real counts (121 essays, 69 mapped, 52 unmapped — matches the data module's own</t>
+          <t>Ported the real ~121-entry PAGES directory (data/searchablePages.ts is a grep-confirmed-dead older duplicate, not used) into lib/content/search-directory.ts, and the real word-frequency/multi-word-AND relevance scoring from lib/searchEngine.ts into lib/search-engine.ts. Fixed 3 stale /assessments/* hrefs to their real canonical routes, repointed the dead /the-index link to /search, and repointed 5 pre-consolidation Attention Theft sub-page links to real in-page anchors on the consolidated /attention-theft. Dropped 4 entries with no real route and no documented deferral (FauxTony, The Open Door, Alex Azzi, Spamtoast — Alex Azzi has since been ported, see below; should be re-added to the directory in a follow-up). Built components/search-modal.tsx on the existing shadcn Dialog (no cmdk, no framer-motion, no new dependency) with a real global Cmd/Ctrl+K shortcut, arrow-key nav + Enter-to-open, and Escape/backdrop close (free from Radix). Blog-post search is a debounced (250ms) fetch to a new app/api/search/route.ts, reusing /search's existing searchPostsQuery/sanityFetch rather than adding a new GROQ query, re-ranked server-side with the same relevance scorer used for static pages — legacy's TF-IDF body-density scoring wasn't portable since Sanity content isn't bundled client-side the way legacy's blogData.json was. Real Loader2 spinner during the fetch, no "..." text. Replaced both header &lt;Link href="/search"&gt; search icons (desktop + mobile) with buttons that open the modal; /s</t>
         </is>
       </c>
       <c r="E133" s="14" t="inlineStr">
@@ -4010,7 +4010,7 @@
       <c r="A134" s="4" t="n"/>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>/impact-futurism</t>
+          <t>/articles</t>
         </is>
       </c>
       <c r="C134" s="13" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>curated category view (built, not yet pushed — pending local review). Real content ported in full — all 7 real essays (3 featured + 4 more) across 5 tags (Health Systems, AI &amp; Energy, Psychedelic Medicine, Infrastructure, Trust &amp; Verification), curated teaser copy, tag filter. Built ImpactFuturismExplorer (client, components/blog/impact-futurism-explorer.tsx) + lib/content/impact-futurism.ts (curated tag/teaser only — real title/date/hero-image/read-time now come live from Sanity via allPostsForArchiveQuery, same content-boundary split as articles-discovery.ts/thesis-threads.ts). Legacy's per-article hero images (/manus-storage/... — banned Manus host — plus one dead CloudFront URL) dropped in favor of each real post's own Sanity heroImage, already present per post, no rescue needed. Both "Get the Dispatch" CTAs linked to /subscribe (Stripe-backed, deferred) — replaced with /blog, same fix already applied on /articles. Fixed legacy's stale hardcoded "All 121 Essays" to a live posts.length. Was an orphan page — added to site-nav-data.ts's "Read" mega-menu category. Verified live: 200 OK, all 7 real titles + real Sanity hero images render, live essay count (121) confirmed in SSR HTML, typecheck/lint clean.</t>
+          <t>full archive grouped by category (built, not yet pushed — pending local review). Real content ported in full — all 6 discovery-mode curations (Start Here, Short Reads, Deep Dives, Contrarian, Changed His Mind, Surprise Me) with their real curated slug lists, all 8 real category descriptions, category-grouped default view, search. Built ArticlesExplorer (client, components/blog/articles-explorer.tsx) + lib/content/articles-discovery.ts. Posts now come live from Sanity (allPostsForArchiveQuery) instead of the static blogData.json import. Caught and fixed a real legacy bug: 3 of the curated discovery-mode slugs (psychedelics-could-become-extractive-capitalism-unless, enterprise-blockchain-can-big-business-co-opt-an-existing-technology, an-ode-to-kusaki-where-plants-become-culinary-art) didn't match any real post slug — verified against blogData.json, corrected to the real slugs, same class of stale-slug bug already fixed on /journeys//recent-creations//series. Footer "SUBSCRIBE" CTA linked to /subscribe (Stripe-backed, deferred) — replaced with a link to /blog. Verified live: 200 OK, all discovery modes + categories present, both corrected slugs render as real working links, typecheck/lint/production-build clean.</t>
         </is>
       </c>
       <c r="E134" s="14" t="inlineStr">
@@ -4033,7 +4033,7 @@
       <c r="A135" s="4" t="n"/>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>On-demand webhook-triggered revalidation on Sanity publish (built, not yet pushed</t>
+          <t>/thesis-threads</t>
         </is>
       </c>
       <c r="C135" s="13" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>pending local review). Corrected mislabel: the old note here said "Phase 11", but Phase 11 is the unrelated Publish-Approval Workflow (Supabase dashboard) — this is its own small piece of infra, not part of that phase. Built app/api/revalidate/route.ts: a Route Handler using next-sanity/webhook's parseBody (wraps @sanity/webhook's isValidSignature — already a transitive dep via next-sanity, no new package needed) to verify the request against SANITY_WEBHOOK_SECRET (already reserved in .env.local.example from an earlier pass, never actually wired up). On a valid signature, calls revalidateTag("sanity", { expire: 0 }) — every sanityFetch() call already tags its cache entry "sanity" (see lib/sanity/client.ts), so one tag covers every Sanity-backed page, no per-route path list to maintain. Real Next.js 16 breaking change caught: revalidateTag(tag) (single-argument) is deprecated and now a type error — the second argument is required. Read node_modules/next/dist/docs/.../revalidateTag.md rather than assuming the old signature; its own webhook example calls out { expire: 0 } specifically for "webhooks or third-party services that need immediate expiration" (the default recommended profile: "max" only refreshes on next visit, wrong for this case). Still needs a human step this migration can't do: creating the actual webhook in Sanity's project dashboard (manage.sanity.io → API → Webhooks) pointing at /api/revalidate with a matching secret — documented in the route's own file comment</t>
+          <t>curated-by-thread view (built, not yet pushed — pending local review). No legacy port of a data file was needed — lib/content/thesis-threads.ts (Tony's own newsletter-curation "content DNA" document, ported from legacy client/src/data/sitePrompt.ts) already existed from an earlier pass with all 69 articleSlugs pre-verified against the real post corpus. Built ThesisThreadsExplorer (client, components/blog/thesis-threads-explorer.tsx) + app/thesis-threads/page.tsx (Server Component, sanityFetch(allPostsForArchiveQuery)). 4 tabs ported in full: Thesis Threads (6 threads, thread selector, per-thread article list with real THESIS_CONNECTORS pull-quotes, unmapped-articles section), Section Map (5 section-to-thesis cards), Research Library (6 citations + 4 LP comparables), Content Rules (voice, 6 content rules, "never use" word list). Fixed legacy's /read/[slug] links to this site's real /blog/[slug] pattern. Two decorative simplifications, matching calls already made elsewhere in this migration: canvas-based floating particles dropped (same as home-hero.tsx), and the legacy hero's generic Unsplash stock photo + scroll-parallax dropped for a plain dark band (not a real editorial image worth rescuing into Sanity, same call as the peptide pages' dead CloudFront heroes). Was an orphan page — added to site-nav-data.ts's "Read" mega-menu category, next to "All Essays". Verified live: 200 OK, stats strip shows real counts (121 essays, 69 mapped, 52 unmapped — matches the data module's own</t>
         </is>
       </c>
       <c r="E135" s="14" t="inlineStr">
@@ -4056,7 +4056,7 @@
       <c r="A136" s="4" t="n"/>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>Article footer standardization (built, not yet pushed</t>
+          <t>/impact-futurism</t>
         </is>
       </c>
       <c r="C136" s="13" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pending local review). Real content ported for all 121 entries from footerData.json (exercise / 2-4 curated related links with hand-written reasons / riddle / further reading), keyed by slug. Built ArticleFooter (components/blog/article-footer.tsx) + lib/content/article-footers.ts, wired into app/blog/[slug]/page.tsx after the "Read next" section. Fetched all 121 real post slugs from Sanity to cross-check every related[].slug reference — found and fixed 3 real stale slugs across 2 renamed posts (the Bentley/EV piece and the Butcher's Daughter piece each had a different stale slug pointing at them), same class of bug already fixed on /journeys//articles//series. Also found: (1) one entry used a relatedArticles key instead of related — the key BlogPost.tsx actually reads — meaning that post's related-links block silently never rendered even in legacy; normalized to related. (2) a trueSelfCTA field in one entry that BlogPost.tsx never reads at all (grepped — zero usages) — dead data, dropped rather than ported. (3) an exercise.steps checklist in one entry that legacy authored but never rendered (component only reads exercise.title/.description) — real content, so rendered here instead of repeating the oversight. The one slug: "manifesto" sentinel (legacy's in-code special case for "link to the manifesto, not a post") resolved to a real href: "/living-declaration" in the data itself. The hardcoded "TrueSelf Soul Print Assessment" CTA (identical on every legacy post) is kept, but </t>
+          <t>curated category view (built, not yet pushed — pending local review). Real content ported in full — all 7 real essays (3 featured + 4 more) across 5 tags (Health Systems, AI &amp; Energy, Psychedelic Medicine, Infrastructure, Trust &amp; Verification), curated teaser copy, tag filter. Built ImpactFuturismExplorer (client, components/blog/impact-futurism-explorer.tsx) + lib/content/impact-futurism.ts (curated tag/teaser only — real title/date/hero-image/read-time now come live from Sanity via allPostsForArchiveQuery, same content-boundary split as articles-discovery.ts/thesis-threads.ts). Legacy's per-article hero images (/manus-storage/... — banned Manus host — plus one dead CloudFront URL) dropped in favor of each real post's own Sanity heroImage, already present per post, no rescue needed. Both "Get the Dispatch" CTAs linked to /subscribe (Stripe-backed, deferred) — replaced with /blog, same fix already applied on /articles. Fixed legacy's stale hardcoded "All 121 Essays" to a live posts.length. Was an orphan page — added to site-nav-data.ts's "Read" mega-menu category. Verified live: 200 OK, all 7 real titles + real Sanity hero images render, live essay count (121) confirmed in SSR HTML, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E136" s="14" t="inlineStr">
@@ -4079,7 +4079,7 @@
       <c r="A137" s="4" t="n"/>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Spot-check all 121 migrated posts' body formatting (automated, not a Studio visual pass</t>
+          <t>On-demand webhook-triggered revalidation on Sanity publish (built, not yet pushed</t>
         </is>
       </c>
       <c r="C137" s="13" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>see note below on what that still leaves open). Wrote a one-off script fetching every post's body from Sanity and scanning for markdown-conversion artifacts (unconverted bold/text/headings/bullets, leaked HTML tags, empty text blocks, link marks with no href). Flagged 12 of 121. Two real bugs found and one fixed: (1) ~8 posts have link marks with href: "" — traced to the actual root cause by reading blogData.json's raw originalContent markdown directly: the source markdown itself has text links with an already-empty URL (predates this migration entirely — e.g. the-tug-of-war-ethical-vs-economic-decisions has subsidy, dairy kills, etc., empty parens in the original text). portable-text.tsx's link renderer was defaulting a missing href to "#", silently turning lost-forever data into a fake dead link on every affected post. Fixed at the renderer level (real code, not data): a link mark with no href now renders its text plain, with no anchor wrapper — verified live on the-tug-of-war-ethical-vs-economic-decisions (zero href="#" in the rendered HTML, previously-"linked" words like "subsidy" and "dairy kills" still read fine as plain text). (2) 4 posts (energy-is-money-money-is-memory, frqncy-the-bus-that-restores-the-world, is-that-a-lot-clarisse-abelarde, you-are-the-moat) had literal un-rendered !alt markdown image syntax visible as plain paragraph text — the markdown→Portable-Text converter (scripts/markdown-to-portable-text.ts) never had image-syntax handling at all. Checked al</t>
+          <t>pending local review). Corrected mislabel: the old note here said "Phase 11", but Phase 11 is the unrelated Publish-Approval Workflow (Supabase dashboard) — this is its own small piece of infra, not part of that phase. Built app/api/revalidate/route.ts: a Route Handler using next-sanity/webhook's parseBody (wraps @sanity/webhook's isValidSignature — already a transitive dep via next-sanity, no new package needed) to verify the request against SANITY_WEBHOOK_SECRET (already reserved in .env.local.example from an earlier pass, never actually wired up). On a valid signature, calls revalidateTag("sanity", { expire: 0 }) — every sanityFetch() call already tags its cache entry "sanity" (see lib/sanity/client.ts), so one tag covers every Sanity-backed page, no per-route path list to maintain. Real Next.js 16 breaking change caught: revalidateTag(tag) (single-argument) is deprecated and now a type error — the second argument is required. Read node_modules/next/dist/docs/.../revalidateTag.md rather than assuming the old signature; its own webhook example calls out { expire: 0 } specifically for "webhooks or third-party services that need immediate expiration" (the default recommended profile: "max" only refreshes on next visit, wrong for this case). Still needs a human step this migration can't do: creating the actual webhook in Sanity's project dashboard (manage.sanity.io → API → Webhooks) pointing at /api/revalidate with a matching secret — documented in the route's own file comment</t>
         </is>
       </c>
       <c r="E137" s="14" t="inlineStr">
@@ -4102,7 +4102,7 @@
       <c r="A138" s="4" t="n"/>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Reconcile blogData.json vs. the legacy blogPosts.ts module. Resolved</t>
+          <t>Article footer standardization (built, not yet pushed</t>
         </is>
       </c>
       <c r="C138" s="13" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>not a duplicate. Traced blogPosts.ts's own header comment ("Blog Post Data — 20 most recent posts... original excerpt, AI-rewritten 'Updated for Today' version") plus its actual 25-entry BlogPost[] array: this is a distinct, unrelated, much smaller dataset (an AI-rewrite/"TonyG Format" exercise with lesson/nextSteps fields) that was never the input to migrate-blog-posts.ts, which reads only blogData.json (confirmed in that script's own top-of-file comment and its LegacyPost type). blogData.json is the sole authoritative source for the 121-post corpus; blogPosts.ts was never a candidate alternate and needs no reconciliation — it's simply out of scope, superseded implicitly by the real 121-post migration.</t>
+          <t xml:space="preserve">pending local review). Real content ported for all 121 entries from footerData.json (exercise / 2-4 curated related links with hand-written reasons / riddle / further reading), keyed by slug. Built ArticleFooter (components/blog/article-footer.tsx) + lib/content/article-footers.ts, wired into app/blog/[slug]/page.tsx after the "Read next" section. Fetched all 121 real post slugs from Sanity to cross-check every related[].slug reference — found and fixed 3 real stale slugs across 2 renamed posts (the Bentley/EV piece and the Butcher's Daughter piece each had a different stale slug pointing at them), same class of bug already fixed on /journeys//articles//series. Also found: (1) one entry used a relatedArticles key instead of related — the key BlogPost.tsx actually reads — meaning that post's related-links block silently never rendered even in legacy; normalized to related. (2) a trueSelfCTA field in one entry that BlogPost.tsx never reads at all (grepped — zero usages) — dead data, dropped rather than ported. (3) an exercise.steps checklist in one entry that legacy authored but never rendered (component only reads exercise.title/.description) — real content, so rendered here instead of repeating the oversight. The one slug: "manifesto" sentinel (legacy's in-code special case for "link to the manifesto, not a post") resolved to a real href: "/living-declaration" in the data itself. The hardcoded "TrueSelf Soul Print Assessment" CTA (identical on every legacy post) is kept, but </t>
         </is>
       </c>
       <c r="E138" s="14" t="inlineStr">
@@ -4125,7 +4125,7 @@
       <c r="A139" s="4" t="n"/>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Preserve internal cross-link structure from client/src/data/linkMap.ts / readingPaths.ts (built, not yet pushed</t>
+          <t>Spot-check all 121 migrated posts' body formatting (automated, not a Studio visual pass</t>
         </is>
       </c>
       <c r="C139" s="13" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>pending local review). Both ported as real, working features, not just cross-referenced.</t>
+          <t>see note below on what that still leaves open). Wrote a one-off script fetching every post's body from Sanity and scanning for markdown-conversion artifacts (unconverted bold/text/headings/bullets, leaked HTML tags, empty text blocks, link marks with no href). Flagged 12 of 121. Two real bugs found and one fixed: (1) ~8 posts have link marks with href: "" — traced to the actual root cause by reading blogData.json's raw originalContent markdown directly: the source markdown itself has text links with an already-empty URL (predates this migration entirely — e.g. the-tug-of-war-ethical-vs-economic-decisions has subsidy, dairy kills, etc., empty parens in the original text). portable-text.tsx's link renderer was defaulting a missing href to "#", silently turning lost-forever data into a fake dead link on every affected post. Fixed at the renderer level (real code, not data): a link mark with no href now renders its text plain, with no anchor wrapper — verified live on the-tug-of-war-ethical-vs-economic-decisions (zero href="#" in the rendered HTML, previously-"linked" words like "subsidy" and "dairy kills" still read fine as plain text). (2) 4 posts (energy-is-money-money-is-memory, frqncy-the-bus-that-restores-the-world, is-that-a-lot-clarisse-abelarde, you-are-the-moat) had literal un-rendered !alt markdown image syntax visible as plain paragraph text — the markdown→Portable-Text converter (scripts/markdown-to-portable-text.ts) never had image-syntax handling at all. Checked al</t>
         </is>
       </c>
       <c r="E139" s="14" t="inlineStr">
@@ -4148,7 +4148,7 @@
       <c r="A140" s="4" t="n"/>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>Post extras from live (2026-10-01)</t>
+          <t>Reconcile blogData.json vs. the legacy blogPosts.ts module. Resolved</t>
         </is>
       </c>
       <c r="C140" s="13" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>every post now shows the blocks legacy BlogPost.tsx and live render around the essay: format tag, validity score and series badge in the header, the summary, "Before You Read" (Reveal/Hint via &lt;details&gt;, answer in the server HTML), then The Lesson, Next Steps, Further Reading, Voices in This Space / Also involves, Since this was written, and the series reading list. Data ported unchanged into src/lib/content/post-extras.ts (from blogData.json, riddleData.ts, thoughtLeaders.ts), further-reading.ts and essay-series.ts (now shared with /series); component src/components/blog/post-extras.tsx. Checked against live: lesson, next steps and validity match on every post that loaded. Left out on purpose: read counts, reactions/comments/"Rate this thinking" (no backend), and the "Updated for Today" toggle (an AI rewrite; live defaults to the original text, which is what Sanity holds).</t>
+          <t>not a duplicate. Traced blogPosts.ts's own header comment ("Blog Post Data — 20 most recent posts... original excerpt, AI-rewritten 'Updated for Today' version") plus its actual 25-entry BlogPost[] array: this is a distinct, unrelated, much smaller dataset (an AI-rewrite/"TonyG Format" exercise with lesson/nextSteps fields) that was never the input to migrate-blog-posts.ts, which reads only blogData.json (confirmed in that script's own top-of-file comment and its LegacyPost type). blogData.json is the sole authoritative source for the 121-post corpus; blogPosts.ts was never a candidate alternate and needs no reconciliation — it's simply out of scope, superseded implicitly by the real 121-post migration.</t>
         </is>
       </c>
       <c r="E140" s="14" t="inlineStr">
@@ -4171,7 +4171,7 @@
       <c r="A141" s="4" t="n"/>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Lost tables restored (2026-10-01)</t>
+          <t>Preserve internal cross-link structure from client/src/data/linkMap.ts / readingPaths.ts (built, not yet pushed</t>
         </is>
       </c>
       <c r="C141" s="13" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>the migration's markdown converter had no table case, so all tables in 18 posts (44 tables) were silently dropped; live still shows them. Added a plain dataTable body type (src/sanity/schemas/dataTable.ts, rendered in src/lib/sanity/portable-text.tsx, scrolls inside its own box on phones), a table case in scripts/markdown-to-portable-text.ts, and put every table back after the paragraph that precedes it in the legacy markdown (scripts/restore-blog-tables.ts), as Sanity drafts built on existing drafts. find-my-ev-... had a malformed table showing as raw "|" text; now a real table (draft).</t>
+          <t>pending local review). Both ported as real, working features, not just cross-referenced.</t>
         </is>
       </c>
       <c r="E141" s="14" t="inlineStr">
@@ -4194,7 +4194,7 @@
       <c r="A142" s="4" t="n"/>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Essays rewritten on live, saved as Sanity drafts (2026-10-01)</t>
+          <t>Post extras from live (2026-10-01)</t>
         </is>
       </c>
       <c r="C142" s="13" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>(scripts/sync-live-essays.ts, from live's essay body; live images rescued into Sanity): your-blood-lies-without-your-dna, energy-is-money-money-is-memory (kept our fixed author bio), the-way-of-dao, what-solutions-are-best-built-with-blockchain replaced with live's version; the-peptide-truth-... got live's "Provenance and Corrections" note and the new stem cell appendix. Checked: every live paragraph is in the drafts. Not changed: posts where live still shows old WordPress furniture we already cleaned (Davos 2022, Boiling the Human, Mastering BD, and others), and /the-stack links (a "Private review draft" page on live, not ported; text kept, link dropped).</t>
+          <t>every post now shows the blocks legacy BlogPost.tsx and live render around the essay: format tag, validity score and series badge in the header, the summary, "Before You Read" (Reveal/Hint via &lt;details&gt;, answer in the server HTML), then The Lesson, Next Steps, Further Reading, Voices in This Space / Also involves, Since this was written, and the series reading list. Data ported unchanged into src/lib/content/post-extras.ts (from blogData.json, riddleData.ts, thoughtLeaders.ts), further-reading.ts and essay-series.ts (now shared with /series); component src/components/blog/post-extras.tsx. Checked against live: lesson, next steps and validity match on every post that loaded. Left out on purpose: read counts, reactions/comments/"Rate this thinking" (no backend), and the "Updated for Today" toggle (an AI rewrite; live defaults to the original text, which is what Sanity holds).</t>
         </is>
       </c>
       <c r="E142" s="14" t="inlineStr">
@@ -4217,7 +4217,7 @@
       <c r="A143" s="4" t="n"/>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Password gate on you-are-the-moat (done 2026-10-06, owner chose a password)</t>
+          <t>Lost tables restored (2026-10-01)</t>
         </is>
       </c>
       <c r="C143" s="13" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Server-checked: the password is in the GATED_POST_PASSWORD env var (in .env.local; must also be set in Netlify, or the essay stays locked for everyone), compared on the server, and the body is only rendered after a correct entry (checked: the locked page HTML has none of the essay text, and it is noindex, nofollow). Unlock lasts 30 days via an httpOnly cookie scoped to the post; changing the password locks everyone out again. Legacy's lock screen copy ("This One's Behind a Door"). Other posts stay statically built. Tested wrong/right password and reload in Chrome and Safari. Still true: the Sanity dataset is publicly readable, so the raw text is reachable through the Sanity API by someone who knows how. Was: (passwordGate, a browser-side check), but the port renders it openly to everyone. Needs a decision on how to gate it (see status block) before launch.</t>
+          <t>the migration's markdown converter had no table case, so all tables in 18 posts (44 tables) were silently dropped; live still shows them. Added a plain dataTable body type (src/sanity/schemas/dataTable.ts, rendered in src/lib/sanity/portable-text.tsx, scrolls inside its own box on phones), a table case in scripts/markdown-to-portable-text.ts, and put every table back after the paragraph that precedes it in the legacy markdown (scripts/restore-blog-tables.ts), as Sanity drafts built on existing drafts. find-my-ev-... had a malformed table showing as raw "|" text; now a real table (draft).</t>
         </is>
       </c>
       <c r="E143" s="14" t="inlineStr">
@@ -4240,7 +4240,7 @@
       <c r="A144" s="4" t="n"/>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Essay page rebuilt to match live (2026-10-07, asked for by the team)</t>
+          <t>Essays rewritten on live, saved as Sanity drafts (2026-10-01)</t>
         </is>
       </c>
       <c r="C144" s="13" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Every post now has live's layout: full-width hero with the title over it (posts without their own photo use live's default arch art, rescued into Sanity, also on post cards), back link, colored format badge, date · category · read time, validity, byline (co-author override field), summary with a rule, labelled share buttons (X, LinkedIn, Facebook, More, Email, Copy link), live's type (Libre Baskerville body with indents, Cormorant Garamond italic section titles, IM Fell English drop cap, Fraunces title; loaded on essays only), red in-text links, the auto pull quote, section breaks, the GemSpark card with "What is this?", and the sticky parchment Contents sidebar (1280px+) that highlights the section being read (IntersectionObserver plus a settle check, so jumps land right; click scrolls there). Checked in Chrome: sidebar stays pinned, highlight follows scrolling, End/Home and clicks, no console errors, every image loads. After the essay, in live's order: The Lesson, Next steps, Further reading, Voices, Also involves (chips), Since this was written, #tags, Did this land?, video moment (Clarisse, FRQNCY), Ask Tony directly (emails Tony), Discourse comments, What's the verdict?, Rate this thinking, diagnostic and ImpactSoul CTAs, The Mirror reflection (85 posts), Try this, Where this leads, riddle, Go deeper, Discover your pattern, Originally published at, Previous/Next (legacy's order, series-aware), Why this matters now, author card, booking box, Subscribe / ABIT, social line,</t>
+          <t>(scripts/sync-live-essays.ts, from live's essay body; live images rescued into Sanity): your-blood-lies-without-your-dna, energy-is-money-money-is-memory (kept our fixed author bio), the-way-of-dao, what-solutions-are-best-built-with-blockchain replaced with live's version; the-peptide-truth-... got live's "Provenance and Corrections" note and the new stem cell appendix. Checked: every live paragraph is in the drafts. Not changed: posts where live still shows old WordPress furniture we already cleaned (Davos 2022, Boiling the Human, Mastering BD, and others), and /the-stack links (a "Private review draft" page on live, not ported; text kept, link dropped).</t>
         </is>
       </c>
       <c r="E144" s="14" t="inlineStr">
@@ -4263,7 +4263,7 @@
       <c r="A145" s="4" t="n"/>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Essay extras moved into Sanity (2026-10-07, owner chose "publish directly")</t>
+          <t>Password gate on you-are-the-moat (done 2026-10-06, owner chose a password)</t>
         </is>
       </c>
       <c r="C145" s="13" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>The per-post blocks that were in code (post-extras.ts, article-footers.ts, reading-paths.ts, deleted) are now fields on each post, "Essay extras" tab in Studio: 152 documents written (every post plus its pending draft), counts checked (105 lessons, 93 riddles, 115 read-next lists). New fields the same day: byline, editorsNote (Forward Health's September 2026 note), provenanceNote (on live's 14 first-hand/accusation posts), videoMoment, updatedBody.</t>
+          <t>Server-checked: the password is in the GATED_POST_PASSWORD env var (in .env.local; must also be set in Netlify, or the essay stays locked for everyone), compared on the server, and the body is only rendered after a correct entry (checked: the locked page HTML has none of the essay text, and it is noindex, nofollow). Unlock lasts 30 days via an httpOnly cookie scoped to the post; changing the password locks everyone out again. Legacy's lock screen copy ("This One's Behind a Door"). Other posts stay statically built. Tested wrong/right password and reload in Chrome and Safari. Still true: the Sanity dataset is publicly readable, so the raw text is reachable through the Sanity API by someone who knows how. Was: (passwordGate, a browser-side check), but the port renders it openly to everyone. Needs a decision on how to gate it (see status block) before launch.</t>
         </is>
       </c>
       <c r="E145" s="14" t="inlineStr">
@@ -4286,7 +4286,7 @@
       <c r="A146" s="4" t="n"/>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>"Original post / Updated for today" switch (2026-10-07; was decision 20)</t>
+          <t>Essay page rebuilt to match live (2026-10-07, asked for by the team)</t>
         </is>
       </c>
       <c r="C146" s="13" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Legacy's updated texts checked against live (98-99% word overlap on 5 posts), imported into updatedBody for 102 essays (scripts/import-2026-10-07-updated-bodies.ts; stray TITLE:/DATE: headers dropped). Skipped: 9 where both versions are identical, 3 whose updated text holds pictures (frqncy, two Molecule as Mirror parts; they show the original only). Both versions are in the page; the switch needs no request, and the Contents sidebar follows it.</t>
+          <t>Every post now has live's layout: full-width hero with the title over it (posts without their own photo use live's default arch art, rescued into Sanity, also on post cards), back link, colored format badge, date · category · read time, validity, byline (co-author override field), summary with a rule, labelled share buttons (X, LinkedIn, Facebook, More, Email, Copy link), live's type (Libre Baskerville body with indents, Cormorant Garamond italic section titles, IM Fell English drop cap, Fraunces title; loaded on essays only), red in-text links, the auto pull quote, section breaks, the GemSpark card with "What is this?", and the sticky parchment Contents sidebar (1280px+) that highlights the section being read (IntersectionObserver plus a settle check, so jumps land right; click scrolls there). Checked in Chrome: sidebar stays pinned, highlight follows scrolling, End/Home and clicks, no console errors, every image loads. After the essay, in live's order: The Lesson, Next steps, Further reading, Voices, Also involves (chips), Since this was written, #tags, Did this land?, video moment (Clarisse, FRQNCY), Ask Tony directly (emails Tony), Discourse comments, What's the verdict?, Rate this thinking, diagnostic and ImpactSoul CTAs, The Mirror reflection (85 posts), Try this, Where this leads, riddle, Go deeper, Discover your pattern, Originally published at, Previous/Next (legacy's order, series-aware), Why this matters now, author card, booking box, Subscribe / ABIT, social line,</t>
         </is>
       </c>
       <c r="E146" s="14" t="inlineStr">
@@ -4309,7 +4309,7 @@
       <c r="A147" s="4" t="n"/>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>The 2 live-only essays imported (2026-10-07; was decision 8)</t>
+          <t>Essay extras moved into Sanity (2026-10-07, owner chose "publish directly")</t>
         </is>
       </c>
       <c r="C147" s="13" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>the-tollbooth-and-the-alternative (with Alex Veytsel; its own hero rescued; lesson, next steps, Try this, Where this leads, riddle, Go deeper) and what-quest-could-fix, published. Tollbooth's 5 body pictures are broken on live itself (a dark placeholder with unreadable text), so they're listed in BLOG-IMAGE-BRIEFS.md to be made instead.</t>
+          <t>The per-post blocks that were in code (post-extras.ts, article-footers.ts, reading-paths.ts, deleted) are now fields on each post, "Essay extras" tab in Studio: 152 documents written (every post plus its pending draft), counts checked (105 lessons, 93 riddles, 115 read-next lists). New fields the same day: byline, editorsNote (Forward Health's September 2026 note), provenanceNote (on live's 14 first-hand/accusation posts), videoMoment, updatedBody.</t>
         </is>
       </c>
       <c r="E147" s="14" t="inlineStr">
@@ -4332,7 +4332,7 @@
       <c r="A148" s="4" t="n"/>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Pending drafts published (2026-10-07, owner said yes; was decision 18)</t>
+          <t>"Original post / Updated for today" switch (2026-10-07; was decision 20)</t>
         </is>
       </c>
       <c r="C148" s="13" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>all 31 post drafts (44 tables on 17 posts, the essays brought in line with live including Your Blood's new hero, link and clean-up fixes). No drafts left. Creation dates checked unchanged (the heading rules depend on them).</t>
+          <t>Legacy's updated texts checked against live (98-99% word overlap on 5 posts), imported into updatedBody for 102 essays (scripts/import-2026-10-07-updated-bodies.ts; stray TITLE:/DATE: headers dropped). Skipped: 9 where both versions are identical, 3 whose updated text holds pictures (frqncy, two Molecule as Mirror parts; they show the original only). Both versions are in the page; the switch needs no request, and the Contents sidebar follows it.</t>
         </is>
       </c>
       <c r="E148" s="14" t="inlineStr">
@@ -4355,7 +4355,7 @@
       <c r="A149" s="4" t="n"/>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Per-post fixes from the 2026-10-07 sweep (all 123 live/our posts compared)</t>
+          <t>The 2 live-only essays imported (2026-10-07; was decision 8)</t>
         </is>
       </c>
       <c r="C149" s="13" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>heart-protocol-addendum heading showed {#heart-protocol-addendum} (fixed in Sanity); lines starting with "◆ " are section titles again, as on live (five-cups had 4); /blog/akbar-cuisine-restoration-economics now redirects to /akbar like live (was decision 21; out of the sitemap); the Elixir of Life product block (photos and order QR codes rescued into Sanity); Clarisse's video rescued.</t>
+          <t>the-tollbooth-and-the-alternative (with Alex Veytsel; its own hero rescued; lesson, next steps, Try this, Where this leads, riddle, Go deeper) and what-quest-could-fix, published. Tollbooth's 5 body pictures are broken on live itself (a dark placeholder with unreadable text), so they're listed in BLOG-IMAGE-BRIEFS.md to be made instead.</t>
         </is>
       </c>
       <c r="E149" s="14" t="inlineStr">
@@ -4378,7 +4378,7 @@
       <c r="A150" s="4" t="n"/>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Reader engagement (2026-10-07)</t>
+          <t>Pending drafts published (2026-10-07, owner said yes; was decision 18)</t>
         </is>
       </c>
       <c r="C150" s="13" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Discourse comments (shown straight away like live, honeypot and a 5-per-10-minutes limit, Tony emailed for each), reactions, Rate this thinking, Micro-commitment: supabase/migrations/0002_blog_engagement.sql, server actions src/app/blog/[slug]/engagement-actions.ts; essays stay prebuilt (the blocks load after the page). Needs the 0002 script run in Supabase (Phase 2) and Resend for the emails; until then the forms say "isn't available just now".</t>
+          <t>all 31 post drafts (44 tables on 17 posts, the essays brought in line with live including Your Blood's new hero, link and clean-up fixes). No drafts left. Creation dates checked unchanged (the heading rules depend on them).</t>
         </is>
       </c>
       <c r="E150" s="14" t="inlineStr">
@@ -4398,20 +4398,33 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="10" t="inlineStr">
-        <is>
-          <t>Phase 6 — BrewSoul (28 routes)</t>
-        </is>
-      </c>
-      <c r="B151" s="11" t="n"/>
-      <c r="C151" s="11" t="n"/>
-      <c r="D151" s="12" t="n"/>
+      <c r="A151" s="4" t="n"/>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>Per-post fixes from the 2026-10-07 sweep (all 123 live/our posts compared)</t>
+        </is>
+      </c>
+      <c r="C151" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>heart-protocol-addendum heading showed {#heart-protocol-addendum} (fixed in Sanity); lines starting with "◆ " are section titles again, as on live (five-cups had 4); /blog/akbar-cuisine-restoration-economics now redirects to /akbar like live (was decision 21; out of the sitemap); the Elixir of Life product block (photos and order QR codes rescued into Sanity); Clarisse's video rescued.</t>
+        </is>
+      </c>
+      <c r="E151" s="14" t="inlineStr">
+        <is>
+          <t>Phase 5 — Blog Engine (Sanity-backed)</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n"/>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul</t>
+          <t>Reader engagement (2026-10-07)</t>
         </is>
       </c>
       <c r="C152" s="13" t="inlineStr">
@@ -4421,43 +4434,30 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>welcome/landing gate (built, not yet pushed — pending local review), along with the shared foundation the rest of Phase 6 depends on. Ported BrewSoulLayout.tsx → app/brewsoul/layout.tsx + components/brewsoul/brewsoul-nav.tsx (BrewSoulNav/BrewSoulFooter), CategoryBadge.tsx → components/brewsoul/category-badge.tsx, brewsoul-config.ts → lib/content/brewsoul-config.ts, and BrewSoulDirectory.tsx's CATEGORIES/PAGE_CATEGORY_MAP data (not the page itself yet) → lib/content/brewsoul-directory.ts. Real architecture decision: BrewSoul is a self-contained sub-site with its own nav/footer/coffee-brown palette, same as legacy — but this app has one flat root layout with no route groups, so the main site's SiteHeader/SiteFooter needed to be suppressed for this one subtree without restructuring every existing route. Added components/site-chrome.tsx (SiteChrome, a small client wrapper checking pathname.startsWith("/brewsoul")) around both in app/layout.tsx — verified via literal &lt;header&gt;/&lt;footer&gt;/&lt;nav&gt; tag counts in real SSR HTML (not text search, which false-positives on Next dev mode's RSC debug payload) that /brewsoul gets zero main-site chrome and its own real nav+footer, while / still gets exactly one of each. Dropped TonyAvatarTrigger (FauxTony chatbot widget — Phase 10, no backend yet, same "don't fake it" call made elsewhere) from the nav. Ported BrewSoulWelcome.tsx → components/brewsoul/brewsoul-welcome-quiz.tsx (8-screen onboarding quiz, real identity-scoring logic, palate questions</t>
+          <t>Discourse comments (shown straight away like live, honeypot and a 5-per-10-minutes limit, Tony emailed for each), reactions, Rate this thinking, Micro-commitment: supabase/migrations/0002_blog_engagement.sql, server actions src/app/blog/[slug]/engagement-actions.ts; essays stay prebuilt (the blocks load after the page). Needs the 0002 script run in Supabase (Phase 2) and Resend for the emails; until then the forms say "isn't available just now".</t>
         </is>
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
+          <t>Phase 5 — Blog Engine (Sanity-backed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="10" t="inlineStr">
+        <is>
           <t>Phase 6 — BrewSoul (28 routes)</t>
         </is>
       </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="4" t="n"/>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>/brewsoul/first-sip</t>
-        </is>
-      </c>
-      <c r="C153" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>onboarding intro (built, not yet pushed — pending local review). Ported "The First Sip Is a Vote" in full — the complete manifesto essay (5 sections, 3 pullquotes, the couplets block, the disclosure-demands grid), the 5-tool journey map, 6 related-essay links (real slugs, cross-checked against this session's already-verified corpus), the closing + sources, and the email capture. Built as a Server Component (all static except the email form) + components/brewsoul/next-steps.tsx (shared "what's next" CTA, itself a Server Component — legacy's hover effects were plain CSS-able, no JS state needed) + components/brewsoul/first-sip-email-capture.tsx (client island, mailto: fallback since no subscribe backend exists, same pattern as newsletter-popup.tsx). Dropped the canvas CoffeeDust decoration and the confirmed-dead hero photo (/api/img/brewsoul-orig_84eb4bc9.jpg, 404, same Manus proxy) — with no image left, the scroll-linked parallax that moved it went too. The 5 tool-card links (prescription/health/pairings/economics/compare) point at later Phase 6 routes not built yet — same forward-reference pattern as /find-my. Verified live: 200 OK, full essay text present, CategoryBadge correctly shows "Start Here" (from PAGE_CATEGORY_MAP), zero main-site chrome leaking in, typecheck/lint clean.</t>
-        </is>
-      </c>
-      <c r="E153" s="14" t="inlineStr">
-        <is>
-          <t>Phase 6 — BrewSoul (28 routes)</t>
-        </is>
-      </c>
+      <c r="B153" s="11" t="n"/>
+      <c r="C153" s="11" t="n"/>
+      <c r="D153" s="12" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="n"/>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/home</t>
+          <t>/brewsoul</t>
         </is>
       </c>
       <c r="C154" s="13" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>the real BrewSoul dashboard (distinct from /brewsoul's identity-quiz welcome gate and /brewsoul/first-sip's manifesto): hero + stats, Follow the Dollar teaser, Top QPR coffees (computed live via computeQPR), the 2025 crisis callout, New Drops, a Wall of Shame preview (SHAME_ENTRIES), the research-hub card grid, and a cyclable health-fact ticker (components/brewsoul/health-ticker.tsx, its own small client island so the rest of the page stays a Server Component). Canvas WarmParticles/ParallaxBg decorations and the dead hero photo (/api/img/brewsoul-orig_84eb4bc9.jpg, same confirmed-404 Manus proxy used elsewhere in Phase 6) dropped for CSS gradients. Stats use the real live BREWSOUL_COFFEES.length (107) in place of legacy's stale "103". Verified live: 200 OK.</t>
+          <t>welcome/landing gate (built, not yet pushed — pending local review), along with the shared foundation the rest of Phase 6 depends on. Ported BrewSoulLayout.tsx → app/brewsoul/layout.tsx + components/brewsoul/brewsoul-nav.tsx (BrewSoulNav/BrewSoulFooter), CategoryBadge.tsx → components/brewsoul/category-badge.tsx, brewsoul-config.ts → lib/content/brewsoul-config.ts, and BrewSoulDirectory.tsx's CATEGORIES/PAGE_CATEGORY_MAP data (not the page itself yet) → lib/content/brewsoul-directory.ts. Real architecture decision: BrewSoul is a self-contained sub-site with its own nav/footer/coffee-brown palette, same as legacy — but this app has one flat root layout with no route groups, so the main site's SiteHeader/SiteFooter needed to be suppressed for this one subtree without restructuring every existing route. Added components/site-chrome.tsx (SiteChrome, a small client wrapper checking pathname.startsWith("/brewsoul")) around both in app/layout.tsx — verified via literal &lt;header&gt;/&lt;footer&gt;/&lt;nav&gt; tag counts in real SSR HTML (not text search, which false-positives on Next dev mode's RSC debug payload) that /brewsoul gets zero main-site chrome and its own real nav+footer, while / still gets exactly one of each. Dropped TonyAvatarTrigger (FauxTony chatbot widget — Phase 10, no backend yet, same "don't fake it" call made elsewhere) from the nav. Ported BrewSoulWelcome.tsx → components/brewsoul/brewsoul-welcome-quiz.tsx (8-screen onboarding quiz, real identity-scoring logic, palate questions</t>
         </is>
       </c>
       <c r="E154" s="14" t="inlineStr">
@@ -4480,7 +4480,7 @@
       <c r="A155" s="4" t="n"/>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/browse</t>
+          <t>/brewsoul/first-sip</t>
         </is>
       </c>
       <c r="C155" s="13" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>coffee listing (components/brewsoul/browse-explorer.tsx), real filter/search over the full BREWSOUL_COFFEES catalog. Verified live: 200 OK.</t>
+          <t>onboarding intro (built, not yet pushed — pending local review). Ported "The First Sip Is a Vote" in full — the complete manifesto essay (5 sections, 3 pullquotes, the couplets block, the disclosure-demands grid), the 5-tool journey map, 6 related-essay links (real slugs, cross-checked against this session's already-verified corpus), the closing + sources, and the email capture. Built as a Server Component (all static except the email form) + components/brewsoul/next-steps.tsx (shared "what's next" CTA, itself a Server Component — legacy's hover effects were plain CSS-able, no JS state needed) + components/brewsoul/first-sip-email-capture.tsx (client island, mailto: fallback since no subscribe backend exists, same pattern as newsletter-popup.tsx). Dropped the canvas CoffeeDust decoration and the confirmed-dead hero photo (/api/img/brewsoul-orig_84eb4bc9.jpg, 404, same Manus proxy) — with no image left, the scroll-linked parallax that moved it went too. The 5 tool-card links (prescription/health/pairings/economics/compare) point at later Phase 6 routes not built yet — same forward-reference pattern as /find-my. Verified live: 200 OK, full essay text present, CategoryBadge correctly shows "Start Here" (from PAGE_CATEGORY_MAP), zero main-site chrome leaking in, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E155" s="14" t="inlineStr">
@@ -4503,7 +4503,7 @@
       <c r="A156" s="4" t="n"/>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/coffee/[id]</t>
+          <t>/brewsoul/home</t>
         </is>
       </c>
       <c r="C156" s="13" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>coffee detail page (breadcrumb, QPR + tier header, quick stats, tasting notes, flavor-profile bars, the 4 intelligence scores, transparency/ethics data, buy links, competition wins, similar-coffees cross-links, journey CTAs), server-rendered with generateStaticParams over all 107 real coffees (this repo's bounded-dynamic-route convention, same as /blog/[slug]) instead of legacy's client-side useParams lookup. Verified live: 200 OK.</t>
+          <t>the real BrewSoul dashboard (distinct from /brewsoul's identity-quiz welcome gate and /brewsoul/first-sip's manifesto): hero + stats, Follow the Dollar teaser, Top QPR coffees (computed live via computeQPR), the 2025 crisis callout, New Drops, a Wall of Shame preview (SHAME_ENTRIES), the research-hub card grid, and a cyclable health-fact ticker (components/brewsoul/health-ticker.tsx, its own small client island so the rest of the page stays a Server Component). Canvas WarmParticles/ParallaxBg decorations and the dead hero photo (/api/img/brewsoul-orig_84eb4bc9.jpg, same confirmed-404 Manus proxy used elsewhere in Phase 6) dropped for CSS gradients. Stats use the real live BREWSOUL_COFFEES.length (107) in place of legacy's stale "103". Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E156" s="14" t="inlineStr">
@@ -4526,7 +4526,7 @@
       <c r="A157" s="4" t="n"/>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/quiz</t>
+          <t>/brewsoul/browse</t>
         </is>
       </c>
       <c r="C157" s="13" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>matching quiz (built, not yet pushed — pending local review), along with the real data/engine foundation most of the rest of Phase 6 depends on. Ported lib/intelligence-engine/{types,scoring}.ts verbatim (generic scoring engine — QPR/availability/scarcity/wow/tier/freshness — reusable beyond BrewSoul) and the full coffee catalog (legacy's 3 files: brewsoul-coffees.ts + -expanded.ts + -expanded2.ts, merged at import time) → one lib/content/brewsoul-coffees.ts, extracted via tsx (not hand-typed — 107 real entries, ~6.5K lines). Caught a real stale count: legacy's own file header claimed "105" and its UI copy said "103", but the actual merged arrays contain 107 — this migration shows the live BREWSOUL_COFFEES.length everywhere instead of a repeated hardcoded number. Ported JourneyBar.tsx (components/brewsoul/journey-bar.tsx) — the fixed bottom "what's next" bar shown on every BrewSoul content page except the identity quiz — and retrofitted it onto /brewsoul/first-sip too (built before JourneyBar existed). Built components/brewsoul/brewsoul-quiz.tsx: real 7-question taste quiz scored against each coffee's real flavorProfile via the real scoring engine, ranking the full catalog by match. Legacy's useMarkVisited was renamed to markVisited (it's a plain localStorage write, not a hook — its old use-prefixed name tripped React's rules-of-hooks lint when called from inside a useEffect). Dropped the canvas WarmParticles decoration and the dead hero photo (same confirmed-404 Manus proxy,</t>
+          <t>coffee listing (components/brewsoul/browse-explorer.tsx), real filter/search over the full BREWSOUL_COFFEES catalog. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E157" s="14" t="inlineStr">
@@ -4549,7 +4549,7 @@
       <c r="A158" s="4" t="n"/>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/wall-of-shame</t>
+          <t>/brewsoul/coffee/[id]</t>
         </is>
       </c>
       <c r="C158" s="13" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>content page. Real 13 entries (brand/category/evidence/severity/response) from SHAME_ENTRIES, unchanged. Category filter buttons extracted into components/brewsoul/shame-explorer.tsx (the only interactive piece) so the page itself stays a Server Component. Verified live: 200 OK.</t>
+          <t>coffee detail page (breadcrumb, QPR + tier header, quick stats, tasting notes, flavor-profile bars, the 4 intelligence scores, transparency/ethics data, buy links, competition wins, similar-coffees cross-links, journey CTAs), server-rendered with generateStaticParams over all 107 real coffees (this repo's bounded-dynamic-route convention, same as /blog/[slug]) instead of legacy's client-side useParams lookup. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E158" s="14" t="inlineStr">
@@ -4572,7 +4572,7 @@
       <c r="A159" s="4" t="n"/>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/follow-the-dollar</t>
+          <t>/brewsoul/quiz</t>
         </is>
       </c>
       <c r="C159" s="13" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>supply-chain essay. Real DOLLAR_BREAKDOWNS segment bars (farmer/exporter/importer/roaster/retailer %, real commentary), unchanged. The farmer-segment bar's data-driven color (green/gold/red by threshold) is a small known set of variants — precomposed as 3 literal Tailwind classes rather than an inline style background, per this repo's dynamic-class rule; only the genuinely per-item width stays as style. Fully static, Server Component. Verified live: 200 OK.</t>
+          <t>matching quiz (built, not yet pushed — pending local review), along with the real data/engine foundation most of the rest of Phase 6 depends on. Ported lib/intelligence-engine/{types,scoring}.ts verbatim (generic scoring engine — QPR/availability/scarcity/wow/tier/freshness — reusable beyond BrewSoul) and the full coffee catalog (legacy's 3 files: brewsoul-coffees.ts + -expanded.ts + -expanded2.ts, merged at import time) → one lib/content/brewsoul-coffees.ts, extracted via tsx (not hand-typed — 107 real entries, ~6.5K lines). Caught a real stale count: legacy's own file header claimed "105" and its UI copy said "103", but the actual merged arrays contain 107 — this migration shows the live BREWSOUL_COFFEES.length everywhere instead of a repeated hardcoded number. Ported JourneyBar.tsx (components/brewsoul/journey-bar.tsx) — the fixed bottom "what's next" bar shown on every BrewSoul content page except the identity quiz — and retrofitted it onto /brewsoul/first-sip too (built before JourneyBar existed). Built components/brewsoul/brewsoul-quiz.tsx: real 7-question taste quiz scored against each coffee's real flavorProfile via the real scoring engine, ranking the full catalog by match. Legacy's useMarkVisited was renamed to markVisited (it's a plain localStorage write, not a hook — its old use-prefixed name tripped React's rules-of-hooks lint when called from inside a useEffect). Dropped the canvas WarmParticles decoration and the dead hero photo (same confirmed-404 Manus proxy,</t>
         </is>
       </c>
       <c r="E159" s="14" t="inlineStr">
@@ -4595,7 +4595,7 @@
       <c r="A160" s="4" t="n"/>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/farms</t>
+          <t>/brewsoul/wall-of-shame</t>
         </is>
       </c>
       <c r="C160" s="13" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>sourcing content ("Farm Passports"). Real FARMS entries (country/region/producer/altitude/story/varieties/certifications), unchanged. Fully static. Verified live: 200 OK.</t>
+          <t>content page. Real 13 entries (brand/category/evidence/severity/response) from SHAME_ENTRIES, unchanged. Category filter buttons extracted into components/brewsoul/shame-explorer.tsx (the only interactive piece) so the page itself stays a Server Component. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E160" s="14" t="inlineStr">
@@ -4618,7 +4618,7 @@
       <c r="A161" s="4" t="n"/>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/mold-free</t>
+          <t>/brewsoul/follow-the-dollar</t>
         </is>
       </c>
       <c r="C161" s="13" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>mycotoxin content. Real verified/claims/untested split computed live over the full BREWSOUL_COFFEES catalog by moldTestStatus. Fully static. Verified live: 200 OK.</t>
+          <t>supply-chain essay. Real DOLLAR_BREAKDOWNS segment bars (farmer/exporter/importer/roaster/retailer %, real commentary), unchanged. The farmer-segment bar's data-driven color (green/gold/red by threshold) is a small known set of variants — precomposed as 3 literal Tailwind classes rather than an inline style background, per this repo's dynamic-class rule; only the genuinely per-item width stays as style. Fully static, Server Component. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E161" s="14" t="inlineStr">
@@ -4641,7 +4641,7 @@
       <c r="A162" s="4" t="n"/>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/experiences</t>
+          <t>/brewsoul/farms</t>
         </is>
       </c>
       <c r="C162" s="13" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>experiential content ("Experience Map"). Real EXPERIENCES entries (farm tours, cafés, cupping labs, roastery visits), unchanged. Country filter buttons extracted into components/brewsoul/experiences-explorer.tsx, same split-out-the-interactive-bit pattern as wall-of-shame. Verified live: 200 OK.</t>
+          <t>sourcing content ("Farm Passports"). Real FARMS entries (country/region/producer/altitude/story/varieties/certifications), unchanged. Fully static. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E162" s="14" t="inlineStr">
@@ -4664,7 +4664,7 @@
       <c r="A163" s="4" t="n"/>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/health</t>
+          <t>/brewsoul/mold-free</t>
         </is>
       </c>
       <c r="C163" s="13" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>health deep-dive, ported from BrewSoulHealthFull.tsx (the file legacy's own router actually uses for this route — BrewSoulContent.tsx's same-named BrewSoulHealth export is real but genuinely dead/unrouted code in legacy, shadowed by this one). Real 8 longevity findings with real citations/participant counts, 7 real risks with severity ratings, CYP1A2 caffeine-metabolism genetics, a 6-step chronobiology timing schedule, 8 real bioactive compounds, 3 real mycotoxin threats, and a 3-step "simplification protocol," all ported unchanged and verbatim. Dead Manus hero image dropped for a CSS gradient. Legacy's own redundant BrewSoulLayout wrapper dropped — app/brewsoul/layout.tsx already wraps every route. The two real interactive pieces (show-all-risks toggle, per-compound click-to-expand) split into components/brewsoul/health-{risks,compounds}.tsx client islands so the rest stays a Server Component. Legacy's bespoke earthy "science" palette (soil/clay/sage/moss — distinct from the rest of BrewSoul's amber/gold commercial palette) kept as a deliberate one-off sub-identity for this one page, same reasoning as /attention-theft's own "crusade" palette elsewhere in this migration. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>mycotoxin content. Real verified/claims/untested split computed live over the full BREWSOUL_COFFEES catalog by moldTestStatus. Fully static. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E163" s="14" t="inlineStr">
@@ -4687,7 +4687,7 @@
       <c r="A164" s="4" t="n"/>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/varieties</t>
+          <t>/brewsoul/experiences</t>
         </is>
       </c>
       <c r="C164" s="13" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>reference: varieties. Real VARIETIES encyclopedia entries (species/origin/genetics/cup profile/yield/disease resistance), unchanged. Search extracted into components/brewsoul/varieties-explorer.tsx. Verified live: 200 OK.</t>
+          <t>experiential content ("Experience Map"). Real EXPERIENCES entries (farm tours, cafés, cupping labs, roastery visits), unchanged. Country filter buttons extracted into components/brewsoul/experiences-explorer.tsx, same split-out-the-interactive-bit pattern as wall-of-shame. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E164" s="14" t="inlineStr">
@@ -4710,7 +4710,7 @@
       <c r="A165" s="4" t="n"/>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/processing</t>
+          <t>/brewsoul/health</t>
         </is>
       </c>
       <c r="C165" s="13" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>reference: processing. Real PROCESSING_METHODS entries (description/flavor impact/complexity/controversy), unchanged. Fully static. Verified live: 200 OK.</t>
+          <t>health deep-dive, ported from BrewSoulHealthFull.tsx (the file legacy's own router actually uses for this route — BrewSoulContent.tsx's same-named BrewSoulHealth export is real but genuinely dead/unrouted code in legacy, shadowed by this one). Real 8 longevity findings with real citations/participant counts, 7 real risks with severity ratings, CYP1A2 caffeine-metabolism genetics, a 6-step chronobiology timing schedule, 8 real bioactive compounds, 3 real mycotoxin threats, and a 3-step "simplification protocol," all ported unchanged and verbatim. Dead Manus hero image dropped for a CSS gradient. Legacy's own redundant BrewSoulLayout wrapper dropped — app/brewsoul/layout.tsx already wraps every route. The two real interactive pieces (show-all-risks toggle, per-compound click-to-expand) split into components/brewsoul/health-{risks,compounds}.tsx client islands so the rest stays a Server Component. Legacy's bespoke earthy "science" palette (soil/clay/sage/moss — distinct from the rest of BrewSoul's amber/gold commercial palette) kept as a deliberate one-off sub-identity for this one page, same reasoning as /attention-theft's own "crusade" palette elsewhere in this migration. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E165" s="14" t="inlineStr">
@@ -4733,7 +4733,7 @@
       <c r="A166" s="4" t="n"/>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/roasters</t>
+          <t>/brewsoul/varieties</t>
         </is>
       </c>
       <c r="C166" s="13" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>reference: roaster directory. Real ROASTERS entries (philosophy/quality/transparency/farmer-equity scores), unchanged. Search + tier filter extracted into components/brewsoul/roasters-explorer.tsx. Verified live: 200 OK.</t>
+          <t>reference: varieties. Real VARIETIES encyclopedia entries (species/origin/genetics/cup profile/yield/disease resistance), unchanged. Search extracted into components/brewsoul/varieties-explorer.tsx. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E166" s="14" t="inlineStr">
@@ -4756,7 +4756,7 @@
       <c r="A167" s="4" t="n"/>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/glossary</t>
+          <t>/brewsoul/processing</t>
         </is>
       </c>
       <c r="C167" s="13" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>reference: glossary. Real GLOSSARY terms, unchanged. Search + alphabetical grouping extracted into components/brewsoul/glossary-explorer.tsx. Verified live: 200 OK.</t>
+          <t>reference: processing. Real PROCESSING_METHODS entries (description/flavor impact/complexity/controversy), unchanged. Fully static. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E167" s="14" t="inlineStr">
@@ -4779,7 +4779,7 @@
       <c r="A168" s="4" t="n"/>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/pairings</t>
+          <t>/brewsoul/roasters</t>
         </is>
       </c>
       <c r="C168" s="13" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>reference: pairings. Real PAIRINGS (food/drink pairings by origin) and 3 real curated FLIGHTS (each linking to real coffees in the catalog), unchanged. Fully static. Verified live: 200 OK.</t>
+          <t>reference: roaster directory. Real ROASTERS entries (philosophy/quality/transparency/farmer-equity scores), unchanged. Search + tier filter extracted into components/brewsoul/roasters-explorer.tsx. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr">
@@ -4802,7 +4802,7 @@
       <c r="A169" s="4" t="n"/>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/economics</t>
+          <t>/brewsoul/glossary</t>
         </is>
       </c>
       <c r="C169" s="13" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>reference: economics. Real live-computed stats (coffee/origin/roaster/variety counts, average price, average farmer share via DOLLAR_BREAKDOWNS), a real price-distribution histogram, and a real top-origins ranking — all computed directly from BREWSOUL_COFFEES at render time, unchanged. Fully static. Verified live: 200 OK.</t>
+          <t>reference: glossary. Real GLOSSARY terms, unchanged. Search + alphabetical grouping extracted into components/brewsoul/glossary-explorer.tsx. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E169" s="14" t="inlineStr">
@@ -4825,7 +4825,7 @@
       <c r="A170" s="4" t="n"/>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/compare</t>
+          <t>/brewsoul/pairings</t>
         </is>
       </c>
       <c r="C170" s="13" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>tool: compare coffees. Real side-by-side comparison of up to 4 coffees across origin/producer/variety/process/price/cupping and the 4 intelligence scores (QPR/availability/wow/overall), unchanged. Interactivity in components/brewsoul/compare-explorer.tsx. Verified live: 200 OK.</t>
+          <t>reference: pairings. Real PAIRINGS (food/drink pairings by origin) and 3 real curated FLIGHTS (each linking to real coffees in the catalog), unchanged. Fully static. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E170" s="14" t="inlineStr">
@@ -4848,7 +4848,7 @@
       <c r="A171" s="4" t="n"/>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/blend-builder</t>
+          <t>/brewsoul/economics</t>
         </is>
       </c>
       <c r="C171" s="13" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>tool: blend builder. Real combine-up-to-5-coffees ratio calculator with weighted-average QPR/Wow/Overall scores via range sliders, unchanged (never persisted anywhere in legacy either — a pure in-session calculator). Interactivity in components/brewsoul/blend-builder-explorer.tsx. Verified live: 200 OK.</t>
+          <t>reference: economics. Real live-computed stats (coffee/origin/roaster/variety counts, average price, average farmer share via DOLLAR_BREAKDOWNS), a real price-distribution histogram, and a real top-origins ranking — all computed directly from BREWSOUL_COFFEES at render time, unchanged. Fully static. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E171" s="14" t="inlineStr">
@@ -4871,7 +4871,7 @@
       <c r="A172" s="4" t="n"/>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/drops</t>
+          <t>/brewsoul/compare</t>
         </is>
       </c>
       <c r="C172" s="13" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>tool: product drops ("Latest Drops"). Real top-12-by-overall-score coffees. No client-side state at all (legacy's own useMemo had no changing dependencies — a pure derived list), so this ships as a plain Server Component. Verified live: 200 OK.</t>
+          <t>tool: compare coffees. Real side-by-side comparison of up to 4 coffees across origin/producer/variety/process/price/cupping and the 4 intelligence scores (QPR/availability/wow/overall), unchanged. Interactivity in components/brewsoul/compare-explorer.tsx. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E172" s="14" t="inlineStr">
@@ -4894,7 +4894,7 @@
       <c r="A173" s="4" t="n"/>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/collection</t>
+          <t>/brewsoul/blend-builder</t>
         </is>
       </c>
       <c r="C173" s="13" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>tool: personal collection tracker ("My Collection"). Real save/toggle-to-collection behavior, unchanged. Real bug found and fixed: legacy read localStorage directly inside a useState initializer — unsafe during SSR, same hydration-mismatch class already fixed in journey-bar.tsx/journey-tracker.tsx — rebuilt around a module-level external store fed through useSyncExternalStore in components/brewsoul/collection-explorer.tsx. Also found and fixed: the already-ported brewsoul-directory.ts listed this page's path as /brewsoul/my-coffees — a real dead link in legacy's own directory (legacy's actual router only ever served this at /brewsoul/collection, /brewsoul/my-coffees never existed) — corrected to the real path. Verified live: 200 OK.</t>
+          <t>tool: blend builder. Real combine-up-to-5-coffees ratio calculator with weighted-average QPR/Wow/Overall scores via range sliders, unchanged (never persisted anywhere in legacy either — a pure in-session calculator). Interactivity in components/brewsoul/blend-builder-explorer.tsx. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E173" s="14" t="inlineStr">
@@ -4917,7 +4917,7 @@
       <c r="A174" s="4" t="n"/>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/submit</t>
+          <t>/brewsoul/drops</t>
         </is>
       </c>
       <c r="C174" s="13" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>tool: submit a coffee ("Submit or Appeal"). Real submit-a-coffee / appeal-a-score form, unchanged in structure. Real bug found and fixed: legacy's own comment admitted "In production this would POST to a tRPC endpoint" but in the meantime wrote the submission to localStorage and showed "Received. We'll review your submission" regardless — actively misleading, since nobody would ever see a localStorage-only write. Replaced with a real mailto: fallback pre-filled with the form fields, same honest-degradation pattern as first-sip-email-capture.tsx — no fake success state. Verified live: 200 OK.</t>
+          <t>tool: product drops ("Latest Drops"). Real top-12-by-overall-score coffees. No client-side state at all (legacy's own useMemo had no changing dependencies — a pure derived list), so this ships as a plain Server Component. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E174" s="14" t="inlineStr">
@@ -4940,7 +4940,7 @@
       <c r="A175" s="4" t="n"/>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/prescription</t>
+          <t>/brewsoul/collection</t>
         </is>
       </c>
       <c r="C175" s="13" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>personalized "prescription", ported from BrewSoulPrescriptionFull.tsx (the file legacy's router actually uses — BrewSoulTools.tsx's same-named export is dead/unrouted, same shadowed-file trap as /brewsoul/health). Real 5-step questionnaire (genetics/timing/health/flavor/budget) generating a real, deterministic prescription (generatePrescription — real roast/cup-count/brand/pricing/warning logic), all ported unchanged and verbatim. Legacy's trpc.coffeePrescription.generate AI-enhancement mutation doesn't exist in this migration — dropped along with its "AI ANALYSIS LOADING..." block, which would otherwise spin forever and never resolve; the real prescription itself never depended on that call, it's already fully computed client-side. Same bespoke earthy "science" palette as /brewsoul/health kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>tool: personal collection tracker ("My Collection"). Real save/toggle-to-collection behavior, unchanged. Real bug found and fixed: legacy read localStorage directly inside a useState initializer — unsafe during SSR, same hydration-mismatch class already fixed in journey-bar.tsx/journey-tracker.tsx — rebuilt around a module-level external store fed through useSyncExternalStore in components/brewsoul/collection-explorer.tsx. Also found and fixed: the already-ported brewsoul-directory.ts listed this page's path as /brewsoul/my-coffees — a real dead link in legacy's own directory (legacy's actual router only ever served this at /brewsoul/collection, /brewsoul/my-coffees never existed) — corrected to the real path. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E175" s="14" t="inlineStr">
@@ -4963,7 +4963,7 @@
       <c r="A176" s="4" t="n"/>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/chains</t>
+          <t>/brewsoul/submit</t>
         </is>
       </c>
       <c r="C176" s="13" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>"Top 100 Coffee Chains" ranking (not supply-chain visualization — that's /brewsoul/economics//brewsoul/follow-the-dollar; this is chain rankings). Real 100-chain dataset extracted from legacy's computed CHAIN_RANKINGS export (5 real weighted dimensions → aggregate → S-F tier) via a one-off tsx script (same approach as brewsoul-coffees.ts) into lib/content/brewsoul-chains.ts, with a new ChainEntry type added to intelligence-engine/types.ts. Real tier/type filters, search, and per-chain expand, unchanged, extracted into components/brewsoul/chains-explorer.tsx. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>tool: submit a coffee ("Submit or Appeal"). Real submit-a-coffee / appeal-a-score form, unchanged in structure. Real bug found and fixed: legacy's own comment admitted "In production this would POST to a tRPC endpoint" but in the meantime wrote the submission to localStorage and showed "Received. We'll review your submission" regardless — actively misleading, since nobody would ever see a localStorage-only write. Replaced with a real mailto: fallback pre-filled with the form fields, same honest-degradation pattern as first-sip-email-capture.tsx — no fake success state. Verified live: 200 OK.</t>
         </is>
       </c>
       <c r="E176" s="14" t="inlineStr">
@@ -4986,7 +4986,7 @@
       <c r="A177" s="4" t="n"/>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/biodynamic</t>
+          <t>/brewsoul/prescription</t>
         </is>
       </c>
       <c r="C177" s="13" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>biodynamic content. The complete real census of Demeter-certified biodynamic coffee: 3 real source farms, 6 real roasters/brands with real product tables and pricing, real nutritional-science compounds, a real cost calculator, and a real impact/tokenization section, all ported unchanged and verbatim. Dead Manus hero image dropped for a CSS gradient. The 3 genuinely interactive pieces (click-to-expand farms/roasters, cups-per-day cost slider) split into components/brewsoul/{biodynamic-farms,biodynamic-roasters,cost-calculator}.tsx client islands so the rest stays a Server Component. Same bespoke earthy "science" palette as /brewsoul/health and /brewsoul/prescription kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>personalized "prescription", ported from BrewSoulPrescriptionFull.tsx (the file legacy's router actually uses — BrewSoulTools.tsx's same-named export is dead/unrouted, same shadowed-file trap as /brewsoul/health). Real 5-step questionnaire (genetics/timing/health/flavor/budget) generating a real, deterministic prescription (generatePrescription — real roast/cup-count/brand/pricing/warning logic), all ported unchanged and verbatim. Legacy's trpc.coffeePrescription.generate AI-enhancement mutation doesn't exist in this migration — dropped along with its "AI ANALYSIS LOADING..." block, which would otherwise spin forever and never resolve; the real prescription itself never depended on that call, it's already fully computed client-side. Same bespoke earthy "science" palette as /brewsoul/health kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E177" s="14" t="inlineStr">
@@ -5009,7 +5009,7 @@
       <c r="A178" s="4" t="n"/>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/decaf</t>
+          <t>/brewsoul/chains</t>
         </is>
       </c>
       <c r="C178" s="13" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>decaf content ("Paint Stripper or Pure Water?"). Real 3-process breakdown (methylene chloride/Swiss Water/supercritical CO₂), 13 real clean-decaf brands ("Hall of Fame"), 10 real methylene-chloride brands ("Wall of Shame," with real Clean Label Project lawsuit citations), a real carbon footprint comparison, real decaf health science, and a real price-comparison table, all ported unchanged and verbatim. Legacy's manual document.title/&lt;meta keywords&gt; mutation in a useEffect (a real anti-pattern — Next's generateMetadata already owns the head) dropped for the real metadata export. Real bug found and fixed: the 13-brand FAME dataset was initially exported from the "use client" decaf-fame.tsx component file and imported into the Server Component page for its price-comparison table — non-component exports from a client module aren't available across the RSC boundary, which threw FAME is not iterable at runtime (only caught by live verification, not typecheck/lint). Moved the data to a plain lib/content/brewsoul-decaf.ts module instead. The 2 genuinely interactive pieces (click-to-expand Hall of Fame, reveal-toggle Wall of Shame) split into components/brewsoul/decaf-{fame,shame}.tsx client islands. Same bespoke earthy "science" palette as the other /brewsoul deep-dive pages kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>"Top 100 Coffee Chains" ranking (not supply-chain visualization — that's /brewsoul/economics//brewsoul/follow-the-dollar; this is chain rankings). Real 100-chain dataset extracted from legacy's computed CHAIN_RANKINGS export (5 real weighted dimensions → aggregate → S-F tier) via a one-off tsx script (same approach as brewsoul-coffees.ts) into lib/content/brewsoul-chains.ts, with a new ChainEntry type added to intelligence-engine/types.ts. Real tier/type filters, search, and per-chain expand, unchanged, extracted into components/brewsoul/chains-explorer.tsx. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E178" s="14" t="inlineStr">
@@ -5032,7 +5032,7 @@
       <c r="A179" s="4" t="n"/>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/esoteric</t>
+          <t>/brewsoul/biodynamic</t>
         </is>
       </c>
       <c r="C179" s="13" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>rare-coffee content ("Esoteric Coffee Index"). Real 9-coffee index across 2 tiers (Panama Geisha, Yemen Mokha, Liberica, Eugenioides, Wush Wush, Sidra, Pink Bourbon, Bourbon Aji, Sudan Rume) with real tasting notes, rarity scores, and real named buy sources, plus a real acquisition-priority list and explorer scorecard, all ported unchanged and verbatim. Real content gap found, not fixed: legacy's own "Top 10 Acquisition Priority" list and scorecard table both reference "Laurina" as a 10th entry, but no coffee card for it exists anywhere in the source dataset — ported as-is rather than inventing card content that was never written. Zero client-side state anywhere in this page (only CSS-able hover) — ships entirely as a Server Component. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>biodynamic content. The complete real census of Demeter-certified biodynamic coffee: 3 real source farms, 6 real roasters/brands with real product tables and pricing, real nutritional-science compounds, a real cost calculator, and a real impact/tokenization section, all ported unchanged and verbatim. Dead Manus hero image dropped for a CSS gradient. The 3 genuinely interactive pieces (click-to-expand farms/roasters, cups-per-day cost slider) split into components/brewsoul/{biodynamic-farms,biodynamic-roasters,cost-calculator}.tsx client islands so the rest stays a Server Component. Same bespoke earthy "science" palette as /brewsoul/health and /brewsoul/prescription kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E179" s="14" t="inlineStr">
@@ -5055,7 +5055,7 @@
       <c r="A180" s="4" t="n"/>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/cities + /brewsoul/cities/[slug]</t>
+          <t>/brewsoul/decaf</t>
         </is>
       </c>
       <c r="C180" s="13" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>city directory + detail ("City Intelligence Module"). Real 25-city leaderboard (name/state/grade/score/tagline/verdict/live stats), a real 7-dimension scoring methodology, and real national + universal/nuanced chain report cards, all ported unchanged and verbatim into lib/content/brewsoul-cities.ts. Real data-completeness note, not a bug: legacy's own comment admits only Portland has full shop-by-shop data (25 real best + 5 real worst shops with real blurbs/scores/order-this/skip-this) — the other 24 cities have real city-level stats but empty shop/chain/bridge-drink/non-coffee arrays; legacy's own UI already handles this honestly (a real "Full data coming soon" state on both the card and detail page, not fake data) — preserved exactly, verified for both Portland (full tabs) and Seattle (coming-soon state). Grade filter, methodology modal, and chain-toggle interactivity in components/brewsoul/cities-explorer.tsx; per-city tab switching and per-shop expand in components/brewsoul/city-detail-tabs.tsx. Detail route uses generateStaticParams over all 25 real slugs. Scroll-linked parallax and floating-particle backgrounds dropped, same decoration call made throughout this migration. Real image-hosting gap flagged, not silently worked around: the 25 city hero photos are real, live Unsplash URLs (not a dead Manus proxy) but aren't yet uploaded to Sanity per this repo's own image convention — added images.unsplash.com to next.config.ts's remotePatterns as an interim measure rather th</t>
+          <t>decaf content ("Paint Stripper or Pure Water?"). Real 3-process breakdown (methylene chloride/Swiss Water/supercritical CO₂), 13 real clean-decaf brands ("Hall of Fame"), 10 real methylene-chloride brands ("Wall of Shame," with real Clean Label Project lawsuit citations), a real carbon footprint comparison, real decaf health science, and a real price-comparison table, all ported unchanged and verbatim. Legacy's manual document.title/&lt;meta keywords&gt; mutation in a useEffect (a real anti-pattern — Next's generateMetadata already owns the head) dropped for the real metadata export. Real bug found and fixed: the 13-brand FAME dataset was initially exported from the "use client" decaf-fame.tsx component file and imported into the Server Component page for its price-comparison table — non-component exports from a client module aren't available across the RSC boundary, which threw FAME is not iterable at runtime (only caught by live verification, not typecheck/lint). Moved the data to a plain lib/content/brewsoul-decaf.ts module instead. The 2 genuinely interactive pieces (click-to-expand Hall of Fame, reveal-toggle Wall of Shame) split into components/brewsoul/decaf-{fame,shame}.tsx client islands. Same bespoke earthy "science" palette as the other /brewsoul deep-dive pages kept as the same deliberate sub-identity. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E180" s="14" t="inlineStr">
@@ -5078,7 +5078,7 @@
       <c r="A181" s="4" t="n"/>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/directory</t>
+          <t>/brewsoul/esoteric</t>
         </is>
       </c>
       <c r="C181" s="13" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>real master page index ("Everything Inside BrewSoul," not a roaster directory — that's /brewsoul/roasters). Real 6 categories with real page descriptions/icons, unchanged; the underlying data already lived in lib/content/brewsoul-directory.ts (built earlier this phase to power CategoryBadge) — this route is where it finally becomes a real browsable page. Category filter extracted into components/brewsoul/directory-explorer.tsx. Fixed the stale "Browse All 103 Coffees" label (real count is 107) by dropping the hardcoded number from the shared data module — benefits every other consumer of that module too. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>rare-coffee content ("Esoteric Coffee Index"). Real 9-coffee index across 2 tiers (Panama Geisha, Yemen Mokha, Liberica, Eugenioides, Wush Wush, Sidra, Pink Bourbon, Bourbon Aji, Sudan Rume) with real tasting notes, rarity scores, and real named buy sources, plus a real acquisition-priority list and explorer scorecard, all ported unchanged and verbatim. Real content gap found, not fixed: legacy's own "Top 10 Acquisition Priority" list and scorecard table both reference "Laurina" as a 10th entry, but no coffee card for it exists anywhere in the source dataset — ported as-is rather than inventing card content that was never written. Zero client-side state anywhere in this page (only CSS-able hover) — ships entirely as a Server Component. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E181" s="14" t="inlineStr">
@@ -5101,7 +5101,7 @@
       <c r="A182" s="4" t="n"/>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>/brewsoul/guest + /brewsoul/guest/shanita-nicholas</t>
+          <t>/brewsoul/cities + /brewsoul/cities/[slug]</t>
         </is>
       </c>
       <c r="C182" s="13" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>guest series index + profile ("Tony G Guest Series"). Real single guest entry (Shanita Nicholas — real headline/teaser/tags) on the index, and the real 10-question interview on the detail page (Fair Trade economics, roasting mythology, the C Market, regenerative vs. sustainable, origin-roasting economics vs. Fair Trade, blockchain traceability, pre-harvest financing — real substantive answers with real citations), all ported unchanged and verbatim into components/brewsoul/shanita-interview.tsx. Legacy's guest photo (/api/img/brewsoul-orig_84eb4bc9.jpg) was the same dead Manus proxy confirmed 404 throughout this migration — dropped for a plain initial avatar on both pages rather than a broken headshot. Per-question expand/collapse, "Expand/Collapse All," and the real Twitter/LinkedIn/copy-link share row are genuinely interactive, split into client islands. Verified live: 200 OK on both, typecheck/lint clean.</t>
+          <t>city directory + detail ("City Intelligence Module"). Real 25-city leaderboard (name/state/grade/score/tagline/verdict/live stats), a real 7-dimension scoring methodology, and real national + universal/nuanced chain report cards, all ported unchanged and verbatim into lib/content/brewsoul-cities.ts. Real data-completeness note, not a bug: legacy's own comment admits only Portland has full shop-by-shop data (25 real best + 5 real worst shops with real blurbs/scores/order-this/skip-this) — the other 24 cities have real city-level stats but empty shop/chain/bridge-drink/non-coffee arrays; legacy's own UI already handles this honestly (a real "Full data coming soon" state on both the card and detail page, not fake data) — preserved exactly, verified for both Portland (full tabs) and Seattle (coming-soon state). Grade filter, methodology modal, and chain-toggle interactivity in components/brewsoul/cities-explorer.tsx; per-city tab switching and per-shop expand in components/brewsoul/city-detail-tabs.tsx. Detail route uses generateStaticParams over all 25 real slugs. Scroll-linked parallax and floating-particle backgrounds dropped, same decoration call made throughout this migration. Real image-hosting gap flagged, not silently worked around: the 25 city hero photos are real, live Unsplash URLs (not a dead Manus proxy) but aren't yet uploaded to Sanity per this repo's own image convention — added images.unsplash.com to next.config.ts's remotePatterns as an interim measure rather th</t>
         </is>
       </c>
       <c r="E182" s="14" t="inlineStr">
@@ -5124,7 +5124,7 @@
       <c r="A183" s="4" t="n"/>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Shared: port BrewSoulLayout, CategoryBadge, JourneyBar, NextSteps as Next.js layout/components</t>
+          <t>/brewsoul/directory</t>
         </is>
       </c>
       <c r="C183" s="13" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>app/brewsoul/layout.tsx + components/brewsoul/{brewsoul-nav,category-badge,journey-bar,next-steps}.tsx, all built and reused by every /brewsoul/* route above.</t>
+          <t>real master page index ("Everything Inside BrewSoul," not a roaster directory — that's /brewsoul/roasters). Real 6 categories with real page descriptions/icons, unchanged; the underlying data already lived in lib/content/brewsoul-directory.ts (built earlier this phase to power CategoryBadge) — this route is where it finally becomes a real browsable page. Category filter extracted into components/brewsoul/directory-explorer.tsx. Fixed the stale "Browse All 103 Coffees" label (real count is 107) by dropping the hardcoded number from the shared data module — benefits every other consumer of that module too. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E183" s="14" t="inlineStr">
@@ -5144,20 +5144,33 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="10" t="inlineStr">
-        <is>
-          <t>Phase 7 — PRI &amp; Kava Encyclopedias (19 routes)</t>
-        </is>
-      </c>
-      <c r="B184" s="11" t="n"/>
-      <c r="C184" s="11" t="n"/>
-      <c r="D184" s="12" t="n"/>
+      <c r="A184" s="4" t="n"/>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>/brewsoul/guest + /brewsoul/guest/shanita-nicholas</t>
+        </is>
+      </c>
+      <c r="C184" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>guest series index + profile ("Tony G Guest Series"). Real single guest entry (Shanita Nicholas — real headline/teaser/tags) on the index, and the real 10-question interview on the detail page (Fair Trade economics, roasting mythology, the C Market, regenerative vs. sustainable, origin-roasting economics vs. Fair Trade, blockchain traceability, pre-harvest financing — real substantive answers with real citations), all ported unchanged and verbatim into components/brewsoul/shanita-interview.tsx. Legacy's guest photo (/api/img/brewsoul-orig_84eb4bc9.jpg) was the same dead Manus proxy confirmed 404 throughout this migration — dropped for a plain initial avatar on both pages rather than a broken headshot. Per-question expand/collapse, "Expand/Collapse All," and the real Twitter/LinkedIn/copy-link share row are genuinely interactive, split into client islands. Verified live: 200 OK on both, typecheck/lint clean.</t>
+        </is>
+      </c>
+      <c r="E184" s="14" t="inlineStr">
+        <is>
+          <t>Phase 6 — BrewSoul (28 routes)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n"/>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Kava shared foundation</t>
+          <t>Shared: port BrewSoulLayout, CategoryBadge, JourneyBar, NextSteps as Next.js layout/components</t>
         </is>
       </c>
       <c r="C185" s="13" t="inlineStr">
@@ -5167,43 +5180,30 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>app/kava/layout.tsx + components/kava/kava-nav.tsx (KavaNav/KavaFooter, 10 real nav items) + components/kava/kava-ui.tsx (KavaHero/KavaSection/KavaSectionTitle/KavaCard/KavaBadge/KavaDivider/KavaDisclaimer, converted from legacy inline style={} to Tailwind + new --kava-* tokens in globals.css). Added /kava to site-chrome.tsx's SUPPRESSED_PREFIXES (self-contained sub-site, same pattern as BrewSoul and /attention-theft). Real dead link fixed: legacy nav pointed at /pri, which legacy's own App.tsx never routed (only /psychedelic-readiness-index exists) — corrected.</t>
+          <t>app/brewsoul/layout.tsx + components/brewsoul/{brewsoul-nav,category-badge,journey-bar,next-steps}.tsx, all built and reused by every /brewsoul/* route above.</t>
         </is>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
+          <t>Phase 6 — BrewSoul (28 routes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="10" t="inlineStr">
+        <is>
           <t>Phase 7 — PRI &amp; Kava Encyclopedias (19 routes)</t>
         </is>
       </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="4" t="n"/>
-      <c r="B186" s="4" t="inlineStr">
-        <is>
-          <t>/kava (home)</t>
-        </is>
-      </c>
-      <c r="C186" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D186" s="4" t="inlineStr">
-        <is>
-          <t>9 module cards, "Threshold Doctrine," "Sacred Masculine Triad" (Mezcal/Kava/Peyote), 4 market stats, all ported unchanged. Verified live: 200 OK, exactly 1 header/1 footer (chrome suppression confirmed), typecheck/lint clean.</t>
-        </is>
-      </c>
-      <c r="E186" s="14" t="inlineStr">
-        <is>
-          <t>Phase 7 — PRI &amp; Kava Encyclopedias (19 routes)</t>
-        </is>
-      </c>
+      <c r="B186" s="11" t="n"/>
+      <c r="C186" s="11" t="n"/>
+      <c r="D186" s="12" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n"/>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>/kava/origins</t>
+          <t>Kava shared foundation</t>
         </is>
       </c>
       <c r="C187" s="13" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>real migration timeline (6 Pacific nations, ~3000 BCE–1000 CE), real 6-island selector (Vanuatu/Fiji/Tonga/Samoa/Hawaii/Pohnpei, each with real facts/ceremony/cultivar/safety content), and the real Noble vs. Tudei safety comparison, all ported unchanged and verbatim. Island-selector interactivity in components/kava/origins-explorer.tsx. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>app/kava/layout.tsx + components/kava/kava-nav.tsx (KavaNav/KavaFooter, 10 real nav items) + components/kava/kava-ui.tsx (KavaHero/KavaSection/KavaSectionTitle/KavaCard/KavaBadge/KavaDivider/KavaDisclaimer, converted from legacy inline style={} to Tailwind + new --kava-* tokens in globals.css). Added /kava to site-chrome.tsx's SUPPRESSED_PREFIXES (self-contained sub-site, same pattern as BrewSoul and /attention-theft). Real dead link fixed: legacy nav pointed at /pri, which legacy's own App.tsx never routed (only /psychedelic-readiness-index exists) — corrected.</t>
         </is>
       </c>
       <c r="E187" s="14" t="inlineStr">
@@ -5226,7 +5226,7 @@
       <c r="A188" s="4" t="n"/>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>/kava/interactions</t>
+          <t>/kava (home)</t>
         </is>
       </c>
       <c r="C188" s="13" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>real 24-substance drug interaction database (real severity ratings across an 11-value scale, real pharmacological mechanisms, real PRI protocol guidance) and real 5-enzyme CYP450 inhibition profile, ported unchanged and verbatim. Search + severity-filter interactivity in components/kava/interactions-explorer.tsx, using a precomposed SEVERITY_CONFIG class lookup (not string-built classes — same Tailwind static-scanner rule enforced elsewhere this migration). Legacy's unused Download icon import (dead code, no export feature attached to it) not ported. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>9 module cards, "Threshold Doctrine," "Sacred Masculine Triad" (Mezcal/Kava/Peyote), 4 market stats, all ported unchanged. Verified live: 200 OK, exactly 1 header/1 footer (chrome suppression confirmed), typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E188" s="14" t="inlineStr">
@@ -5249,7 +5249,7 @@
       <c r="A189" s="4" t="n"/>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>/kava/science</t>
+          <t>/kava/origins</t>
         </is>
       </c>
       <c r="C189" s="13" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>real 6 major kavalactones (real receptor mechanisms, real PRI relevance) and real 11-item combined pharmacological profile, ported unchanged into lib/content/kava-science.ts. RSC-boundary bug caught proactively before shipping: initially drafted KAVALACTONES as an export of the "use client" chemotype-decoder.tsx, which would have thrown the same TypeError: X is not iterable already hit once this migration on /brewsoul/decaf when the Server Component page tried to import it — moved to the plain data module before ever running it. Chemotype decoder tool (enter e.g. 4-2-6-5-3-1, see dominant kavalactones) kept as the real interactive client island. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>real migration timeline (6 Pacific nations, ~3000 BCE–1000 CE), real 6-island selector (Vanuatu/Fiji/Tonga/Samoa/Hawaii/Pohnpei, each with real facts/ceremony/cultivar/safety content), and the real Noble vs. Tudei safety comparison, all ported unchanged and verbatim. Island-selector interactivity in components/kava/origins-explorer.tsx. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E189" s="14" t="inlineStr">
@@ -5272,7 +5272,7 @@
       <c r="A190" s="4" t="n"/>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>/kava/assessment</t>
+          <t>/kava/interactions</t>
         </is>
       </c>
       <c r="C190" s="13" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>real 5-domain, 20-question PRI readiness assessment (somatic/psychological/relational/cultural/integration), real per-domain point weights, and real 4-band recommendation scoring (CLEARED/CONDITIONAL/DEFER/NOT READY), all ported unchanged into components/kava/assessment-quiz.tsx. Fully stateful (domain navigation, per-question answers, results view), so kept as a single client island per this migration's established pattern for multi-step assessments. Domain and recommendation accent colors (5 + 4 distinct hexes, none matching the --kava-* brand palette) precomposed into literal DOMAIN_STYLES/RECOMMENDATION_STYLES lookup objects rather than style={}, avoiding the dynamic-class bug already caught twice this migration (chains-explorer.tsx, biodynamic/page.tsx). Real backend gap, handled honestly: legacy's AssessmentResultActions took sessionId/serialized-answers props feeding a trpc.assessments.submit mutation this migration never built — used the already-simplified, print-only AssessmentResultActions (components/assessments/result-actions.tsx, built during Phase 9) instead of reproducing a submit call with no backend. Verified live: 200 OK, real domain/question content confirmed in rendered HTML, typecheck/lint clean.</t>
+          <t>real 24-substance drug interaction database (real severity ratings across an 11-value scale, real pharmacological mechanisms, real PRI protocol guidance) and real 5-enzyme CYP450 inhibition profile, ported unchanged and verbatim. Search + severity-filter interactivity in components/kava/interactions-explorer.tsx, using a precomposed SEVERITY_CONFIG class lookup (not string-built classes — same Tailwind static-scanner rule enforced elsewhere this migration). Legacy's unused Download icon import (dead code, no export feature attached to it) not ported. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E190" s="14" t="inlineStr">
@@ -5295,7 +5295,7 @@
       <c r="A191" s="4" t="n"/>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>/kava/hawaii</t>
+          <t>/kava/science</t>
         </is>
       </c>
       <c r="C191" s="13" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>real ICE/meth crisis statistics (Quest Diagnostics 410% figure, Hawaii DOH conviction rates, law enforcement seizure data), real dual crisis/revival timeline (1985–present), the real (explicitly-labeled hypothesis, not proven) pharmacological alignment table, and real recovery resource listings, all ported unchanged and verbatim. Fully static, no client island needed. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>real 6 major kavalactones (real receptor mechanisms, real PRI relevance) and real 11-item combined pharmacological profile, ported unchanged into lib/content/kava-science.ts. RSC-boundary bug caught proactively before shipping: initially drafted KAVALACTONES as an export of the "use client" chemotype-decoder.tsx, which would have thrown the same TypeError: X is not iterable already hit once this migration on /brewsoul/decaf when the Server Component page tried to import it — moved to the plain data module before ever running it. Chemotype decoder tool (enter e.g. 4-2-6-5-3-1, see dominant kavalactones) kept as the real interactive client island. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E191" s="14" t="inlineStr">
@@ -5318,7 +5318,7 @@
       <c r="A192" s="4" t="n"/>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>/kava/myths</t>
+          <t>/kava/assessment</t>
         </is>
       </c>
       <c r="C192" s="13" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>real 7-myth evidence review (2002/2014 European kava ban and reversal, WHO findings, CYP2D6 metabolism differences by population, chemotype/preparation distinctions) and the real closing takeaway, ported unchanged. Expand/collapse interactivity in components/kava/myths-explorer.tsx, verdict colors (3-value enum) precomposed into a literal VERDICT_CLASS lookup. Extended shared KavaCard (kava-ui.tsx) with an optional onClick prop to support this — first Kava page needing a clickable card. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>real 5-domain, 20-question PRI readiness assessment (somatic/psychological/relational/cultural/integration), real per-domain point weights, and real 4-band recommendation scoring (CLEARED/CONDITIONAL/DEFER/NOT READY), all ported unchanged into components/kava/assessment-quiz.tsx. Fully stateful (domain navigation, per-question answers, results view), so kept as a single client island per this migration's established pattern for multi-step assessments. Domain and recommendation accent colors (5 + 4 distinct hexes, none matching the --kava-* brand palette) precomposed into literal DOMAIN_STYLES/RECOMMENDATION_STYLES lookup objects rather than style={}, avoiding the dynamic-class bug already caught twice this migration (chains-explorer.tsx, biodynamic/page.tsx). Real backend gap, handled honestly: legacy's AssessmentResultActions took sessionId/serialized-answers props feeding a trpc.assessments.submit mutation this migration never built — used the already-simplified, print-only AssessmentResultActions (components/assessments/result-actions.tsx, built during Phase 9) instead of reproducing a submit call with no backend. Verified live: 200 OK, real domain/question content confirmed in rendered HTML, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E192" s="14" t="inlineStr">
@@ -5341,7 +5341,7 @@
       <c r="A193" s="4" t="n"/>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>/kava/caffeine</t>
+          <t>/kava/hawaii</t>
         </is>
       </c>
       <c r="C193" s="13" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>real CYP1A2 inhibition mechanism (56%, the same pathway grapefruit juice uses on medications), real caffeine cutoff protocol, and the real kava-vs-coffee comparison table, ported unchanged. Fully static, no client island needed. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>real ICE/meth crisis statistics (Quest Diagnostics 410% figure, Hawaii DOH conviction rates, law enforcement seizure data), real dual crisis/revival timeline (1985–present), the real (explicitly-labeled hypothesis, not proven) pharmacological alignment table, and real recovery resource listings, all ported unchanged and verbatim. Fully static, no client island needed. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E193" s="14" t="inlineStr">
@@ -5364,7 +5364,7 @@
       <c r="A194" s="4" t="n"/>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>/kava/products</t>
+          <t>/kava/myths</t>
         </is>
       </c>
       <c r="C194" s="13" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>real 5-category product index (ceremonial powder, fresh frozen, RTD beverages, supplements, kava bars) with real named vendors/cultivars/chemotypes/pricing/PRI ratings and real outbound buy links (all live vendor domains, not Manus proxies — no image assets on this page to check), ported unchanged into components/kava/products-explorer.tsx. Category-tab interactivity kept as the client island. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>real 7-myth evidence review (2002/2014 European kava ban and reversal, WHO findings, CYP2D6 metabolism differences by population, chemotype/preparation distinctions) and the real closing takeaway, ported unchanged. Expand/collapse interactivity in components/kava/myths-explorer.tsx, verdict colors (3-value enum) precomposed into a literal VERDICT_CLASS lookup. Extended shared KavaCard (kava-ui.tsx) with an optional onClick prop to support this — first Kava page needing a clickable card. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E194" s="14" t="inlineStr">
@@ -5387,7 +5387,7 @@
       <c r="A195" s="4" t="n"/>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>/kava/certification</t>
+          <t>/kava/caffeine</t>
         </is>
       </c>
       <c r="C195" s="13" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>real 12-module, 80-hour facilitator curriculum, real 3-tier certification structure (Practitioner/Threshold Facilitator/Master Facilitator), and real prerequisites list, ported unchanged. Fully static, no client island needed; legacy's wouter cross-links replaced with next/link. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>real CYP1A2 inhibition mechanism (56%, the same pathway grapefruit juice uses on medications), real caffeine cutoff protocol, and the real kava-vs-coffee comparison table, ported unchanged. Fully static, no client island needed. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E195" s="14" t="inlineStr">
@@ -5410,7 +5410,7 @@
       <c r="A196" s="4" t="n"/>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>PRI shared data: lib/content/pri-data.ts (copied verbatim from legacy pri/data.ts</t>
+          <t>/kava/products</t>
         </is>
       </c>
       <c r="C196" s="13" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>real 39-medicine pharmacopoeia, 50+ questions across 6 domains, MAO-B interaction matrix, medication interaction guide, crisis/integration resources, pathway questions), lib/content/pri-safety-data.ts (verbatim safety data merge source), lib/content/pri-medicine-images.ts (verbatim real CloudFront hero-image map, all spot-checked 200 OK — RampRate's own CDN, already whitelisted, not Manus), lib/content/pri-shared.ts (the real scoring engine — computeScores/READINESS_LEVELS/getMedicineWithSafety — extracted to a plain module per the RSC-boundary lesson from /brewsoul/decaf and /kava/science). Added --pri-* CSS custom properties to globals.css (this subsystem's own purple/parchment/near-black palette, same pattern as --kava-/--crusade-) since Phase 7's PRI section spans 9 more routes.</t>
+          <t>real 5-category product index (ceremonial powder, fresh frozen, RTD beverages, supplements, kava bars) with real named vendors/cultivars/chemotypes/pricing/PRI ratings and real outbound buy links (all live vendor domains, not Manus proxies — no image assets on this page to check), ported unchanged into components/kava/products-explorer.tsx. Category-tab interactivity kept as the client island. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E196" s="14" t="inlineStr">
@@ -5433,7 +5433,7 @@
       <c r="A197" s="4" t="n"/>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>/psychedelic-readiness-index (core tool)</t>
+          <t>/kava/certification</t>
         </is>
       </c>
       <c r="C197" s="13" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>the real hero, 39-medicine grid with compare/save/bookmark tooling, MAO-B interaction matrix, medication interaction guide, crisis resources, the real 5-state assessment flow (philosophy intro → readiness quiz → pathway &amp; access questions → legal disclaimer gate → results), medicine detail modal (overview/safety/correction tabs), testimonials, and ImpactSoul cross-promotion, all ported unchanged and verbatim into components/pri/psychedelic-readiness-index.tsx plus supporting client islands (disclaimer-gate.tsx, medicine-modal.tsx, safety-section.tsx, correction-form.tsx, share-bar.tsx, cinematic-band.tsx). Kept as one client island — a single state machine drives which section renders, same call made for other large multi-step assessments this migration. Real hero/section photography (8 CloudFront images) kept via next/image; legacy's purely decorative glitch-scanline overlay divs and CSS shimmer/glow @keyframes dropped (no framer-motion — CONTRIBUTING.md rule 5 — and "decoration not worth the cost," same call made throughout this migration).</t>
+          <t>real 12-module, 80-hour facilitator curriculum, real 3-tier certification structure (Practitioner/Threshold Facilitator/Master Facilitator), and real prerequisites list, ported unchanged. Fully static, no client island needed; legacy's wouter cross-links replaced with next/link. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E197" s="14" t="inlineStr">
@@ -5456,7 +5456,7 @@
       <c r="A198" s="4" t="n"/>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>PRI: /peyote-mescaline</t>
+          <t>PRI shared data: lib/content/pri-data.ts (copied verbatim from legacy pri/data.ts</t>
         </is>
       </c>
       <c r="C198" s="13" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>MescalineDeepDive, real receptor pharmacology table, the real "Latuda Mirror" same-target-opposite-action comparison, real clinical outcomes (Agin-Liebes et al. 2021, n=452), the real 16-row pharma-to-plant alternatives table, real supplement protocol (pre/day-of/post-integration), real mescaline-specific PRI dimension scores, the real medicine-selector comparison table, and real sources, all ported unchanged and verbatim into lib/content/pri-mescaline-module.ts (copied verbatim) + app/peyote-mescaline/page.tsx. Fully static except the pharma-table expand toggle, extracted into components/pri/pharma-table.tsx; shared PriSection/PriEyebrow wrapper (components/pri/pri-section.tsx) introduced here for reuse by the remaining PRI deep-dive modules. All 8 real section photos (CloudFront) spot-checked live before use; legacy's purely decorative glitch-scanline overlays dropped. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
+          <t>real 39-medicine pharmacopoeia, 50+ questions across 6 domains, MAO-B interaction matrix, medication interaction guide, crisis/integration resources, pathway questions), lib/content/pri-safety-data.ts (verbatim safety data merge source), lib/content/pri-medicine-images.ts (verbatim real CloudFront hero-image map, all spot-checked 200 OK — RampRate's own CDN, already whitelisted, not Manus), lib/content/pri-shared.ts (the real scoring engine — computeScores/READINESS_LEVELS/getMedicineWithSafety — extracted to a plain module per the RSC-boundary lesson from /brewsoul/decaf and /kava/science). Added --pri-* CSS custom properties to globals.css (this subsystem's own purple/parchment/near-black palette, same pattern as --kava-/--crusade-) since Phase 7's PRI section spans 9 more routes.</t>
         </is>
       </c>
       <c r="E198" s="14" t="inlineStr">
@@ -5479,7 +5479,7 @@
       <c r="A199" s="4" t="n"/>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>PRI: /iboga-ibogaine</t>
+          <t>/psychedelic-readiness-index (core tool)</t>
         </is>
       </c>
       <c r="C199" s="13" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>IbogaDeepDive, "The Plant vs The Isolate": real alkaloid-profile comparison, real receptor pharmacology, real head-to-head iboga-vs-ibogaine table, real clinical outcomes (Mash/Noller/Schenberg/Brown &amp; Alper/Cherian/Williams — including the 2024 Stanford Nature Medicine SOF-veteran data and the 2026 19,071-patient safety analysis), real pharma-to-plant alternatives, real supplement protocol, real dimension thresholds, real medicine selector, Tony's real first-hand account of sitting ibogaine at The Mission Within, real hard-stop contraindications, a real 9-facility directory (with the 2 facilities legacy explicitly removed and why), real Nagoya Protocol / extractive-capitalism argument, real 2026 US legal-status rundown, the embedded Iboga Compass v2 documentation section (components/pri/iboga-compass-section.tsx, its own client island for the question-group toggles), and real sources — all ported unchanged and verbatim into lib/content/pri-iboga-module.ts + lib/content/pri-iboga-compass-data.ts (both copied verbatim) + app/iboga-ibogaine/page.tsx. Fully static except the pharma-table expand toggle (components/pri/iboga-pharma-table.tsx) and the compass section's toggles; reused the shared PriSection/PriEyebrow wrapper from the mescaline module. All 5 real hero/section photos (CloudFront) spot-checked live before use. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
+          <t>the real hero, 39-medicine grid with compare/save/bookmark tooling, MAO-B interaction matrix, medication interaction guide, crisis resources, the real 5-state assessment flow (philosophy intro → readiness quiz → pathway &amp; access questions → legal disclaimer gate → results), medicine detail modal (overview/safety/correction tabs), testimonials, and ImpactSoul cross-promotion, all ported unchanged and verbatim into components/pri/psychedelic-readiness-index.tsx plus supporting client islands (disclaimer-gate.tsx, medicine-modal.tsx, safety-section.tsx, correction-form.tsx, share-bar.tsx, cinematic-band.tsx). Kept as one client island — a single state machine drives which section renders, same call made for other large multi-step assessments this migration. Real hero/section photography (8 CloudFront images) kept via next/image; legacy's purely decorative glitch-scanline overlay divs and CSS shimmer/glow @keyframes dropped (no framer-motion — CONTRIBUTING.md rule 5 — and "decoration not worth the cost," same call made throughout this migration).</t>
         </is>
       </c>
       <c r="E199" s="14" t="inlineStr">
@@ -5502,7 +5502,7 @@
       <c r="A200" s="4" t="n"/>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>PRI: /iboga-compass</t>
+          <t>PRI: /peyote-mescaline</t>
         </is>
       </c>
       <c r="C200" s="13" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>IbogaCompassAssessment, the real interactive 28-question / 7-section compass (outcome/medical/approach/logistics/geography/personal/aftercare), the real drag-or-arrow priority-rank step (top dimension ×2.0, bottom ×0.5), the real facility-scoring engine, and the real results view (matched facilities with real "why this matched" reasoning and real elimination reasons), all ported unchanged and verbatim. lib/content/pri-iboga-compass-engine.ts (real scoring logic — weight deltas, hard filters, substance bonuses, priority-rank application, facility scoring) and lib/content/pri-iboga-facility-data.ts (real facility directory + substance-bonus data) both copied verbatim from legacy rather than hand-transcribed, given this is the actual matching algorithm — correctness matters more here than anywhere else in this migration. Uses this site's own brand-gold/foreground/muted-foreground design tokens rather than the pri-* palette — legacy's own hex here (#8B6914) is an exact match for brand-gold, confirming this one page always used the main site identity, not a PRI-specific one. Real backend gap handled honestly: legacy's lead-capture gate posted a rich structured payload (question-by-question answers, top facility matches, primary goal, budget range) to trpc.assessments.submit (no backend built for this migration) — replaced with a mailto: to Tony carrying the same structured summary, same pattern used throughout this migration; the meaningless "Submitting..." pending state and its e</t>
+          <t>MescalineDeepDive, real receptor pharmacology table, the real "Latuda Mirror" same-target-opposite-action comparison, real clinical outcomes (Agin-Liebes et al. 2021, n=452), the real 16-row pharma-to-plant alternatives table, real supplement protocol (pre/day-of/post-integration), real mescaline-specific PRI dimension scores, the real medicine-selector comparison table, and real sources, all ported unchanged and verbatim into lib/content/pri-mescaline-module.ts (copied verbatim) + app/peyote-mescaline/page.tsx. Fully static except the pharma-table expand toggle, extracted into components/pri/pharma-table.tsx; shared PriSection/PriEyebrow wrapper (components/pri/pri-section.tsx) introduced here for reuse by the remaining PRI deep-dive modules. All 8 real section photos (CloudFront) spot-checked live before use; legacy's purely decorative glitch-scanline overlays dropped. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E200" s="14" t="inlineStr">
@@ -5525,7 +5525,7 @@
       <c r="A201" s="4" t="n"/>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>PRI: /pri-calibration</t>
+          <t>PRI: /iboga-ibogaine</t>
         </is>
       </c>
       <c r="C201" s="13" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>forced-rank calibration study, the real Bradley-Terry pairwise-comparison model (all 15 unique pairs of the 6 PRI dimensions), the real drag-or-arrow full ranking step, real methodology copy (acquiescence-bias explanation, the 4 headline validation stats), and the real Monte Carlo validation metrics (lib/content/pri-efficacy-data.json, copied verbatim from legacy — also feeds /pri-efficacy below), all ported unchanged into components/pri/calibration-assessment.tsx. Real backend gap, handled honestly: legacy's "Contribute to Research?" opt-in phase posted to trpc.priCalibration.submit (no backend built for this migration), and the results view's "Community Data" section read a live trpc.priCalibration.stats aggregate query showing other users' scores — neither has an honest backend-free equivalent (a cross-user aggregate can't be faked locally, and a research opt-in toggle with nothing behind it would be dishonest UI, the same call already made dropping the main PRI results page's inert research-pool checkbox). Both dropped; the flow goes straight from ranking to results. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
+          <t>IbogaDeepDive, "The Plant vs The Isolate": real alkaloid-profile comparison, real receptor pharmacology, real head-to-head iboga-vs-ibogaine table, real clinical outcomes (Mash/Noller/Schenberg/Brown &amp; Alper/Cherian/Williams — including the 2024 Stanford Nature Medicine SOF-veteran data and the 2026 19,071-patient safety analysis), real pharma-to-plant alternatives, real supplement protocol, real dimension thresholds, real medicine selector, Tony's real first-hand account of sitting ibogaine at The Mission Within, real hard-stop contraindications, a real 9-facility directory (with the 2 facilities legacy explicitly removed and why), real Nagoya Protocol / extractive-capitalism argument, real 2026 US legal-status rundown, the embedded Iboga Compass v2 documentation section (components/pri/iboga-compass-section.tsx, its own client island for the question-group toggles), and real sources — all ported unchanged and verbatim into lib/content/pri-iboga-module.ts + lib/content/pri-iboga-compass-data.ts (both copied verbatim) + app/iboga-ibogaine/page.tsx. Fully static except the pharma-table expand toggle (components/pri/iboga-pharma-table.tsx) and the compass section's toggles; reused the shared PriSection/PriEyebrow wrapper from the mescaline module. All 5 real hero/section photos (CloudFront) spot-checked live before use. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E201" s="14" t="inlineStr">
@@ -5548,7 +5548,7 @@
       <c r="A202" s="4" t="n"/>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>PRI: /pri-efficacy</t>
+          <t>PRI: /iboga-compass</t>
         </is>
       </c>
       <c r="C202" s="13" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>psychometric validation dashboard, the real Monte Carlo simulation results (10,000 synthetic respondents), real classification-accuracy comparison, real dimension-priority distribution (the real first-dimension-inflation finding), real test-retest reliability and entropy metrics, and the real methodology writeup, all ported unchanged into app/pri-efficacy/page.tsx, reading the same lib/content/pri-efficacy-data.json also used by /pri-calibration. Real backend gap, handled honestly: legacy's "Live Calibrations" tab read a live trpc.priCalibration.stats query — since /pri-calibration's own submit call was already dropped (no backend, see that page's port note), this tab would permanently render "0 total calibrations, no data yet," a dead feature masquerading as a live one. Dropped entirely rather than ship a perpetually-empty tab; only the real, fully-populated Simulation view ships — which also means this page has no state left at all, so it's a plain Server Component now instead of a client one. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
+          <t>IbogaCompassAssessment, the real interactive 28-question / 7-section compass (outcome/medical/approach/logistics/geography/personal/aftercare), the real drag-or-arrow priority-rank step (top dimension ×2.0, bottom ×0.5), the real facility-scoring engine, and the real results view (matched facilities with real "why this matched" reasoning and real elimination reasons), all ported unchanged and verbatim. lib/content/pri-iboga-compass-engine.ts (real scoring logic — weight deltas, hard filters, substance bonuses, priority-rank application, facility scoring) and lib/content/pri-iboga-facility-data.ts (real facility directory + substance-bonus data) both copied verbatim from legacy rather than hand-transcribed, given this is the actual matching algorithm — correctness matters more here than anywhere else in this migration. Uses this site's own brand-gold/foreground/muted-foreground design tokens rather than the pri-* palette — legacy's own hex here (#8B6914) is an exact match for brand-gold, confirming this one page always used the main site identity, not a PRI-specific one. Real backend gap handled honestly: legacy's lead-capture gate posted a rich structured payload (question-by-question answers, top facility matches, primary goal, budget range) to trpc.assessments.submit (no backend built for this migration) — replaced with a mailto: to Tony carrying the same structured summary, same pattern used throughout this migration; the meaningless "Submitting..." pending state and its e</t>
         </is>
       </c>
       <c r="E202" s="14" t="inlineStr">
@@ -5571,7 +5571,7 @@
       <c r="A203" s="4" t="n"/>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>PRI: /pri-research Built 2026-10-06 behind the login: admins are the emails in ADMIN_EMAILS; everyone else gets live's "Access Denied"</t>
+          <t>PRI: /pri-calibration</t>
         </is>
       </c>
       <c r="C203" s="13" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Totals, anonymized opt-in table, admin-only CSV export (/pri-research/export). /pri-calibration regained legacy's "Contribute to Research?" step and now saves every calibration anonymously to pri_calibrations (opt-ins flagged). Was: — Deferred, not skipped (access-model question resolved by inspection). Read the real legacy source: this is a genuine admin-only dashboard (useAuth() gated to role === "admin") showing trpc.priCalibration.researchData — the same calibration-submission backend already confirmed absent and intentionally not built for /pri-calibration and /pri-efficacy (see their port notes). No admin-auth system exists anywhere in this Next.js migration yet either. So this isn't just an access-control decision — even fully wired up, the page would have zero real data to show, forever. Not worth building an admin dashboard against a backend this migration has twice already decided not to build. Added to "Explicitly deferred" below alongside the other admin dashboards; revisit only if/when both a real admin-auth system and a real calibration-submission backend exist.</t>
+          <t>forced-rank calibration study, the real Bradley-Terry pairwise-comparison model (all 15 unique pairs of the 6 PRI dimensions), the real drag-or-arrow full ranking step, real methodology copy (acquiescence-bias explanation, the 4 headline validation stats), and the real Monte Carlo validation metrics (lib/content/pri-efficacy-data.json, copied verbatim from legacy — also feeds /pri-efficacy below), all ported unchanged into components/pri/calibration-assessment.tsx. Real backend gap, handled honestly: legacy's "Contribute to Research?" opt-in phase posted to trpc.priCalibration.submit (no backend built for this migration), and the results view's "Community Data" section read a live trpc.priCalibration.stats aggregate query showing other users' scores — neither has an honest backend-free equivalent (a cross-user aggregate can't be faked locally, and a research opt-in toggle with nothing behind it would be dishonest UI, the same call already made dropping the main PRI results page's inert research-pool checkbox). Both dropped; the flow goes straight from ranking to results. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E203" s="14" t="inlineStr">
@@ -5594,7 +5594,7 @@
       <c r="A204" s="4" t="n"/>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>PRI: /facilitator-index</t>
+          <t>PRI: /pri-efficacy</t>
         </is>
       </c>
       <c r="C204" s="13" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>"The Facilitator Index: Know Who You Go With," the real 15-question quick-intake archetype quiz (real Bradley-Terry-style axis derivation, fully client-computed via deriveArchetype()), the real 108-item, 12-band (plus Band 0) practitioner self-assessment instrument, and the real methodology prose (rationale, code/tier system, data-handling policy, Reciprocity Gate, Corroboration token system), all ported unchanged and verbatim into lib/content/facilitator-index-data.ts (single authoritative content source) + components/facilitator/* + app/facilitator-index/page.tsx. Real content-drift bug found and fixed: legacy shipped two divergent copies of the same "108 items" — the on-page JSX and a separate printFacilitatorQuestions() print/PDF export using an older, different set of item numbers and band groupings (missing the on-page "Twenty-Five Traditions and Protocols" band entirely) — the print export was never updated when the on-page instrument was revised. Used the on-page version (the one actually shown to visitors) as the single source of truth and rebuilt the print export to generate from that same data, so the two can never diverge again. Real fake-data found and dropped: legacy's PeerStats component's own comment admits its numbers ("163 practitioners mapped so far," etc.) are "seeded, realistic-feeling" — fabricated, not real — dropped entirely, same principle as BrewSoul's stale "reads" counts; UsageCounter's hardcoded 160-practitioner fallback (shown forever since no ba</t>
+          <t>psychometric validation dashboard, the real Monte Carlo simulation results (10,000 synthetic respondents), real classification-accuracy comparison, real dimension-priority distribution (the real first-dimension-inflation finding), real test-retest reliability and entropy metrics, and the real methodology writeup, all ported unchanged into app/pri-efficacy/page.tsx, reading the same lib/content/pri-efficacy-data.json also used by /pri-calibration. Real backend gap, handled honestly: legacy's "Live Calibrations" tab read a live trpc.priCalibration.stats query — since /pri-calibration's own submit call was already dropped (no backend, see that page's port note), this tab would permanently render "0 total calibrations, no data yet," a dead feature masquerading as a live one. Dropped entirely rather than ship a perpetually-empty tab; only the real, fully-populated Simulation view ships — which also means this page has no state left at all, so it's a plain Server Component now instead of a client one. Verified live: 200 OK, real content confirmed in rendered HTML, exactly 1 header/1 footer, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E204" s="14" t="inlineStr">
@@ -5617,7 +5617,7 @@
       <c r="A205" s="4" t="n"/>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Port shared safety/medicine data modules (safety-data.ts, medicine-images.ts) as typed .ts content in the new codebase</t>
+          <t>PRI: /pri-research Built 2026-10-06 behind the login: admins are the emails in ADMIN_EMAILS; everyone else gets live's "Access Denied"</t>
         </is>
       </c>
       <c r="C205" s="13" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>done as part of the main PRI page above (lib/content/pri-safety-data.ts, lib/content/pri-medicine-images.ts, both copied verbatim).</t>
+          <t>Totals, anonymized opt-in table, admin-only CSV export (/pri-research/export). /pri-calibration regained legacy's "Contribute to Research?" step and now saves every calibration anonymously to pri_calibrations (opt-ins flagged). Was: — Deferred, not skipped (access-model question resolved by inspection). Read the real legacy source: this is a genuine admin-only dashboard (useAuth() gated to role === "admin") showing trpc.priCalibration.researchData — the same calibration-submission backend already confirmed absent and intentionally not built for /pri-calibration and /pri-efficacy (see their port notes). No admin-auth system exists anywhere in this Next.js migration yet either. So this isn't just an access-control decision — even fully wired up, the page would have zero real data to show, forever. Not worth building an admin dashboard against a backend this migration has twice already decided not to build. Added to "Explicitly deferred" below alongside the other admin dashboards; revisit only if/when both a real admin-auth system and a real calibration-submission backend exist.</t>
         </is>
       </c>
       <c r="E205" s="14" t="inlineStr">
@@ -5637,20 +5637,33 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="10" t="inlineStr">
-        <is>
-          <t>Phase 8 — Attention Theft Manifesto (7 routes)</t>
-        </is>
-      </c>
-      <c r="B206" s="11" t="n"/>
-      <c r="C206" s="11" t="n"/>
-      <c r="D206" s="12" t="n"/>
+      <c r="A206" s="4" t="n"/>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>PRI: /facilitator-index</t>
+        </is>
+      </c>
+      <c r="C206" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D206" s="4" t="inlineStr">
+        <is>
+          <t>"The Facilitator Index: Know Who You Go With," the real 15-question quick-intake archetype quiz (real Bradley-Terry-style axis derivation, fully client-computed via deriveArchetype()), the real 108-item, 12-band (plus Band 0) practitioner self-assessment instrument, and the real methodology prose (rationale, code/tier system, data-handling policy, Reciprocity Gate, Corroboration token system), all ported unchanged and verbatim into lib/content/facilitator-index-data.ts (single authoritative content source) + components/facilitator/* + app/facilitator-index/page.tsx. Real content-drift bug found and fixed: legacy shipped two divergent copies of the same "108 items" — the on-page JSX and a separate printFacilitatorQuestions() print/PDF export using an older, different set of item numbers and band groupings (missing the on-page "Twenty-Five Traditions and Protocols" band entirely) — the print export was never updated when the on-page instrument was revised. Used the on-page version (the one actually shown to visitors) as the single source of truth and rebuilt the print export to generate from that same data, so the two can never diverge again. Real fake-data found and dropped: legacy's PeerStats component's own comment admits its numbers ("163 practitioners mapped so far," etc.) are "seeded, realistic-feeling" — fabricated, not real — dropped entirely, same principle as BrewSoul's stale "reads" counts; UsageCounter's hardcoded 160-practitioner fallback (shown forever since no ba</t>
+        </is>
+      </c>
+      <c r="E206" s="14" t="inlineStr">
+        <is>
+          <t>Phase 7 — PRI &amp; Kava Encyclopedias (19 routes)</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="n"/>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>/attention-theft</t>
+          <t>Port shared safety/medicine data modules (safety-data.ts, medicine-images.ts) as typed .ts content in the new codebase</t>
         </is>
       </c>
       <c r="C207" s="13" t="inlineStr">
@@ -5660,43 +5673,30 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>consolidated mega-page. Real content ported in full across all 9 sections (hero, The Sacred, The Heresy economics data + full breakdown table + sources, the 10 Weapons, Legal Arsenal w/ filter + letter template, AI Blocker Finder quiz, Report a Spammer, closing vow + related reading) — AttentionTheft.tsx used as the single source, the 5 pre-consolidation sub-pages not resurrected (they never existed in this codebase anyway). Section "glamour" photography is real, live imagery on RampRate's own CloudFront (already whitelisted in next.config.ts as a non-Manus, permanent host — confirmed all 7 URLs 200 before using them), rendered via next/image. Real backend gap found and handled honestly: legacy's Wall of Shame (a live trpc.spam.wallOfShame ranked list) and the Report form's trpc.spam.submit both depended on a spam-tracking backend that this migration explicitly defers (see "Explicitly deferred" list below: "/youve-been-reported, /spamtoast, admin spam tooling") — rather than fake a public database with no real data behind it, the report form now composes a mailto: to Tony (same honest non-fake-success pattern as newsletter-popup.tsx), and the ranked Wall of Shame list isn't reproduced. Two simplifications matching precedent set elsewhere in this migration: legacy's "Fraunces" serif (loaded for this one page only) was dropped for font-heading (Playfair Display, already loaded — same call made on /akbar), and the glitch/VHS/ember-particle/shattered-glass decoration layer was dr</t>
+          <t>done as part of the main PRI page above (lib/content/pri-safety-data.ts, lib/content/pri-medicine-images.ts, both copied verbatim).</t>
         </is>
       </c>
       <c r="E207" s="14" t="inlineStr">
         <is>
+          <t>Phase 7 — PRI &amp; Kava Encyclopedias (19 routes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="10" t="inlineStr">
+        <is>
           <t>Phase 8 — Attention Theft Manifesto (7 routes)</t>
         </is>
       </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="4" t="n"/>
-      <c r="B208" s="4" t="inlineStr">
-        <is>
-          <t>Legacy anchor redirects</t>
-        </is>
-      </c>
-      <c r="C208" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D208" s="4" t="inlineStr">
-        <is>
-          <t>/attention-theft/economics, /blocker-finder, /legal, /weapons, /report → /attention-theft#&lt;anchor&gt; via next.config.ts redirects(). Verified live: all return real 308s to the correct anchor.</t>
-        </is>
-      </c>
-      <c r="E208" s="14" t="inlineStr">
-        <is>
-          <t>Phase 8 — Attention Theft Manifesto (7 routes)</t>
-        </is>
-      </c>
+      <c r="B208" s="11" t="n"/>
+      <c r="C208" s="11" t="n"/>
+      <c r="D208" s="12" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="n"/>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Port ManifestoLayout scroll-tracking wrapper behavior</t>
+          <t>/attention-theft</t>
         </is>
       </c>
       <c r="C209" s="13" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>components/manifesto/manifesto-nav.tsx tracks which section is in view on scroll and highlights the matching nav pill (desktop + mobile), real behavior kept per this line item rather than simplified away.</t>
+          <t>consolidated mega-page. Real content ported in full across all 9 sections (hero, The Sacred, The Heresy economics data + full breakdown table + sources, the 10 Weapons, Legal Arsenal w/ filter + letter template, AI Blocker Finder quiz, Report a Spammer, closing vow + related reading) — AttentionTheft.tsx used as the single source, the 5 pre-consolidation sub-pages not resurrected (they never existed in this codebase anyway). Section "glamour" photography is real, live imagery on RampRate's own CloudFront (already whitelisted in next.config.ts as a non-Manus, permanent host — confirmed all 7 URLs 200 before using them), rendered via next/image. Real backend gap found and handled honestly: legacy's Wall of Shame (a live trpc.spam.wallOfShame ranked list) and the Report form's trpc.spam.submit both depended on a spam-tracking backend that this migration explicitly defers (see "Explicitly deferred" list below: "/youve-been-reported, /spamtoast, admin spam tooling") — rather than fake a public database with no real data behind it, the report form now composes a mailto: to Tony (same honest non-fake-success pattern as newsletter-popup.tsx), and the ranked Wall of Shame list isn't reproduced. Two simplifications matching precedent set elsewhere in this migration: legacy's "Fraunces" serif (loaded for this one page only) was dropped for font-heading (Playfair Display, already loaded — same call made on /akbar), and the glitch/VHS/ember-particle/shattered-glass decoration layer was dr</t>
         </is>
       </c>
       <c r="E209" s="14" t="inlineStr">
@@ -5716,20 +5716,33 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="10" t="inlineStr">
-        <is>
-          <t>Phase 9 — Assessments (33 routes)</t>
-        </is>
-      </c>
-      <c r="B210" s="11" t="n"/>
-      <c r="C210" s="11" t="n"/>
-      <c r="D210" s="12" t="n"/>
+      <c r="A210" s="4" t="n"/>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>Legacy anchor redirects</t>
+        </is>
+      </c>
+      <c r="C210" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D210" s="4" t="inlineStr">
+        <is>
+          <t>/attention-theft/economics, /blocker-finder, /legal, /weapons, /report → /attention-theft#&lt;anchor&gt; via next.config.ts redirects(). Verified live: all return real 308s to the correct anchor.</t>
+        </is>
+      </c>
+      <c r="E210" s="14" t="inlineStr">
+        <is>
+          <t>Phase 8 — Attention Theft Manifesto (7 routes)</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="n"/>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>HumanOS section</t>
+          <t>Port ManifestoLayout scroll-tracking wrapper behavior</t>
         </is>
       </c>
       <c r="C211" s="13" t="inlineStr">
@@ -5739,43 +5752,30 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>/humanos, /humanos/philosophy, /humanos/ecosystem, /humanos/resources, /humanos/connect, /humanos/path-to-here, ported from _legacy-manus-app/client/src/pages/HumanOS.tsx + humanos/*.tsx. The top-level HumanOS.tsx (an iframe embed of an external manus.space site) turned out to be dead code, never wired into legacy's router — the real, routed implementation is HumanosHome/HumanosPhilosophy/HumanosEcosystem/HumanosResources/HumanosConnect/HumanosPathToHere behind HumanosLayout, which is what got ported, with its own nested layout.tsx (route now added to site-chrome.tsx's SUPPRESSED_PREFIXES so the main SiteHeader/SiteFooter don't double up around HumanOS's own nav/footer). Real content in full: the Maximizer-vs-Satisficer framework and "Boiling the Human"/"Maximizer Trap"/"Conscious Satisficer" philosophy sections, the full ecosystem roster (1 mentor, 8 advisors, 3 partners, 29 clients), all 4 transformation playbooks + 3 daily-practice protocols + 8-book reading list, all 4 connect channels, and the 6-entry "Path to Here" timeline (2010 H+ Summit through 2025). Real bugs fixed: every "Take the Diagnostic" CTA site-wide pointed at /assessment, an 8-question Maximizer/Satisficer quiz that was never actually built anywhere (legacy's real /assessment and /assessments routes are two different, unrelated quiz sets) — redirected to /humanos/philosophy, which delivers the actual promised content; Connect's "Read the Living Declaration" pointed at /manifesto, a dead redirect stub in le</t>
+          <t>components/manifesto/manifesto-nav.tsx tracks which section is in view on scroll and highlights the matching nav pill (desktop + mobile), real behavior kept per this line item rather than simplified away.</t>
         </is>
       </c>
       <c r="E211" s="14" t="inlineStr">
         <is>
+          <t>Phase 8 — Attention Theft Manifesto (7 routes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="10" t="inlineStr">
+        <is>
           <t>Phase 9 — Assessments (33 routes)</t>
         </is>
       </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="4" t="n"/>
-      <c r="B212" s="4" t="inlineStr">
-        <is>
-          <t>/find-your-me (+ /find-my-me, /discover)</t>
-        </is>
-      </c>
-      <c r="C212" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D212" s="4" t="inlineStr">
-        <is>
-          <t>"Find My — To Find Your We," the ecosystem hub assessment and by far the largest page in Phase 9. Real 5 NLP-driven questions, 6 dimensions (relationships/purpose/body/truth/tribe/consciousness), and 6 real archetypes (each with a real description, real blog article links, real satellite-site links, real "go deeper" forward-references, and a real share text) ported unchanged and verbatim into a new lib/content/find-your-me.ts data module (kept separate from the component given the file's exceptional size, same pattern as brewsoul-directory.ts). All 17 unique blog article slugs referenced across the 6 archetypes were individually verified live (200 OK) against this migration's real Sanity blog before porting — zero dead article links. Real accuracy fix: legacy's "Full Ecosystem Directory" (26 items across 5 categories, with a real LIVE/COMING pill UI already built for exactly this purpose) marked everything "live," including several routes that don't exist anywhere in this migration yet (/find-my, /the-mirror, /assessments/dharma-finder, /assessments/consciousness-scale, /assessments/grant-study, /flow-circuit) — corrected each item's status to this app's actual current build state rather than shipping false LIVE labels on what would be 404s. Real completeness fix: added Find Your Peptide and Find Your Sexuality to the directory (Body &amp; Temple and Love &amp; Belonging) — both are real, fully-built assessments elsewhere in this migration that didn't exist yet when legacy was writte</t>
-        </is>
-      </c>
-      <c r="E212" s="14" t="inlineStr">
-        <is>
-          <t>Phase 9 — Assessments (33 routes)</t>
-        </is>
-      </c>
+      <c r="B212" s="11" t="n"/>
+      <c r="C212" s="11" t="n"/>
+      <c r="D212" s="12" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="n"/>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>/find-your-therapy (+ /find-my-therapy)</t>
+          <t>HumanOS section</t>
         </is>
       </c>
       <c r="C213" s="13" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real 25 questions across 6 dimensions (Cognitive/Somatic/Relational/Depth-Unconscious/Altered States/Integrative), 6 real therapeutic modalities (each with a real description, "how it works," best-for/not-ideal-for lists, real named pioneers, and real book/directory resources), and the real archetype-matching logic (highest-scoring dimension wins) ported unchanged and verbatim. Three real stale-count bugs found and fixed: legacy's own file-header comment claimed "10 questions," its AssessmentIntro stats prop claimed 20 — neither matches the real 25-item array (the scoring code's own maxPossible = 30 // rough max per dimension with 25 questions comment confirms 25 is correct) — replaced both with live QUESTIONS.length. Real dead-link bug fixed: legacy's "Journey Continues" grid linked "Find Your Spirit"/"Find Your Religion" to external findmyassess-9eekxcob.manus.space stub URLs (dead Manus domain) despite this migration already having real, fully-built internal pages at /find-your-spirit and /find-your-religion — repointed to the real internal routes, and corrected Religion's stale "15 Questions" badge to the real 20. Real accent-color inconsistency fixed: legacy passed accentColor="#7B1FA2" only to the landing screen, then hardcoded brand-gold everywhere on the results screen instead — threaded one ACCENT constant through intro/radar/result-actions consistently, matching every other assessment in this migration. The "Also Worth Exploring" related-modality cards were dropped </t>
+          <t>/humanos, /humanos/philosophy, /humanos/ecosystem, /humanos/resources, /humanos/connect, /humanos/path-to-here, ported from _legacy-manus-app/client/src/pages/HumanOS.tsx + humanos/*.tsx. The top-level HumanOS.tsx (an iframe embed of an external manus.space site) turned out to be dead code, never wired into legacy's router — the real, routed implementation is HumanosHome/HumanosPhilosophy/HumanosEcosystem/HumanosResources/HumanosConnect/HumanosPathToHere behind HumanosLayout, which is what got ported, with its own nested layout.tsx (route now added to site-chrome.tsx's SUPPRESSED_PREFIXES so the main SiteHeader/SiteFooter don't double up around HumanOS's own nav/footer). Real content in full: the Maximizer-vs-Satisficer framework and "Boiling the Human"/"Maximizer Trap"/"Conscious Satisficer" philosophy sections, the full ecosystem roster (1 mentor, 8 advisors, 3 partners, 29 clients), all 4 transformation playbooks + 3 daily-practice protocols + 8-book reading list, all 4 connect channels, and the 6-entry "Path to Here" timeline (2010 H+ Summit through 2025). Real bugs fixed: every "Take the Diagnostic" CTA site-wide pointed at /assessment, an 8-question Maximizer/Satisficer quiz that was never actually built anywhere (legacy's real /assessment and /assessments routes are two different, unrelated quiz sets) — redirected to /humanos/philosophy, which delivers the actual promised content; Connect's "Read the Living Declaration" pointed at /manifesto, a dead redirect stub in le</t>
         </is>
       </c>
       <c r="E213" s="14" t="inlineStr">
@@ -5798,7 +5798,7 @@
       <c r="A214" s="4" t="n"/>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>/find-your-sake</t>
+          <t>/find-your-me (+ /find-my-me, /discover)</t>
         </is>
       </c>
       <c r="C214" s="13" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Real 20 questions across 5 dimensions (Palate/Ritual/Terroir/Philosophy/Season) and the real 5 sake profiles (each with real Japanese name, tasting notes, food pairings, serving temperature, named producers with region/note, and further-reading resources) ported unchanged and verbatim. Legacy's own AssessmentIntro stats prop claimed "15 questions, 6 dimensions" — didn't match the real 20/5 implementation — replaced with live QUESTIONS.length/DIMENSIONS.length counts, same fix pattern already applied on /find-your-attachment-style and /find-your-sexuality. Two real bugs found and fixed: (1) legacy's "Journey Continues" list read "Find Myzcal" — a literal typo for "Find Your Mezcal" — corrected. (2) legacy's JSX rendered &lt;WhatsNext /&gt; (a full page section) nested inside the small "Retake the Tasting" &lt;button&gt; element — moved to a proper top-level section, same class of nested-interactive-content bug already fixed on /find-your-religion. The dark GlassPanel treatment (near-black translucent cards with light cream text, sitting on the page's own light parchment ThemedBackground) was kept as a real, intentional design choice rather than "fixed" to this migration's usual light-card convention — unlike the light-text-directly-on-light-background contrast bugs found on Style/Sexuality/Peptide/Religion, the text here sits inside its own correctly-contrasted dark card. SacredGeometryBg's canvas-based floating rice-grain particles dropped (same decoration-not-worth-the-JS-cost call made</t>
+          <t>"Find My — To Find Your We," the ecosystem hub assessment and by far the largest page in Phase 9. Real 5 NLP-driven questions, 6 dimensions (relationships/purpose/body/truth/tribe/consciousness), and 6 real archetypes (each with a real description, real blog article links, real satellite-site links, real "go deeper" forward-references, and a real share text) ported unchanged and verbatim into a new lib/content/find-your-me.ts data module (kept separate from the component given the file's exceptional size, same pattern as brewsoul-directory.ts). All 17 unique blog article slugs referenced across the 6 archetypes were individually verified live (200 OK) against this migration's real Sanity blog before porting — zero dead article links. Real accuracy fix: legacy's "Full Ecosystem Directory" (26 items across 5 categories, with a real LIVE/COMING pill UI already built for exactly this purpose) marked everything "live," including several routes that don't exist anywhere in this migration yet (/find-my, /the-mirror, /assessments/dharma-finder, /assessments/consciousness-scale, /assessments/grant-study, /flow-circuit) — corrected each item's status to this app's actual current build state rather than shipping false LIVE labels on what would be 404s. Real completeness fix: added Find Your Peptide and Find Your Sexuality to the directory (Body &amp; Temple and Love &amp; Belonging) — both are real, fully-built assessments elsewhere in this migration that didn't exist yet when legacy was writte</t>
         </is>
       </c>
       <c r="E214" s="14" t="inlineStr">
@@ -5821,7 +5821,7 @@
       <c r="A215" s="4" t="n"/>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>/find-your-spirit (+ /find-my-spirit), along with a shared PDF-export component the rest of Phase 9 can reuse</t>
+          <t>/find-your-therapy (+ /find-my-therapy)</t>
         </is>
       </c>
       <c r="C215" s="13" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Real 35 questions, 10 dimensions, and the 6 real spiritual traditions (each with real description/practices/key texts/figures/modern expressions/growth edge) ported unchanged and verbatim — legacy's own file-header comment claimed "12 archetypes," but only 6 TRADITIONS actually exist in the code; ported the real 6, not the stale doc comment. The real weighted tradition-matching logic (top 3 dimensions per tradition, weighted 3/2/1) is unchanged. Ported components/assessments/result-actions.tsx from legacy's AssessmentResultActions — kept only the real, backend-free "Download PDF" action (browser print); the "Send to Tony"/"Keep Private" buttons posted to an unbuilt trpc.assessments.submit and weren't reproduced, same honest-degradation pattern used throughout this migration. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
+          <t xml:space="preserve">Real 25 questions across 6 dimensions (Cognitive/Somatic/Relational/Depth-Unconscious/Altered States/Integrative), 6 real therapeutic modalities (each with a real description, "how it works," best-for/not-ideal-for lists, real named pioneers, and real book/directory resources), and the real archetype-matching logic (highest-scoring dimension wins) ported unchanged and verbatim. Three real stale-count bugs found and fixed: legacy's own file-header comment claimed "10 questions," its AssessmentIntro stats prop claimed 20 — neither matches the real 25-item array (the scoring code's own maxPossible = 30 // rough max per dimension with 25 questions comment confirms 25 is correct) — replaced both with live QUESTIONS.length. Real dead-link bug fixed: legacy's "Journey Continues" grid linked "Find Your Spirit"/"Find Your Religion" to external findmyassess-9eekxcob.manus.space stub URLs (dead Manus domain) despite this migration already having real, fully-built internal pages at /find-your-spirit and /find-your-religion — repointed to the real internal routes, and corrected Religion's stale "15 Questions" badge to the real 20. Real accent-color inconsistency fixed: legacy passed accentColor="#7B1FA2" only to the landing screen, then hardcoded brand-gold everywhere on the results screen instead — threaded one ACCENT constant through intro/radar/result-actions consistently, matching every other assessment in this migration. The "Also Worth Exploring" related-modality cards were dropped </t>
         </is>
       </c>
       <c r="E215" s="14" t="inlineStr">
@@ -5844,7 +5844,7 @@
       <c r="A216" s="4" t="n"/>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>/find-your-religion</t>
+          <t>/find-your-sake</t>
         </is>
       </c>
       <c r="C216" s="13" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Real 20 questions across 8 dimensions, 8 real spiritual/philosophical archetypes (each with real description/practices/key texts/figures/resonant traditions/growth-edge tensions), and the real scoring/matching logic ported unchanged and verbatim. Real bug found and fixed: legacy's own JSX rendered &lt;AssessmentResultActions&gt; nested inside the "Retake Assessment" &lt;button&gt; element — a button inside a button, invalid HTML — fixed by rendering it as a sibling instead, same fix pattern already applied on /find-your-spirit. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>Real 20 questions across 5 dimensions (Palate/Ritual/Terroir/Philosophy/Season) and the real 5 sake profiles (each with real Japanese name, tasting notes, food pairings, serving temperature, named producers with region/note, and further-reading resources) ported unchanged and verbatim. Legacy's own AssessmentIntro stats prop claimed "15 questions, 6 dimensions" — didn't match the real 20/5 implementation — replaced with live QUESTIONS.length/DIMENSIONS.length counts, same fix pattern already applied on /find-your-attachment-style and /find-your-sexuality. Two real bugs found and fixed: (1) legacy's "Journey Continues" list read "Find Myzcal" — a literal typo for "Find Your Mezcal" — corrected. (2) legacy's JSX rendered &lt;WhatsNext /&gt; (a full page section) nested inside the small "Retake the Tasting" &lt;button&gt; element — moved to a proper top-level section, same class of nested-interactive-content bug already fixed on /find-your-religion. The dark GlassPanel treatment (near-black translucent cards with light cream text, sitting on the page's own light parchment ThemedBackground) was kept as a real, intentional design choice rather than "fixed" to this migration's usual light-card convention — unlike the light-text-directly-on-light-background contrast bugs found on Style/Sexuality/Peptide/Religion, the text here sits inside its own correctly-contrasted dark card. SacredGeometryBg's canvas-based floating rice-grain particles dropped (same decoration-not-worth-the-JS-cost call made</t>
         </is>
       </c>
       <c r="E216" s="14" t="inlineStr">
@@ -5867,7 +5867,7 @@
       <c r="A217" s="4" t="n"/>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>/find-your-diet (+ /find-my-diet)</t>
+          <t>/find-your-spirit (+ /find-my-spirit), along with a shared PDF-export component the rest of Phase 9 can reuse</t>
         </is>
       </c>
       <c r="C217" s="13" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>Real 15 questions, 6 real archetypes (with descriptions), and the real nearest-neighbor archetype-matching logic ported unchanged. Legacy's dead JourneyTracker import wired in for real (see journey-tracker.tsx). /find-my-diet → /find-your-diet redirect added. Verified live: 200 OK, full quiz flow, redirect confirmed 308, typecheck/lint clean.</t>
+          <t>Real 35 questions, 10 dimensions, and the 6 real spiritual traditions (each with real description/practices/key texts/figures/modern expressions/growth edge) ported unchanged and verbatim — legacy's own file-header comment claimed "12 archetypes," but only 6 TRADITIONS actually exist in the code; ported the real 6, not the stale doc comment. The real weighted tradition-matching logic (top 3 dimensions per tradition, weighted 3/2/1) is unchanged. Ported components/assessments/result-actions.tsx from legacy's AssessmentResultActions — kept only the real, backend-free "Download PDF" action (browser print); the "Send to Tony"/"Keep Private" buttons posted to an unbuilt trpc.assessments.submit and weren't reproduced, same honest-degradation pattern used throughout this migration. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E217" s="14" t="inlineStr">
@@ -5890,7 +5890,7 @@
       <c r="A218" s="4" t="n"/>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>/find-your-movement (+ /find-my-movement), along with the shared assessment foundation the rest of Phase 9 depends on</t>
+          <t>/find-your-religion</t>
         </is>
       </c>
       <c r="C218" s="13" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Ported components/assessments/{themed-background,assessment-intro,email-gate,whats-next}.tsx from legacy's ThemedBackground/AssessmentIntro/EmailGate/WhatsNext — real content/behavior unchanged, with 2 real fixes along the way: (1) EmailGate now posts to the real /api/subscribe Route Handler (built earlier this migration) using the exact find-your-&lt;slug&gt; source keys already defined in lib/content/kit-source-tags.ts's KIT_TAG_MAP — legacy's own assessment-gate:&lt;slug&gt; prefix didn't match any tag in that map, so this is a genuine improvement, not just a port. (2) ThemedBackground's per-theme decorative particle field + SVG sacred-geometry overlay + 2 extra radial-glow layers dropped (same "not worth the cost" call made repeatedly elsewhere) — the real per-theme base gradient (16 themes) is kept, precomposed as one literal Tailwind class per theme rather than assembled from fragments. find-your-movement-quiz.tsx ports all 15 real questions and the real 6-dimension (Strength/Flexibility/Endurance/Mindfulness/Community/Adventure) scoring unchanged; the legacy JourneyTracker/useJourneyProgress import in the source file was dead code (imported, never rendered) and not ported. /find-my-movement → /find-your-movement redirect added (next.config.ts), same duplicate-route pattern as /find-my-tribe. Verified live: 200 OK, full quiz flow renders, redirect confirmed 308, typecheck/lint clean.</t>
+          <t>Real 20 questions across 8 dimensions, 8 real spiritual/philosophical archetypes (each with real description/practices/key texts/figures/resonant traditions/growth-edge tensions), and the real scoring/matching logic ported unchanged and verbatim. Real bug found and fixed: legacy's own JSX rendered &lt;AssessmentResultActions&gt; nested inside the "Retake Assessment" &lt;button&gt; element — a button inside a button, invalid HTML — fixed by rendering it as a sibling instead, same fix pattern already applied on /find-your-spirit. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E218" s="14" t="inlineStr">
@@ -5913,7 +5913,7 @@
       <c r="A219" s="4" t="n"/>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>/find-your-sleep (+ /find-my-sleep)</t>
+          <t>/find-your-diet (+ /find-my-diet)</t>
         </is>
       </c>
       <c r="C219" s="13" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>Real 15 questions, 6 real archetypes, and the real cascading archetype-match logic ported unchanged, including legacy's own real behavioral quirk of rendering JourneyTracker on every phase (not just results). One real duplicate-destination "Journey Continues" link pair dropped (see file's own port note), the one real distinct link (Find Your Diet) kept. /find-my-sleep → /find-your-sleep redirect added. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
+          <t>Real 15 questions, 6 real archetypes (with descriptions), and the real nearest-neighbor archetype-matching logic ported unchanged. Legacy's dead JourneyTracker import wired in for real (see journey-tracker.tsx). /find-my-diet → /find-your-diet redirect added. Verified live: 200 OK, full quiz flow, redirect confirmed 308, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E219" s="14" t="inlineStr">
@@ -5936,7 +5936,7 @@
       <c r="A220" s="4" t="n"/>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>/find-your-coffee (+ /find-my-coffee)</t>
+          <t>/find-your-movement (+ /find-my-movement), along with the shared assessment foundation the rest of Phase 9 depends on</t>
         </is>
       </c>
       <c r="C220" s="13" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Real 15 questions, 6 dimensions (Roast Preference/Origin Curiosity/Brewing Ritual/Social Context/Caffeine Sensitivity/Flavor Complexity), 6 real archetypes (each with a real description and 5 real named coffee recommendations — roaster, origin, roast level, tasting notes, real "why" rationale), and the real archetype-matching logic (sum of each archetype's 2 primary dimensions, highest wins) ported unchanged and verbatim. This legacy page predates the shared ThemedBackground/AssessmentIntro component system the rest of Phase 9 is built on — it hand-rolled its own hero-image page shell — so it needed more normalization than most: its hero image (/api/img/coffee-orig_a935f111.jpg) was a dead Manus asset, dropped for the standard ThemedBackground light theme (added a new "coffee" warm-cream entry) instead of reproducing a broken background; the canvas bean-particle field, floating steam-wisp divs, and SVG sacred-geometry overlay all dropped (same decoration-not-worth-the-JS-cost call made repeatedly elsewhere). Real bug found and fixed: legacy read window.innerWidth directly during render (twice — to pick grid columns and flex direction), unsafe during SSR and a real hydration-mismatch source — replaced with responsive Tailwind classes. EmailGate's prop was legacy's assessmentName; ported using this repo's real assessmentSlug="coffee" to match find-your-coffee in KIT_TAG_MAP. Legacy imported useJourneyProgress for markComplete but never rendered a visible JourneyTracker, and nev</t>
+          <t>Ported components/assessments/{themed-background,assessment-intro,email-gate,whats-next}.tsx from legacy's ThemedBackground/AssessmentIntro/EmailGate/WhatsNext — real content/behavior unchanged, with 2 real fixes along the way: (1) EmailGate now posts to the real /api/subscribe Route Handler (built earlier this migration) using the exact find-your-&lt;slug&gt; source keys already defined in lib/content/kit-source-tags.ts's KIT_TAG_MAP — legacy's own assessment-gate:&lt;slug&gt; prefix didn't match any tag in that map, so this is a genuine improvement, not just a port. (2) ThemedBackground's per-theme decorative particle field + SVG sacred-geometry overlay + 2 extra radial-glow layers dropped (same "not worth the cost" call made repeatedly elsewhere) — the real per-theme base gradient (16 themes) is kept, precomposed as one literal Tailwind class per theme rather than assembled from fragments. find-your-movement-quiz.tsx ports all 15 real questions and the real 6-dimension (Strength/Flexibility/Endurance/Mindfulness/Community/Adventure) scoring unchanged; the legacy JourneyTracker/useJourneyProgress import in the source file was dead code (imported, never rendered) and not ported. /find-my-movement → /find-your-movement redirect added (next.config.ts), same duplicate-route pattern as /find-my-tribe. Verified live: 200 OK, full quiz flow renders, redirect confirmed 308, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E220" s="14" t="inlineStr">
@@ -5959,7 +5959,7 @@
       <c r="A221" s="4" t="n"/>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>/find-your-kitchen. Real 15 questions (all rendered on one page at once</t>
+          <t>/find-your-sleep (+ /find-my-sleep)</t>
         </is>
       </c>
       <c r="C221" s="13" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>a genuinely different, legacy-intentional UX from the other paginated quizzes, kept as-is) and the real dual-tracking scoring (answer score keys split into archetype tallies vs. 6 separate radar-chart dimensions) ported unchanged, including the 3 real "Journey Continues" links (one to already-built /find-your-diet, one forward-reference to /find-your-style). Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>Real 15 questions, 6 real archetypes, and the real cascading archetype-match logic ported unchanged, including legacy's own real behavioral quirk of rendering JourneyTracker on every phase (not just results). One real duplicate-destination "Journey Continues" link pair dropped (see file's own port note), the one real distinct link (Find Your Diet) kept. /find-my-sleep → /find-your-sleep redirect added. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E221" s="14" t="inlineStr">
@@ -5982,7 +5982,7 @@
       <c r="A222" s="4" t="n"/>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>/find-your-style. Real 15 questions, 6 real archetypes, and the real (if crude</t>
+          <t>/find-your-coffee (+ /find-my-coffee)</t>
         </is>
       </c>
       <c r="C222" s="13" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>legacy's own comment admits "Simple mapping for demonstration") threshold-based archetype match ported unchanged. Two real inconsistencies found and normalized: legacy's own inline styles used near-illegible light text on ThemedBackground's actual light pastel "style" theme (inconsistent with every other assessment in this migration); and legacy rendered &lt;JourneyTracker /&gt; defaulting to variant="dark" on a light results screen instead of the variant="light" every other assessment passes. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>Real 15 questions, 6 dimensions (Roast Preference/Origin Curiosity/Brewing Ritual/Social Context/Caffeine Sensitivity/Flavor Complexity), 6 real archetypes (each with a real description and 5 real named coffee recommendations — roaster, origin, roast level, tasting notes, real "why" rationale), and the real archetype-matching logic (sum of each archetype's 2 primary dimensions, highest wins) ported unchanged and verbatim. This legacy page predates the shared ThemedBackground/AssessmentIntro component system the rest of Phase 9 is built on — it hand-rolled its own hero-image page shell — so it needed more normalization than most: its hero image (/api/img/coffee-orig_a935f111.jpg) was a dead Manus asset, dropped for the standard ThemedBackground light theme (added a new "coffee" warm-cream entry) instead of reproducing a broken background; the canvas bean-particle field, floating steam-wisp divs, and SVG sacred-geometry overlay all dropped (same decoration-not-worth-the-JS-cost call made repeatedly elsewhere). Real bug found and fixed: legacy read window.innerWidth directly during render (twice — to pick grid columns and flex direction), unsafe during SSR and a real hydration-mismatch source — replaced with responsive Tailwind classes. EmailGate's prop was legacy's assessmentName; ported using this repo's real assessmentSlug="coffee" to match find-your-coffee in KIT_TAG_MAP. Legacy imported useJourneyProgress for markComplete but never rendered a visible JourneyTracker, and nev</t>
         </is>
       </c>
       <c r="E222" s="14" t="inlineStr">
@@ -6005,7 +6005,7 @@
       <c r="A223" s="4" t="n"/>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>/find-your-attachment-style (+ /find-my-attachment-style, /find-my-we)</t>
+          <t>/find-your-kitchen. Real 15 questions (all rendered on one page at once</t>
         </is>
       </c>
       <c r="C223" s="13" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>Real 18 questions (legacy's own AssessmentIntro stats prop under-reported this as "15" — used the live QUESTIONS.length instead of repeating the stale number, same live-count discipline used elsewhere in this migration), the 4 real archetypes, and the real scoring/selection logic all ported unchanged, including the real closing note on attachment theory. Both alt-path redirects added. Verified live: 200 OK, both redirects confirmed 308, typecheck/lint clean.</t>
+          <t>a genuinely different, legacy-intentional UX from the other paginated quizzes, kept as-is) and the real dual-tracking scoring (answer score keys split into archetype tallies vs. 6 separate radar-chart dimensions) ported unchanged, including the 3 real "Journey Continues" links (one to already-built /find-your-diet, one forward-reference to /find-your-style). Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E223" s="14" t="inlineStr">
@@ -6028,7 +6028,7 @@
       <c r="A224" s="4" t="n"/>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>/find-your-love-language</t>
+          <t>/find-your-style. Real 15 questions, 6 real archetypes, and the real (if crude</t>
         </is>
       </c>
       <c r="C224" s="13" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Real 15 questions (incl. the negative-score "disconnect" question), 5 real archetypes with descriptions/tips, and Dr. Gary Chapman's real attribution note all ported unchanged. Verified live: 200 OK, full quiz flow, typecheck/lint clean.</t>
+          <t>legacy's own comment admits "Simple mapping for demonstration") threshold-based archetype match ported unchanged. Two real inconsistencies found and normalized: legacy's own inline styles used near-illegible light text on ThemedBackground's actual light pastel "style" theme (inconsistent with every other assessment in this migration); and legacy rendered &lt;JourneyTracker /&gt; defaulting to variant="dark" on a light results screen instead of the variant="light" every other assessment passes. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E224" s="14" t="inlineStr">
@@ -6051,7 +6051,7 @@
       <c r="A225" s="4" t="n"/>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>/find-your-peptide (+ /find-my-peptide)</t>
+          <t>/find-your-attachment-style (+ /find-my-attachment-style, /find-my-we)</t>
         </is>
       </c>
       <c r="C225" s="13" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>"The Peptide Clarity Index™." A real, evidence-cited 10-question assessment across 7 clinical axes, mapping to 16 real peptide archetype profiles — every question (with its real PubMed/journal citation), every profile's real primary/secondary peptides with mechanisms and evidence, suggested lab work, red flags, and stacking notes ported unchanged and verbatim (clinical-adjacent content, not paraphrased). The real Peptide Readiness Score, contraindication-flag screening, share buttons (Twitter/LinkedIn/email/copy — real, backend-free), and the real medical disclaimer are all preserved. Real hero image (CloudFront, confirmed live) kept via next/image. Reused the simplified AssessmentResultActions (PDF-only) built for /find-your-spirit. Same light-text-on-light-background contrast bug already caught elsewhere was fixed here too. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
+          <t>Real 18 questions (legacy's own AssessmentIntro stats prop under-reported this as "15" — used the live QUESTIONS.length instead of repeating the stale number, same live-count discipline used elsewhere in this migration), the 4 real archetypes, and the real scoring/selection logic all ported unchanged, including the real closing note on attachment theory. Both alt-path redirects added. Verified live: 200 OK, both redirects confirmed 308, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E225" s="14" t="inlineStr">
@@ -6074,7 +6074,7 @@
       <c r="A226" s="4" t="n"/>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>/find-your-sexuality (+ /find-my-sexuality)</t>
+          <t>/find-your-love-language</t>
         </is>
       </c>
       <c r="C226" s="13" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>A research-informed assessment across 6 real dimensions, grounded in real cited research (Klein Sexual Orientation Grid 1978, Kinsey Scale 1948, Lisa Diamond 2008, Sari van Anders 2015) — real 16 questions (with per-question research context notes), real 12 archetypes (each with a real description + research note), and the real scoring/selection logic all ported unchanged and verbatim, including the real closing disclaimer. Legacy's own AssessmentIntro stats prop claimed "20 questions, 7 dimensions" — didn't match the real 16/6 implementation, used the live counts instead. Legacy's results screen also used light grey text on the real light pastel theme background (same low-contrast bug already caught on /find-your-style) — normalized to dark ink. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
+          <t>Real 15 questions (incl. the negative-score "disconnect" question), 5 real archetypes with descriptions/tips, and Dr. Gary Chapman's real attribution note all ported unchanged. Verified live: 200 OK, full quiz flow, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E226" s="14" t="inlineStr">
@@ -6097,7 +6097,7 @@
       <c r="A227" s="4" t="n"/>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>/find-my</t>
+          <t>/find-your-peptide (+ /find-my-peptide)</t>
         </is>
       </c>
       <c r="C227" s="13" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Find What's Yours," the real destination of the homepage's "Diagnose" door (confirmed by grepping lib/content/home-doors.ts's /find-my href) and of whats-next.tsx's "Take Another Assessment" link, both already pointing here as forward-references before this page existed. Legacy's 26-item ALL_LINKS directory (Featured + 6 categories) ported unchanged and verbatim into lib/content/find-my-directory.ts. Real accuracy fix, same pattern as /find-your-me's own port note: cross-checked all 26 destinations against the real route list — /find-your-ev, /life-assessment, and /soulscore (at the time) didn't exist yet, rendered as real "Coming Soon" cards instead of links that would 404 (dharma-finder/consciousness-scale/grant-study have since shipped and now flip to live — see below). Real reuse, not re-derivation: every item whose destination already exists in find-your-me.ts's audited DIRECTORY pulls that entry's real hook text and status at build time via a lookup helper, instead of hand-copying a second, driftable copy of the same facts. Two real live destinations added that legacy linked but find-your-me.ts's directory didn't track: /brewsoul (confirmed 200) and the external findmystem-s3lknc4h.manus.space sibling tool (confirmed live), both using the same "real external sibling product" trust already established for the other manus.space tools. Legacy's dead Manus hero image dropped for ThemedBackground (theme="ecosystem"), same call as /find-your-me. AssessmentProgressBar (never </t>
+          <t>"The Peptide Clarity Index™." A real, evidence-cited 10-question assessment across 7 clinical axes, mapping to 16 real peptide archetype profiles — every question (with its real PubMed/journal citation), every profile's real primary/secondary peptides with mechanisms and evidence, suggested lab work, red flags, and stacking notes ported unchanged and verbatim (clinical-adjacent content, not paraphrased). The real Peptide Readiness Score, contraindication-flag screening, share buttons (Twitter/LinkedIn/email/copy — real, backend-free), and the real medical disclaimer are all preserved. Real hero image (CloudFront, confirmed live) kept via next/image. Reused the simplified AssessmentResultActions (PDF-only) built for /find-your-spirit. Same light-text-on-light-background contrast bug already caught elsewhere was fixed here too. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E227" s="14" t="inlineStr">
@@ -6120,7 +6120,7 @@
       <c r="A228" s="4" t="n"/>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>/assessments</t>
+          <t>/find-your-sexuality (+ /find-my-sexuality)</t>
         </is>
       </c>
       <c r="C228" s="13" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>"Three Maps. One Journey," confirmed genuinely distinct from /find-my rather than a duplicate: /find-my is the wide 26-item ecosystem directory, /assessments is its own page for exactly 3 long research-grounded instruments (Dharma Finder / Consciousness Scale / Grant Study) that also happen to appear as one category inside /find-my's directory — legacy kept these as two separate pages, so the port does too. Real title/subtitle/description/time/icon/accent content for all 3 instruments ported unchanged and verbatim into lib/content/assessments-hub.ts, including the full "Why These Three" closing essay (Schmachtenberger/Hawkins/Harvard Grant Study triangulation). All 3 instrument cards now link live (dharma-finder/consciousness-scale/grant-study shipped alongside this page). Legacy's footer claim "Results saved for your return" was dropped — replaced with an honest line since nothing persists results yet. Added a real cross-link to /find-my. JourneyTracker reused unchanged; no EmailGate/AssessmentResultActions — pure preview/hub page with no quiz or results step of its own. Verified live: 200 OK, exactly 1 header/footer, real content in all 3 cards, typecheck/lint clean.</t>
+          <t>A research-informed assessment across 6 real dimensions, grounded in real cited research (Klein Sexual Orientation Grid 1978, Kinsey Scale 1948, Lisa Diamond 2008, Sari van Anders 2015) — real 16 questions (with per-question research context notes), real 12 archetypes (each with a real description + research note), and the real scoring/selection logic all ported unchanged and verbatim, including the real closing disclaimer. Legacy's own AssessmentIntro stats prop claimed "20 questions, 7 dimensions" — didn't match the real 16/6 implementation, used the live counts instead. Legacy's results screen also used light grey text on the real light pastel theme background (same low-contrast bug already caught on /find-your-style) — normalized to dark ink. Verified live: 200 OK, redirect confirmed 308, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E228" s="14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       <c r="A229" s="4" t="n"/>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>/dharma-finder (+ /assessments/dharma-finder redirect). Structurally different from every other Phase 9 quiz</t>
+          <t>/find-my</t>
         </is>
       </c>
       <c r="C229" s="13" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>legacy's real 25 questions are open-text reflection prompts, not multiple choice, distilled from Daniel Schmachtenberger's Dharma Inquiry and grouped into 4 real sections (Capacities/Values/Propensities/The Shadow Inquiry), each with a real framing quote, plus 3 real interstitial quotes shown between sections with the original 4-second auto-advance. All 25 questions, all quotes, and legacy's own keyword-matching generateDharmaProfile (deriving up to 3 archetypal roles and up to 4 core values from free-text answers, plus a completion-depth percentage) are ported unchanged and verbatim into a new dharma-finder-quiz.tsx. Real bug found and fixed: legacy's result-screen JSX rendered &lt;AssessmentResultActions&gt; nested inside the "Retake Assessment" &lt;button&gt; element — a button inside a button, invalid HTML — fixed the same way as /find-your-religion. Real dead-link bug fixed: "Journey Continues" linked to /assessments/consciousness-scale (repointed to the real /consciousness-scale) and /assessments/grant-study (dropped at the time, now live too). EmailGate (new here; legacy had none) is a real ecosystem-consistency addition. find-your-me.ts's ecosystem-directory status flipped from "coming" to "live" now that this page ships. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t xml:space="preserve">"Find What's Yours," the real destination of the homepage's "Diagnose" door (confirmed by grepping lib/content/home-doors.ts's /find-my href) and of whats-next.tsx's "Take Another Assessment" link, both already pointing here as forward-references before this page existed. Legacy's 26-item ALL_LINKS directory (Featured + 6 categories) ported unchanged and verbatim into lib/content/find-my-directory.ts. Real accuracy fix, same pattern as /find-your-me's own port note: cross-checked all 26 destinations against the real route list — /find-your-ev, /life-assessment, and /soulscore (at the time) didn't exist yet, rendered as real "Coming Soon" cards instead of links that would 404 (dharma-finder/consciousness-scale/grant-study have since shipped and now flip to live — see below). Real reuse, not re-derivation: every item whose destination already exists in find-your-me.ts's audited DIRECTORY pulls that entry's real hook text and status at build time via a lookup helper, instead of hand-copying a second, driftable copy of the same facts. Two real live destinations added that legacy linked but find-your-me.ts's directory didn't track: /brewsoul (confirmed 200) and the external findmystem-s3lknc4h.manus.space sibling tool (confirmed live), both using the same "real external sibling product" trust already established for the other manus.space tools. Legacy's dead Manus hero image dropped for ThemedBackground (theme="ecosystem"), same call as /find-your-me. AssessmentProgressBar (never </t>
         </is>
       </c>
       <c r="E229" s="14" t="inlineStr">
@@ -6166,7 +6166,7 @@
       <c r="A230" s="4" t="n"/>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>/consciousness-scale (+ /assessments/consciousness-scale redirect)</t>
+          <t>/assessments</t>
         </is>
       </c>
       <c r="C230" s="13" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Real 25 questions, each scored against David R. Hawkins' real 17-level Map of Consciousness (Shame 20 through Enlightenment 700+, final score = average of all 25 answers) — every question/option, every level's name/emotion/threshold, and getInsight's exact 6 tiers of interpretive copy ported unchanged and verbatim into a new consciousness-scale-quiz.tsx, along with the real live running-average indicator, visual scale gauge, full 17-level map, 6-month reminder, and X/LinkedIn/copy share. Since this assessment produces one composite score on a single axis rather than independent dimensions, a bespoke single-axis gauge replaces AssessmentRadarChart; per-level colors (17 known-at-build-time values) are precomposed literal Tailwind classes rather than assembled from hex fragments. Real Manus-dependency bug found and fixed: legacy's cinematic Q1 hero used a /api/img/consciousness-scale-hero-v2_085e0746.jpg Manus-proxied image — forbidden even temporarily per this migration's Zero-Manus rule — dropped for the plain question-card layout every other assessment uses; a real Sanity-hosted replacement is a tracked follow-up (see BLOG-IMAGE-BRIEFS.md-style tracking). find-your-me.ts's ecosystem-directory status flipped from "coming" to "live" now that this page ships. Verified live: 200 OK, typecheck/lint clean.</t>
+          <t>"Three Maps. One Journey," confirmed genuinely distinct from /find-my rather than a duplicate: /find-my is the wide 26-item ecosystem directory, /assessments is its own page for exactly 3 long research-grounded instruments (Dharma Finder / Consciousness Scale / Grant Study) that also happen to appear as one category inside /find-my's directory — legacy kept these as two separate pages, so the port does too. Real title/subtitle/description/time/icon/accent content for all 3 instruments ported unchanged and verbatim into lib/content/assessments-hub.ts, including the full "Why These Three" closing essay (Schmachtenberger/Hawkins/Harvard Grant Study triangulation). All 3 instrument cards now link live (dharma-finder/consciousness-scale/grant-study shipped alongside this page). Legacy's footer claim "Results saved for your return" was dropped — replaced with an honest line since nothing persists results yet. Added a real cross-link to /find-my. JourneyTracker reused unchanged; no EmailGate/AssessmentResultActions — pure preview/hub page with no quiz or results step of its own. Verified live: 200 OK, exactly 1 header/footer, real content in all 3 cards, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E230" s="14" t="inlineStr">
@@ -6189,7 +6189,7 @@
       <c r="A231" s="4" t="n"/>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>/grant-study (+ /assessments/grant-study redirect)</t>
+          <t>/dharma-finder (+ /assessments/dharma-finder redirect). Structurally different from every other Phase 9 quiz</t>
         </is>
       </c>
       <c r="C231" s="13" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>"Find Your Score," the real 25-question (5 per factor), 5-factor Harvard Grant Study life-satisfaction assessment (724 men, 1938–present, 85+ years — the longest-running study of human happiness). Every question, the 5 real factors (Warm Relationships/Adaptive Coping/Generativity/Career Satisfaction/Physical Vitality), every per-factor/per-tier insight (real named findings — Vaillant's "mature defenses," Erikson's generativity, Waldinger's quote), and the closing "Tony's Note" (Vaillant's "Happiness is love. Full stop." + Waldinger's "good relationships keep us happier and healthier") all ported unchanged and verbatim. Real nested-interactive-element bug found and fixed: legacy rendered &lt;AssessmentResultActions&gt; (its own &lt;button&gt;) literally inside the "Retake Assessment" &lt;button&gt; — same bug class already caught on /find-your-religion//find-your-sake — split into siblings. Real dead-link fix: "Journey Continues" pointed "Find Your Spirit" at a dead external Manus stub despite the real internal /find-your-spirit existing — repointed. Real ecosystem-consistency normalization: unlike every sibling "Find Your X" quiz, legacy skipped EmailGate entirely and went straight to results — added for consistency, plus new find-your-grant-study/find-your-dharma-finder/find-your-consciousness-scale alias keys in kit-source-tags.ts's KIT_TAG_MAP so EmailGate's fixed find-your-&lt;slug&gt; source prefix actually resolves to the intended tag instead of a generic fallback. resultSlug="grant-study" pas</t>
+          <t>legacy's real 25 questions are open-text reflection prompts, not multiple choice, distilled from Daniel Schmachtenberger's Dharma Inquiry and grouped into 4 real sections (Capacities/Values/Propensities/The Shadow Inquiry), each with a real framing quote, plus 3 real interstitial quotes shown between sections with the original 4-second auto-advance. All 25 questions, all quotes, and legacy's own keyword-matching generateDharmaProfile (deriving up to 3 archetypal roles and up to 4 core values from free-text answers, plus a completion-depth percentage) are ported unchanged and verbatim into a new dharma-finder-quiz.tsx. Real bug found and fixed: legacy's result-screen JSX rendered &lt;AssessmentResultActions&gt; nested inside the "Retake Assessment" &lt;button&gt; element — a button inside a button, invalid HTML — fixed the same way as /find-your-religion. Real dead-link bug fixed: "Journey Continues" linked to /assessments/consciousness-scale (repointed to the real /consciousness-scale) and /assessments/grant-study (dropped at the time, now live too). EmailGate (new here; legacy had none) is a real ecosystem-consistency addition. find-your-me.ts's ecosystem-directory status flipped from "coming" to "live" now that this page ships. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E231" s="14" t="inlineStr">
@@ -6212,7 +6212,7 @@
       <c r="A232" s="4" t="n"/>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>/soulscore</t>
+          <t>/consciousness-scale (+ /assessments/consciousness-scale redirect)</t>
         </is>
       </c>
       <c r="C232" s="13" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>SoulScore™, ImpactSoul's 12-dimension impact measurement engine (1231-line legacy file, the largest remaining port). Unlike the quiz-style "Find Your X" assessments, this is a live interactive calculator, not a Q&amp;A flow: entity-type picker, 12 weighted dimension sliders (Hawkins-scale Consciousness + 11 others), real-time score/grade/radar/auto-diagnosis, a benchmark table against 7 real entities (Patagonia, BP, Fortune 500 Avg, etc.), a 6-tier/30-factor supply chain drill-down, 20 "why every impact system failed" entries, a real Consciousness-Adjusted NPV calculator, and the gig-economy 5-layer stack comparison — all real content/formulas ported verbatim. Fixed: legacy's own SEO block described an unrelated assessment (stale copy-paste, replaced with real metadata); a div-pretending-to-be-a-button wrapping 30 nested range-input sliders (fixed to a real &lt;button&gt; + sibling content div); hardcoded intro/tab counts now read off real array lengths. No EmailGate (legacy never had one here — it's an open calculator, not a report unlock), matching /find-your-peptide's precedent. AssessmentResultActions wired with resultSlug="soulscore". journey-tracker.tsx's JOURNEY_MAP and /impact-dashboard's "Launch SoulScore Engine"/"Launch C-NPV Calculator" links (previously a disabled "Coming Soon" note) now point at the real page. This closes the real dead-end referenced from site-nav-data.ts (/soulscore appears twice in nav) and from /impact-dashboard — the last item in the STATUS.md dead-end</t>
+          <t>Real 25 questions, each scored against David R. Hawkins' real 17-level Map of Consciousness (Shame 20 through Enlightenment 700+, final score = average of all 25 answers) — every question/option, every level's name/emotion/threshold, and getInsight's exact 6 tiers of interpretive copy ported unchanged and verbatim into a new consciousness-scale-quiz.tsx, along with the real live running-average indicator, visual scale gauge, full 17-level map, 6-month reminder, and X/LinkedIn/copy share. Since this assessment produces one composite score on a single axis rather than independent dimensions, a bespoke single-axis gauge replaces AssessmentRadarChart; per-level colors (17 known-at-build-time values) are precomposed literal Tailwind classes rather than assembled from hex fragments. Real Manus-dependency bug found and fixed: legacy's cinematic Q1 hero used a /api/img/consciousness-scale-hero-v2_085e0746.jpg Manus-proxied image — forbidden even temporarily per this migration's Zero-Manus rule — dropped for the plain question-card layout every other assessment uses; a real Sanity-hosted replacement is a tracked follow-up (see BLOG-IMAGE-BRIEFS.md-style tracking). find-your-me.ts's ecosystem-directory status flipped from "coming" to "live" now that this page ships. Verified live: 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E232" s="14" t="inlineStr">
@@ -6235,7 +6235,7 @@
       <c r="A233" s="4" t="n"/>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>/self-portrait</t>
+          <t>/grant-study (+ /assessments/grant-study redirect)</t>
         </is>
       </c>
       <c r="C233" s="13" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>composite of completed assessments. Decision made: local-only (a real cookie, not Supabase — Phase 2 isn't provisioned yet). AssessmentResultActions (components/assessments/result-actions.tsx) takes an optional resultSlug and logs completions to a tg_assessment_results cookie via lib/assessments/result-log.ts, the same real-cookie-read-via-next/headers pattern already established by returning-visitor-hero.tsx/track-last-blog-visit.tsx — the page itself is a Server Component reading that cookie with zero client hydration step. Real, deliberate scope cut, not a silent one: legacy's SelfPortrait.tsx combined each assessment's own per-dimension scores (16 separate localStorage keys) into one composite radar chart across 15 unified dimensions, gated behind "5+ completed." This migration's result log only ever records that an assessment was completed, not its actual scored answers — building the real composite radar would mean threading a second, much larger data channel through every quiz. Shipped the honest subset instead: a real completed-assessments list (title, real completion date, retake link) plus a real "X of N completed" count and a "Still to Explore" section for the rest, via a new lib/content/self-portrait-catalog.ts. Wired resultSlug into the 7 remaining older "Find Your X" quizzes that already call AssessmentResultActions but hadn't been threaded yet (spirit/therapy/religion/sake/coffee/peptide/me) — /self-portrait now tracks 13 real assessments total. /find-my's "Sel</t>
+          <t>"Find Your Score," the real 25-question (5 per factor), 5-factor Harvard Grant Study life-satisfaction assessment (724 men, 1938–present, 85+ years — the longest-running study of human happiness). Every question, the 5 real factors (Warm Relationships/Adaptive Coping/Generativity/Career Satisfaction/Physical Vitality), every per-factor/per-tier insight (real named findings — Vaillant's "mature defenses," Erikson's generativity, Waldinger's quote), and the closing "Tony's Note" (Vaillant's "Happiness is love. Full stop." + Waldinger's "good relationships keep us happier and healthier") all ported unchanged and verbatim. Real nested-interactive-element bug found and fixed: legacy rendered &lt;AssessmentResultActions&gt; (its own &lt;button&gt;) literally inside the "Retake Assessment" &lt;button&gt; — same bug class already caught on /find-your-religion//find-your-sake — split into siblings. Real dead-link fix: "Journey Continues" pointed "Find Your Spirit" at a dead external Manus stub despite the real internal /find-your-spirit existing — repointed. Real ecosystem-consistency normalization: unlike every sibling "Find Your X" quiz, legacy skipped EmailGate entirely and went straight to results — added for consistency, plus new find-your-grant-study/find-your-dharma-finder/find-your-consciousness-scale alias keys in kit-source-tags.ts's KIT_TAG_MAP so EmailGate's fixed find-your-&lt;slug&gt; source prefix actually resolves to the intended tag instead of a generic fallback. resultSlug="grant-study" pas</t>
         </is>
       </c>
       <c r="E233" s="14" t="inlineStr">
@@ -6258,7 +6258,7 @@
       <c r="A234" s="4" t="n"/>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>/the-mirror (+ /life-assessment)</t>
+          <t>/soulscore</t>
         </is>
       </c>
       <c r="C234" s="13" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>uses mirrorData.json, real 6-dimension/18-question life assessment ("The Mirror") ported into a typed lib/content/mirror-data.ts. Legacy served the identical component at both paths; /the-mirror is canonical (it's the only URL every existing internal link already pointed to — nav, journey tracker, Find Your Me), /life-assessment permanently redirects there. Real dimension-averaged scoring, radar chart via the shared AssessmentRadarChart, and weakest-dimension article/satellite-site recommendations ported unchanged. A live Sanity check found only 27 of 85 legacy article slugs still resolve; recommendations now resolve server-side and defensively skip missing ones, matching legacy's own behavior. Fixed: a hydration-unsafe typeof window branch computing the share URL, three stale manus.space satellite URLs superseded by their current live counterparts already used elsewhere in this migration, and dead /assessments/*/external-stub links in the "Journey Continues" grid. Added find-your-mirror to kit-source-tags.ts's KIT_TAG_MAP and reconciled journey-tracker.tsx's stale 10-minute estimate to legacy's real "~4 minutes" claim. find-your-me.ts's ecosystem-directory status flipped to "live." Verified live: 200 OK on both paths, redirect confirmed, typecheck/lint clean.</t>
+          <t>SoulScore™, ImpactSoul's 12-dimension impact measurement engine (1231-line legacy file, the largest remaining port). Unlike the quiz-style "Find Your X" assessments, this is a live interactive calculator, not a Q&amp;A flow: entity-type picker, 12 weighted dimension sliders (Hawkins-scale Consciousness + 11 others), real-time score/grade/radar/auto-diagnosis, a benchmark table against 7 real entities (Patagonia, BP, Fortune 500 Avg, etc.), a 6-tier/30-factor supply chain drill-down, 20 "why every impact system failed" entries, a real Consciousness-Adjusted NPV calculator, and the gig-economy 5-layer stack comparison — all real content/formulas ported verbatim. Fixed: legacy's own SEO block described an unrelated assessment (stale copy-paste, replaced with real metadata); a div-pretending-to-be-a-button wrapping 30 nested range-input sliders (fixed to a real &lt;button&gt; + sibling content div); hardcoded intro/tab counts now read off real array lengths. No EmailGate (legacy never had one here — it's an open calculator, not a report unlock), matching /find-your-peptide's precedent. AssessmentResultActions wired with resultSlug="soulscore". journey-tracker.tsx's JOURNEY_MAP and /impact-dashboard's "Launch SoulScore Engine"/"Launch C-NPV Calculator" links (previously a disabled "Coming Soon" note) now point at the real page. This closes the real dead-end referenced from site-nav-data.ts (/soulscore appears twice in nav) and from /impact-dashboard — the last item in the STATUS.md dead-end</t>
         </is>
       </c>
       <c r="E234" s="14" t="inlineStr">
@@ -6281,7 +6281,7 @@
       <c r="A235" s="4" t="n"/>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>/assessment</t>
+          <t>/self-portrait</t>
         </is>
       </c>
       <c r="C235" s="13" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>confirmed via full legacy read this is not a "Find Your X" quiz (it predates that convention): it's Tony's own 3-way reader-path diagnostic — Builder / Crusader / Investor — 5 real questions, one point per matching answer, highest tally wins. Real questions and real archetype copy ported unchanged, reused from lib/content/archetypes.ts (already ported for /essays's archetype filter) rather than duplicated — added the page's ASSESSMENT_QUESTIONS to that same module since both come from the identical legacy source file. Preserved the real, distinct UX (no landing screen, no ThemedBackground/JourneyTracker — this page sits outside that ecosystem). Real bugs fixed: JS onMouseEnter/onMouseLeave inline-style hover hack replaced with Tailwind hover: classes; literal "..." pending-state text replaced with a real Loader2 spinner per house rule; dead trpc.subscribe.add replaced with a real POST /api/subscribe call. Real link audit: kept /impact-dashboard, /find-your-me, /living-declaration, and the real /blog/boiling-the-human-summit-harvard-kurzweil article as live links; /soulscore and /humanos are established forward-references used repeatedly elsewhere in this migration and both now ship too. The Human OS CTA reuses the border-red-800/30 text-red-800 treatment /living-declaration already established for the identical button instead of a new one-off raw-hex pair. AssessmentResultActions resultSlug="assessment" added (didn't exist when legacy was written). Added assessment-builder/as</t>
+          <t>composite of completed assessments. Decision made: local-only (a real cookie, not Supabase — Phase 2 isn't provisioned yet). AssessmentResultActions (components/assessments/result-actions.tsx) takes an optional resultSlug and logs completions to a tg_assessment_results cookie via lib/assessments/result-log.ts, the same real-cookie-read-via-next/headers pattern already established by returning-visitor-hero.tsx/track-last-blog-visit.tsx — the page itself is a Server Component reading that cookie with zero client hydration step. Real, deliberate scope cut, not a silent one: legacy's SelfPortrait.tsx combined each assessment's own per-dimension scores (16 separate localStorage keys) into one composite radar chart across 15 unified dimensions, gated behind "5+ completed." This migration's result log only ever records that an assessment was completed, not its actual scored answers — building the real composite radar would mean threading a second, much larger data channel through every quiz. Shipped the honest subset instead: a real completed-assessments list (title, real completion date, retake link) plus a real "X of N completed" count and a "Still to Explore" section for the rest, via a new lib/content/self-portrait-catalog.ts. Wired resultSlug into the 7 remaining older "Find Your X" quizzes that already call AssessmentResultActions but hadn't been threaded yet (spirit/therapy/religion/sake/coffee/peptide/me) — /self-portrait now tracks 13 real assessments total. /find-my's "Sel</t>
         </is>
       </c>
       <c r="E235" s="14" t="inlineStr">
@@ -6304,7 +6304,7 @@
       <c r="A236" s="4" t="n"/>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>Fix dead-end pages flagged in STATUS.md</t>
+          <t>/the-mirror (+ /life-assessment)</t>
         </is>
       </c>
       <c r="C236" s="13" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>sake, therapy, and love-language all got real next-step navigation (WhatsNext + real "Journey Continues" links) during their ports — the last remaining one, soulscore, is now built (see above), closing this out.</t>
+          <t>uses mirrorData.json, real 6-dimension/18-question life assessment ("The Mirror") ported into a typed lib/content/mirror-data.ts. Legacy served the identical component at both paths; /the-mirror is canonical (it's the only URL every existing internal link already pointed to — nav, journey tracker, Find Your Me), /life-assessment permanently redirects there. Real dimension-averaged scoring, radar chart via the shared AssessmentRadarChart, and weakest-dimension article/satellite-site recommendations ported unchanged. A live Sanity check found only 27 of 85 legacy article slugs still resolve; recommendations now resolve server-side and defensively skip missing ones, matching legacy's own behavior. Fixed: a hydration-unsafe typeof window branch computing the share URL, three stale manus.space satellite URLs superseded by their current live counterparts already used elsewhere in this migration, and dead /assessments/*/external-stub links in the "Journey Continues" grid. Added find-your-mirror to kit-source-tags.ts's KIT_TAG_MAP and reconciled journey-tracker.tsx's stale 10-minute estimate to legacy's real "~4 minutes" claim. find-your-me.ts's ecosystem-directory status flipped to "live." Verified live: 200 OK on both paths, redirect confirmed, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E236" s="14" t="inlineStr">
@@ -6327,7 +6327,7 @@
       <c r="A237" s="4" t="n"/>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Port shared radar-chart / PDF-export / email-gate components used across assessments</t>
+          <t>/assessment</t>
         </is>
       </c>
       <c r="C237" s="13" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>components/assessments/{radar-chart,result-actions,email-gate}.tsx, built during Phase 9 and reused unchanged by all 15 "Find Your X" quizzes plus /find-your-me.</t>
+          <t>confirmed via full legacy read this is not a "Find Your X" quiz (it predates that convention): it's Tony's own 3-way reader-path diagnostic — Builder / Crusader / Investor — 5 real questions, one point per matching answer, highest tally wins. Real questions and real archetype copy ported unchanged, reused from lib/content/archetypes.ts (already ported for /essays's archetype filter) rather than duplicated — added the page's ASSESSMENT_QUESTIONS to that same module since both come from the identical legacy source file. Preserved the real, distinct UX (no landing screen, no ThemedBackground/JourneyTracker — this page sits outside that ecosystem). Real bugs fixed: JS onMouseEnter/onMouseLeave inline-style hover hack replaced with Tailwind hover: classes; literal "..." pending-state text replaced with a real Loader2 spinner per house rule; dead trpc.subscribe.add replaced with a real POST /api/subscribe call. Real link audit: kept /impact-dashboard, /find-your-me, /living-declaration, and the real /blog/boiling-the-human-summit-harvard-kurzweil article as live links; /soulscore and /humanos are established forward-references used repeatedly elsewhere in this migration and both now ship too. The Human OS CTA reuses the border-red-800/30 text-red-800 treatment /living-declaration already established for the identical button instead of a new one-off raw-hex pair. AssessmentResultActions resultSlug="assessment" added (didn't exist when legacy was written). Added assessment-builder/as</t>
         </is>
       </c>
       <c r="E237" s="14" t="inlineStr">
@@ -6347,20 +6347,33 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="10" t="inlineStr">
-        <is>
-          <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
-        </is>
-      </c>
-      <c r="B238" s="11" t="n"/>
-      <c r="C238" s="11" t="n"/>
-      <c r="D238" s="12" t="n"/>
+      <c r="A238" s="4" t="n"/>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>Fix dead-end pages flagged in STATUS.md</t>
+        </is>
+      </c>
+      <c r="C238" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D238" s="4" t="inlineStr">
+        <is>
+          <t>sake, therapy, and love-language all got real next-step navigation (WhatsNext + real "Journey Continues" links) during their ports — the last remaining one, soulscore, is now built (see above), closing this out.</t>
+        </is>
+      </c>
+      <c r="E238" s="14" t="inlineStr">
+        <is>
+          <t>Phase 9 — Assessments (33 routes)</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="4" t="n"/>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>src/lib/admin/</t>
+          <t>Port shared radar-chart / PDF-export / email-gate components used across assessments</t>
         </is>
       </c>
       <c r="C239" s="13" t="inlineStr">
@@ -6370,43 +6383,30 @@
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>guardrails (fixes the removed version's proxy.ts pattern, which missed the real src/proxy.ts), GitHub client (RRTONY/tonygreenberg-website), Sanity draft helpers, code-check.ts (ESLint + CONTRIBUTING.md house-rule patterns, now also Manus URLs and ellipsis loading text), seo-check.ts, tools.ts, mcp-server.ts, mcp-handler.ts, mcp-tool-context.ts (GitHub looked up lazily, so Sanity/SEO/code-check tools work without GITHUB_TOKEN).</t>
+          <t>components/assessments/{radar-chart,result-actions,email-gate}.tsx, built during Phase 9 and reused unchanged by all 15 "Find Your X" quizzes plus /find-your-me.</t>
         </is>
       </c>
       <c r="E239" s="14" t="inlineStr">
         <is>
+          <t>Phase 9 — Assessments (33 routes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="10" t="inlineStr">
+        <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
         </is>
       </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="4" t="n"/>
-      <c r="B240" s="4" t="inlineStr">
-        <is>
-          <t>Per-person access via MCP_ADMIN_USERS (read/edit/write roles, tools filtered per role, calls logged, commits stamped [by &lt;name&gt;])</t>
-        </is>
-      </c>
-      <c r="C240" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D240" s="4" t="inlineStr">
-        <is>
-          <t>mcp-auth.ts.</t>
-        </is>
-      </c>
-      <c r="E240" s="14" t="inlineStr">
-        <is>
-          <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
-        </is>
-      </c>
+      <c r="B240" s="11" t="n"/>
+      <c r="C240" s="11" t="n"/>
+      <c r="D240" s="12" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="4" t="n"/>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Rules gate: get_project_rules serves CONTRIBUTING.md + AGENTS.md + docs/ai/ guides with a rulesVersion; all 6 write tools require it</t>
+          <t>src/lib/admin/</t>
         </is>
       </c>
       <c r="C241" s="13" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>project-rules.ts.</t>
+          <t>guardrails (fixes the removed version's proxy.ts pattern, which missed the real src/proxy.ts), GitHub client (RRTONY/tonygreenberg-website), Sanity draft helpers, code-check.ts (ESLint + CONTRIBUTING.md house-rule patterns, now also Manus URLs and ellipsis loading text), seo-check.ts, tools.ts, mcp-server.ts, mcp-handler.ts, mcp-tool-context.ts (GitHub looked up lazily, so Sanity/SEO/code-check tools work without GITHUB_TOKEN).</t>
         </is>
       </c>
       <c r="E241" s="14" t="inlineStr">
@@ -6429,7 +6429,7 @@
       <c r="A242" s="4" t="n"/>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>src/app/api/mcp/route.ts (header auth) + src/app/api/mcp/[token]/route.ts (token in URL).</t>
+          <t>Per-person access via MCP_ADMIN_USERS (read/edit/write roles, tools filtered per role, calls logged, commits stamped [by &lt;name&gt;])</t>
         </is>
       </c>
       <c r="C242" s="13" t="inlineStr">
@@ -6437,7 +6437,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D242" s="4" t="inlineStr"/>
+      <c r="D242" s="4" t="inlineStr">
+        <is>
+          <t>mcp-auth.ts.</t>
+        </is>
+      </c>
       <c r="E242" s="14" t="inlineStr">
         <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
@@ -6448,7 +6452,7 @@
       <c r="A243" s="4" t="n"/>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>docs/ai/ knowledge base (README, TASK_GUIDE, PROJECT_STRUCTURE, project_mcp_server), linked from CONTRIBUTING.md.</t>
+          <t>Rules gate: get_project_rules serves CONTRIBUTING.md + AGENTS.md + docs/ai/ guides with a rulesVersion; all 6 write tools require it</t>
         </is>
       </c>
       <c r="C243" s="13" t="inlineStr">
@@ -6456,7 +6460,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D243" s="4" t="inlineStr"/>
+      <c r="D243" s="4" t="inlineStr">
+        <is>
+          <t>project-rules.ts.</t>
+        </is>
+      </c>
       <c r="E243" s="14" t="inlineStr">
         <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
@@ -6467,7 +6475,7 @@
       <c r="A244" s="4" t="n"/>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>@modelcontextprotocol/sdk ^1.30.0 re-added (approved 2026-09-29); GITHUB_TOKEN/MCP_ADMIN_USERS/MCP_SITE_ORIGIN documented in .env.local.example.</t>
+          <t>src/app/api/mcp/route.ts (header auth) + src/app/api/mcp/[token]/route.ts (token in URL).</t>
         </is>
       </c>
       <c r="C244" s="13" t="inlineStr">
@@ -6486,7 +6494,7 @@
       <c r="A245" s="4" t="n"/>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Verified locally</t>
+          <t>docs/ai/ knowledge base (README, TASK_GUIDE, PROJECT_STRUCTURE, project_mcp_server), linked from CONTRIBUTING.md.</t>
         </is>
       </c>
       <c r="C245" s="13" t="inlineStr">
@@ -6494,11 +6502,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D245" s="4" t="inlineStr">
-        <is>
-          <t>auth (401/405), role filtering, rules-gate markers, token-in-URL route, code check, Sanity query, SEO check.</t>
-        </is>
-      </c>
+      <c r="D245" s="4" t="inlineStr"/>
       <c r="E245" s="14" t="inlineStr">
         <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
@@ -6509,7 +6513,7 @@
       <c r="A246" s="4" t="n"/>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>Sign-in for the MCP server (OAuth 2.1, ported from ramprate-ui, 2026-09-30)</t>
+          <t>@modelcontextprotocol/sdk ^1.30.0 re-added (approved 2026-09-29); GITHUB_TOKEN/MCP_ADMIN_USERS/MCP_SITE_ORIGIN documented in .env.local.example.</t>
         </is>
       </c>
       <c r="C246" s="13" t="inlineStr">
@@ -6517,11 +6521,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D246" s="4" t="inlineStr">
-        <is>
-          <t>/oauth/authorize sign-in page + /.well-known metadata + register/authorize/token endpoints, stateless (signed tokens, no database), no new dependency. Verified end to end on a local production build. See docs/ai/project_mcp_server.md.</t>
-        </is>
-      </c>
+      <c r="D246" s="4" t="inlineStr"/>
       <c r="E246" s="14" t="inlineStr">
         <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
@@ -6532,17 +6532,17 @@
       <c r="A247" s="4" t="n"/>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Set GITHUB_TOKEN, MCP_ADMIN_USERS, MCP_LOGIN_PASSWORD, MCP_OAUTH_SECRET, MCP_SITE_ORIGIN, MCP_PUBLIC_ORIGIN in Netlify (done) (checked 2026-…</t>
-        </is>
-      </c>
-      <c r="C247" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Verified locally</t>
+        </is>
+      </c>
+      <c r="C247" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>10-07: all already set in Netlify). Left: connect Claude.ai to /api/mcp for real, and verify the GitHub flow end to end (branch → PR → deploy preview → publish_changes) against a real PR.</t>
+          <t>auth (401/405), role filtering, rules-gate markers, token-in-URL route, code check, Sanity query, SEO check.</t>
         </is>
       </c>
       <c r="E247" s="14" t="inlineStr">
@@ -6555,15 +6555,19 @@
       <c r="A248" s="4" t="n"/>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>Commit a team-wide .mcp.json (URL only) once the production URL is settled.</t>
-        </is>
-      </c>
-      <c r="C248" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D248" s="4" t="inlineStr"/>
+          <t>Sign-in for the MCP server (OAuth 2.1, ported from ramprate-ui, 2026-09-30)</t>
+        </is>
+      </c>
+      <c r="C248" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="inlineStr">
+        <is>
+          <t>/oauth/authorize sign-in page + /.well-known metadata + register/authorize/token endpoints, stateless (signed tokens, no database), no new dependency. Verified end to end on a local production build. See docs/ai/project_mcp_server.md.</t>
+        </is>
+      </c>
       <c r="E248" s="14" t="inlineStr">
         <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
@@ -6574,17 +6578,17 @@
       <c r="A249" s="4" t="n"/>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Google read-only tools added (2026-10-02)</t>
-        </is>
-      </c>
-      <c r="C249" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Set GITHUB_TOKEN, MCP_ADMIN_USERS, MCP_LOGIN_PASSWORD, MCP_OAUTH_SECRET, MCP_SITE_ORIGIN, MCP_PUBLIC_ORIGIN in Netlify (done) (checked 2026-…</t>
+        </is>
+      </c>
+      <c r="C249" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>check_analytics (GA4), search_console_sites / _performance / _inspect_url / _sitemaps (list only, no submit or delete), lighthouse_check_page (PageSpeed Insights). New files google-auth.ts, ga4-client.ts, gsc-client.ts, lighthouse-check.ts; no new dependency. Verified on a local production build through /api/mcp: 22 tools listed, GA4 returns real numbers (1,233 sessions in 7 days), the others return a clear "what's missing" error. Env vars added to .env.local.example.</t>
+          <t>10-07: all already set in Netlify). Left: connect Claude.ai to /api/mcp for real, and verify the GitHub flow end to end (branch → PR → deploy preview → publish_changes) against a real PR.</t>
         </is>
       </c>
       <c r="E249" s="14" t="inlineStr">
@@ -6597,19 +6601,15 @@
       <c r="A250" s="4" t="n"/>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>publish_changes fixed (2026-10-02)</t>
-        </is>
-      </c>
-      <c r="C250" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D250" s="4" t="inlineStr">
-        <is>
-          <t>it published every draft in Sanity (31 waiting for review today), so any one-line fix would have pushed them all live. Now it publishes only the drafts named in draft_ids; unknown ids are refused before anything happens (verified).</t>
-        </is>
-      </c>
+          <t>Commit a team-wide .mcp.json (URL only) once the production URL is settled.</t>
+        </is>
+      </c>
+      <c r="C250" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="D250" s="4" t="inlineStr"/>
       <c r="E250" s="14" t="inlineStr">
         <is>
           <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
@@ -6620,7 +6620,7 @@
       <c r="A251" s="4" t="n"/>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>seo_check_page decoded &amp;#39; but not React's &amp;#x27;, so descriptions showed Tony Greenberg&amp;#x27;s and the length was off</t>
+          <t>Google read-only tools added (2026-10-02)</t>
         </is>
       </c>
       <c r="C251" s="13" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>Fixed and verified (2026-10-02).</t>
+          <t>check_analytics (GA4), search_console_sites / _performance / _inspect_url / _sitemaps (list only, no submit or delete), lighthouse_check_page (PageSpeed Insights). New files google-auth.ts, ga4-client.ts, gsc-client.ts, lighthouse-check.ts; no new dependency. Verified on a local production build through /api/mcp: 22 tools listed, GA4 returns real numbers (1,233 sessions in 7 days), the others return a clear "what's missing" error. Env vars added to .env.local.example.</t>
         </is>
       </c>
       <c r="E251" s="14" t="inlineStr">
@@ -6643,7 +6643,7 @@
       <c r="A252" s="4" t="n"/>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>Search Console access for the service account added by the team (2026-10-02); all four search_console_* tools verified with real tonygreenbe…</t>
+          <t>publish_changes fixed (2026-10-02)</t>
         </is>
       </c>
       <c r="C252" s="13" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>rg.com data (99 clicks / 1,663 impressions in 28 days, homepage indexed, sitemap 284 URLs, 0 errors, 82 warnings).</t>
+          <t>it published every draft in Sanity (31 waiting for review today), so any one-line fix would have pushed them all live. Now it publishes only the drafts named in draft_ids; unknown ids are refused before anything happens (verified).</t>
         </is>
       </c>
       <c r="E252" s="14" t="inlineStr">
@@ -6666,7 +6666,7 @@
       <c r="A253" s="4" t="n"/>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>GOOGLE_GA_CLIENT_EMAIL, GOOGLE_GA_PRIVATE_KEY, GA4_PROPERTY_ID_TONYGREENBERG set in Netlify (2026-10-02, via the Netlify API, values checked…</t>
+          <t>seo_check_page decoded &amp;#39; but not React's &amp;#x27;, so descriptions showed Tony Greenberg&amp;#x27;s and the length was off</t>
         </is>
       </c>
       <c r="C253" s="13" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> equal to .env.local; this plan can't limit a variable's scopes, so they're available to builds and functions). Used from the next deploy.</t>
+          <t>Fixed and verified (2026-10-02).</t>
         </is>
       </c>
       <c r="E253" s="14" t="inlineStr">
@@ -6689,7 +6689,7 @@
       <c r="A254" s="4" t="n"/>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>Per-request change system ported from ramprate-ui (2026-10-02, owner said yes)</t>
+          <t>Search Console access for the service account added by the team (2026-10-02); all four search_console_* tools verified with real tonygreenbe…</t>
         </is>
       </c>
       <c r="C254" s="13" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>, covering the 10 review points the team raised for RampRate's setup: (1) discard_change; (2) one request = one change with its own branch, PR and drafts, so publishing never takes another request live; (3) a review with pages affected, a server-written "what's included" line and preview links; (4) publish needs the review's reviewToken, and the rules make the AI ask "You are about to publish these changes to the live tonygreenberg.com website. Are you sure you want to continue?"; (5) list_change_history, also visible read-only in Studio under "Website change history" (new adminChange type); (6) undo_change; (7) before/after (automatic for Sanity, given by the AI for code); (8) preview_on_devices phone + laptop screenshots (needs GOOGLE_API_KEY); (9) the AI's plain summary plus the server's facts line; (10) Draft → Ready for review → Published / Discarded. Files: change-sets.ts, change-describe.ts, device-preview.ts, mcp-tool-context.ts, mcp-server.ts, github-client.ts (RampRate's full version), src/sanity/schemas/adminChange.ts, sanity.config.ts. Tested end to end with a real throwaway change, then discarded (see docs/ai/project_mcp_server.md).</t>
+          <t>rg.com data (99 clicks / 1,663 impressions in 28 days, homepage indexed, sitemap 284 URLs, 0 errors, 82 warnings).</t>
         </is>
       </c>
       <c r="E254" s="14" t="inlineStr">
@@ -6712,7 +6712,7 @@
       <c r="A255" s="4" t="n"/>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Merge the CI fix into main</t>
+          <t>GOOGLE_GA_CLIENT_EMAIL, GOOGLE_GA_PRIVATE_KEY, GA4_PROPERTY_ID_TONYGREENBERG set in Netlify (2026-10-02, via the Netlify API, values checked…</t>
         </is>
       </c>
       <c r="C255" s="13" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>(done with PR #3; checked 2026-10-06: main's pr-lint.yml runs Node 22 and next typegen before the type check). The test change's GitHub check failed because main still has the old pr-lint.yml (Node 20 crash). Every MCP change will fail its site check, and so can't be published, until this branch's work (or at least .github/workflows/pr-lint.yml) is on main. Then test a real publish and undo_change.</t>
+          <t xml:space="preserve"> equal to .env.local; this plan can't limit a variable's scopes, so they're available to builds and functions). Used from the next deploy.</t>
         </is>
       </c>
       <c r="E255" s="14" t="inlineStr">
@@ -6735,17 +6735,17 @@
       <c r="A256" s="4" t="n"/>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Blocked on you (Google)</t>
-        </is>
-      </c>
-      <c r="C256" s="15" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+          <t>Per-request change system ported from ramprate-ui (2026-10-02, owner said yes)</t>
+        </is>
+      </c>
+      <c r="C256" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>create a GOOGLE_API_KEY in Google Cloud (project of the vcos-ga4-reader service account, where the PageSpeed Insights API is already on), restricted to the PageSpeed Insights API, then add it to .env.local and Netlify. Creating it from here was blocked by the session's safety check (it would use the service account's credentials to change the Cloud project). Note lighthouse_check_page may time out on Netlify (10 s function limit on the free plan).</t>
+          <t>, covering the 10 review points the team raised for RampRate's setup: (1) discard_change; (2) one request = one change with its own branch, PR and drafts, so publishing never takes another request live; (3) a review with pages affected, a server-written "what's included" line and preview links; (4) publish needs the review's reviewToken, and the rules make the AI ask "You are about to publish these changes to the live tonygreenberg.com website. Are you sure you want to continue?"; (5) list_change_history, also visible read-only in Studio under "Website change history" (new adminChange type); (6) undo_change; (7) before/after (automatic for Sanity, given by the AI for code); (8) preview_on_devices phone + laptop screenshots (needs GOOGLE_API_KEY); (9) the AI's plain summary plus the server's facts line; (10) Draft → Ready for review → Published / Discarded. Files: change-sets.ts, change-describe.ts, device-preview.ts, mcp-tool-context.ts, mcp-server.ts, github-client.ts (RampRate's full version), src/sanity/schemas/adminChange.ts, sanity.config.ts. Tested end to end with a real throwaway change, then discarded (see docs/ai/project_mcp_server.md).</t>
         </is>
       </c>
       <c r="E256" s="14" t="inlineStr">
@@ -6758,7 +6758,7 @@
       <c r="A257" s="4" t="n"/>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Synced with ramprate-ui's MCP server (2026-10-09, owner asked; card included by their choice)</t>
+          <t>Merge the CI fix into main</t>
         </is>
       </c>
       <c r="C257" s="13" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>the review card for ChatGPT/Claude (one status and next step, Build / Type check / Lint / GitHub / phone-and-laptop checks, "what goes live" and what doesn't, Preview / Discard / Publish / Retry, history with Restore); start_change restates the request (understood_as) and unclear ones wait for the person's OK (confirm_change); before (live) / after (preview) screenshots on phone and laptop; attached images and files (ChatGPT file, or request_upload_link, a private 30-minute upload page at /api/mcp/upload, size and real-type checked); every change result lists the other waiting changes and the AI ends its reply with them (new Status Report line); the server lints changed files itself; ESLint now traced into the deployed function (serverExternalPackages; ramprate's tracing globs crash Turbopack under pnpm, left out). Everything named for tonygreenberg.com only (Netlify tonygreenberg-website, live tonygreenberg.com, card ui://tonygreenberg-admin/...). Verified on a local production build: type check, lint, build; 30 tools listed; card served and its script valid; rules include migrationStatus; list_pending_changes returns other pending changes; check_code_quality runs ESLint; upload page refuses bad links (401). See docs/ai/project_mcp_server.md.</t>
+          <t>(done with PR #3; checked 2026-10-06: main's pr-lint.yml runs Node 22 and next typegen before the type check). The test change's GitHub check failed because main still has the old pr-lint.yml (Node 20 crash). Every MCP change will fail its site check, and so can't be published, until this branch's work (or at least .github/workflows/pr-lint.yml) is on main. Then test a real publish and undo_change.</t>
         </is>
       </c>
       <c r="E257" s="14" t="inlineStr">
@@ -6781,7 +6781,7 @@
       <c r="A258" s="4" t="n"/>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>Test the new review end to end on a deploy preview</t>
+          <t>Blocked on you (Google)</t>
         </is>
       </c>
       <c r="C258" s="15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>(needs a yes, it opens a real pull request): one throwaway change from Claude.ai or ChatGPT: start (unclear request, so the confirm step shows), confirm, edit, review card, screenshots, upload link, then discard.</t>
+          <t>create a GOOGLE_API_KEY in Google Cloud (project of the vcos-ga4-reader service account, where the PageSpeed Insights API is already on), restricted to the PageSpeed Insights API, then add it to .env.local and Netlify. Creating it from here was blocked by the session's safety check (it would use the service account's credentials to change the Cloud project). Note lighthouse_check_page may time out on Netlify (10 s function limit on the free plan).</t>
         </is>
       </c>
       <c r="E258" s="14" t="inlineStr">
@@ -6801,66 +6801,66 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="10" t="inlineStr">
-        <is>
-          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
-        </is>
-      </c>
-      <c r="B259" s="11" t="n"/>
-      <c r="C259" s="11" t="n"/>
-      <c r="D259" s="12" t="n"/>
+      <c r="A259" s="4" t="n"/>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>Synced with ramprate-ui's MCP server (2026-10-09, owner asked; card included by their choice)</t>
+        </is>
+      </c>
+      <c r="C259" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D259" s="4" t="inlineStr">
+        <is>
+          <t>the review card for ChatGPT/Claude (one status and next step, Build / Type check / Lint / GitHub / phone-and-laptop checks, "what goes live" and what doesn't, Preview / Discard / Publish / Retry, history with Restore); start_change restates the request (understood_as) and unclear ones wait for the person's OK (confirm_change); before (live) / after (preview) screenshots on phone and laptop; attached images and files (ChatGPT file, or request_upload_link, a private 30-minute upload page at /api/mcp/upload, size and real-type checked); every change result lists the other waiting changes and the AI ends its reply with them (new Status Report line); the server lints changed files itself; ESLint now traced into the deployed function (serverExternalPackages; ramprate's tracing globs crash Turbopack under pnpm, left out). Everything named for tonygreenberg.com only (Netlify tonygreenberg-website, live tonygreenberg.com, card ui://tonygreenberg-admin/...). Verified on a local production build: type check, lint, build; 30 tools listed; card served and its script valid; rules include migrationStatus; list_pending_changes returns other pending changes; check_code_quality runs ESLint; upload page refuses bad links (401). See docs/ai/project_mcp_server.md.</t>
+        </is>
+      </c>
+      <c r="E259" s="14" t="inlineStr">
+        <is>
+          <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="4" t="n"/>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>Per-page generateMetadata (title, description, OG, Twitter Card, canonical) for every ported route, sourced from Sanity seo object where con…</t>
-        </is>
-      </c>
-      <c r="C260" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Test the new review end to end on a deploy preview</t>
+        </is>
+      </c>
+      <c r="C260" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>tent is CMS-backed, static otherwise. Audited all 140 page.tsx files: only /studio has none (correct — it's robots.txt-disallowed, not public content). Real gap found and fixed: /blog/category/[slug] had no alternates.canonical at all, and no page-aware title for its own real pagination (?page=N) — every paginated page was serving an identical title with no canonical, a real duplicate-content signal. Fixed: generateMetadata now reads searchParams too, self-canonicals each page (?page=N pages canonical to themselves, not consolidated to page 1 — genuinely different posts per page, matching Google's current pagination guidance) and appends "— Page N" to the title past page 1. Verified live: page 1 canonicals to the bare URL, ?page=2 canonicals to ?page=2 with a distinct title.</t>
+          <t>(needs a yes, it opens a real pull request): one throwaway change from Claude.ai or ChatGPT: start (unclear request, so the confirm step shows), confirm, edit, review card, screenshots, upload link, then discard.</t>
         </is>
       </c>
       <c r="E260" s="14" t="inlineStr">
         <is>
+          <t>Phase 11 — Code MCP Server — REBUILT (2026-09-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="10" t="inlineStr">
+        <is>
           <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
         </is>
       </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="4" t="n"/>
-      <c r="B261" s="4" t="inlineStr">
-        <is>
-          <t>sitemap.ts generated from real Sanity content + static route list, auto-updates on publish</t>
-        </is>
-      </c>
-      <c r="C261" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D261" s="4" t="inlineStr">
-        <is>
-          <t>Extended from the Phase 5-era version (homepage + blog posts only, 122 URLs) to every real route: the full static route list (130 routes, generated from find src/app -name page.tsx, excluding /studio (robots.txt-disallowed), /(auth)/login (noindex via its own metadata), and /life-assessment (a pure redirect, not distinct content)) plus all 5 real dynamic sources — blog categories (allCategorySlugsQuery), BrewSoul cities (25), BrewSoul coffees (107), and charity-scorecard entries (103) — each pulled from the exact same data source its own page's generateStaticParams already uses, not re-derived. Auto-updates on publish for anything Sanity-backed (blog posts/categories) since it's a live client.fetch on every build; the static route list itself needs a one-line addition whenever a new page ships (same as any other route-registration step). Verified live: 496 real &lt;loc&gt; entries, spot-checked a coffee/city/charity/category URL each, typecheck/lint clean.</t>
-        </is>
-      </c>
-      <c r="E261" s="14" t="inlineStr">
-        <is>
-          <t>Phase 12 — SEO Hardening, Redirects &amp; Cutover Prep</t>
-        </is>
-      </c>
+      <c r="B261" s="11" t="n"/>
+      <c r="C261" s="11" t="n"/>
+      <c r="D261" s="12" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="4" t="n"/>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>llms.txt</t>
+          <t>Per-page generateMetadata (title, description, OG, Twitter Card, canonical) for every ported route, sourced from Sanity seo object where con…</t>
         </is>
       </c>
       <c r="C262" s="13" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>fetched verbatim from the still-live site and saved to web/public/llms.txt (real content: Tony's bio, expertise, full article index by category, every product/tool section) — do this before Manus goes away, it won't be recoverable after</t>
+          <t>tent is CMS-backed, static otherwise. Audited all 140 page.tsx files: only /studio has none (correct — it's robots.txt-disallowed, not public content). Real gap found and fixed: /blog/category/[slug] had no alternates.canonical at all, and no page-aware title for its own real pagination (?page=N) — every paginated page was serving an identical title with no canonical, a real duplicate-content signal. Fixed: generateMetadata now reads searchParams too, self-canonicals each page (?page=N pages canonical to themselves, not consolidated to page 1 — genuinely different posts per page, matching Google's current pagination guidance) and appends "— Page N" to the title past page 1. Verified live: page 1 canonicals to the bare URL, ?page=2 canonicals to ?page=2 with a distinct title.</t>
         </is>
       </c>
       <c r="E262" s="14" t="inlineStr">
@@ -6883,7 +6883,7 @@
       <c r="A263" s="4" t="n"/>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>robots.txt</t>
+          <t>sitemap.ts generated from real Sanity content + static route list, auto-updates on publish</t>
         </is>
       </c>
       <c r="C263" s="13" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>same approach: fetched the real live file (not my earlier guessed robots.ts, which has been removed) and saved verbatim to web/public/robots.txt, plus added Disallow: /studio for the new Sanity Studio route. Confirmed live: real AI-crawler allowlist (GPTBot, Claude-Web, PerplexityBot, etc.), scraper blocklist, and the site's non-standard LLMs: directive all intact</t>
+          <t>Extended from the Phase 5-era version (homepage + blog posts only, 122 URLs) to every real route: the full static route list (130 routes, generated from find src/app -name page.tsx, excluding /studio (robots.txt-disallowed), /(auth)/login (noindex via its own metadata), and /life-assessment (a pure redirect, not distinct content)) plus all 5 real dynamic sources — blog categories (allCategorySlugsQuery), BrewSoul cities (25), BrewSoul coffees (107), and charity-scorecard entries (103) — each pulled from the exact same data source its own page's generateStaticParams already uses, not re-derived. Auto-updates on publish for anything Sanity-backed (blog posts/categories) since it's a live client.fetch on every build; the static route list itself needs a one-line addition whenever a new page ships (same as any other route-registration step). Verified live: 496 real &lt;loc&gt; entries, spot-checked a coffee/city/charity/category URL each, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E263" s="14" t="inlineStr">
@@ -6906,7 +6906,7 @@
       <c r="A264" s="4" t="n"/>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>JSON-LD</t>
+          <t>llms.txt</t>
         </is>
       </c>
       <c r="C264" s="13" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>WebSite + Person schema ported verbatim from the live homepage's actual &lt;script type="application/ld+json"&gt; tags (not reconstructed from memory) — rendered site-wide from src/lib/structured-data.ts in the root layout. The Person image was hardcoded to a /api/img/... legacy proxy path on the live site — rescued that headshot (downloaded it while still live, uploaded to Sanity as the author-tony-greenberg document's avatar) so the new site's JSON-LD has zero Manus dependency instead of just copying the fragile path forward</t>
+          <t>fetched verbatim from the still-live site and saved to web/public/llms.txt (real content: Tony's bio, expertise, full article index by category, every product/tool section) — do this before Manus goes away, it won't be recoverable after</t>
         </is>
       </c>
       <c r="E264" s="14" t="inlineStr">
@@ -6929,7 +6929,7 @@
       <c r="A265" s="4" t="n"/>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Article JSON-LD on /blog/[slug], built from real per-post Sanity data (headline, image, datePublished/dateModified, author, canonical URL)</t>
+          <t>robots.txt</t>
         </is>
       </c>
       <c r="C265" s="13" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>verified live on a real post</t>
+          <t>same approach: fetched the real live file (not my earlier guessed robots.ts, which has been removed) and saved verbatim to web/public/robots.txt, plus added Disallow: /studio for the new Sanity Studio route. Confirmed live: real AI-crawler allowlist (GPTBot, Claude-Web, PerplexityBot, etc.), scraper blocklist, and the site's non-standard LLMs: directive all intact</t>
         </is>
       </c>
       <c r="E265" s="14" t="inlineStr">
@@ -6952,7 +6952,7 @@
       <c r="A266" s="4" t="n"/>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>Build the full Manus/legacy-URL → Next.js-URL 301 redirect map (next.config.ts redirects() or Sanity redirect documents)</t>
+          <t>JSON-LD</t>
         </is>
       </c>
       <c r="C266" s="13" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>hard QA gate, nothing proceeds to DNS cutover until this is complete and tested. First real pass done: extracted all 197 real path= routes from legacy's App.tsx router (not guessed — the actual route table), diffed against this app's real current routes (find src/app -maxdepth 1 -name page.tsx) + next.config.ts's existing redirect sources, normalizing :param/[param] syntax to compare like-for-like. Started at 41 real gaps, closed 10 with new redirects: /attention-theft/{blocker-finder,legal,report,weapons} (legacy registered both a bare AND a /attention-theft/-nested path for each, only the bare ones had redirects before), /find-my-car → /find-my, /the-index → /search (matching the fix already applied to other pages' dead links to it), /supplier-intake-long (bare) + /vendor-intake + /vendor-intake-long (+/:token) → the same real ramprate.com/biochain/supplier-intake destination the token'd path already redirected to, and /spamtoast + /youve-been-reported → / (the live half of legacy's "report a spammer" confrontation flow — a fake IP-fingerprinting/countdown-timer page; the other half, ReportSpammer.tsx, was already a documented drop in Phase 4, this is the same call for its sequel). 21 of the remaining 31 gaps need no redirect — they're /admin/*//analytics//edit/frqncy (internal tools never meant for public discovery) or already-documented intentional defers from Phase 4/7/10 (/clock-keeper-part-2, /ecosystem-map, /friend-gate, /friend-survey/:token, /medicine-sequencing, /m</t>
+          <t>WebSite + Person schema ported verbatim from the live homepage's actual &lt;script type="application/ld+json"&gt; tags (not reconstructed from memory) — rendered site-wide from src/lib/structured-data.ts in the root layout. The Person image was hardcoded to a /api/img/... legacy proxy path on the live site — rescued that headshot (downloaded it while still live, uploaded to Sanity as the author-tony-greenberg document's avatar) so the new site's JSON-LD has zero Manus dependency instead of just copying the fragile path forward</t>
         </is>
       </c>
       <c r="E266" s="14" t="inlineStr">
@@ -6975,7 +6975,7 @@
       <c r="A267" s="4" t="n"/>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>/path/:archetype (src/app/path/[archetype]/page.tsx)</t>
+          <t>Article JSON-LD on /blog/[slug], built from real per-post Sanity data (headline, image, datePublished/dateModified, author, canonical URL)</t>
         </is>
       </c>
       <c r="C267" s="13" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>per-archetype landing page for /assessment's Builder/Crusader/Investor result, reusing lib/content/archetypes.ts. Real content ported in full (top-5 essential-reading list per archetype via allPostsForArchiveQuery, real PathSubscribeForm posting to /api/subscribe, AUTHORITY_ITEMS strip). Real bug fixed vs. legacy: replaced a hand-rolled inline-styled "Path not found" div with a real notFound() (this route's generateStaticParams only ever produces the 3 real keys). Verified live: all 3 archetype routes 200 OK, typecheck/lint clean.</t>
+          <t>verified live on a real post</t>
         </is>
       </c>
       <c r="E267" s="14" t="inlineStr">
@@ -6998,7 +6998,7 @@
       <c r="A268" s="4" t="n"/>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>/my-journey (src/app/my-journey/page.tsx + components/assessments/my-journey-dashboard.tsx)</t>
+          <t>Build the full Manus/legacy-URL → Next.js-URL 301 redirect map (next.config.ts redirects() or Sanity redirect documents)</t>
         </is>
       </c>
       <c r="C268" s="13" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>"My Journey Dashboard," real grid/timeline views across all 28 JOURNEY_MAP experiences, category/status filters, phase progress ring, recommended-next card, using the same real useJourneyProgress/JOURNEY_MAP completion tracking every "Find Your X" quiz already writes to (not the narrower tg_assessment_results cookie built for /self-portrait). Legacy's per-quiz scored-result caching (RESULT_KEYS, feeding a mini radar chart) was not ported — no quiz in this migration writes that data either, same honest-degradation call already made for /self-portrait's own composite radar. Fixed a real legacy dead link (/ecosystem-map, a still-unbuilt page) to /self-portrait. Verified live: 200 OK, real content confirmed, typecheck/lint clean.</t>
+          <t>hard QA gate, nothing proceeds to DNS cutover until this is complete and tested. First real pass done: extracted all 197 real path= routes from legacy's App.tsx router (not guessed — the actual route table), diffed against this app's real current routes (find src/app -maxdepth 1 -name page.tsx) + next.config.ts's existing redirect sources, normalizing :param/[param] syntax to compare like-for-like. Started at 41 real gaps, closed 10 with new redirects: /attention-theft/{blocker-finder,legal,report,weapons} (legacy registered both a bare AND a /attention-theft/-nested path for each, only the bare ones had redirects before), /find-my-car → /find-my, /the-index → /search (matching the fix already applied to other pages' dead links to it), /supplier-intake-long (bare) + /vendor-intake + /vendor-intake-long (+/:token) → the same real ramprate.com/biochain/supplier-intake destination the token'd path already redirected to, and /spamtoast + /youve-been-reported → / (the live half of legacy's "report a spammer" confrontation flow — a fake IP-fingerprinting/countdown-timer page; the other half, ReportSpammer.tsx, was already a documented drop in Phase 4, this is the same call for its sequel). 21 of the remaining 31 gaps need no redirect — they're /admin/*//analytics//edit/frqncy (internal tools never meant for public discovery) or already-documented intentional defers from Phase 4/7/10 (/clock-keeper-part-2, /ecosystem-map, /friend-gate, /friend-survey/:token, /medicine-sequencing, /m</t>
         </is>
       </c>
       <c r="E268" s="14" t="inlineStr">
@@ -7021,7 +7021,7 @@
       <c r="A269" s="4" t="n"/>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>/the-open-door (src/app/the-open-door/page.tsx)</t>
+          <t>/path/:archetype (src/app/path/[archetype]/page.tsx)</t>
         </is>
       </c>
       <c r="C269" s="13" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>real press/credibility content: all 10 "Magic Genie" client-pitch prompts (real named targets — Marco Argenti/Goldman Sachs, Adam Smith/Disney, etc.), 18 real client testimonials, all 8 explicitly-labeled satirical "parody" quotes (kept with disclaimers, not presented as real). Real overlap found and reconciled: this page's publications/speaking/podcasts arrays substantially duplicate the already-shipped /published's fuller bibliography — kept only what /published doesn't cover (Forbes + Business Insider bylines, the Clinton Global Initiative keynote, 4 of 5 podcast appearances) and cross-linked to /published for the rest, same reconciliation pattern as /assessments vs /find-my. Real bugs fixed: 3 genie/keynote links pointed externally at tonygreenberg.com/&lt;slug&gt; for posts that are real internal posts in this migration — relinked to /blog/psychedelics-could-become-extractive-capitalism, /blog/boiling-the-human-summit-harvard-kurzweil, /blog/return-on-investment-going-green-going-green-2 (all verified 200); a bare self-link to tonygreenberg.com remapped to /. Ships as a pure Server Component (legacy's FadeIn/Section/editorial-component dependencies don't exist here and weren't needed). Verified live: 200 OK, real content in raw SSR HTML, typecheck/lint clean.</t>
+          <t>per-archetype landing page for /assessment's Builder/Crusader/Investor result, reusing lib/content/archetypes.ts. Real content ported in full (top-5 essential-reading list per archetype via allPostsForArchiveQuery, real PathSubscribeForm posting to /api/subscribe, AUTHORITY_ITEMS strip). Real bug fixed vs. legacy: replaced a hand-rolled inline-styled "Path not found" div with a real notFound() (this route's generateStaticParams only ever produces the 3 real keys). Verified live: all 3 archetype routes 200 OK, typecheck/lint clean.</t>
         </is>
       </c>
       <c r="E269" s="14" t="inlineStr">
@@ -7044,7 +7044,7 @@
       <c r="A270" s="4" t="n"/>
       <c r="B270" s="4" t="inli